--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -987,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5599,12 +5599,12 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>CMD_MERIT</t>
         </is>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
-          <t>A COMMANDER COMPLETES THEIR FIRST TASK</t>
+          <t>FIELD PROMOTION: [COMMANDER_NAME] DISTINGUISHED IN EARLY OPERATIONS</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="G74" s="31" t="inlineStr">
         <is>
-          <t>→ CMD_REUNION (arc conclusion)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
@@ -5627,11 +5627,7 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
-        <is>
-          <t>commander_obj1</t>
-        </is>
-      </c>
+      <c r="I74" s="30" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -5650,7 +5646,7 @@
       </c>
       <c r="N74" s="31" t="inlineStr">
         <is>
-          <t>commander_objective type; non-repeatable; [COMMANDER_NAME] substitution</t>
+          <t>Fires at governorLevel==1 after 5 turns stationed; promote_commander BTN1; morale_boost BTN2</t>
         </is>
       </c>
     </row>
@@ -5667,148 +5663,140 @@
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>CMD_REUNION</t>
+          <t>CMD_RECOGNITION</t>
         </is>
       </c>
       <c r="D75" s="31" t="inlineStr">
         <is>
-          <t>THE REUNION</t>
-        </is>
-      </c>
-      <c r="E75" s="22" t="inlineStr">
+          <t>CITATION FOR EXCEPTIONAL SERVICE: [COMMANDER_NAME] AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>CMD_MERIT</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr"/>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>Fires at governorLevel==2 after 20 turns stationed; promote_commander BTN1; claim_change BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>Commander Arc</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>CMD_THANKS</t>
+        </is>
+      </c>
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMMANDER_NAME] AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>CMD_OBJECTIVE_1</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I75" s="30" t="inlineStr">
-        <is>
-          <t>commander_reunion</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K75" s="26" t="inlineStr">
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>CMD_RECOGNITION</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K76" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>commander_reunion type; explicit gated; non-repeatable</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="8" customHeight="1">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="9" t="n"/>
-      <c r="C76" s="9" t="n"/>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
-      <c r="H76" s="9" t="n"/>
-      <c r="I76" s="9" t="n"/>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
-      <c r="L76" s="9" t="n"/>
-      <c r="M76" s="9" t="n"/>
-      <c r="N76" s="9" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="33" t="inlineStr">
-        <is>
-          <t>Fort Chain</t>
-        </is>
-      </c>
-      <c r="B77" s="33" t="inlineStr">
-        <is>
-          <t>Fort Disrepair</t>
-        </is>
-      </c>
-      <c r="C77" s="34" t="inlineStr">
-        <is>
-          <t>FORT_001</t>
-        </is>
-      </c>
-      <c r="D77" s="35" t="inlineStr">
-        <is>
-          <t>FORT [TILE_NAME]: STRUCTURAL CONCERNS AND A PAMPHLET PROBLEM</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="35" t="inlineStr">
-        <is>
-          <t>→ FORT_003 (BTN1) | → FORT_004 (BTN2)</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I77" s="34" t="inlineStr">
-        <is>
-          <t>fort_pamphlets</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K77" s="36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L77" s="34" t="inlineStr"/>
-      <c r="M77" s="36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N77" s="35" t="inlineStr">
-        <is>
-          <t>Fires at Fortress tiles; requires governor + no fortDisrepair; army station required</t>
-        </is>
-      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>Fires at governorLevel==3 after 50 turns stationed; BTN2 explicit morale_boost +40; non-repeatable</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="n"/>
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
+      <c r="N77" s="9" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="33" t="inlineStr">
@@ -5823,27 +5811,27 @@
       </c>
       <c r="C78" s="34" t="inlineStr">
         <is>
-          <t>FORT_003</t>
+          <t>FORT_001</t>
         </is>
       </c>
       <c r="D78" s="35" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE FIRES [COMMANDER_NAME] IN FRONT OF GOD AND THE GARRISON</t>
-        </is>
-      </c>
-      <c r="E78" s="28" t="inlineStr">
-        <is>
-          <t>Branch</t>
+          <t>FORT [TILE_NAME]: STRUCTURAL CONCERNS AND A PAMPHLET PROBLEM</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F78" s="35" t="inlineStr">
         <is>
-          <t>FORT_001 BTN1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ FORT_003 (BTN1) | → FORT_004 (BTN2)</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -5853,7 +5841,7 @@
       </c>
       <c r="I78" s="34" t="inlineStr">
         <is>
-          <t>fort_confrontation</t>
+          <t>fort_pamphlets</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -5874,7 +5862,7 @@
       </c>
       <c r="N78" s="35" t="inlineStr">
         <is>
-          <t>Public confrontation path; removes governor; generates replacement</t>
+          <t>Fires at Fortress tiles; requires governor + no fortDisrepair; army station required</t>
         </is>
       </c>
     </row>
@@ -5891,12 +5879,12 @@
       </c>
       <c r="C79" s="34" t="inlineStr">
         <is>
-          <t>FORT_004</t>
+          <t>FORT_003</t>
         </is>
       </c>
       <c r="D79" s="35" t="inlineStr">
         <is>
-          <t>FORT [TILE_NAME] REPAIR ORDER SIGNED — GRIEVANCES RESOLVED</t>
+          <t>PRESIDENT CARLISLE FIRES [COMMANDER_NAME] IN FRONT OF GOD AND THE GARRISON</t>
         </is>
       </c>
       <c r="E79" s="28" t="inlineStr">
@@ -5906,12 +5894,12 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>FORT_001 BTN2</t>
+          <t>FORT_001 BTN1</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
         <is>
-          <t>→ FORT_005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -5921,7 +5909,7 @@
       </c>
       <c r="I79" s="34" t="inlineStr">
         <is>
-          <t>fort_handshake</t>
+          <t>fort_confrontation</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -5942,7 +5930,7 @@
       </c>
       <c r="N79" s="35" t="inlineStr">
         <is>
-          <t>Private resolution path; repair_fort outcome; chains to FORT_005</t>
+          <t>Public confrontation path; removes governor; generates replacement</t>
         </is>
       </c>
     </row>
@@ -5959,148 +5947,148 @@
       </c>
       <c r="C80" s="34" t="inlineStr">
         <is>
+          <t>FORT_004</t>
+        </is>
+      </c>
+      <c r="D80" s="35" t="inlineStr">
+        <is>
+          <t>FORT [TILE_NAME] REPAIR ORDER SIGNED — GRIEVANCES RESOLVED</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F80" s="35" t="inlineStr">
+        <is>
+          <t>FORT_001 BTN2</t>
+        </is>
+      </c>
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>→ FORT_005</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I80" s="34" t="inlineStr">
+        <is>
+          <t>fort_handshake</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K80" s="36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L80" s="34" t="inlineStr"/>
+      <c r="M80" s="36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N80" s="35" t="inlineStr">
+        <is>
+          <t>Private resolution path; repair_fort outcome; chains to FORT_005</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>Fort Chain</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t>Fort Disrepair</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="inlineStr">
+        <is>
           <t>FORT_005</t>
         </is>
       </c>
-      <c r="D80" s="35" t="inlineStr">
+      <c r="D81" s="35" t="inlineStr">
         <is>
           <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME]</t>
         </is>
       </c>
-      <c r="E80" s="22" t="inlineStr">
+      <c r="E81" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F80" s="35" t="inlineStr">
+      <c r="F81" s="35" t="inlineStr">
         <is>
           <t>FORT_004</t>
         </is>
       </c>
-      <c r="G80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I80" s="34" t="inlineStr">
+      <c r="G81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I81" s="34" t="inlineStr">
         <is>
           <t>fort_diplomatic</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K80" s="26" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K81" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L80" s="34" t="inlineStr">
+      <c r="L81" s="34" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="M80" s="36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N80" s="35" t="inlineStr">
+      <c r="M81" s="36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N81" s="35" t="inlineStr">
         <is>
           <t>Explicit reward event; BTN1 explicit morale+30 / BTN2 standard morale+10</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="8" customHeight="1">
-      <c r="A81" s="9" t="n"/>
-      <c r="B81" s="9" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
-      <c r="H81" s="9" t="n"/>
-      <c r="I81" s="9" t="n"/>
-      <c r="J81" s="9" t="n"/>
-      <c r="K81" s="9" t="n"/>
-      <c r="L81" s="9" t="n"/>
-      <c r="M81" s="9" t="n"/>
-      <c r="N81" s="9" t="n"/>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="37" t="inlineStr">
-        <is>
-          <t>Collapse</t>
-        </is>
-      </c>
-      <c r="B82" s="37" t="inlineStr">
-        <is>
-          <t>Republic Falls</t>
-        </is>
-      </c>
-      <c r="C82" s="38" t="inlineStr">
-        <is>
-          <t>COLLAPSE_01</t>
-        </is>
-      </c>
-      <c r="D82" s="39" t="inlineStr">
-        <is>
-          <t>THE REPUBLIC HAS FALLEN</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="39" t="inlineStr">
-        <is>
-          <t>→ COLLAPSE_02</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I82" s="38" t="inlineStr">
-        <is>
-          <t>collapse_republic</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K82" s="40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L82" s="38" t="inlineStr"/>
-      <c r="M82" s="40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N82" s="39" t="inlineStr">
-        <is>
-          <t>trigger_collapse outcome; fires when all metros fall</t>
-        </is>
-      </c>
+    <row r="82" ht="8" customHeight="1">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="9" t="n"/>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="n"/>
+      <c r="K82" s="9" t="n"/>
+      <c r="L82" s="9" t="n"/>
+      <c r="M82" s="9" t="n"/>
+      <c r="N82" s="9" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="37" t="inlineStr">
@@ -6115,148 +6103,148 @@
       </c>
       <c r="C83" s="38" t="inlineStr">
         <is>
+          <t>COLLAPSE_01</t>
+        </is>
+      </c>
+      <c r="D83" s="39" t="inlineStr">
+        <is>
+          <t>THE REPUBLIC HAS FALLEN</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F83" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="39" t="inlineStr">
+        <is>
+          <t>→ COLLAPSE_02</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I83" s="38" t="inlineStr">
+        <is>
+          <t>collapse_republic</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K83" s="40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L83" s="38" t="inlineStr"/>
+      <c r="M83" s="40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N83" s="39" t="inlineStr">
+        <is>
+          <t>trigger_collapse outcome; fires when all metros fall</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="37" t="inlineStr">
+        <is>
+          <t>Collapse</t>
+        </is>
+      </c>
+      <c r="B84" s="37" t="inlineStr">
+        <is>
+          <t>Republic Falls</t>
+        </is>
+      </c>
+      <c r="C84" s="38" t="inlineStr">
+        <is>
           <t>COLLAPSE_02</t>
         </is>
       </c>
-      <c r="D83" s="39" t="inlineStr">
+      <c r="D84" s="39" t="inlineStr">
         <is>
           <t>WASHINGTON STANDS ALONE</t>
         </is>
       </c>
-      <c r="E83" s="22" t="inlineStr">
+      <c r="E84" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F83" s="39" t="inlineStr">
+      <c r="F84" s="39" t="inlineStr">
         <is>
           <t>COLLAPSE_01</t>
         </is>
       </c>
-      <c r="G83" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I83" s="38" t="inlineStr">
+      <c r="G84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I84" s="38" t="inlineStr">
         <is>
           <t>ualani_washington</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K83" s="26" t="inlineStr">
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K84" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L83" s="38" t="inlineStr">
+      <c r="L84" s="38" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M83" s="40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N83" s="39" t="inlineStr">
+      <c r="M84" s="40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N84" s="39" t="inlineStr">
         <is>
           <t>BTN1 explicit 'The Long Night' morale+30 / BTN2 standard 'Hold the Line' morale+10</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="8" customHeight="1">
-      <c r="A84" s="9" t="n"/>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="n"/>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
-      <c r="L84" s="9" t="n"/>
-      <c r="M84" s="9" t="n"/>
-      <c r="N84" s="9" t="n"/>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="41" t="inlineStr">
-        <is>
-          <t>Tile Crisis</t>
-        </is>
-      </c>
-      <c r="B85" s="41" t="inlineStr">
-        <is>
-          <t>Harvest Crisis</t>
-        </is>
-      </c>
-      <c r="C85" s="42" t="inlineStr">
-        <is>
-          <t>HARVEST_001</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
-        <is>
-          <t>THE ARMY ATE THE SEED CORN</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F85" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G85" s="43" t="inlineStr">
-        <is>
-          <t>→ HARVEST_VISIT_01 (BTN1 mission)</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I85" s="42" t="inlineStr">
-        <is>
-          <t>harvest_crisis</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K85" s="44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L85" s="42" t="inlineStr"/>
-      <c r="M85" s="44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N85" s="43" t="inlineStr">
-        <is>
-          <t>Fires when food &lt; 50; Farm tile required; set_mission_flag BTN1</t>
-        </is>
-      </c>
+    <row r="85" ht="8" customHeight="1">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="9" t="n"/>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
+      <c r="N85" s="9" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="41" t="inlineStr">
@@ -6271,27 +6259,27 @@
       </c>
       <c r="C86" s="42" t="inlineStr">
         <is>
-          <t>HARVEST_VISIT_01</t>
+          <t>HARVEST_001</t>
         </is>
       </c>
       <c r="D86" s="43" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SAVES THE HARVEST</t>
-        </is>
-      </c>
-      <c r="E86" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>THE ARMY ATE THE SEED CORN</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F86" s="43" t="inlineStr">
         <is>
-          <t>HARVEST_001 BTN1 (army mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ HARVEST_VISIT_01 (BTN1 mission)</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -6301,7 +6289,7 @@
       </c>
       <c r="I86" s="42" t="inlineStr">
         <is>
-          <t>harvest_complete</t>
+          <t>harvest_crisis</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
@@ -6309,16 +6297,12 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K86" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L86" s="42" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
+      <c r="K86" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L86" s="42" t="inlineStr"/>
       <c r="M86" s="44" t="inlineStr">
         <is>
           <t>0</t>
@@ -6326,7 +6310,7 @@
       </c>
       <c r="N86" s="43" t="inlineStr">
         <is>
-          <t>BTN2 explicit 'Presidential Persuasion' +food 80 vs BTN1 standard +food 60</t>
+          <t>Fires when food &lt; 50; Farm tile required; set_mission_flag BTN1</t>
         </is>
       </c>
     </row>
@@ -6338,32 +6322,32 @@
       </c>
       <c r="B87" s="41" t="inlineStr">
         <is>
-          <t>Harbor Threat</t>
+          <t>Harvest Crisis</t>
         </is>
       </c>
       <c r="C87" s="42" t="inlineStr">
         <is>
-          <t>HARBOR_001</t>
+          <t>HARVEST_VISIT_01</t>
         </is>
       </c>
       <c r="D87" s="43" t="inlineStr">
         <is>
-          <t>CROWN VESSELS SPOTTED: DOCK AT [TILE_NAME] AT RISK</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>PRESIDENT CARLISLE SAVES THE HARVEST</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F87" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HARVEST_001 BTN1 (army mission)</t>
         </is>
       </c>
       <c r="G87" s="43" t="inlineStr">
         <is>
-          <t>→ HARBOR_ESCORT_01 (BTN1) | → HARBOR_BURN_01 (BTN2)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -6373,7 +6357,7 @@
       </c>
       <c r="I87" s="42" t="inlineStr">
         <is>
-          <t>harbor_threat</t>
+          <t>harvest_complete</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
@@ -6381,12 +6365,16 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K87" s="44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L87" s="42" t="inlineStr"/>
+      <c r="K87" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L87" s="42" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M87" s="44" t="inlineStr">
         <is>
           <t>0</t>
@@ -6394,7 +6382,7 @@
       </c>
       <c r="N87" s="43" t="inlineStr">
         <is>
-          <t>Dock tile required + UK neighbor; army station required</t>
+          <t>BTN2 explicit 'Presidential Persuasion' +food 80 vs BTN1 standard +food 60</t>
         </is>
       </c>
     </row>
@@ -6411,27 +6399,27 @@
       </c>
       <c r="C88" s="42" t="inlineStr">
         <is>
-          <t>HARBOR_ESCORT_01</t>
+          <t>HARBOR_001</t>
         </is>
       </c>
       <c r="D88" s="43" t="inlineStr">
         <is>
-          <t>HARBOR SECURED: CROWN FRIGATE RETREATS</t>
-        </is>
-      </c>
-      <c r="E88" s="28" t="inlineStr">
-        <is>
-          <t>Branch</t>
+          <t>CROWN VESSELS SPOTTED: DOCK AT [TILE_NAME] AT RISK</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F88" s="43" t="inlineStr">
         <is>
-          <t>HARBOR_001 BTN1 (army mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G88" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ HARBOR_ESCORT_01 (BTN1) | → HARBOR_BURN_01 (BTN2)</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
@@ -6441,7 +6429,7 @@
       </c>
       <c r="I88" s="42" t="inlineStr">
         <is>
-          <t>harbor_secure</t>
+          <t>harbor_threat</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
@@ -6462,7 +6450,7 @@
       </c>
       <c r="N88" s="43" t="inlineStr">
         <is>
-          <t>+food 30; garrison path</t>
+          <t>Dock tile required + UK neighbor; army station required</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6467,12 @@
       </c>
       <c r="C89" s="42" t="inlineStr">
         <is>
-          <t>HARBOR_BURN_01</t>
+          <t>HARBOR_ESCORT_01</t>
         </is>
       </c>
       <c r="D89" s="43" t="inlineStr">
         <is>
-          <t>DOCK FACILITIES DESTROYED: ACCESS DENIED</t>
+          <t>HARBOR SECURED: CROWN FRIGATE RETREATS</t>
         </is>
       </c>
       <c r="E89" s="28" t="inlineStr">
@@ -6494,7 +6482,7 @@
       </c>
       <c r="F89" s="43" t="inlineStr">
         <is>
-          <t>HARBOR_001 BTN2 (army mission)</t>
+          <t>HARBOR_001 BTN1 (army mission)</t>
         </is>
       </c>
       <c r="G89" s="43" t="inlineStr">
@@ -6509,7 +6497,7 @@
       </c>
       <c r="I89" s="42" t="inlineStr">
         <is>
-          <t>harbor_burned</t>
+          <t>harbor_secure</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
@@ -6530,7 +6518,7 @@
       </c>
       <c r="N89" s="43" t="inlineStr">
         <is>
-          <t>disable_building Dock 8 turns; destruction path</t>
+          <t>+food 30; garrison path</t>
         </is>
       </c>
     </row>
@@ -6542,32 +6530,32 @@
       </c>
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>Forge Threat</t>
+          <t>Harbor Threat</t>
         </is>
       </c>
       <c r="C90" s="42" t="inlineStr">
         <is>
-          <t>FORGE_001</t>
+          <t>HARBOR_BURN_01</t>
         </is>
       </c>
       <c r="D90" s="43" t="inlineStr">
         <is>
-          <t>INTELLIGENCE ALERT: CROWN FORCES LOCATE THE FORGE AT [TILE_NAME]</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>DOCK FACILITIES DESTROYED: ACCESS DENIED</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F90" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HARBOR_001 BTN2 (army mission)</t>
         </is>
       </c>
       <c r="G90" s="43" t="inlineStr">
         <is>
-          <t>→ FORGE_REINFORCE_01 (BTN1) | → FORGE_EVACUATE_01 (BTN2)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -6577,7 +6565,7 @@
       </c>
       <c r="I90" s="42" t="inlineStr">
         <is>
-          <t>forge_threat</t>
+          <t>harbor_burned</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
@@ -6598,7 +6586,7 @@
       </c>
       <c r="N90" s="43" t="inlineStr">
         <is>
-          <t>Forge tile required + UK neighbor; army station required</t>
+          <t>disable_building Dock 8 turns; destruction path</t>
         </is>
       </c>
     </row>
@@ -6615,27 +6603,27 @@
       </c>
       <c r="C91" s="42" t="inlineStr">
         <is>
-          <t>FORGE_REINFORCE_01</t>
+          <t>FORGE_001</t>
         </is>
       </c>
       <c r="D91" s="43" t="inlineStr">
         <is>
-          <t>FORGE SECURED: CROWN ASSAULT PLAN ABANDONED</t>
-        </is>
-      </c>
-      <c r="E91" s="28" t="inlineStr">
-        <is>
-          <t>Branch</t>
+          <t>INTELLIGENCE ALERT: CROWN FORCES LOCATE THE FORGE AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F91" s="43" t="inlineStr">
         <is>
-          <t>FORGE_001 BTN1 (army mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ FORGE_REINFORCE_01 (BTN1) | → FORGE_EVACUATE_01 (BTN2)</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -6645,7 +6633,7 @@
       </c>
       <c r="I91" s="42" t="inlineStr">
         <is>
-          <t>forge_secure</t>
+          <t>forge_threat</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
@@ -6666,7 +6654,7 @@
       </c>
       <c r="N91" s="43" t="inlineStr">
         <is>
-          <t>+weapons 30; defense path</t>
+          <t>Forge tile required + UK neighbor; army station required</t>
         </is>
       </c>
     </row>
@@ -6683,12 +6671,12 @@
       </c>
       <c r="C92" s="42" t="inlineStr">
         <is>
-          <t>FORGE_EVACUATE_01</t>
+          <t>FORGE_REINFORCE_01</t>
         </is>
       </c>
       <c r="D92" s="43" t="inlineStr">
         <is>
-          <t>EMERGENCY EXTRACTION: WEAPONS CACHE SECURED</t>
+          <t>FORGE SECURED: CROWN ASSAULT PLAN ABANDONED</t>
         </is>
       </c>
       <c r="E92" s="28" t="inlineStr">
@@ -6698,7 +6686,7 @@
       </c>
       <c r="F92" s="43" t="inlineStr">
         <is>
-          <t>FORGE_001 BTN2 (army mission)</t>
+          <t>FORGE_001 BTN1 (army mission)</t>
         </is>
       </c>
       <c r="G92" s="43" t="inlineStr">
@@ -6713,7 +6701,7 @@
       </c>
       <c r="I92" s="42" t="inlineStr">
         <is>
-          <t>forge_evac</t>
+          <t>forge_secure</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
@@ -6734,7 +6722,7 @@
       </c>
       <c r="N92" s="43" t="inlineStr">
         <is>
-          <t>+weapons 25; Forge temporarily offline</t>
+          <t>+weapons 30; defense path</t>
         </is>
       </c>
     </row>
@@ -6746,32 +6734,32 @@
       </c>
       <c r="B93" s="41" t="inlineStr">
         <is>
-          <t>Corruption Crisis</t>
+          <t>Forge Threat</t>
         </is>
       </c>
       <c r="C93" s="42" t="inlineStr">
         <is>
-          <t>CORRUPT_001</t>
+          <t>FORGE_EVACUATE_01</t>
         </is>
       </c>
       <c r="D93" s="43" t="inlineStr">
         <is>
-          <t>MAGISTRATE [COMMANDER_NAME] UNDER INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>EMERGENCY EXTRACTION: WEAPONS CACHE SECURED</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F93" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FORGE_001 BTN2 (army mission)</t>
         </is>
       </c>
       <c r="G93" s="43" t="inlineStr">
         <is>
-          <t>→ CORRUPT_TRIAL_01 (BTN1) | → CORRUPT_DEAL_01 (BTN2)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -6781,7 +6769,7 @@
       </c>
       <c r="I93" s="42" t="inlineStr">
         <is>
-          <t>corruption_crisis</t>
+          <t>forge_evac</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
@@ -6802,7 +6790,7 @@
       </c>
       <c r="N93" s="43" t="inlineStr">
         <is>
-          <t>Fires when tileMoralDecay &gt;= 50 on Courthouse tile; army station required</t>
+          <t>+weapons 25; Forge temporarily offline</t>
         </is>
       </c>
     </row>
@@ -6819,27 +6807,27 @@
       </c>
       <c r="C94" s="42" t="inlineStr">
         <is>
-          <t>CORRUPT_TRIAL_01</t>
+          <t>CORRUPT_001</t>
         </is>
       </c>
       <c r="D94" s="43" t="inlineStr">
         <is>
-          <t>MAGISTRATE REMOVED IN DISGRACE</t>
-        </is>
-      </c>
-      <c r="E94" s="28" t="inlineStr">
-        <is>
-          <t>Branch</t>
+          <t>MAGISTRATE [COMMANDER_NAME] UNDER INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F94" s="43" t="inlineStr">
         <is>
-          <t>CORRUPT_001 BTN1 (army mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="43" t="inlineStr">
         <is>
-          <t>→ CORRUPT_REFORM_01</t>
+          <t>→ CORRUPT_TRIAL_01 (BTN1) | → CORRUPT_DEAL_01 (BTN2)</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -6849,7 +6837,7 @@
       </c>
       <c r="I94" s="42" t="inlineStr">
         <is>
-          <t>corrupt_trial</t>
+          <t>corruption_crisis</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
@@ -6870,7 +6858,7 @@
       </c>
       <c r="N94" s="43" t="inlineStr">
         <is>
-          <t>remove_governor; chains to CORRUPT_REFORM_01</t>
+          <t>Fires when tileMoralDecay &gt;= 50 on Courthouse tile; army station required</t>
         </is>
       </c>
     </row>
@@ -6887,27 +6875,27 @@
       </c>
       <c r="C95" s="42" t="inlineStr">
         <is>
-          <t>CORRUPT_REFORM_01</t>
+          <t>CORRUPT_TRIAL_01</t>
         </is>
       </c>
       <c r="D95" s="43" t="inlineStr">
         <is>
-          <t>COURTHOUSE REFORMS UNDERWAY AT [TILE_NAME]</t>
-        </is>
-      </c>
-      <c r="E95" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>MAGISTRATE REMOVED IN DISGRACE</t>
+        </is>
+      </c>
+      <c r="E95" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F95" s="43" t="inlineStr">
         <is>
-          <t>CORRUPT_TRIAL_01</t>
+          <t>CORRUPT_001 BTN1 (army mission)</t>
         </is>
       </c>
       <c r="G95" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ CORRUPT_REFORM_01</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -6917,7 +6905,7 @@
       </c>
       <c r="I95" s="42" t="inlineStr">
         <is>
-          <t>courthouse_reform</t>
+          <t>corrupt_trial</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -6938,7 +6926,7 @@
       </c>
       <c r="N95" s="43" t="inlineStr">
         <is>
-          <t>tile_moral_decay_change -50</t>
+          <t>remove_governor; chains to CORRUPT_REFORM_01</t>
         </is>
       </c>
     </row>
@@ -6955,22 +6943,22 @@
       </c>
       <c r="C96" s="42" t="inlineStr">
         <is>
-          <t>CORRUPT_DEAL_01</t>
+          <t>CORRUPT_REFORM_01</t>
         </is>
       </c>
       <c r="D96" s="43" t="inlineStr">
         <is>
-          <t>ARRANGEMENT REACHED AT [TILE_NAME]</t>
-        </is>
-      </c>
-      <c r="E96" s="28" t="inlineStr">
-        <is>
-          <t>Branch</t>
+          <t>COURTHOUSE REFORMS UNDERWAY AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F96" s="43" t="inlineStr">
         <is>
-          <t>CORRUPT_001 BTN2 (army mission)</t>
+          <t>CORRUPT_TRIAL_01</t>
         </is>
       </c>
       <c r="G96" s="43" t="inlineStr">
@@ -6985,7 +6973,7 @@
       </c>
       <c r="I96" s="42" t="inlineStr">
         <is>
-          <t>corrupt_deal</t>
+          <t>courthouse_reform</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
@@ -7006,7 +6994,7 @@
       </c>
       <c r="N96" s="43" t="inlineStr">
         <is>
-          <t>+gold 40; private deal path; magistrate stays</t>
+          <t>tile_moral_decay_change -50</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7006,32 @@
       </c>
       <c r="B97" s="41" t="inlineStr">
         <is>
-          <t>Border Dispute</t>
+          <t>Corruption Crisis</t>
         </is>
       </c>
       <c r="C97" s="42" t="inlineStr">
         <is>
-          <t>BORDER_001</t>
+          <t>CORRUPT_DEAL_01</t>
         </is>
       </c>
       <c r="D97" s="43" t="inlineStr">
         <is>
-          <t>CANADIAN BORDER INCIDENT AT [TILE_NAME]: THE LINE IS IN QUESTION</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>ARRANGEMENT REACHED AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F97" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRUPT_001 BTN2 (army mission)</t>
         </is>
       </c>
       <c r="G97" s="43" t="inlineStr">
         <is>
-          <t>→ BORDER_ASSERT_01 (BTN1) | → BORDER_SURVEY_01 (BTN3)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -7053,7 +7041,7 @@
       </c>
       <c r="I97" s="42" t="inlineStr">
         <is>
-          <t>border_dispute</t>
+          <t>corrupt_deal</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -7074,7 +7062,7 @@
       </c>
       <c r="N97" s="43" t="inlineStr">
         <is>
-          <t>Woods/Foothills tile + CA neighbor; BTN2 claim_change -1 (diplomacy)</t>
+          <t>+gold 40; private deal path; magistrate stays</t>
         </is>
       </c>
     </row>
@@ -7091,27 +7079,27 @@
       </c>
       <c r="C98" s="42" t="inlineStr">
         <is>
-          <t>BORDER_ASSERT_01</t>
+          <t>BORDER_001</t>
         </is>
       </c>
       <c r="D98" s="43" t="inlineStr">
         <is>
-          <t>FEDERAL BOUNDARY MARKER PLANTED AT [TILE_NAME]</t>
-        </is>
-      </c>
-      <c r="E98" s="28" t="inlineStr">
-        <is>
-          <t>Branch</t>
+          <t>CANADIAN BORDER INCIDENT AT [TILE_NAME]: THE LINE IS IN QUESTION</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F98" s="43" t="inlineStr">
         <is>
-          <t>BORDER_001 BTN1 (army mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ BORDER_ASSERT_01 (BTN1) | → BORDER_SURVEY_01 (BTN3)</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
@@ -7121,7 +7109,7 @@
       </c>
       <c r="I98" s="42" t="inlineStr">
         <is>
-          <t>border_assert</t>
+          <t>border_dispute</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
@@ -7142,7 +7130,7 @@
       </c>
       <c r="N98" s="43" t="inlineStr">
         <is>
-          <t>+claim 2; garrison asserts sovereignty</t>
+          <t>Woods/Foothills tile + CA neighbor; BTN2 claim_change -1 (diplomacy)</t>
         </is>
       </c>
     </row>
@@ -7159,12 +7147,12 @@
       </c>
       <c r="C99" s="42" t="inlineStr">
         <is>
-          <t>BORDER_SURVEY_01</t>
+          <t>BORDER_ASSERT_01</t>
         </is>
       </c>
       <c r="D99" s="43" t="inlineStr">
         <is>
-          <t>SURVEY COMPLETE AT [TILE_NAME]: THE LAND IS OURS</t>
+          <t>FEDERAL BOUNDARY MARKER PLANTED AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="E99" s="28" t="inlineStr">
@@ -7174,7 +7162,7 @@
       </c>
       <c r="F99" s="43" t="inlineStr">
         <is>
-          <t>BORDER_001 BTN3 (army mission)</t>
+          <t>BORDER_001 BTN1 (army mission)</t>
         </is>
       </c>
       <c r="G99" s="43" t="inlineStr">
@@ -7189,7 +7177,7 @@
       </c>
       <c r="I99" s="42" t="inlineStr">
         <is>
-          <t>border_survey</t>
+          <t>border_assert</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
@@ -7210,7 +7198,7 @@
       </c>
       <c r="N99" s="43" t="inlineStr">
         <is>
-          <t>+gold 20; diplomatic survey path</t>
+          <t>+claim 2; garrison asserts sovereignty</t>
         </is>
       </c>
     </row>
@@ -7222,27 +7210,27 @@
       </c>
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>Garrison Hunger</t>
+          <t>Border Dispute</t>
         </is>
       </c>
       <c r="C100" s="42" t="inlineStr">
         <is>
-          <t>GARRISON_001</t>
+          <t>BORDER_SURVEY_01</t>
         </is>
       </c>
       <c r="D100" s="43" t="inlineStr">
         <is>
-          <t>FIELD REPORT: [TILE_NAME] GARRISON REPORTING CRITICAL SUPPLY SHORTFALL</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>SURVEY COMPLETE AT [TILE_NAME]: THE LAND IS OURS</t>
+        </is>
+      </c>
+      <c r="E100" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F100" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BORDER_001 BTN3 (army mission)</t>
         </is>
       </c>
       <c r="G100" s="43" t="inlineStr">
@@ -7257,7 +7245,7 @@
       </c>
       <c r="I100" s="42" t="inlineStr">
         <is>
-          <t>garrison_starving</t>
+          <t>border_survey</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -7278,7 +7266,7 @@
       </c>
       <c r="N100" s="43" t="inlineStr">
         <is>
-          <t>Fires when any USA army &lt; 50 manpower; BTN1 spend -30 gold / BTN2 retreat</t>
+          <t>+gold 20; diplomatic survey path</t>
         </is>
       </c>
     </row>
@@ -7290,17 +7278,17 @@
       </c>
       <c r="B101" s="41" t="inlineStr">
         <is>
-          <t>Legitimacy Crisis</t>
+          <t>Garrison Hunger</t>
         </is>
       </c>
       <c r="C101" s="42" t="inlineStr">
         <is>
-          <t>CRISIS_CLAIM_001</t>
+          <t>GARRISON_001</t>
         </is>
       </c>
       <c r="D101" s="43" t="inlineStr">
         <is>
-          <t>LEGITIMACY CRISIS: THE REPUBLIC'S CLAIM ON ITSELF IS IN QUESTION</t>
+          <t>FIELD REPORT: [TILE_NAME] GARRISON REPORTING CRITICAL SUPPLY SHORTFALL</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -7325,7 +7313,7 @@
       </c>
       <c r="I101" s="42" t="inlineStr">
         <is>
-          <t>legitimacy_crisis</t>
+          <t>garrison_starving</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -7346,7 +7334,7 @@
       </c>
       <c r="N101" s="43" t="inlineStr">
         <is>
-          <t>Fires when presidentialClaim &lt;= -5; 3 claim_change response buttons</t>
+          <t>Fires when any USA army &lt; 50 manpower; BTN1 spend -30 gold / BTN2 retreat</t>
         </is>
       </c>
     </row>
@@ -7358,17 +7346,17 @@
       </c>
       <c r="B102" s="41" t="inlineStr">
         <is>
-          <t>Turncoat General</t>
+          <t>Legitimacy Crisis</t>
         </is>
       </c>
       <c r="C102" s="42" t="inlineStr">
         <is>
-          <t>TURNCOAT_001</t>
+          <t>CRISIS_CLAIM_001</t>
         </is>
       </c>
       <c r="D102" s="43" t="inlineStr">
         <is>
-          <t>INTELLIGENCE REPORT: COMMANDER [COMMANDER_NAME] IN CONTACT WITH CROWN</t>
+          <t>LEGITIMACY CRISIS: THE REPUBLIC'S CLAIM ON ITSELF IS IN QUESTION</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -7393,7 +7381,7 @@
       </c>
       <c r="I102" s="42" t="inlineStr">
         <is>
-          <t>turncoat_report</t>
+          <t>legitimacy_crisis</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -7414,7 +7402,7 @@
       </c>
       <c r="N102" s="43" t="inlineStr">
         <is>
-          <t>Fires when any governor loyalty &lt;= -8; remove / double-agent / watch</t>
+          <t>Fires when presidentialClaim &lt;= -5; 3 claim_change response buttons</t>
         </is>
       </c>
     </row>
@@ -7426,17 +7414,17 @@
       </c>
       <c r="B103" s="41" t="inlineStr">
         <is>
-          <t>Memorial Lost</t>
+          <t>Turncoat General</t>
         </is>
       </c>
       <c r="C103" s="42" t="inlineStr">
         <is>
-          <t>MEMORIAL_001</t>
+          <t>TURNCOAT_001</t>
         </is>
       </c>
       <c r="D103" s="43" t="inlineStr">
         <is>
-          <t>[TILE_NAME] FALLS TO THE CROWN: HISTORICAL SITE UNDER OCCUPATION</t>
+          <t>INTELLIGENCE REPORT: COMMANDER [COMMANDER_NAME] IN CONTACT WITH CROWN</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -7451,7 +7439,7 @@
       </c>
       <c r="G103" s="43" t="inlineStr">
         <is>
-          <t>→ MEMORIAL_RESTORE_01 (BTN1 own-mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
@@ -7461,7 +7449,7 @@
       </c>
       <c r="I103" s="42" t="inlineStr">
         <is>
-          <t>memorial_lost</t>
+          <t>turncoat_report</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -7482,7 +7470,7 @@
       </c>
       <c r="N103" s="43" t="inlineStr">
         <is>
-          <t>Fires when UK captures tile with tileSpecialFeatures; set_mission_flag_own</t>
+          <t>Fires when any governor loyalty &lt;= -8; remove / double-agent / watch</t>
         </is>
       </c>
     </row>
@@ -7499,27 +7487,27 @@
       </c>
       <c r="C104" s="42" t="inlineStr">
         <is>
-          <t>MEMORIAL_RESTORE_01</t>
+          <t>MEMORIAL_001</t>
         </is>
       </c>
       <c r="D104" s="43" t="inlineStr">
         <is>
-          <t>[TILE_NAME] LIBERATED: THE MEMORIAL IS OURS AGAIN</t>
-        </is>
-      </c>
-      <c r="E104" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>[TILE_NAME] FALLS TO THE CROWN: HISTORICAL SITE UNDER OCCUPATION</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F104" s="43" t="inlineStr">
         <is>
-          <t>MEMORIAL_001 BTN1 (own-mission)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G104" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ MEMORIAL_RESTORE_01 (BTN1 own-mission)</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
@@ -7529,7 +7517,7 @@
       </c>
       <c r="I104" s="42" t="inlineStr">
         <is>
-          <t>memorial_restored</t>
+          <t>memorial_lost</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -7550,93 +7538,93 @@
       </c>
       <c r="N104" s="43" t="inlineStr">
         <is>
+          <t>Fires when UK captures tile with tileSpecialFeatures; set_mission_flag_own</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="41" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B105" s="41" t="inlineStr">
+        <is>
+          <t>Memorial Lost</t>
+        </is>
+      </c>
+      <c r="C105" s="42" t="inlineStr">
+        <is>
+          <t>MEMORIAL_RESTORE_01</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="inlineStr">
+        <is>
+          <t>[TILE_NAME] LIBERATED: THE MEMORIAL IS OURS AGAIN</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F105" s="43" t="inlineStr">
+        <is>
+          <t>MEMORIAL_001 BTN1 (own-mission)</t>
+        </is>
+      </c>
+      <c r="G105" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I105" s="42" t="inlineStr">
+        <is>
+          <t>memorial_restored</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K105" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L105" s="42" t="inlineStr"/>
+      <c r="M105" s="44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N105" s="43" t="inlineStr">
+        <is>
           <t>Fires when USA retakes the special-feature tile; +morale 20</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="8" customHeight="1">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
-      <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-      <c r="L105" s="9" t="n"/>
-      <c r="M105" s="9" t="n"/>
-      <c r="N105" s="9" t="n"/>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="45" t="inlineStr">
-        <is>
-          <t>Ualani</t>
-        </is>
-      </c>
-      <c r="B106" s="45" t="inlineStr">
-        <is>
-          <t>Ambush</t>
-        </is>
-      </c>
-      <c r="C106" s="46" t="inlineStr">
-        <is>
-          <t>UALANI_AMBUSH_01</t>
-        </is>
-      </c>
-      <c r="D106" s="47" t="inlineStr">
-        <is>
-          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE WETLANDS</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F106" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G106" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I106" s="46" t="inlineStr"/>
-      <c r="J106" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K106" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L106" s="46" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M106" s="48" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N106" s="47" t="inlineStr">
-        <is>
-          <t>Ualani in Wetlands + UK neighbor; BTN3 explicit +weapons 40</t>
-        </is>
-      </c>
+    <row r="106" ht="8" customHeight="1">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="L106" s="9" t="n"/>
+      <c r="M106" s="9" t="n"/>
+      <c r="N106" s="9" t="n"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="45" t="inlineStr">
@@ -7646,17 +7634,17 @@
       </c>
       <c r="B107" s="45" t="inlineStr">
         <is>
-          <t>Dignitary Reception</t>
+          <t>Ambush</t>
         </is>
       </c>
       <c r="C107" s="46" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01</t>
+          <t>UALANI_AMBUSH_01</t>
         </is>
       </c>
       <c r="D107" s="47" t="inlineStr">
         <is>
-          <t>STATE RECEPTION AT [TILE_NAME]</t>
+          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE WETLANDS</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -7697,12 +7685,12 @@
       </c>
       <c r="M107" s="48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N107" s="47" t="inlineStr">
         <is>
-          <t>Ualani in Metro/Suburbs + Courthouse + tileMoralDecay &lt; 30; BTN3 explicit -20 moralDecay</t>
+          <t>Ualani in Wetlands + UK neighbor; BTN3 explicit +weapons 40</t>
         </is>
       </c>
     </row>
@@ -7714,17 +7702,17 @@
       </c>
       <c r="B108" s="45" t="inlineStr">
         <is>
-          <t>Memorial Address</t>
+          <t>Dignitary Reception</t>
         </is>
       </c>
       <c r="C108" s="46" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01</t>
+          <t>UALANI_DIGNITARY_01</t>
         </is>
       </c>
       <c r="D108" s="47" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ADDRESS AT THE MEMORIAL</t>
+          <t>STATE RECEPTION AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -7765,12 +7753,12 @@
       </c>
       <c r="M108" s="48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N108" s="47" t="inlineStr">
         <is>
-          <t>Ualani at tile with tileSpecialFeatures; BTN3 explicit +morale 50</t>
+          <t>Ualani in Metro/Suburbs + Courthouse + tileMoralDecay &lt; 30; BTN3 explicit -20 moralDecay</t>
         </is>
       </c>
     </row>
@@ -7782,17 +7770,17 @@
       </c>
       <c r="B109" s="45" t="inlineStr">
         <is>
-          <t>Field Hospital</t>
+          <t>Memorial Address</t>
         </is>
       </c>
       <c r="C109" s="46" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01</t>
+          <t>UALANI_MEMORIAL_01</t>
         </is>
       </c>
       <c r="D109" s="47" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME]</t>
+          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ADDRESS AT THE MEMORIAL</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -7833,12 +7821,12 @@
       </c>
       <c r="M109" s="48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N109" s="47" t="inlineStr">
         <is>
-          <t>Ualani army &lt; 80% manpower; BTN2 explicit +manpower 40</t>
+          <t>Ualani at tile with tileSpecialFeatures; BTN3 explicit +morale 50</t>
         </is>
       </c>
     </row>
@@ -7850,17 +7838,17 @@
       </c>
       <c r="B110" s="45" t="inlineStr">
         <is>
-          <t>Winter March</t>
+          <t>Field Hospital</t>
         </is>
       </c>
       <c r="C110" s="46" t="inlineStr">
         <is>
-          <t>UALANI_WINTER_01</t>
+          <t>UALANI_WOUNDED_01</t>
         </is>
       </c>
       <c r="D110" s="47" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE MARCHES THROUGH [TILE_NAME] IN THE DEAD OF WINTER</t>
+          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -7889,20 +7877,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K110" s="48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L110" s="46" t="inlineStr"/>
+      <c r="K110" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L110" s="46" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M110" s="48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N110" s="47" t="inlineStr">
         <is>
-          <t>Ualani in Foothills/Woods; winter months [11,12,1,2]; winterScore &gt; 0; no explicit</t>
+          <t>Ualani army &lt; 80% manpower; BTN2 explicit +manpower 40</t>
         </is>
       </c>
     </row>
@@ -7914,17 +7906,17 @@
       </c>
       <c r="B111" s="45" t="inlineStr">
         <is>
-          <t>Forge Inspection</t>
+          <t>Winter March</t>
         </is>
       </c>
       <c r="C111" s="46" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01</t>
+          <t>UALANI_WINTER_01</t>
         </is>
       </c>
       <c r="D111" s="47" t="inlineStr">
         <is>
-          <t>SURPRISE INSPECTION OF FORGE AT [TILE_NAME]</t>
+          <t>PRESIDENT CARLISLE MARCHES THROUGH [TILE_NAME] IN THE DEAD OF WINTER</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -7953,24 +7945,20 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K111" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L111" s="46" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
+      <c r="K111" s="48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L111" s="46" t="inlineStr"/>
       <c r="M111" s="48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N111" s="47" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Forge; BTN3 explicit +weapons 60</t>
+          <t>Ualani in Foothills/Woods; winter months [11,12,1,2]; winterScore &gt; 0; no explicit</t>
         </is>
       </c>
     </row>
@@ -7982,17 +7970,17 @@
       </c>
       <c r="B112" s="45" t="inlineStr">
         <is>
-          <t>Culper Ring</t>
+          <t>Forge Inspection</t>
         </is>
       </c>
       <c r="C112" s="46" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01</t>
+          <t>UALANI_FORGE_01</t>
         </is>
       </c>
       <c r="D112" s="47" t="inlineStr">
         <is>
-          <t>CULPER RING CONTACT AT [TILE_NAME]</t>
+          <t>SURPRISE INSPECTION OF FORGE AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -8007,7 +7995,7 @@
       </c>
       <c r="G112" s="47" t="inlineStr">
         <is>
-          <t>→ UALANI_CULPER_BRIEF_01 (BTN1/BTN3 next_event_id)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
@@ -8033,12 +8021,12 @@
       </c>
       <c r="M112" s="48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N112" s="47" t="inlineStr">
         <is>
-          <t>Ualani neighbors tile with espionageActive; BTN3 explicit +gold 40 then brief</t>
+          <t>Ualani at tile with enabled Forge; BTN3 explicit +weapons 60</t>
         </is>
       </c>
     </row>
@@ -8055,27 +8043,27 @@
       </c>
       <c r="C113" s="46" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_BRIEF_01</t>
+          <t>UALANI_CULPER_01</t>
         </is>
       </c>
       <c r="D113" s="47" t="inlineStr">
         <is>
-          <t>CULPER RING INTELLIGENCE RECEIVED: CROWN PLANS CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E113" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>CULPER RING CONTACT AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F113" s="47" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01 BTN1 / BTN3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G113" s="47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ UALANI_CULPER_BRIEF_01 (BTN1/BTN3 next_event_id)</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -8089,20 +8077,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K113" s="48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L113" s="46" t="inlineStr"/>
+      <c r="K113" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L113" s="46" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M113" s="48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N113" s="47" t="inlineStr">
         <is>
-          <t>Sets culper_active flag; single button; no explicit</t>
+          <t>Ualani neighbors tile with espionageActive; BTN3 explicit +gold 40 then brief</t>
         </is>
       </c>
     </row>
@@ -8114,27 +8106,27 @@
       </c>
       <c r="B114" s="45" t="inlineStr">
         <is>
-          <t>Alliance Council</t>
+          <t>Culper Ring</t>
         </is>
       </c>
       <c r="C114" s="46" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01</t>
+          <t>UALANI_CULPER_BRIEF_01</t>
         </is>
       </c>
       <c r="D114" s="47" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [TILE_NAME]</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>CULPER RING INTELLIGENCE RECEIVED: CROWN PLANS CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E114" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F114" s="47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UALANI_CULPER_01 BTN1 / BTN3</t>
         </is>
       </c>
       <c r="G114" s="47" t="inlineStr">
@@ -8153,24 +8145,20 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K114" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L114" s="46" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
+      <c r="K114" s="48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L114" s="46" t="inlineStr"/>
       <c r="M114" s="48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N114" s="47" t="inlineStr">
         <is>
-          <t>Fires at NEIGHBOR tile (named hist. governor); BTN3 explicit governor_loyalty +12</t>
+          <t>Sets culper_active flag; single button; no explicit</t>
         </is>
       </c>
     </row>
@@ -8182,17 +8170,17 @@
       </c>
       <c r="B115" s="45" t="inlineStr">
         <is>
-          <t>Frontier</t>
+          <t>Alliance Council</t>
         </is>
       </c>
       <c r="C115" s="46" t="inlineStr">
         <is>
-          <t>UALANI_FRONTIER_01</t>
+          <t>UALANI_ALLIANCE_01</t>
         </is>
       </c>
       <c r="D115" s="47" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT [TILE_NAME]</t>
+          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -8233,98 +8221,98 @@
       </c>
       <c r="M115" s="48" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N115" s="47" t="inlineStr">
+        <is>
+          <t>Fires at NEIGHBOR tile (named hist. governor); BTN3 explicit governor_loyalty +12</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B116" s="45" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="C116" s="46" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01</t>
+        </is>
+      </c>
+      <c r="D116" s="47" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT [TILE_NAME]</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F116" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I116" s="46" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K116" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L116" s="46" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M116" s="48" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N115" s="47" t="inlineStr">
+      <c r="N116" s="47" t="inlineStr">
         <is>
           <t>Ualani in Woods/Foothills bordering CA - * tile; BTN3 explicit +morale 30</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="8" customHeight="1">
-      <c r="A116" s="9" t="n"/>
-      <c r="B116" s="9" t="n"/>
-      <c r="C116" s="9" t="n"/>
-      <c r="D116" s="9" t="n"/>
-      <c r="E116" s="9" t="n"/>
-      <c r="F116" s="9" t="n"/>
-      <c r="G116" s="9" t="n"/>
-      <c r="H116" s="9" t="n"/>
-      <c r="I116" s="9" t="n"/>
-      <c r="J116" s="9" t="n"/>
-      <c r="K116" s="9" t="n"/>
-      <c r="L116" s="9" t="n"/>
-      <c r="M116" s="9" t="n"/>
-      <c r="N116" s="9" t="n"/>
-    </row>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="49" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B117" s="49" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C117" s="50" t="inlineStr">
-        <is>
-          <t>UALANI_DOCK_01</t>
-        </is>
-      </c>
-      <c r="D117" s="51" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F117" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G117" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H117" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I117" s="50" t="inlineStr"/>
-      <c r="J117" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K117" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L117" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M117" s="53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N117" s="51" t="inlineStr">
-        <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
-        </is>
-      </c>
+    <row r="117" ht="8" customHeight="1">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
+      <c r="H117" s="9" t="n"/>
+      <c r="I117" s="9" t="n"/>
+      <c r="J117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
+      <c r="L117" s="9" t="n"/>
+      <c r="M117" s="9" t="n"/>
+      <c r="N117" s="9" t="n"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="49" t="inlineStr">
@@ -8339,12 +8327,12 @@
       </c>
       <c r="C118" s="50" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>UALANI_DOCK_01</t>
         </is>
       </c>
       <c r="D118" s="51" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -8390,7 +8378,7 @@
       </c>
       <c r="N118" s="51" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8395,12 @@
       </c>
       <c r="C119" s="50" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>UALANI_FARM_01</t>
         </is>
       </c>
       <c r="D119" s="51" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -8458,7 +8446,7 @@
       </c>
       <c r="N119" s="51" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
         </is>
       </c>
     </row>
@@ -8475,12 +8463,12 @@
       </c>
       <c r="C120" s="50" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>UALANI_BARRACKS_01</t>
         </is>
       </c>
       <c r="D120" s="51" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -8526,7 +8514,7 @@
       </c>
       <c r="N120" s="51" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
         </is>
       </c>
     </row>
@@ -8538,17 +8526,17 @@
       </c>
       <c r="B121" s="49" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C121" s="50" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
       <c r="D121" s="51" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -8577,20 +8565,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K121" s="53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L121" s="50" t="inlineStr"/>
+      <c r="K121" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L121" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M121" s="53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N121" s="51" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
@@ -8607,12 +8599,12 @@
       </c>
       <c r="C122" s="50" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>CL_WASHINGTON_01</t>
         </is>
       </c>
       <c r="D122" s="51" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -8654,7 +8646,7 @@
       </c>
       <c r="N122" s="51" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
@@ -8671,12 +8663,12 @@
       </c>
       <c r="C123" s="50" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
       <c r="D123" s="51" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -8718,7 +8710,7 @@
       </c>
       <c r="N123" s="51" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
@@ -8730,17 +8722,17 @@
       </c>
       <c r="B124" s="49" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C124" s="50" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>CX_NYC_01</t>
         </is>
       </c>
       <c r="D124" s="51" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -8782,7 +8774,7 @@
       </c>
       <c r="N124" s="51" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
@@ -8794,32 +8786,32 @@
       </c>
       <c r="B125" s="49" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>Espionage Events</t>
         </is>
       </c>
       <c r="C125" s="50" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
       <c r="D125" s="51" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E125" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F125" s="51" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G125" s="51" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H125" s="52" t="inlineStr">
@@ -8846,7 +8838,7 @@
       </c>
       <c r="N125" s="51" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8850,32 @@
       </c>
       <c r="B126" s="49" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Commander Expansion</t>
         </is>
       </c>
       <c r="C126" s="50" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>CMD_OBJECTIVE_2</t>
         </is>
       </c>
       <c r="D126" s="51" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E126" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F126" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CMD_OBJECTIVE_1</t>
         </is>
       </c>
       <c r="G126" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ CMD_OBJECTIVE_3?</t>
         </is>
       </c>
       <c r="H126" s="52" t="inlineStr">
@@ -8910,7 +8902,7 @@
       </c>
       <c r="N126" s="51" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
@@ -8927,12 +8919,12 @@
       </c>
       <c r="C127" s="50" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>WINTER_SIEGE_01</t>
         </is>
       </c>
       <c r="D127" s="51" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -8974,47 +8966,111 @@
       </c>
       <c r="N127" s="51" t="inlineStr">
         <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="49" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B128" s="49" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C128" s="50" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F128" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H128" s="52" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I128" s="50" t="inlineStr"/>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K128" s="53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L128" s="50" t="inlineStr"/>
+      <c r="M128" s="53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N128" s="51" t="inlineStr">
+        <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="54" t="inlineStr">
-        <is>
-          <t>Total events in spreadsheet</t>
-        </is>
-      </c>
-      <c r="B129" s="55" t="n">
-        <v>116</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="54" t="inlineStr">
         <is>
-          <t>FIRST PASS (coded &amp; wired)</t>
+          <t>Total events in spreadsheet</t>
         </is>
       </c>
       <c r="B130" s="55" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="54" t="inlineStr">
         <is>
-          <t>IDEA (not yet implemented)</t>
+          <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
       <c r="B131" s="55" t="n">
-        <v>11</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="54" t="inlineStr">
         <is>
+          <t>IDEA (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="B132" s="55" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="54" t="inlineStr">
+        <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B132" s="55" t="n">
+      <c r="B133" s="55" t="n">
         <v>35</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -184,7 +184,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -278,6 +278,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F5E6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE0F7"/>
       </patternFill>
     </fill>
@@ -328,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -481,10 +486,22 @@
     <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -496,10 +513,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -508,10 +525,10 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -520,10 +537,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -532,10 +549,10 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -620,6 +637,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -987,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8315,24 +8338,24 @@
       <c r="N117" s="9" t="n"/>
     </row>
     <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="49" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B118" s="49" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C118" s="50" t="inlineStr">
-        <is>
-          <t>UALANI_DOCK_01</t>
-        </is>
-      </c>
-      <c r="D118" s="51" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+      <c r="A118" s="41" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B118" s="41" t="inlineStr">
+        <is>
+          <t>Election Arc</t>
+        </is>
+      </c>
+      <c r="C118" s="42" t="inlineStr">
+        <is>
+          <t>ELECTION_SEASON</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="inlineStr">
+        <is>
+          <t>UALANI'S TERM IS ENDING — THE REPUBLIC MUST CHOOSE A SUCCESSOR</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -8340,335 +8363,275 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F118" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G118" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H118" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I118" s="50" t="inlineStr"/>
+      <c r="F118" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I118" s="42" t="inlineStr"/>
       <c r="J118" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K118" s="26" t="inlineStr">
+      <c r="K118" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L118" s="42" t="inlineStr"/>
+      <c r="M118" s="44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N118" s="43" t="inlineStr">
+        <is>
+          <t>Fires once turns 93-95; presents 5 faction endorsement buttons; ELECTION_BTN1 gated by !vp_declined_candidacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="41" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B119" s="41" t="inlineStr">
+        <is>
+          <t>Election Arc</t>
+        </is>
+      </c>
+      <c r="C119" s="42" t="inlineStr">
+        <is>
+          <t>STUMP_SPEECH_01</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — THE CAMPAIGN IS HERE</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F119" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I119" s="42" t="inlineStr"/>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K119" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L118" s="50" t="inlineStr">
+      <c r="L119" s="42" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M118" s="53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N118" s="51" t="inlineStr">
-        <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="30" customHeight="1">
-      <c r="A119" s="49" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B119" s="49" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C119" s="50" t="inlineStr">
-        <is>
-          <t>UALANI_FARM_01</t>
-        </is>
-      </c>
-      <c r="D119" s="51" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F119" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G119" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I119" s="50" t="inlineStr"/>
-      <c r="J119" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K119" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L119" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M119" s="53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N119" s="51" t="inlineStr">
-        <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+      <c r="M119" s="44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N119" s="43" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse turns 90-100; BTN1 +15 pressure / BTN2 explicit +25 pressure</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
-      <c r="A120" s="49" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B120" s="49" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C120" s="50" t="inlineStr">
-        <is>
-          <t>UALANI_BARRACKS_01</t>
-        </is>
-      </c>
-      <c r="D120" s="51" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F120" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G120" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H120" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I120" s="50" t="inlineStr"/>
+      <c r="A120" s="41" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B120" s="41" t="inlineStr">
+        <is>
+          <t>Election Arc</t>
+        </is>
+      </c>
+      <c r="C120" s="42" t="inlineStr">
+        <is>
+          <t>ELECTION_NIGHT_WIN</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="inlineStr">
+        <is>
+          <t>THE REPUBLIC ENDURES: UALANI'S COALITION CARRIES THE ELECTION</t>
+        </is>
+      </c>
+      <c r="E120" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F120" s="43" t="inlineStr">
+        <is>
+          <t>turn 100 (pressure &gt; 0)</t>
+        </is>
+      </c>
+      <c r="G120" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I120" s="42" t="inlineStr"/>
       <c r="J120" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K120" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L120" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M120" s="53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N120" s="51" t="inlineStr">
-        <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+      <c r="K120" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L120" s="42" t="inlineStr"/>
+      <c r="M120" s="44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N120" s="43" t="inlineStr">
+        <is>
+          <t>End-game WIN; fires when sum(electionPressure) &gt; 0 at turn 100</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
-      <c r="A121" s="49" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B121" s="49" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C121" s="50" t="inlineStr">
-        <is>
-          <t>UALANI_COURTHOUSE_01</t>
-        </is>
-      </c>
-      <c r="D121" s="51" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F121" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G121" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H121" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I121" s="50" t="inlineStr"/>
+      <c r="A121" s="41" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B121" s="41" t="inlineStr">
+        <is>
+          <t>Election Arc</t>
+        </is>
+      </c>
+      <c r="C121" s="42" t="inlineStr">
+        <is>
+          <t>ELECTION_NIGHT_LOSE</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="inlineStr">
+        <is>
+          <t>WELL. THIS IS SOMETHING: KING GEORGE III WINS THE AMERICAN POPULAR VOTE</t>
+        </is>
+      </c>
+      <c r="E121" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F121" s="43" t="inlineStr">
+        <is>
+          <t>turn 100 (pressure ≤ 0)</t>
+        </is>
+      </c>
+      <c r="G121" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I121" s="42" t="inlineStr"/>
       <c r="J121" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K121" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L121" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M121" s="53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N121" s="51" t="inlineStr">
-        <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="49" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B122" s="49" t="inlineStr">
-        <is>
-          <t>More City Events</t>
-        </is>
-      </c>
-      <c r="C122" s="50" t="inlineStr">
-        <is>
-          <t>CL_WASHINGTON_01</t>
-        </is>
-      </c>
-      <c r="D122" s="51" t="inlineStr">
-        <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F122" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G122" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H122" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I122" s="50" t="inlineStr"/>
-      <c r="J122" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K122" s="53" t="inlineStr">
+      <c r="K121" s="44" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L122" s="50" t="inlineStr"/>
-      <c r="M122" s="53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N122" s="51" t="inlineStr">
-        <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
-        </is>
-      </c>
+      <c r="L121" s="42" t="inlineStr"/>
+      <c r="M121" s="44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N121" s="43" t="inlineStr">
+        <is>
+          <t>End-game LOSE; fires when sum(electionPressure) ≤ 0 at turn 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="8" customHeight="1">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="9" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="9" t="n"/>
+      <c r="H122" s="9" t="n"/>
+      <c r="I122" s="9" t="n"/>
+      <c r="J122" s="9" t="n"/>
+      <c r="K122" s="9" t="n"/>
+      <c r="L122" s="9" t="n"/>
+      <c r="M122" s="9" t="n"/>
+      <c r="N122" s="9" t="n"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="49" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B123" s="49" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C123" s="50" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>VP_FIRST_MEETING</t>
         </is>
       </c>
       <c r="D123" s="51" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>THE VICE PRESIDENT REQUESTS A WORD: [COMMANDER_NAME] MAKES THEIR POSITION CLEAR</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -8686,9 +8649,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H123" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I123" s="50" t="inlineStr"/>
@@ -8697,52 +8660,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K123" s="53" t="inlineStr">
+      <c r="K123" s="52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L123" s="50" t="inlineStr"/>
-      <c r="M123" s="53" t="inlineStr">
+      <c r="M123" s="52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N123" s="51" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Fires turn 5+, one-time; sets vp_met flag; gates all other VP events</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="49" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B124" s="49" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C124" s="50" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>VP_COUNSEL</t>
         </is>
       </c>
       <c r="D124" s="51" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE VICE PRESIDENT ARRIVES LATE WITH GOOD ADVICE: [COMMANDER_NAME] READS THE SITUATION</t>
+        </is>
+      </c>
+      <c r="E124" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F124" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
         </is>
       </c>
       <c r="G124" s="51" t="inlineStr">
@@ -8750,9 +8713,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H124" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I124" s="50" t="inlineStr"/>
@@ -8761,52 +8724,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K124" s="53" t="inlineStr">
+      <c r="K124" s="52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L124" s="50" t="inlineStr"/>
-      <c r="M124" s="53" t="inlineStr">
+      <c r="M124" s="52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N124" s="51" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Fires when presidentialClaim &lt; -2; BTN1 morale +10 / BTN2 loyalty vp_faction +10</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="49" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B125" s="49" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C125" s="50" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>VP_DOUBT</t>
         </is>
       </c>
       <c r="D125" s="51" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QUESTIONING EVERYTHING</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F125" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
         </is>
       </c>
       <c r="G125" s="51" t="inlineStr">
@@ -8814,9 +8777,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H125" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I125" s="50" t="inlineStr"/>
@@ -8825,62 +8788,66 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K125" s="53" t="inlineStr">
+      <c r="K125" s="52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L125" s="50" t="inlineStr"/>
-      <c r="M125" s="53" t="inlineStr">
+      <c r="L125" s="50" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M125" s="52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N125" s="51" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Fires when VP tile moralDecay &gt;= 30; BTN2 sensual morale +25</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="49" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B126" s="49" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C126" s="50" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>VP_LOYALTY_TEST</t>
         </is>
       </c>
       <c r="D126" s="51" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E126" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>[COMMANDER_NAME]'S COALITION WANTS ANSWERS — THE FACTION DEMANDS A PUBLIC STATEMENT</t>
+        </is>
+      </c>
+      <c r="E126" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F126" s="51" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
         </is>
       </c>
       <c r="G126" s="51" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
-        </is>
-      </c>
-      <c r="H126" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I126" s="50" t="inlineStr"/>
@@ -8889,52 +8856,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K126" s="53" t="inlineStr">
+      <c r="K126" s="52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L126" s="50" t="inlineStr"/>
-      <c r="M126" s="53" t="inlineStr">
+      <c r="M126" s="52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N126" s="51" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Fires when VP faction loyalty &lt; 20; BTN1 vp_faction +15 / BTN2 vp_faction +5</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="49" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B127" s="49" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C127" s="50" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>VP_BATTLEFIELD</t>
         </is>
       </c>
       <c r="D127" s="51" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAME] AT THE FRONT LINE</t>
+        </is>
+      </c>
+      <c r="E127" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F127" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
         </is>
       </c>
       <c r="G127" s="51" t="inlineStr">
@@ -8942,9 +8909,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H127" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I127" s="50" t="inlineStr"/>
@@ -8953,52 +8920,56 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K127" s="53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L127" s="50" t="inlineStr"/>
-      <c r="M127" s="53" t="inlineStr">
+      <c r="K127" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L127" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M127" s="52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N127" s="51" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Fires when VP tile has UK neighbor + stationed army; BTN2 explicit morale +30</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="49" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B128" s="49" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C128" s="50" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>VP_PRE_ELECTION</t>
         </is>
       </c>
       <c r="D128" s="51" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [COMMANDER_NAME] ISN'T SURE THEY WANT TO RUN</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F128" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
         </is>
       </c>
       <c r="G128" s="51" t="inlineStr">
@@ -9006,9 +8977,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H128" s="52" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I128" s="50" t="inlineStr"/>
@@ -9017,61 +8988,997 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K128" s="53" t="inlineStr">
+      <c r="K128" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L128" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M128" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N128" s="51" t="inlineStr">
+        <is>
+          <t>Fires turns 88-92; BTN1 sets vp_declined_candidacy (hides ELECTION_BTN1); BTN2 explicit morale +20</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B129" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C129" s="50" t="inlineStr">
+        <is>
+          <t>VP_SACRIFICE</t>
+        </is>
+      </c>
+      <c r="D129" s="51" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT OFFERS THEIR RESIGNATION — [COMMANDER_NAME] WANTS TO PROTECT THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="E129" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F129" s="51" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
+        </is>
+      </c>
+      <c r="G129" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I129" s="50" t="inlineStr"/>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K129" s="52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L128" s="50" t="inlineStr"/>
-      <c r="M128" s="53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N128" s="51" t="inlineStr">
+      <c r="L129" s="50" t="inlineStr"/>
+      <c r="M129" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N129" s="51" t="inlineStr">
+        <is>
+          <t>Fires when VP tile electionPressure &lt; -20; BTN1 sets vp_resigned / BTN2 vp_faction +10</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B130" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C130" s="50" t="inlineStr">
+        <is>
+          <t>VP_SOLIDARITY</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT HAS BEEN PAYING ATTENTION — [COMMANDER_NAME] MAKES A SPECIFIC OBSERVATION</t>
+        </is>
+      </c>
+      <c r="E130" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F130" s="51" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (vp_met flag)</t>
+        </is>
+      </c>
+      <c r="G130" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I130" s="50" t="inlineStr"/>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K130" s="52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L130" s="50" t="inlineStr"/>
+      <c r="M130" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N130" s="51" t="inlineStr">
+        <is>
+          <t>Fires when agreed_protectors &gt;= 3; BTN1 morale +15 / BTN2 vp_faction +10</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B131" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C131" s="50" t="inlineStr">
+        <is>
+          <t>VP_LEGACY</t>
+        </is>
+      </c>
+      <c r="D131" s="51" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
+        </is>
+      </c>
+      <c r="E131" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F131" s="51" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (turn 96+)</t>
+        </is>
+      </c>
+      <c r="G131" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I131" s="50" t="inlineStr"/>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K131" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L131" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M131" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N131" s="51" t="inlineStr">
+        <is>
+          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="9" t="n"/>
+      <c r="H132" s="9" t="n"/>
+      <c r="I132" s="9" t="n"/>
+      <c r="J132" s="9" t="n"/>
+      <c r="K132" s="9" t="n"/>
+      <c r="L132" s="9" t="n"/>
+      <c r="M132" s="9" t="n"/>
+      <c r="N132" s="9" t="n"/>
+    </row>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B133" s="53" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C133" s="54" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D133" s="55" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F133" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H133" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I133" s="54" t="inlineStr"/>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K133" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L133" s="54" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M133" s="57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N133" s="55" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B134" s="53" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C134" s="54" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D134" s="55" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F134" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G134" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I134" s="54" t="inlineStr"/>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K134" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L134" s="54" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M134" s="57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N134" s="55" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B135" s="53" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C135" s="54" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D135" s="55" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F135" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G135" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H135" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I135" s="54" t="inlineStr"/>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K135" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L135" s="54" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M135" s="57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N135" s="55" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B136" s="53" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C136" s="54" t="inlineStr">
+        <is>
+          <t>UALANI_COURTHOUSE_01</t>
+        </is>
+      </c>
+      <c r="D136" s="55" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F136" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G136" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H136" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I136" s="54" t="inlineStr"/>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K136" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L136" s="54" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M136" s="57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N136" s="55" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B137" s="53" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C137" s="54" t="inlineStr">
+        <is>
+          <t>CL_WASHINGTON_01</t>
+        </is>
+      </c>
+      <c r="D137" s="55" t="inlineStr">
+        <is>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F137" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G137" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I137" s="54" t="inlineStr"/>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K137" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L137" s="54" t="inlineStr"/>
+      <c r="M137" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N137" s="55" t="inlineStr">
+        <is>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B138" s="53" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C138" s="54" t="inlineStr">
+        <is>
+          <t>CL_VALLEY_FORGE_01</t>
+        </is>
+      </c>
+      <c r="D138" s="55" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F138" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H138" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I138" s="54" t="inlineStr"/>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K138" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L138" s="54" t="inlineStr"/>
+      <c r="M138" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N138" s="55" t="inlineStr">
+        <is>
+          <t>Tile 1; historically significant; would fire on liberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B139" s="53" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C139" s="54" t="inlineStr">
+        <is>
+          <t>CX_NYC_01</t>
+        </is>
+      </c>
+      <c r="D139" s="55" t="inlineStr">
+        <is>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F139" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G139" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I139" s="54" t="inlineStr"/>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K139" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L139" s="54" t="inlineStr"/>
+      <c r="M139" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N139" s="55" t="inlineStr">
+        <is>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B140" s="53" t="inlineStr">
+        <is>
+          <t>Espionage Events</t>
+        </is>
+      </c>
+      <c r="C140" s="54" t="inlineStr">
+        <is>
+          <t>ESPIONAGE_DISCOVERY_01</t>
+        </is>
+      </c>
+      <c r="D140" s="55" t="inlineStr">
+        <is>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F140" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I140" s="54" t="inlineStr"/>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K140" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L140" s="54" t="inlineStr"/>
+      <c r="M140" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N140" s="55" t="inlineStr">
+        <is>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B141" s="53" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C141" s="54" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D141" s="55" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F141" s="55" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G141" s="55" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H141" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I141" s="54" t="inlineStr"/>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K141" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L141" s="54" t="inlineStr"/>
+      <c r="M141" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N141" s="55" t="inlineStr">
+        <is>
+          <t>Extend the commander arc beyond first objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B142" s="53" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C142" s="54" t="inlineStr">
+        <is>
+          <t>WINTER_SIEGE_01</t>
+        </is>
+      </c>
+      <c r="D142" s="55" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F142" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G142" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H142" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I142" s="54" t="inlineStr"/>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K142" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L142" s="54" t="inlineStr"/>
+      <c r="M142" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N142" s="55" t="inlineStr">
+        <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="53" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B143" s="53" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C143" s="54" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D143" s="55" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F143" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G143" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="56" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I143" s="54" t="inlineStr"/>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K143" s="57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L143" s="54" t="inlineStr"/>
+      <c r="M143" s="57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N143" s="55" t="inlineStr">
         <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="54" t="inlineStr">
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="58" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B130" s="55" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="54" t="inlineStr">
+      <c r="B145" s="59" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="58" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B131" s="55" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="54" t="inlineStr">
+      <c r="B146" s="59" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="58" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B132" s="55" t="n">
+      <c r="B147" s="59" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="54" t="inlineStr">
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="58" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B133" s="55" t="n">
-        <v>35</v>
+      <c r="B148" s="59" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -9085,7 +9992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9094,325 +10001,334 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>Final pass done — art integrated, text finalized, fully tested</t>
         </is>
       </c>
-      <c r="C2" s="58" t="n"/>
+      <c r="C2" s="62" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>Event is coded, in CSV, all buttons wired; no final polish yet</t>
         </is>
       </c>
-      <c r="C3" s="60" t="n"/>
+      <c r="C3" s="64" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>Concept stage: not in events.csv; some referenced in button CSV</t>
         </is>
       </c>
-      <c r="C4" s="62" t="n"/>
+      <c r="C4" s="66" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="56" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>ART STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="63" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>No art asset exists yet</t>
         </is>
       </c>
-      <c r="C7" s="64" t="n"/>
+      <c r="C7" s="68" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Art is being created but not in engine</t>
         </is>
       </c>
-      <c r="C8" s="62" t="n"/>
+      <c r="C8" s="66" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="B9" s="66" t="inlineStr">
+      <c r="B9" s="70" t="inlineStr">
         <is>
           <t>Art is in the project and referenced correctly</t>
         </is>
       </c>
-      <c r="C9" s="66" t="n"/>
+      <c r="C9" s="70" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>EXPLICIT ART LEGEND</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>YES — Explicit Art Needed</t>
         </is>
       </c>
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Event has explicit or kinky_lewd content flag OR has at least one explicit button option that will need unique explicit artwork</t>
         </is>
       </c>
-      <c r="C12" s="68" t="n"/>
+      <c r="C12" s="72" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="69" t="inlineStr">
+      <c r="A13" s="73" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B13" s="74" t="inlineStr">
         <is>
           <t>Standard event — no adult artwork required</t>
         </is>
       </c>
-      <c r="C13" s="70" t="n"/>
+      <c r="C13" s="74" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>CHAIN POSITION LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B16" s="72" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
         <is>
           <t>Standalone event or first event in a chain; fires from world.gd check function or EventDatabase date trigger</t>
         </is>
       </c>
-      <c r="C16" s="72" t="n"/>
+      <c r="C16" s="76" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B17" s="78" t="inlineStr">
         <is>
           <t>Fires as outcome of a choice button on a Root/prior event; represents one path in a fork</t>
         </is>
       </c>
-      <c r="C17" s="74" t="n"/>
+      <c r="C17" s="78" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="79" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="B18" s="76" t="inlineStr">
+      <c r="B18" s="80" t="inlineStr">
         <is>
           <t>Fires automatically after a mission completes (via next_event_id or mission flag return)</t>
         </is>
       </c>
-      <c r="C18" s="76" t="n"/>
+      <c r="C18" s="80" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>CATEGORY COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="77" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B21" s="78" t="inlineStr">
+      <c r="B21" s="82" t="inlineStr">
         <is>
           <t>Calendar-triggered events; month or turn-based</t>
         </is>
       </c>
-      <c r="C21" s="78" t="n"/>
+      <c r="C21" s="82" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="79" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>City Liberated</t>
         </is>
       </c>
-      <c r="B22" s="80" t="inlineStr">
+      <c r="B22" s="84" t="inlineStr">
         <is>
           <t>Fires when a specific tile is liberated (city_liberated type)</t>
         </is>
       </c>
-      <c r="C22" s="80" t="n"/>
+      <c r="C22" s="84" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="81" t="inlineStr">
+      <c r="A23" s="85" t="inlineStr">
         <is>
           <t>City Lost</t>
         </is>
       </c>
-      <c r="B23" s="82" t="inlineStr">
+      <c r="B23" s="86" t="inlineStr">
         <is>
           <t>Fires when a specific tile falls to the enemy (city_lost type)</t>
         </is>
       </c>
-      <c r="C23" s="82" t="n"/>
+      <c r="C23" s="86" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="83" t="inlineStr">
+      <c r="A24" s="87" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B24" s="84" t="inlineStr">
+      <c r="B24" s="88" t="inlineStr">
         <is>
           <t>State-level liberation, secession, and reintegration</t>
         </is>
       </c>
-      <c r="C24" s="84" t="n"/>
+      <c r="C24" s="88" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="85" t="inlineStr">
+      <c r="A25" s="89" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B25" s="86" t="inlineStr">
+      <c r="B25" s="90" t="inlineStr">
         <is>
           <t>Mythological entity summon events (protector_summon type)</t>
         </is>
       </c>
-      <c r="C25" s="86" t="n"/>
+      <c r="C25" s="90" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="87" t="inlineStr">
+      <c r="A26" s="91" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B26" s="88" t="inlineStr">
+      <c r="B26" s="92" t="inlineStr">
         <is>
           <t>Named commander arc events (commander_* types)</t>
         </is>
       </c>
-      <c r="C26" s="88" t="n"/>
+      <c r="C26" s="92" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="89" t="inlineStr">
+      <c r="A27" s="93" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B27" s="90" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>Fort disrepair investigation chain (fort_* types)</t>
         </is>
       </c>
-      <c r="C27" s="90" t="n"/>
+      <c r="C27" s="94" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="91" t="inlineStr">
+      <c r="A28" s="95" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B28" s="92" t="inlineStr">
+      <c r="B28" s="96" t="inlineStr">
         <is>
           <t>Republic collapse sequence</t>
         </is>
       </c>
-      <c r="C28" s="92" t="n"/>
+      <c r="C28" s="96" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="93" t="inlineStr">
+      <c r="A29" s="97" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B29" s="94" t="inlineStr">
+      <c r="B29" s="98" t="inlineStr">
         <is>
           <t>Dynamic tile-based crisis chains; triggered by world.gd check functions</t>
         </is>
       </c>
-      <c r="C29" s="94" t="n"/>
+      <c r="C29" s="98" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="95" t="inlineStr">
+      <c r="A30" s="99" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B30" s="96" t="inlineStr">
+      <c r="B30" s="100" t="inlineStr">
         <is>
           <t>Ualani Carlisle army presence events; personal storyline</t>
         </is>
       </c>
-      <c r="C30" s="96" t="n"/>
+      <c r="C30" s="100" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="97" t="inlineStr">
+      <c r="A31" s="101" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B31" s="102" t="inlineStr"/>
+      <c r="C31" s="102" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="103" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B31" s="98" t="inlineStr">
+      <c r="B32" s="104" t="inlineStr">
         <is>
           <t>Not yet implemented; concept stage or referenced-but-missing events</t>
         </is>
       </c>
-      <c r="C31" s="98" t="n"/>
+      <c r="C32" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -333,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -489,6 +489,18 @@
     <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -637,6 +649,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1010,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9137,119 +9155,115 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="30" customHeight="1">
-      <c r="A131" s="49" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="B131" s="49" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="C131" s="50" t="inlineStr">
-        <is>
-          <t>VP_LEGACY</t>
-        </is>
-      </c>
-      <c r="D131" s="51" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
-        </is>
-      </c>
-      <c r="E131" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
-        </is>
-      </c>
-      <c r="F131" s="51" t="inlineStr">
-        <is>
-          <t>VP_FIRST_MEETING (turn 96+)</t>
-        </is>
-      </c>
-      <c r="G131" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H131" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I131" s="50" t="inlineStr"/>
-      <c r="J131" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K131" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L131" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M131" s="52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N131" s="51" t="inlineStr">
-        <is>
-          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="8" customHeight="1">
-      <c r="A132" s="9" t="n"/>
-      <c r="B132" s="9" t="n"/>
-      <c r="C132" s="9" t="n"/>
-      <c r="D132" s="9" t="n"/>
-      <c r="E132" s="9" t="n"/>
-      <c r="F132" s="9" t="n"/>
-      <c r="G132" s="9" t="n"/>
-      <c r="H132" s="9" t="n"/>
-      <c r="I132" s="9" t="n"/>
-      <c r="J132" s="9" t="n"/>
-      <c r="K132" s="9" t="n"/>
-      <c r="L132" s="9" t="n"/>
-      <c r="M132" s="9" t="n"/>
-      <c r="N132" s="9" t="n"/>
+    <row r="131" ht="8" customHeight="1">
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="9" t="n"/>
+      <c r="G131" s="9" t="n"/>
+      <c r="H131" s="9" t="n"/>
+      <c r="I131" s="9" t="n"/>
+      <c r="J131" s="9" t="n"/>
+      <c r="K131" s="9" t="n"/>
+      <c r="L131" s="9" t="n"/>
+      <c r="M131" s="9" t="n"/>
+      <c r="N131" s="9" t="n"/>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B132" s="53" t="inlineStr">
+        <is>
+          <t>War Arc</t>
+        </is>
+      </c>
+      <c r="C132" s="54" t="inlineStr">
+        <is>
+          <t>UK_BUILDUP_01</t>
+        </is>
+      </c>
+      <c r="D132" s="55" t="inlineStr">
+        <is>
+          <t>INTELLIGENCE REPORT: CROWN FORCES AMASSING ON ALL BORDERS</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F132" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G132" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_CALL_01 (uk_buildup_known flag)</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I132" s="54" t="inlineStr"/>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K132" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L132" s="54" t="inlineStr"/>
+      <c r="M132" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N132" s="55" t="inlineStr">
+        <is>
+          <t>Fires turn 7, one-time; BTN1 alert / BTN2 contact Ottawa; both set uk_buildup_known</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B133" s="53" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>War Arc</t>
         </is>
       </c>
       <c r="C133" s="54" t="inlineStr">
         <is>
-          <t>UALANI_DOCK_01</t>
+          <t>UK_DECLARATION_01</t>
         </is>
       </c>
       <c r="D133" s="55" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>KING GEORGE III DECLARES WAR: THE CROWN HAS MOVED ON BOTH FRONTS</t>
+        </is>
+      </c>
+      <c r="E133" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F133" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UK_BUILDUP_01</t>
         </is>
       </c>
       <c r="G133" s="55" t="inlineStr">
@@ -9257,9 +9271,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H133" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I133" s="54" t="inlineStr"/>
@@ -9268,46 +9282,42 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K133" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L133" s="54" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M133" s="57" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K133" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L133" s="54" t="inlineStr"/>
+      <c r="M133" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N133" s="55" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+          <t>Fires turns 10-16 (30%/turn) once uk_buildup_known; sets uk_declared_war</t>
         </is>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B134" s="53" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C134" s="54" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>CAN_CALL_01</t>
         </is>
       </c>
       <c r="D134" s="55" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>THE OTTAWA CALL: PRESIDENT PENOIT AND PM CLEAR-WATER ARE ON THE LINE</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -9317,17 +9327,17 @@
       </c>
       <c r="F134" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UK_BUILDUP_01 (flag)</t>
         </is>
       </c>
       <c r="G134" s="55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H134" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CAN_PENOIT_01 (BTN1) or END (BTN2)</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I134" s="54" t="inlineStr"/>
@@ -9336,66 +9346,62 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K134" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L134" s="54" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M134" s="57" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K134" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L134" s="54" t="inlineStr"/>
+      <c r="M134" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N134" s="55" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Fires turn 8+ after uk_buildup_known; BTN1 sets can_contact / BTN2 sets can_rejected (ends arc)</t>
         </is>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B135" s="53" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C135" s="54" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>CAN_PENOIT_01</t>
         </is>
       </c>
       <c r="D135" s="55" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>PRESIDENT PENOIT'S CONDITIONS: MARK PENOIT PUTS IT IN WRITING</t>
+        </is>
+      </c>
+      <c r="E135" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F135" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAN_CALL_01 (can_contact)</t>
         </is>
       </c>
       <c r="G135" s="55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H135" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CAN_CLEARWATER_01</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I135" s="54" t="inlineStr"/>
@@ -9404,66 +9410,62 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K135" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L135" s="54" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M135" s="57" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K135" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L135" s="54" t="inlineStr"/>
+      <c r="M135" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N135" s="55" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Fires turn 12+ after can_contact; BTN1 can_penoit_agreed / BTN2 can_penoit_negotiating</t>
         </is>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B136" s="53" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C136" s="54" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>CAN_CLEARWATER_01</t>
         </is>
       </c>
       <c r="D136" s="55" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUTSIDE OFFICIAL CHANNELS</t>
+        </is>
+      </c>
+      <c r="E136" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F136" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAN_PENOIT_01</t>
         </is>
       </c>
       <c r="G136" s="55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H136" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CAN_JOINT_OPS_01</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I136" s="54" t="inlineStr"/>
@@ -9472,66 +9474,66 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K136" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K136" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L136" s="54" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M136" s="57" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M136" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N136" s="55" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>After penoit path + can_contact; BTN1 can_clearwater_warm / BTN2 sensual can_clearwater_close</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B137" s="53" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C137" s="54" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>CAN_JOINT_OPS_01</t>
         </is>
       </c>
       <c r="D137" s="55" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE ONE MAP</t>
+        </is>
+      </c>
+      <c r="E137" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F137" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAN_CLEARWATER_01</t>
         </is>
       </c>
       <c r="G137" s="55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H137" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CAN_SUMMIT_01</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I137" s="54" t="inlineStr"/>
@@ -9540,62 +9542,66 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K137" s="57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L137" s="54" t="inlineStr"/>
-      <c r="M137" s="57" t="inlineStr">
+      <c r="K137" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L137" s="54" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M137" s="56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N137" s="55" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>After penoit+clearwater paths; BTN1 +weapons 20 / BTN2 explicit +morale 25</t>
         </is>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B138" s="53" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C138" s="54" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>CAN_SUMMIT_01</t>
         </is>
       </c>
       <c r="D138" s="55" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR THE FIRST TIME</t>
+        </is>
+      </c>
+      <c r="E138" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F138" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAN_JOINT_OPS_01</t>
         </is>
       </c>
       <c r="G138" s="55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H138" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CAN_ALLIANCE_SIGNED</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I138" s="54" t="inlineStr"/>
@@ -9604,62 +9610,66 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K138" s="57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L138" s="54" t="inlineStr"/>
-      <c r="M138" s="57" t="inlineStr">
+      <c r="K138" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L138" s="54" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="M138" s="56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N138" s="55" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>EXPLICIT #1 (all three); turn 13+, penoit_agreed+clearwater; BTN1/BTN2 set can_summit_complete</t>
         </is>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B139" s="53" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C139" s="54" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>CAN_ALLIANCE_SIGNED</t>
         </is>
       </c>
       <c r="D139" s="55" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE CONTINENTAL DEFENSE ALLIANCE IS SIGNED: THREE NATIONS — ONE FRONT</t>
+        </is>
+      </c>
+      <c r="E139" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F139" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAN_SUMMIT_01</t>
         </is>
       </c>
       <c r="G139" s="55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H139" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CAN_PEACE_01</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I139" s="54" t="inlineStr"/>
@@ -9668,52 +9678,56 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K139" s="57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L139" s="54" t="inlineStr"/>
-      <c r="M139" s="57" t="inlineStr">
+      <c r="K139" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L139" s="54" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="M139" s="56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N139" s="55" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B140" s="53" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C140" s="54" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>CAN_PEACE_01</t>
         </is>
       </c>
       <c r="D140" s="55" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E140" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F140" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAN_ALLIANCE_SIGNED (can_allied flag)</t>
         </is>
       </c>
       <c r="G140" s="55" t="inlineStr">
@@ -9721,9 +9735,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H140" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I140" s="54" t="inlineStr"/>
@@ -9732,42 +9746,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K140" s="57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L140" s="54" t="inlineStr"/>
-      <c r="M140" s="57" t="inlineStr">
+      <c r="K140" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L140" s="54" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="M140" s="56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N140" s="55" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>EXPLICIT #3 (all three); fires when can_allied + UK tiles ≤ 20 + turn ≥ 60; BTN2 +morale 40</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="53" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B141" s="53" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C141" s="54" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>CAN_ELECTION_LUCK</t>
         </is>
       </c>
       <c r="D141" s="55" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY BEFORE THE ELECTION</t>
         </is>
       </c>
       <c r="E141" s="22" t="inlineStr">
@@ -9777,17 +9795,17 @@
       </c>
       <c r="F141" s="55" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>CAN_PEACE_01 (can_allied)</t>
         </is>
       </c>
       <c r="G141" s="55" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
-        </is>
-      </c>
-      <c r="H141" s="56" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I141" s="54" t="inlineStr"/>
@@ -9796,189 +9814,885 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K141" s="57" t="inlineStr">
+      <c r="K141" s="56" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L141" s="54" t="inlineStr"/>
-      <c r="M141" s="57" t="inlineStr">
+      <c r="L141" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M141" s="56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N141" s="55" t="inlineStr">
         <is>
+          <t>End-game; fires turn 93+ if can_allied; BTN1 +pressure 10 / BTN2 sensual +pressure 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="8" customHeight="1">
+      <c r="A142" s="9" t="n"/>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
+      <c r="H142" s="9" t="n"/>
+      <c r="I142" s="9" t="n"/>
+      <c r="J142" s="9" t="n"/>
+      <c r="K142" s="9" t="n"/>
+      <c r="L142" s="9" t="n"/>
+      <c r="M142" s="9" t="n"/>
+      <c r="N142" s="9" t="n"/>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B143" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C143" s="50" t="inlineStr">
+        <is>
+          <t>VP_LEGACY</t>
+        </is>
+      </c>
+      <c r="D143" s="51" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
+        </is>
+      </c>
+      <c r="E143" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F143" s="51" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (turn 96+)</t>
+        </is>
+      </c>
+      <c r="G143" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I143" s="50" t="inlineStr"/>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K143" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L143" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M143" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N143" s="51" t="inlineStr">
+        <is>
+          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="8" customHeight="1">
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
+      <c r="H144" s="9" t="n"/>
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
+      <c r="L144" s="9" t="n"/>
+      <c r="M144" s="9" t="n"/>
+      <c r="N144" s="9" t="n"/>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B145" s="57" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C145" s="58" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D145" s="59" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F145" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I145" s="58" t="inlineStr"/>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K145" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L145" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M145" s="61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N145" s="59" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B146" s="57" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C146" s="58" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D146" s="59" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F146" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G146" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H146" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I146" s="58" t="inlineStr"/>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K146" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L146" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M146" s="61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N146" s="59" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B147" s="57" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C147" s="58" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D147" s="59" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F147" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H147" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I147" s="58" t="inlineStr"/>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K147" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L147" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M147" s="61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N147" s="59" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B148" s="57" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C148" s="58" t="inlineStr">
+        <is>
+          <t>UALANI_COURTHOUSE_01</t>
+        </is>
+      </c>
+      <c r="D148" s="59" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F148" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G148" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I148" s="58" t="inlineStr"/>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K148" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L148" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M148" s="61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N148" s="59" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B149" s="57" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C149" s="58" t="inlineStr">
+        <is>
+          <t>CL_WASHINGTON_01</t>
+        </is>
+      </c>
+      <c r="D149" s="59" t="inlineStr">
+        <is>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F149" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I149" s="58" t="inlineStr"/>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K149" s="61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L149" s="58" t="inlineStr"/>
+      <c r="M149" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N149" s="59" t="inlineStr">
+        <is>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B150" s="57" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C150" s="58" t="inlineStr">
+        <is>
+          <t>CL_VALLEY_FORGE_01</t>
+        </is>
+      </c>
+      <c r="D150" s="59" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F150" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H150" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I150" s="58" t="inlineStr"/>
+      <c r="J150" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K150" s="61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L150" s="58" t="inlineStr"/>
+      <c r="M150" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N150" s="59" t="inlineStr">
+        <is>
+          <t>Tile 1; historically significant; would fire on liberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B151" s="57" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C151" s="58" t="inlineStr">
+        <is>
+          <t>CX_NYC_01</t>
+        </is>
+      </c>
+      <c r="D151" s="59" t="inlineStr">
+        <is>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F151" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H151" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I151" s="58" t="inlineStr"/>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K151" s="61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L151" s="58" t="inlineStr"/>
+      <c r="M151" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N151" s="59" t="inlineStr">
+        <is>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B152" s="57" t="inlineStr">
+        <is>
+          <t>Espionage Events</t>
+        </is>
+      </c>
+      <c r="C152" s="58" t="inlineStr">
+        <is>
+          <t>ESPIONAGE_DISCOVERY_01</t>
+        </is>
+      </c>
+      <c r="D152" s="59" t="inlineStr">
+        <is>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F152" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H152" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I152" s="58" t="inlineStr"/>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K152" s="61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L152" s="58" t="inlineStr"/>
+      <c r="M152" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N152" s="59" t="inlineStr">
+        <is>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="57" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B153" s="57" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C153" s="58" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D153" s="59" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E153" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F153" s="59" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G153" s="59" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H153" s="60" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I153" s="58" t="inlineStr"/>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K153" s="61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L153" s="58" t="inlineStr"/>
+      <c r="M153" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N153" s="59" t="inlineStr">
+        <is>
           <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="30" customHeight="1">
-      <c r="A142" s="53" t="inlineStr">
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="57" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B142" s="53" t="inlineStr">
+      <c r="B154" s="57" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C142" s="54" t="inlineStr">
+      <c r="C154" s="58" t="inlineStr">
         <is>
           <t>WINTER_SIEGE_01</t>
         </is>
       </c>
-      <c r="D142" s="55" t="inlineStr">
+      <c r="D154" s="59" t="inlineStr">
         <is>
           <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E154" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F142" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G142" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H142" s="56" t="inlineStr">
+      <c r="F154" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G154" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H154" s="60" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I142" s="54" t="inlineStr"/>
-      <c r="J142" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K142" s="57" t="inlineStr">
+      <c r="I154" s="58" t="inlineStr"/>
+      <c r="J154" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K154" s="61" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L142" s="54" t="inlineStr"/>
-      <c r="M142" s="57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N142" s="55" t="inlineStr">
+      <c r="L154" s="58" t="inlineStr"/>
+      <c r="M154" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N154" s="59" t="inlineStr">
         <is>
           <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="30" customHeight="1">
-      <c r="A143" s="53" t="inlineStr">
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="57" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B143" s="53" t="inlineStr">
+      <c r="B155" s="57" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C143" s="54" t="inlineStr">
+      <c r="C155" s="58" t="inlineStr">
         <is>
           <t>SPRING_OFFENSIVE_01</t>
         </is>
       </c>
-      <c r="D143" s="55" t="inlineStr">
+      <c r="D155" s="59" t="inlineStr">
         <is>
           <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E155" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F143" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G143" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H143" s="56" t="inlineStr">
+      <c r="F155" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H155" s="60" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I143" s="54" t="inlineStr"/>
-      <c r="J143" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K143" s="57" t="inlineStr">
+      <c r="I155" s="58" t="inlineStr"/>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K155" s="61" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L143" s="54" t="inlineStr"/>
-      <c r="M143" s="57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N143" s="55" t="inlineStr">
+      <c r="L155" s="58" t="inlineStr"/>
+      <c r="M155" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N155" s="59" t="inlineStr">
         <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="58" t="inlineStr">
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="62" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B145" s="59" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="58" t="inlineStr">
+      <c r="B157" s="63" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="62" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B146" s="59" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="58" t="inlineStr">
+      <c r="B158" s="63" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="62" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B147" s="59" t="n">
+      <c r="B159" s="63" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="58" t="inlineStr">
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="62" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B148" s="59" t="n">
-        <v>39</v>
+      <c r="B160" s="63" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -9992,7 +10706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10001,334 +10715,343 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="B2" s="62" t="inlineStr">
+      <c r="B2" s="66" t="inlineStr">
         <is>
           <t>Final pass done — art integrated, text finalized, fully tested</t>
         </is>
       </c>
-      <c r="C2" s="62" t="n"/>
+      <c r="C2" s="66" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="63" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>Event is coded, in CSV, all buttons wired; no final polish yet</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n"/>
+      <c r="C3" s="68" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>Concept stage: not in events.csv; some referenced in button CSV</t>
         </is>
       </c>
-      <c r="C4" s="66" t="n"/>
+      <c r="C4" s="70" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>ART STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="67" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>No art asset exists yet</t>
         </is>
       </c>
-      <c r="C7" s="68" t="n"/>
+      <c r="C7" s="72" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>Art is being created but not in engine</t>
         </is>
       </c>
-      <c r="C8" s="66" t="n"/>
+      <c r="C8" s="70" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="69" t="inlineStr">
+      <c r="A9" s="73" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="B9" s="70" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>Art is in the project and referenced correctly</t>
         </is>
       </c>
-      <c r="C9" s="70" t="n"/>
+      <c r="C9" s="74" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>EXPLICIT ART LEGEND</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>YES — Explicit Art Needed</t>
         </is>
       </c>
-      <c r="B12" s="72" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>Event has explicit or kinky_lewd content flag OR has at least one explicit button option that will need unique explicit artwork</t>
         </is>
       </c>
-      <c r="C12" s="72" t="n"/>
+      <c r="C12" s="76" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="78" t="inlineStr">
         <is>
           <t>Standard event — no adult artwork required</t>
         </is>
       </c>
-      <c r="C13" s="74" t="n"/>
+      <c r="C13" s="78" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>CHAIN POSITION LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="75" t="inlineStr">
+      <c r="A16" s="79" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B16" s="76" t="inlineStr">
+      <c r="B16" s="80" t="inlineStr">
         <is>
           <t>Standalone event or first event in a chain; fires from world.gd check function or EventDatabase date trigger</t>
         </is>
       </c>
-      <c r="C16" s="76" t="n"/>
+      <c r="C16" s="80" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B17" s="78" t="inlineStr">
+      <c r="B17" s="82" t="inlineStr">
         <is>
           <t>Fires as outcome of a choice button on a Root/prior event; represents one path in a fork</t>
         </is>
       </c>
-      <c r="C17" s="78" t="n"/>
+      <c r="C17" s="82" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="79" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="B18" s="80" t="inlineStr">
+      <c r="B18" s="84" t="inlineStr">
         <is>
           <t>Fires automatically after a mission completes (via next_event_id or mission flag return)</t>
         </is>
       </c>
-      <c r="C18" s="80" t="n"/>
+      <c r="C18" s="84" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="64" t="inlineStr">
         <is>
           <t>CATEGORY COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
+      <c r="A21" s="85" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>Calendar-triggered events; month or turn-based</t>
         </is>
       </c>
-      <c r="C21" s="82" t="n"/>
+      <c r="C21" s="86" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="87" t="inlineStr">
         <is>
           <t>City Liberated</t>
         </is>
       </c>
-      <c r="B22" s="84" t="inlineStr">
+      <c r="B22" s="88" t="inlineStr">
         <is>
           <t>Fires when a specific tile is liberated (city_liberated type)</t>
         </is>
       </c>
-      <c r="C22" s="84" t="n"/>
+      <c r="C22" s="88" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="85" t="inlineStr">
+      <c r="A23" s="89" t="inlineStr">
         <is>
           <t>City Lost</t>
         </is>
       </c>
-      <c r="B23" s="86" t="inlineStr">
+      <c r="B23" s="90" t="inlineStr">
         <is>
           <t>Fires when a specific tile falls to the enemy (city_lost type)</t>
         </is>
       </c>
-      <c r="C23" s="86" t="n"/>
+      <c r="C23" s="90" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="87" t="inlineStr">
+      <c r="A24" s="91" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B24" s="88" t="inlineStr">
+      <c r="B24" s="92" t="inlineStr">
         <is>
           <t>State-level liberation, secession, and reintegration</t>
         </is>
       </c>
-      <c r="C24" s="88" t="n"/>
+      <c r="C24" s="92" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="89" t="inlineStr">
+      <c r="A25" s="93" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B25" s="90" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>Mythological entity summon events (protector_summon type)</t>
         </is>
       </c>
-      <c r="C25" s="90" t="n"/>
+      <c r="C25" s="94" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="91" t="inlineStr">
+      <c r="A26" s="95" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="96" t="inlineStr">
         <is>
           <t>Named commander arc events (commander_* types)</t>
         </is>
       </c>
-      <c r="C26" s="92" t="n"/>
+      <c r="C26" s="96" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="93" t="inlineStr">
+      <c r="A27" s="97" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="98" t="inlineStr">
         <is>
           <t>Fort disrepair investigation chain (fort_* types)</t>
         </is>
       </c>
-      <c r="C27" s="94" t="n"/>
+      <c r="C27" s="98" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="95" t="inlineStr">
+      <c r="A28" s="99" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B28" s="96" t="inlineStr">
+      <c r="B28" s="100" t="inlineStr">
         <is>
           <t>Republic collapse sequence</t>
         </is>
       </c>
-      <c r="C28" s="96" t="n"/>
+      <c r="C28" s="100" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="97" t="inlineStr">
+      <c r="A29" s="101" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B29" s="98" t="inlineStr">
+      <c r="B29" s="102" t="inlineStr">
         <is>
           <t>Dynamic tile-based crisis chains; triggered by world.gd check functions</t>
         </is>
       </c>
-      <c r="C29" s="98" t="n"/>
+      <c r="C29" s="102" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="99" t="inlineStr">
+      <c r="A30" s="103" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B30" s="100" t="inlineStr">
+      <c r="B30" s="104" t="inlineStr">
         <is>
           <t>Ualani Carlisle army presence events; personal storyline</t>
         </is>
       </c>
-      <c r="C30" s="100" t="n"/>
+      <c r="C30" s="104" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="101" t="inlineStr">
+      <c r="A31" s="105" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B31" s="102" t="inlineStr"/>
-      <c r="C31" s="102" t="n"/>
+      <c r="B31" s="106" t="inlineStr"/>
+      <c r="C31" s="106" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="103" t="inlineStr">
+      <c r="A32" s="107" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B32" s="108" t="inlineStr"/>
+      <c r="C32" s="108" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="109" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B32" s="104" t="inlineStr">
+      <c r="B33" s="110" t="inlineStr">
         <is>
           <t>Not yet implemented; concept stage or referenced-but-missing events</t>
         </is>
       </c>
-      <c r="C32" s="104" t="n"/>
+      <c r="C33" s="110" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="All Events" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Canadian Events" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -184,7 +185,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -283,6 +284,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00B8D6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE0F7"/>
       </patternFill>
     </fill>
@@ -333,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -510,10 +516,22 @@
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -525,10 +543,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -537,10 +555,10 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -549,10 +567,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -561,10 +579,10 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -661,6 +679,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1028,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9852,39 +9876,39 @@
       <c r="N142" s="9" t="n"/>
     </row>
     <row r="143" ht="30" customHeight="1">
-      <c r="A143" s="49" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="B143" s="49" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="C143" s="50" t="inlineStr">
-        <is>
-          <t>VP_LEGACY</t>
-        </is>
-      </c>
-      <c r="D143" s="51" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
-        </is>
-      </c>
-      <c r="E143" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
-        </is>
-      </c>
-      <c r="F143" s="51" t="inlineStr">
-        <is>
-          <t>VP_FIRST_MEETING (turn 96+)</t>
-        </is>
-      </c>
-      <c r="G143" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A143" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B143" s="57" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C143" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_SUMMON</t>
+        </is>
+      </c>
+      <c r="D143" s="59" t="inlineStr">
+        <is>
+          <t>LE WENDIGO WAKES IN THE LAURENTIAN FOREST</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F143" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G143" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_01_TAME</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
@@ -9892,78 +9916,126 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I143" s="50" t="inlineStr"/>
+      <c r="I143" s="58" t="inlineStr">
+        <is>
+          <t>wendigo_approach</t>
+        </is>
+      </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K143" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L143" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M143" s="52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N143" s="51" t="inlineStr">
-        <is>
-          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="8" customHeight="1">
-      <c r="A144" s="9" t="n"/>
-      <c r="B144" s="9" t="n"/>
-      <c r="C144" s="9" t="n"/>
-      <c r="D144" s="9" t="n"/>
-      <c r="E144" s="9" t="n"/>
-      <c r="F144" s="9" t="n"/>
-      <c r="G144" s="9" t="n"/>
-      <c r="H144" s="9" t="n"/>
-      <c r="I144" s="9" t="n"/>
-      <c r="J144" s="9" t="n"/>
-      <c r="K144" s="9" t="n"/>
-      <c r="L144" s="9" t="n"/>
-      <c r="M144" s="9" t="n"/>
-      <c r="N144" s="9" t="n"/>
+      <c r="K143" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L143" s="58" t="inlineStr"/>
+      <c r="M143" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N143" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn (25% chance) to CA tiles; fires turn 8+; Saint-Georges tile 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B144" s="57" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C144" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_TAME</t>
+        </is>
+      </c>
+      <c r="D144" s="59" t="inlineStr">
+        <is>
+          <t>THE WENDIGO RECEDES FROM THE HARVEST CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E144" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F144" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_SUMMON</t>
+        </is>
+      </c>
+      <c r="G144" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_01_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I144" s="58" t="inlineStr"/>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K144" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L144" s="58" t="inlineStr"/>
+      <c r="M144" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N144" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_01_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B145" s="57" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Le Wendigo</t>
         </is>
       </c>
       <c r="C145" s="58" t="inlineStr">
         <is>
-          <t>UALANI_DOCK_01</t>
+          <t>CA_PROT_01_AGREE</t>
         </is>
       </c>
       <c r="D145" s="59" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD</t>
+        </is>
+      </c>
+      <c r="E145" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F145" s="59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA_PROT_01_TAME</t>
         </is>
       </c>
       <c r="G145" s="59" t="inlineStr">
@@ -9971,9 +10043,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H145" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I145" s="58" t="inlineStr"/>
@@ -9992,36 +10064,36 @@
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M145" s="61" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="M145" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N145" s="59" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+          <t>Sets ca_prot_01_agreed; BTN2 explicit — private dispatch from Jessica</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B146" s="57" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C146" s="58" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>CA_PROT_02_SUMMON</t>
         </is>
       </c>
       <c r="D146" s="59" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>LE LOUP-GAROU RUNS THE RIVER ROAD — RIVIÈRE-DU-LOUP QUARANTINED</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -10036,80 +10108,80 @@
       </c>
       <c r="G146" s="59" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H146" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I146" s="58" t="inlineStr"/>
+          <t>→ CA_PROT_02_TAME</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I146" s="58" t="inlineStr">
+        <is>
+          <t>loup_garou</t>
+        </is>
+      </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K146" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L146" s="58" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M146" s="61" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K146" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L146" s="58" t="inlineStr"/>
+      <c r="M146" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N146" s="59" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 13+; Rivière-du-Loup tile 105</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B147" s="57" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C147" s="58" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>CA_PROT_02_TAME</t>
         </is>
       </c>
       <c r="D147" s="59" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>LE LOUP-GAROU ALLOWS PASSAGE — THE RIVER ROAD REOPENS</t>
+        </is>
+      </c>
+      <c r="E147" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F147" s="59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA_PROT_02_SUMMON</t>
         </is>
       </c>
       <c r="G147" s="59" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H147" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CA_PROT_02_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I147" s="58" t="inlineStr"/>
@@ -10118,56 +10190,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K147" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L147" s="58" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M147" s="61" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K147" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L147" s="58" t="inlineStr"/>
+      <c r="M147" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N147" s="59" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Sets ca_prot_02_tame flag; immediately chains to AGREE</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B148" s="57" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C148" s="58" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>CA_PROT_02_AGREE</t>
         </is>
       </c>
       <c r="D148" s="59" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLEDGED BY THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F148" s="59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA_PROT_02_TAME</t>
         </is>
       </c>
       <c r="G148" s="59" t="inlineStr">
@@ -10175,9 +10243,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H148" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I148" s="58" t="inlineStr"/>
@@ -10196,36 +10264,36 @@
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M148" s="61" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="M148" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N148" s="59" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Sets ca_prot_02_agreed; BTN2 explicit — the wolf stops running</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B149" s="57" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C149" s="58" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>CA_PROT_03_SUMMON</t>
         </is>
       </c>
       <c r="D149" s="59" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>LES FEUX FOLLETS RISE OVER THE SAINT JOHN MARSHES — NAVIGATION DISRUPTED</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -10240,76 +10308,80 @@
       </c>
       <c r="G149" s="59" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H149" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I149" s="58" t="inlineStr"/>
+          <t>→ CA_PROT_03_TAME</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I149" s="58" t="inlineStr">
+        <is>
+          <t>feux_follets</t>
+        </is>
+      </c>
       <c r="J149" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K149" s="61" t="inlineStr">
+      <c r="K149" s="60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L149" s="58" t="inlineStr"/>
-      <c r="M149" s="61" t="inlineStr">
+      <c r="M149" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N149" s="59" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 18+; Saint John tile 194</t>
         </is>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B150" s="57" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C150" s="58" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>CA_PROT_03_TAME</t>
         </is>
       </c>
       <c r="D150" s="59" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>LES FEUX FOLLETS QUIET — MALISEET PROTOCOLS ESTABLISHED</t>
+        </is>
+      </c>
+      <c r="E150" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F150" s="59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA_PROT_03_SUMMON</t>
         </is>
       </c>
       <c r="G150" s="59" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H150" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CA_PROT_03_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I150" s="58" t="inlineStr"/>
@@ -10318,52 +10390,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K150" s="61" t="inlineStr">
+      <c r="K150" s="60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L150" s="58" t="inlineStr"/>
-      <c r="M150" s="61" t="inlineStr">
+      <c r="M150" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N150" s="59" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Sets ca_prot_03_tame flag; immediately chains to AGREE</t>
         </is>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B151" s="57" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C151" s="58" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>CA_PROT_03_AGREE</t>
         </is>
       </c>
       <c r="D151" s="59" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JOHN MARSH ACCORD</t>
+        </is>
+      </c>
+      <c r="E151" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F151" s="59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA_PROT_03_TAME</t>
         </is>
       </c>
       <c r="G151" s="59" t="inlineStr">
@@ -10371,9 +10443,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H151" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I151" s="58" t="inlineStr"/>
@@ -10382,42 +10454,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K151" s="61" t="inlineStr">
+      <c r="K151" s="60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L151" s="58" t="inlineStr"/>
-      <c r="M151" s="61" t="inlineStr">
+      <c r="L151" s="58" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M151" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N151" s="59" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Sets ca_prot_03_agreed; BTN2 sensual — Jessica walks you through the marsh</t>
         </is>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B152" s="57" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C152" s="58" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>CA_PROT_04_SUMMON</t>
         </is>
       </c>
       <c r="D152" s="59" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>MISHEPESHU STIRS BENEATH LAKE SIMCOE — CROSSINGS CONTESTED</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -10432,76 +10508,80 @@
       </c>
       <c r="G152" s="59" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H152" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I152" s="58" t="inlineStr"/>
+          <t>→ CA_PROT_04_TAME</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I152" s="58" t="inlineStr">
+        <is>
+          <t>mishepeshu</t>
+        </is>
+      </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K152" s="61" t="inlineStr">
+      <c r="K152" s="60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L152" s="58" t="inlineStr"/>
-      <c r="M152" s="61" t="inlineStr">
+      <c r="M152" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N152" s="59" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 23+; Barrie tile 131</t>
         </is>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B153" s="57" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C153" s="58" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>CA_PROT_04_TAME</t>
         </is>
       </c>
       <c r="D153" s="59" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E153" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>MISHEPESHU WITHDRAWS FROM THE CROSSING LANES — LAKE SIMCOE NAVIGABLE</t>
+        </is>
+      </c>
+      <c r="E153" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
         </is>
       </c>
       <c r="F153" s="59" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>CA_PROT_04_SUMMON</t>
         </is>
       </c>
       <c r="G153" s="59" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
-        </is>
-      </c>
-      <c r="H153" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>→ CA_PROT_04_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I153" s="58" t="inlineStr"/>
@@ -10510,52 +10590,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K153" s="61" t="inlineStr">
+      <c r="K153" s="60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L153" s="58" t="inlineStr"/>
-      <c r="M153" s="61" t="inlineStr">
+      <c r="M153" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N153" s="59" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Sets ca_prot_04_tame flag; immediately chains to AGREE</t>
         </is>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="57" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B154" s="57" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C154" s="58" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>CA_PROT_04_AGREE</t>
         </is>
       </c>
       <c r="D154" s="59" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE ONTARIO WATERWAYS</t>
+        </is>
+      </c>
+      <c r="E154" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F154" s="59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA_PROT_04_TAME</t>
         </is>
       </c>
       <c r="G154" s="59" t="inlineStr">
@@ -10563,9 +10643,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H154" s="60" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I154" s="58" t="inlineStr"/>
@@ -10574,125 +10654,1685 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K154" s="61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L154" s="58" t="inlineStr"/>
-      <c r="M154" s="61" t="inlineStr">
+      <c r="K154" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L154" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M154" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N154" s="59" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Sets ca_prot_04_agreed; BTN2 explicit — why the Republic had to apologize first</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="57" t="inlineStr">
         <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B155" s="57" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C155" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_SUMMON</t>
+        </is>
+      </c>
+      <c r="D155" s="59" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU IS FREE — THE IRON CAGE HAS BEEN SWINGING IN TROIS-PISTOLES</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F155" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I155" s="58" t="inlineStr">
+        <is>
+          <t>la_corriveau</t>
+        </is>
+      </c>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K155" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L155" s="58" t="inlineStr"/>
+      <c r="M155" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N155" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 28+; Trois-Pistoles tile 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B156" s="57" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C156" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="D156" s="59" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU QUIETS — THE REPUBLIC ACKNOWLEDGES THE VERDICT WAS WRONG</t>
+        </is>
+      </c>
+      <c r="E156" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F156" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_SUMMON</t>
+        </is>
+      </c>
+      <c r="G156" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_05_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I156" s="58" t="inlineStr"/>
+      <c r="J156" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K156" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L156" s="58" t="inlineStr"/>
+      <c r="M156" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N156" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_05_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B157" s="57" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C157" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_AGREE</t>
+        </is>
+      </c>
+      <c r="D157" s="59" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THREE GARRISONS EVACUATED THIS WEEK</t>
+        </is>
+      </c>
+      <c r="E157" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F157" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="G157" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I157" s="58" t="inlineStr"/>
+      <c r="J157" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K157" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L157" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M157" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N157" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_05_agreed; BTN2 explicit — what Corriveau actually wanted to say</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="30" customHeight="1">
+      <c r="A158" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B158" s="57" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C158" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_SUMMON</t>
+        </is>
+      </c>
+      <c r="D158" s="59" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU MOVES THROUGH THE MONCTON FOREST — NOTHING STOPS IT</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F158" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G158" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I158" s="58" t="inlineStr">
+        <is>
+          <t>carcajou</t>
+        </is>
+      </c>
+      <c r="J158" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K158" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L158" s="58" t="inlineStr"/>
+      <c r="M158" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N158" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 33+; Moncton tile 193</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B159" s="57" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C159" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="D159" s="59" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU REDIRECTS — CONTINENTAL LINES EXEMPTED FROM DESTRUCTION</t>
+        </is>
+      </c>
+      <c r="E159" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F159" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_SUMMON</t>
+        </is>
+      </c>
+      <c r="G159" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_06_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I159" s="58" t="inlineStr"/>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K159" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L159" s="58" t="inlineStr"/>
+      <c r="M159" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N159" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_06_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B160" s="57" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C160" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE</t>
+        </is>
+      </c>
+      <c r="D160" s="59" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDOR ACCORD</t>
+        </is>
+      </c>
+      <c r="E160" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F160" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="G160" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I160" s="58" t="inlineStr"/>
+      <c r="J160" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K160" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L160" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M160" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N160" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_06_agreed; BTN2 explicit — why the Carcajou accepted the accord</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B161" s="57" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C161" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_SUMMON</t>
+        </is>
+      </c>
+      <c r="D161" s="59" t="inlineStr">
+        <is>
+          <t>THE FLYING CANOE RUNS THE OTTAWA RIVER — THREE SIGHTINGS, TWO MISSING PATROLS</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F161" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G161" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I161" s="58" t="inlineStr">
+        <is>
+          <t>chasse_galerie</t>
+        </is>
+      </c>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K161" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L161" s="58" t="inlineStr"/>
+      <c r="M161" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N161" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 38+; Deep River tile 128</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B162" s="57" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C162" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="D162" s="59" t="inlineStr">
+        <is>
+          <t>THE FLYING CANOE ACKNOWLEDGES THE REPUBLIC — THE OTTAWA RIVER CORRIDOR SECURED</t>
+        </is>
+      </c>
+      <c r="E162" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F162" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_SUMMON</t>
+        </is>
+      </c>
+      <c r="G162" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_07_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I162" s="58" t="inlineStr"/>
+      <c r="J162" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K162" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L162" s="58" t="inlineStr"/>
+      <c r="M162" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N162" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_07_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="30" customHeight="1">
+      <c r="A163" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B163" s="57" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C163" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE</t>
+        </is>
+      </c>
+      <c r="D163" s="59" t="inlineStr">
+        <is>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW</t>
+        </is>
+      </c>
+      <c r="E163" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F163" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="G163" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I163" s="58" t="inlineStr"/>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K163" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L163" s="58" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M163" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N163" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_07_agreed; BTN2 sensual — Mark Penoit on the river</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="A164" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B164" s="57" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C164" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="D164" s="59" t="inlineStr">
+        <is>
+          <t>THE GOUGOU RISES IN THE CHALEUR BAY — CHAMPLAIN'S MONSTER IS REAL</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F164" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G164" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I164" s="58" t="inlineStr">
+        <is>
+          <t>le_gougou</t>
+        </is>
+      </c>
+      <c r="J164" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K164" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L164" s="58" t="inlineStr"/>
+      <c r="M164" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N164" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 43+; Bathurst tile 109</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B165" s="57" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C165" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="D165" s="59" t="inlineStr">
+        <is>
+          <t>THE GOUGOU WITHDRAWS FROM THE BAY LANES — RESTITUTION PROTOCOLS ACTIVE</t>
+        </is>
+      </c>
+      <c r="E165" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F165" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="G165" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_08_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I165" s="58" t="inlineStr"/>
+      <c r="J165" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K165" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L165" s="58" t="inlineStr"/>
+      <c r="M165" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N165" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_08_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B166" s="57" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C166" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE</t>
+        </is>
+      </c>
+      <c r="D166" s="59" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE CONTINENTAL ALLIANCE</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F166" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="G166" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I166" s="58" t="inlineStr"/>
+      <c r="J166" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K166" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L166" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M166" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N166" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_08_agreed; BTN2 explicit — the Gougou's real name</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="8" customHeight="1">
+      <c r="A167" s="9" t="n"/>
+      <c r="B167" s="9" t="n"/>
+      <c r="C167" s="9" t="n"/>
+      <c r="D167" s="9" t="n"/>
+      <c r="E167" s="9" t="n"/>
+      <c r="F167" s="9" t="n"/>
+      <c r="G167" s="9" t="n"/>
+      <c r="H167" s="9" t="n"/>
+      <c r="I167" s="9" t="n"/>
+      <c r="J167" s="9" t="n"/>
+      <c r="K167" s="9" t="n"/>
+      <c r="L167" s="9" t="n"/>
+      <c r="M167" s="9" t="n"/>
+      <c r="N167" s="9" t="n"/>
+    </row>
+    <row r="168" ht="30" customHeight="1">
+      <c r="A168" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B168" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C168" s="50" t="inlineStr">
+        <is>
+          <t>VP_LEGACY</t>
+        </is>
+      </c>
+      <c r="D168" s="51" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
+        </is>
+      </c>
+      <c r="E168" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F168" s="51" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (turn 96+)</t>
+        </is>
+      </c>
+      <c r="G168" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I168" s="50" t="inlineStr"/>
+      <c r="J168" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K168" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L168" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M168" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N168" s="51" t="inlineStr">
+        <is>
+          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="8" customHeight="1">
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="9" t="n"/>
+      <c r="D169" s="9" t="n"/>
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="9" t="n"/>
+      <c r="G169" s="9" t="n"/>
+      <c r="H169" s="9" t="n"/>
+      <c r="I169" s="9" t="n"/>
+      <c r="J169" s="9" t="n"/>
+      <c r="K169" s="9" t="n"/>
+      <c r="L169" s="9" t="n"/>
+      <c r="M169" s="9" t="n"/>
+      <c r="N169" s="9" t="n"/>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="61" t="inlineStr">
+        <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B155" s="57" t="inlineStr">
+      <c r="B170" s="61" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C170" s="62" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D170" s="63" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F170" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G170" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H170" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I170" s="62" t="inlineStr"/>
+      <c r="J170" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K170" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L170" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M170" s="65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N170" s="63" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B171" s="61" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C171" s="62" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D171" s="63" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F171" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G171" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H171" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I171" s="62" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K171" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L171" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M171" s="65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N171" s="63" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B172" s="61" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C172" s="62" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D172" s="63" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F172" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G172" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H172" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I172" s="62" t="inlineStr"/>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K172" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L172" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M172" s="65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N172" s="63" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B173" s="61" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C173" s="62" t="inlineStr">
+        <is>
+          <t>UALANI_COURTHOUSE_01</t>
+        </is>
+      </c>
+      <c r="D173" s="63" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F173" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G173" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H173" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I173" s="62" t="inlineStr"/>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K173" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L173" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M173" s="65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N173" s="63" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B174" s="61" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C174" s="62" t="inlineStr">
+        <is>
+          <t>CL_WASHINGTON_01</t>
+        </is>
+      </c>
+      <c r="D174" s="63" t="inlineStr">
+        <is>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F174" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H174" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I174" s="62" t="inlineStr"/>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K174" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L174" s="62" t="inlineStr"/>
+      <c r="M174" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N174" s="63" t="inlineStr">
+        <is>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="30" customHeight="1">
+      <c r="A175" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B175" s="61" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C175" s="62" t="inlineStr">
+        <is>
+          <t>CL_VALLEY_FORGE_01</t>
+        </is>
+      </c>
+      <c r="D175" s="63" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F175" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G175" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H175" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I175" s="62" t="inlineStr"/>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K175" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L175" s="62" t="inlineStr"/>
+      <c r="M175" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N175" s="63" t="inlineStr">
+        <is>
+          <t>Tile 1; historically significant; would fire on liberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B176" s="61" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C176" s="62" t="inlineStr">
+        <is>
+          <t>CX_NYC_01</t>
+        </is>
+      </c>
+      <c r="D176" s="63" t="inlineStr">
+        <is>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F176" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G176" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H176" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I176" s="62" t="inlineStr"/>
+      <c r="J176" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K176" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L176" s="62" t="inlineStr"/>
+      <c r="M176" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N176" s="63" t="inlineStr">
+        <is>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B177" s="61" t="inlineStr">
+        <is>
+          <t>Espionage Events</t>
+        </is>
+      </c>
+      <c r="C177" s="62" t="inlineStr">
+        <is>
+          <t>ESPIONAGE_DISCOVERY_01</t>
+        </is>
+      </c>
+      <c r="D177" s="63" t="inlineStr">
+        <is>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F177" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G177" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H177" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I177" s="62" t="inlineStr"/>
+      <c r="J177" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K177" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L177" s="62" t="inlineStr"/>
+      <c r="M177" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N177" s="63" t="inlineStr">
+        <is>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B178" s="61" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C178" s="62" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D178" s="63" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F178" s="63" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G178" s="63" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H178" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I178" s="62" t="inlineStr"/>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K178" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L178" s="62" t="inlineStr"/>
+      <c r="M178" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N178" s="63" t="inlineStr">
+        <is>
+          <t>Extend the commander arc beyond first objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B179" s="61" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C155" s="58" t="inlineStr">
+      <c r="C179" s="62" t="inlineStr">
+        <is>
+          <t>WINTER_SIEGE_01</t>
+        </is>
+      </c>
+      <c r="D179" s="63" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F179" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G179" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H179" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I179" s="62" t="inlineStr"/>
+      <c r="J179" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K179" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L179" s="62" t="inlineStr"/>
+      <c r="M179" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N179" s="63" t="inlineStr">
+        <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B180" s="61" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C180" s="62" t="inlineStr">
         <is>
           <t>SPRING_OFFENSIVE_01</t>
         </is>
       </c>
-      <c r="D155" s="59" t="inlineStr">
+      <c r="D180" s="63" t="inlineStr">
         <is>
           <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E180" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F155" s="59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G155" s="59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H155" s="60" t="inlineStr">
+      <c r="F180" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G180" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H180" s="64" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I155" s="58" t="inlineStr"/>
-      <c r="J155" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K155" s="61" t="inlineStr">
+      <c r="I180" s="62" t="inlineStr"/>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K180" s="65" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L155" s="58" t="inlineStr"/>
-      <c r="M155" s="61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N155" s="59" t="inlineStr">
+      <c r="L180" s="62" t="inlineStr"/>
+      <c r="M180" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N180" s="63" t="inlineStr">
         <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="62" t="inlineStr">
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="66" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B157" s="63" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="62" t="inlineStr">
+      <c r="B182" s="67" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="66" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B158" s="63" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="62" t="inlineStr">
+      <c r="B183" s="67" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="66" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B159" s="63" t="n">
+      <c r="B184" s="67" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="62" t="inlineStr">
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="66" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B160" s="63" t="n">
-        <v>43</v>
+      <c r="B185" s="67" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -10706,7 +12346,2429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CHAIN / GROUP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EVENT ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HEADLINE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CHAIN POSITION</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PARENT EVENT(S)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CHILD EVENT(S)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ART TAG</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ART STATUS</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>EXPLICIT ART?</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CONTENT FLAG</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>COOLDOWN</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>NOTES / TRIGGERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="inlineStr">
+        <is>
+          <t>War Arc</t>
+        </is>
+      </c>
+      <c r="C2" s="54" t="inlineStr">
+        <is>
+          <t>UK_BUILDUP_01</t>
+        </is>
+      </c>
+      <c r="D2" s="55" t="inlineStr">
+        <is>
+          <t>INTELLIGENCE REPORT: CROWN FORCES AMASSING ON ALL BORDERS</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F2" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_CALL_01 (uk_buildup_known flag)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="54" t="inlineStr"/>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K2" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L2" s="54" t="inlineStr"/>
+      <c r="M2" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" s="55" t="inlineStr">
+        <is>
+          <t>Fires turn 7, one-time; BTN1 alert / BTN2 contact Ottawa; both set uk_buildup_known</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B3" s="53" t="inlineStr">
+        <is>
+          <t>War Arc</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>UK_DECLARATION_01</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>KING GEORGE III DECLARES WAR: THE CROWN HAS MOVED ON BOTH FRONTS</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F3" s="55" t="inlineStr">
+        <is>
+          <t>UK_BUILDUP_01</t>
+        </is>
+      </c>
+      <c r="G3" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="54" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K3" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L3" s="54" t="inlineStr"/>
+      <c r="M3" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" s="55" t="inlineStr">
+        <is>
+          <t>Fires turns 10-16 (30%/turn) once uk_buildup_known; sets uk_declared_war</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>CAN_CALL_01</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>THE OTTAWA CALL: PRESIDENT PENOIT AND PM CLEAR-WATER ARE ON THE LINE</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F4" s="55" t="inlineStr">
+        <is>
+          <t>UK_BUILDUP_01 (flag)</t>
+        </is>
+      </c>
+      <c r="G4" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_PENOIT_01 (BTN1) or END (BTN2)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="54" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K4" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L4" s="54" t="inlineStr"/>
+      <c r="M4" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="55" t="inlineStr">
+        <is>
+          <t>Fires turn 8+ after uk_buildup_known; BTN1 sets can_contact / BTN2 sets can_rejected (ends arc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>CAN_PENOIT_01</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>PRESIDENT PENOIT'S CONDITIONS: MARK PENOIT PUTS IT IN WRITING</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>CAN_CALL_01 (can_contact)</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_CLEARWATER_01</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="54" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K5" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L5" s="54" t="inlineStr"/>
+      <c r="M5" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>Fires turn 12+ after can_contact; BTN1 can_penoit_agreed / BTN2 can_penoit_negotiating</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUTSIDE OFFICIAL CHANNELS</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>CAN_PENOIT_01</t>
+        </is>
+      </c>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_JOINT_OPS_01</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="54" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K6" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L6" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M6" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" s="55" t="inlineStr">
+        <is>
+          <t>After penoit path + can_contact; BTN1 can_clearwater_warm / BTN2 sensual can_clearwater_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE ONE MAP</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01</t>
+        </is>
+      </c>
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_SUMMIT_01</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="54" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L7" s="54" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M7" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>After penoit+clearwater paths; BTN1 +weapons 20 / BTN2 explicit +morale 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR THE FIRST TIME</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01</t>
+        </is>
+      </c>
+      <c r="G8" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_ALLIANCE_SIGNED</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="54" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L8" s="54" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="M8" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="55" t="inlineStr">
+        <is>
+          <t>EXPLICIT #1 (all three); turn 13+, penoit_agreed+clearwater; BTN1/BTN2 set can_summit_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>CAN_ALLIANCE_SIGNED</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>THE CONTINENTAL DEFENSE ALLIANCE IS SIGNED: THREE NATIONS — ONE FRONT</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01</t>
+        </is>
+      </c>
+      <c r="G9" s="55" t="inlineStr">
+        <is>
+          <t>→ CAN_PEACE_01</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L9" s="54" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="M9" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" s="55" t="inlineStr">
+        <is>
+          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>CAN_ALLIANCE_SIGNED (can_allied flag)</t>
+        </is>
+      </c>
+      <c r="G10" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="54" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L10" s="54" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="M10" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="55" t="inlineStr">
+        <is>
+          <t>EXPLICIT #3 (all three); fires when can_allied + UK tiles ≤ 20 + turn ≥ 60; BTN2 +morale 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_LUCK</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY BEFORE THE ELECTION</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01 (can_allied)</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="54" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K11" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L11" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M11" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="55" t="inlineStr">
+        <is>
+          <t>End-game; fires turn 93+ if can_allied; BTN1 +pressure 10 / BTN2 sensual +pressure 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_SUMMON</t>
+        </is>
+      </c>
+      <c r="D13" s="59" t="inlineStr">
+        <is>
+          <t>LE WENDIGO WAKES IN THE LAURENTIAN FOREST</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F13" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_01_TAME</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="58" t="inlineStr">
+        <is>
+          <t>wendigo_approach</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K13" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L13" s="58" t="inlineStr"/>
+      <c r="M13" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn (25% chance) to CA tiles; fires turn 8+; Saint-Georges tile 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_TAME</t>
+        </is>
+      </c>
+      <c r="D14" s="59" t="inlineStr">
+        <is>
+          <t>THE WENDIGO RECEDES FROM THE HARVEST CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F14" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_SUMMON</t>
+        </is>
+      </c>
+      <c r="G14" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_01_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="58" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K14" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L14" s="58" t="inlineStr"/>
+      <c r="M14" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_01_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C15" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE</t>
+        </is>
+      </c>
+      <c r="D15" s="59" t="inlineStr">
+        <is>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F15" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_TAME</t>
+        </is>
+      </c>
+      <c r="G15" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="58" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L15" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M15" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_01_agreed; BTN2 explicit — private dispatch from Jessica</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="inlineStr">
+        <is>
+          <t>Le Loup-Garou</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_SUMMON</t>
+        </is>
+      </c>
+      <c r="D16" s="59" t="inlineStr">
+        <is>
+          <t>LE LOUP-GAROU RUNS THE RIVER ROAD — RIVIÈRE-DU-LOUP QUARANTINED</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F16" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_02_TAME</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="58" t="inlineStr">
+        <is>
+          <t>loup_garou</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K16" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L16" s="58" t="inlineStr"/>
+      <c r="M16" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 13+; Rivière-du-Loup tile 105</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="inlineStr">
+        <is>
+          <t>Le Loup-Garou</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_TAME</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="inlineStr">
+        <is>
+          <t>LE LOUP-GAROU ALLOWS PASSAGE — THE RIVER ROAD REOPENS</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F17" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_SUMMON</t>
+        </is>
+      </c>
+      <c r="G17" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_02_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="58" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K17" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L17" s="58" t="inlineStr"/>
+      <c r="M17" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_02_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="inlineStr">
+        <is>
+          <t>Le Loup-Garou</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_AGREE</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLEDGED BY THE REPUBLIC</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F18" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_TAME</t>
+        </is>
+      </c>
+      <c r="G18" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="58" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K18" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L18" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M18" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_02_agreed; BTN2 explicit — the wolf stops running</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="inlineStr">
+        <is>
+          <t>Les Feux Follets</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_SUMMON</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS RISE OVER THE SAINT JOHN MARSHES — NAVIGATION DISRUPTED</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_03_TAME</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="58" t="inlineStr">
+        <is>
+          <t>feux_follets</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K19" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L19" s="58" t="inlineStr"/>
+      <c r="M19" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 18+; Saint John tile 194</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="inlineStr">
+        <is>
+          <t>Les Feux Follets</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_TAME</t>
+        </is>
+      </c>
+      <c r="D20" s="59" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS QUIET — MALISEET PROTOCOLS ESTABLISHED</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F20" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_SUMMON</t>
+        </is>
+      </c>
+      <c r="G20" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_03_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="58" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K20" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L20" s="58" t="inlineStr"/>
+      <c r="M20" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_03_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B21" s="57" t="inlineStr">
+        <is>
+          <t>Les Feux Follets</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE</t>
+        </is>
+      </c>
+      <c r="D21" s="59" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JOHN MARSH ACCORD</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F21" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_TAME</t>
+        </is>
+      </c>
+      <c r="G21" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="58" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K21" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L21" s="58" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M21" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_03_agreed; BTN2 sensual — Jessica walks you through the marsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B22" s="57" t="inlineStr">
+        <is>
+          <t>Mishepeshu</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_SUMMON</t>
+        </is>
+      </c>
+      <c r="D22" s="59" t="inlineStr">
+        <is>
+          <t>MISHEPESHU STIRS BENEATH LAKE SIMCOE — CROSSINGS CONTESTED</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F22" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_04_TAME</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I22" s="58" t="inlineStr">
+        <is>
+          <t>mishepeshu</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K22" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L22" s="58" t="inlineStr"/>
+      <c r="M22" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 23+; Barrie tile 131</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B23" s="57" t="inlineStr">
+        <is>
+          <t>Mishepeshu</t>
+        </is>
+      </c>
+      <c r="C23" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_TAME</t>
+        </is>
+      </c>
+      <c r="D23" s="59" t="inlineStr">
+        <is>
+          <t>MISHEPESHU WITHDRAWS FROM THE CROSSING LANES — LAKE SIMCOE NAVIGABLE</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F23" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_SUMMON</t>
+        </is>
+      </c>
+      <c r="G23" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_04_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I23" s="58" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K23" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L23" s="58" t="inlineStr"/>
+      <c r="M23" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_04_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B24" s="57" t="inlineStr">
+        <is>
+          <t>Mishepeshu</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_AGREE</t>
+        </is>
+      </c>
+      <c r="D24" s="59" t="inlineStr">
+        <is>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE ONTARIO WATERWAYS</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F24" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_TAME</t>
+        </is>
+      </c>
+      <c r="G24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I24" s="58" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M24" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_04_agreed; BTN2 explicit — why the Republic had to apologize first</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B25" s="57" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C25" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_SUMMON</t>
+        </is>
+      </c>
+      <c r="D25" s="59" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU IS FREE — THE IRON CAGE HAS BEEN SWINGING IN TROIS-PISTOLES</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I25" s="58" t="inlineStr">
+        <is>
+          <t>la_corriveau</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K25" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L25" s="58" t="inlineStr"/>
+      <c r="M25" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 28+; Trois-Pistoles tile 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B26" s="57" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="D26" s="59" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU QUIETS — THE REPUBLIC ACKNOWLEDGES THE VERDICT WAS WRONG</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F26" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_SUMMON</t>
+        </is>
+      </c>
+      <c r="G26" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_05_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I26" s="58" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K26" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L26" s="58" t="inlineStr"/>
+      <c r="M26" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_05_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C27" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_AGREE</t>
+        </is>
+      </c>
+      <c r="D27" s="59" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THREE GARRISONS EVACUATED THIS WEEK</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F27" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_TAME</t>
+        </is>
+      </c>
+      <c r="G27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I27" s="58" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L27" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M27" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N27" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_05_agreed; BTN2 explicit — what Corriveau actually wanted to say</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_SUMMON</t>
+        </is>
+      </c>
+      <c r="D28" s="59" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU MOVES THROUGH THE MONCTON FOREST — NOTHING STOPS IT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I28" s="58" t="inlineStr">
+        <is>
+          <t>carcajou</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K28" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L28" s="58" t="inlineStr"/>
+      <c r="M28" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 33+; Moncton tile 193</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C29" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="D29" s="59" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU REDIRECTS — CONTINENTAL LINES EXEMPTED FROM DESTRUCTION</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F29" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_SUMMON</t>
+        </is>
+      </c>
+      <c r="G29" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_06_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I29" s="58" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K29" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L29" s="58" t="inlineStr"/>
+      <c r="M29" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_06_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C30" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE</t>
+        </is>
+      </c>
+      <c r="D30" s="59" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDOR ACCORD</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F30" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_TAME</t>
+        </is>
+      </c>
+      <c r="G30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I30" s="58" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L30" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M30" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N30" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_06_agreed; BTN2 explicit — why the Carcajou accepted the accord</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C31" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_SUMMON</t>
+        </is>
+      </c>
+      <c r="D31" s="59" t="inlineStr">
+        <is>
+          <t>THE FLYING CANOE RUNS THE OTTAWA RIVER — THREE SIGHTINGS, TWO MISSING PATROLS</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I31" s="58" t="inlineStr">
+        <is>
+          <t>chasse_galerie</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K31" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L31" s="58" t="inlineStr"/>
+      <c r="M31" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 38+; Deep River tile 128</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B32" s="57" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C32" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="D32" s="59" t="inlineStr">
+        <is>
+          <t>THE FLYING CANOE ACKNOWLEDGES THE REPUBLIC — THE OTTAWA RIVER CORRIDOR SECURED</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F32" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_SUMMON</t>
+        </is>
+      </c>
+      <c r="G32" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_07_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I32" s="58" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K32" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L32" s="58" t="inlineStr"/>
+      <c r="M32" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_07_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C33" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE</t>
+        </is>
+      </c>
+      <c r="D33" s="59" t="inlineStr">
+        <is>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F33" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_TAME</t>
+        </is>
+      </c>
+      <c r="G33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I33" s="58" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K33" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L33" s="58" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M33" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N33" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_07_agreed; BTN2 sensual — Mark Penoit on the river</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B34" s="57" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C34" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="D34" s="59" t="inlineStr">
+        <is>
+          <t>THE GOUGOU RISES IN THE CHALEUR BAY — CHAMPLAIN'S MONSTER IS REAL</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I34" s="58" t="inlineStr">
+        <is>
+          <t>le_gougou</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K34" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L34" s="58" t="inlineStr"/>
+      <c r="M34" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" s="59" t="inlineStr">
+        <is>
+          <t>Wild: +1 corruption/turn to CA tiles; fires turn 43+; Bathurst tile 109</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B35" s="57" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C35" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="inlineStr">
+        <is>
+          <t>THE GOUGOU WITHDRAWS FROM THE BAY LANES — RESTITUTION PROTOCOLS ACTIVE</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="F35" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="G35" s="59" t="inlineStr">
+        <is>
+          <t>→ CA_PROT_08_AGREE (next_event_id)</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I35" s="58" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K35" s="60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L35" s="58" t="inlineStr"/>
+      <c r="M35" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_08_tame flag; immediately chains to AGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="57" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B36" s="57" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C36" s="58" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE</t>
+        </is>
+      </c>
+      <c r="D36" s="59" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE CONTINENTAL ALLIANCE</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F36" s="59" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_TAME</t>
+        </is>
+      </c>
+      <c r="G36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I36" s="58" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L36" s="58" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M36" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N36" s="59" t="inlineStr">
+        <is>
+          <t>Sets ca_prot_08_agreed; BTN2 explicit — the Gougou's real name</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="66" t="inlineStr">
+        <is>
+          <t>Canadian events total</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="66" t="inlineStr">
+        <is>
+          <t>Canada (Alliance arc)</t>
+        </is>
+      </c>
+      <c r="B39" s="67" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="66" t="inlineStr">
+        <is>
+          <t>CA Protector (Jessica's creatures)</t>
+        </is>
+      </c>
+      <c r="B40" s="67" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="66" t="inlineStr">
+        <is>
+          <t>Need explicit art (YES)</t>
+        </is>
+      </c>
+      <c r="B41" s="67" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10715,343 +14777,364 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="B2" s="66" t="inlineStr">
+      <c r="B2" s="70" t="inlineStr">
         <is>
           <t>Final pass done — art integrated, text finalized, fully tested</t>
         </is>
       </c>
-      <c r="C2" s="66" t="n"/>
+      <c r="C2" s="70" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="67" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Event is coded, in CSV, all buttons wired; no final polish yet</t>
         </is>
       </c>
-      <c r="C3" s="68" t="n"/>
+      <c r="C3" s="72" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="69" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B4" s="70" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Concept stage: not in events.csv; some referenced in button CSV</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
+      <c r="C4" s="74" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>ART STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="71" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B7" s="72" t="inlineStr">
+      <c r="A7" s="75" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>No art asset exists yet</t>
         </is>
       </c>
-      <c r="C7" s="72" t="n"/>
+      <c r="C7" s="76" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="69" t="inlineStr">
+      <c r="A8" s="73" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>Art is being created but not in engine</t>
         </is>
       </c>
-      <c r="C8" s="70" t="n"/>
+      <c r="C8" s="74" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>Art is in the project and referenced correctly</t>
         </is>
       </c>
-      <c r="C9" s="74" t="n"/>
+      <c r="C9" s="78" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="64" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>EXPLICIT ART LEGEND</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="79" t="inlineStr">
         <is>
           <t>YES — Explicit Art Needed</t>
         </is>
       </c>
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>Event has explicit or kinky_lewd content flag OR has at least one explicit button option that will need unique explicit artwork</t>
         </is>
       </c>
-      <c r="C12" s="76" t="n"/>
+      <c r="C12" s="80" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="78" t="inlineStr">
+      <c r="B13" s="82" t="inlineStr">
         <is>
           <t>Standard event — no adult artwork required</t>
         </is>
       </c>
-      <c r="C13" s="78" t="n"/>
+      <c r="C13" s="82" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>CHAIN POSITION LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="79" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B16" s="84" t="inlineStr">
         <is>
           <t>Standalone event or first event in a chain; fires from world.gd check function or EventDatabase date trigger</t>
         </is>
       </c>
-      <c r="C16" s="80" t="n"/>
+      <c r="C16" s="84" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="81" t="inlineStr">
+      <c r="A17" s="85" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="86" t="inlineStr">
         <is>
           <t>Fires as outcome of a choice button on a Root/prior event; represents one path in a fork</t>
         </is>
       </c>
-      <c r="C17" s="82" t="n"/>
+      <c r="C17" s="86" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="83" t="inlineStr">
+      <c r="A18" s="87" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="B18" s="84" t="inlineStr">
+      <c r="B18" s="88" t="inlineStr">
         <is>
           <t>Fires automatically after a mission completes (via next_event_id or mission flag return)</t>
         </is>
       </c>
-      <c r="C18" s="84" t="n"/>
+      <c r="C18" s="88" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="64" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>CATEGORY COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="85" t="inlineStr">
+      <c r="A21" s="89" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B21" s="86" t="inlineStr">
+      <c r="B21" s="90" t="inlineStr">
         <is>
           <t>Calendar-triggered events; month or turn-based</t>
         </is>
       </c>
-      <c r="C21" s="86" t="n"/>
+      <c r="C21" s="90" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="87" t="inlineStr">
+      <c r="A22" s="91" t="inlineStr">
         <is>
           <t>City Liberated</t>
         </is>
       </c>
-      <c r="B22" s="88" t="inlineStr">
+      <c r="B22" s="92" t="inlineStr">
         <is>
           <t>Fires when a specific tile is liberated (city_liberated type)</t>
         </is>
       </c>
-      <c r="C22" s="88" t="n"/>
+      <c r="C22" s="92" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="89" t="inlineStr">
+      <c r="A23" s="93" t="inlineStr">
         <is>
           <t>City Lost</t>
         </is>
       </c>
-      <c r="B23" s="90" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>Fires when a specific tile falls to the enemy (city_lost type)</t>
         </is>
       </c>
-      <c r="C23" s="90" t="n"/>
+      <c r="C23" s="94" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="91" t="inlineStr">
+      <c r="A24" s="95" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B24" s="92" t="inlineStr">
+      <c r="B24" s="96" t="inlineStr">
         <is>
           <t>State-level liberation, secession, and reintegration</t>
         </is>
       </c>
-      <c r="C24" s="92" t="n"/>
+      <c r="C24" s="96" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="93" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B25" s="94" t="inlineStr">
+      <c r="B25" s="98" t="inlineStr">
         <is>
           <t>Mythological entity summon events (protector_summon type)</t>
         </is>
       </c>
-      <c r="C25" s="94" t="n"/>
+      <c r="C25" s="98" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="95" t="inlineStr">
+      <c r="A26" s="99" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B26" s="96" t="inlineStr">
+      <c r="B26" s="100" t="inlineStr">
         <is>
           <t>Named commander arc events (commander_* types)</t>
         </is>
       </c>
-      <c r="C26" s="96" t="n"/>
+      <c r="C26" s="100" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="97" t="inlineStr">
+      <c r="A27" s="101" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B27" s="98" t="inlineStr">
+      <c r="B27" s="102" t="inlineStr">
         <is>
           <t>Fort disrepair investigation chain (fort_* types)</t>
         </is>
       </c>
-      <c r="C27" s="98" t="n"/>
+      <c r="C27" s="102" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="99" t="inlineStr">
+      <c r="A28" s="103" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B28" s="100" t="inlineStr">
+      <c r="B28" s="104" t="inlineStr">
         <is>
           <t>Republic collapse sequence</t>
         </is>
       </c>
-      <c r="C28" s="100" t="n"/>
+      <c r="C28" s="104" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="101" t="inlineStr">
+      <c r="A29" s="105" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B29" s="102" t="inlineStr">
+      <c r="B29" s="106" t="inlineStr">
         <is>
           <t>Dynamic tile-based crisis chains; triggered by world.gd check functions</t>
         </is>
       </c>
-      <c r="C29" s="102" t="n"/>
+      <c r="C29" s="106" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="103" t="inlineStr">
+      <c r="A30" s="107" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B30" s="104" t="inlineStr">
+      <c r="B30" s="108" t="inlineStr">
         <is>
           <t>Ualani Carlisle army presence events; personal storyline</t>
         </is>
       </c>
-      <c r="C30" s="104" t="n"/>
+      <c r="C30" s="108" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="105" t="inlineStr">
+      <c r="A31" s="109" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B31" s="106" t="inlineStr"/>
-      <c r="C31" s="106" t="n"/>
+      <c r="B31" s="110" t="inlineStr">
+        <is>
+          <t>Vice President relationship arc; 9 events tied to the VP governor</t>
+        </is>
+      </c>
+      <c r="C31" s="110" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="107" t="inlineStr">
+      <c r="A32" s="111" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B32" s="108" t="inlineStr"/>
-      <c r="C32" s="108" t="n"/>
+      <c r="B32" s="112" t="inlineStr">
+        <is>
+          <t>Canadian Alliance diplomatic arc (war declaration + 8 CAN_ events)</t>
+        </is>
+      </c>
+      <c r="C32" s="112" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="109" t="inlineStr">
+      <c r="A33" s="113" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B33" s="114" t="inlineStr">
+        <is>
+          <t>Jessica Clear-Water's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
+        </is>
+      </c>
+      <c r="C33" s="114" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="115" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B33" s="110" t="inlineStr">
+      <c r="B34" s="116" t="inlineStr">
         <is>
           <t>Not yet implemented; concept stage or referenced-but-missing events</t>
         </is>
       </c>
-      <c r="C33" s="110" t="n"/>
+      <c r="C34" s="116" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N185"/>
+  <dimension ref="A1:N189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11492,360 +11492,308 @@
       <c r="N167" s="9" t="n"/>
     </row>
     <row r="168" ht="30" customHeight="1">
-      <c r="A168" s="49" t="inlineStr">
+      <c r="A168" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B168" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C168" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01</t>
+        </is>
+      </c>
+      <c r="D168" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F168" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G168" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I168" s="54" t="inlineStr"/>
+      <c r="J168" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K168" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L168" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M168" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N168" s="55" t="inlineStr">
+        <is>
+          <t>Allied peace: fires when all UK dock tiles in USA+CA regions liberated (can_allied); sets uk_usa_peace+uk_ca_peace on UK country; BTN2 sensual — Ualani+Jessica celebrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B169" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C169" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_USA_01</t>
+        </is>
+      </c>
+      <c r="D169" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F169" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G169" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I169" s="54" t="inlineStr"/>
+      <c r="J169" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K169" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L169" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M169" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N169" s="55" t="inlineStr">
+        <is>
+          <t>USA separate peace (unallied): fires when all USA dock tiles liberated (65,66,67,151); sets uk_usa_peace on UK country; BTN2 sensual — Ualani alone at dawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B170" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C170" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_CA_AI_01</t>
+        </is>
+      </c>
+      <c r="D170" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — CANADA NEGOTIATES SEPARATE PEACE</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F170" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G170" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I170" s="54" t="inlineStr"/>
+      <c r="J170" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K170" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L170" s="54" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M170" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N170" s="55" t="inlineStr">
+        <is>
+          <t>CA separate peace (unallied): fires when Halifax (tile 114) liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="8" customHeight="1">
+      <c r="A171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="9" t="n"/>
+      <c r="D171" s="9" t="n"/>
+      <c r="E171" s="9" t="n"/>
+      <c r="F171" s="9" t="n"/>
+      <c r="G171" s="9" t="n"/>
+      <c r="H171" s="9" t="n"/>
+      <c r="I171" s="9" t="n"/>
+      <c r="J171" s="9" t="n"/>
+      <c r="K171" s="9" t="n"/>
+      <c r="L171" s="9" t="n"/>
+      <c r="M171" s="9" t="n"/>
+      <c r="N171" s="9" t="n"/>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="49" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B168" s="49" t="inlineStr">
+      <c r="B172" s="49" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C168" s="50" t="inlineStr">
+      <c r="C172" s="50" t="inlineStr">
         <is>
           <t>VP_LEGACY</t>
         </is>
       </c>
-      <c r="D168" s="51" t="inlineStr">
+      <c r="D172" s="51" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
         </is>
       </c>
-      <c r="E168" s="22" t="inlineStr">
+      <c r="E172" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F168" s="51" t="inlineStr">
+      <c r="F172" s="51" t="inlineStr">
         <is>
           <t>VP_FIRST_MEETING (turn 96+)</t>
         </is>
       </c>
-      <c r="G168" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H168" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I168" s="50" t="inlineStr"/>
-      <c r="J168" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K168" s="26" t="inlineStr">
+      <c r="G172" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I172" s="50" t="inlineStr"/>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K172" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L168" s="50" t="inlineStr">
+      <c r="L172" s="50" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M168" s="52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N168" s="51" t="inlineStr">
+      <c r="M172" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N172" s="51" t="inlineStr">
         <is>
           <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="8" customHeight="1">
-      <c r="A169" s="9" t="n"/>
-      <c r="B169" s="9" t="n"/>
-      <c r="C169" s="9" t="n"/>
-      <c r="D169" s="9" t="n"/>
-      <c r="E169" s="9" t="n"/>
-      <c r="F169" s="9" t="n"/>
-      <c r="G169" s="9" t="n"/>
-      <c r="H169" s="9" t="n"/>
-      <c r="I169" s="9" t="n"/>
-      <c r="J169" s="9" t="n"/>
-      <c r="K169" s="9" t="n"/>
-      <c r="L169" s="9" t="n"/>
-      <c r="M169" s="9" t="n"/>
-      <c r="N169" s="9" t="n"/>
-    </row>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="61" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B170" s="61" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C170" s="62" t="inlineStr">
-        <is>
-          <t>UALANI_DOCK_01</t>
-        </is>
-      </c>
-      <c r="D170" s="63" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E170" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F170" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G170" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H170" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I170" s="62" t="inlineStr"/>
-      <c r="J170" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K170" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L170" s="62" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M170" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N170" s="63" t="inlineStr">
-        <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="30" customHeight="1">
-      <c r="A171" s="61" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B171" s="61" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C171" s="62" t="inlineStr">
-        <is>
-          <t>UALANI_FARM_01</t>
-        </is>
-      </c>
-      <c r="D171" s="63" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F171" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G171" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H171" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I171" s="62" t="inlineStr"/>
-      <c r="J171" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K171" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L171" s="62" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M171" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N171" s="63" t="inlineStr">
-        <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="30" customHeight="1">
-      <c r="A172" s="61" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B172" s="61" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C172" s="62" t="inlineStr">
-        <is>
-          <t>UALANI_BARRACKS_01</t>
-        </is>
-      </c>
-      <c r="D172" s="63" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F172" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G172" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H172" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I172" s="62" t="inlineStr"/>
-      <c r="J172" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K172" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L172" s="62" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M172" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N172" s="63" t="inlineStr">
-        <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="61" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B173" s="61" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C173" s="62" t="inlineStr">
-        <is>
-          <t>UALANI_COURTHOUSE_01</t>
-        </is>
-      </c>
-      <c r="D173" s="63" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F173" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G173" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H173" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I173" s="62" t="inlineStr"/>
-      <c r="J173" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K173" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L173" s="62" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M173" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N173" s="63" t="inlineStr">
-        <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
-        </is>
-      </c>
+    <row r="173" ht="8" customHeight="1">
+      <c r="A173" s="9" t="n"/>
+      <c r="B173" s="9" t="n"/>
+      <c r="C173" s="9" t="n"/>
+      <c r="D173" s="9" t="n"/>
+      <c r="E173" s="9" t="n"/>
+      <c r="F173" s="9" t="n"/>
+      <c r="G173" s="9" t="n"/>
+      <c r="H173" s="9" t="n"/>
+      <c r="I173" s="9" t="n"/>
+      <c r="J173" s="9" t="n"/>
+      <c r="K173" s="9" t="n"/>
+      <c r="L173" s="9" t="n"/>
+      <c r="M173" s="9" t="n"/>
+      <c r="N173" s="9" t="n"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="61" t="inlineStr">
@@ -11855,17 +11803,17 @@
       </c>
       <c r="B174" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C174" s="62" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>UALANI_DOCK_01</t>
         </is>
       </c>
       <c r="D174" s="63" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -11894,20 +11842,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K174" s="65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L174" s="62" t="inlineStr"/>
+      <c r="K174" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L174" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M174" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N174" s="63" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
         </is>
       </c>
     </row>
@@ -11919,17 +11871,17 @@
       </c>
       <c r="B175" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C175" s="62" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>UALANI_FARM_01</t>
         </is>
       </c>
       <c r="D175" s="63" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -11958,20 +11910,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K175" s="65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L175" s="62" t="inlineStr"/>
+      <c r="K175" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L175" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M175" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N175" s="63" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
         </is>
       </c>
     </row>
@@ -11983,17 +11939,17 @@
       </c>
       <c r="B176" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C176" s="62" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>UALANI_BARRACKS_01</t>
         </is>
       </c>
       <c r="D176" s="63" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -12022,20 +11978,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K176" s="65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L176" s="62" t="inlineStr"/>
+      <c r="K176" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L176" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M176" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N176" s="63" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
         </is>
       </c>
     </row>
@@ -12047,17 +12007,17 @@
       </c>
       <c r="B177" s="61" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C177" s="62" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
       <c r="D177" s="63" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -12086,20 +12046,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K177" s="65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L177" s="62" t="inlineStr"/>
+      <c r="K177" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L177" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M177" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N177" s="63" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
@@ -12111,32 +12075,32 @@
       </c>
       <c r="B178" s="61" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C178" s="62" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>CL_WASHINGTON_01</t>
         </is>
       </c>
       <c r="D178" s="63" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E178" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F178" s="63" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G178" s="63" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H178" s="64" t="inlineStr">
@@ -12163,7 +12127,7 @@
       </c>
       <c r="N178" s="63" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
@@ -12175,17 +12139,17 @@
       </c>
       <c r="B179" s="61" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C179" s="62" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
       <c r="D179" s="63" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -12227,7 +12191,7 @@
       </c>
       <c r="N179" s="63" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
@@ -12239,17 +12203,17 @@
       </c>
       <c r="B180" s="61" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C180" s="62" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>CX_NYC_01</t>
         </is>
       </c>
       <c r="D180" s="63" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -12291,48 +12255,304 @@
       </c>
       <c r="N180" s="63" t="inlineStr">
         <is>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B181" s="61" t="inlineStr">
+        <is>
+          <t>Espionage Events</t>
+        </is>
+      </c>
+      <c r="C181" s="62" t="inlineStr">
+        <is>
+          <t>ESPIONAGE_DISCOVERY_01</t>
+        </is>
+      </c>
+      <c r="D181" s="63" t="inlineStr">
+        <is>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F181" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G181" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H181" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I181" s="62" t="inlineStr"/>
+      <c r="J181" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K181" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L181" s="62" t="inlineStr"/>
+      <c r="M181" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N181" s="63" t="inlineStr">
+        <is>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B182" s="61" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C182" s="62" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D182" s="63" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E182" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F182" s="63" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G182" s="63" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H182" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I182" s="62" t="inlineStr"/>
+      <c r="J182" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K182" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L182" s="62" t="inlineStr"/>
+      <c r="M182" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N182" s="63" t="inlineStr">
+        <is>
+          <t>Extend the commander arc beyond first objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B183" s="61" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C183" s="62" t="inlineStr">
+        <is>
+          <t>WINTER_SIEGE_01</t>
+        </is>
+      </c>
+      <c r="D183" s="63" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F183" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G183" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H183" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I183" s="62" t="inlineStr"/>
+      <c r="J183" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K183" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L183" s="62" t="inlineStr"/>
+      <c r="M183" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N183" s="63" t="inlineStr">
+        <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B184" s="61" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C184" s="62" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D184" s="63" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F184" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G184" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H184" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I184" s="62" t="inlineStr"/>
+      <c r="J184" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K184" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L184" s="62" t="inlineStr"/>
+      <c r="M184" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N184" s="63" t="inlineStr">
+        <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="66" t="inlineStr">
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="66" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B182" s="67" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="66" t="inlineStr">
+      <c r="B186" s="67" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="66" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B183" s="67" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="184" ht="20" customHeight="1">
-      <c r="A184" s="66" t="inlineStr">
+      <c r="B187" s="67" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="66" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B184" s="67" t="n">
+      <c r="B188" s="67" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="185" ht="20" customHeight="1">
-      <c r="A185" s="66" t="inlineStr">
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="66" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B185" s="67" t="n">
-        <v>49</v>
+      <c r="B189" s="67" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -12346,7 +12566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14717,44 +14937,264 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="66" t="inlineStr">
+    <row r="37" ht="8" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C38" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01</t>
+        </is>
+      </c>
+      <c r="D38" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F38" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I38" s="54" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L38" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M38" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" s="55" t="inlineStr">
+        <is>
+          <t>Allied peace: fires when all UK dock tiles in USA+CA regions liberated (can_allied); sets uk_usa_peace+uk_ca_peace on UK country; BTN2 sensual — Ualani+Jessica celebrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C39" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_USA_01</t>
+        </is>
+      </c>
+      <c r="D39" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F39" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I39" s="54" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K39" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L39" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M39" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" s="55" t="inlineStr">
+        <is>
+          <t>USA separate peace (unallied): fires when all USA dock tiles liberated (65,66,67,151); sets uk_usa_peace on UK country; BTN2 sensual — Ualani alone at dawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C40" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_CA_AI_01</t>
+        </is>
+      </c>
+      <c r="D40" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — CANADA NEGOTIATES SEPARATE PEACE</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F40" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I40" s="54" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K40" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L40" s="54" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M40" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N40" s="55" t="inlineStr">
+        <is>
+          <t>CA separate peace (unallied): fires when Halifax (tile 114) liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="66" t="inlineStr">
         <is>
           <t>Canadian events total</t>
         </is>
       </c>
-      <c r="B38" s="67" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="66" t="inlineStr">
+      <c r="B42" s="67" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="66" t="inlineStr">
         <is>
           <t>Canada (Alliance arc)</t>
         </is>
       </c>
-      <c r="B39" s="67" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="66" t="inlineStr">
+      <c r="B43" s="67" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="66" t="inlineStr">
         <is>
           <t>CA Protector (Jessica's creatures)</t>
         </is>
       </c>
-      <c r="B40" s="67" t="n">
+      <c r="B44" s="67" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="66" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="66" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B41" s="67" t="n">
-        <v>10</v>
+      <c r="B45" s="67" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -15105,7 +15545,7 @@
       </c>
       <c r="B32" s="112" t="inlineStr">
         <is>
-          <t>Canadian Alliance diplomatic arc (war declaration + 8 CAN_ events)</t>
+          <t>Canadian Alliance diplomatic arc + 3 peace events (PEACE_ALLIED_01, PEACE_USA_01, PEACE_CA_AI_01)</t>
         </is>
       </c>
       <c r="C32" s="112" t="n"/>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -11691,7 +11691,7 @@
       </c>
       <c r="N170" s="55" t="inlineStr">
         <is>
-          <t>CA separate peace (unallied): fires when Halifax (tile 114) liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
+          <t>CA separate peace (unallied): fires when Halifax (114), Quebec City (123), and Anticosti (195) all liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
         </is>
       </c>
     </row>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="N40" s="55" t="inlineStr">
         <is>
-          <t>CA separate peace (unallied): fires when Halifax (tile 114) liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
+          <t>CA separate peace (unallied): fires when Halifax (114), Quebec City (123), and Anticosti (195) all liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
         </is>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N189"/>
+  <dimension ref="A1:N190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11504,12 +11504,12 @@
       </c>
       <c r="C168" s="54" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01</t>
+          <t>GEORGE_PEACE_01</t>
         </is>
       </c>
       <c r="D168" s="55" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
+          <t>A ROYAL LETTER ARRIVES — HIS MAJESTY PROPOSES PEACE</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -11538,14 +11538,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K168" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K168" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L168" s="54" t="inlineStr">
         <is>
-          <t>sensual option</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="M168" s="56" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N168" s="55" t="inlineStr">
         <is>
-          <t>Allied peace: fires when all UK dock tiles in USA+CA regions liberated (can_allied); sets uk_usa_peace+uk_ca_peace on UK country; BTN2 sensual — Ualani+Jessica celebrate</t>
+          <t>Fires turn 75-80 if war ongoing; BTN1 george_peace_accept (allied=both peaces, unallied=USA only); BTN2 george_peace_reject (+claim +1); never fires if peace already settled</t>
         </is>
       </c>
     </row>
@@ -11572,12 +11572,12 @@
       </c>
       <c r="C169" s="54" t="inlineStr">
         <is>
-          <t>PEACE_USA_01</t>
+          <t>PEACE_ALLIED_01</t>
         </is>
       </c>
       <c r="D169" s="55" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="N169" s="55" t="inlineStr">
         <is>
-          <t>USA separate peace (unallied): fires when all USA dock tiles liberated (65,66,67,151); sets uk_usa_peace on UK country; BTN2 sensual — Ualani alone at dawn</t>
+          <t>Allied peace: fires when all UK dock tiles in USA+CA regions liberated (can_allied); sets uk_usa_peace+uk_ca_peace on UK country; BTN2 sensual — Ualani+Jessica celebrate</t>
         </is>
       </c>
     </row>
@@ -11640,12 +11640,12 @@
       </c>
       <c r="C170" s="54" t="inlineStr">
         <is>
-          <t>PEACE_CA_AI_01</t>
+          <t>PEACE_USA_01</t>
         </is>
       </c>
       <c r="D170" s="55" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — CANADA NEGOTIATES SEPARATE PEACE</t>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -11674,194 +11674,194 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K170" s="56" t="inlineStr">
+      <c r="K170" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L170" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M170" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N170" s="55" t="inlineStr">
+        <is>
+          <t>USA separate peace (unallied): fires when all USA dock tiles liberated (65,66,67,151); sets uk_usa_peace on UK country; BTN2 sensual — Ualani alone at dawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B171" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C171" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_CA_AI_01</t>
+        </is>
+      </c>
+      <c r="D171" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — CANADA NEGOTIATES SEPARATE PEACE</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F171" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G171" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I171" s="54" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K171" s="56" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L170" s="54" t="inlineStr">
+      <c r="L171" s="54" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M170" s="56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N170" s="55" t="inlineStr">
+      <c r="M171" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N171" s="55" t="inlineStr">
         <is>
           <t>CA separate peace (unallied): fires when Halifax (114), Quebec City (123), and Anticosti (195) all liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="8" customHeight="1">
-      <c r="A171" s="9" t="n"/>
-      <c r="B171" s="9" t="n"/>
-      <c r="C171" s="9" t="n"/>
-      <c r="D171" s="9" t="n"/>
-      <c r="E171" s="9" t="n"/>
-      <c r="F171" s="9" t="n"/>
-      <c r="G171" s="9" t="n"/>
-      <c r="H171" s="9" t="n"/>
-      <c r="I171" s="9" t="n"/>
-      <c r="J171" s="9" t="n"/>
-      <c r="K171" s="9" t="n"/>
-      <c r="L171" s="9" t="n"/>
-      <c r="M171" s="9" t="n"/>
-      <c r="N171" s="9" t="n"/>
-    </row>
-    <row r="172" ht="30" customHeight="1">
-      <c r="A172" s="49" t="inlineStr">
+    <row r="172" ht="8" customHeight="1">
+      <c r="A172" s="9" t="n"/>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="9" t="n"/>
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="n"/>
+      <c r="G172" s="9" t="n"/>
+      <c r="H172" s="9" t="n"/>
+      <c r="I172" s="9" t="n"/>
+      <c r="J172" s="9" t="n"/>
+      <c r="K172" s="9" t="n"/>
+      <c r="L172" s="9" t="n"/>
+      <c r="M172" s="9" t="n"/>
+      <c r="N172" s="9" t="n"/>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="49" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B172" s="49" t="inlineStr">
+      <c r="B173" s="49" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C172" s="50" t="inlineStr">
+      <c r="C173" s="50" t="inlineStr">
         <is>
           <t>VP_LEGACY</t>
         </is>
       </c>
-      <c r="D172" s="51" t="inlineStr">
+      <c r="D173" s="51" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
         </is>
       </c>
-      <c r="E172" s="22" t="inlineStr">
+      <c r="E173" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F172" s="51" t="inlineStr">
+      <c r="F173" s="51" t="inlineStr">
         <is>
           <t>VP_FIRST_MEETING (turn 96+)</t>
         </is>
       </c>
-      <c r="G172" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I172" s="50" t="inlineStr"/>
-      <c r="J172" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K172" s="26" t="inlineStr">
+      <c r="G173" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I173" s="50" t="inlineStr"/>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K173" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L172" s="50" t="inlineStr">
+      <c r="L173" s="50" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M172" s="52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N172" s="51" t="inlineStr">
+      <c r="M173" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N173" s="51" t="inlineStr">
         <is>
           <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="8" customHeight="1">
-      <c r="A173" s="9" t="n"/>
-      <c r="B173" s="9" t="n"/>
-      <c r="C173" s="9" t="n"/>
-      <c r="D173" s="9" t="n"/>
-      <c r="E173" s="9" t="n"/>
-      <c r="F173" s="9" t="n"/>
-      <c r="G173" s="9" t="n"/>
-      <c r="H173" s="9" t="n"/>
-      <c r="I173" s="9" t="n"/>
-      <c r="J173" s="9" t="n"/>
-      <c r="K173" s="9" t="n"/>
-      <c r="L173" s="9" t="n"/>
-      <c r="M173" s="9" t="n"/>
-      <c r="N173" s="9" t="n"/>
-    </row>
-    <row r="174" ht="30" customHeight="1">
-      <c r="A174" s="61" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B174" s="61" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C174" s="62" t="inlineStr">
-        <is>
-          <t>UALANI_DOCK_01</t>
-        </is>
-      </c>
-      <c r="D174" s="63" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F174" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G174" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H174" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I174" s="62" t="inlineStr"/>
-      <c r="J174" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K174" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L174" s="62" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M174" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N174" s="63" t="inlineStr">
-        <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
-        </is>
-      </c>
+    <row r="174" ht="8" customHeight="1">
+      <c r="A174" s="9" t="n"/>
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="9" t="n"/>
+      <c r="D174" s="9" t="n"/>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="n"/>
+      <c r="G174" s="9" t="n"/>
+      <c r="H174" s="9" t="n"/>
+      <c r="I174" s="9" t="n"/>
+      <c r="J174" s="9" t="n"/>
+      <c r="K174" s="9" t="n"/>
+      <c r="L174" s="9" t="n"/>
+      <c r="M174" s="9" t="n"/>
+      <c r="N174" s="9" t="n"/>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="61" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C175" s="62" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>UALANI_DOCK_01</t>
         </is>
       </c>
       <c r="D175" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="N175" s="63" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
         </is>
       </c>
     </row>
@@ -11944,12 +11944,12 @@
       </c>
       <c r="C176" s="62" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>UALANI_FARM_01</t>
         </is>
       </c>
       <c r="D176" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="N176" s="63" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="C177" s="62" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>UALANI_BARRACKS_01</t>
         </is>
       </c>
       <c r="D177" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="N177" s="63" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
         </is>
       </c>
     </row>
@@ -12075,17 +12075,17 @@
       </c>
       <c r="B178" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C178" s="62" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
       <c r="D178" s="63" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -12114,20 +12114,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K178" s="65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L178" s="62" t="inlineStr"/>
+      <c r="K178" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L178" s="62" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M178" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N178" s="63" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
@@ -12144,12 +12148,12 @@
       </c>
       <c r="C179" s="62" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>CL_WASHINGTON_01</t>
         </is>
       </c>
       <c r="D179" s="63" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -12191,7 +12195,7 @@
       </c>
       <c r="N179" s="63" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
@@ -12208,12 +12212,12 @@
       </c>
       <c r="C180" s="62" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
       <c r="D180" s="63" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -12255,7 +12259,7 @@
       </c>
       <c r="N180" s="63" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
@@ -12267,17 +12271,17 @@
       </c>
       <c r="B181" s="61" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C181" s="62" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>CX_NYC_01</t>
         </is>
       </c>
       <c r="D181" s="63" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -12319,7 +12323,7 @@
       </c>
       <c r="N181" s="63" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12335,32 @@
       </c>
       <c r="B182" s="61" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>Espionage Events</t>
         </is>
       </c>
       <c r="C182" s="62" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
       <c r="D182" s="63" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E182" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F182" s="63" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G182" s="63" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H182" s="64" t="inlineStr">
@@ -12383,7 +12387,7 @@
       </c>
       <c r="N182" s="63" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
         </is>
       </c>
     </row>
@@ -12395,32 +12399,32 @@
       </c>
       <c r="B183" s="61" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Commander Expansion</t>
         </is>
       </c>
       <c r="C183" s="62" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>CMD_OBJECTIVE_2</t>
         </is>
       </c>
       <c r="D183" s="63" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E183" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E183" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F183" s="63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CMD_OBJECTIVE_1</t>
         </is>
       </c>
       <c r="G183" s="63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ CMD_OBJECTIVE_3?</t>
         </is>
       </c>
       <c r="H183" s="64" t="inlineStr">
@@ -12447,7 +12451,7 @@
       </c>
       <c r="N183" s="63" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
@@ -12464,12 +12468,12 @@
       </c>
       <c r="C184" s="62" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>WINTER_SIEGE_01</t>
         </is>
       </c>
       <c r="D184" s="63" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -12511,47 +12515,111 @@
       </c>
       <c r="N184" s="63" t="inlineStr">
         <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="61" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B185" s="61" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C185" s="62" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D185" s="63" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F185" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G185" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H185" s="64" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I185" s="62" t="inlineStr"/>
+      <c r="J185" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K185" s="65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L185" s="62" t="inlineStr"/>
+      <c r="M185" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N185" s="63" t="inlineStr">
+        <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="66" t="inlineStr">
-        <is>
-          <t>Total events in spreadsheet</t>
-        </is>
-      </c>
-      <c r="B186" s="67" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="66" t="inlineStr">
         <is>
-          <t>FIRST PASS (coded &amp; wired)</t>
+          <t>Total events in spreadsheet</t>
         </is>
       </c>
       <c r="B187" s="67" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="66" t="inlineStr">
         <is>
-          <t>IDEA (not yet implemented)</t>
+          <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
       <c r="B188" s="67" t="n">
-        <v>11</v>
+        <v>157</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="66" t="inlineStr">
         <is>
+          <t>IDEA (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="B189" s="67" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="66" t="inlineStr">
+        <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B189" s="67" t="n">
+      <c r="B190" s="67" t="n">
         <v>51</v>
       </c>
     </row>
@@ -12566,7 +12634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14966,12 +15034,12 @@
       </c>
       <c r="C38" s="54" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01</t>
+          <t>GEORGE_PEACE_01</t>
         </is>
       </c>
       <c r="D38" s="55" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
+          <t>A ROYAL LETTER ARRIVES — HIS MAJESTY PROPOSES PEACE</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15000,14 +15068,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K38" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K38" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L38" s="54" t="inlineStr">
         <is>
-          <t>sensual option</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="M38" s="56" t="inlineStr">
@@ -15017,7 +15085,7 @@
       </c>
       <c r="N38" s="55" t="inlineStr">
         <is>
-          <t>Allied peace: fires when all UK dock tiles in USA+CA regions liberated (can_allied); sets uk_usa_peace+uk_ca_peace on UK country; BTN2 sensual — Ualani+Jessica celebrate</t>
+          <t>Fires turn 75-80 if war ongoing; BTN1 george_peace_accept (allied=both peaces, unallied=USA only); BTN2 george_peace_reject (+claim +1); never fires if peace already settled</t>
         </is>
       </c>
     </row>
@@ -15034,12 +15102,12 @@
       </c>
       <c r="C39" s="54" t="inlineStr">
         <is>
-          <t>PEACE_USA_01</t>
+          <t>PEACE_ALLIED_01</t>
         </is>
       </c>
       <c r="D39" s="55" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15085,7 +15153,7 @@
       </c>
       <c r="N39" s="55" t="inlineStr">
         <is>
-          <t>USA separate peace (unallied): fires when all USA dock tiles liberated (65,66,67,151); sets uk_usa_peace on UK country; BTN2 sensual — Ualani alone at dawn</t>
+          <t>Allied peace: fires when all UK dock tiles in USA+CA regions liberated (can_allied); sets uk_usa_peace+uk_ca_peace on UK country; BTN2 sensual — Ualani+Jessica celebrate</t>
         </is>
       </c>
     </row>
@@ -15102,12 +15170,12 @@
       </c>
       <c r="C40" s="54" t="inlineStr">
         <is>
-          <t>PEACE_CA_AI_01</t>
+          <t>PEACE_USA_01</t>
         </is>
       </c>
       <c r="D40" s="55" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — CANADA NEGOTIATES SEPARATE PEACE</t>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15136,64 +15204,132 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K40" s="56" t="inlineStr">
+      <c r="K40" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L40" s="54" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M40" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N40" s="55" t="inlineStr">
+        <is>
+          <t>USA separate peace (unallied): fires when all USA dock tiles liberated (65,66,67,151); sets uk_usa_peace on UK country; BTN2 sensual — Ualani alone at dawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B41" s="53" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C41" s="54" t="inlineStr">
+        <is>
+          <t>PEACE_CA_AI_01</t>
+        </is>
+      </c>
+      <c r="D41" s="55" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — CANADA NEGOTIATES SEPARATE PEACE</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F41" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I41" s="54" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K41" s="56" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L40" s="54" t="inlineStr">
+      <c r="L41" s="54" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M40" s="56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N40" s="55" t="inlineStr">
+      <c r="M41" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N41" s="55" t="inlineStr">
         <is>
           <t>CA separate peace (unallied): fires when Halifax (114), Quebec City (123), and Anticosti (195) all liberated; sets uk_ca_peace on UK+CA; player-visible dispatch; both buttons standard</t>
         </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="66" t="inlineStr">
-        <is>
-          <t>Canadian events total</t>
-        </is>
-      </c>
-      <c r="B42" s="67" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="66" t="inlineStr">
         <is>
-          <t>Canada (Alliance arc)</t>
+          <t>Canadian events total</t>
         </is>
       </c>
       <c r="B43" s="67" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="66" t="inlineStr">
         <is>
-          <t>CA Protector (Jessica's creatures)</t>
+          <t>Canada (Alliance arc)</t>
         </is>
       </c>
       <c r="B44" s="67" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="66" t="inlineStr">
         <is>
+          <t>CA Protector (Jessica's creatures)</t>
+        </is>
+      </c>
+      <c r="B45" s="67" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="66" t="inlineStr">
+        <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B45" s="67" t="n">
+      <c r="B46" s="67" t="n">
         <v>12</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -185,7 +185,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -289,6 +289,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F5ECD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE0F7"/>
       </patternFill>
     </fill>
@@ -339,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -528,10 +533,22 @@
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -543,10 +560,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -555,10 +572,10 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -567,10 +584,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,10 +596,10 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -685,6 +702,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1052,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N190"/>
+  <dimension ref="A1:N216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11780,37 +11803,37 @@
       <c r="N172" s="9" t="n"/>
     </row>
     <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="49" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="B173" s="49" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="C173" s="50" t="inlineStr">
-        <is>
-          <t>VP_LEGACY</t>
-        </is>
-      </c>
-      <c r="D173" s="51" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
-        </is>
-      </c>
-      <c r="E173" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
-        </is>
-      </c>
-      <c r="F173" s="51" t="inlineStr">
-        <is>
-          <t>VP_FIRST_MEETING (turn 96+)</t>
-        </is>
-      </c>
-      <c r="G173" s="51" t="inlineStr">
+      <c r="A173" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B173" s="61" t="inlineStr">
+        <is>
+          <t>Wetlands Fisher</t>
+        </is>
+      </c>
+      <c r="C173" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_01</t>
+        </is>
+      </c>
+      <c r="D173" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL WETLANDS FISHER)</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F173" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G173" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11820,68 +11843,120 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I173" s="50" t="inlineStr"/>
+      <c r="I173" s="62" t="inlineStr"/>
       <c r="J173" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K173" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L173" s="50" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M173" s="52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N173" s="51" t="inlineStr">
-        <is>
-          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="8" customHeight="1">
-      <c r="A174" s="9" t="n"/>
-      <c r="B174" s="9" t="n"/>
-      <c r="C174" s="9" t="n"/>
-      <c r="D174" s="9" t="n"/>
-      <c r="E174" s="9" t="n"/>
-      <c r="F174" s="9" t="n"/>
-      <c r="G174" s="9" t="n"/>
-      <c r="H174" s="9" t="n"/>
-      <c r="I174" s="9" t="n"/>
-      <c r="J174" s="9" t="n"/>
-      <c r="K174" s="9" t="n"/>
-      <c r="L174" s="9" t="n"/>
-      <c r="M174" s="9" t="n"/>
-      <c r="N174" s="9" t="n"/>
+      <c r="K173" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L173" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M173" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N173" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B174" s="61" t="inlineStr">
+        <is>
+          <t>Appalachian Miner</t>
+        </is>
+      </c>
+      <c r="C174" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_02</t>
+        </is>
+      </c>
+      <c r="D174" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL APPALACHIAN MINER)</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F174" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I174" s="62" t="inlineStr"/>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K174" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L174" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M174" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N174" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield metal×5; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B175" s="61" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Ivy League Dropout</t>
         </is>
       </c>
       <c r="C175" s="62" t="inlineStr">
         <is>
-          <t>UALANI_DOCK_01</t>
+          <t>GOV_LOYAL_ARC_03</t>
         </is>
       </c>
       <c r="D175" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL IVY LEAGUE DROPOUT)</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -11899,9 +11974,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H175" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I175" s="62" t="inlineStr"/>
@@ -11910,46 +11985,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K175" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K175" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L175" s="62" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M175" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M175" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N175" s="63" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B176" s="61" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Seminole Fighter</t>
         </is>
       </c>
       <c r="C176" s="62" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>GOV_LOYAL_ARC_04</t>
         </is>
       </c>
       <c r="D176" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SEMINOLE FIGHTER)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -11967,9 +12042,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H176" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I176" s="62" t="inlineStr"/>
@@ -11978,46 +12053,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K176" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K176" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L176" s="62" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M176" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M176" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N176" s="63" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>tile_yield manpower×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B177" s="61" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Green Mountain Farmer</t>
         </is>
       </c>
       <c r="C177" s="62" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>GOV_LOYAL_ARC_05</t>
         </is>
       </c>
       <c r="D177" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GREEN MOUNTAIN FARMER)</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -12035,9 +12110,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H177" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I177" s="62" t="inlineStr"/>
@@ -12046,46 +12121,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K177" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K177" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L177" s="62" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M177" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M177" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N177" s="63" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>tile_yield food×5; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B178" s="61" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Chesapeake Shipwright</t>
         </is>
       </c>
       <c r="C178" s="62" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>GOV_LOYAL_ARC_06</t>
         </is>
       </c>
       <c r="D178" s="63" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CHESAPEAKE SHIPWRIGHT)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -12103,9 +12178,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H178" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I178" s="62" t="inlineStr"/>
@@ -12114,46 +12189,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K178" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K178" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L178" s="62" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M178" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M178" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N178" s="63" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B179" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Loyalist Turncoat</t>
         </is>
       </c>
       <c r="C179" s="62" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>GOV_LOYAL_ARC_07</t>
         </is>
       </c>
       <c r="D179" s="63" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LOYALIST TURNCOAT)</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -12171,9 +12246,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H179" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I179" s="62" t="inlineStr"/>
@@ -12182,42 +12257,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K179" s="65" t="inlineStr">
+      <c r="K179" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L179" s="62" t="inlineStr"/>
-      <c r="M179" s="65" t="inlineStr">
+      <c r="L179" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M179" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N179" s="63" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B180" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Tobacco Belt Drifter</t>
         </is>
       </c>
       <c r="C180" s="62" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>GOV_LOYAL_ARC_08</t>
         </is>
       </c>
       <c r="D180" s="63" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL TOBACCO BELT DRIFTER)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -12235,9 +12314,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H180" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I180" s="62" t="inlineStr"/>
@@ -12246,42 +12325,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K180" s="65" t="inlineStr">
+      <c r="K180" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L180" s="62" t="inlineStr"/>
-      <c r="M180" s="65" t="inlineStr">
+      <c r="L180" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M180" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N180" s="63" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B181" s="61" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>War Widow</t>
         </is>
       </c>
       <c r="C181" s="62" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>GOV_LOYAL_ARC_09</t>
         </is>
       </c>
       <c r="D181" s="63" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL WAR WIDOW)</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -12299,9 +12382,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H181" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I181" s="62" t="inlineStr"/>
@@ -12310,42 +12393,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K181" s="65" t="inlineStr">
+      <c r="K181" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L181" s="62" t="inlineStr"/>
-      <c r="M181" s="65" t="inlineStr">
+      <c r="L181" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M181" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N181" s="63" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B182" s="61" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>Indigenous Scout</t>
         </is>
       </c>
       <c r="C182" s="62" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>GOV_LOYAL_ARC_10</t>
         </is>
       </c>
       <c r="D182" s="63" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL INDIGENOUS SCOUT)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -12363,9 +12450,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H182" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I182" s="62" t="inlineStr"/>
@@ -12374,62 +12461,66 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K182" s="65" t="inlineStr">
+      <c r="K182" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L182" s="62" t="inlineStr"/>
-      <c r="M182" s="65" t="inlineStr">
+      <c r="L182" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M182" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N182" s="63" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>tile_yield manpower×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B183" s="61" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="C183" s="62" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>GOV_LOYAL_ARC_11</t>
         </is>
       </c>
       <c r="D183" s="63" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E183" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BOSTON RABBLE-ROUSER)</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F183" s="63" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G183" s="63" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
-        </is>
-      </c>
-      <c r="H183" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I183" s="62" t="inlineStr"/>
@@ -12438,42 +12529,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K183" s="65" t="inlineStr">
+      <c r="K183" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L183" s="62" t="inlineStr"/>
-      <c r="M183" s="65" t="inlineStr">
+      <c r="L183" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M183" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N183" s="63" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B184" s="61" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C184" s="62" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>GOV_LOYAL_ARC_12</t>
         </is>
       </c>
       <c r="D184" s="63" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CONTINENTAL SURGEON)</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -12491,9 +12586,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H184" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I184" s="62" t="inlineStr"/>
@@ -12502,42 +12597,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K184" s="65" t="inlineStr">
+      <c r="K184" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L184" s="62" t="inlineStr"/>
-      <c r="M184" s="65" t="inlineStr">
+      <c r="L184" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M184" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N184" s="63" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="61" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Loyal Governor</t>
         </is>
       </c>
       <c r="B185" s="61" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C185" s="62" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>GOV_LOYAL_ARC_13</t>
         </is>
       </c>
       <c r="D185" s="63" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL NANTUCKET SAILOR)</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -12555,9 +12654,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H185" s="64" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I185" s="62" t="inlineStr"/>
@@ -12566,60 +12665,1700 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K185" s="65" t="inlineStr">
+      <c r="K185" s="64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L185" s="62" t="inlineStr"/>
-      <c r="M185" s="65" t="inlineStr">
+      <c r="L185" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M185" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N185" s="63" t="inlineStr">
         <is>
+          <t>tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B186" s="61" t="inlineStr">
+        <is>
+          <t>Frontier Preacher</t>
+        </is>
+      </c>
+      <c r="C186" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_14</t>
+        </is>
+      </c>
+      <c r="D186" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL FRONTIER PREACHER)</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F186" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G186" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I186" s="62" t="inlineStr"/>
+      <c r="J186" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K186" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L186" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M186" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N186" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B187" s="61" t="inlineStr">
+        <is>
+          <t>DC Bureaucrat</t>
+        </is>
+      </c>
+      <c r="C187" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_15</t>
+        </is>
+      </c>
+      <c r="D187" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL DC BUREAUCRAT)</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F187" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G187" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I187" s="62" t="inlineStr"/>
+      <c r="J187" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K187" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L187" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M187" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N187" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B188" s="61" t="inlineStr">
+        <is>
+          <t>Rust Belt Steelworker</t>
+        </is>
+      </c>
+      <c r="C188" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_16</t>
+        </is>
+      </c>
+      <c r="D188" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL RUST BELT STEELWORKER)</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F188" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G188" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I188" s="62" t="inlineStr"/>
+      <c r="J188" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K188" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L188" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M188" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N188" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield metal×5; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B189" s="61" t="inlineStr">
+        <is>
+          <t>Plantation Deserter</t>
+        </is>
+      </c>
+      <c r="C189" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_17</t>
+        </is>
+      </c>
+      <c r="D189" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL PLANTATION DESERTER)</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F189" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G189" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I189" s="62" t="inlineStr"/>
+      <c r="J189" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K189" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L189" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M189" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N189" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B190" s="61" t="inlineStr">
+        <is>
+          <t>Swamp Witch</t>
+        </is>
+      </c>
+      <c r="C190" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_18</t>
+        </is>
+      </c>
+      <c r="D190" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SWAMP WITCH)</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F190" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G190" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I190" s="62" t="inlineStr"/>
+      <c r="J190" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K190" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L190" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M190" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N190" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield magic×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B191" s="61" t="inlineStr">
+        <is>
+          <t>Caribbean Privateer</t>
+        </is>
+      </c>
+      <c r="C191" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_19</t>
+        </is>
+      </c>
+      <c r="D191" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARIBBEAN PRIVATEER)</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F191" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G191" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I191" s="62" t="inlineStr"/>
+      <c r="J191" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K191" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L191" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M191" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N191" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B192" s="61" t="inlineStr">
+        <is>
+          <t>Hawaiian Refugee</t>
+        </is>
+      </c>
+      <c r="C192" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_20</t>
+        </is>
+      </c>
+      <c r="D192" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL HAWAIIAN REFUGEE)</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F192" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G192" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I192" s="62" t="inlineStr"/>
+      <c r="J192" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K192" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L192" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M192" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N192" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield food×3; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B193" s="61" t="inlineStr">
+        <is>
+          <t>Border Mercenary</t>
+        </is>
+      </c>
+      <c r="C193" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_21</t>
+        </is>
+      </c>
+      <c r="D193" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BORDER MERCENARY)</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F193" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G193" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I193" s="62" t="inlineStr"/>
+      <c r="J193" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K193" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L193" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M193" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N193" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield weapons×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B194" s="61" t="inlineStr">
+        <is>
+          <t>Acadian Forest Ranger</t>
+        </is>
+      </c>
+      <c r="C194" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_22</t>
+        </is>
+      </c>
+      <c r="D194" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F194" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G194" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I194" s="62" t="inlineStr"/>
+      <c r="J194" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K194" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L194" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M194" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N194" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B195" s="61" t="inlineStr">
+        <is>
+          <t>Gettysburg Descendant</t>
+        </is>
+      </c>
+      <c r="C195" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_23</t>
+        </is>
+      </c>
+      <c r="D195" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F195" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G195" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I195" s="62" t="inlineStr"/>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K195" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L195" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M195" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N195" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B196" s="61" t="inlineStr">
+        <is>
+          <t>LGBTQ+ Organizer</t>
+        </is>
+      </c>
+      <c r="C196" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_24</t>
+        </is>
+      </c>
+      <c r="D196" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F196" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I196" s="62" t="inlineStr"/>
+      <c r="J196" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K196" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L196" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M196" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N196" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="61" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B197" s="61" t="inlineStr">
+        <is>
+          <t>Carnival Barker</t>
+        </is>
+      </c>
+      <c r="C197" s="62" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_25</t>
+        </is>
+      </c>
+      <c r="D197" s="63" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F197" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I197" s="62" t="inlineStr"/>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K197" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L197" s="62" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M197" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N197" s="63" t="inlineStr">
+        <is>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="8" customHeight="1">
+      <c r="A198" s="9" t="n"/>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="9" t="n"/>
+      <c r="E198" s="9" t="n"/>
+      <c r="F198" s="9" t="n"/>
+      <c r="G198" s="9" t="n"/>
+      <c r="H198" s="9" t="n"/>
+      <c r="I198" s="9" t="n"/>
+      <c r="J198" s="9" t="n"/>
+      <c r="K198" s="9" t="n"/>
+      <c r="L198" s="9" t="n"/>
+      <c r="M198" s="9" t="n"/>
+      <c r="N198" s="9" t="n"/>
+    </row>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B199" s="49" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C199" s="50" t="inlineStr">
+        <is>
+          <t>VP_LEGACY</t>
+        </is>
+      </c>
+      <c r="D199" s="51" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
+        </is>
+      </c>
+      <c r="E199" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F199" s="51" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (turn 96+)</t>
+        </is>
+      </c>
+      <c r="G199" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I199" s="50" t="inlineStr"/>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K199" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L199" s="50" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M199" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N199" s="51" t="inlineStr">
+        <is>
+          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="8" customHeight="1">
+      <c r="A200" s="9" t="n"/>
+      <c r="B200" s="9" t="n"/>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="9" t="n"/>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="9" t="n"/>
+      <c r="G200" s="9" t="n"/>
+      <c r="H200" s="9" t="n"/>
+      <c r="I200" s="9" t="n"/>
+      <c r="J200" s="9" t="n"/>
+      <c r="K200" s="9" t="n"/>
+      <c r="L200" s="9" t="n"/>
+      <c r="M200" s="9" t="n"/>
+      <c r="N200" s="9" t="n"/>
+    </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B201" s="65" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C201" s="66" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D201" s="67" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F201" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G201" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H201" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I201" s="66" t="inlineStr"/>
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K201" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L201" s="66" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M201" s="69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N201" s="67" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="30" customHeight="1">
+      <c r="A202" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B202" s="65" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C202" s="66" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D202" s="67" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F202" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G202" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H202" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I202" s="66" t="inlineStr"/>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K202" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L202" s="66" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M202" s="69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N202" s="67" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="30" customHeight="1">
+      <c r="A203" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B203" s="65" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C203" s="66" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D203" s="67" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F203" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G203" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H203" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I203" s="66" t="inlineStr"/>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K203" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L203" s="66" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M203" s="69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N203" s="67" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="30" customHeight="1">
+      <c r="A204" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B204" s="65" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C204" s="66" t="inlineStr">
+        <is>
+          <t>UALANI_COURTHOUSE_01</t>
+        </is>
+      </c>
+      <c r="D204" s="67" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F204" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G204" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H204" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I204" s="66" t="inlineStr"/>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K204" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L204" s="66" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M204" s="69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N204" s="67" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="30" customHeight="1">
+      <c r="A205" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B205" s="65" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C205" s="66" t="inlineStr">
+        <is>
+          <t>CL_WASHINGTON_01</t>
+        </is>
+      </c>
+      <c r="D205" s="67" t="inlineStr">
+        <is>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F205" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H205" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I205" s="66" t="inlineStr"/>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K205" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L205" s="66" t="inlineStr"/>
+      <c r="M205" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N205" s="67" t="inlineStr">
+        <is>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="30" customHeight="1">
+      <c r="A206" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B206" s="65" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C206" s="66" t="inlineStr">
+        <is>
+          <t>CL_VALLEY_FORGE_01</t>
+        </is>
+      </c>
+      <c r="D206" s="67" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F206" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G206" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H206" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I206" s="66" t="inlineStr"/>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K206" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L206" s="66" t="inlineStr"/>
+      <c r="M206" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N206" s="67" t="inlineStr">
+        <is>
+          <t>Tile 1; historically significant; would fire on liberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B207" s="65" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C207" s="66" t="inlineStr">
+        <is>
+          <t>CX_NYC_01</t>
+        </is>
+      </c>
+      <c r="D207" s="67" t="inlineStr">
+        <is>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F207" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H207" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I207" s="66" t="inlineStr"/>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K207" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L207" s="66" t="inlineStr"/>
+      <c r="M207" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N207" s="67" t="inlineStr">
+        <is>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B208" s="65" t="inlineStr">
+        <is>
+          <t>Espionage Events</t>
+        </is>
+      </c>
+      <c r="C208" s="66" t="inlineStr">
+        <is>
+          <t>ESPIONAGE_DISCOVERY_01</t>
+        </is>
+      </c>
+      <c r="D208" s="67" t="inlineStr">
+        <is>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F208" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H208" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I208" s="66" t="inlineStr"/>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K208" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L208" s="66" t="inlineStr"/>
+      <c r="M208" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N208" s="67" t="inlineStr">
+        <is>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B209" s="65" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C209" s="66" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D209" s="67" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E209" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F209" s="67" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G209" s="67" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H209" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I209" s="66" t="inlineStr"/>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K209" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L209" s="66" t="inlineStr"/>
+      <c r="M209" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N209" s="67" t="inlineStr">
+        <is>
+          <t>Extend the commander arc beyond first objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B210" s="65" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C210" s="66" t="inlineStr">
+        <is>
+          <t>WINTER_SIEGE_01</t>
+        </is>
+      </c>
+      <c r="D210" s="67" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F210" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G210" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H210" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I210" s="66" t="inlineStr"/>
+      <c r="J210" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K210" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L210" s="66" t="inlineStr"/>
+      <c r="M210" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N210" s="67" t="inlineStr">
+        <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="30" customHeight="1">
+      <c r="A211" s="65" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B211" s="65" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C211" s="66" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D211" s="67" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F211" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G211" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H211" s="68" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I211" s="66" t="inlineStr"/>
+      <c r="J211" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K211" s="69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L211" s="66" t="inlineStr"/>
+      <c r="M211" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N211" s="67" t="inlineStr">
+        <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="66" t="inlineStr">
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="70" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B187" s="67" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="66" t="inlineStr">
+      <c r="B213" s="71" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="70" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B188" s="67" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="189" ht="20" customHeight="1">
-      <c r="A189" s="66" t="inlineStr">
+      <c r="B214" s="71" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="70" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B189" s="67" t="n">
+      <c r="B215" s="71" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="66" t="inlineStr">
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="70" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B190" s="67" t="n">
+      <c r="B216" s="71" t="n">
         <v>51</v>
       </c>
     </row>
@@ -15294,42 +17033,42 @@
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="66" t="inlineStr">
+      <c r="A43" s="70" t="inlineStr">
         <is>
           <t>Canadian events total</t>
         </is>
       </c>
-      <c r="B43" s="67" t="n">
+      <c r="B43" s="71" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="66" t="inlineStr">
+      <c r="A44" s="70" t="inlineStr">
         <is>
           <t>Canada (Alliance arc)</t>
         </is>
       </c>
-      <c r="B44" s="67" t="n">
+      <c r="B44" s="71" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="66" t="inlineStr">
+      <c r="A45" s="70" t="inlineStr">
         <is>
           <t>CA Protector (Jessica's creatures)</t>
         </is>
       </c>
-      <c r="B45" s="67" t="n">
+      <c r="B45" s="71" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="66" t="inlineStr">
+      <c r="A46" s="70" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B46" s="67" t="n">
+      <c r="B46" s="71" t="n">
         <v>12</v>
       </c>
     </row>
@@ -15344,7 +17083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15353,364 +17092,377 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="73" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="B2" s="70" t="inlineStr">
+      <c r="B2" s="74" t="inlineStr">
         <is>
           <t>Final pass done — art integrated, text finalized, fully tested</t>
         </is>
       </c>
-      <c r="C2" s="70" t="n"/>
+      <c r="C2" s="74" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="71" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Event is coded, in CSV, all buttons wired; no final polish yet</t>
         </is>
       </c>
-      <c r="C3" s="72" t="n"/>
+      <c r="C3" s="76" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="73" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>Concept stage: not in events.csv; some referenced in button CSV</t>
         </is>
       </c>
-      <c r="C4" s="74" t="n"/>
+      <c r="C4" s="78" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>ART STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="A7" s="79" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>No art asset exists yet</t>
         </is>
       </c>
-      <c r="C7" s="76" t="n"/>
+      <c r="C7" s="80" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>Art is being created but not in engine</t>
         </is>
       </c>
-      <c r="C8" s="74" t="n"/>
+      <c r="C8" s="78" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="B9" s="78" t="inlineStr">
+      <c r="B9" s="82" t="inlineStr">
         <is>
           <t>Art is in the project and referenced correctly</t>
         </is>
       </c>
-      <c r="C9" s="78" t="n"/>
+      <c r="C9" s="82" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>EXPLICIT ART LEGEND</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>YES — Explicit Art Needed</t>
         </is>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="84" t="inlineStr">
         <is>
           <t>Event has explicit or kinky_lewd content flag OR has at least one explicit button option that will need unique explicit artwork</t>
         </is>
       </c>
-      <c r="C12" s="80" t="n"/>
+      <c r="C12" s="84" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="81" t="inlineStr">
+      <c r="A13" s="85" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B13" s="86" t="inlineStr">
         <is>
           <t>Standard event — no adult artwork required</t>
         </is>
       </c>
-      <c r="C13" s="82" t="n"/>
+      <c r="C13" s="86" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>CHAIN POSITION LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="83" t="inlineStr">
+      <c r="A16" s="87" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B16" s="84" t="inlineStr">
+      <c r="B16" s="88" t="inlineStr">
         <is>
           <t>Standalone event or first event in a chain; fires from world.gd check function or EventDatabase date trigger</t>
         </is>
       </c>
-      <c r="C16" s="84" t="n"/>
+      <c r="C16" s="88" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="85" t="inlineStr">
+      <c r="A17" s="89" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B17" s="86" t="inlineStr">
+      <c r="B17" s="90" t="inlineStr">
         <is>
           <t>Fires as outcome of a choice button on a Root/prior event; represents one path in a fork</t>
         </is>
       </c>
-      <c r="C17" s="86" t="n"/>
+      <c r="C17" s="90" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="87" t="inlineStr">
+      <c r="A18" s="91" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="B18" s="88" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
         <is>
           <t>Fires automatically after a mission completes (via next_event_id or mission flag return)</t>
         </is>
       </c>
-      <c r="C18" s="88" t="n"/>
+      <c r="C18" s="92" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="68" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>CATEGORY COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="89" t="inlineStr">
+      <c r="A21" s="93" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B21" s="90" t="inlineStr">
+      <c r="B21" s="94" t="inlineStr">
         <is>
           <t>Calendar-triggered events; month or turn-based</t>
         </is>
       </c>
-      <c r="C21" s="90" t="n"/>
+      <c r="C21" s="94" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="91" t="inlineStr">
+      <c r="A22" s="95" t="inlineStr">
         <is>
           <t>City Liberated</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
+      <c r="B22" s="96" t="inlineStr">
         <is>
           <t>Fires when a specific tile is liberated (city_liberated type)</t>
         </is>
       </c>
-      <c r="C22" s="92" t="n"/>
+      <c r="C22" s="96" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="93" t="inlineStr">
+      <c r="A23" s="97" t="inlineStr">
         <is>
           <t>City Lost</t>
         </is>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B23" s="98" t="inlineStr">
         <is>
           <t>Fires when a specific tile falls to the enemy (city_lost type)</t>
         </is>
       </c>
-      <c r="C23" s="94" t="n"/>
+      <c r="C23" s="98" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="95" t="inlineStr">
+      <c r="A24" s="99" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B24" s="96" t="inlineStr">
+      <c r="B24" s="100" t="inlineStr">
         <is>
           <t>State-level liberation, secession, and reintegration</t>
         </is>
       </c>
-      <c r="C24" s="96" t="n"/>
+      <c r="C24" s="100" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="97" t="inlineStr">
+      <c r="A25" s="101" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B25" s="98" t="inlineStr">
+      <c r="B25" s="102" t="inlineStr">
         <is>
           <t>Mythological entity summon events (protector_summon type)</t>
         </is>
       </c>
-      <c r="C25" s="98" t="n"/>
+      <c r="C25" s="102" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="99" t="inlineStr">
+      <c r="A26" s="103" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B26" s="100" t="inlineStr">
+      <c r="B26" s="104" t="inlineStr">
         <is>
           <t>Named commander arc events (commander_* types)</t>
         </is>
       </c>
-      <c r="C26" s="100" t="n"/>
+      <c r="C26" s="104" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="101" t="inlineStr">
+      <c r="A27" s="105" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B27" s="102" t="inlineStr">
+      <c r="B27" s="106" t="inlineStr">
         <is>
           <t>Fort disrepair investigation chain (fort_* types)</t>
         </is>
       </c>
-      <c r="C27" s="102" t="n"/>
+      <c r="C27" s="106" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="103" t="inlineStr">
+      <c r="A28" s="107" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B28" s="104" t="inlineStr">
+      <c r="B28" s="108" t="inlineStr">
         <is>
           <t>Republic collapse sequence</t>
         </is>
       </c>
-      <c r="C28" s="104" t="n"/>
+      <c r="C28" s="108" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="105" t="inlineStr">
+      <c r="A29" s="109" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B29" s="106" t="inlineStr">
+      <c r="B29" s="110" t="inlineStr">
         <is>
           <t>Dynamic tile-based crisis chains; triggered by world.gd check functions</t>
         </is>
       </c>
-      <c r="C29" s="106" t="n"/>
+      <c r="C29" s="110" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="107" t="inlineStr">
+      <c r="A30" s="111" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B30" s="108" t="inlineStr">
+      <c r="B30" s="112" t="inlineStr">
         <is>
           <t>Ualani Carlisle army presence events; personal storyline</t>
         </is>
       </c>
-      <c r="C30" s="108" t="n"/>
+      <c r="C30" s="112" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="109" t="inlineStr">
+      <c r="A31" s="113" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B31" s="110" t="inlineStr">
+      <c r="B31" s="114" t="inlineStr">
         <is>
           <t>Vice President relationship arc; 9 events tied to the VP governor</t>
         </is>
       </c>
-      <c r="C31" s="110" t="n"/>
+      <c r="C31" s="114" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="111" t="inlineStr">
+      <c r="A32" s="115" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B32" s="112" t="inlineStr">
+      <c r="B32" s="116" t="inlineStr">
         <is>
           <t>Canadian Alliance diplomatic arc + 3 peace events (PEACE_ALLIED_01, PEACE_USA_01, PEACE_CA_AI_01)</t>
         </is>
       </c>
-      <c r="C32" s="112" t="n"/>
+      <c r="C32" s="116" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="113" t="inlineStr">
+      <c r="A33" s="117" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B33" s="114" t="inlineStr">
+      <c r="B33" s="118" t="inlineStr">
         <is>
           <t>Jessica Clear-Water's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
         </is>
       </c>
-      <c r="C33" s="114" t="n"/>
+      <c r="C33" s="118" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="115" t="inlineStr">
+      <c r="A34" s="119" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B34" s="120" t="inlineStr">
+        <is>
+          <t>25 one-shot dispatch events, one per USA governor archetype; tile_yield resource×turns; 3% chance/turn at loyalty≥8</t>
+        </is>
+      </c>
+      <c r="C34" s="120" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="121" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B34" s="116" t="inlineStr">
+      <c r="B35" s="122" t="inlineStr">
         <is>
           <t>Not yet implemented; concept stage or referenced-but-missing events</t>
         </is>
       </c>
-      <c r="C34" s="116" t="n"/>
+      <c r="C35" s="122" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -185,7 +185,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -294,6 +294,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F5E6F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE0F7"/>
       </patternFill>
     </fill>
@@ -344,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -545,10 +550,22 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -560,10 +577,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,10 +589,10 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -584,10 +601,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -596,10 +613,10 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -708,6 +725,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1075,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N216"/>
+  <dimension ref="A1:N229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13605,22 +13628,22 @@
     <row r="201" ht="30" customHeight="1">
       <c r="A201" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B201" s="65" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C201" s="66" t="inlineStr">
         <is>
-          <t>UALANI_DOCK_01</t>
+          <t>WH_SECRET_01</t>
         </is>
       </c>
       <c r="D201" s="67" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13638,9 +13661,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H201" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I201" s="66" t="inlineStr"/>
@@ -13656,39 +13679,39 @@
       </c>
       <c r="L201" s="66" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M201" s="69" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M201" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N201" s="67" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
         </is>
       </c>
     </row>
     <row r="202" ht="30" customHeight="1">
       <c r="A202" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B202" s="65" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C202" s="66" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>WH_SECRET_02</t>
         </is>
       </c>
       <c r="D202" s="67" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13706,9 +13729,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H202" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I202" s="66" t="inlineStr"/>
@@ -13717,46 +13740,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K202" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K202" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L202" s="66" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M202" s="69" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M202" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N202" s="67" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
         </is>
       </c>
     </row>
     <row r="203" ht="30" customHeight="1">
       <c r="A203" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B203" s="65" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C203" s="66" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>WH_SECRET_03</t>
         </is>
       </c>
       <c r="D203" s="67" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13774,9 +13797,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H203" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I203" s="66" t="inlineStr"/>
@@ -13785,46 +13808,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K203" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K203" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L203" s="66" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M203" s="69" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M203" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N203" s="67" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
         </is>
       </c>
     </row>
     <row r="204" ht="30" customHeight="1">
       <c r="A204" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B204" s="65" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C204" s="66" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>WH_SECRET_04</t>
         </is>
       </c>
       <c r="D204" s="67" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -13842,9 +13865,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H204" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I204" s="66" t="inlineStr"/>
@@ -13853,46 +13876,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K204" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K204" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L204" s="66" t="inlineStr">
         <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M204" s="69" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M204" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N204" s="67" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
         </is>
       </c>
     </row>
     <row r="205" ht="30" customHeight="1">
       <c r="A205" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B205" s="65" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C205" s="66" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>WH_SECRET_05</t>
         </is>
       </c>
       <c r="D205" s="67" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -13910,9 +13933,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H205" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I205" s="66" t="inlineStr"/>
@@ -13921,42 +13944,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K205" s="69" t="inlineStr">
+      <c r="K205" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L205" s="66" t="inlineStr"/>
-      <c r="M205" s="69" t="inlineStr">
+      <c r="L205" s="66" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M205" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N205" s="67" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
         </is>
       </c>
     </row>
     <row r="206" ht="30" customHeight="1">
       <c r="A206" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B206" s="65" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Month 6</t>
         </is>
       </c>
       <c r="C206" s="66" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>WH_SECRET_06</t>
         </is>
       </c>
       <c r="D206" s="67" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -13974,9 +14001,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H206" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I206" s="66" t="inlineStr"/>
@@ -13985,42 +14012,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K206" s="69" t="inlineStr">
+      <c r="K206" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L206" s="66" t="inlineStr"/>
-      <c r="M206" s="69" t="inlineStr">
+      <c r="L206" s="66" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M206" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N206" s="67" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
         </is>
       </c>
     </row>
     <row r="207" ht="30" customHeight="1">
       <c r="A207" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B207" s="65" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C207" s="66" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>WH_SECRET_07</t>
         </is>
       </c>
       <c r="D207" s="67" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -14038,9 +14069,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H207" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I207" s="66" t="inlineStr"/>
@@ -14049,42 +14080,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K207" s="69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L207" s="66" t="inlineStr"/>
-      <c r="M207" s="69" t="inlineStr">
+      <c r="K207" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L207" s="66" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M207" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N207" s="67" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
         </is>
       </c>
     </row>
     <row r="208" ht="30" customHeight="1">
       <c r="A208" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B208" s="65" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>Month 8</t>
         </is>
       </c>
       <c r="C208" s="66" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>WH_SECRET_08</t>
         </is>
       </c>
       <c r="D208" s="67" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — DIWALI</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -14102,9 +14137,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H208" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I208" s="66" t="inlineStr"/>
@@ -14113,62 +14148,66 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K208" s="69" t="inlineStr">
+      <c r="K208" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L208" s="66" t="inlineStr"/>
-      <c r="M208" s="69" t="inlineStr">
+      <c r="L208" s="66" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M208" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N208" s="67" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
         </is>
       </c>
     </row>
     <row r="209" ht="30" customHeight="1">
       <c r="A209" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B209" s="65" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>Month 9</t>
         </is>
       </c>
       <c r="C209" s="66" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>WH_SECRET_09</t>
         </is>
       </c>
       <c r="D209" s="67" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E209" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F209" s="67" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G209" s="67" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
-        </is>
-      </c>
-      <c r="H209" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I209" s="66" t="inlineStr"/>
@@ -14177,42 +14216,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K209" s="69" t="inlineStr">
+      <c r="K209" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L209" s="66" t="inlineStr"/>
-      <c r="M209" s="69" t="inlineStr">
+      <c r="L209" s="66" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M209" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N209" s="67" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
         </is>
       </c>
     </row>
     <row r="210" ht="30" customHeight="1">
       <c r="A210" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B210" s="65" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Month 10</t>
         </is>
       </c>
       <c r="C210" s="66" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>WH_SECRET_10</t>
         </is>
       </c>
       <c r="D210" s="67" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -14230,9 +14273,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H210" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I210" s="66" t="inlineStr"/>
@@ -14241,42 +14284,46 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K210" s="69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L210" s="66" t="inlineStr"/>
-      <c r="M210" s="69" t="inlineStr">
+      <c r="K210" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L210" s="66" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M210" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N210" s="67" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
         </is>
       </c>
     </row>
     <row r="211" ht="30" customHeight="1">
       <c r="A211" s="65" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B211" s="65" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Month 11</t>
         </is>
       </c>
       <c r="C211" s="66" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>WH_SECRET_11</t>
         </is>
       </c>
       <c r="D211" s="67" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -14294,9 +14341,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H211" s="68" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I211" s="66" t="inlineStr"/>
@@ -14305,61 +14352,869 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K211" s="69" t="inlineStr">
+      <c r="K211" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L211" s="66" t="inlineStr"/>
-      <c r="M211" s="69" t="inlineStr">
+      <c r="L211" s="66" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M211" s="68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N211" s="67" t="inlineStr">
         <is>
+          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="30" customHeight="1">
+      <c r="A212" s="65" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B212" s="65" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="C212" s="66" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12</t>
+        </is>
+      </c>
+      <c r="D212" s="67" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F212" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G212" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I212" s="66" t="inlineStr"/>
+      <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K212" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L212" s="66" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M212" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N212" s="67" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="8" customHeight="1">
+      <c r="A213" s="9" t="n"/>
+      <c r="B213" s="9" t="n"/>
+      <c r="C213" s="9" t="n"/>
+      <c r="D213" s="9" t="n"/>
+      <c r="E213" s="9" t="n"/>
+      <c r="F213" s="9" t="n"/>
+      <c r="G213" s="9" t="n"/>
+      <c r="H213" s="9" t="n"/>
+      <c r="I213" s="9" t="n"/>
+      <c r="J213" s="9" t="n"/>
+      <c r="K213" s="9" t="n"/>
+      <c r="L213" s="9" t="n"/>
+      <c r="M213" s="9" t="n"/>
+      <c r="N213" s="9" t="n"/>
+    </row>
+    <row r="214" ht="30" customHeight="1">
+      <c r="A214" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B214" s="69" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C214" s="70" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D214" s="71" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F214" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G214" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H214" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I214" s="70" t="inlineStr"/>
+      <c r="J214" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K214" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L214" s="70" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M214" s="73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N214" s="71" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="30" customHeight="1">
+      <c r="A215" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B215" s="69" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C215" s="70" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D215" s="71" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F215" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G215" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H215" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I215" s="70" t="inlineStr"/>
+      <c r="J215" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K215" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L215" s="70" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M215" s="73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N215" s="71" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="30" customHeight="1">
+      <c r="A216" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B216" s="69" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C216" s="70" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D216" s="71" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F216" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G216" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H216" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I216" s="70" t="inlineStr"/>
+      <c r="J216" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K216" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L216" s="70" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M216" s="73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N216" s="71" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="30" customHeight="1">
+      <c r="A217" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B217" s="69" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C217" s="70" t="inlineStr">
+        <is>
+          <t>UALANI_COURTHOUSE_01</t>
+        </is>
+      </c>
+      <c r="D217" s="71" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F217" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G217" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H217" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I217" s="70" t="inlineStr"/>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K217" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L217" s="70" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M217" s="73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N217" s="71" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="30" customHeight="1">
+      <c r="A218" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B218" s="69" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C218" s="70" t="inlineStr">
+        <is>
+          <t>CL_WASHINGTON_01</t>
+        </is>
+      </c>
+      <c r="D218" s="71" t="inlineStr">
+        <is>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F218" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G218" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H218" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I218" s="70" t="inlineStr"/>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K218" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L218" s="70" t="inlineStr"/>
+      <c r="M218" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N218" s="71" t="inlineStr">
+        <is>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="30" customHeight="1">
+      <c r="A219" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B219" s="69" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C219" s="70" t="inlineStr">
+        <is>
+          <t>CL_VALLEY_FORGE_01</t>
+        </is>
+      </c>
+      <c r="D219" s="71" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F219" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G219" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H219" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I219" s="70" t="inlineStr"/>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K219" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L219" s="70" t="inlineStr"/>
+      <c r="M219" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N219" s="71" t="inlineStr">
+        <is>
+          <t>Tile 1; historically significant; would fire on liberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B220" s="69" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C220" s="70" t="inlineStr">
+        <is>
+          <t>CX_NYC_01</t>
+        </is>
+      </c>
+      <c r="D220" s="71" t="inlineStr">
+        <is>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F220" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G220" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H220" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I220" s="70" t="inlineStr"/>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K220" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L220" s="70" t="inlineStr"/>
+      <c r="M220" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N220" s="71" t="inlineStr">
+        <is>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B221" s="69" t="inlineStr">
+        <is>
+          <t>Espionage Events</t>
+        </is>
+      </c>
+      <c r="C221" s="70" t="inlineStr">
+        <is>
+          <t>ESPIONAGE_DISCOVERY_01</t>
+        </is>
+      </c>
+      <c r="D221" s="71" t="inlineStr">
+        <is>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F221" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G221" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H221" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I221" s="70" t="inlineStr"/>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K221" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L221" s="70" t="inlineStr"/>
+      <c r="M221" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N221" s="71" t="inlineStr">
+        <is>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B222" s="69" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C222" s="70" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D222" s="71" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E222" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F222" s="71" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G222" s="71" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H222" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I222" s="70" t="inlineStr"/>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K222" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L222" s="70" t="inlineStr"/>
+      <c r="M222" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N222" s="71" t="inlineStr">
+        <is>
+          <t>Extend the commander arc beyond first objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B223" s="69" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C223" s="70" t="inlineStr">
+        <is>
+          <t>WINTER_SIEGE_01</t>
+        </is>
+      </c>
+      <c r="D223" s="71" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F223" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G223" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H223" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I223" s="70" t="inlineStr"/>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K223" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L223" s="70" t="inlineStr"/>
+      <c r="M223" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N223" s="71" t="inlineStr">
+        <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="30" customHeight="1">
+      <c r="A224" s="69" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B224" s="69" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C224" s="70" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D224" s="71" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F224" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G224" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H224" s="72" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I224" s="70" t="inlineStr"/>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K224" s="73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L224" s="70" t="inlineStr"/>
+      <c r="M224" s="73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N224" s="71" t="inlineStr">
+        <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="20" customHeight="1">
-      <c r="A213" s="70" t="inlineStr">
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="74" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B213" s="71" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="214" ht="20" customHeight="1">
-      <c r="A214" s="70" t="inlineStr">
+      <c r="B226" s="75" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="74" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B214" s="71" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="215" ht="20" customHeight="1">
-      <c r="A215" s="70" t="inlineStr">
+      <c r="B227" s="75" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="74" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B215" s="71" t="n">
+      <c r="B228" s="75" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="216" ht="20" customHeight="1">
-      <c r="A216" s="70" t="inlineStr">
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="74" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B216" s="71" t="n">
-        <v>51</v>
+      <c r="B229" s="75" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -17033,42 +17888,42 @@
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="70" t="inlineStr">
+      <c r="A43" s="74" t="inlineStr">
         <is>
           <t>Canadian events total</t>
         </is>
       </c>
-      <c r="B43" s="71" t="n">
+      <c r="B43" s="75" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="70" t="inlineStr">
+      <c r="A44" s="74" t="inlineStr">
         <is>
           <t>Canada (Alliance arc)</t>
         </is>
       </c>
-      <c r="B44" s="71" t="n">
+      <c r="B44" s="75" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="70" t="inlineStr">
+      <c r="A45" s="74" t="inlineStr">
         <is>
           <t>CA Protector (Jessica's creatures)</t>
         </is>
       </c>
-      <c r="B45" s="71" t="n">
+      <c r="B45" s="75" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="70" t="inlineStr">
+      <c r="A46" s="74" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B46" s="71" t="n">
+      <c r="B46" s="75" t="n">
         <v>12</v>
       </c>
     </row>
@@ -17083,7 +17938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17092,377 +17947,390 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="72" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="73" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="B2" s="74" t="inlineStr">
+      <c r="B2" s="78" t="inlineStr">
         <is>
           <t>Final pass done — art integrated, text finalized, fully tested</t>
         </is>
       </c>
-      <c r="C2" s="74" t="n"/>
+      <c r="C2" s="78" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="75" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="A3" s="79" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>Event is coded, in CSV, all buttons wired; no final polish yet</t>
         </is>
       </c>
-      <c r="C3" s="76" t="n"/>
+      <c r="C3" s="80" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B4" s="78" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Concept stage: not in events.csv; some referenced in button CSV</t>
         </is>
       </c>
-      <c r="C4" s="78" t="n"/>
+      <c r="C4" s="82" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>ART STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="79" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>No art asset exists yet</t>
         </is>
       </c>
-      <c r="C7" s="80" t="n"/>
+      <c r="C7" s="84" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B8" s="78" t="inlineStr">
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>Art is being created but not in engine</t>
         </is>
       </c>
-      <c r="C8" s="78" t="n"/>
+      <c r="C8" s="82" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="A9" s="85" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="B9" s="82" t="inlineStr">
+      <c r="B9" s="86" t="inlineStr">
         <is>
           <t>Art is in the project and referenced correctly</t>
         </is>
       </c>
-      <c r="C9" s="82" t="n"/>
+      <c r="C9" s="86" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>EXPLICIT ART LEGEND</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="83" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>YES — Explicit Art Needed</t>
         </is>
       </c>
-      <c r="B12" s="84" t="inlineStr">
+      <c r="B12" s="88" t="inlineStr">
         <is>
           <t>Event has explicit or kinky_lewd content flag OR has at least one explicit button option that will need unique explicit artwork</t>
         </is>
       </c>
-      <c r="C12" s="84" t="n"/>
+      <c r="C12" s="88" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="85" t="inlineStr">
+      <c r="A13" s="89" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="86" t="inlineStr">
+      <c r="B13" s="90" t="inlineStr">
         <is>
           <t>Standard event — no adult artwork required</t>
         </is>
       </c>
-      <c r="C13" s="86" t="n"/>
+      <c r="C13" s="90" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>CHAIN POSITION LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="87" t="inlineStr">
+      <c r="A16" s="91" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B16" s="92" t="inlineStr">
         <is>
           <t>Standalone event or first event in a chain; fires from world.gd check function or EventDatabase date trigger</t>
         </is>
       </c>
-      <c r="C16" s="88" t="n"/>
+      <c r="C16" s="92" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="89" t="inlineStr">
+      <c r="A17" s="93" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B17" s="90" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>Fires as outcome of a choice button on a Root/prior event; represents one path in a fork</t>
         </is>
       </c>
-      <c r="C17" s="90" t="n"/>
+      <c r="C17" s="94" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="91" t="inlineStr">
+      <c r="A18" s="95" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="96" t="inlineStr">
         <is>
           <t>Fires automatically after a mission completes (via next_event_id or mission flag return)</t>
         </is>
       </c>
-      <c r="C18" s="92" t="n"/>
+      <c r="C18" s="96" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>CATEGORY COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="93" t="inlineStr">
+      <c r="A21" s="97" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B21" s="94" t="inlineStr">
+      <c r="B21" s="98" t="inlineStr">
         <is>
           <t>Calendar-triggered events; month or turn-based</t>
         </is>
       </c>
-      <c r="C21" s="94" t="n"/>
+      <c r="C21" s="98" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="95" t="inlineStr">
+      <c r="A22" s="99" t="inlineStr">
         <is>
           <t>City Liberated</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
+      <c r="B22" s="100" t="inlineStr">
         <is>
           <t>Fires when a specific tile is liberated (city_liberated type)</t>
         </is>
       </c>
-      <c r="C22" s="96" t="n"/>
+      <c r="C22" s="100" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="97" t="inlineStr">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>City Lost</t>
         </is>
       </c>
-      <c r="B23" s="98" t="inlineStr">
+      <c r="B23" s="102" t="inlineStr">
         <is>
           <t>Fires when a specific tile falls to the enemy (city_lost type)</t>
         </is>
       </c>
-      <c r="C23" s="98" t="n"/>
+      <c r="C23" s="102" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="99" t="inlineStr">
+      <c r="A24" s="103" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B24" s="100" t="inlineStr">
+      <c r="B24" s="104" t="inlineStr">
         <is>
           <t>State-level liberation, secession, and reintegration</t>
         </is>
       </c>
-      <c r="C24" s="100" t="n"/>
+      <c r="C24" s="104" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="101" t="inlineStr">
+      <c r="A25" s="105" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B25" s="102" t="inlineStr">
+      <c r="B25" s="106" t="inlineStr">
         <is>
           <t>Mythological entity summon events (protector_summon type)</t>
         </is>
       </c>
-      <c r="C25" s="102" t="n"/>
+      <c r="C25" s="106" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="103" t="inlineStr">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B26" s="104" t="inlineStr">
+      <c r="B26" s="108" t="inlineStr">
         <is>
           <t>Named commander arc events (commander_* types)</t>
         </is>
       </c>
-      <c r="C26" s="104" t="n"/>
+      <c r="C26" s="108" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="105" t="inlineStr">
+      <c r="A27" s="109" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B27" s="106" t="inlineStr">
+      <c r="B27" s="110" t="inlineStr">
         <is>
           <t>Fort disrepair investigation chain (fort_* types)</t>
         </is>
       </c>
-      <c r="C27" s="106" t="n"/>
+      <c r="C27" s="110" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="107" t="inlineStr">
+      <c r="A28" s="111" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B28" s="108" t="inlineStr">
+      <c r="B28" s="112" t="inlineStr">
         <is>
           <t>Republic collapse sequence</t>
         </is>
       </c>
-      <c r="C28" s="108" t="n"/>
+      <c r="C28" s="112" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="109" t="inlineStr">
+      <c r="A29" s="113" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B29" s="110" t="inlineStr">
+      <c r="B29" s="114" t="inlineStr">
         <is>
           <t>Dynamic tile-based crisis chains; triggered by world.gd check functions</t>
         </is>
       </c>
-      <c r="C29" s="110" t="n"/>
+      <c r="C29" s="114" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="111" t="inlineStr">
+      <c r="A30" s="115" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B30" s="112" t="inlineStr">
+      <c r="B30" s="116" t="inlineStr">
         <is>
           <t>Ualani Carlisle army presence events; personal storyline</t>
         </is>
       </c>
-      <c r="C30" s="112" t="n"/>
+      <c r="C30" s="116" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="113" t="inlineStr">
+      <c r="A31" s="117" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B31" s="114" t="inlineStr">
+      <c r="B31" s="118" t="inlineStr">
         <is>
           <t>Vice President relationship arc; 9 events tied to the VP governor</t>
         </is>
       </c>
-      <c r="C31" s="114" t="n"/>
+      <c r="C31" s="118" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="115" t="inlineStr">
+      <c r="A32" s="119" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B32" s="116" t="inlineStr">
+      <c r="B32" s="120" t="inlineStr">
         <is>
           <t>Canadian Alliance diplomatic arc + 3 peace events (PEACE_ALLIED_01, PEACE_USA_01, PEACE_CA_AI_01)</t>
         </is>
       </c>
-      <c r="C32" s="116" t="n"/>
+      <c r="C32" s="120" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="117" t="inlineStr">
+      <c r="A33" s="121" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B33" s="118" t="inlineStr">
+      <c r="B33" s="122" t="inlineStr">
         <is>
           <t>Jessica Clear-Water's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
         </is>
       </c>
-      <c r="C33" s="118" t="n"/>
+      <c r="C33" s="122" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="119" t="inlineStr">
+      <c r="A34" s="123" t="inlineStr">
         <is>
           <t>Loyal Governor</t>
         </is>
       </c>
-      <c r="B34" s="120" t="inlineStr">
+      <c r="B34" s="124" t="inlineStr">
         <is>
           <t>25 one-shot dispatch events, one per USA governor archetype; tile_yield resource×turns; 3% chance/turn at loyalty≥8</t>
         </is>
       </c>
-      <c r="C34" s="120" t="n"/>
+      <c r="C34" s="124" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="121" t="inlineStr">
+      <c r="A35" s="125" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B35" s="126" t="inlineStr">
+        <is>
+          <t>12 personal Ualani events (WH_SECRET_01–12); fires when she is stationed at DC (tile 188) during the matching calendar month; all sensual in tone; some have explicit BTN2</t>
+        </is>
+      </c>
+      <c r="C35" s="126" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="127" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B35" s="122" t="inlineStr">
+      <c r="B36" s="128" t="inlineStr">
         <is>
           <t>Not yet implemented; concept stage or referenced-but-missing events</t>
         </is>
       </c>
-      <c r="C35" s="122" t="n"/>
+      <c r="C36" s="128" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -185,7 +185,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -299,6 +299,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6F5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE0F7"/>
       </patternFill>
     </fill>
@@ -349,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -562,10 +567,22 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -577,10 +594,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -589,10 +606,10 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -601,10 +618,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -613,10 +630,10 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,6 +748,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1098,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N229"/>
+  <dimension ref="A1:N235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14460,22 +14483,22 @@
     <row r="214" ht="30" customHeight="1">
       <c r="A214" s="69" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Chalchiuhtotolin</t>
         </is>
       </c>
       <c r="B214" s="69" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Jade Turkey Arc</t>
         </is>
       </c>
       <c r="C214" s="70" t="inlineStr">
         <is>
-          <t>UALANI_DOCK_01</t>
+          <t>CHALCH_SUMMON</t>
         </is>
       </c>
       <c r="D214" s="71" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+          <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -14490,12 +14513,12 @@
       </c>
       <c r="G214" s="71" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H214" s="72" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>CHALCH_Q1</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I214" s="70" t="inlineStr"/>
@@ -14504,66 +14527,62 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K214" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L214" s="70" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M214" s="73" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K214" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L214" s="70" t="inlineStr"/>
+      <c r="M214" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N214" s="71" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+          <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
         </is>
       </c>
     </row>
     <row r="215" ht="30" customHeight="1">
       <c r="A215" s="69" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Chalchiuhtotolin</t>
         </is>
       </c>
       <c r="B215" s="69" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Jade Turkey Arc</t>
         </is>
       </c>
       <c r="C215" s="70" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>CHALCH_Q1</t>
         </is>
       </c>
       <c r="D215" s="71" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E215" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
+        </is>
+      </c>
+      <c r="E215" s="72" t="inlineStr">
+        <is>
+          <t>Quest 1</t>
         </is>
       </c>
       <c r="F215" s="71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHALCH_SUMMON</t>
         </is>
       </c>
       <c r="G215" s="71" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H215" s="72" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>CHALCH_Q2</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I215" s="70" t="inlineStr"/>
@@ -14572,66 +14591,62 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K215" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L215" s="70" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M215" s="73" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K215" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L215" s="70" t="inlineStr"/>
+      <c r="M215" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N215" s="71" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
         </is>
       </c>
     </row>
     <row r="216" ht="30" customHeight="1">
       <c r="A216" s="69" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Chalchiuhtotolin</t>
         </is>
       </c>
       <c r="B216" s="69" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Jade Turkey Arc</t>
         </is>
       </c>
       <c r="C216" s="70" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>CHALCH_Q2</t>
         </is>
       </c>
       <c r="D216" s="71" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E216" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
+        </is>
+      </c>
+      <c r="E216" s="72" t="inlineStr">
+        <is>
+          <t>Quest 2</t>
         </is>
       </c>
       <c r="F216" s="71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHALCH_Q1</t>
         </is>
       </c>
       <c r="G216" s="71" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H216" s="72" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>CHALCH_Q3</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I216" s="70" t="inlineStr"/>
@@ -14640,66 +14655,62 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K216" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L216" s="70" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M216" s="73" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K216" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L216" s="70" t="inlineStr"/>
+      <c r="M216" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N216" s="71" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
         </is>
       </c>
     </row>
     <row r="217" ht="30" customHeight="1">
       <c r="A217" s="69" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Chalchiuhtotolin</t>
         </is>
       </c>
       <c r="B217" s="69" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>Jade Turkey Arc</t>
         </is>
       </c>
       <c r="C217" s="70" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>CHALCH_Q3</t>
         </is>
       </c>
       <c r="D217" s="71" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
+        </is>
+      </c>
+      <c r="E217" s="72" t="inlineStr">
+        <is>
+          <t>Quest 3</t>
         </is>
       </c>
       <c r="F217" s="71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHALCH_Q2</t>
         </is>
       </c>
       <c r="G217" s="71" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H217" s="72" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+          <t>CHALCH_AGREE</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I217" s="70" t="inlineStr"/>
@@ -14708,56 +14719,52 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K217" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L217" s="70" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M217" s="73" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K217" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L217" s="70" t="inlineStr"/>
+      <c r="M217" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="N217" s="71" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
         </is>
       </c>
     </row>
     <row r="218" ht="30" customHeight="1">
       <c r="A218" s="69" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Chalchiuhtotolin</t>
         </is>
       </c>
       <c r="B218" s="69" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Jade Turkey Arc</t>
         </is>
       </c>
       <c r="C218" s="70" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>CHALCH_AGREE</t>
         </is>
       </c>
       <c r="D218" s="71" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E218" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
+        </is>
+      </c>
+      <c r="E218" s="72" t="inlineStr">
+        <is>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F218" s="71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHALCH_Q3</t>
         </is>
       </c>
       <c r="G218" s="71" t="inlineStr">
@@ -14765,9 +14772,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H218" s="72" t="inlineStr">
-        <is>
-          <t>IDEA</t>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I218" s="70" t="inlineStr"/>
@@ -14776,444 +14783,796 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K218" s="73" t="inlineStr">
+      <c r="K218" s="72" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="L218" s="70" t="inlineStr"/>
-      <c r="M218" s="73" t="inlineStr">
+      <c r="M218" s="72" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N218" s="71" t="inlineStr">
         <is>
+          <t>Fires when chalch_q3_done; BTN1: +100 food; closes the arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="8" customHeight="1">
+      <c r="A219" s="9" t="n"/>
+      <c r="B219" s="9" t="n"/>
+      <c r="C219" s="9" t="n"/>
+      <c r="D219" s="9" t="n"/>
+      <c r="E219" s="9" t="n"/>
+      <c r="F219" s="9" t="n"/>
+      <c r="G219" s="9" t="n"/>
+      <c r="H219" s="9" t="n"/>
+      <c r="I219" s="9" t="n"/>
+      <c r="J219" s="9" t="n"/>
+      <c r="K219" s="9" t="n"/>
+      <c r="L219" s="9" t="n"/>
+      <c r="M219" s="9" t="n"/>
+      <c r="N219" s="9" t="n"/>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="73" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B220" s="73" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C220" s="74" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D220" s="75" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F220" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G220" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H220" s="76" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I220" s="74" t="inlineStr"/>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K220" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L220" s="74" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M220" s="77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N220" s="75" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="73" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B221" s="73" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C221" s="74" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D221" s="75" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F221" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G221" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H221" s="76" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I221" s="74" t="inlineStr"/>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K221" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L221" s="74" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M221" s="77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N221" s="75" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="73" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B222" s="73" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C222" s="74" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D222" s="75" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F222" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G222" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H222" s="76" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I222" s="74" t="inlineStr"/>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K222" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L222" s="74" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M222" s="77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N222" s="75" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="73" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B223" s="73" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C223" s="74" t="inlineStr">
+        <is>
+          <t>UALANI_COURTHOUSE_01</t>
+        </is>
+      </c>
+      <c r="D223" s="75" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F223" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G223" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H223" s="76" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I223" s="74" t="inlineStr"/>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K223" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L223" s="74" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M223" s="77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N223" s="75" t="inlineStr">
+        <is>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="30" customHeight="1">
+      <c r="A224" s="73" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B224" s="73" t="inlineStr">
+        <is>
+          <t>More City Events</t>
+        </is>
+      </c>
+      <c r="C224" s="74" t="inlineStr">
+        <is>
+          <t>CL_WASHINGTON_01</t>
+        </is>
+      </c>
+      <c r="D224" s="75" t="inlineStr">
+        <is>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F224" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G224" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H224" s="76" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I224" s="74" t="inlineStr"/>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K224" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L224" s="74" t="inlineStr"/>
+      <c r="M224" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N224" s="75" t="inlineStr">
+        <is>
           <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="30" customHeight="1">
-      <c r="A219" s="69" t="inlineStr">
+    <row r="225" ht="30" customHeight="1">
+      <c r="A225" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B219" s="69" t="inlineStr">
+      <c r="B225" s="73" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C219" s="70" t="inlineStr">
+      <c r="C225" s="74" t="inlineStr">
         <is>
           <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
-      <c r="D219" s="71" t="inlineStr">
+      <c r="D225" s="75" t="inlineStr">
         <is>
           <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
       </c>
-      <c r="E219" s="5" t="inlineStr">
+      <c r="E225" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F219" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G219" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H219" s="72" t="inlineStr">
+      <c r="F225" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G225" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H225" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I219" s="70" t="inlineStr"/>
-      <c r="J219" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K219" s="73" t="inlineStr">
+      <c r="I225" s="74" t="inlineStr"/>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K225" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L219" s="70" t="inlineStr"/>
-      <c r="M219" s="73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N219" s="71" t="inlineStr">
+      <c r="L225" s="74" t="inlineStr"/>
+      <c r="M225" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N225" s="75" t="inlineStr">
         <is>
           <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="30" customHeight="1">
-      <c r="A220" s="69" t="inlineStr">
+    <row r="226" ht="30" customHeight="1">
+      <c r="A226" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B220" s="69" t="inlineStr">
+      <c r="B226" s="73" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C220" s="70" t="inlineStr">
+      <c r="C226" s="74" t="inlineStr">
         <is>
           <t>CX_NYC_01</t>
         </is>
       </c>
-      <c r="D220" s="71" t="inlineStr">
+      <c r="D226" s="75" t="inlineStr">
         <is>
           <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
-      <c r="E220" s="5" t="inlineStr">
+      <c r="E226" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F220" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G220" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H220" s="72" t="inlineStr">
+      <c r="F226" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G226" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H226" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I220" s="70" t="inlineStr"/>
-      <c r="J220" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K220" s="73" t="inlineStr">
+      <c r="I226" s="74" t="inlineStr"/>
+      <c r="J226" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K226" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L220" s="70" t="inlineStr"/>
-      <c r="M220" s="73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N220" s="71" t="inlineStr">
+      <c r="L226" s="74" t="inlineStr"/>
+      <c r="M226" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N226" s="75" t="inlineStr">
         <is>
           <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="30" customHeight="1">
-      <c r="A221" s="69" t="inlineStr">
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B221" s="69" t="inlineStr">
+      <c r="B227" s="73" t="inlineStr">
         <is>
           <t>Espionage Events</t>
         </is>
       </c>
-      <c r="C221" s="70" t="inlineStr">
+      <c r="C227" s="74" t="inlineStr">
         <is>
           <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
-      <c r="D221" s="71" t="inlineStr">
+      <c r="D227" s="75" t="inlineStr">
         <is>
           <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
-      <c r="E221" s="5" t="inlineStr">
+      <c r="E227" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F221" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G221" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H221" s="72" t="inlineStr">
+      <c r="F227" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G227" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H227" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I221" s="70" t="inlineStr"/>
-      <c r="J221" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K221" s="73" t="inlineStr">
+      <c r="I227" s="74" t="inlineStr"/>
+      <c r="J227" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K227" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L221" s="70" t="inlineStr"/>
-      <c r="M221" s="73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N221" s="71" t="inlineStr">
+      <c r="L227" s="74" t="inlineStr"/>
+      <c r="M227" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N227" s="75" t="inlineStr">
         <is>
           <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="30" customHeight="1">
-      <c r="A222" s="69" t="inlineStr">
+    <row r="228" ht="30" customHeight="1">
+      <c r="A228" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B222" s="69" t="inlineStr">
+      <c r="B228" s="73" t="inlineStr">
         <is>
           <t>Commander Expansion</t>
         </is>
       </c>
-      <c r="C222" s="70" t="inlineStr">
+      <c r="C228" s="74" t="inlineStr">
         <is>
           <t>CMD_OBJECTIVE_2</t>
         </is>
       </c>
-      <c r="D222" s="71" t="inlineStr">
+      <c r="D228" s="75" t="inlineStr">
         <is>
           <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
         </is>
       </c>
-      <c r="E222" s="22" t="inlineStr">
+      <c r="E228" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F222" s="71" t="inlineStr">
+      <c r="F228" s="75" t="inlineStr">
         <is>
           <t>CMD_OBJECTIVE_1</t>
         </is>
       </c>
-      <c r="G222" s="71" t="inlineStr">
+      <c r="G228" s="75" t="inlineStr">
         <is>
           <t>→ CMD_OBJECTIVE_3?</t>
         </is>
       </c>
-      <c r="H222" s="72" t="inlineStr">
+      <c r="H228" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I222" s="70" t="inlineStr"/>
-      <c r="J222" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K222" s="73" t="inlineStr">
+      <c r="I228" s="74" t="inlineStr"/>
+      <c r="J228" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K228" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L222" s="70" t="inlineStr"/>
-      <c r="M222" s="73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N222" s="71" t="inlineStr">
+      <c r="L228" s="74" t="inlineStr"/>
+      <c r="M228" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N228" s="75" t="inlineStr">
         <is>
           <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="30" customHeight="1">
-      <c r="A223" s="69" t="inlineStr">
+    <row r="229" ht="30" customHeight="1">
+      <c r="A229" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B223" s="69" t="inlineStr">
+      <c r="B229" s="73" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C223" s="70" t="inlineStr">
+      <c r="C229" s="74" t="inlineStr">
         <is>
           <t>WINTER_SIEGE_01</t>
         </is>
       </c>
-      <c r="D223" s="71" t="inlineStr">
+      <c r="D229" s="75" t="inlineStr">
         <is>
           <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E229" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F223" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G223" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H223" s="72" t="inlineStr">
+      <c r="F229" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G229" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H229" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I223" s="70" t="inlineStr"/>
-      <c r="J223" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K223" s="73" t="inlineStr">
+      <c r="I229" s="74" t="inlineStr"/>
+      <c r="J229" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K229" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L223" s="70" t="inlineStr"/>
-      <c r="M223" s="73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N223" s="71" t="inlineStr">
+      <c r="L229" s="74" t="inlineStr"/>
+      <c r="M229" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N229" s="75" t="inlineStr">
         <is>
           <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="30" customHeight="1">
-      <c r="A224" s="69" t="inlineStr">
+    <row r="230" ht="30" customHeight="1">
+      <c r="A230" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B224" s="69" t="inlineStr">
+      <c r="B230" s="73" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C224" s="70" t="inlineStr">
+      <c r="C230" s="74" t="inlineStr">
         <is>
           <t>SPRING_OFFENSIVE_01</t>
         </is>
       </c>
-      <c r="D224" s="71" t="inlineStr">
+      <c r="D230" s="75" t="inlineStr">
         <is>
           <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
         </is>
       </c>
-      <c r="E224" s="5" t="inlineStr">
+      <c r="E230" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F224" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G224" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H224" s="72" t="inlineStr">
+      <c r="F230" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G230" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H230" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I224" s="70" t="inlineStr"/>
-      <c r="J224" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K224" s="73" t="inlineStr">
+      <c r="I230" s="74" t="inlineStr"/>
+      <c r="J230" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K230" s="77" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="L224" s="70" t="inlineStr"/>
-      <c r="M224" s="73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N224" s="71" t="inlineStr">
+      <c r="L230" s="74" t="inlineStr"/>
+      <c r="M230" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N230" s="75" t="inlineStr">
         <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="20" customHeight="1">
-      <c r="A226" s="74" t="inlineStr">
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="78" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B226" s="75" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="227" ht="20" customHeight="1">
-      <c r="A227" s="74" t="inlineStr">
+      <c r="B232" s="79" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="78" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B227" s="75" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="228" ht="20" customHeight="1">
-      <c r="A228" s="74" t="inlineStr">
+      <c r="B233" s="79" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="78" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B228" s="75" t="n">
+      <c r="B234" s="79" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="229" ht="20" customHeight="1">
-      <c r="A229" s="74" t="inlineStr">
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="78" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B229" s="75" t="n">
+      <c r="B235" s="79" t="n">
         <v>55</v>
       </c>
     </row>
@@ -17888,42 +18247,42 @@
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="74" t="inlineStr">
+      <c r="A43" s="78" t="inlineStr">
         <is>
           <t>Canadian events total</t>
         </is>
       </c>
-      <c r="B43" s="75" t="n">
+      <c r="B43" s="79" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="74" t="inlineStr">
+      <c r="A44" s="78" t="inlineStr">
         <is>
           <t>Canada (Alliance arc)</t>
         </is>
       </c>
-      <c r="B44" s="75" t="n">
+      <c r="B44" s="79" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="74" t="inlineStr">
+      <c r="A45" s="78" t="inlineStr">
         <is>
           <t>CA Protector (Jessica's creatures)</t>
         </is>
       </c>
-      <c r="B45" s="75" t="n">
+      <c r="B45" s="79" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="74" t="inlineStr">
+      <c r="A46" s="78" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B46" s="75" t="n">
+      <c r="B46" s="79" t="n">
         <v>12</v>
       </c>
     </row>
@@ -17938,7 +18297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17947,390 +18306,403 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="82" t="inlineStr">
         <is>
           <t>Final pass done — art integrated, text finalized, fully tested</t>
         </is>
       </c>
-      <c r="C2" s="78" t="n"/>
+      <c r="C2" s="82" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="79" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="A3" s="83" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>Event is coded, in CSV, all buttons wired; no final polish yet</t>
         </is>
       </c>
-      <c r="C3" s="80" t="n"/>
+      <c r="C3" s="84" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="85" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>Concept stage: not in events.csv; some referenced in button CSV</t>
         </is>
       </c>
-      <c r="C4" s="82" t="n"/>
+      <c r="C4" s="86" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>ART STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="83" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B7" s="84" t="inlineStr">
+      <c r="A7" s="87" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>No art asset exists yet</t>
         </is>
       </c>
-      <c r="C7" s="84" t="n"/>
+      <c r="C7" s="88" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="81" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
         <is>
           <t>Art is being created but not in engine</t>
         </is>
       </c>
-      <c r="C8" s="82" t="n"/>
+      <c r="C8" s="86" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="85" t="inlineStr">
+      <c r="A9" s="89" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="B9" s="86" t="inlineStr">
+      <c r="B9" s="90" t="inlineStr">
         <is>
           <t>Art is in the project and referenced correctly</t>
         </is>
       </c>
-      <c r="C9" s="86" t="n"/>
+      <c r="C9" s="90" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="76" t="inlineStr">
+      <c r="A11" s="80" t="inlineStr">
         <is>
           <t>EXPLICIT ART LEGEND</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="87" t="inlineStr">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>YES — Explicit Art Needed</t>
         </is>
       </c>
-      <c r="B12" s="88" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>Event has explicit or kinky_lewd content flag OR has at least one explicit button option that will need unique explicit artwork</t>
         </is>
       </c>
-      <c r="C12" s="88" t="n"/>
+      <c r="C12" s="92" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="89" t="inlineStr">
+      <c r="A13" s="93" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B13" s="90" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>Standard event — no adult artwork required</t>
         </is>
       </c>
-      <c r="C13" s="90" t="n"/>
+      <c r="C13" s="94" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="76" t="inlineStr">
+      <c r="A15" s="80" t="inlineStr">
         <is>
           <t>CHAIN POSITION LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="91" t="inlineStr">
+      <c r="A16" s="95" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B16" s="92" t="inlineStr">
+      <c r="B16" s="96" t="inlineStr">
         <is>
           <t>Standalone event or first event in a chain; fires from world.gd check function or EventDatabase date trigger</t>
         </is>
       </c>
-      <c r="C16" s="92" t="n"/>
+      <c r="C16" s="96" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="93" t="inlineStr">
+      <c r="A17" s="97" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="98" t="inlineStr">
         <is>
           <t>Fires as outcome of a choice button on a Root/prior event; represents one path in a fork</t>
         </is>
       </c>
-      <c r="C17" s="94" t="n"/>
+      <c r="C17" s="98" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="95" t="inlineStr">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="B18" s="96" t="inlineStr">
+      <c r="B18" s="100" t="inlineStr">
         <is>
           <t>Fires automatically after a mission completes (via next_event_id or mission flag return)</t>
         </is>
       </c>
-      <c r="C18" s="96" t="n"/>
+      <c r="C18" s="100" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="76" t="inlineStr">
+      <c r="A20" s="80" t="inlineStr">
         <is>
           <t>CATEGORY COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="97" t="inlineStr">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B21" s="98" t="inlineStr">
+      <c r="B21" s="102" t="inlineStr">
         <is>
           <t>Calendar-triggered events; month or turn-based</t>
         </is>
       </c>
-      <c r="C21" s="98" t="n"/>
+      <c r="C21" s="102" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="99" t="inlineStr">
+      <c r="A22" s="103" t="inlineStr">
         <is>
           <t>City Liberated</t>
         </is>
       </c>
-      <c r="B22" s="100" t="inlineStr">
+      <c r="B22" s="104" t="inlineStr">
         <is>
           <t>Fires when a specific tile is liberated (city_liberated type)</t>
         </is>
       </c>
-      <c r="C22" s="100" t="n"/>
+      <c r="C22" s="104" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="101" t="inlineStr">
+      <c r="A23" s="105" t="inlineStr">
         <is>
           <t>City Lost</t>
         </is>
       </c>
-      <c r="B23" s="102" t="inlineStr">
+      <c r="B23" s="106" t="inlineStr">
         <is>
           <t>Fires when a specific tile falls to the enemy (city_lost type)</t>
         </is>
       </c>
-      <c r="C23" s="102" t="n"/>
+      <c r="C23" s="106" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="103" t="inlineStr">
+      <c r="A24" s="107" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B24" s="104" t="inlineStr">
+      <c r="B24" s="108" t="inlineStr">
         <is>
           <t>State-level liberation, secession, and reintegration</t>
         </is>
       </c>
-      <c r="C24" s="104" t="n"/>
+      <c r="C24" s="108" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="105" t="inlineStr">
+      <c r="A25" s="109" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B25" s="106" t="inlineStr">
+      <c r="B25" s="110" t="inlineStr">
         <is>
           <t>Mythological entity summon events (protector_summon type)</t>
         </is>
       </c>
-      <c r="C25" s="106" t="n"/>
+      <c r="C25" s="110" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="107" t="inlineStr">
+      <c r="A26" s="111" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B26" s="108" t="inlineStr">
+      <c r="B26" s="112" t="inlineStr">
         <is>
           <t>Named commander arc events (commander_* types)</t>
         </is>
       </c>
-      <c r="C26" s="108" t="n"/>
+      <c r="C26" s="112" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="109" t="inlineStr">
+      <c r="A27" s="113" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B27" s="110" t="inlineStr">
+      <c r="B27" s="114" t="inlineStr">
         <is>
           <t>Fort disrepair investigation chain (fort_* types)</t>
         </is>
       </c>
-      <c r="C27" s="110" t="n"/>
+      <c r="C27" s="114" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="111" t="inlineStr">
+      <c r="A28" s="115" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B28" s="112" t="inlineStr">
+      <c r="B28" s="116" t="inlineStr">
         <is>
           <t>Republic collapse sequence</t>
         </is>
       </c>
-      <c r="C28" s="112" t="n"/>
+      <c r="C28" s="116" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="113" t="inlineStr">
+      <c r="A29" s="117" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B29" s="114" t="inlineStr">
+      <c r="B29" s="118" t="inlineStr">
         <is>
           <t>Dynamic tile-based crisis chains; triggered by world.gd check functions</t>
         </is>
       </c>
-      <c r="C29" s="114" t="n"/>
+      <c r="C29" s="118" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="115" t="inlineStr">
+      <c r="A30" s="119" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B30" s="116" t="inlineStr">
+      <c r="B30" s="120" t="inlineStr">
         <is>
           <t>Ualani Carlisle army presence events; personal storyline</t>
         </is>
       </c>
-      <c r="C30" s="116" t="n"/>
+      <c r="C30" s="120" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="117" t="inlineStr">
+      <c r="A31" s="121" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B31" s="118" t="inlineStr">
+      <c r="B31" s="122" t="inlineStr">
         <is>
           <t>Vice President relationship arc; 9 events tied to the VP governor</t>
         </is>
       </c>
-      <c r="C31" s="118" t="n"/>
+      <c r="C31" s="122" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="119" t="inlineStr">
+      <c r="A32" s="123" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B32" s="120" t="inlineStr">
+      <c r="B32" s="124" t="inlineStr">
         <is>
           <t>Canadian Alliance diplomatic arc + 3 peace events (PEACE_ALLIED_01, PEACE_USA_01, PEACE_CA_AI_01)</t>
         </is>
       </c>
-      <c r="C32" s="120" t="n"/>
+      <c r="C32" s="124" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="121" t="inlineStr">
+      <c r="A33" s="125" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B33" s="122" t="inlineStr">
+      <c r="B33" s="126" t="inlineStr">
         <is>
           <t>Jessica Clear-Water's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
         </is>
       </c>
-      <c r="C33" s="122" t="n"/>
+      <c r="C33" s="126" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="123" t="inlineStr">
+      <c r="A34" s="127" t="inlineStr">
         <is>
           <t>Loyal Governor</t>
         </is>
       </c>
-      <c r="B34" s="124" t="inlineStr">
+      <c r="B34" s="128" t="inlineStr">
         <is>
           <t>25 one-shot dispatch events, one per USA governor archetype; tile_yield resource×turns; 3% chance/turn at loyalty≥8</t>
         </is>
       </c>
-      <c r="C34" s="124" t="n"/>
+      <c r="C34" s="128" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="125" t="inlineStr">
+      <c r="A35" s="129" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B35" s="126" t="inlineStr">
+      <c r="B35" s="130" t="inlineStr">
         <is>
           <t>12 personal Ualani events (WH_SECRET_01–12); fires when she is stationed at DC (tile 188) during the matching calendar month; all sensual in tone; some have explicit BTN2</t>
         </is>
       </c>
-      <c r="C35" s="126" t="n"/>
+      <c r="C35" s="130" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="127" t="inlineStr">
+      <c r="A36" s="131" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B36" s="132" t="inlineStr">
+        <is>
+          <t>5-event super-secret arc (CHALCH_SUMMON → Q1 → Q2 → Q3 → AGREE); fires only when Ualani is at Plymouth (tile 66) on Thanksgiving (month 11); quests: 3 farms, 150 food, 5 farms; reward: up to +220 food total</t>
+        </is>
+      </c>
+      <c r="C36" s="132" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="133" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B36" s="128" t="inlineStr">
+      <c r="B37" s="134" t="inlineStr">
         <is>
           <t>Not yet implemented; concept stage or referenced-but-missing events</t>
         </is>
       </c>
-      <c r="C36" s="128" t="n"/>
+      <c r="C37" s="134" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N235"/>
+  <dimension ref="A1:N286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13565,2014 +13565,5230 @@
       <c r="N198" s="9" t="n"/>
     </row>
     <row r="199" ht="30" customHeight="1">
-      <c r="A199" s="49" t="inlineStr">
+      <c r="A199" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B199" s="29" t="inlineStr">
+        <is>
+          <t>Wetlands Fisher</t>
+        </is>
+      </c>
+      <c r="C199" s="30" t="inlineStr">
+        <is>
+          <t>ARC_01_FIRST</t>
+        </is>
+      </c>
+      <c r="D199" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WETLANDS FISHER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E199" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F199" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G199" s="31" t="inlineStr">
+        <is>
+          <t>ARC_01_DONE</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I199" s="30" t="inlineStr"/>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K199" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L199" s="30" t="inlineStr"/>
+      <c r="M199" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N199" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_01 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="30" customHeight="1">
+      <c r="A200" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B200" s="29" t="inlineStr">
+        <is>
+          <t>Wetlands Fisher</t>
+        </is>
+      </c>
+      <c r="C200" s="30" t="inlineStr">
+        <is>
+          <t>ARC_01_DONE</t>
+        </is>
+      </c>
+      <c r="D200" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WETLANDS FISHER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E200" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F200" s="31" t="inlineStr">
+        <is>
+          <t>ARC_01_FIRST</t>
+        </is>
+      </c>
+      <c r="G200" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I200" s="30" t="inlineStr"/>
+      <c r="J200" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K200" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L200" s="30" t="inlineStr"/>
+      <c r="M200" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N200" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_01 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B201" s="29" t="inlineStr">
+        <is>
+          <t>Appalachian Miner</t>
+        </is>
+      </c>
+      <c r="C201" s="30" t="inlineStr">
+        <is>
+          <t>ARC_02_FIRST</t>
+        </is>
+      </c>
+      <c r="D201" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — APPALACHIAN MINER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E201" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F201" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G201" s="31" t="inlineStr">
+        <is>
+          <t>ARC_02_DONE</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I201" s="30" t="inlineStr"/>
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K201" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L201" s="30" t="inlineStr"/>
+      <c r="M201" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N201" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_02 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="30" customHeight="1">
+      <c r="A202" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B202" s="29" t="inlineStr">
+        <is>
+          <t>Appalachian Miner</t>
+        </is>
+      </c>
+      <c r="C202" s="30" t="inlineStr">
+        <is>
+          <t>ARC_02_DONE</t>
+        </is>
+      </c>
+      <c r="D202" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — APPALACHIAN MINER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E202" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F202" s="31" t="inlineStr">
+        <is>
+          <t>ARC_02_FIRST</t>
+        </is>
+      </c>
+      <c r="G202" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I202" s="30" t="inlineStr"/>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K202" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L202" s="30" t="inlineStr"/>
+      <c r="M202" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N202" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_02 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="30" customHeight="1">
+      <c r="A203" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B203" s="29" t="inlineStr">
+        <is>
+          <t>Ivy League Dropout</t>
+        </is>
+      </c>
+      <c r="C203" s="30" t="inlineStr">
+        <is>
+          <t>ARC_03_FIRST</t>
+        </is>
+      </c>
+      <c r="D203" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E203" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F203" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G203" s="31" t="inlineStr">
+        <is>
+          <t>ARC_03_DONE</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I203" s="30" t="inlineStr"/>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K203" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L203" s="30" t="inlineStr"/>
+      <c r="M203" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N203" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_03 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="30" customHeight="1">
+      <c r="A204" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B204" s="29" t="inlineStr">
+        <is>
+          <t>Ivy League Dropout</t>
+        </is>
+      </c>
+      <c r="C204" s="30" t="inlineStr">
+        <is>
+          <t>ARC_03_DONE</t>
+        </is>
+      </c>
+      <c r="D204" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E204" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F204" s="31" t="inlineStr">
+        <is>
+          <t>ARC_03_FIRST</t>
+        </is>
+      </c>
+      <c r="G204" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I204" s="30" t="inlineStr"/>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K204" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L204" s="30" t="inlineStr"/>
+      <c r="M204" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N204" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_03 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="30" customHeight="1">
+      <c r="A205" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B205" s="29" t="inlineStr">
+        <is>
+          <t>Seminole Fighter</t>
+        </is>
+      </c>
+      <c r="C205" s="30" t="inlineStr">
+        <is>
+          <t>ARC_04_FIRST</t>
+        </is>
+      </c>
+      <c r="D205" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E205" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F205" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="31" t="inlineStr">
+        <is>
+          <t>ARC_04_DONE</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I205" s="30" t="inlineStr"/>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K205" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L205" s="30" t="inlineStr"/>
+      <c r="M205" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N205" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_04 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="30" customHeight="1">
+      <c r="A206" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B206" s="29" t="inlineStr">
+        <is>
+          <t>Seminole Fighter</t>
+        </is>
+      </c>
+      <c r="C206" s="30" t="inlineStr">
+        <is>
+          <t>ARC_04_DONE</t>
+        </is>
+      </c>
+      <c r="D206" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E206" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F206" s="31" t="inlineStr">
+        <is>
+          <t>ARC_04_FIRST</t>
+        </is>
+      </c>
+      <c r="G206" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I206" s="30" t="inlineStr"/>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K206" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L206" s="30" t="inlineStr"/>
+      <c r="M206" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N206" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_04 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B207" s="29" t="inlineStr">
+        <is>
+          <t>Green Mountain Farmer</t>
+        </is>
+      </c>
+      <c r="C207" s="30" t="inlineStr">
+        <is>
+          <t>ARC_05_FIRST</t>
+        </is>
+      </c>
+      <c r="D207" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E207" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F207" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="31" t="inlineStr">
+        <is>
+          <t>ARC_05_DONE</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I207" s="30" t="inlineStr"/>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K207" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L207" s="30" t="inlineStr"/>
+      <c r="M207" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N207" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_05 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B208" s="29" t="inlineStr">
+        <is>
+          <t>Green Mountain Farmer</t>
+        </is>
+      </c>
+      <c r="C208" s="30" t="inlineStr">
+        <is>
+          <t>ARC_05_DONE</t>
+        </is>
+      </c>
+      <c r="D208" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E208" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F208" s="31" t="inlineStr">
+        <is>
+          <t>ARC_05_FIRST</t>
+        </is>
+      </c>
+      <c r="G208" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I208" s="30" t="inlineStr"/>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K208" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L208" s="30" t="inlineStr"/>
+      <c r="M208" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N208" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_05 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B209" s="29" t="inlineStr">
+        <is>
+          <t>Chesapeake Shipwright</t>
+        </is>
+      </c>
+      <c r="C209" s="30" t="inlineStr">
+        <is>
+          <t>ARC_06_FIRST</t>
+        </is>
+      </c>
+      <c r="D209" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E209" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F209" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="31" t="inlineStr">
+        <is>
+          <t>ARC_06_DONE</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I209" s="30" t="inlineStr"/>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K209" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L209" s="30" t="inlineStr"/>
+      <c r="M209" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N209" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_06 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B210" s="29" t="inlineStr">
+        <is>
+          <t>Chesapeake Shipwright</t>
+        </is>
+      </c>
+      <c r="C210" s="30" t="inlineStr">
+        <is>
+          <t>ARC_06_DONE</t>
+        </is>
+      </c>
+      <c r="D210" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E210" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F210" s="31" t="inlineStr">
+        <is>
+          <t>ARC_06_FIRST</t>
+        </is>
+      </c>
+      <c r="G210" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I210" s="30" t="inlineStr"/>
+      <c r="J210" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K210" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L210" s="30" t="inlineStr"/>
+      <c r="M210" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N210" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_06 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="30" customHeight="1">
+      <c r="A211" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B211" s="29" t="inlineStr">
+        <is>
+          <t>Loyalist Turncoat</t>
+        </is>
+      </c>
+      <c r="C211" s="30" t="inlineStr">
+        <is>
+          <t>ARC_07_FIRST</t>
+        </is>
+      </c>
+      <c r="D211" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E211" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F211" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G211" s="31" t="inlineStr">
+        <is>
+          <t>ARC_07_DONE</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I211" s="30" t="inlineStr"/>
+      <c r="J211" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K211" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L211" s="30" t="inlineStr"/>
+      <c r="M211" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N211" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_07 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="30" customHeight="1">
+      <c r="A212" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B212" s="29" t="inlineStr">
+        <is>
+          <t>Loyalist Turncoat</t>
+        </is>
+      </c>
+      <c r="C212" s="30" t="inlineStr">
+        <is>
+          <t>ARC_07_DONE</t>
+        </is>
+      </c>
+      <c r="D212" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E212" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F212" s="31" t="inlineStr">
+        <is>
+          <t>ARC_07_FIRST</t>
+        </is>
+      </c>
+      <c r="G212" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I212" s="30" t="inlineStr"/>
+      <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K212" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L212" s="30" t="inlineStr"/>
+      <c r="M212" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N212" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_07 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="30" customHeight="1">
+      <c r="A213" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B213" s="29" t="inlineStr">
+        <is>
+          <t>Tobacco Belt Drifter</t>
+        </is>
+      </c>
+      <c r="C213" s="30" t="inlineStr">
+        <is>
+          <t>ARC_08_FIRST</t>
+        </is>
+      </c>
+      <c r="D213" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E213" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F213" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G213" s="31" t="inlineStr">
+        <is>
+          <t>ARC_08_DONE</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I213" s="30" t="inlineStr"/>
+      <c r="J213" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K213" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L213" s="30" t="inlineStr"/>
+      <c r="M213" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N213" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_08 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="30" customHeight="1">
+      <c r="A214" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B214" s="29" t="inlineStr">
+        <is>
+          <t>Tobacco Belt Drifter</t>
+        </is>
+      </c>
+      <c r="C214" s="30" t="inlineStr">
+        <is>
+          <t>ARC_08_DONE</t>
+        </is>
+      </c>
+      <c r="D214" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E214" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F214" s="31" t="inlineStr">
+        <is>
+          <t>ARC_08_FIRST</t>
+        </is>
+      </c>
+      <c r="G214" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I214" s="30" t="inlineStr"/>
+      <c r="J214" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K214" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L214" s="30" t="inlineStr"/>
+      <c r="M214" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N214" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_08 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="30" customHeight="1">
+      <c r="A215" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B215" s="29" t="inlineStr">
+        <is>
+          <t>War Widow</t>
+        </is>
+      </c>
+      <c r="C215" s="30" t="inlineStr">
+        <is>
+          <t>ARC_09_FIRST</t>
+        </is>
+      </c>
+      <c r="D215" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WAR WIDOW FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E215" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F215" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G215" s="31" t="inlineStr">
+        <is>
+          <t>ARC_09_DONE</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I215" s="30" t="inlineStr"/>
+      <c r="J215" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K215" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L215" s="30" t="inlineStr"/>
+      <c r="M215" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N215" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_09 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="30" customHeight="1">
+      <c r="A216" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B216" s="29" t="inlineStr">
+        <is>
+          <t>War Widow</t>
+        </is>
+      </c>
+      <c r="C216" s="30" t="inlineStr">
+        <is>
+          <t>ARC_09_DONE</t>
+        </is>
+      </c>
+      <c r="D216" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WAR WIDOW ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E216" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F216" s="31" t="inlineStr">
+        <is>
+          <t>ARC_09_FIRST</t>
+        </is>
+      </c>
+      <c r="G216" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I216" s="30" t="inlineStr"/>
+      <c r="J216" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K216" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L216" s="30" t="inlineStr"/>
+      <c r="M216" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N216" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_09 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="30" customHeight="1">
+      <c r="A217" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B217" s="29" t="inlineStr">
+        <is>
+          <t>Indigenous Scout</t>
+        </is>
+      </c>
+      <c r="C217" s="30" t="inlineStr">
+        <is>
+          <t>ARC_10_FIRST</t>
+        </is>
+      </c>
+      <c r="D217" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E217" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F217" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G217" s="31" t="inlineStr">
+        <is>
+          <t>ARC_10_DONE</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I217" s="30" t="inlineStr"/>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K217" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L217" s="30" t="inlineStr"/>
+      <c r="M217" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N217" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_10 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="30" customHeight="1">
+      <c r="A218" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B218" s="29" t="inlineStr">
+        <is>
+          <t>Indigenous Scout</t>
+        </is>
+      </c>
+      <c r="C218" s="30" t="inlineStr">
+        <is>
+          <t>ARC_10_DONE</t>
+        </is>
+      </c>
+      <c r="D218" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E218" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F218" s="31" t="inlineStr">
+        <is>
+          <t>ARC_10_FIRST</t>
+        </is>
+      </c>
+      <c r="G218" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I218" s="30" t="inlineStr"/>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K218" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L218" s="30" t="inlineStr"/>
+      <c r="M218" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N218" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_10 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="30" customHeight="1">
+      <c r="A219" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B219" s="29" t="inlineStr">
+        <is>
+          <t>Boston Rabble-Rouser</t>
+        </is>
+      </c>
+      <c r="C219" s="30" t="inlineStr">
+        <is>
+          <t>ARC_11_FIRST</t>
+        </is>
+      </c>
+      <c r="D219" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E219" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F219" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G219" s="31" t="inlineStr">
+        <is>
+          <t>ARC_11_DONE</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I219" s="30" t="inlineStr"/>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K219" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L219" s="30" t="inlineStr"/>
+      <c r="M219" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N219" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_11 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B220" s="29" t="inlineStr">
+        <is>
+          <t>Boston Rabble-Rouser</t>
+        </is>
+      </c>
+      <c r="C220" s="30" t="inlineStr">
+        <is>
+          <t>ARC_11_DONE</t>
+        </is>
+      </c>
+      <c r="D220" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E220" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F220" s="31" t="inlineStr">
+        <is>
+          <t>ARC_11_FIRST</t>
+        </is>
+      </c>
+      <c r="G220" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I220" s="30" t="inlineStr"/>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K220" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L220" s="30" t="inlineStr"/>
+      <c r="M220" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N220" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_11 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B221" s="29" t="inlineStr">
+        <is>
+          <t>Continental Surgeon</t>
+        </is>
+      </c>
+      <c r="C221" s="30" t="inlineStr">
+        <is>
+          <t>ARC_12_FIRST</t>
+        </is>
+      </c>
+      <c r="D221" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E221" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F221" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G221" s="31" t="inlineStr">
+        <is>
+          <t>ARC_12_DONE</t>
+        </is>
+      </c>
+      <c r="H221" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I221" s="30" t="inlineStr"/>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K221" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L221" s="30" t="inlineStr"/>
+      <c r="M221" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N221" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_12 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B222" s="29" t="inlineStr">
+        <is>
+          <t>Continental Surgeon</t>
+        </is>
+      </c>
+      <c r="C222" s="30" t="inlineStr">
+        <is>
+          <t>ARC_12_DONE</t>
+        </is>
+      </c>
+      <c r="D222" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E222" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F222" s="31" t="inlineStr">
+        <is>
+          <t>ARC_12_FIRST</t>
+        </is>
+      </c>
+      <c r="G222" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I222" s="30" t="inlineStr"/>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K222" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L222" s="30" t="inlineStr"/>
+      <c r="M222" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N222" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_12 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B223" s="29" t="inlineStr">
+        <is>
+          <t>Nantucket Sailor</t>
+        </is>
+      </c>
+      <c r="C223" s="30" t="inlineStr">
+        <is>
+          <t>ARC_13_FIRST</t>
+        </is>
+      </c>
+      <c r="D223" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — NANTUCKET SAILOR FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E223" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F223" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G223" s="31" t="inlineStr">
+        <is>
+          <t>ARC_13_DONE</t>
+        </is>
+      </c>
+      <c r="H223" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I223" s="30" t="inlineStr"/>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K223" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L223" s="30" t="inlineStr"/>
+      <c r="M223" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N223" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_13 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="30" customHeight="1">
+      <c r="A224" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B224" s="29" t="inlineStr">
+        <is>
+          <t>Nantucket Sailor</t>
+        </is>
+      </c>
+      <c r="C224" s="30" t="inlineStr">
+        <is>
+          <t>ARC_13_DONE</t>
+        </is>
+      </c>
+      <c r="D224" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — NANTUCKET SAILOR ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E224" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F224" s="31" t="inlineStr">
+        <is>
+          <t>ARC_13_FIRST</t>
+        </is>
+      </c>
+      <c r="G224" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I224" s="30" t="inlineStr"/>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K224" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L224" s="30" t="inlineStr"/>
+      <c r="M224" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N224" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_13 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="30" customHeight="1">
+      <c r="A225" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B225" s="29" t="inlineStr">
+        <is>
+          <t>Frontier Preacher</t>
+        </is>
+      </c>
+      <c r="C225" s="30" t="inlineStr">
+        <is>
+          <t>ARC_14_FIRST</t>
+        </is>
+      </c>
+      <c r="D225" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — FRONTIER PREACHER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E225" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F225" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G225" s="31" t="inlineStr">
+        <is>
+          <t>ARC_14_DONE</t>
+        </is>
+      </c>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I225" s="30" t="inlineStr"/>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K225" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L225" s="30" t="inlineStr"/>
+      <c r="M225" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N225" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_14 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="30" customHeight="1">
+      <c r="A226" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B226" s="29" t="inlineStr">
+        <is>
+          <t>Frontier Preacher</t>
+        </is>
+      </c>
+      <c r="C226" s="30" t="inlineStr">
+        <is>
+          <t>ARC_14_DONE</t>
+        </is>
+      </c>
+      <c r="D226" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — FRONTIER PREACHER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E226" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F226" s="31" t="inlineStr">
+        <is>
+          <t>ARC_14_FIRST</t>
+        </is>
+      </c>
+      <c r="G226" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I226" s="30" t="inlineStr"/>
+      <c r="J226" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K226" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L226" s="30" t="inlineStr"/>
+      <c r="M226" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N226" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_14 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B227" s="29" t="inlineStr">
+        <is>
+          <t>DC Bureaucrat</t>
+        </is>
+      </c>
+      <c r="C227" s="30" t="inlineStr">
+        <is>
+          <t>ARC_15_FIRST</t>
+        </is>
+      </c>
+      <c r="D227" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — DC BUREAUCRAT FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E227" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F227" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G227" s="31" t="inlineStr">
+        <is>
+          <t>ARC_15_DONE</t>
+        </is>
+      </c>
+      <c r="H227" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I227" s="30" t="inlineStr"/>
+      <c r="J227" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K227" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L227" s="30" t="inlineStr"/>
+      <c r="M227" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N227" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_15 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="30" customHeight="1">
+      <c r="A228" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B228" s="29" t="inlineStr">
+        <is>
+          <t>DC Bureaucrat</t>
+        </is>
+      </c>
+      <c r="C228" s="30" t="inlineStr">
+        <is>
+          <t>ARC_15_DONE</t>
+        </is>
+      </c>
+      <c r="D228" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — DC BUREAUCRAT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E228" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F228" s="31" t="inlineStr">
+        <is>
+          <t>ARC_15_FIRST</t>
+        </is>
+      </c>
+      <c r="G228" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I228" s="30" t="inlineStr"/>
+      <c r="J228" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K228" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L228" s="30" t="inlineStr"/>
+      <c r="M228" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N228" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_15 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="30" customHeight="1">
+      <c r="A229" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B229" s="29" t="inlineStr">
+        <is>
+          <t>Rust Belt Steelworker</t>
+        </is>
+      </c>
+      <c r="C229" s="30" t="inlineStr">
+        <is>
+          <t>ARC_16_FIRST</t>
+        </is>
+      </c>
+      <c r="D229" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E229" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F229" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G229" s="31" t="inlineStr">
+        <is>
+          <t>ARC_16_DONE</t>
+        </is>
+      </c>
+      <c r="H229" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I229" s="30" t="inlineStr"/>
+      <c r="J229" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K229" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L229" s="30" t="inlineStr"/>
+      <c r="M229" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N229" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_16 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="30" customHeight="1">
+      <c r="A230" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B230" s="29" t="inlineStr">
+        <is>
+          <t>Rust Belt Steelworker</t>
+        </is>
+      </c>
+      <c r="C230" s="30" t="inlineStr">
+        <is>
+          <t>ARC_16_DONE</t>
+        </is>
+      </c>
+      <c r="D230" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E230" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F230" s="31" t="inlineStr">
+        <is>
+          <t>ARC_16_FIRST</t>
+        </is>
+      </c>
+      <c r="G230" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H230" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I230" s="30" t="inlineStr"/>
+      <c r="J230" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K230" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L230" s="30" t="inlineStr"/>
+      <c r="M230" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N230" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_16 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="30" customHeight="1">
+      <c r="A231" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B231" s="29" t="inlineStr">
+        <is>
+          <t>Plantation Deserter</t>
+        </is>
+      </c>
+      <c r="C231" s="30" t="inlineStr">
+        <is>
+          <t>ARC_17_FIRST</t>
+        </is>
+      </c>
+      <c r="D231" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — PLANTATION DESERTER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E231" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F231" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G231" s="31" t="inlineStr">
+        <is>
+          <t>ARC_17_DONE</t>
+        </is>
+      </c>
+      <c r="H231" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I231" s="30" t="inlineStr"/>
+      <c r="J231" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K231" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L231" s="30" t="inlineStr"/>
+      <c r="M231" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N231" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_17 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="30" customHeight="1">
+      <c r="A232" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B232" s="29" t="inlineStr">
+        <is>
+          <t>Plantation Deserter</t>
+        </is>
+      </c>
+      <c r="C232" s="30" t="inlineStr">
+        <is>
+          <t>ARC_17_DONE</t>
+        </is>
+      </c>
+      <c r="D232" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — PLANTATION DESERTER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E232" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F232" s="31" t="inlineStr">
+        <is>
+          <t>ARC_17_FIRST</t>
+        </is>
+      </c>
+      <c r="G232" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I232" s="30" t="inlineStr"/>
+      <c r="J232" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K232" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L232" s="30" t="inlineStr"/>
+      <c r="M232" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N232" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_17 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="30" customHeight="1">
+      <c r="A233" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B233" s="29" t="inlineStr">
+        <is>
+          <t>Swamp Witch</t>
+        </is>
+      </c>
+      <c r="C233" s="30" t="inlineStr">
+        <is>
+          <t>ARC_18_FIRST</t>
+        </is>
+      </c>
+      <c r="D233" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — SWAMP WITCH FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E233" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F233" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G233" s="31" t="inlineStr">
+        <is>
+          <t>ARC_18_DONE</t>
+        </is>
+      </c>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I233" s="30" t="inlineStr"/>
+      <c r="J233" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K233" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L233" s="30" t="inlineStr"/>
+      <c r="M233" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N233" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_18 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B234" s="29" t="inlineStr">
+        <is>
+          <t>Swamp Witch</t>
+        </is>
+      </c>
+      <c r="C234" s="30" t="inlineStr">
+        <is>
+          <t>ARC_18_DONE</t>
+        </is>
+      </c>
+      <c r="D234" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — SWAMP WITCH ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E234" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F234" s="31" t="inlineStr">
+        <is>
+          <t>ARC_18_FIRST</t>
+        </is>
+      </c>
+      <c r="G234" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H234" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I234" s="30" t="inlineStr"/>
+      <c r="J234" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K234" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L234" s="30" t="inlineStr"/>
+      <c r="M234" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N234" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_18 completes all 3 objectives; BTN1: morale+20, BTN2: magic</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B235" s="29" t="inlineStr">
+        <is>
+          <t>Caribbean Privateer</t>
+        </is>
+      </c>
+      <c r="C235" s="30" t="inlineStr">
+        <is>
+          <t>ARC_19_FIRST</t>
+        </is>
+      </c>
+      <c r="D235" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E235" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F235" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G235" s="31" t="inlineStr">
+        <is>
+          <t>ARC_19_DONE</t>
+        </is>
+      </c>
+      <c r="H235" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I235" s="30" t="inlineStr"/>
+      <c r="J235" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K235" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L235" s="30" t="inlineStr"/>
+      <c r="M235" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N235" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_19 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="30" customHeight="1">
+      <c r="A236" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B236" s="29" t="inlineStr">
+        <is>
+          <t>Caribbean Privateer</t>
+        </is>
+      </c>
+      <c r="C236" s="30" t="inlineStr">
+        <is>
+          <t>ARC_19_DONE</t>
+        </is>
+      </c>
+      <c r="D236" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E236" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F236" s="31" t="inlineStr">
+        <is>
+          <t>ARC_19_FIRST</t>
+        </is>
+      </c>
+      <c r="G236" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I236" s="30" t="inlineStr"/>
+      <c r="J236" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K236" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L236" s="30" t="inlineStr"/>
+      <c r="M236" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N236" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_19 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="30" customHeight="1">
+      <c r="A237" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B237" s="29" t="inlineStr">
+        <is>
+          <t>Hawaiian Refugee</t>
+        </is>
+      </c>
+      <c r="C237" s="30" t="inlineStr">
+        <is>
+          <t>ARC_20_FIRST</t>
+        </is>
+      </c>
+      <c r="D237" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — HAWAIIAN REFUGEE FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E237" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F237" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G237" s="31" t="inlineStr">
+        <is>
+          <t>ARC_20_DONE</t>
+        </is>
+      </c>
+      <c r="H237" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I237" s="30" t="inlineStr"/>
+      <c r="J237" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K237" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L237" s="30" t="inlineStr"/>
+      <c r="M237" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N237" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_20 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="30" customHeight="1">
+      <c r="A238" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B238" s="29" t="inlineStr">
+        <is>
+          <t>Hawaiian Refugee</t>
+        </is>
+      </c>
+      <c r="C238" s="30" t="inlineStr">
+        <is>
+          <t>ARC_20_DONE</t>
+        </is>
+      </c>
+      <c r="D238" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — HAWAIIAN REFUGEE ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E238" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F238" s="31" t="inlineStr">
+        <is>
+          <t>ARC_20_FIRST</t>
+        </is>
+      </c>
+      <c r="G238" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H238" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I238" s="30" t="inlineStr"/>
+      <c r="J238" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K238" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L238" s="30" t="inlineStr"/>
+      <c r="M238" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N238" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_20 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="30" customHeight="1">
+      <c r="A239" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B239" s="29" t="inlineStr">
+        <is>
+          <t>Border Mercenary</t>
+        </is>
+      </c>
+      <c r="C239" s="30" t="inlineStr">
+        <is>
+          <t>ARC_21_FIRST</t>
+        </is>
+      </c>
+      <c r="D239" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — BORDER MERCENARY FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E239" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F239" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G239" s="31" t="inlineStr">
+        <is>
+          <t>ARC_21_DONE</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I239" s="30" t="inlineStr"/>
+      <c r="J239" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K239" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L239" s="30" t="inlineStr"/>
+      <c r="M239" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N239" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_21 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="30" customHeight="1">
+      <c r="A240" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B240" s="29" t="inlineStr">
+        <is>
+          <t>Border Mercenary</t>
+        </is>
+      </c>
+      <c r="C240" s="30" t="inlineStr">
+        <is>
+          <t>ARC_21_DONE</t>
+        </is>
+      </c>
+      <c r="D240" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — BORDER MERCENARY ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E240" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F240" s="31" t="inlineStr">
+        <is>
+          <t>ARC_21_FIRST</t>
+        </is>
+      </c>
+      <c r="G240" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I240" s="30" t="inlineStr"/>
+      <c r="J240" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K240" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L240" s="30" t="inlineStr"/>
+      <c r="M240" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N240" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_21 completes all 3 objectives; BTN1: morale+20, BTN2: weapons</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="30" customHeight="1">
+      <c r="A241" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B241" s="29" t="inlineStr">
+        <is>
+          <t>Acadian Forest Ranger</t>
+        </is>
+      </c>
+      <c r="C241" s="30" t="inlineStr">
+        <is>
+          <t>ARC_22_FIRST</t>
+        </is>
+      </c>
+      <c r="D241" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E241" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F241" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G241" s="31" t="inlineStr">
+        <is>
+          <t>ARC_22_DONE</t>
+        </is>
+      </c>
+      <c r="H241" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I241" s="30" t="inlineStr"/>
+      <c r="J241" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K241" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L241" s="30" t="inlineStr"/>
+      <c r="M241" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N241" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_22 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="30" customHeight="1">
+      <c r="A242" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B242" s="29" t="inlineStr">
+        <is>
+          <t>Acadian Forest Ranger</t>
+        </is>
+      </c>
+      <c r="C242" s="30" t="inlineStr">
+        <is>
+          <t>ARC_22_DONE</t>
+        </is>
+      </c>
+      <c r="D242" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E242" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F242" s="31" t="inlineStr">
+        <is>
+          <t>ARC_22_FIRST</t>
+        </is>
+      </c>
+      <c r="G242" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I242" s="30" t="inlineStr"/>
+      <c r="J242" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K242" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L242" s="30" t="inlineStr"/>
+      <c r="M242" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N242" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_22 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="30" customHeight="1">
+      <c r="A243" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B243" s="29" t="inlineStr">
+        <is>
+          <t>Gettysburg Descendant</t>
+        </is>
+      </c>
+      <c r="C243" s="30" t="inlineStr">
+        <is>
+          <t>ARC_23_FIRST</t>
+        </is>
+      </c>
+      <c r="D243" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E243" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F243" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G243" s="31" t="inlineStr">
+        <is>
+          <t>ARC_23_DONE</t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I243" s="30" t="inlineStr"/>
+      <c r="J243" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K243" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L243" s="30" t="inlineStr"/>
+      <c r="M243" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N243" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_23 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="30" customHeight="1">
+      <c r="A244" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B244" s="29" t="inlineStr">
+        <is>
+          <t>Gettysburg Descendant</t>
+        </is>
+      </c>
+      <c r="C244" s="30" t="inlineStr">
+        <is>
+          <t>ARC_23_DONE</t>
+        </is>
+      </c>
+      <c r="D244" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E244" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F244" s="31" t="inlineStr">
+        <is>
+          <t>ARC_23_FIRST</t>
+        </is>
+      </c>
+      <c r="G244" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I244" s="30" t="inlineStr"/>
+      <c r="J244" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K244" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L244" s="30" t="inlineStr"/>
+      <c r="M244" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N244" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_23 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="30" customHeight="1">
+      <c r="A245" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B245" s="29" t="inlineStr">
+        <is>
+          <t>LGBTQ+ Organizer</t>
+        </is>
+      </c>
+      <c r="C245" s="30" t="inlineStr">
+        <is>
+          <t>ARC_24_FIRST</t>
+        </is>
+      </c>
+      <c r="D245" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E245" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F245" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G245" s="31" t="inlineStr">
+        <is>
+          <t>ARC_24_DONE</t>
+        </is>
+      </c>
+      <c r="H245" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I245" s="30" t="inlineStr"/>
+      <c r="J245" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K245" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L245" s="30" t="inlineStr"/>
+      <c r="M245" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N245" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_24 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B246" s="29" t="inlineStr">
+        <is>
+          <t>LGBTQ+ Organizer</t>
+        </is>
+      </c>
+      <c r="C246" s="30" t="inlineStr">
+        <is>
+          <t>ARC_24_DONE</t>
+        </is>
+      </c>
+      <c r="D246" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E246" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F246" s="31" t="inlineStr">
+        <is>
+          <t>ARC_24_FIRST</t>
+        </is>
+      </c>
+      <c r="G246" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H246" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I246" s="30" t="inlineStr"/>
+      <c r="J246" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K246" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L246" s="30" t="inlineStr"/>
+      <c r="M246" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N246" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_24 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B247" s="29" t="inlineStr">
+        <is>
+          <t>Carnival Barker</t>
+        </is>
+      </c>
+      <c r="C247" s="30" t="inlineStr">
+        <is>
+          <t>ARC_25_FIRST</t>
+        </is>
+      </c>
+      <c r="D247" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CARNIVAL BARKER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E247" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F247" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G247" s="31" t="inlineStr">
+        <is>
+          <t>ARC_25_DONE</t>
+        </is>
+      </c>
+      <c r="H247" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I247" s="30" t="inlineStr"/>
+      <c r="J247" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K247" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L247" s="30" t="inlineStr"/>
+      <c r="M247" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N247" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_25 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="29" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B248" s="29" t="inlineStr">
+        <is>
+          <t>Carnival Barker</t>
+        </is>
+      </c>
+      <c r="C248" s="30" t="inlineStr">
+        <is>
+          <t>ARC_25_DONE</t>
+        </is>
+      </c>
+      <c r="D248" s="31" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CARNIVAL BARKER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E248" s="32" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F248" s="31" t="inlineStr">
+        <is>
+          <t>ARC_25_FIRST</t>
+        </is>
+      </c>
+      <c r="G248" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I248" s="30" t="inlineStr"/>
+      <c r="J248" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K248" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L248" s="30" t="inlineStr"/>
+      <c r="M248" s="32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N248" s="31" t="inlineStr">
+        <is>
+          <t>Fires when ARC_25 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="8" customHeight="1">
+      <c r="A249" s="9" t="n"/>
+      <c r="B249" s="9" t="n"/>
+      <c r="C249" s="9" t="n"/>
+      <c r="D249" s="9" t="n"/>
+      <c r="E249" s="9" t="n"/>
+      <c r="F249" s="9" t="n"/>
+      <c r="G249" s="9" t="n"/>
+      <c r="H249" s="9" t="n"/>
+      <c r="I249" s="9" t="n"/>
+      <c r="J249" s="9" t="n"/>
+      <c r="K249" s="9" t="n"/>
+      <c r="L249" s="9" t="n"/>
+      <c r="M249" s="9" t="n"/>
+      <c r="N249" s="9" t="n"/>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="49" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B199" s="49" t="inlineStr">
+      <c r="B250" s="49" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C199" s="50" t="inlineStr">
+      <c r="C250" s="50" t="inlineStr">
         <is>
           <t>VP_LEGACY</t>
         </is>
       </c>
-      <c r="D199" s="51" t="inlineStr">
+      <c r="D250" s="51" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
         </is>
       </c>
-      <c r="E199" s="22" t="inlineStr">
+      <c r="E250" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F199" s="51" t="inlineStr">
+      <c r="F250" s="51" t="inlineStr">
         <is>
           <t>VP_FIRST_MEETING (turn 96+)</t>
         </is>
       </c>
-      <c r="G199" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H199" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I199" s="50" t="inlineStr"/>
-      <c r="J199" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K199" s="26" t="inlineStr">
+      <c r="G250" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I250" s="50" t="inlineStr"/>
+      <c r="J250" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K250" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L199" s="50" t="inlineStr">
+      <c r="L250" s="50" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M199" s="52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N199" s="51" t="inlineStr">
+      <c r="M250" s="52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N250" s="51" t="inlineStr">
         <is>
           <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="8" customHeight="1">
-      <c r="A200" s="9" t="n"/>
-      <c r="B200" s="9" t="n"/>
-      <c r="C200" s="9" t="n"/>
-      <c r="D200" s="9" t="n"/>
-      <c r="E200" s="9" t="n"/>
-      <c r="F200" s="9" t="n"/>
-      <c r="G200" s="9" t="n"/>
-      <c r="H200" s="9" t="n"/>
-      <c r="I200" s="9" t="n"/>
-      <c r="J200" s="9" t="n"/>
-      <c r="K200" s="9" t="n"/>
-      <c r="L200" s="9" t="n"/>
-      <c r="M200" s="9" t="n"/>
-      <c r="N200" s="9" t="n"/>
-    </row>
-    <row r="201" ht="30" customHeight="1">
-      <c r="A201" s="65" t="inlineStr">
+    <row r="251" ht="8" customHeight="1">
+      <c r="A251" s="9" t="n"/>
+      <c r="B251" s="9" t="n"/>
+      <c r="C251" s="9" t="n"/>
+      <c r="D251" s="9" t="n"/>
+      <c r="E251" s="9" t="n"/>
+      <c r="F251" s="9" t="n"/>
+      <c r="G251" s="9" t="n"/>
+      <c r="H251" s="9" t="n"/>
+      <c r="I251" s="9" t="n"/>
+      <c r="J251" s="9" t="n"/>
+      <c r="K251" s="9" t="n"/>
+      <c r="L251" s="9" t="n"/>
+      <c r="M251" s="9" t="n"/>
+      <c r="N251" s="9" t="n"/>
+    </row>
+    <row r="252" ht="30" customHeight="1">
+      <c r="A252" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B201" s="65" t="inlineStr">
+      <c r="B252" s="65" t="inlineStr">
         <is>
           <t>Month 1</t>
         </is>
       </c>
-      <c r="C201" s="66" t="inlineStr">
+      <c r="C252" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_01</t>
         </is>
       </c>
-      <c r="D201" s="67" t="inlineStr">
+      <c r="D252" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
+      <c r="E252" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F201" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G201" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H201" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I201" s="66" t="inlineStr"/>
-      <c r="J201" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K201" s="26" t="inlineStr">
+      <c r="F252" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G252" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I252" s="66" t="inlineStr"/>
+      <c r="J252" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K252" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L201" s="66" t="inlineStr">
+      <c r="L252" s="66" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M201" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N201" s="67" t="inlineStr">
+      <c r="M252" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N252" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="30" customHeight="1">
-      <c r="A202" s="65" t="inlineStr">
+    <row r="253" ht="30" customHeight="1">
+      <c r="A253" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B202" s="65" t="inlineStr">
+      <c r="B253" s="65" t="inlineStr">
         <is>
           <t>Month 2</t>
         </is>
       </c>
-      <c r="C202" s="66" t="inlineStr">
+      <c r="C253" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_02</t>
         </is>
       </c>
-      <c r="D202" s="67" t="inlineStr">
+      <c r="D253" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr">
+      <c r="E253" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F202" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G202" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H202" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I202" s="66" t="inlineStr"/>
-      <c r="J202" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K202" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L202" s="66" t="inlineStr">
+      <c r="F253" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G253" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H253" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I253" s="66" t="inlineStr"/>
+      <c r="J253" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K253" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L253" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M202" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N202" s="67" t="inlineStr">
+      <c r="M253" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N253" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="30" customHeight="1">
-      <c r="A203" s="65" t="inlineStr">
+    <row r="254" ht="30" customHeight="1">
+      <c r="A254" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B203" s="65" t="inlineStr">
+      <c r="B254" s="65" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
-      <c r="C203" s="66" t="inlineStr">
+      <c r="C254" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_03</t>
         </is>
       </c>
-      <c r="D203" s="67" t="inlineStr">
+      <c r="D254" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
+      <c r="E254" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F203" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G203" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H203" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I203" s="66" t="inlineStr"/>
-      <c r="J203" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K203" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L203" s="66" t="inlineStr">
+      <c r="F254" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G254" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H254" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I254" s="66" t="inlineStr"/>
+      <c r="J254" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K254" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L254" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M203" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N203" s="67" t="inlineStr">
+      <c r="M254" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N254" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="30" customHeight="1">
-      <c r="A204" s="65" t="inlineStr">
+    <row r="255" ht="30" customHeight="1">
+      <c r="A255" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B204" s="65" t="inlineStr">
+      <c r="B255" s="65" t="inlineStr">
         <is>
           <t>Month 4</t>
         </is>
       </c>
-      <c r="C204" s="66" t="inlineStr">
+      <c r="C255" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_04</t>
         </is>
       </c>
-      <c r="D204" s="67" t="inlineStr">
+      <c r="D255" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — EASTER MORNING</t>
         </is>
       </c>
-      <c r="E204" s="5" t="inlineStr">
+      <c r="E255" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F204" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G204" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I204" s="66" t="inlineStr"/>
-      <c r="J204" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K204" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L204" s="66" t="inlineStr">
+      <c r="F255" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G255" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I255" s="66" t="inlineStr"/>
+      <c r="J255" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K255" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L255" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M204" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N204" s="67" t="inlineStr">
+      <c r="M255" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N255" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="30" customHeight="1">
-      <c r="A205" s="65" t="inlineStr">
+    <row r="256" ht="30" customHeight="1">
+      <c r="A256" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B205" s="65" t="inlineStr">
+      <c r="B256" s="65" t="inlineStr">
         <is>
           <t>Month 5</t>
         </is>
       </c>
-      <c r="C205" s="66" t="inlineStr">
+      <c r="C256" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_05</t>
         </is>
       </c>
-      <c r="D205" s="67" t="inlineStr">
+      <c r="D256" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
+      <c r="E256" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F205" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G205" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H205" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I205" s="66" t="inlineStr"/>
-      <c r="J205" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K205" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L205" s="66" t="inlineStr">
+      <c r="F256" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G256" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I256" s="66" t="inlineStr"/>
+      <c r="J256" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K256" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L256" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M205" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N205" s="67" t="inlineStr">
+      <c r="M256" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N256" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="30" customHeight="1">
-      <c r="A206" s="65" t="inlineStr">
+    <row r="257" ht="30" customHeight="1">
+      <c r="A257" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B206" s="65" t="inlineStr">
+      <c r="B257" s="65" t="inlineStr">
         <is>
           <t>Month 6</t>
         </is>
       </c>
-      <c r="C206" s="66" t="inlineStr">
+      <c r="C257" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_06</t>
         </is>
       </c>
-      <c r="D206" s="67" t="inlineStr">
+      <c r="D257" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — JUNETEENTH</t>
         </is>
       </c>
-      <c r="E206" s="5" t="inlineStr">
+      <c r="E257" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F206" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G206" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H206" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I206" s="66" t="inlineStr"/>
-      <c r="J206" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K206" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L206" s="66" t="inlineStr">
+      <c r="F257" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G257" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H257" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I257" s="66" t="inlineStr"/>
+      <c r="J257" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K257" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L257" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M206" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N206" s="67" t="inlineStr">
+      <c r="M257" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N257" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="65" t="inlineStr">
+    <row r="258" ht="30" customHeight="1">
+      <c r="A258" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B207" s="65" t="inlineStr">
+      <c r="B258" s="65" t="inlineStr">
         <is>
           <t>Month 7</t>
         </is>
       </c>
-      <c r="C207" s="66" t="inlineStr">
+      <c r="C258" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_07</t>
         </is>
       </c>
-      <c r="D207" s="67" t="inlineStr">
+      <c r="D258" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
         </is>
       </c>
-      <c r="E207" s="5" t="inlineStr">
+      <c r="E258" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F207" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G207" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H207" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I207" s="66" t="inlineStr"/>
-      <c r="J207" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K207" s="26" t="inlineStr">
+      <c r="F258" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G258" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I258" s="66" t="inlineStr"/>
+      <c r="J258" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K258" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L207" s="66" t="inlineStr">
+      <c r="L258" s="66" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M207" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N207" s="67" t="inlineStr">
+      <c r="M258" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N258" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="30" customHeight="1">
-      <c r="A208" s="65" t="inlineStr">
+    <row r="259" ht="30" customHeight="1">
+      <c r="A259" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B208" s="65" t="inlineStr">
+      <c r="B259" s="65" t="inlineStr">
         <is>
           <t>Month 8</t>
         </is>
       </c>
-      <c r="C208" s="66" t="inlineStr">
+      <c r="C259" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_08</t>
         </is>
       </c>
-      <c r="D208" s="67" t="inlineStr">
+      <c r="D259" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — DIWALI</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
+      <c r="E259" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F208" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G208" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H208" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I208" s="66" t="inlineStr"/>
-      <c r="J208" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K208" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L208" s="66" t="inlineStr">
+      <c r="F259" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G259" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H259" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I259" s="66" t="inlineStr"/>
+      <c r="J259" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K259" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L259" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M208" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N208" s="67" t="inlineStr">
+      <c r="M259" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N259" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="30" customHeight="1">
-      <c r="A209" s="65" t="inlineStr">
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B209" s="65" t="inlineStr">
+      <c r="B260" s="65" t="inlineStr">
         <is>
           <t>Month 9</t>
         </is>
       </c>
-      <c r="C209" s="66" t="inlineStr">
+      <c r="C260" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_09</t>
         </is>
       </c>
-      <c r="D209" s="67" t="inlineStr">
+      <c r="D260" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — HALLOWEEN</t>
         </is>
       </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="E260" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F209" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G209" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H209" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I209" s="66" t="inlineStr"/>
-      <c r="J209" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K209" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L209" s="66" t="inlineStr">
+      <c r="F260" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H260" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I260" s="66" t="inlineStr"/>
+      <c r="J260" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K260" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L260" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M209" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N209" s="67" t="inlineStr">
+      <c r="M260" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N260" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="30" customHeight="1">
-      <c r="A210" s="65" t="inlineStr">
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B210" s="65" t="inlineStr">
+      <c r="B261" s="65" t="inlineStr">
         <is>
           <t>Month 10</t>
         </is>
       </c>
-      <c r="C210" s="66" t="inlineStr">
+      <c r="C261" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_10</t>
         </is>
       </c>
-      <c r="D210" s="67" t="inlineStr">
+      <c r="D261" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E261" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F210" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G210" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H210" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I210" s="66" t="inlineStr"/>
-      <c r="J210" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K210" s="26" t="inlineStr">
+      <c r="F261" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G261" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I261" s="66" t="inlineStr"/>
+      <c r="J261" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K261" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L210" s="66" t="inlineStr">
+      <c r="L261" s="66" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M210" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N210" s="67" t="inlineStr">
+      <c r="M261" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N261" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="30" customHeight="1">
-      <c r="A211" s="65" t="inlineStr">
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B211" s="65" t="inlineStr">
+      <c r="B262" s="65" t="inlineStr">
         <is>
           <t>Month 11</t>
         </is>
       </c>
-      <c r="C211" s="66" t="inlineStr">
+      <c r="C262" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_11</t>
         </is>
       </c>
-      <c r="D211" s="67" t="inlineStr">
+      <c r="D262" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — THANKSGIVING</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E262" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F211" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G211" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H211" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I211" s="66" t="inlineStr"/>
-      <c r="J211" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K211" s="68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L211" s="66" t="inlineStr">
+      <c r="F262" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G262" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H262" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I262" s="66" t="inlineStr"/>
+      <c r="J262" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K262" s="68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L262" s="66" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M211" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N211" s="67" t="inlineStr">
+      <c r="M262" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N262" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="30" customHeight="1">
-      <c r="A212" s="65" t="inlineStr">
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="65" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B212" s="65" t="inlineStr">
+      <c r="B263" s="65" t="inlineStr">
         <is>
           <t>Month 12</t>
         </is>
       </c>
-      <c r="C212" s="66" t="inlineStr">
+      <c r="C263" s="66" t="inlineStr">
         <is>
           <t>WH_SECRET_12</t>
         </is>
       </c>
-      <c r="D212" s="67" t="inlineStr">
+      <c r="D263" s="67" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — CHRISTMAS</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E263" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F212" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G212" s="67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H212" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I212" s="66" t="inlineStr"/>
-      <c r="J212" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K212" s="26" t="inlineStr">
+      <c r="F263" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G263" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I263" s="66" t="inlineStr"/>
+      <c r="J263" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K263" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L212" s="66" t="inlineStr">
+      <c r="L263" s="66" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M212" s="68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N212" s="67" t="inlineStr">
+      <c r="M263" s="68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N263" s="67" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="8" customHeight="1">
-      <c r="A213" s="9" t="n"/>
-      <c r="B213" s="9" t="n"/>
-      <c r="C213" s="9" t="n"/>
-      <c r="D213" s="9" t="n"/>
-      <c r="E213" s="9" t="n"/>
-      <c r="F213" s="9" t="n"/>
-      <c r="G213" s="9" t="n"/>
-      <c r="H213" s="9" t="n"/>
-      <c r="I213" s="9" t="n"/>
-      <c r="J213" s="9" t="n"/>
-      <c r="K213" s="9" t="n"/>
-      <c r="L213" s="9" t="n"/>
-      <c r="M213" s="9" t="n"/>
-      <c r="N213" s="9" t="n"/>
-    </row>
-    <row r="214" ht="30" customHeight="1">
-      <c r="A214" s="69" t="inlineStr">
+    <row r="264" ht="8" customHeight="1">
+      <c r="A264" s="9" t="n"/>
+      <c r="B264" s="9" t="n"/>
+      <c r="C264" s="9" t="n"/>
+      <c r="D264" s="9" t="n"/>
+      <c r="E264" s="9" t="n"/>
+      <c r="F264" s="9" t="n"/>
+      <c r="G264" s="9" t="n"/>
+      <c r="H264" s="9" t="n"/>
+      <c r="I264" s="9" t="n"/>
+      <c r="J264" s="9" t="n"/>
+      <c r="K264" s="9" t="n"/>
+      <c r="L264" s="9" t="n"/>
+      <c r="M264" s="9" t="n"/>
+      <c r="N264" s="9" t="n"/>
+    </row>
+    <row r="265" ht="30" customHeight="1">
+      <c r="A265" s="69" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B214" s="69" t="inlineStr">
+      <c r="B265" s="69" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C214" s="70" t="inlineStr">
+      <c r="C265" s="70" t="inlineStr">
         <is>
           <t>CHALCH_SUMMON</t>
         </is>
       </c>
-      <c r="D214" s="71" t="inlineStr">
+      <c r="D265" s="71" t="inlineStr">
         <is>
           <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F214" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G214" s="71" t="inlineStr">
+      <c r="F265" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G265" s="71" t="inlineStr">
         <is>
           <t>CHALCH_Q1</t>
         </is>
       </c>
-      <c r="H214" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I214" s="70" t="inlineStr"/>
-      <c r="J214" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K214" s="72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L214" s="70" t="inlineStr"/>
-      <c r="M214" s="72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N214" s="71" t="inlineStr">
+      <c r="H265" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I265" s="70" t="inlineStr"/>
+      <c r="J265" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K265" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L265" s="70" t="inlineStr"/>
+      <c r="M265" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N265" s="71" t="inlineStr">
         <is>
           <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="30" customHeight="1">
-      <c r="A215" s="69" t="inlineStr">
+    <row r="266" ht="30" customHeight="1">
+      <c r="A266" s="69" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B215" s="69" t="inlineStr">
+      <c r="B266" s="69" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C215" s="70" t="inlineStr">
+      <c r="C266" s="70" t="inlineStr">
         <is>
           <t>CHALCH_Q1</t>
         </is>
       </c>
-      <c r="D215" s="71" t="inlineStr">
+      <c r="D266" s="71" t="inlineStr">
         <is>
           <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
         </is>
       </c>
-      <c r="E215" s="72" t="inlineStr">
+      <c r="E266" s="72" t="inlineStr">
         <is>
           <t>Quest 1</t>
         </is>
       </c>
-      <c r="F215" s="71" t="inlineStr">
+      <c r="F266" s="71" t="inlineStr">
         <is>
           <t>CHALCH_SUMMON</t>
         </is>
       </c>
-      <c r="G215" s="71" t="inlineStr">
+      <c r="G266" s="71" t="inlineStr">
         <is>
           <t>CHALCH_Q2</t>
         </is>
       </c>
-      <c r="H215" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I215" s="70" t="inlineStr"/>
-      <c r="J215" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K215" s="72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L215" s="70" t="inlineStr"/>
-      <c r="M215" s="72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N215" s="71" t="inlineStr">
+      <c r="H266" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I266" s="70" t="inlineStr"/>
+      <c r="J266" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K266" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L266" s="70" t="inlineStr"/>
+      <c r="M266" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N266" s="71" t="inlineStr">
         <is>
           <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="30" customHeight="1">
-      <c r="A216" s="69" t="inlineStr">
+    <row r="267" ht="30" customHeight="1">
+      <c r="A267" s="69" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B216" s="69" t="inlineStr">
+      <c r="B267" s="69" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C216" s="70" t="inlineStr">
+      <c r="C267" s="70" t="inlineStr">
         <is>
           <t>CHALCH_Q2</t>
         </is>
       </c>
-      <c r="D216" s="71" t="inlineStr">
+      <c r="D267" s="71" t="inlineStr">
         <is>
           <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
         </is>
       </c>
-      <c r="E216" s="72" t="inlineStr">
+      <c r="E267" s="72" t="inlineStr">
         <is>
           <t>Quest 2</t>
         </is>
       </c>
-      <c r="F216" s="71" t="inlineStr">
+      <c r="F267" s="71" t="inlineStr">
         <is>
           <t>CHALCH_Q1</t>
         </is>
       </c>
-      <c r="G216" s="71" t="inlineStr">
+      <c r="G267" s="71" t="inlineStr">
         <is>
           <t>CHALCH_Q3</t>
         </is>
       </c>
-      <c r="H216" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I216" s="70" t="inlineStr"/>
-      <c r="J216" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K216" s="72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L216" s="70" t="inlineStr"/>
-      <c r="M216" s="72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N216" s="71" t="inlineStr">
+      <c r="H267" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I267" s="70" t="inlineStr"/>
+      <c r="J267" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K267" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L267" s="70" t="inlineStr"/>
+      <c r="M267" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N267" s="71" t="inlineStr">
         <is>
           <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="30" customHeight="1">
-      <c r="A217" s="69" t="inlineStr">
+    <row r="268" ht="30" customHeight="1">
+      <c r="A268" s="69" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B217" s="69" t="inlineStr">
+      <c r="B268" s="69" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C217" s="70" t="inlineStr">
+      <c r="C268" s="70" t="inlineStr">
         <is>
           <t>CHALCH_Q3</t>
         </is>
       </c>
-      <c r="D217" s="71" t="inlineStr">
+      <c r="D268" s="71" t="inlineStr">
         <is>
           <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
         </is>
       </c>
-      <c r="E217" s="72" t="inlineStr">
+      <c r="E268" s="72" t="inlineStr">
         <is>
           <t>Quest 3</t>
         </is>
       </c>
-      <c r="F217" s="71" t="inlineStr">
+      <c r="F268" s="71" t="inlineStr">
         <is>
           <t>CHALCH_Q2</t>
         </is>
       </c>
-      <c r="G217" s="71" t="inlineStr">
+      <c r="G268" s="71" t="inlineStr">
         <is>
           <t>CHALCH_AGREE</t>
         </is>
       </c>
-      <c r="H217" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I217" s="70" t="inlineStr"/>
-      <c r="J217" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K217" s="72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L217" s="70" t="inlineStr"/>
-      <c r="M217" s="72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N217" s="71" t="inlineStr">
+      <c r="H268" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I268" s="70" t="inlineStr"/>
+      <c r="J268" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K268" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L268" s="70" t="inlineStr"/>
+      <c r="M268" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N268" s="71" t="inlineStr">
         <is>
           <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="30" customHeight="1">
-      <c r="A218" s="69" t="inlineStr">
+    <row r="269" ht="30" customHeight="1">
+      <c r="A269" s="69" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B218" s="69" t="inlineStr">
+      <c r="B269" s="69" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C218" s="70" t="inlineStr">
+      <c r="C269" s="70" t="inlineStr">
         <is>
           <t>CHALCH_AGREE</t>
         </is>
       </c>
-      <c r="D218" s="71" t="inlineStr">
+      <c r="D269" s="71" t="inlineStr">
         <is>
           <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
         </is>
       </c>
-      <c r="E218" s="72" t="inlineStr">
+      <c r="E269" s="72" t="inlineStr">
         <is>
           <t>Resolution</t>
         </is>
       </c>
-      <c r="F218" s="71" t="inlineStr">
+      <c r="F269" s="71" t="inlineStr">
         <is>
           <t>CHALCH_Q3</t>
         </is>
       </c>
-      <c r="G218" s="71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H218" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I218" s="70" t="inlineStr"/>
-      <c r="J218" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K218" s="72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L218" s="70" t="inlineStr"/>
-      <c r="M218" s="72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N218" s="71" t="inlineStr">
+      <c r="G269" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H269" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I269" s="70" t="inlineStr"/>
+      <c r="J269" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K269" s="72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L269" s="70" t="inlineStr"/>
+      <c r="M269" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N269" s="71" t="inlineStr">
         <is>
           <t>Fires when chalch_q3_done; BTN1: +100 food; closes the arc</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="8" customHeight="1">
-      <c r="A219" s="9" t="n"/>
-      <c r="B219" s="9" t="n"/>
-      <c r="C219" s="9" t="n"/>
-      <c r="D219" s="9" t="n"/>
-      <c r="E219" s="9" t="n"/>
-      <c r="F219" s="9" t="n"/>
-      <c r="G219" s="9" t="n"/>
-      <c r="H219" s="9" t="n"/>
-      <c r="I219" s="9" t="n"/>
-      <c r="J219" s="9" t="n"/>
-      <c r="K219" s="9" t="n"/>
-      <c r="L219" s="9" t="n"/>
-      <c r="M219" s="9" t="n"/>
-      <c r="N219" s="9" t="n"/>
-    </row>
-    <row r="220" ht="30" customHeight="1">
-      <c r="A220" s="73" t="inlineStr">
+    <row r="270" ht="8" customHeight="1">
+      <c r="A270" s="9" t="n"/>
+      <c r="B270" s="9" t="n"/>
+      <c r="C270" s="9" t="n"/>
+      <c r="D270" s="9" t="n"/>
+      <c r="E270" s="9" t="n"/>
+      <c r="F270" s="9" t="n"/>
+      <c r="G270" s="9" t="n"/>
+      <c r="H270" s="9" t="n"/>
+      <c r="I270" s="9" t="n"/>
+      <c r="J270" s="9" t="n"/>
+      <c r="K270" s="9" t="n"/>
+      <c r="L270" s="9" t="n"/>
+      <c r="M270" s="9" t="n"/>
+      <c r="N270" s="9" t="n"/>
+    </row>
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B220" s="73" t="inlineStr">
+      <c r="B271" s="73" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C220" s="74" t="inlineStr">
+      <c r="C271" s="74" t="inlineStr">
         <is>
           <t>UALANI_DOCK_01</t>
         </is>
       </c>
-      <c r="D220" s="75" t="inlineStr">
+      <c r="D271" s="75" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
-      <c r="E220" s="5" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F220" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G220" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H220" s="76" t="inlineStr">
+      <c r="F271" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G271" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H271" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I220" s="74" t="inlineStr"/>
-      <c r="J220" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K220" s="26" t="inlineStr">
+      <c r="I271" s="74" t="inlineStr"/>
+      <c r="J271" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K271" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L220" s="74" t="inlineStr">
+      <c r="L271" s="74" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M220" s="77" t="inlineStr">
+      <c r="M271" s="77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N220" s="75" t="inlineStr">
+      <c r="N271" s="75" t="inlineStr">
         <is>
           <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="30" customHeight="1">
-      <c r="A221" s="73" t="inlineStr">
+    <row r="272" ht="30" customHeight="1">
+      <c r="A272" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B221" s="73" t="inlineStr">
+      <c r="B272" s="73" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C221" s="74" t="inlineStr">
+      <c r="C272" s="74" t="inlineStr">
         <is>
           <t>UALANI_FARM_01</t>
         </is>
       </c>
-      <c r="D221" s="75" t="inlineStr">
+      <c r="D272" s="75" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
-      <c r="E221" s="5" t="inlineStr">
+      <c r="E272" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F221" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G221" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H221" s="76" t="inlineStr">
+      <c r="F272" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G272" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H272" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I221" s="74" t="inlineStr"/>
-      <c r="J221" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K221" s="26" t="inlineStr">
+      <c r="I272" s="74" t="inlineStr"/>
+      <c r="J272" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K272" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L221" s="74" t="inlineStr">
+      <c r="L272" s="74" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M221" s="77" t="inlineStr">
+      <c r="M272" s="77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N221" s="75" t="inlineStr">
+      <c r="N272" s="75" t="inlineStr">
         <is>
           <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="30" customHeight="1">
-      <c r="A222" s="73" t="inlineStr">
+    <row r="273" ht="30" customHeight="1">
+      <c r="A273" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B222" s="73" t="inlineStr">
+      <c r="B273" s="73" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C222" s="74" t="inlineStr">
+      <c r="C273" s="74" t="inlineStr">
         <is>
           <t>UALANI_BARRACKS_01</t>
         </is>
       </c>
-      <c r="D222" s="75" t="inlineStr">
+      <c r="D273" s="75" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
-      <c r="E222" s="5" t="inlineStr">
+      <c r="E273" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F222" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G222" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H222" s="76" t="inlineStr">
+      <c r="F273" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G273" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H273" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I222" s="74" t="inlineStr"/>
-      <c r="J222" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K222" s="26" t="inlineStr">
+      <c r="I273" s="74" t="inlineStr"/>
+      <c r="J273" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K273" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L222" s="74" t="inlineStr">
+      <c r="L273" s="74" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M222" s="77" t="inlineStr">
+      <c r="M273" s="77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N222" s="75" t="inlineStr">
+      <c r="N273" s="75" t="inlineStr">
         <is>
           <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="30" customHeight="1">
-      <c r="A223" s="73" t="inlineStr">
+    <row r="274" ht="30" customHeight="1">
+      <c r="A274" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B223" s="73" t="inlineStr">
+      <c r="B274" s="73" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C223" s="74" t="inlineStr">
+      <c r="C274" s="74" t="inlineStr">
         <is>
           <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
-      <c r="D223" s="75" t="inlineStr">
+      <c r="D274" s="75" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E274" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F223" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G223" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H223" s="76" t="inlineStr">
+      <c r="F274" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G274" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H274" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I223" s="74" t="inlineStr"/>
-      <c r="J223" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K223" s="26" t="inlineStr">
+      <c r="I274" s="74" t="inlineStr"/>
+      <c r="J274" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K274" s="26" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L223" s="74" t="inlineStr">
+      <c r="L274" s="74" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M223" s="77" t="inlineStr">
+      <c r="M274" s="77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N223" s="75" t="inlineStr">
+      <c r="N274" s="75" t="inlineStr">
         <is>
           <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="30" customHeight="1">
-      <c r="A224" s="73" t="inlineStr">
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B224" s="73" t="inlineStr">
+      <c r="B275" s="73" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C224" s="74" t="inlineStr">
+      <c r="C275" s="74" t="inlineStr">
         <is>
           <t>CL_WASHINGTON_01</t>
         </is>
       </c>
-      <c r="D224" s="75" t="inlineStr">
+      <c r="D275" s="75" t="inlineStr">
         <is>
           <t>WASHINGTON DC LIBERATED  ← IDEA</t>
         </is>
       </c>
-      <c r="E224" s="5" t="inlineStr">
+      <c r="E275" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F224" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G224" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H224" s="76" t="inlineStr">
+      <c r="F275" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G275" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H275" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I224" s="74" t="inlineStr"/>
-      <c r="J224" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K224" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L224" s="74" t="inlineStr"/>
-      <c r="M224" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N224" s="75" t="inlineStr">
+      <c r="I275" s="74" t="inlineStr"/>
+      <c r="J275" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K275" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L275" s="74" t="inlineStr"/>
+      <c r="M275" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N275" s="75" t="inlineStr">
         <is>
           <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="30" customHeight="1">
-      <c r="A225" s="73" t="inlineStr">
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B225" s="73" t="inlineStr">
+      <c r="B276" s="73" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C225" s="74" t="inlineStr">
+      <c r="C276" s="74" t="inlineStr">
         <is>
           <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
-      <c r="D225" s="75" t="inlineStr">
+      <c r="D276" s="75" t="inlineStr">
         <is>
           <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
       </c>
-      <c r="E225" s="5" t="inlineStr">
+      <c r="E276" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F225" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G225" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H225" s="76" t="inlineStr">
+      <c r="F276" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G276" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H276" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I225" s="74" t="inlineStr"/>
-      <c r="J225" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K225" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L225" s="74" t="inlineStr"/>
-      <c r="M225" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N225" s="75" t="inlineStr">
+      <c r="I276" s="74" t="inlineStr"/>
+      <c r="J276" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K276" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L276" s="74" t="inlineStr"/>
+      <c r="M276" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N276" s="75" t="inlineStr">
         <is>
           <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="30" customHeight="1">
-      <c r="A226" s="73" t="inlineStr">
+    <row r="277" ht="30" customHeight="1">
+      <c r="A277" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B226" s="73" t="inlineStr">
+      <c r="B277" s="73" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C226" s="74" t="inlineStr">
+      <c r="C277" s="74" t="inlineStr">
         <is>
           <t>CX_NYC_01</t>
         </is>
       </c>
-      <c r="D226" s="75" t="inlineStr">
+      <c r="D277" s="75" t="inlineStr">
         <is>
           <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
-      <c r="E226" s="5" t="inlineStr">
+      <c r="E277" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F226" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G226" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H226" s="76" t="inlineStr">
+      <c r="F277" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G277" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H277" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I226" s="74" t="inlineStr"/>
-      <c r="J226" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K226" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L226" s="74" t="inlineStr"/>
-      <c r="M226" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N226" s="75" t="inlineStr">
+      <c r="I277" s="74" t="inlineStr"/>
+      <c r="J277" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K277" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L277" s="74" t="inlineStr"/>
+      <c r="M277" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N277" s="75" t="inlineStr">
         <is>
           <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="30" customHeight="1">
-      <c r="A227" s="73" t="inlineStr">
+    <row r="278" ht="30" customHeight="1">
+      <c r="A278" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B227" s="73" t="inlineStr">
+      <c r="B278" s="73" t="inlineStr">
         <is>
           <t>Espionage Events</t>
         </is>
       </c>
-      <c r="C227" s="74" t="inlineStr">
+      <c r="C278" s="74" t="inlineStr">
         <is>
           <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
-      <c r="D227" s="75" t="inlineStr">
+      <c r="D278" s="75" t="inlineStr">
         <is>
           <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
-      <c r="E227" s="5" t="inlineStr">
+      <c r="E278" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F227" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G227" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H227" s="76" t="inlineStr">
+      <c r="F278" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G278" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H278" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I227" s="74" t="inlineStr"/>
-      <c r="J227" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K227" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L227" s="74" t="inlineStr"/>
-      <c r="M227" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N227" s="75" t="inlineStr">
+      <c r="I278" s="74" t="inlineStr"/>
+      <c r="J278" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K278" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L278" s="74" t="inlineStr"/>
+      <c r="M278" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N278" s="75" t="inlineStr">
         <is>
           <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="30" customHeight="1">
-      <c r="A228" s="73" t="inlineStr">
+    <row r="279" ht="30" customHeight="1">
+      <c r="A279" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B228" s="73" t="inlineStr">
+      <c r="B279" s="73" t="inlineStr">
         <is>
           <t>Commander Expansion</t>
         </is>
       </c>
-      <c r="C228" s="74" t="inlineStr">
+      <c r="C279" s="74" t="inlineStr">
         <is>
           <t>CMD_OBJECTIVE_2</t>
         </is>
       </c>
-      <c r="D228" s="75" t="inlineStr">
+      <c r="D279" s="75" t="inlineStr">
         <is>
           <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
         </is>
       </c>
-      <c r="E228" s="22" t="inlineStr">
+      <c r="E279" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F228" s="75" t="inlineStr">
+      <c r="F279" s="75" t="inlineStr">
         <is>
           <t>CMD_OBJECTIVE_1</t>
         </is>
       </c>
-      <c r="G228" s="75" t="inlineStr">
+      <c r="G279" s="75" t="inlineStr">
         <is>
           <t>→ CMD_OBJECTIVE_3?</t>
         </is>
       </c>
-      <c r="H228" s="76" t="inlineStr">
+      <c r="H279" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I228" s="74" t="inlineStr"/>
-      <c r="J228" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K228" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L228" s="74" t="inlineStr"/>
-      <c r="M228" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N228" s="75" t="inlineStr">
+      <c r="I279" s="74" t="inlineStr"/>
+      <c r="J279" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K279" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L279" s="74" t="inlineStr"/>
+      <c r="M279" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N279" s="75" t="inlineStr">
         <is>
           <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="30" customHeight="1">
-      <c r="A229" s="73" t="inlineStr">
+    <row r="280" ht="30" customHeight="1">
+      <c r="A280" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B229" s="73" t="inlineStr">
+      <c r="B280" s="73" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C229" s="74" t="inlineStr">
+      <c r="C280" s="74" t="inlineStr">
         <is>
           <t>WINTER_SIEGE_01</t>
         </is>
       </c>
-      <c r="D229" s="75" t="inlineStr">
+      <c r="D280" s="75" t="inlineStr">
         <is>
           <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
       </c>
-      <c r="E229" s="5" t="inlineStr">
+      <c r="E280" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F229" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G229" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H229" s="76" t="inlineStr">
+      <c r="F280" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G280" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H280" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I229" s="74" t="inlineStr"/>
-      <c r="J229" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K229" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L229" s="74" t="inlineStr"/>
-      <c r="M229" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N229" s="75" t="inlineStr">
+      <c r="I280" s="74" t="inlineStr"/>
+      <c r="J280" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K280" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L280" s="74" t="inlineStr"/>
+      <c r="M280" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N280" s="75" t="inlineStr">
         <is>
           <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="30" customHeight="1">
-      <c r="A230" s="73" t="inlineStr">
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="73" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B230" s="73" t="inlineStr">
+      <c r="B281" s="73" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C230" s="74" t="inlineStr">
+      <c r="C281" s="74" t="inlineStr">
         <is>
           <t>SPRING_OFFENSIVE_01</t>
         </is>
       </c>
-      <c r="D230" s="75" t="inlineStr">
+      <c r="D281" s="75" t="inlineStr">
         <is>
           <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
         </is>
       </c>
-      <c r="E230" s="5" t="inlineStr">
+      <c r="E281" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F230" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G230" s="75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H230" s="76" t="inlineStr">
+      <c r="F281" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G281" s="75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H281" s="76" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I230" s="74" t="inlineStr"/>
-      <c r="J230" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K230" s="77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L230" s="74" t="inlineStr"/>
-      <c r="M230" s="77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N230" s="75" t="inlineStr">
+      <c r="I281" s="74" t="inlineStr"/>
+      <c r="J281" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K281" s="77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L281" s="74" t="inlineStr"/>
+      <c r="M281" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N281" s="75" t="inlineStr">
         <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="20" customHeight="1">
-      <c r="A232" s="78" t="inlineStr">
+    <row r="283" ht="20" customHeight="1">
+      <c r="A283" s="78" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B232" s="79" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="233" ht="20" customHeight="1">
-      <c r="A233" s="78" t="inlineStr">
+      <c r="B283" s="79" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="284" ht="20" customHeight="1">
+      <c r="A284" s="78" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B233" s="79" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="234" ht="20" customHeight="1">
-      <c r="A234" s="78" t="inlineStr">
+      <c r="B284" s="79" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="285" ht="20" customHeight="1">
+      <c r="A285" s="78" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B234" s="79" t="n">
+      <c r="B285" s="79" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="235" ht="20" customHeight="1">
-      <c r="A235" s="78" t="inlineStr">
+    <row r="286" ht="20" customHeight="1">
+      <c r="A286" s="78" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B235" s="79" t="n">
+      <c r="B286" s="79" t="n">
         <v>55</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -21863,7 +21863,7 @@
       </c>
       <c r="B33" s="126" t="inlineStr">
         <is>
-          <t>Jessica Clear-Water's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
+          <t>Jessica Commanda's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
         </is>
       </c>
       <c r="C33" s="126" t="n"/>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -21863,7 +21863,7 @@
       </c>
       <c r="B33" s="126" t="inlineStr">
         <is>
-          <t>Jessica Commanda's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
+          <t>Jessica Commanda Odjick's 8 creature arcs; Algonquin, Mi'kmaq, French-Canadian folklore</t>
         </is>
       </c>
       <c r="C33" s="126" t="n"/>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -11340,7 +11340,7 @@
       </c>
       <c r="N163" s="59" t="inlineStr">
         <is>
-          <t>Sets ca_prot_07_agreed; BTN2 sensual — Mark Penoit on the river</t>
+          <t>Sets ca_prot_07_agreed; BTN2 sensual — Marc Penoit on the river</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="N33" s="59" t="inlineStr">
         <is>
-          <t>Sets ca_prot_07_agreed; BTN2 sensual — Mark Penoit on the river</t>
+          <t>Sets ca_prot_07_agreed; BTN2 sensual — Marc Penoit on the river</t>
         </is>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -9765,7 +9765,11 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I139" s="54" t="inlineStr"/>
+      <c r="I139" s="54" t="inlineStr">
+        <is>
+          <t>can_alliance_signed_scene</t>
+        </is>
+      </c>
       <c r="J139" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -9788,7 +9792,7 @@
       </c>
       <c r="N139" s="55" t="inlineStr">
         <is>
-          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome</t>
+          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome. Text polished: ceremony + addendum comedy + 'principals remain in the treaty room' pivot. Art commissioned (120x120 pixel, 4 panels: ceremony/addendum/private room/explicit). Awaiting art integration for FULL COMPLETION.</t>
         </is>
       </c>
     </row>
@@ -19395,7 +19399,11 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I9" s="54" t="inlineStr"/>
+      <c r="I9" s="54" t="inlineStr">
+        <is>
+          <t>can_alliance_signed_scene</t>
+        </is>
+      </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -19418,7 +19426,7 @@
       </c>
       <c r="N9" s="55" t="inlineStr">
         <is>
-          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome</t>
+          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome. Text polished: ceremony + addendum comedy + 'principals remain in the treaty room' pivot. Art commissioned (120x120 pixel, 4 panels: ceremony/addendum/private room/explicit). Awaiting art integration for FULL COMPLETION.</t>
         </is>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -9792,7 +9792,7 @@
       </c>
       <c r="N139" s="55" t="inlineStr">
         <is>
-          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome. Text polished: ceremony + addendum comedy + 'principals remain in the treaty room' pivot. Art commissioned (120x120 pixel, 4 panels: ceremony/addendum/private room/explicit). Awaiting art integration for FULL COMPLETION.</t>
+          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome. Text polished: Lake Erie at sundown — ceremony + addendum comedy — cameras clear — Marc borrows tricorne and walks to the beach — Ualani + Jessica alone at the table — Marc's silhouette gets the perfect shot. Awaiting art integration for FULL COMPLETION.</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="N9" s="55" t="inlineStr">
         <is>
-          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome. Text polished: ceremony + addendum comedy + 'principals remain in the treaty room' pivot. Art commissioned (120x120 pixel, 4 panels: ceremony/addendum/private room/explicit). Awaiting art integration for FULL COMPLETION.</t>
+          <t>EXPLICIT #2 (all three); fires after can_summit_complete; form_alliance CA outcome. Text polished: Lake Erie at sundown — ceremony + addendum comedy — cameras clear — Marc borrows tricorne and walks to the beach — Ualani + Jessica alone at the table — Marc's silhouette gets the perfect shot. Awaiting art integration for FULL COMPLETION.</t>
         </is>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N287"/>
+  <dimension ref="A1:N350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18828,43 +18828,3595 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="20" customHeight="1">
-      <c r="A284" s="79" t="inlineStr">
+    <row r="283" ht="8" customHeight="1">
+      <c r="A283" s="9" t="n"/>
+      <c r="B283" s="9" t="n"/>
+      <c r="C283" s="9" t="n"/>
+      <c r="D283" s="9" t="n"/>
+      <c r="E283" s="9" t="n"/>
+      <c r="F283" s="9" t="n"/>
+      <c r="G283" s="9" t="n"/>
+      <c r="H283" s="9" t="n"/>
+      <c r="I283" s="9" t="n"/>
+      <c r="J283" s="9" t="n"/>
+      <c r="K283" s="9" t="n"/>
+      <c r="L283" s="9" t="n"/>
+      <c r="M283" s="9" t="n"/>
+      <c r="N283" s="9" t="n"/>
+    </row>
+    <row r="284" ht="30" customHeight="1">
+      <c r="A284" s="74" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B284" s="74" t="inlineStr">
+        <is>
+          <t>Commander Arc</t>
+        </is>
+      </c>
+      <c r="C284" s="75" t="inlineStr">
+        <is>
+          <t>CMD_THANKS_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D284" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMM... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E284" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F284" s="76" t="inlineStr">
+        <is>
+          <t>CMD_THANKS (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G284" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H284" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I284" s="75" t="inlineStr"/>
+      <c r="J284" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K284" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L284" s="75" t="inlineStr"/>
+      <c r="M284" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N284" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CMD_THANKS. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="8" customHeight="1">
+      <c r="A285" s="9" t="n"/>
+      <c r="B285" s="9" t="n"/>
+      <c r="C285" s="9" t="n"/>
+      <c r="D285" s="9" t="n"/>
+      <c r="E285" s="9" t="n"/>
+      <c r="F285" s="9" t="n"/>
+      <c r="G285" s="9" t="n"/>
+      <c r="H285" s="9" t="n"/>
+      <c r="I285" s="9" t="n"/>
+      <c r="J285" s="9" t="n"/>
+      <c r="K285" s="9" t="n"/>
+      <c r="L285" s="9" t="n"/>
+      <c r="M285" s="9" t="n"/>
+      <c r="N285" s="9" t="n"/>
+    </row>
+    <row r="286" ht="30" customHeight="1">
+      <c r="A286" s="74" t="inlineStr">
+        <is>
+          <t>Fort Chain</t>
+        </is>
+      </c>
+      <c r="B286" s="74" t="inlineStr">
+        <is>
+          <t>Fort Disrepair</t>
+        </is>
+      </c>
+      <c r="C286" s="75" t="inlineStr">
+        <is>
+          <t>FORT_005_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D286" s="76" t="inlineStr">
+        <is>
+          <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME] — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E286" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F286" s="76" t="inlineStr">
+        <is>
+          <t>FORT_005 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G286" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H286" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I286" s="75" t="inlineStr"/>
+      <c r="J286" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K286" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L286" s="75" t="inlineStr"/>
+      <c r="M286" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N286" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of FORT_005. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="8" customHeight="1">
+      <c r="A287" s="9" t="n"/>
+      <c r="B287" s="9" t="n"/>
+      <c r="C287" s="9" t="n"/>
+      <c r="D287" s="9" t="n"/>
+      <c r="E287" s="9" t="n"/>
+      <c r="F287" s="9" t="n"/>
+      <c r="G287" s="9" t="n"/>
+      <c r="H287" s="9" t="n"/>
+      <c r="I287" s="9" t="n"/>
+      <c r="J287" s="9" t="n"/>
+      <c r="K287" s="9" t="n"/>
+      <c r="L287" s="9" t="n"/>
+      <c r="M287" s="9" t="n"/>
+      <c r="N287" s="9" t="n"/>
+    </row>
+    <row r="288" ht="30" customHeight="1">
+      <c r="A288" s="74" t="inlineStr">
+        <is>
+          <t>Collapse</t>
+        </is>
+      </c>
+      <c r="B288" s="74" t="inlineStr">
+        <is>
+          <t>Republic Falls</t>
+        </is>
+      </c>
+      <c r="C288" s="75" t="inlineStr">
+        <is>
+          <t>COLLAPSE_02_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D288" s="76" t="inlineStr">
+        <is>
+          <t>WASHINGTON STANDS ALONE — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E288" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F288" s="76" t="inlineStr">
+        <is>
+          <t>COLLAPSE_02 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G288" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H288" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I288" s="75" t="inlineStr"/>
+      <c r="J288" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K288" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L288" s="75" t="inlineStr"/>
+      <c r="M288" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N288" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of COLLAPSE_02. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="8" customHeight="1">
+      <c r="A289" s="9" t="n"/>
+      <c r="B289" s="9" t="n"/>
+      <c r="C289" s="9" t="n"/>
+      <c r="D289" s="9" t="n"/>
+      <c r="E289" s="9" t="n"/>
+      <c r="F289" s="9" t="n"/>
+      <c r="G289" s="9" t="n"/>
+      <c r="H289" s="9" t="n"/>
+      <c r="I289" s="9" t="n"/>
+      <c r="J289" s="9" t="n"/>
+      <c r="K289" s="9" t="n"/>
+      <c r="L289" s="9" t="n"/>
+      <c r="M289" s="9" t="n"/>
+      <c r="N289" s="9" t="n"/>
+    </row>
+    <row r="290" ht="30" customHeight="1">
+      <c r="A290" s="74" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B290" s="74" t="inlineStr">
+        <is>
+          <t>Harvest Crisis</t>
+        </is>
+      </c>
+      <c r="C290" s="75" t="inlineStr">
+        <is>
+          <t>HARVEST_VISIT_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D290" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SAVES THE HARVEST — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E290" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F290" s="76" t="inlineStr">
+        <is>
+          <t>HARVEST_VISIT_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G290" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H290" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I290" s="75" t="inlineStr"/>
+      <c r="J290" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K290" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L290" s="75" t="inlineStr"/>
+      <c r="M290" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N290" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of HARVEST_VISIT_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="30" customHeight="1">
+      <c r="A291" s="74" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B291" s="74" t="inlineStr">
+        <is>
+          <t>Election Arc</t>
+        </is>
+      </c>
+      <c r="C291" s="75" t="inlineStr">
+        <is>
+          <t>STUMP_SPEECH_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D291" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E291" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F291" s="76" t="inlineStr">
+        <is>
+          <t>STUMP_SPEECH_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G291" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H291" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I291" s="75" t="inlineStr"/>
+      <c r="J291" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K291" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L291" s="75" t="inlineStr"/>
+      <c r="M291" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N291" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of STUMP_SPEECH_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="8" customHeight="1">
+      <c r="A292" s="9" t="n"/>
+      <c r="B292" s="9" t="n"/>
+      <c r="C292" s="9" t="n"/>
+      <c r="D292" s="9" t="n"/>
+      <c r="E292" s="9" t="n"/>
+      <c r="F292" s="9" t="n"/>
+      <c r="G292" s="9" t="n"/>
+      <c r="H292" s="9" t="n"/>
+      <c r="I292" s="9" t="n"/>
+      <c r="J292" s="9" t="n"/>
+      <c r="K292" s="9" t="n"/>
+      <c r="L292" s="9" t="n"/>
+      <c r="M292" s="9" t="n"/>
+      <c r="N292" s="9" t="n"/>
+    </row>
+    <row r="293" ht="30" customHeight="1">
+      <c r="A293" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B293" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C293" s="75" t="inlineStr">
+        <is>
+          <t>VP_DOUBT_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D293" s="76" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QU... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E293" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F293" s="76" t="inlineStr">
+        <is>
+          <t>VP_DOUBT (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G293" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H293" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I293" s="75" t="inlineStr"/>
+      <c r="J293" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K293" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L293" s="75" t="inlineStr"/>
+      <c r="M293" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N293" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of VP_DOUBT. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B294" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C294" s="75" t="inlineStr">
+        <is>
+          <t>VP_BATTLEFIELD_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D294" s="76" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAM... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E294" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F294" s="76" t="inlineStr">
+        <is>
+          <t>VP_BATTLEFIELD (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G294" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H294" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I294" s="75" t="inlineStr"/>
+      <c r="J294" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K294" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L294" s="75" t="inlineStr"/>
+      <c r="M294" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N294" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of VP_BATTLEFIELD. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B295" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C295" s="75" t="inlineStr">
+        <is>
+          <t>VP_PRE_ELECTION_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D295" s="76" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E295" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F295" s="76" t="inlineStr">
+        <is>
+          <t>VP_PRE_ELECTION (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G295" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H295" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I295" s="75" t="inlineStr"/>
+      <c r="J295" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K295" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L295" s="75" t="inlineStr"/>
+      <c r="M295" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N295" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of VP_PRE_ELECTION. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B296" s="74" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C296" s="75" t="inlineStr">
+        <is>
+          <t>VP_LEGACY_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D296" s="76" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E296" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F296" s="76" t="inlineStr">
+        <is>
+          <t>VP_LEGACY (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G296" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H296" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I296" s="75" t="inlineStr"/>
+      <c r="J296" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K296" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L296" s="75" t="inlineStr"/>
+      <c r="M296" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N296" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of VP_LEGACY. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="8" customHeight="1">
+      <c r="A297" s="9" t="n"/>
+      <c r="B297" s="9" t="n"/>
+      <c r="C297" s="9" t="n"/>
+      <c r="D297" s="9" t="n"/>
+      <c r="E297" s="9" t="n"/>
+      <c r="F297" s="9" t="n"/>
+      <c r="G297" s="9" t="n"/>
+      <c r="H297" s="9" t="n"/>
+      <c r="I297" s="9" t="n"/>
+      <c r="J297" s="9" t="n"/>
+      <c r="K297" s="9" t="n"/>
+      <c r="L297" s="9" t="n"/>
+      <c r="M297" s="9" t="n"/>
+      <c r="N297" s="9" t="n"/>
+    </row>
+    <row r="298" ht="30" customHeight="1">
+      <c r="A298" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B298" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C298" s="75" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D298" s="76" t="inlineStr">
+        <is>
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E298" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F298" s="76" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G298" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H298" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I298" s="75" t="inlineStr"/>
+      <c r="J298" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K298" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L298" s="75" t="inlineStr"/>
+      <c r="M298" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N298" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="30" customHeight="1">
+      <c r="A299" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B299" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C299" s="75" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D299" s="76" t="inlineStr">
+        <is>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E299" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F299" s="76" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G299" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H299" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I299" s="75" t="inlineStr"/>
+      <c r="J299" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K299" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L299" s="75" t="inlineStr"/>
+      <c r="M299" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N299" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="30" customHeight="1">
+      <c r="A300" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B300" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C300" s="75" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D300" s="76" t="inlineStr">
+        <is>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E300" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F300" s="76" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G300" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H300" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I300" s="75" t="inlineStr"/>
+      <c r="J300" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K300" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L300" s="75" t="inlineStr"/>
+      <c r="M300" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N300" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="30" customHeight="1">
+      <c r="A301" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B301" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C301" s="75" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_LUCK_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D301" s="76" t="inlineStr">
+        <is>
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E301" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F301" s="76" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_LUCK (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G301" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H301" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I301" s="75" t="inlineStr"/>
+      <c r="J301" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K301" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L301" s="75" t="inlineStr"/>
+      <c r="M301" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N301" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="30" customHeight="1">
+      <c r="A302" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B302" s="74" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C302" s="75" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D302" s="76" t="inlineStr">
+        <is>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E302" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F302" s="76" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G302" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H302" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I302" s="75" t="inlineStr"/>
+      <c r="J302" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K302" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L302" s="75" t="inlineStr"/>
+      <c r="M302" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N302" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="30" customHeight="1">
+      <c r="A303" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B303" s="74" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C303" s="75" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D303" s="76" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E303" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F303" s="76" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G303" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H303" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I303" s="75" t="inlineStr"/>
+      <c r="J303" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K303" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L303" s="75" t="inlineStr"/>
+      <c r="M303" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N303" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="30" customHeight="1">
+      <c r="A304" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B304" s="74" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C304" s="75" t="inlineStr">
+        <is>
+          <t>PEACE_USA_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D304" s="76" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E304" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F304" s="76" t="inlineStr">
+        <is>
+          <t>PEACE_USA_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G304" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H304" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I304" s="75" t="inlineStr"/>
+      <c r="J304" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K304" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L304" s="75" t="inlineStr"/>
+      <c r="M304" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N304" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="8" customHeight="1">
+      <c r="A305" s="9" t="n"/>
+      <c r="B305" s="9" t="n"/>
+      <c r="C305" s="9" t="n"/>
+      <c r="D305" s="9" t="n"/>
+      <c r="E305" s="9" t="n"/>
+      <c r="F305" s="9" t="n"/>
+      <c r="G305" s="9" t="n"/>
+      <c r="H305" s="9" t="n"/>
+      <c r="I305" s="9" t="n"/>
+      <c r="J305" s="9" t="n"/>
+      <c r="K305" s="9" t="n"/>
+      <c r="L305" s="9" t="n"/>
+      <c r="M305" s="9" t="n"/>
+      <c r="N305" s="9" t="n"/>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B306" s="74" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C306" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D306" s="76" t="inlineStr">
+        <is>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E306" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F306" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G306" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H306" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I306" s="75" t="inlineStr"/>
+      <c r="J306" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K306" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L306" s="75" t="inlineStr"/>
+      <c r="M306" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N306" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="30" customHeight="1">
+      <c r="A307" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B307" s="74" t="inlineStr">
+        <is>
+          <t>Le Loup-Garou</t>
+        </is>
+      </c>
+      <c r="C307" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D307" s="76" t="inlineStr">
+        <is>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E307" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F307" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G307" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H307" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I307" s="75" t="inlineStr"/>
+      <c r="J307" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K307" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L307" s="75" t="inlineStr"/>
+      <c r="M307" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N307" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="30" customHeight="1">
+      <c r="A308" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B308" s="74" t="inlineStr">
+        <is>
+          <t>Les Feux Follets</t>
+        </is>
+      </c>
+      <c r="C308" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D308" s="76" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E308" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F308" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G308" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H308" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I308" s="75" t="inlineStr"/>
+      <c r="J308" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K308" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L308" s="75" t="inlineStr"/>
+      <c r="M308" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N308" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B309" s="74" t="inlineStr">
+        <is>
+          <t>Mishepeshu</t>
+        </is>
+      </c>
+      <c r="C309" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D309" s="76" t="inlineStr">
+        <is>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E309" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F309" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G309" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H309" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I309" s="75" t="inlineStr"/>
+      <c r="J309" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K309" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L309" s="75" t="inlineStr"/>
+      <c r="M309" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N309" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="30" customHeight="1">
+      <c r="A310" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B310" s="74" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C310" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D310" s="76" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E310" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F310" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G310" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H310" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I310" s="75" t="inlineStr"/>
+      <c r="J310" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K310" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L310" s="75" t="inlineStr"/>
+      <c r="M310" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N310" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="30" customHeight="1">
+      <c r="A311" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B311" s="74" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C311" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D311" s="76" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E311" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F311" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G311" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H311" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I311" s="75" t="inlineStr"/>
+      <c r="J311" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K311" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L311" s="75" t="inlineStr"/>
+      <c r="M311" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N311" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="30" customHeight="1">
+      <c r="A312" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B312" s="74" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C312" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D312" s="76" t="inlineStr">
+        <is>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E312" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F312" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G312" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H312" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I312" s="75" t="inlineStr"/>
+      <c r="J312" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K312" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L312" s="75" t="inlineStr"/>
+      <c r="M312" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N312" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="30" customHeight="1">
+      <c r="A313" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B313" s="74" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C313" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D313" s="76" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E313" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F313" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G313" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H313" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I313" s="75" t="inlineStr"/>
+      <c r="J313" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K313" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L313" s="75" t="inlineStr"/>
+      <c r="M313" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N313" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="8" customHeight="1">
+      <c r="A314" s="9" t="n"/>
+      <c r="B314" s="9" t="n"/>
+      <c r="C314" s="9" t="n"/>
+      <c r="D314" s="9" t="n"/>
+      <c r="E314" s="9" t="n"/>
+      <c r="F314" s="9" t="n"/>
+      <c r="G314" s="9" t="n"/>
+      <c r="H314" s="9" t="n"/>
+      <c r="I314" s="9" t="n"/>
+      <c r="J314" s="9" t="n"/>
+      <c r="K314" s="9" t="n"/>
+      <c r="L314" s="9" t="n"/>
+      <c r="M314" s="9" t="n"/>
+      <c r="N314" s="9" t="n"/>
+    </row>
+    <row r="315" ht="30" customHeight="1">
+      <c r="A315" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B315" s="74" t="inlineStr">
+        <is>
+          <t>Ambush</t>
+        </is>
+      </c>
+      <c r="C315" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_AMBUSH_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D315" s="76" t="inlineStr">
+        <is>
+          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E315" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F315" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_AMBUSH_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G315" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H315" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I315" s="75" t="inlineStr"/>
+      <c r="J315" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K315" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L315" s="75" t="inlineStr"/>
+      <c r="M315" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N315" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="30" customHeight="1">
+      <c r="A316" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B316" s="74" t="inlineStr">
+        <is>
+          <t>Dignitary Reception</t>
+        </is>
+      </c>
+      <c r="C316" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_DIGNITARY_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D316" s="76" t="inlineStr">
+        <is>
+          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E316" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F316" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G316" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H316" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I316" s="75" t="inlineStr"/>
+      <c r="J316" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K316" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L316" s="75" t="inlineStr"/>
+      <c r="M316" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N316" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="30" customHeight="1">
+      <c r="A317" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B317" s="74" t="inlineStr">
+        <is>
+          <t>Memorial Address</t>
+        </is>
+      </c>
+      <c r="C317" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_MEMORIAL_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D317" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E317" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F317" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G317" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H317" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I317" s="75" t="inlineStr"/>
+      <c r="J317" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K317" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L317" s="75" t="inlineStr"/>
+      <c r="M317" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N317" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="30" customHeight="1">
+      <c r="A318" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B318" s="74" t="inlineStr">
+        <is>
+          <t>Field Hospital</t>
+        </is>
+      </c>
+      <c r="C318" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_WOUNDED_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D318" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E318" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F318" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_WOUNDED_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G318" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H318" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I318" s="75" t="inlineStr"/>
+      <c r="J318" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K318" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L318" s="75" t="inlineStr"/>
+      <c r="M318" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N318" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B319" s="74" t="inlineStr">
+        <is>
+          <t>Forge Inspection</t>
+        </is>
+      </c>
+      <c r="C319" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_FORGE_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D319" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E319" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F319" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_FORGE_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G319" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H319" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I319" s="75" t="inlineStr"/>
+      <c r="J319" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K319" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L319" s="75" t="inlineStr"/>
+      <c r="M319" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N319" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="30" customHeight="1">
+      <c r="A320" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B320" s="74" t="inlineStr">
+        <is>
+          <t>Culper Ring</t>
+        </is>
+      </c>
+      <c r="C320" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_CULPER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D320" s="76" t="inlineStr">
+        <is>
+          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E320" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F320" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_CULPER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G320" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H320" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I320" s="75" t="inlineStr"/>
+      <c r="J320" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K320" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L320" s="75" t="inlineStr"/>
+      <c r="M320" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N320" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="30" customHeight="1">
+      <c r="A321" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B321" s="74" t="inlineStr">
+        <is>
+          <t>Alliance Council</t>
+        </is>
+      </c>
+      <c r="C321" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_ALLIANCE_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D321" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E321" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F321" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G321" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H321" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I321" s="75" t="inlineStr"/>
+      <c r="J321" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K321" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L321" s="75" t="inlineStr"/>
+      <c r="M321" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N321" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="30" customHeight="1">
+      <c r="A322" s="74" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B322" s="74" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="C322" s="75" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D322" s="76" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E322" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F322" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G322" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H322" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I322" s="75" t="inlineStr"/>
+      <c r="J322" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K322" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L322" s="75" t="inlineStr"/>
+      <c r="M322" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N322" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="8" customHeight="1">
+      <c r="A323" s="9" t="n"/>
+      <c r="B323" s="9" t="n"/>
+      <c r="C323" s="9" t="n"/>
+      <c r="D323" s="9" t="n"/>
+      <c r="E323" s="9" t="n"/>
+      <c r="F323" s="9" t="n"/>
+      <c r="G323" s="9" t="n"/>
+      <c r="H323" s="9" t="n"/>
+      <c r="I323" s="9" t="n"/>
+      <c r="J323" s="9" t="n"/>
+      <c r="K323" s="9" t="n"/>
+      <c r="L323" s="9" t="n"/>
+      <c r="M323" s="9" t="n"/>
+      <c r="N323" s="9" t="n"/>
+    </row>
+    <row r="324" ht="30" customHeight="1">
+      <c r="A324" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B324" s="74" t="inlineStr">
+        <is>
+          <t>Mothman</t>
+        </is>
+      </c>
+      <c r="C324" s="75" t="inlineStr">
+        <is>
+          <t>PROT_01_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D324" s="76" t="inlineStr">
+        <is>
+          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E324" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F324" s="76" t="inlineStr">
+        <is>
+          <t>PROT_01_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G324" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H324" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I324" s="75" t="inlineStr"/>
+      <c r="J324" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K324" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L324" s="75" t="inlineStr"/>
+      <c r="M324" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N324" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B325" s="74" t="inlineStr">
+        <is>
+          <t>Jersey Devil</t>
+        </is>
+      </c>
+      <c r="C325" s="75" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D325" s="76" t="inlineStr">
+        <is>
+          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E325" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F325" s="76" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G325" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H325" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I325" s="75" t="inlineStr"/>
+      <c r="J325" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K325" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L325" s="75" t="inlineStr"/>
+      <c r="M325" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N325" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="30" customHeight="1">
+      <c r="A326" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B326" s="74" t="inlineStr">
+        <is>
+          <t>Bigfoot</t>
+        </is>
+      </c>
+      <c r="C326" s="75" t="inlineStr">
+        <is>
+          <t>PROT_03_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D326" s="76" t="inlineStr">
+        <is>
+          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E326" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F326" s="76" t="inlineStr">
+        <is>
+          <t>PROT_03_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G326" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H326" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I326" s="75" t="inlineStr"/>
+      <c r="J326" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K326" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L326" s="75" t="inlineStr"/>
+      <c r="M326" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N326" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="30" customHeight="1">
+      <c r="A327" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B327" s="74" t="inlineStr">
+        <is>
+          <t>Thunderbird</t>
+        </is>
+      </c>
+      <c r="C327" s="75" t="inlineStr">
+        <is>
+          <t>PROT_04_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D327" s="76" t="inlineStr">
+        <is>
+          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E327" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F327" s="76" t="inlineStr">
+        <is>
+          <t>PROT_04_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G327" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H327" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I327" s="75" t="inlineStr"/>
+      <c r="J327" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K327" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L327" s="75" t="inlineStr"/>
+      <c r="M327" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N327" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="30" customHeight="1">
+      <c r="A328" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B328" s="74" t="inlineStr">
+        <is>
+          <t>Headless Horseman</t>
+        </is>
+      </c>
+      <c r="C328" s="75" t="inlineStr">
+        <is>
+          <t>PROT_05_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D328" s="76" t="inlineStr">
+        <is>
+          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E328" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F328" s="76" t="inlineStr">
+        <is>
+          <t>PROT_05_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G328" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H328" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I328" s="75" t="inlineStr"/>
+      <c r="J328" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K328" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L328" s="75" t="inlineStr"/>
+      <c r="M328" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N328" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="30" customHeight="1">
+      <c r="A329" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B329" s="74" t="inlineStr">
+        <is>
+          <t>Chessie</t>
+        </is>
+      </c>
+      <c r="C329" s="75" t="inlineStr">
+        <is>
+          <t>PROT_06_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D329" s="76" t="inlineStr">
+        <is>
+          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E329" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F329" s="76" t="inlineStr">
+        <is>
+          <t>PROT_06_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G329" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H329" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I329" s="75" t="inlineStr"/>
+      <c r="J329" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K329" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L329" s="75" t="inlineStr"/>
+      <c r="M329" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N329" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="A330" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B330" s="74" t="inlineStr">
+        <is>
+          <t>Bell Witch</t>
+        </is>
+      </c>
+      <c r="C330" s="75" t="inlineStr">
+        <is>
+          <t>PROT_07_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D330" s="76" t="inlineStr">
+        <is>
+          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E330" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F330" s="76" t="inlineStr">
+        <is>
+          <t>PROT_07_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G330" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H330" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I330" s="75" t="inlineStr"/>
+      <c r="J330" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K330" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L330" s="75" t="inlineStr"/>
+      <c r="M330" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N330" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="30" customHeight="1">
+      <c r="A331" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B331" s="74" t="inlineStr">
+        <is>
+          <t>Old Ironsides</t>
+        </is>
+      </c>
+      <c r="C331" s="75" t="inlineStr">
+        <is>
+          <t>PROT_08_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D331" s="76" t="inlineStr">
+        <is>
+          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E331" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F331" s="76" t="inlineStr">
+        <is>
+          <t>PROT_08_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G331" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H331" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I331" s="75" t="inlineStr"/>
+      <c r="J331" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K331" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L331" s="75" t="inlineStr"/>
+      <c r="M331" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N331" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="A332" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B332" s="74" t="inlineStr">
+        <is>
+          <t>Valley Forge Guardian</t>
+        </is>
+      </c>
+      <c r="C332" s="75" t="inlineStr">
+        <is>
+          <t>PROT_09_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D332" s="76" t="inlineStr">
+        <is>
+          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E332" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F332" s="76" t="inlineStr">
+        <is>
+          <t>PROT_09_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G332" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H332" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I332" s="75" t="inlineStr"/>
+      <c r="J332" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K332" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L332" s="75" t="inlineStr"/>
+      <c r="M332" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N332" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="30" customHeight="1">
+      <c r="A333" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B333" s="74" t="inlineStr">
+        <is>
+          <t>Snallygaster</t>
+        </is>
+      </c>
+      <c r="C333" s="75" t="inlineStr">
+        <is>
+          <t>PROT_10_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D333" s="76" t="inlineStr">
+        <is>
+          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E333" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F333" s="76" t="inlineStr">
+        <is>
+          <t>PROT_10_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G333" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H333" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I333" s="75" t="inlineStr"/>
+      <c r="J333" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K333" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L333" s="75" t="inlineStr"/>
+      <c r="M333" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N333" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="30" customHeight="1">
+      <c r="A334" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B334" s="74" t="inlineStr">
+        <is>
+          <t>Paul Revere</t>
+        </is>
+      </c>
+      <c r="C334" s="75" t="inlineStr">
+        <is>
+          <t>PROT_11_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D334" s="76" t="inlineStr">
+        <is>
+          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E334" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F334" s="76" t="inlineStr">
+        <is>
+          <t>PROT_11_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G334" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H334" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I334" s="75" t="inlineStr"/>
+      <c r="J334" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K334" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L334" s="75" t="inlineStr"/>
+      <c r="M334" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N334" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="30" customHeight="1">
+      <c r="A335" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B335" s="74" t="inlineStr">
+        <is>
+          <t>Liberty Bell</t>
+        </is>
+      </c>
+      <c r="C335" s="75" t="inlineStr">
+        <is>
+          <t>PROT_12_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D335" s="76" t="inlineStr">
+        <is>
+          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E335" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F335" s="76" t="inlineStr">
+        <is>
+          <t>PROT_12_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G335" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H335" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I335" s="75" t="inlineStr"/>
+      <c r="J335" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K335" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L335" s="75" t="inlineStr"/>
+      <c r="M335" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N335" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="30" customHeight="1">
+      <c r="A336" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B336" s="74" t="inlineStr">
+        <is>
+          <t>Green Mountain Ghost</t>
+        </is>
+      </c>
+      <c r="C336" s="75" t="inlineStr">
+        <is>
+          <t>PROT_13_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D336" s="76" t="inlineStr">
+        <is>
+          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E336" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F336" s="76" t="inlineStr">
+        <is>
+          <t>PROT_13_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G336" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H336" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I336" s="75" t="inlineStr"/>
+      <c r="J336" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K336" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L336" s="75" t="inlineStr"/>
+      <c r="M336" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N336" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="30" customHeight="1">
+      <c r="A337" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B337" s="74" t="inlineStr">
+        <is>
+          <t>Mount Rushmore</t>
+        </is>
+      </c>
+      <c r="C337" s="75" t="inlineStr">
+        <is>
+          <t>PROT_14_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D337" s="76" t="inlineStr">
+        <is>
+          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E337" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F337" s="76" t="inlineStr">
+        <is>
+          <t>PROT_14_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G337" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H337" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I337" s="75" t="inlineStr"/>
+      <c r="J337" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K337" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L337" s="75" t="inlineStr"/>
+      <c r="M337" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N337" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="30" customHeight="1">
+      <c r="A338" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B338" s="74" t="inlineStr">
+        <is>
+          <t>Skunk Ape</t>
+        </is>
+      </c>
+      <c r="C338" s="75" t="inlineStr">
+        <is>
+          <t>PROT_15_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D338" s="76" t="inlineStr">
+        <is>
+          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E338" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F338" s="76" t="inlineStr">
+        <is>
+          <t>PROT_15_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G338" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H338" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I338" s="75" t="inlineStr"/>
+      <c r="J338" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K338" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L338" s="75" t="inlineStr"/>
+      <c r="M338" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N338" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="30" customHeight="1">
+      <c r="A339" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B339" s="74" t="inlineStr">
+        <is>
+          <t>Minuteman</t>
+        </is>
+      </c>
+      <c r="C339" s="75" t="inlineStr">
+        <is>
+          <t>PROT_16_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D339" s="76" t="inlineStr">
+        <is>
+          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E339" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F339" s="76" t="inlineStr">
+        <is>
+          <t>PROT_16_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G339" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H339" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I339" s="75" t="inlineStr"/>
+      <c r="J339" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K339" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L339" s="75" t="inlineStr"/>
+      <c r="M339" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N339" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="30" customHeight="1">
+      <c r="A340" s="74" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B340" s="74" t="inlineStr">
+        <is>
+          <t>Lincoln's Ghost</t>
+        </is>
+      </c>
+      <c r="C340" s="75" t="inlineStr">
+        <is>
+          <t>PROT_17_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D340" s="76" t="inlineStr">
+        <is>
+          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E340" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F340" s="76" t="inlineStr">
+        <is>
+          <t>PROT_17_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G340" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H340" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I340" s="75" t="inlineStr"/>
+      <c r="J340" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K340" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L340" s="75" t="inlineStr"/>
+      <c r="M340" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N340" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="8" customHeight="1">
+      <c r="A341" s="9" t="n"/>
+      <c r="B341" s="9" t="n"/>
+      <c r="C341" s="9" t="n"/>
+      <c r="D341" s="9" t="n"/>
+      <c r="E341" s="9" t="n"/>
+      <c r="F341" s="9" t="n"/>
+      <c r="G341" s="9" t="n"/>
+      <c r="H341" s="9" t="n"/>
+      <c r="I341" s="9" t="n"/>
+      <c r="J341" s="9" t="n"/>
+      <c r="K341" s="9" t="n"/>
+      <c r="L341" s="9" t="n"/>
+      <c r="M341" s="9" t="n"/>
+      <c r="N341" s="9" t="n"/>
+    </row>
+    <row r="342" ht="30" customHeight="1">
+      <c r="A342" s="74" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B342" s="74" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="C342" s="75" t="inlineStr">
+        <is>
+          <t>WH_SECRET_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D342" s="76" t="inlineStr">
+        <is>
+          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E342" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F342" s="76" t="inlineStr">
+        <is>
+          <t>WH_SECRET_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G342" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H342" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I342" s="75" t="inlineStr"/>
+      <c r="J342" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K342" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L342" s="75" t="inlineStr"/>
+      <c r="M342" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N342" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="30" customHeight="1">
+      <c r="A343" s="74" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B343" s="74" t="inlineStr">
+        <is>
+          <t>Month 7</t>
+        </is>
+      </c>
+      <c r="C343" s="75" t="inlineStr">
+        <is>
+          <t>WH_SECRET_07_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D343" s="76" t="inlineStr">
+        <is>
+          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E343" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F343" s="76" t="inlineStr">
+        <is>
+          <t>WH_SECRET_07 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G343" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H343" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I343" s="75" t="inlineStr"/>
+      <c r="J343" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K343" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L343" s="75" t="inlineStr"/>
+      <c r="M343" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N343" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="30" customHeight="1">
+      <c r="A344" s="74" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B344" s="74" t="inlineStr">
+        <is>
+          <t>Month 10</t>
+        </is>
+      </c>
+      <c r="C344" s="75" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D344" s="76" t="inlineStr">
+        <is>
+          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E344" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F344" s="76" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G344" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H344" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I344" s="75" t="inlineStr"/>
+      <c r="J344" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K344" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L344" s="75" t="inlineStr"/>
+      <c r="M344" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N344" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="30" customHeight="1">
+      <c r="A345" s="74" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B345" s="74" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="C345" s="75" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D345" s="76" t="inlineStr">
+        <is>
+          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E345" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F345" s="76" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G345" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H345" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I345" s="75" t="inlineStr"/>
+      <c r="J345" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K345" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L345" s="75" t="inlineStr"/>
+      <c r="M345" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N345" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_12. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="20" customHeight="1">
+      <c r="A347" s="79" t="inlineStr">
         <is>
           <t>Total events in spreadsheet</t>
         </is>
       </c>
-      <c r="B284" s="80" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="285" ht="20" customHeight="1">
-      <c r="A285" s="79" t="inlineStr">
+      <c r="B347" s="80" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="348" ht="20" customHeight="1">
+      <c r="A348" s="79" t="inlineStr">
         <is>
           <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
-      <c r="B285" s="80" t="n">
+      <c r="B348" s="80" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="286" ht="20" customHeight="1">
-      <c r="A286" s="79" t="inlineStr">
+    <row r="349" ht="20" customHeight="1">
+      <c r="A349" s="79" t="inlineStr">
         <is>
           <t>IDEA (not yet implemented)</t>
         </is>
       </c>
-      <c r="B286" s="80" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="287" ht="20" customHeight="1">
-      <c r="A287" s="79" t="inlineStr">
+      <c r="B349" s="80" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="350" ht="20" customHeight="1">
+      <c r="A350" s="79" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B287" s="80" t="n">
+      <c r="B350" s="80" t="n">
         <v>55</v>
       </c>
     </row>
@@ -18879,7 +22431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21606,43 +25158,1019 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="79" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B43" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C43" s="75" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D43" s="76" t="inlineStr">
+        <is>
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E43" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G43" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I43" s="75" t="inlineStr"/>
+      <c r="J43" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L43" s="75" t="inlineStr"/>
+      <c r="M43" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N43" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B44" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C44" s="75" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D44" s="76" t="inlineStr">
+        <is>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E44" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G44" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I44" s="75" t="inlineStr"/>
+      <c r="J44" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L44" s="75" t="inlineStr"/>
+      <c r="M44" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N44" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B45" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C45" s="75" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D45" s="76" t="inlineStr">
+        <is>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E45" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G45" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I45" s="75" t="inlineStr"/>
+      <c r="J45" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L45" s="75" t="inlineStr"/>
+      <c r="M45" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N45" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B46" s="74" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C46" s="75" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_LUCK_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D46" s="76" t="inlineStr">
+        <is>
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E46" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F46" s="76" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_LUCK (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G46" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I46" s="75" t="inlineStr"/>
+      <c r="J46" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L46" s="75" t="inlineStr"/>
+      <c r="M46" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N46" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B47" s="74" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C47" s="75" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D47" s="76" t="inlineStr">
+        <is>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E47" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F47" s="76" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G47" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I47" s="75" t="inlineStr"/>
+      <c r="J47" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L47" s="75" t="inlineStr"/>
+      <c r="M47" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N47" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B48" s="74" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C48" s="75" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D48" s="76" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E48" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F48" s="76" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G48" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I48" s="75" t="inlineStr"/>
+      <c r="J48" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L48" s="75" t="inlineStr"/>
+      <c r="M48" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B49" s="74" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C49" s="75" t="inlineStr">
+        <is>
+          <t>PEACE_USA_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D49" s="76" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E49" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F49" s="76" t="inlineStr">
+        <is>
+          <t>PEACE_USA_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G49" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I49" s="75" t="inlineStr"/>
+      <c r="J49" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L49" s="75" t="inlineStr"/>
+      <c r="M49" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N49" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B51" s="74" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C51" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D51" s="76" t="inlineStr">
+        <is>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E51" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F51" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G51" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I51" s="75" t="inlineStr"/>
+      <c r="J51" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L51" s="75" t="inlineStr"/>
+      <c r="M51" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N51" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B52" s="74" t="inlineStr">
+        <is>
+          <t>Le Loup-Garou</t>
+        </is>
+      </c>
+      <c r="C52" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D52" s="76" t="inlineStr">
+        <is>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E52" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F52" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G52" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I52" s="75" t="inlineStr"/>
+      <c r="J52" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L52" s="75" t="inlineStr"/>
+      <c r="M52" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N52" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B53" s="74" t="inlineStr">
+        <is>
+          <t>Les Feux Follets</t>
+        </is>
+      </c>
+      <c r="C53" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D53" s="76" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E53" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F53" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G53" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I53" s="75" t="inlineStr"/>
+      <c r="J53" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L53" s="75" t="inlineStr"/>
+      <c r="M53" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N53" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B54" s="74" t="inlineStr">
+        <is>
+          <t>Mishepeshu</t>
+        </is>
+      </c>
+      <c r="C54" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D54" s="76" t="inlineStr">
+        <is>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E54" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F54" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G54" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I54" s="75" t="inlineStr"/>
+      <c r="J54" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L54" s="75" t="inlineStr"/>
+      <c r="M54" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N54" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B55" s="74" t="inlineStr">
+        <is>
+          <t>La Corriveau</t>
+        </is>
+      </c>
+      <c r="C55" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D55" s="76" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E55" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F55" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G55" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I55" s="75" t="inlineStr"/>
+      <c r="J55" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L55" s="75" t="inlineStr"/>
+      <c r="M55" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B56" s="74" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C56" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D56" s="76" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E56" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F56" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G56" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I56" s="75" t="inlineStr"/>
+      <c r="J56" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L56" s="75" t="inlineStr"/>
+      <c r="M56" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N56" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B57" s="74" t="inlineStr">
+        <is>
+          <t>La Chasse-Galerie</t>
+        </is>
+      </c>
+      <c r="C57" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D57" s="76" t="inlineStr">
+        <is>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E57" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F57" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G57" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I57" s="75" t="inlineStr"/>
+      <c r="J57" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L57" s="75" t="inlineStr"/>
+      <c r="M57" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N57" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="74" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B58" s="74" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C58" s="75" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D58" s="76" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E58" s="78" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F58" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G58" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="77" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I58" s="75" t="inlineStr"/>
+      <c r="J58" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K58" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L58" s="75" t="inlineStr"/>
+      <c r="M58" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N58" s="76" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="79" t="inlineStr">
         <is>
           <t>Canadian events total</t>
         </is>
       </c>
-      <c r="B44" s="80" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="79" t="inlineStr">
+      <c r="B60" s="80" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="79" t="inlineStr">
         <is>
           <t>Canada (Alliance arc)</t>
         </is>
       </c>
-      <c r="B45" s="80" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="79" t="inlineStr">
+      <c r="B61" s="80" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="79" t="inlineStr">
         <is>
           <t>CA Protector (Jessica's creatures)</t>
         </is>
       </c>
-      <c r="B46" s="80" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="79" t="inlineStr">
+      <c r="B62" s="80" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="79" t="inlineStr">
         <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B47" s="80" t="n">
+      <c r="B63" s="80" t="n">
         <v>12</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1140,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N350"/>
+  <dimension ref="A1:N351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D135" s="55" t="inlineStr">
         <is>
-          <t>PRESIDENT PENOIT'S CONDITIONS: MARK PENOIT PUTS IT IN WRITING</t>
+          <t>PRESIDENT PENOIT'S CONDITIONS: MARC PENOIT PUTS IT IN WRITING</t>
         </is>
       </c>
       <c r="E135" s="28" t="inlineStr">
@@ -19963,85 +19963,85 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="8" customHeight="1">
-      <c r="A305" s="9" t="n"/>
-      <c r="B305" s="9" t="n"/>
-      <c r="C305" s="9" t="n"/>
-      <c r="D305" s="9" t="n"/>
-      <c r="E305" s="9" t="n"/>
-      <c r="F305" s="9" t="n"/>
-      <c r="G305" s="9" t="n"/>
-      <c r="H305" s="9" t="n"/>
-      <c r="I305" s="9" t="n"/>
-      <c r="J305" s="9" t="n"/>
-      <c r="K305" s="9" t="n"/>
-      <c r="L305" s="9" t="n"/>
-      <c r="M305" s="9" t="n"/>
-      <c r="N305" s="9" t="n"/>
-    </row>
-    <row r="306" ht="30" customHeight="1">
-      <c r="A306" s="75" t="inlineStr">
-        <is>
-          <t>CA Protector</t>
-        </is>
-      </c>
-      <c r="B306" s="75" t="inlineStr">
-        <is>
-          <t>Le Wendigo</t>
-        </is>
-      </c>
-      <c r="C306" s="76" t="inlineStr">
-        <is>
-          <t>CA_PROT_01_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D306" s="77" t="inlineStr">
-        <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E306" s="79" t="inlineStr">
+    <row r="305" ht="30" customHeight="1">
+      <c r="A305" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B305" s="53" t="inlineStr">
+        <is>
+          <t>PM Arc</t>
+        </is>
+      </c>
+      <c r="C305" s="54" t="inlineStr">
+        <is>
+          <t>CA_PM_LEGACY_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D305" s="55" t="inlineStr">
+        <is>
+          <t>MARC PENOIT'S FINAL ASSESSMENT — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E305" s="56" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F306" s="77" t="inlineStr">
-        <is>
-          <t>CA_PROT_01_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G306" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H306" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I306" s="76" t="inlineStr"/>
-      <c r="J306" s="80" t="inlineStr">
+      <c r="F305" s="55" t="inlineStr">
+        <is>
+          <t>CA_PM_LEGACY (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G305" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H305" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I305" s="54" t="inlineStr"/>
+      <c r="J305" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K306" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L306" s="76" t="inlineStr"/>
-      <c r="M306" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N306" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+      <c r="K305" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L305" s="54" t="inlineStr"/>
+      <c r="M305" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N305" s="55" t="inlineStr">
+        <is>
+          <t>By morning: Penoit at the desk before light, writing page forty-one. Emotional resolution — he was wrong about what this would feel like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="8" customHeight="1">
+      <c r="A306" s="9" t="n"/>
+      <c r="B306" s="9" t="n"/>
+      <c r="C306" s="9" t="n"/>
+      <c r="D306" s="9" t="n"/>
+      <c r="E306" s="9" t="n"/>
+      <c r="F306" s="9" t="n"/>
+      <c r="G306" s="9" t="n"/>
+      <c r="H306" s="9" t="n"/>
+      <c r="I306" s="9" t="n"/>
+      <c r="J306" s="9" t="n"/>
+      <c r="K306" s="9" t="n"/>
+      <c r="L306" s="9" t="n"/>
+      <c r="M306" s="9" t="n"/>
+      <c r="N306" s="9" t="n"/>
     </row>
     <row r="307" ht="30" customHeight="1">
       <c r="A307" s="75" t="inlineStr">
@@ -20051,17 +20051,17 @@
       </c>
       <c r="B307" s="75" t="inlineStr">
         <is>
-          <t>Le Loup-Garou</t>
+          <t>Le Wendigo</t>
         </is>
       </c>
       <c r="C307" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE_INTIMATE</t>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D307" s="77" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
         </is>
       </c>
       <c r="E307" s="79" t="inlineStr">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="F307" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE (intimate choice)</t>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G307" s="77" t="inlineStr">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="N307" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20115,17 +20115,17 @@
       </c>
       <c r="B308" s="75" t="inlineStr">
         <is>
-          <t>Les Feux Follets</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C308" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE_INTIMATE</t>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D308" s="77" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
       <c r="E308" s="79" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="F308" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE (intimate choice)</t>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G308" s="77" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="N308" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20179,17 +20179,17 @@
       </c>
       <c r="B309" s="75" t="inlineStr">
         <is>
-          <t>Mishepeshu</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C309" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE_INTIMATE</t>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D309" s="77" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
       <c r="E309" s="79" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="F309" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE (intimate choice)</t>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G309" s="77" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="N309" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20243,17 +20243,17 @@
       </c>
       <c r="B310" s="75" t="inlineStr">
         <is>
-          <t>La Corriveau</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C310" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE_INTIMATE</t>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D310" s="77" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E310" s="79" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="F310" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE (intimate choice)</t>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G310" s="77" t="inlineStr">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="N310" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20307,17 +20307,17 @@
       </c>
       <c r="B311" s="75" t="inlineStr">
         <is>
-          <t>Le Carcajou</t>
+          <t>La Corriveau</t>
         </is>
       </c>
       <c r="C311" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE_INTIMATE</t>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D311" s="77" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
       <c r="E311" s="79" t="inlineStr">
@@ -20327,7 +20327,7 @@
       </c>
       <c r="F311" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE (intimate choice)</t>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G311" s="77" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="N311" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20371,17 +20371,17 @@
       </c>
       <c r="B312" s="75" t="inlineStr">
         <is>
-          <t>La Chasse-Galerie</t>
+          <t>Le Carcajou</t>
         </is>
       </c>
       <c r="C312" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE_INTIMATE</t>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D312" s="77" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
       <c r="E312" s="79" t="inlineStr">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="F312" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE (intimate choice)</t>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G312" s="77" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="N312" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20435,17 +20435,17 @@
       </c>
       <c r="B313" s="75" t="inlineStr">
         <is>
-          <t>Le Gougou</t>
+          <t>La Chasse-Galerie</t>
         </is>
       </c>
       <c r="C313" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE_INTIMATE</t>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D313" s="77" t="inlineStr">
         <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
       <c r="E313" s="79" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="F313" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE (intimate choice)</t>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G313" s="77" t="inlineStr">
@@ -20487,89 +20487,89 @@
       </c>
       <c r="N313" s="77" t="inlineStr">
         <is>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="75" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B314" s="75" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C314" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D314" s="77" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E314" s="79" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F314" s="77" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G314" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H314" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I314" s="76" t="inlineStr"/>
+      <c r="J314" s="80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K314" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L314" s="76" t="inlineStr"/>
+      <c r="M314" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N314" s="77" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
-    <row r="314" ht="8" customHeight="1">
-      <c r="A314" s="9" t="n"/>
-      <c r="B314" s="9" t="n"/>
-      <c r="C314" s="9" t="n"/>
-      <c r="D314" s="9" t="n"/>
-      <c r="E314" s="9" t="n"/>
-      <c r="F314" s="9" t="n"/>
-      <c r="G314" s="9" t="n"/>
-      <c r="H314" s="9" t="n"/>
-      <c r="I314" s="9" t="n"/>
-      <c r="J314" s="9" t="n"/>
-      <c r="K314" s="9" t="n"/>
-      <c r="L314" s="9" t="n"/>
-      <c r="M314" s="9" t="n"/>
-      <c r="N314" s="9" t="n"/>
-    </row>
-    <row r="315" ht="30" customHeight="1">
-      <c r="A315" s="75" t="inlineStr">
-        <is>
-          <t>Ualani</t>
-        </is>
-      </c>
-      <c r="B315" s="75" t="inlineStr">
-        <is>
-          <t>Ambush</t>
-        </is>
-      </c>
-      <c r="C315" s="76" t="inlineStr">
-        <is>
-          <t>UALANI_AMBUSH_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D315" s="77" t="inlineStr">
-        <is>
-          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E315" s="79" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F315" s="77" t="inlineStr">
-        <is>
-          <t>UALANI_AMBUSH_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G315" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H315" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I315" s="76" t="inlineStr"/>
-      <c r="J315" s="80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K315" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L315" s="76" t="inlineStr"/>
-      <c r="M315" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N315" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+    <row r="315" ht="8" customHeight="1">
+      <c r="A315" s="9" t="n"/>
+      <c r="B315" s="9" t="n"/>
+      <c r="C315" s="9" t="n"/>
+      <c r="D315" s="9" t="n"/>
+      <c r="E315" s="9" t="n"/>
+      <c r="F315" s="9" t="n"/>
+      <c r="G315" s="9" t="n"/>
+      <c r="H315" s="9" t="n"/>
+      <c r="I315" s="9" t="n"/>
+      <c r="J315" s="9" t="n"/>
+      <c r="K315" s="9" t="n"/>
+      <c r="L315" s="9" t="n"/>
+      <c r="M315" s="9" t="n"/>
+      <c r="N315" s="9" t="n"/>
     </row>
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="75" t="inlineStr">
@@ -20579,17 +20579,17 @@
       </c>
       <c r="B316" s="75" t="inlineStr">
         <is>
-          <t>Dignitary Reception</t>
+          <t>Ambush</t>
         </is>
       </c>
       <c r="C316" s="76" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01_INTIMATE</t>
+          <t>UALANI_AMBUSH_01_INTIMATE</t>
         </is>
       </c>
       <c r="D316" s="77" t="inlineStr">
         <is>
-          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
+          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
         </is>
       </c>
       <c r="E316" s="79" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="F316" s="77" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
+          <t>UALANI_AMBUSH_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G316" s="77" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="N316" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20643,17 +20643,17 @@
       </c>
       <c r="B317" s="75" t="inlineStr">
         <is>
-          <t>Memorial Address</t>
+          <t>Dignitary Reception</t>
         </is>
       </c>
       <c r="C317" s="76" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01_INTIMATE</t>
+          <t>UALANI_DIGNITARY_01_INTIMATE</t>
         </is>
       </c>
       <c r="D317" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
+          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
         </is>
       </c>
       <c r="E317" s="79" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F317" s="77" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
+          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G317" s="77" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="N317" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20707,17 +20707,17 @@
       </c>
       <c r="B318" s="75" t="inlineStr">
         <is>
-          <t>Field Hospital</t>
+          <t>Memorial Address</t>
         </is>
       </c>
       <c r="C318" s="76" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01_INTIMATE</t>
+          <t>UALANI_MEMORIAL_01_INTIMATE</t>
         </is>
       </c>
       <c r="D318" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E318" s="79" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="F318" s="77" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01 (intimate choice)</t>
+          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G318" s="77" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="N318" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20771,17 +20771,17 @@
       </c>
       <c r="B319" s="75" t="inlineStr">
         <is>
-          <t>Forge Inspection</t>
+          <t>Field Hospital</t>
         </is>
       </c>
       <c r="C319" s="76" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01_INTIMATE</t>
+          <t>UALANI_WOUNDED_01_INTIMATE</t>
         </is>
       </c>
       <c r="D319" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
       <c r="E319" s="79" t="inlineStr">
@@ -20791,7 +20791,7 @@
       </c>
       <c r="F319" s="77" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01 (intimate choice)</t>
+          <t>UALANI_WOUNDED_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G319" s="77" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="N319" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20835,17 +20835,17 @@
       </c>
       <c r="B320" s="75" t="inlineStr">
         <is>
-          <t>Culper Ring</t>
+          <t>Forge Inspection</t>
         </is>
       </c>
       <c r="C320" s="76" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01_INTIMATE</t>
+          <t>UALANI_FORGE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D320" s="77" t="inlineStr">
         <is>
-          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
         </is>
       </c>
       <c r="E320" s="79" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="F320" s="77" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01 (intimate choice)</t>
+          <t>UALANI_FORGE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G320" s="77" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="N320" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20899,17 +20899,17 @@
       </c>
       <c r="B321" s="75" t="inlineStr">
         <is>
-          <t>Alliance Council</t>
+          <t>Culper Ring</t>
         </is>
       </c>
       <c r="C321" s="76" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01_INTIMATE</t>
+          <t>UALANI_CULPER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D321" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
+          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
         </is>
       </c>
       <c r="E321" s="79" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="F321" s="77" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
+          <t>UALANI_CULPER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G321" s="77" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="N321" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20963,17 +20963,17 @@
       </c>
       <c r="B322" s="75" t="inlineStr">
         <is>
-          <t>Frontier</t>
+          <t>Alliance Council</t>
         </is>
       </c>
       <c r="C322" s="76" t="inlineStr">
         <is>
-          <t>UALANI_FRONTIER_01_INTIMATE</t>
+          <t>UALANI_ALLIANCE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D322" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
         </is>
       </c>
       <c r="E322" s="79" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="F322" s="77" t="inlineStr">
         <is>
-          <t>UALANI_FRONTIER_01 (intimate choice)</t>
+          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G322" s="77" t="inlineStr">
@@ -21015,89 +21015,89 @@
       </c>
       <c r="N322" s="77" t="inlineStr">
         <is>
+          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="30" customHeight="1">
+      <c r="A323" s="75" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B323" s="75" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="C323" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D323" s="77" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E323" s="79" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F323" s="77" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G323" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H323" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I323" s="76" t="inlineStr"/>
+      <c r="J323" s="80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K323" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L323" s="76" t="inlineStr"/>
+      <c r="M323" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N323" s="77" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
-    <row r="323" ht="8" customHeight="1">
-      <c r="A323" s="9" t="n"/>
-      <c r="B323" s="9" t="n"/>
-      <c r="C323" s="9" t="n"/>
-      <c r="D323" s="9" t="n"/>
-      <c r="E323" s="9" t="n"/>
-      <c r="F323" s="9" t="n"/>
-      <c r="G323" s="9" t="n"/>
-      <c r="H323" s="9" t="n"/>
-      <c r="I323" s="9" t="n"/>
-      <c r="J323" s="9" t="n"/>
-      <c r="K323" s="9" t="n"/>
-      <c r="L323" s="9" t="n"/>
-      <c r="M323" s="9" t="n"/>
-      <c r="N323" s="9" t="n"/>
-    </row>
-    <row r="324" ht="30" customHeight="1">
-      <c r="A324" s="75" t="inlineStr">
-        <is>
-          <t>Protector</t>
-        </is>
-      </c>
-      <c r="B324" s="75" t="inlineStr">
-        <is>
-          <t>Mothman</t>
-        </is>
-      </c>
-      <c r="C324" s="76" t="inlineStr">
-        <is>
-          <t>PROT_01_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D324" s="77" t="inlineStr">
-        <is>
-          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E324" s="79" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F324" s="77" t="inlineStr">
-        <is>
-          <t>PROT_01_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G324" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H324" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I324" s="76" t="inlineStr"/>
-      <c r="J324" s="80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K324" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L324" s="76" t="inlineStr"/>
-      <c r="M324" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N324" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+    <row r="324" ht="8" customHeight="1">
+      <c r="A324" s="9" t="n"/>
+      <c r="B324" s="9" t="n"/>
+      <c r="C324" s="9" t="n"/>
+      <c r="D324" s="9" t="n"/>
+      <c r="E324" s="9" t="n"/>
+      <c r="F324" s="9" t="n"/>
+      <c r="G324" s="9" t="n"/>
+      <c r="H324" s="9" t="n"/>
+      <c r="I324" s="9" t="n"/>
+      <c r="J324" s="9" t="n"/>
+      <c r="K324" s="9" t="n"/>
+      <c r="L324" s="9" t="n"/>
+      <c r="M324" s="9" t="n"/>
+      <c r="N324" s="9" t="n"/>
     </row>
     <row r="325" ht="30" customHeight="1">
       <c r="A325" s="75" t="inlineStr">
@@ -21107,17 +21107,17 @@
       </c>
       <c r="B325" s="75" t="inlineStr">
         <is>
-          <t>Jersey Devil</t>
+          <t>Mothman</t>
         </is>
       </c>
       <c r="C325" s="76" t="inlineStr">
         <is>
-          <t>PROT_02_AGREE_INTIMATE</t>
+          <t>PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D325" s="77" t="inlineStr">
         <is>
-          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
+          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E325" s="79" t="inlineStr">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="F325" s="77" t="inlineStr">
         <is>
-          <t>PROT_02_AGREE (intimate choice)</t>
+          <t>PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G325" s="77" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="N325" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21171,17 +21171,17 @@
       </c>
       <c r="B326" s="75" t="inlineStr">
         <is>
-          <t>Bigfoot</t>
+          <t>Jersey Devil</t>
         </is>
       </c>
       <c r="C326" s="76" t="inlineStr">
         <is>
-          <t>PROT_03_AGREE_INTIMATE</t>
+          <t>PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D326" s="77" t="inlineStr">
         <is>
-          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
+          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
         </is>
       </c>
       <c r="E326" s="79" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F326" s="77" t="inlineStr">
         <is>
-          <t>PROT_03_AGREE (intimate choice)</t>
+          <t>PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G326" s="77" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="N326" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21235,17 +21235,17 @@
       </c>
       <c r="B327" s="75" t="inlineStr">
         <is>
-          <t>Thunderbird</t>
+          <t>Bigfoot</t>
         </is>
       </c>
       <c r="C327" s="76" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE_INTIMATE</t>
+          <t>PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D327" s="77" t="inlineStr">
         <is>
-          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
+          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
         </is>
       </c>
       <c r="E327" s="79" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="F327" s="77" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE (intimate choice)</t>
+          <t>PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G327" s="77" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="N327" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21299,17 +21299,17 @@
       </c>
       <c r="B328" s="75" t="inlineStr">
         <is>
-          <t>Headless Horseman</t>
+          <t>Thunderbird</t>
         </is>
       </c>
       <c r="C328" s="76" t="inlineStr">
         <is>
-          <t>PROT_05_AGREE_INTIMATE</t>
+          <t>PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D328" s="77" t="inlineStr">
         <is>
-          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
+          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
         </is>
       </c>
       <c r="E328" s="79" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="F328" s="77" t="inlineStr">
         <is>
-          <t>PROT_05_AGREE (intimate choice)</t>
+          <t>PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G328" s="77" t="inlineStr">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="N328" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21363,17 +21363,17 @@
       </c>
       <c r="B329" s="75" t="inlineStr">
         <is>
-          <t>Chessie</t>
+          <t>Headless Horseman</t>
         </is>
       </c>
       <c r="C329" s="76" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE_INTIMATE</t>
+          <t>PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D329" s="77" t="inlineStr">
         <is>
-          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
         </is>
       </c>
       <c r="E329" s="79" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="F329" s="77" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE (intimate choice)</t>
+          <t>PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G329" s="77" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="N329" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21427,17 +21427,17 @@
       </c>
       <c r="B330" s="75" t="inlineStr">
         <is>
-          <t>Bell Witch</t>
+          <t>Chessie</t>
         </is>
       </c>
       <c r="C330" s="76" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE_INTIMATE</t>
+          <t>PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D330" s="77" t="inlineStr">
         <is>
-          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
+          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E330" s="79" t="inlineStr">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="F330" s="77" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE (intimate choice)</t>
+          <t>PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G330" s="77" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="N330" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21491,17 +21491,17 @@
       </c>
       <c r="B331" s="75" t="inlineStr">
         <is>
-          <t>Old Ironsides</t>
+          <t>Bell Witch</t>
         </is>
       </c>
       <c r="C331" s="76" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE_INTIMATE</t>
+          <t>PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D331" s="77" t="inlineStr">
         <is>
-          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
         </is>
       </c>
       <c r="E331" s="79" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="F331" s="77" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE (intimate choice)</t>
+          <t>PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G331" s="77" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="N331" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21555,17 +21555,17 @@
       </c>
       <c r="B332" s="75" t="inlineStr">
         <is>
-          <t>Valley Forge Guardian</t>
+          <t>Old Ironsides</t>
         </is>
       </c>
       <c r="C332" s="76" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE_INTIMATE</t>
+          <t>PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D332" s="77" t="inlineStr">
         <is>
-          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
+          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E332" s="79" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="F332" s="77" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE (intimate choice)</t>
+          <t>PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G332" s="77" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="N332" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21619,17 +21619,17 @@
       </c>
       <c r="B333" s="75" t="inlineStr">
         <is>
-          <t>Snallygaster</t>
+          <t>Valley Forge Guardian</t>
         </is>
       </c>
       <c r="C333" s="76" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE_INTIMATE</t>
+          <t>PROT_09_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D333" s="77" t="inlineStr">
         <is>
-          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
+          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E333" s="79" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="F333" s="77" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE (intimate choice)</t>
+          <t>PROT_09_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G333" s="77" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="N333" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21683,17 +21683,17 @@
       </c>
       <c r="B334" s="75" t="inlineStr">
         <is>
-          <t>Paul Revere</t>
+          <t>Snallygaster</t>
         </is>
       </c>
       <c r="C334" s="76" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE_INTIMATE</t>
+          <t>PROT_10_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D334" s="77" t="inlineStr">
         <is>
-          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
+          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
         </is>
       </c>
       <c r="E334" s="79" t="inlineStr">
@@ -21703,7 +21703,7 @@
       </c>
       <c r="F334" s="77" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE (intimate choice)</t>
+          <t>PROT_10_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G334" s="77" t="inlineStr">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="N334" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21747,17 +21747,17 @@
       </c>
       <c r="B335" s="75" t="inlineStr">
         <is>
-          <t>Liberty Bell</t>
+          <t>Paul Revere</t>
         </is>
       </c>
       <c r="C335" s="76" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE_INTIMATE</t>
+          <t>PROT_11_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D335" s="77" t="inlineStr">
         <is>
-          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
+          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
         </is>
       </c>
       <c r="E335" s="79" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="F335" s="77" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE (intimate choice)</t>
+          <t>PROT_11_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G335" s="77" t="inlineStr">
@@ -21799,7 +21799,7 @@
       </c>
       <c r="N335" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21811,17 +21811,17 @@
       </c>
       <c r="B336" s="75" t="inlineStr">
         <is>
-          <t>Green Mountain Ghost</t>
+          <t>Liberty Bell</t>
         </is>
       </c>
       <c r="C336" s="76" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE_INTIMATE</t>
+          <t>PROT_12_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D336" s="77" t="inlineStr">
         <is>
-          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
+          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E336" s="79" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="F336" s="77" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE (intimate choice)</t>
+          <t>PROT_12_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G336" s="77" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="N336" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21875,17 +21875,17 @@
       </c>
       <c r="B337" s="75" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Green Mountain Ghost</t>
         </is>
       </c>
       <c r="C337" s="76" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE_INTIMATE</t>
+          <t>PROT_13_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D337" s="77" t="inlineStr">
         <is>
-          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
+          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
         </is>
       </c>
       <c r="E337" s="79" t="inlineStr">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="F337" s="77" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE (intimate choice)</t>
+          <t>PROT_13_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G337" s="77" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="N337" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21939,17 +21939,17 @@
       </c>
       <c r="B338" s="75" t="inlineStr">
         <is>
-          <t>Skunk Ape</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="C338" s="76" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE_INTIMATE</t>
+          <t>PROT_14_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D338" s="77" t="inlineStr">
         <is>
-          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
+          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
         </is>
       </c>
       <c r="E338" s="79" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="F338" s="77" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE (intimate choice)</t>
+          <t>PROT_14_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G338" s="77" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="N338" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22003,17 +22003,17 @@
       </c>
       <c r="B339" s="75" t="inlineStr">
         <is>
-          <t>Minuteman</t>
+          <t>Skunk Ape</t>
         </is>
       </c>
       <c r="C339" s="76" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE_INTIMATE</t>
+          <t>PROT_15_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D339" s="77" t="inlineStr">
         <is>
-          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
+          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E339" s="79" t="inlineStr">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="F339" s="77" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE (intimate choice)</t>
+          <t>PROT_15_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G339" s="77" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="N339" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22067,17 +22067,17 @@
       </c>
       <c r="B340" s="75" t="inlineStr">
         <is>
-          <t>Lincoln's Ghost</t>
+          <t>Minuteman</t>
         </is>
       </c>
       <c r="C340" s="76" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE_INTIMATE</t>
+          <t>PROT_16_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D340" s="77" t="inlineStr">
         <is>
-          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
+          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E340" s="79" t="inlineStr">
@@ -22087,7 +22087,7 @@
       </c>
       <c r="F340" s="77" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE (intimate choice)</t>
+          <t>PROT_16_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G340" s="77" t="inlineStr">
@@ -22119,89 +22119,89 @@
       </c>
       <c r="N340" s="77" t="inlineStr">
         <is>
+          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="30" customHeight="1">
+      <c r="A341" s="75" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B341" s="75" t="inlineStr">
+        <is>
+          <t>Lincoln's Ghost</t>
+        </is>
+      </c>
+      <c r="C341" s="76" t="inlineStr">
+        <is>
+          <t>PROT_17_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D341" s="77" t="inlineStr">
+        <is>
+          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E341" s="79" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F341" s="77" t="inlineStr">
+        <is>
+          <t>PROT_17_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G341" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H341" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I341" s="76" t="inlineStr"/>
+      <c r="J341" s="80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K341" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L341" s="76" t="inlineStr"/>
+      <c r="M341" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N341" s="77" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
-    <row r="341" ht="8" customHeight="1">
-      <c r="A341" s="9" t="n"/>
-      <c r="B341" s="9" t="n"/>
-      <c r="C341" s="9" t="n"/>
-      <c r="D341" s="9" t="n"/>
-      <c r="E341" s="9" t="n"/>
-      <c r="F341" s="9" t="n"/>
-      <c r="G341" s="9" t="n"/>
-      <c r="H341" s="9" t="n"/>
-      <c r="I341" s="9" t="n"/>
-      <c r="J341" s="9" t="n"/>
-      <c r="K341" s="9" t="n"/>
-      <c r="L341" s="9" t="n"/>
-      <c r="M341" s="9" t="n"/>
-      <c r="N341" s="9" t="n"/>
-    </row>
-    <row r="342" ht="30" customHeight="1">
-      <c r="A342" s="75" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B342" s="75" t="inlineStr">
-        <is>
-          <t>Month 1</t>
-        </is>
-      </c>
-      <c r="C342" s="76" t="inlineStr">
-        <is>
-          <t>WH_SECRET_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D342" s="77" t="inlineStr">
-        <is>
-          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E342" s="79" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F342" s="77" t="inlineStr">
-        <is>
-          <t>WH_SECRET_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G342" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H342" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I342" s="76" t="inlineStr"/>
-      <c r="J342" s="80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K342" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L342" s="76" t="inlineStr"/>
-      <c r="M342" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N342" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+    <row r="342" ht="8" customHeight="1">
+      <c r="A342" s="9" t="n"/>
+      <c r="B342" s="9" t="n"/>
+      <c r="C342" s="9" t="n"/>
+      <c r="D342" s="9" t="n"/>
+      <c r="E342" s="9" t="n"/>
+      <c r="F342" s="9" t="n"/>
+      <c r="G342" s="9" t="n"/>
+      <c r="H342" s="9" t="n"/>
+      <c r="I342" s="9" t="n"/>
+      <c r="J342" s="9" t="n"/>
+      <c r="K342" s="9" t="n"/>
+      <c r="L342" s="9" t="n"/>
+      <c r="M342" s="9" t="n"/>
+      <c r="N342" s="9" t="n"/>
     </row>
     <row r="343" ht="30" customHeight="1">
       <c r="A343" s="75" t="inlineStr">
@@ -22211,17 +22211,17 @@
       </c>
       <c r="B343" s="75" t="inlineStr">
         <is>
-          <t>Month 7</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C343" s="76" t="inlineStr">
         <is>
-          <t>WH_SECRET_07_INTIMATE</t>
+          <t>WH_SECRET_01_INTIMATE</t>
         </is>
       </c>
       <c r="D343" s="77" t="inlineStr">
         <is>
-          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
+          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
         </is>
       </c>
       <c r="E343" s="79" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="F343" s="77" t="inlineStr">
         <is>
-          <t>WH_SECRET_07 (intimate choice)</t>
+          <t>WH_SECRET_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G343" s="77" t="inlineStr">
@@ -22263,7 +22263,7 @@
       </c>
       <c r="N343" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22275,17 +22275,17 @@
       </c>
       <c r="B344" s="75" t="inlineStr">
         <is>
-          <t>Month 10</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C344" s="76" t="inlineStr">
         <is>
-          <t>WH_SECRET_10_INTIMATE</t>
+          <t>WH_SECRET_07_INTIMATE</t>
         </is>
       </c>
       <c r="D344" s="77" t="inlineStr">
         <is>
-          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
+          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
         </is>
       </c>
       <c r="E344" s="79" t="inlineStr">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F344" s="77" t="inlineStr">
         <is>
-          <t>WH_SECRET_10 (intimate choice)</t>
+          <t>WH_SECRET_07 (intimate choice)</t>
         </is>
       </c>
       <c r="G344" s="77" t="inlineStr">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="N344" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22339,17 +22339,17 @@
       </c>
       <c r="B345" s="75" t="inlineStr">
         <is>
-          <t>Month 12</t>
+          <t>Month 10</t>
         </is>
       </c>
       <c r="C345" s="76" t="inlineStr">
         <is>
-          <t>WH_SECRET_12_INTIMATE</t>
+          <t>WH_SECRET_10_INTIMATE</t>
         </is>
       </c>
       <c r="D345" s="77" t="inlineStr">
         <is>
-          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
+          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
         </is>
       </c>
       <c r="E345" s="79" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="F345" s="77" t="inlineStr">
         <is>
-          <t>WH_SECRET_12 (intimate choice)</t>
+          <t>WH_SECRET_10 (intimate choice)</t>
         </is>
       </c>
       <c r="G345" s="77" t="inlineStr">
@@ -22391,47 +22391,111 @@
       </c>
       <c r="N345" s="77" t="inlineStr">
         <is>
+          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="30" customHeight="1">
+      <c r="A346" s="75" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B346" s="75" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="C346" s="76" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D346" s="77" t="inlineStr">
+        <is>
+          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E346" s="79" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F346" s="77" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G346" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H346" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I346" s="76" t="inlineStr"/>
+      <c r="J346" s="80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K346" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L346" s="76" t="inlineStr"/>
+      <c r="M346" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N346" s="77" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of WH_SECRET_12. By morning: emotional arc, no explicit imagery.</t>
         </is>
-      </c>
-    </row>
-    <row r="347" ht="20" customHeight="1">
-      <c r="A347" s="81" t="inlineStr">
-        <is>
-          <t>Total events in spreadsheet</t>
-        </is>
-      </c>
-      <c r="B347" s="82" t="n">
-        <v>314</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
       <c r="A348" s="81" t="inlineStr">
         <is>
-          <t>FIRST PASS (coded &amp; wired)</t>
+          <t>Total events in spreadsheet</t>
         </is>
       </c>
       <c r="B348" s="82" t="n">
-        <v>248</v>
+        <v>315</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
       <c r="A349" s="81" t="inlineStr">
         <is>
-          <t>IDEA (not yet implemented)</t>
+          <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
       <c r="B349" s="82" t="n">
-        <v>64</v>
+        <v>249</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
       <c r="A350" s="81" t="inlineStr">
         <is>
+          <t>IDEA (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="B350" s="82" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="351" ht="20" customHeight="1">
+      <c r="A351" s="81" t="inlineStr">
+        <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B350" s="82" t="n">
+      <c r="B351" s="82" t="n">
         <v>55</v>
       </c>
     </row>
@@ -22446,7 +22510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22747,7 +22811,7 @@
       </c>
       <c r="D5" s="55" t="inlineStr">
         <is>
-          <t>PRESIDENT PENOIT'S CONDITIONS: MARK PENOIT PUTS IT IN WRITING</t>
+          <t>PRESIDENT PENOIT'S CONDITIONS: MARC PENOIT PUTS IT IN WRITING</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
@@ -25625,85 +25689,85 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="8" customHeight="1">
-      <c r="A50" s="9" t="n"/>
-      <c r="B50" s="9" t="n"/>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="9" t="n"/>
-      <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="75" t="inlineStr">
-        <is>
-          <t>CA Protector</t>
-        </is>
-      </c>
-      <c r="B51" s="75" t="inlineStr">
-        <is>
-          <t>Le Wendigo</t>
-        </is>
-      </c>
-      <c r="C51" s="76" t="inlineStr">
-        <is>
-          <t>CA_PROT_01_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D51" s="77" t="inlineStr">
-        <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E51" s="79" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B50" s="53" t="inlineStr">
+        <is>
+          <t>PM Arc</t>
+        </is>
+      </c>
+      <c r="C50" s="54" t="inlineStr">
+        <is>
+          <t>CA_PM_LEGACY_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D50" s="55" t="inlineStr">
+        <is>
+          <t>MARC PENOIT'S FINAL ASSESSMENT — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E50" s="56" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F51" s="77" t="inlineStr">
-        <is>
-          <t>CA_PROT_01_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G51" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I51" s="76" t="inlineStr"/>
-      <c r="J51" s="80" t="inlineStr">
+      <c r="F50" s="55" t="inlineStr">
+        <is>
+          <t>CA_PM_LEGACY (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G50" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I50" s="54" t="inlineStr"/>
+      <c r="J50" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K51" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L51" s="76" t="inlineStr"/>
-      <c r="M51" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N51" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+      <c r="K50" s="56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L50" s="54" t="inlineStr"/>
+      <c r="M50" s="56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" s="55" t="inlineStr">
+        <is>
+          <t>By morning: Penoit at the desk before light, writing page forty-one. Emotional resolution — he was wrong about what this would feel like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="8" customHeight="1">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="75" t="inlineStr">
@@ -25713,17 +25777,17 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>Le Loup-Garou</t>
+          <t>Le Wendigo</t>
         </is>
       </c>
       <c r="C52" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE_INTIMATE</t>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D52" s="77" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
         </is>
       </c>
       <c r="E52" s="79" t="inlineStr">
@@ -25733,7 +25797,7 @@
       </c>
       <c r="F52" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE (intimate choice)</t>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G52" s="77" t="inlineStr">
@@ -25765,7 +25829,7 @@
       </c>
       <c r="N52" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25777,17 +25841,17 @@
       </c>
       <c r="B53" s="75" t="inlineStr">
         <is>
-          <t>Les Feux Follets</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C53" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE_INTIMATE</t>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D53" s="77" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
       <c r="E53" s="79" t="inlineStr">
@@ -25797,7 +25861,7 @@
       </c>
       <c r="F53" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE (intimate choice)</t>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G53" s="77" t="inlineStr">
@@ -25829,7 +25893,7 @@
       </c>
       <c r="N53" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25841,17 +25905,17 @@
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>Mishepeshu</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C54" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE_INTIMATE</t>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D54" s="77" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
       <c r="E54" s="79" t="inlineStr">
@@ -25861,7 +25925,7 @@
       </c>
       <c r="F54" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE (intimate choice)</t>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G54" s="77" t="inlineStr">
@@ -25893,7 +25957,7 @@
       </c>
       <c r="N54" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25905,17 +25969,17 @@
       </c>
       <c r="B55" s="75" t="inlineStr">
         <is>
-          <t>La Corriveau</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C55" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE_INTIMATE</t>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D55" s="77" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E55" s="79" t="inlineStr">
@@ -25925,7 +25989,7 @@
       </c>
       <c r="F55" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE (intimate choice)</t>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G55" s="77" t="inlineStr">
@@ -25957,7 +26021,7 @@
       </c>
       <c r="N55" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25969,17 +26033,17 @@
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>Le Carcajou</t>
+          <t>La Corriveau</t>
         </is>
       </c>
       <c r="C56" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE_INTIMATE</t>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D56" s="77" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
       <c r="E56" s="79" t="inlineStr">
@@ -25989,7 +26053,7 @@
       </c>
       <c r="F56" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE (intimate choice)</t>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G56" s="77" t="inlineStr">
@@ -26021,7 +26085,7 @@
       </c>
       <c r="N56" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -26033,17 +26097,17 @@
       </c>
       <c r="B57" s="75" t="inlineStr">
         <is>
-          <t>La Chasse-Galerie</t>
+          <t>Le Carcajou</t>
         </is>
       </c>
       <c r="C57" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE_INTIMATE</t>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D57" s="77" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
       <c r="E57" s="79" t="inlineStr">
@@ -26053,7 +26117,7 @@
       </c>
       <c r="F57" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE (intimate choice)</t>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G57" s="77" t="inlineStr">
@@ -26085,7 +26149,7 @@
       </c>
       <c r="N57" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -26097,17 +26161,17 @@
       </c>
       <c r="B58" s="75" t="inlineStr">
         <is>
-          <t>Le Gougou</t>
+          <t>La Chasse-Galerie</t>
         </is>
       </c>
       <c r="C58" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE_INTIMATE</t>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D58" s="77" t="inlineStr">
         <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
       <c r="E58" s="79" t="inlineStr">
@@ -26117,7 +26181,7 @@
       </c>
       <c r="F58" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE (intimate choice)</t>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G58" s="77" t="inlineStr">
@@ -26149,47 +26213,111 @@
       </c>
       <c r="N58" s="77" t="inlineStr">
         <is>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="75" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B59" s="75" t="inlineStr">
+        <is>
+          <t>Le Gougou</t>
+        </is>
+      </c>
+      <c r="C59" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D59" s="77" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E59" s="79" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F59" s="77" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G59" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I59" s="76" t="inlineStr"/>
+      <c r="J59" s="80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K59" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L59" s="76" t="inlineStr"/>
+      <c r="M59" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N59" s="77" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="81" t="inlineStr">
-        <is>
-          <t>Canadian events total</t>
-        </is>
-      </c>
-      <c r="B60" s="82" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="81" t="inlineStr">
         <is>
-          <t>Canada (Alliance arc)</t>
+          <t>Canadian events total</t>
         </is>
       </c>
       <c r="B61" s="82" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="81" t="inlineStr">
         <is>
-          <t>CA Protector (Jessica's creatures)</t>
+          <t>Canada (Alliance arc)</t>
         </is>
       </c>
       <c r="B62" s="82" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="81" t="inlineStr">
         <is>
+          <t>CA Protector (Jessica's creatures)</t>
+        </is>
+      </c>
+      <c r="B63" s="82" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="81" t="inlineStr">
+        <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B63" s="82" t="n">
+      <c r="B64" s="82" t="n">
         <v>12</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1140,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N351"/>
+  <dimension ref="A1:N350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19963,85 +19963,85 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="30" customHeight="1">
-      <c r="A305" s="53" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B305" s="53" t="inlineStr">
-        <is>
-          <t>PM Arc</t>
-        </is>
-      </c>
-      <c r="C305" s="54" t="inlineStr">
-        <is>
-          <t>CA_PM_LEGACY_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D305" s="55" t="inlineStr">
-        <is>
-          <t>MARC PENOIT'S FINAL ASSESSMENT — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E305" s="56" t="inlineStr">
+    <row r="305" ht="8" customHeight="1">
+      <c r="A305" s="9" t="n"/>
+      <c r="B305" s="9" t="n"/>
+      <c r="C305" s="9" t="n"/>
+      <c r="D305" s="9" t="n"/>
+      <c r="E305" s="9" t="n"/>
+      <c r="F305" s="9" t="n"/>
+      <c r="G305" s="9" t="n"/>
+      <c r="H305" s="9" t="n"/>
+      <c r="I305" s="9" t="n"/>
+      <c r="J305" s="9" t="n"/>
+      <c r="K305" s="9" t="n"/>
+      <c r="L305" s="9" t="n"/>
+      <c r="M305" s="9" t="n"/>
+      <c r="N305" s="9" t="n"/>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="75" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B306" s="75" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C306" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D306" s="77" t="inlineStr">
+        <is>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E306" s="79" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F305" s="55" t="inlineStr">
-        <is>
-          <t>CA_PM_LEGACY (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G305" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H305" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I305" s="54" t="inlineStr"/>
-      <c r="J305" s="80" t="inlineStr">
+      <c r="F306" s="77" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G306" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H306" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I306" s="76" t="inlineStr"/>
+      <c r="J306" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K305" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L305" s="54" t="inlineStr"/>
-      <c r="M305" s="56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N305" s="55" t="inlineStr">
-        <is>
-          <t>By morning: Penoit at the desk before light, writing page forty-one. Emotional resolution — he was wrong about what this would feel like.</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="8" customHeight="1">
-      <c r="A306" s="9" t="n"/>
-      <c r="B306" s="9" t="n"/>
-      <c r="C306" s="9" t="n"/>
-      <c r="D306" s="9" t="n"/>
-      <c r="E306" s="9" t="n"/>
-      <c r="F306" s="9" t="n"/>
-      <c r="G306" s="9" t="n"/>
-      <c r="H306" s="9" t="n"/>
-      <c r="I306" s="9" t="n"/>
-      <c r="J306" s="9" t="n"/>
-      <c r="K306" s="9" t="n"/>
-      <c r="L306" s="9" t="n"/>
-      <c r="M306" s="9" t="n"/>
-      <c r="N306" s="9" t="n"/>
+      <c r="K306" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L306" s="76" t="inlineStr"/>
+      <c r="M306" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N306" s="77" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="30" customHeight="1">
       <c r="A307" s="75" t="inlineStr">
@@ -20051,17 +20051,17 @@
       </c>
       <c r="B307" s="75" t="inlineStr">
         <is>
-          <t>Le Wendigo</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C307" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE_INTIMATE</t>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D307" s="77" t="inlineStr">
         <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
       <c r="E307" s="79" t="inlineStr">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="F307" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE (intimate choice)</t>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G307" s="77" t="inlineStr">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="N307" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20115,17 +20115,17 @@
       </c>
       <c r="B308" s="75" t="inlineStr">
         <is>
-          <t>Le Loup-Garou</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C308" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE_INTIMATE</t>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D308" s="77" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
       <c r="E308" s="79" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="F308" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE (intimate choice)</t>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G308" s="77" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="N308" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20179,17 +20179,17 @@
       </c>
       <c r="B309" s="75" t="inlineStr">
         <is>
-          <t>Les Feux Follets</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C309" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE_INTIMATE</t>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D309" s="77" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E309" s="79" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="F309" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE (intimate choice)</t>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G309" s="77" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="N309" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20243,17 +20243,17 @@
       </c>
       <c r="B310" s="75" t="inlineStr">
         <is>
-          <t>Mishepeshu</t>
+          <t>La Corriveau</t>
         </is>
       </c>
       <c r="C310" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE_INTIMATE</t>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D310" s="77" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
       <c r="E310" s="79" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="F310" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE (intimate choice)</t>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G310" s="77" t="inlineStr">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="N310" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20307,17 +20307,17 @@
       </c>
       <c r="B311" s="75" t="inlineStr">
         <is>
-          <t>La Corriveau</t>
+          <t>Le Carcajou</t>
         </is>
       </c>
       <c r="C311" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE_INTIMATE</t>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D311" s="77" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
       <c r="E311" s="79" t="inlineStr">
@@ -20327,7 +20327,7 @@
       </c>
       <c r="F311" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE (intimate choice)</t>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G311" s="77" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="N311" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20371,17 +20371,17 @@
       </c>
       <c r="B312" s="75" t="inlineStr">
         <is>
-          <t>Le Carcajou</t>
+          <t>La Chasse-Galerie</t>
         </is>
       </c>
       <c r="C312" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE_INTIMATE</t>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D312" s="77" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
       <c r="E312" s="79" t="inlineStr">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="F312" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE (intimate choice)</t>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G312" s="77" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="N312" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20435,17 +20435,17 @@
       </c>
       <c r="B313" s="75" t="inlineStr">
         <is>
-          <t>La Chasse-Galerie</t>
+          <t>Le Gougou</t>
         </is>
       </c>
       <c r="C313" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE_INTIMATE</t>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D313" s="77" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
         </is>
       </c>
       <c r="E313" s="79" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="F313" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE (intimate choice)</t>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G313" s="77" t="inlineStr">
@@ -20487,89 +20487,89 @@
       </c>
       <c r="N313" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="30" customHeight="1">
-      <c r="A314" s="75" t="inlineStr">
-        <is>
-          <t>CA Protector</t>
-        </is>
-      </c>
-      <c r="B314" s="75" t="inlineStr">
-        <is>
-          <t>Le Gougou</t>
-        </is>
-      </c>
-      <c r="C314" s="76" t="inlineStr">
-        <is>
-          <t>CA_PROT_08_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D314" s="77" t="inlineStr">
-        <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E314" s="79" t="inlineStr">
+          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="8" customHeight="1">
+      <c r="A314" s="9" t="n"/>
+      <c r="B314" s="9" t="n"/>
+      <c r="C314" s="9" t="n"/>
+      <c r="D314" s="9" t="n"/>
+      <c r="E314" s="9" t="n"/>
+      <c r="F314" s="9" t="n"/>
+      <c r="G314" s="9" t="n"/>
+      <c r="H314" s="9" t="n"/>
+      <c r="I314" s="9" t="n"/>
+      <c r="J314" s="9" t="n"/>
+      <c r="K314" s="9" t="n"/>
+      <c r="L314" s="9" t="n"/>
+      <c r="M314" s="9" t="n"/>
+      <c r="N314" s="9" t="n"/>
+    </row>
+    <row r="315" ht="30" customHeight="1">
+      <c r="A315" s="75" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B315" s="75" t="inlineStr">
+        <is>
+          <t>Ambush</t>
+        </is>
+      </c>
+      <c r="C315" s="76" t="inlineStr">
+        <is>
+          <t>UALANI_AMBUSH_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D315" s="77" t="inlineStr">
+        <is>
+          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E315" s="79" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F314" s="77" t="inlineStr">
-        <is>
-          <t>CA_PROT_08_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G314" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H314" s="78" t="inlineStr">
+      <c r="F315" s="77" t="inlineStr">
+        <is>
+          <t>UALANI_AMBUSH_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G315" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H315" s="78" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I314" s="76" t="inlineStr"/>
-      <c r="J314" s="80" t="inlineStr">
+      <c r="I315" s="76" t="inlineStr"/>
+      <c r="J315" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K314" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L314" s="76" t="inlineStr"/>
-      <c r="M314" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N314" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="8" customHeight="1">
-      <c r="A315" s="9" t="n"/>
-      <c r="B315" s="9" t="n"/>
-      <c r="C315" s="9" t="n"/>
-      <c r="D315" s="9" t="n"/>
-      <c r="E315" s="9" t="n"/>
-      <c r="F315" s="9" t="n"/>
-      <c r="G315" s="9" t="n"/>
-      <c r="H315" s="9" t="n"/>
-      <c r="I315" s="9" t="n"/>
-      <c r="J315" s="9" t="n"/>
-      <c r="K315" s="9" t="n"/>
-      <c r="L315" s="9" t="n"/>
-      <c r="M315" s="9" t="n"/>
-      <c r="N315" s="9" t="n"/>
+      <c r="K315" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L315" s="76" t="inlineStr"/>
+      <c r="M315" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N315" s="77" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="75" t="inlineStr">
@@ -20579,17 +20579,17 @@
       </c>
       <c r="B316" s="75" t="inlineStr">
         <is>
-          <t>Ambush</t>
+          <t>Dignitary Reception</t>
         </is>
       </c>
       <c r="C316" s="76" t="inlineStr">
         <is>
-          <t>UALANI_AMBUSH_01_INTIMATE</t>
+          <t>UALANI_DIGNITARY_01_INTIMATE</t>
         </is>
       </c>
       <c r="D316" s="77" t="inlineStr">
         <is>
-          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
+          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
         </is>
       </c>
       <c r="E316" s="79" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="F316" s="77" t="inlineStr">
         <is>
-          <t>UALANI_AMBUSH_01 (intimate choice)</t>
+          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G316" s="77" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="N316" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20643,17 +20643,17 @@
       </c>
       <c r="B317" s="75" t="inlineStr">
         <is>
-          <t>Dignitary Reception</t>
+          <t>Memorial Address</t>
         </is>
       </c>
       <c r="C317" s="76" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01_INTIMATE</t>
+          <t>UALANI_MEMORIAL_01_INTIMATE</t>
         </is>
       </c>
       <c r="D317" s="77" t="inlineStr">
         <is>
-          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E317" s="79" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F317" s="77" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
+          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G317" s="77" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="N317" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20707,17 +20707,17 @@
       </c>
       <c r="B318" s="75" t="inlineStr">
         <is>
-          <t>Memorial Address</t>
+          <t>Field Hospital</t>
         </is>
       </c>
       <c r="C318" s="76" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01_INTIMATE</t>
+          <t>UALANI_WOUNDED_01_INTIMATE</t>
         </is>
       </c>
       <c r="D318" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
       <c r="E318" s="79" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="F318" s="77" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
+          <t>UALANI_WOUNDED_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G318" s="77" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="N318" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20771,17 +20771,17 @@
       </c>
       <c r="B319" s="75" t="inlineStr">
         <is>
-          <t>Field Hospital</t>
+          <t>Forge Inspection</t>
         </is>
       </c>
       <c r="C319" s="76" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01_INTIMATE</t>
+          <t>UALANI_FORGE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D319" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
+          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
         </is>
       </c>
       <c r="E319" s="79" t="inlineStr">
@@ -20791,7 +20791,7 @@
       </c>
       <c r="F319" s="77" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01 (intimate choice)</t>
+          <t>UALANI_FORGE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G319" s="77" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="N319" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20835,17 +20835,17 @@
       </c>
       <c r="B320" s="75" t="inlineStr">
         <is>
-          <t>Forge Inspection</t>
+          <t>Culper Ring</t>
         </is>
       </c>
       <c r="C320" s="76" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01_INTIMATE</t>
+          <t>UALANI_CULPER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D320" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
+          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
         </is>
       </c>
       <c r="E320" s="79" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="F320" s="77" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01 (intimate choice)</t>
+          <t>UALANI_CULPER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G320" s="77" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="N320" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20899,17 +20899,17 @@
       </c>
       <c r="B321" s="75" t="inlineStr">
         <is>
-          <t>Culper Ring</t>
+          <t>Alliance Council</t>
         </is>
       </c>
       <c r="C321" s="76" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01_INTIMATE</t>
+          <t>UALANI_ALLIANCE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D321" s="77" t="inlineStr">
         <is>
-          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
         </is>
       </c>
       <c r="E321" s="79" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="F321" s="77" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01 (intimate choice)</t>
+          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G321" s="77" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="N321" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20963,17 +20963,17 @@
       </c>
       <c r="B322" s="75" t="inlineStr">
         <is>
-          <t>Alliance Council</t>
+          <t>Frontier</t>
         </is>
       </c>
       <c r="C322" s="76" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01_INTIMATE</t>
+          <t>UALANI_FRONTIER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D322" s="77" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
         </is>
       </c>
       <c r="E322" s="79" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="F322" s="77" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
+          <t>UALANI_FRONTIER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G322" s="77" t="inlineStr">
@@ -21015,89 +21015,89 @@
       </c>
       <c r="N322" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="323" ht="30" customHeight="1">
-      <c r="A323" s="75" t="inlineStr">
-        <is>
-          <t>Ualani</t>
-        </is>
-      </c>
-      <c r="B323" s="75" t="inlineStr">
-        <is>
-          <t>Frontier</t>
-        </is>
-      </c>
-      <c r="C323" s="76" t="inlineStr">
-        <is>
-          <t>UALANI_FRONTIER_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D323" s="77" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E323" s="79" t="inlineStr">
+          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="8" customHeight="1">
+      <c r="A323" s="9" t="n"/>
+      <c r="B323" s="9" t="n"/>
+      <c r="C323" s="9" t="n"/>
+      <c r="D323" s="9" t="n"/>
+      <c r="E323" s="9" t="n"/>
+      <c r="F323" s="9" t="n"/>
+      <c r="G323" s="9" t="n"/>
+      <c r="H323" s="9" t="n"/>
+      <c r="I323" s="9" t="n"/>
+      <c r="J323" s="9" t="n"/>
+      <c r="K323" s="9" t="n"/>
+      <c r="L323" s="9" t="n"/>
+      <c r="M323" s="9" t="n"/>
+      <c r="N323" s="9" t="n"/>
+    </row>
+    <row r="324" ht="30" customHeight="1">
+      <c r="A324" s="75" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B324" s="75" t="inlineStr">
+        <is>
+          <t>Mothman</t>
+        </is>
+      </c>
+      <c r="C324" s="76" t="inlineStr">
+        <is>
+          <t>PROT_01_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D324" s="77" t="inlineStr">
+        <is>
+          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E324" s="79" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F323" s="77" t="inlineStr">
-        <is>
-          <t>UALANI_FRONTIER_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G323" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H323" s="78" t="inlineStr">
+      <c r="F324" s="77" t="inlineStr">
+        <is>
+          <t>PROT_01_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G324" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H324" s="78" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I323" s="76" t="inlineStr"/>
-      <c r="J323" s="80" t="inlineStr">
+      <c r="I324" s="76" t="inlineStr"/>
+      <c r="J324" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K323" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L323" s="76" t="inlineStr"/>
-      <c r="M323" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N323" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="324" ht="8" customHeight="1">
-      <c r="A324" s="9" t="n"/>
-      <c r="B324" s="9" t="n"/>
-      <c r="C324" s="9" t="n"/>
-      <c r="D324" s="9" t="n"/>
-      <c r="E324" s="9" t="n"/>
-      <c r="F324" s="9" t="n"/>
-      <c r="G324" s="9" t="n"/>
-      <c r="H324" s="9" t="n"/>
-      <c r="I324" s="9" t="n"/>
-      <c r="J324" s="9" t="n"/>
-      <c r="K324" s="9" t="n"/>
-      <c r="L324" s="9" t="n"/>
-      <c r="M324" s="9" t="n"/>
-      <c r="N324" s="9" t="n"/>
+      <c r="K324" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L324" s="76" t="inlineStr"/>
+      <c r="M324" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N324" s="77" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="30" customHeight="1">
       <c r="A325" s="75" t="inlineStr">
@@ -21107,17 +21107,17 @@
       </c>
       <c r="B325" s="75" t="inlineStr">
         <is>
-          <t>Mothman</t>
+          <t>Jersey Devil</t>
         </is>
       </c>
       <c r="C325" s="76" t="inlineStr">
         <is>
-          <t>PROT_01_AGREE_INTIMATE</t>
+          <t>PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D325" s="77" t="inlineStr">
         <is>
-          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
+          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
         </is>
       </c>
       <c r="E325" s="79" t="inlineStr">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="F325" s="77" t="inlineStr">
         <is>
-          <t>PROT_01_AGREE (intimate choice)</t>
+          <t>PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G325" s="77" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="N325" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21171,17 +21171,17 @@
       </c>
       <c r="B326" s="75" t="inlineStr">
         <is>
-          <t>Jersey Devil</t>
+          <t>Bigfoot</t>
         </is>
       </c>
       <c r="C326" s="76" t="inlineStr">
         <is>
-          <t>PROT_02_AGREE_INTIMATE</t>
+          <t>PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D326" s="77" t="inlineStr">
         <is>
-          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
+          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
         </is>
       </c>
       <c r="E326" s="79" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F326" s="77" t="inlineStr">
         <is>
-          <t>PROT_02_AGREE (intimate choice)</t>
+          <t>PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G326" s="77" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="N326" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21235,17 +21235,17 @@
       </c>
       <c r="B327" s="75" t="inlineStr">
         <is>
-          <t>Bigfoot</t>
+          <t>Thunderbird</t>
         </is>
       </c>
       <c r="C327" s="76" t="inlineStr">
         <is>
-          <t>PROT_03_AGREE_INTIMATE</t>
+          <t>PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D327" s="77" t="inlineStr">
         <is>
-          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
+          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
         </is>
       </c>
       <c r="E327" s="79" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="F327" s="77" t="inlineStr">
         <is>
-          <t>PROT_03_AGREE (intimate choice)</t>
+          <t>PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G327" s="77" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="N327" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21299,17 +21299,17 @@
       </c>
       <c r="B328" s="75" t="inlineStr">
         <is>
-          <t>Thunderbird</t>
+          <t>Headless Horseman</t>
         </is>
       </c>
       <c r="C328" s="76" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE_INTIMATE</t>
+          <t>PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D328" s="77" t="inlineStr">
         <is>
-          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
+          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
         </is>
       </c>
       <c r="E328" s="79" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="F328" s="77" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE (intimate choice)</t>
+          <t>PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G328" s="77" t="inlineStr">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="N328" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21363,17 +21363,17 @@
       </c>
       <c r="B329" s="75" t="inlineStr">
         <is>
-          <t>Headless Horseman</t>
+          <t>Chessie</t>
         </is>
       </c>
       <c r="C329" s="76" t="inlineStr">
         <is>
-          <t>PROT_05_AGREE_INTIMATE</t>
+          <t>PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D329" s="77" t="inlineStr">
         <is>
-          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
+          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E329" s="79" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="F329" s="77" t="inlineStr">
         <is>
-          <t>PROT_05_AGREE (intimate choice)</t>
+          <t>PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G329" s="77" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="N329" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21427,17 +21427,17 @@
       </c>
       <c r="B330" s="75" t="inlineStr">
         <is>
-          <t>Chessie</t>
+          <t>Bell Witch</t>
         </is>
       </c>
       <c r="C330" s="76" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE_INTIMATE</t>
+          <t>PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D330" s="77" t="inlineStr">
         <is>
-          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
         </is>
       </c>
       <c r="E330" s="79" t="inlineStr">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="F330" s="77" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE (intimate choice)</t>
+          <t>PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G330" s="77" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="N330" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21491,17 +21491,17 @@
       </c>
       <c r="B331" s="75" t="inlineStr">
         <is>
-          <t>Bell Witch</t>
+          <t>Old Ironsides</t>
         </is>
       </c>
       <c r="C331" s="76" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE_INTIMATE</t>
+          <t>PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D331" s="77" t="inlineStr">
         <is>
-          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
+          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E331" s="79" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="F331" s="77" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE (intimate choice)</t>
+          <t>PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G331" s="77" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="N331" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21555,17 +21555,17 @@
       </c>
       <c r="B332" s="75" t="inlineStr">
         <is>
-          <t>Old Ironsides</t>
+          <t>Valley Forge Guardian</t>
         </is>
       </c>
       <c r="C332" s="76" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE_INTIMATE</t>
+          <t>PROT_09_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D332" s="77" t="inlineStr">
         <is>
-          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E332" s="79" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="F332" s="77" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE (intimate choice)</t>
+          <t>PROT_09_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G332" s="77" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="N332" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21619,17 +21619,17 @@
       </c>
       <c r="B333" s="75" t="inlineStr">
         <is>
-          <t>Valley Forge Guardian</t>
+          <t>Snallygaster</t>
         </is>
       </c>
       <c r="C333" s="76" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE_INTIMATE</t>
+          <t>PROT_10_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D333" s="77" t="inlineStr">
         <is>
-          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
+          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
         </is>
       </c>
       <c r="E333" s="79" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="F333" s="77" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE (intimate choice)</t>
+          <t>PROT_10_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G333" s="77" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="N333" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21683,17 +21683,17 @@
       </c>
       <c r="B334" s="75" t="inlineStr">
         <is>
-          <t>Snallygaster</t>
+          <t>Paul Revere</t>
         </is>
       </c>
       <c r="C334" s="76" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE_INTIMATE</t>
+          <t>PROT_11_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D334" s="77" t="inlineStr">
         <is>
-          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
+          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
         </is>
       </c>
       <c r="E334" s="79" t="inlineStr">
@@ -21703,7 +21703,7 @@
       </c>
       <c r="F334" s="77" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE (intimate choice)</t>
+          <t>PROT_11_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G334" s="77" t="inlineStr">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="N334" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21747,17 +21747,17 @@
       </c>
       <c r="B335" s="75" t="inlineStr">
         <is>
-          <t>Paul Revere</t>
+          <t>Liberty Bell</t>
         </is>
       </c>
       <c r="C335" s="76" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE_INTIMATE</t>
+          <t>PROT_12_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D335" s="77" t="inlineStr">
         <is>
-          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
+          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E335" s="79" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="F335" s="77" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE (intimate choice)</t>
+          <t>PROT_12_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G335" s="77" t="inlineStr">
@@ -21799,7 +21799,7 @@
       </c>
       <c r="N335" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21811,17 +21811,17 @@
       </c>
       <c r="B336" s="75" t="inlineStr">
         <is>
-          <t>Liberty Bell</t>
+          <t>Green Mountain Ghost</t>
         </is>
       </c>
       <c r="C336" s="76" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE_INTIMATE</t>
+          <t>PROT_13_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D336" s="77" t="inlineStr">
         <is>
-          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
+          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
         </is>
       </c>
       <c r="E336" s="79" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="F336" s="77" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE (intimate choice)</t>
+          <t>PROT_13_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G336" s="77" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="N336" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21875,17 +21875,17 @@
       </c>
       <c r="B337" s="75" t="inlineStr">
         <is>
-          <t>Green Mountain Ghost</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="C337" s="76" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE_INTIMATE</t>
+          <t>PROT_14_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D337" s="77" t="inlineStr">
         <is>
-          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
+          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
         </is>
       </c>
       <c r="E337" s="79" t="inlineStr">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="F337" s="77" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE (intimate choice)</t>
+          <t>PROT_14_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G337" s="77" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="N337" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21939,17 +21939,17 @@
       </c>
       <c r="B338" s="75" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Skunk Ape</t>
         </is>
       </c>
       <c r="C338" s="76" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE_INTIMATE</t>
+          <t>PROT_15_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D338" s="77" t="inlineStr">
         <is>
-          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
+          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E338" s="79" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="F338" s="77" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE (intimate choice)</t>
+          <t>PROT_15_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G338" s="77" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="N338" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22003,17 +22003,17 @@
       </c>
       <c r="B339" s="75" t="inlineStr">
         <is>
-          <t>Skunk Ape</t>
+          <t>Minuteman</t>
         </is>
       </c>
       <c r="C339" s="76" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE_INTIMATE</t>
+          <t>PROT_16_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D339" s="77" t="inlineStr">
         <is>
-          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
+          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E339" s="79" t="inlineStr">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="F339" s="77" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE (intimate choice)</t>
+          <t>PROT_16_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G339" s="77" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="N339" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22067,17 +22067,17 @@
       </c>
       <c r="B340" s="75" t="inlineStr">
         <is>
-          <t>Minuteman</t>
+          <t>Lincoln's Ghost</t>
         </is>
       </c>
       <c r="C340" s="76" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE_INTIMATE</t>
+          <t>PROT_17_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D340" s="77" t="inlineStr">
         <is>
-          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
+          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
         </is>
       </c>
       <c r="E340" s="79" t="inlineStr">
@@ -22087,7 +22087,7 @@
       </c>
       <c r="F340" s="77" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE (intimate choice)</t>
+          <t>PROT_17_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G340" s="77" t="inlineStr">
@@ -22119,89 +22119,89 @@
       </c>
       <c r="N340" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="30" customHeight="1">
-      <c r="A341" s="75" t="inlineStr">
-        <is>
-          <t>Protector</t>
-        </is>
-      </c>
-      <c r="B341" s="75" t="inlineStr">
-        <is>
-          <t>Lincoln's Ghost</t>
-        </is>
-      </c>
-      <c r="C341" s="76" t="inlineStr">
-        <is>
-          <t>PROT_17_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D341" s="77" t="inlineStr">
-        <is>
-          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E341" s="79" t="inlineStr">
+          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="8" customHeight="1">
+      <c r="A341" s="9" t="n"/>
+      <c r="B341" s="9" t="n"/>
+      <c r="C341" s="9" t="n"/>
+      <c r="D341" s="9" t="n"/>
+      <c r="E341" s="9" t="n"/>
+      <c r="F341" s="9" t="n"/>
+      <c r="G341" s="9" t="n"/>
+      <c r="H341" s="9" t="n"/>
+      <c r="I341" s="9" t="n"/>
+      <c r="J341" s="9" t="n"/>
+      <c r="K341" s="9" t="n"/>
+      <c r="L341" s="9" t="n"/>
+      <c r="M341" s="9" t="n"/>
+      <c r="N341" s="9" t="n"/>
+    </row>
+    <row r="342" ht="30" customHeight="1">
+      <c r="A342" s="75" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B342" s="75" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="C342" s="76" t="inlineStr">
+        <is>
+          <t>WH_SECRET_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D342" s="77" t="inlineStr">
+        <is>
+          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E342" s="79" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F341" s="77" t="inlineStr">
-        <is>
-          <t>PROT_17_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G341" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H341" s="78" t="inlineStr">
+      <c r="F342" s="77" t="inlineStr">
+        <is>
+          <t>WH_SECRET_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G342" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H342" s="78" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I341" s="76" t="inlineStr"/>
-      <c r="J341" s="80" t="inlineStr">
+      <c r="I342" s="76" t="inlineStr"/>
+      <c r="J342" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K341" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L341" s="76" t="inlineStr"/>
-      <c r="M341" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N341" s="77" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="8" customHeight="1">
-      <c r="A342" s="9" t="n"/>
-      <c r="B342" s="9" t="n"/>
-      <c r="C342" s="9" t="n"/>
-      <c r="D342" s="9" t="n"/>
-      <c r="E342" s="9" t="n"/>
-      <c r="F342" s="9" t="n"/>
-      <c r="G342" s="9" t="n"/>
-      <c r="H342" s="9" t="n"/>
-      <c r="I342" s="9" t="n"/>
-      <c r="J342" s="9" t="n"/>
-      <c r="K342" s="9" t="n"/>
-      <c r="L342" s="9" t="n"/>
-      <c r="M342" s="9" t="n"/>
-      <c r="N342" s="9" t="n"/>
+      <c r="K342" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L342" s="76" t="inlineStr"/>
+      <c r="M342" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N342" s="77" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="30" customHeight="1">
       <c r="A343" s="75" t="inlineStr">
@@ -22211,17 +22211,17 @@
       </c>
       <c r="B343" s="75" t="inlineStr">
         <is>
-          <t>Month 1</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C343" s="76" t="inlineStr">
         <is>
-          <t>WH_SECRET_01_INTIMATE</t>
+          <t>WH_SECRET_07_INTIMATE</t>
         </is>
       </c>
       <c r="D343" s="77" t="inlineStr">
         <is>
-          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
+          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
         </is>
       </c>
       <c r="E343" s="79" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="F343" s="77" t="inlineStr">
         <is>
-          <t>WH_SECRET_01 (intimate choice)</t>
+          <t>WH_SECRET_07 (intimate choice)</t>
         </is>
       </c>
       <c r="G343" s="77" t="inlineStr">
@@ -22263,7 +22263,7 @@
       </c>
       <c r="N343" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22275,17 +22275,17 @@
       </c>
       <c r="B344" s="75" t="inlineStr">
         <is>
-          <t>Month 7</t>
+          <t>Month 10</t>
         </is>
       </c>
       <c r="C344" s="76" t="inlineStr">
         <is>
-          <t>WH_SECRET_07_INTIMATE</t>
+          <t>WH_SECRET_10_INTIMATE</t>
         </is>
       </c>
       <c r="D344" s="77" t="inlineStr">
         <is>
-          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
+          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
         </is>
       </c>
       <c r="E344" s="79" t="inlineStr">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F344" s="77" t="inlineStr">
         <is>
-          <t>WH_SECRET_07 (intimate choice)</t>
+          <t>WH_SECRET_10 (intimate choice)</t>
         </is>
       </c>
       <c r="G344" s="77" t="inlineStr">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="N344" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22339,17 +22339,17 @@
       </c>
       <c r="B345" s="75" t="inlineStr">
         <is>
-          <t>Month 10</t>
+          <t>Month 12</t>
         </is>
       </c>
       <c r="C345" s="76" t="inlineStr">
         <is>
-          <t>WH_SECRET_10_INTIMATE</t>
+          <t>WH_SECRET_12_INTIMATE</t>
         </is>
       </c>
       <c r="D345" s="77" t="inlineStr">
         <is>
-          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
+          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
         </is>
       </c>
       <c r="E345" s="79" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="F345" s="77" t="inlineStr">
         <is>
-          <t>WH_SECRET_10 (intimate choice)</t>
+          <t>WH_SECRET_12 (intimate choice)</t>
         </is>
       </c>
       <c r="G345" s="77" t="inlineStr">
@@ -22391,111 +22391,47 @@
       </c>
       <c r="N345" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="30" customHeight="1">
-      <c r="A346" s="75" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B346" s="75" t="inlineStr">
-        <is>
-          <t>Month 12</t>
-        </is>
-      </c>
-      <c r="C346" s="76" t="inlineStr">
-        <is>
-          <t>WH_SECRET_12_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D346" s="77" t="inlineStr">
-        <is>
-          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E346" s="79" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F346" s="77" t="inlineStr">
-        <is>
-          <t>WH_SECRET_12 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G346" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H346" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I346" s="76" t="inlineStr"/>
-      <c r="J346" s="80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K346" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L346" s="76" t="inlineStr"/>
-      <c r="M346" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N346" s="77" t="inlineStr">
-        <is>
           <t>Stub — author intimate version of WH_SECRET_12. By morning: emotional arc, no explicit imagery.</t>
         </is>
+      </c>
+    </row>
+    <row r="347" ht="20" customHeight="1">
+      <c r="A347" s="81" t="inlineStr">
+        <is>
+          <t>Total events in spreadsheet</t>
+        </is>
+      </c>
+      <c r="B347" s="82" t="n">
+        <v>314</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
       <c r="A348" s="81" t="inlineStr">
         <is>
-          <t>Total events in spreadsheet</t>
+          <t>FIRST PASS (coded &amp; wired)</t>
         </is>
       </c>
       <c r="B348" s="82" t="n">
-        <v>315</v>
+        <v>248</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
       <c r="A349" s="81" t="inlineStr">
         <is>
-          <t>FIRST PASS (coded &amp; wired)</t>
+          <t>IDEA (not yet implemented)</t>
         </is>
       </c>
       <c r="B349" s="82" t="n">
-        <v>249</v>
+        <v>64</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
       <c r="A350" s="81" t="inlineStr">
         <is>
-          <t>IDEA (not yet implemented)</t>
+          <t>Need explicit art (YES)</t>
         </is>
       </c>
       <c r="B350" s="82" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="351" ht="20" customHeight="1">
-      <c r="A351" s="81" t="inlineStr">
-        <is>
-          <t>Need explicit art (YES)</t>
-        </is>
-      </c>
-      <c r="B351" s="82" t="n">
         <v>55</v>
       </c>
     </row>
@@ -22510,7 +22446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25689,85 +25625,85 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="53" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B50" s="53" t="inlineStr">
-        <is>
-          <t>PM Arc</t>
-        </is>
-      </c>
-      <c r="C50" s="54" t="inlineStr">
-        <is>
-          <t>CA_PM_LEGACY_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D50" s="55" t="inlineStr">
-        <is>
-          <t>MARC PENOIT'S FINAL ASSESSMENT — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E50" s="56" t="inlineStr">
+    <row r="50" ht="8" customHeight="1">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="75" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B51" s="75" t="inlineStr">
+        <is>
+          <t>Le Wendigo</t>
+        </is>
+      </c>
+      <c r="C51" s="76" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D51" s="77" t="inlineStr">
+        <is>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E51" s="79" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F50" s="55" t="inlineStr">
-        <is>
-          <t>CA_PM_LEGACY (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G50" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I50" s="54" t="inlineStr"/>
-      <c r="J50" s="80" t="inlineStr">
+      <c r="F51" s="77" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G51" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="78" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I51" s="76" t="inlineStr"/>
+      <c r="J51" s="80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K50" s="56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L50" s="54" t="inlineStr"/>
-      <c r="M50" s="56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N50" s="55" t="inlineStr">
-        <is>
-          <t>By morning: Penoit at the desk before light, writing page forty-one. Emotional resolution — he was wrong about what this would feel like.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="8" customHeight="1">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
-      <c r="K51" s="9" t="n"/>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="9" t="n"/>
+      <c r="K51" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L51" s="76" t="inlineStr"/>
+      <c r="M51" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N51" s="77" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="75" t="inlineStr">
@@ -25777,17 +25713,17 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>Le Wendigo</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C52" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE_INTIMATE</t>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D52" s="77" t="inlineStr">
         <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
       <c r="E52" s="79" t="inlineStr">
@@ -25797,7 +25733,7 @@
       </c>
       <c r="F52" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE (intimate choice)</t>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G52" s="77" t="inlineStr">
@@ -25829,7 +25765,7 @@
       </c>
       <c r="N52" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25841,17 +25777,17 @@
       </c>
       <c r="B53" s="75" t="inlineStr">
         <is>
-          <t>Le Loup-Garou</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C53" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE_INTIMATE</t>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D53" s="77" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
       <c r="E53" s="79" t="inlineStr">
@@ -25861,7 +25797,7 @@
       </c>
       <c r="F53" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE (intimate choice)</t>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G53" s="77" t="inlineStr">
@@ -25893,7 +25829,7 @@
       </c>
       <c r="N53" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25905,17 +25841,17 @@
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>Les Feux Follets</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C54" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE_INTIMATE</t>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D54" s="77" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E54" s="79" t="inlineStr">
@@ -25925,7 +25861,7 @@
       </c>
       <c r="F54" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE (intimate choice)</t>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G54" s="77" t="inlineStr">
@@ -25957,7 +25893,7 @@
       </c>
       <c r="N54" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -25969,17 +25905,17 @@
       </c>
       <c r="B55" s="75" t="inlineStr">
         <is>
-          <t>Mishepeshu</t>
+          <t>La Corriveau</t>
         </is>
       </c>
       <c r="C55" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE_INTIMATE</t>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D55" s="77" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
       <c r="E55" s="79" t="inlineStr">
@@ -25989,7 +25925,7 @@
       </c>
       <c r="F55" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE (intimate choice)</t>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G55" s="77" t="inlineStr">
@@ -26021,7 +25957,7 @@
       </c>
       <c r="N55" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -26033,17 +25969,17 @@
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>La Corriveau</t>
+          <t>Le Carcajou</t>
         </is>
       </c>
       <c r="C56" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE_INTIMATE</t>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D56" s="77" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
       <c r="E56" s="79" t="inlineStr">
@@ -26053,7 +25989,7 @@
       </c>
       <c r="F56" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE (intimate choice)</t>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G56" s="77" t="inlineStr">
@@ -26085,7 +26021,7 @@
       </c>
       <c r="N56" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -26097,17 +26033,17 @@
       </c>
       <c r="B57" s="75" t="inlineStr">
         <is>
-          <t>Le Carcajou</t>
+          <t>La Chasse-Galerie</t>
         </is>
       </c>
       <c r="C57" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE_INTIMATE</t>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D57" s="77" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
       <c r="E57" s="79" t="inlineStr">
@@ -26117,7 +26053,7 @@
       </c>
       <c r="F57" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE (intimate choice)</t>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G57" s="77" t="inlineStr">
@@ -26149,7 +26085,7 @@
       </c>
       <c r="N57" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -26161,17 +26097,17 @@
       </c>
       <c r="B58" s="75" t="inlineStr">
         <is>
-          <t>La Chasse-Galerie</t>
+          <t>Le Gougou</t>
         </is>
       </c>
       <c r="C58" s="76" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE_INTIMATE</t>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D58" s="77" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
         </is>
       </c>
       <c r="E58" s="79" t="inlineStr">
@@ -26181,7 +26117,7 @@
       </c>
       <c r="F58" s="77" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE (intimate choice)</t>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G58" s="77" t="inlineStr">
@@ -26213,111 +26149,47 @@
       </c>
       <c r="N58" s="77" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="75" t="inlineStr">
-        <is>
-          <t>CA Protector</t>
-        </is>
-      </c>
-      <c r="B59" s="75" t="inlineStr">
-        <is>
-          <t>Le Gougou</t>
-        </is>
-      </c>
-      <c r="C59" s="76" t="inlineStr">
-        <is>
-          <t>CA_PROT_08_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D59" s="77" t="inlineStr">
-        <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E59" s="79" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F59" s="77" t="inlineStr">
-        <is>
-          <t>CA_PROT_08_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G59" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="78" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I59" s="76" t="inlineStr"/>
-      <c r="J59" s="80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L59" s="76" t="inlineStr"/>
-      <c r="M59" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N59" s="77" t="inlineStr">
-        <is>
           <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="81" t="inlineStr">
+        <is>
+          <t>Canadian events total</t>
+        </is>
+      </c>
+      <c r="B60" s="82" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="81" t="inlineStr">
         <is>
-          <t>Canadian events total</t>
+          <t>Canada (Alliance arc)</t>
         </is>
       </c>
       <c r="B61" s="82" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="81" t="inlineStr">
         <is>
-          <t>Canada (Alliance arc)</t>
+          <t>CA Protector (Jessica's creatures)</t>
         </is>
       </c>
       <c r="B62" s="82" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="81" t="inlineStr">
         <is>
-          <t>CA Protector (Jessica's creatures)</t>
+          <t>Need explicit art (YES)</t>
         </is>
       </c>
       <c r="B63" s="82" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="81" t="inlineStr">
-        <is>
-          <t>Need explicit art (YES)</t>
-        </is>
-      </c>
-      <c r="B64" s="82" t="n">
         <v>12</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -2506,15 +2506,19 @@
           <t>→ PROT_01_AGREE (next_event_id)</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>prot_01_tame_scene</t>
+        </is>
+      </c>
+      <c r="J23" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
         </is>
       </c>
       <c r="K23" s="29" t="inlineStr">
@@ -22995,7 +22999,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -2574,15 +2574,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>prot_01_agree</t>
+        </is>
+      </c>
+      <c r="J24" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
         </is>
       </c>
       <c r="K24" s="28" t="inlineStr">
@@ -22999,7 +23003,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -2646,9 +2646,9 @@
           <t>→ PROT_02_TAME</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr">
@@ -2656,9 +2656,9 @@
           <t>jersey_devil</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J25" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
         </is>
       </c>
       <c r="K25" s="29" t="inlineStr">
@@ -2720,9 +2720,9 @@
         </is>
       </c>
       <c r="I26" s="24" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J26" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
         </is>
       </c>
       <c r="K26" s="29" t="inlineStr">
@@ -2784,9 +2784,9 @@
         </is>
       </c>
       <c r="I27" s="24" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J27" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr">
@@ -21691,66 +21691,70 @@
       </c>
     </row>
     <row r="334" ht="30" customHeight="1">
-      <c r="A334" s="79" t="inlineStr">
+      <c r="A334" s="23" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B334" s="79" t="inlineStr">
+      <c r="B334" s="23" t="inlineStr">
         <is>
           <t>Jersey Devil</t>
         </is>
       </c>
-      <c r="C334" s="80" t="inlineStr">
+      <c r="C334" s="24" t="inlineStr">
         <is>
           <t>PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D334" s="81" t="inlineStr">
+      <c r="D334" s="25" t="inlineStr">
         <is>
           <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
         </is>
       </c>
-      <c r="E334" s="83" t="inlineStr">
+      <c r="E334" s="29" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F334" s="81" t="inlineStr">
+      <c r="F334" s="25" t="inlineStr">
         <is>
           <t>PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G334" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H334" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I334" s="80" t="inlineStr"/>
-      <c r="J334" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K334" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L334" s="80" t="inlineStr"/>
-      <c r="M334" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N334" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+      <c r="G334" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H334" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I334" s="24" t="inlineStr">
+        <is>
+          <t>prot_02_agree_intimate</t>
+        </is>
+      </c>
+      <c r="J334" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K334" s="29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L334" s="24" t="inlineStr"/>
+      <c r="M334" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N334" s="25" t="inlineStr">
+        <is>
+          <t>New Jersey's most complicated asset. By morning: recognition without negotiation.</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23007,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -23013,7 +23017,7 @@
         </is>
       </c>
       <c r="B358" s="86" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -2714,12 +2714,16 @@
           <t>→ PROT_02_AGREE (next_event_id)</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr"/>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>prot_02_tame</t>
+        </is>
+      </c>
       <c r="J26" s="27" t="inlineStr">
         <is>
           <t>Integrated</t>
@@ -23007,7 +23011,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -14350,12 +14350,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H210" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I210" s="32" t="inlineStr"/>
+      <c r="H210" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I210" s="32" t="inlineStr">
+        <is>
+          <t>arc_01_done_scene</t>
+        </is>
+      </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -23011,7 +23015,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1163,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N359"/>
+  <dimension ref="A1:N362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17454,309 +17454,309 @@
         </is>
       </c>
     </row>
-    <row r="259" ht="8" customHeight="1">
-      <c r="A259" s="9" t="n"/>
-      <c r="B259" s="9" t="n"/>
-      <c r="C259" s="9" t="n"/>
-      <c r="D259" s="9" t="n"/>
-      <c r="E259" s="9" t="n"/>
-      <c r="F259" s="9" t="n"/>
-      <c r="G259" s="9" t="n"/>
-      <c r="H259" s="9" t="n"/>
-      <c r="I259" s="9" t="n"/>
-      <c r="J259" s="9" t="n"/>
-      <c r="K259" s="9" t="n"/>
-      <c r="L259" s="9" t="n"/>
-      <c r="M259" s="9" t="n"/>
-      <c r="N259" s="9" t="n"/>
+    <row r="259" ht="30" customHeight="1">
+      <c r="A259" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B259" s="31" t="inlineStr">
+        <is>
+          <t>Governor Ceremony</t>
+        </is>
+      </c>
+      <c r="C259" s="32" t="inlineStr">
+        <is>
+          <t>GOV_LVL2_HONOR</t>
+        </is>
+      </c>
+      <c r="D259" s="33" t="inlineStr">
+        <is>
+          <t>FIELD CITATION — [COMMANDER_NAME]</t>
+        </is>
+      </c>
+      <c r="E259" s="34" t="inlineStr">
+        <is>
+          <t>Level-Up</t>
+        </is>
+      </c>
+      <c r="F259" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G259" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H259" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I259" s="32" t="inlineStr"/>
+      <c r="J259" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K259" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L259" s="32" t="inlineStr"/>
+      <c r="M259" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N259" s="33" t="inlineStr">
+        <is>
+          <t>Fires on promote_commander to lvl 2; BTN1: morale+10</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="30" customHeight="1">
-      <c r="A260" s="51" t="inlineStr">
+      <c r="A260" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B260" s="31" t="inlineStr">
+        <is>
+          <t>Governor Ceremony</t>
+        </is>
+      </c>
+      <c r="C260" s="32" t="inlineStr">
+        <is>
+          <t>GOV_LVL3_CEREMONY</t>
+        </is>
+      </c>
+      <c r="D260" s="33" t="inlineStr">
+        <is>
+          <t>GENERAL [COMMANDER_NAME] — WHITE HOUSE RECOGNITION CEREMONY</t>
+        </is>
+      </c>
+      <c r="E260" s="34" t="inlineStr">
+        <is>
+          <t>Level-Up</t>
+        </is>
+      </c>
+      <c r="F260" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="33" t="inlineStr">
+        <is>
+          <t>GOV_REWARD</t>
+        </is>
+      </c>
+      <c r="H260" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I260" s="32" t="inlineStr">
+        <is>
+          <t>gov_lvl3_ceremony_scene</t>
+        </is>
+      </c>
+      <c r="J260" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K260" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L260" s="32" t="inlineStr"/>
+      <c r="M260" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N260" s="33" t="inlineStr">
+        <is>
+          <t>Fires on promote_commander to lvl 3; BTN1: morale+20; BTN2: → GOV_REWARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B261" s="31" t="inlineStr">
+        <is>
+          <t>Governor Ceremony</t>
+        </is>
+      </c>
+      <c r="C261" s="32" t="inlineStr">
+        <is>
+          <t>GOV_REWARD</t>
+        </is>
+      </c>
+      <c r="D261" s="33" t="inlineStr">
+        <is>
+          <t>GENERAL [COMMANDER_NAME] — THE LINCOLN BEDROOM</t>
+        </is>
+      </c>
+      <c r="E261" s="34" t="inlineStr">
+        <is>
+          <t>Intimate</t>
+        </is>
+      </c>
+      <c r="F261" s="33" t="inlineStr">
+        <is>
+          <t>GOV_LVL3_CEREMONY BTN2</t>
+        </is>
+      </c>
+      <c r="G261" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H261" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I261" s="32" t="inlineStr">
+        <is>
+          <t>gov_reward_scene</t>
+        </is>
+      </c>
+      <c r="J261" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K261" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L261" s="32" t="inlineStr">
+        <is>
+          <t>intimate</t>
+        </is>
+      </c>
+      <c r="M261" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N261" s="33" t="inlineStr">
+        <is>
+          <t>Fires from GOV_LVL3_CEREMONY BTN2; BTN1: governor_loyalty +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="8" customHeight="1">
+      <c r="A262" s="9" t="n"/>
+      <c r="B262" s="9" t="n"/>
+      <c r="C262" s="9" t="n"/>
+      <c r="D262" s="9" t="n"/>
+      <c r="E262" s="9" t="n"/>
+      <c r="F262" s="9" t="n"/>
+      <c r="G262" s="9" t="n"/>
+      <c r="H262" s="9" t="n"/>
+      <c r="I262" s="9" t="n"/>
+      <c r="J262" s="9" t="n"/>
+      <c r="K262" s="9" t="n"/>
+      <c r="L262" s="9" t="n"/>
+      <c r="M262" s="9" t="n"/>
+      <c r="N262" s="9" t="n"/>
+    </row>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="51" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B260" s="51" t="inlineStr">
+      <c r="B263" s="51" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C260" s="52" t="inlineStr">
+      <c r="C263" s="52" t="inlineStr">
         <is>
           <t>VP_LEGACY</t>
         </is>
       </c>
-      <c r="D260" s="53" t="inlineStr">
+      <c r="D263" s="53" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
         </is>
       </c>
-      <c r="E260" s="22" t="inlineStr">
+      <c r="E263" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F260" s="53" t="inlineStr">
+      <c r="F263" s="53" t="inlineStr">
         <is>
           <t>VP_FIRST_MEETING (turn 96+)</t>
         </is>
       </c>
-      <c r="G260" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H260" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I260" s="52" t="inlineStr"/>
-      <c r="J260" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K260" s="28" t="inlineStr">
+      <c r="G263" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I263" s="52" t="inlineStr"/>
+      <c r="J263" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K263" s="28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L260" s="52" t="inlineStr">
+      <c r="L263" s="52" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M260" s="54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N260" s="53" t="inlineStr">
+      <c r="M263" s="54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N263" s="53" t="inlineStr">
         <is>
           <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="8" customHeight="1">
-      <c r="A261" s="9" t="n"/>
-      <c r="B261" s="9" t="n"/>
-      <c r="C261" s="9" t="n"/>
-      <c r="D261" s="9" t="n"/>
-      <c r="E261" s="9" t="n"/>
-      <c r="F261" s="9" t="n"/>
-      <c r="G261" s="9" t="n"/>
-      <c r="H261" s="9" t="n"/>
-      <c r="I261" s="9" t="n"/>
-      <c r="J261" s="9" t="n"/>
-      <c r="K261" s="9" t="n"/>
-      <c r="L261" s="9" t="n"/>
-      <c r="M261" s="9" t="n"/>
-      <c r="N261" s="9" t="n"/>
-    </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="71" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B262" s="71" t="inlineStr">
-        <is>
-          <t>Month 1</t>
-        </is>
-      </c>
-      <c r="C262" s="72" t="inlineStr">
-        <is>
-          <t>WH_SECRET_01</t>
-        </is>
-      </c>
-      <c r="D262" s="73" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
-        </is>
-      </c>
-      <c r="E262" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F262" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G262" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H262" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I262" s="72" t="inlineStr"/>
-      <c r="J262" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K262" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L262" s="72" t="inlineStr">
-        <is>
-          <t>sensual option</t>
-        </is>
-      </c>
-      <c r="M262" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N262" s="73" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="71" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B263" s="71" t="inlineStr">
-        <is>
-          <t>Month 2</t>
-        </is>
-      </c>
-      <c r="C263" s="72" t="inlineStr">
-        <is>
-          <t>WH_SECRET_02</t>
-        </is>
-      </c>
-      <c r="D263" s="73" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F263" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G263" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H263" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I263" s="72" t="inlineStr"/>
-      <c r="J263" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K263" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L263" s="72" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M263" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N263" s="73" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="30" customHeight="1">
-      <c r="A264" s="71" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B264" s="71" t="inlineStr">
-        <is>
-          <t>Month 3</t>
-        </is>
-      </c>
-      <c r="C264" s="72" t="inlineStr">
-        <is>
-          <t>WH_SECRET_03</t>
-        </is>
-      </c>
-      <c r="D264" s="73" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F264" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G264" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H264" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I264" s="72" t="inlineStr"/>
-      <c r="J264" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K264" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L264" s="72" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M264" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N264" s="73" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
-        </is>
-      </c>
+    <row r="264" ht="8" customHeight="1">
+      <c r="A264" s="9" t="n"/>
+      <c r="B264" s="9" t="n"/>
+      <c r="C264" s="9" t="n"/>
+      <c r="D264" s="9" t="n"/>
+      <c r="E264" s="9" t="n"/>
+      <c r="F264" s="9" t="n"/>
+      <c r="G264" s="9" t="n"/>
+      <c r="H264" s="9" t="n"/>
+      <c r="I264" s="9" t="n"/>
+      <c r="J264" s="9" t="n"/>
+      <c r="K264" s="9" t="n"/>
+      <c r="L264" s="9" t="n"/>
+      <c r="M264" s="9" t="n"/>
+      <c r="N264" s="9" t="n"/>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="71" t="inlineStr">
@@ -17766,17 +17766,17 @@
       </c>
       <c r="B265" s="71" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C265" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_04</t>
+          <t>WH_SECRET_01</t>
         </is>
       </c>
       <c r="D265" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
+          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17805,14 +17805,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K265" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="K265" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="L265" s="72" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>sensual option</t>
         </is>
       </c>
       <c r="M265" s="74" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="N265" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
         </is>
       </c>
     </row>
@@ -17834,17 +17834,17 @@
       </c>
       <c r="B266" s="71" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C266" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_05</t>
+          <t>WH_SECRET_02</t>
         </is>
       </c>
       <c r="D266" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
+          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="N266" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
         </is>
       </c>
     </row>
@@ -17902,17 +17902,17 @@
       </c>
       <c r="B267" s="71" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C267" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_06</t>
+          <t>WH_SECRET_03</t>
         </is>
       </c>
       <c r="D267" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
+          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="N267" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
         </is>
       </c>
     </row>
@@ -17970,17 +17970,17 @@
       </c>
       <c r="B268" s="71" t="inlineStr">
         <is>
-          <t>Month 7</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C268" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_07</t>
+          <t>WH_SECRET_04</t>
         </is>
       </c>
       <c r="D268" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
+          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -18009,14 +18009,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K268" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K268" s="74" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L268" s="72" t="inlineStr">
         <is>
-          <t>explicit option</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="M268" s="74" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="N268" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
         </is>
       </c>
     </row>
@@ -18038,17 +18038,17 @@
       </c>
       <c r="B269" s="71" t="inlineStr">
         <is>
-          <t>Month 8</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C269" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_08</t>
+          <t>WH_SECRET_05</t>
         </is>
       </c>
       <c r="D269" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — DIWALI</t>
+          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="N269" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
         </is>
       </c>
     </row>
@@ -18106,17 +18106,17 @@
       </c>
       <c r="B270" s="71" t="inlineStr">
         <is>
-          <t>Month 9</t>
+          <t>Month 6</t>
         </is>
       </c>
       <c r="C270" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_09</t>
+          <t>WH_SECRET_06</t>
         </is>
       </c>
       <c r="D270" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
+          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="N270" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
         </is>
       </c>
     </row>
@@ -18174,17 +18174,17 @@
       </c>
       <c r="B271" s="71" t="inlineStr">
         <is>
-          <t>Month 10</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C271" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_10</t>
+          <t>WH_SECRET_07</t>
         </is>
       </c>
       <c r="D271" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
+          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="L271" s="72" t="inlineStr">
         <is>
-          <t>sensual option</t>
+          <t>explicit option</t>
         </is>
       </c>
       <c r="M271" s="74" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="N271" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
         </is>
       </c>
     </row>
@@ -18242,17 +18242,17 @@
       </c>
       <c r="B272" s="71" t="inlineStr">
         <is>
-          <t>Month 11</t>
+          <t>Month 8</t>
         </is>
       </c>
       <c r="C272" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_11</t>
+          <t>WH_SECRET_08</t>
         </is>
       </c>
       <c r="D272" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
+          <t>WHITE HOUSE SECRET — DIWALI</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="N272" s="73" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
         </is>
       </c>
     </row>
@@ -18310,17 +18310,17 @@
       </c>
       <c r="B273" s="71" t="inlineStr">
         <is>
-          <t>Month 12</t>
+          <t>Month 9</t>
         </is>
       </c>
       <c r="C273" s="72" t="inlineStr">
         <is>
-          <t>WH_SECRET_12</t>
+          <t>WH_SECRET_09</t>
         </is>
       </c>
       <c r="D273" s="73" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
+          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -18349,234 +18349,246 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K273" s="28" t="inlineStr">
+      <c r="K273" s="74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L273" s="72" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M273" s="74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N273" s="73" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="30" customHeight="1">
+      <c r="A274" s="71" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B274" s="71" t="inlineStr">
+        <is>
+          <t>Month 10</t>
+        </is>
+      </c>
+      <c r="C274" s="72" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10</t>
+        </is>
+      </c>
+      <c r="D274" s="73" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F274" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G274" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I274" s="72" t="inlineStr"/>
+      <c r="J274" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K274" s="28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L273" s="72" t="inlineStr">
+      <c r="L274" s="72" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M273" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N273" s="73" t="inlineStr">
+      <c r="M274" s="74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N274" s="73" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="71" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B275" s="71" t="inlineStr">
+        <is>
+          <t>Month 11</t>
+        </is>
+      </c>
+      <c r="C275" s="72" t="inlineStr">
+        <is>
+          <t>WH_SECRET_11</t>
+        </is>
+      </c>
+      <c r="D275" s="73" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F275" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G275" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I275" s="72" t="inlineStr"/>
+      <c r="J275" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K275" s="74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L275" s="72" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M275" s="74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N275" s="73" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="71" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B276" s="71" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="C276" s="72" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12</t>
+        </is>
+      </c>
+      <c r="D276" s="73" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F276" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G276" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I276" s="72" t="inlineStr"/>
+      <c r="J276" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K276" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L276" s="72" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M276" s="74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N276" s="73" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="274" ht="8" customHeight="1">
-      <c r="A274" s="9" t="n"/>
-      <c r="B274" s="9" t="n"/>
-      <c r="C274" s="9" t="n"/>
-      <c r="D274" s="9" t="n"/>
-      <c r="E274" s="9" t="n"/>
-      <c r="F274" s="9" t="n"/>
-      <c r="G274" s="9" t="n"/>
-      <c r="H274" s="9" t="n"/>
-      <c r="I274" s="9" t="n"/>
-      <c r="J274" s="9" t="n"/>
-      <c r="K274" s="9" t="n"/>
-      <c r="L274" s="9" t="n"/>
-      <c r="M274" s="9" t="n"/>
-      <c r="N274" s="9" t="n"/>
-    </row>
-    <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="75" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B275" s="75" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C275" s="76" t="inlineStr">
-        <is>
-          <t>CHALCH_SUMMON</t>
-        </is>
-      </c>
-      <c r="D275" s="77" t="inlineStr">
-        <is>
-          <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F275" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G275" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q1</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I275" s="76" t="inlineStr"/>
-      <c r="J275" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K275" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L275" s="76" t="inlineStr"/>
-      <c r="M275" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N275" s="77" t="inlineStr">
-        <is>
-          <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="30" customHeight="1">
-      <c r="A276" s="75" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B276" s="75" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C276" s="76" t="inlineStr">
-        <is>
-          <t>CHALCH_Q1</t>
-        </is>
-      </c>
-      <c r="D276" s="77" t="inlineStr">
-        <is>
-          <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
-        </is>
-      </c>
-      <c r="E276" s="78" t="inlineStr">
-        <is>
-          <t>Quest 1</t>
-        </is>
-      </c>
-      <c r="F276" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_SUMMON</t>
-        </is>
-      </c>
-      <c r="G276" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q2</t>
-        </is>
-      </c>
-      <c r="H276" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I276" s="76" t="inlineStr"/>
-      <c r="J276" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K276" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L276" s="76" t="inlineStr"/>
-      <c r="M276" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N276" s="77" t="inlineStr">
-        <is>
-          <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="30" customHeight="1">
-      <c r="A277" s="75" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B277" s="75" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C277" s="76" t="inlineStr">
-        <is>
-          <t>CHALCH_Q2</t>
-        </is>
-      </c>
-      <c r="D277" s="77" t="inlineStr">
-        <is>
-          <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
-        </is>
-      </c>
-      <c r="E277" s="78" t="inlineStr">
-        <is>
-          <t>Quest 2</t>
-        </is>
-      </c>
-      <c r="F277" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q1</t>
-        </is>
-      </c>
-      <c r="G277" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q3</t>
-        </is>
-      </c>
-      <c r="H277" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I277" s="76" t="inlineStr"/>
-      <c r="J277" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K277" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L277" s="76" t="inlineStr"/>
-      <c r="M277" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N277" s="77" t="inlineStr">
-        <is>
-          <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
-        </is>
-      </c>
+    <row r="277" ht="8" customHeight="1">
+      <c r="A277" s="9" t="n"/>
+      <c r="B277" s="9" t="n"/>
+      <c r="C277" s="9" t="n"/>
+      <c r="D277" s="9" t="n"/>
+      <c r="E277" s="9" t="n"/>
+      <c r="F277" s="9" t="n"/>
+      <c r="G277" s="9" t="n"/>
+      <c r="H277" s="9" t="n"/>
+      <c r="I277" s="9" t="n"/>
+      <c r="J277" s="9" t="n"/>
+      <c r="K277" s="9" t="n"/>
+      <c r="L277" s="9" t="n"/>
+      <c r="M277" s="9" t="n"/>
+      <c r="N277" s="9" t="n"/>
     </row>
     <row r="278" ht="30" customHeight="1">
       <c r="A278" s="75" t="inlineStr">
@@ -18591,27 +18603,27 @@
       </c>
       <c r="C278" s="76" t="inlineStr">
         <is>
-          <t>CHALCH_Q3</t>
+          <t>CHALCH_SUMMON</t>
         </is>
       </c>
       <c r="D278" s="77" t="inlineStr">
         <is>
-          <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
-        </is>
-      </c>
-      <c r="E278" s="78" t="inlineStr">
-        <is>
-          <t>Quest 3</t>
+          <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F278" s="77" t="inlineStr">
         <is>
-          <t>CHALCH_Q2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G278" s="77" t="inlineStr">
         <is>
-          <t>CHALCH_AGREE</t>
+          <t>CHALCH_Q1</t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr">
@@ -18638,7 +18650,7 @@
       </c>
       <c r="N278" s="77" t="inlineStr">
         <is>
-          <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
+          <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
         </is>
       </c>
     </row>
@@ -18655,27 +18667,27 @@
       </c>
       <c r="C279" s="76" t="inlineStr">
         <is>
-          <t>CHALCH_AGREE</t>
+          <t>CHALCH_Q1</t>
         </is>
       </c>
       <c r="D279" s="77" t="inlineStr">
         <is>
-          <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
+          <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
         </is>
       </c>
       <c r="E279" s="78" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Quest 1</t>
         </is>
       </c>
       <c r="F279" s="77" t="inlineStr">
         <is>
-          <t>CHALCH_Q3</t>
+          <t>CHALCH_SUMMON</t>
         </is>
       </c>
       <c r="G279" s="77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHALCH_Q2</t>
         </is>
       </c>
       <c r="H279" s="6" t="inlineStr">
@@ -18702,229 +18714,217 @@
       </c>
       <c r="N279" s="77" t="inlineStr">
         <is>
+          <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="30" customHeight="1">
+      <c r="A280" s="75" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B280" s="75" t="inlineStr">
+        <is>
+          <t>Jade Turkey Arc</t>
+        </is>
+      </c>
+      <c r="C280" s="76" t="inlineStr">
+        <is>
+          <t>CHALCH_Q2</t>
+        </is>
+      </c>
+      <c r="D280" s="77" t="inlineStr">
+        <is>
+          <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
+        </is>
+      </c>
+      <c r="E280" s="78" t="inlineStr">
+        <is>
+          <t>Quest 2</t>
+        </is>
+      </c>
+      <c r="F280" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_Q1</t>
+        </is>
+      </c>
+      <c r="G280" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_Q3</t>
+        </is>
+      </c>
+      <c r="H280" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I280" s="76" t="inlineStr"/>
+      <c r="J280" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K280" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L280" s="76" t="inlineStr"/>
+      <c r="M280" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N280" s="77" t="inlineStr">
+        <is>
+          <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="75" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B281" s="75" t="inlineStr">
+        <is>
+          <t>Jade Turkey Arc</t>
+        </is>
+      </c>
+      <c r="C281" s="76" t="inlineStr">
+        <is>
+          <t>CHALCH_Q3</t>
+        </is>
+      </c>
+      <c r="D281" s="77" t="inlineStr">
+        <is>
+          <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
+        </is>
+      </c>
+      <c r="E281" s="78" t="inlineStr">
+        <is>
+          <t>Quest 3</t>
+        </is>
+      </c>
+      <c r="F281" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_Q2</t>
+        </is>
+      </c>
+      <c r="G281" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_AGREE</t>
+        </is>
+      </c>
+      <c r="H281" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I281" s="76" t="inlineStr"/>
+      <c r="J281" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K281" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L281" s="76" t="inlineStr"/>
+      <c r="M281" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N281" s="77" t="inlineStr">
+        <is>
+          <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="30" customHeight="1">
+      <c r="A282" s="75" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B282" s="75" t="inlineStr">
+        <is>
+          <t>Jade Turkey Arc</t>
+        </is>
+      </c>
+      <c r="C282" s="76" t="inlineStr">
+        <is>
+          <t>CHALCH_AGREE</t>
+        </is>
+      </c>
+      <c r="D282" s="77" t="inlineStr">
+        <is>
+          <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
+        </is>
+      </c>
+      <c r="E282" s="78" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F282" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_Q3</t>
+        </is>
+      </c>
+      <c r="G282" s="77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I282" s="76" t="inlineStr"/>
+      <c r="J282" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K282" s="78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L282" s="76" t="inlineStr"/>
+      <c r="M282" s="78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N282" s="77" t="inlineStr">
+        <is>
           <t>Fires when chalch_q3_done; BTN1: +100 food; closes the arc</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="8" customHeight="1">
-      <c r="A280" s="9" t="n"/>
-      <c r="B280" s="9" t="n"/>
-      <c r="C280" s="9" t="n"/>
-      <c r="D280" s="9" t="n"/>
-      <c r="E280" s="9" t="n"/>
-      <c r="F280" s="9" t="n"/>
-      <c r="G280" s="9" t="n"/>
-      <c r="H280" s="9" t="n"/>
-      <c r="I280" s="9" t="n"/>
-      <c r="J280" s="9" t="n"/>
-      <c r="K280" s="9" t="n"/>
-      <c r="L280" s="9" t="n"/>
-      <c r="M280" s="9" t="n"/>
-      <c r="N280" s="9" t="n"/>
-    </row>
-    <row r="281" ht="30" customHeight="1">
-      <c r="A281" s="79" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B281" s="79" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C281" s="80" t="inlineStr">
-        <is>
-          <t>UALANI_DOCK_01</t>
-        </is>
-      </c>
-      <c r="D281" s="81" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E281" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F281" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G281" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H281" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I281" s="80" t="inlineStr"/>
-      <c r="J281" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K281" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L281" s="80" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M281" s="83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N281" s="81" t="inlineStr">
-        <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="30" customHeight="1">
-      <c r="A282" s="79" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B282" s="79" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C282" s="80" t="inlineStr">
-        <is>
-          <t>UALANI_FARM_01</t>
-        </is>
-      </c>
-      <c r="D282" s="81" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E282" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F282" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G282" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H282" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I282" s="80" t="inlineStr"/>
-      <c r="J282" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K282" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L282" s="80" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M282" s="83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N282" s="81" t="inlineStr">
-        <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="30" customHeight="1">
-      <c r="A283" s="79" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B283" s="79" t="inlineStr">
-        <is>
-          <t>Ualani Expansion</t>
-        </is>
-      </c>
-      <c r="C283" s="80" t="inlineStr">
-        <is>
-          <t>UALANI_BARRACKS_01</t>
-        </is>
-      </c>
-      <c r="D283" s="81" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E283" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F283" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G283" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H283" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I283" s="80" t="inlineStr"/>
-      <c r="J283" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K283" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L283" s="80" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M283" s="83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N283" s="81" t="inlineStr">
-        <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
-        </is>
-      </c>
+    <row r="283" ht="8" customHeight="1">
+      <c r="A283" s="9" t="n"/>
+      <c r="B283" s="9" t="n"/>
+      <c r="C283" s="9" t="n"/>
+      <c r="D283" s="9" t="n"/>
+      <c r="E283" s="9" t="n"/>
+      <c r="F283" s="9" t="n"/>
+      <c r="G283" s="9" t="n"/>
+      <c r="H283" s="9" t="n"/>
+      <c r="I283" s="9" t="n"/>
+      <c r="J283" s="9" t="n"/>
+      <c r="K283" s="9" t="n"/>
+      <c r="L283" s="9" t="n"/>
+      <c r="M283" s="9" t="n"/>
+      <c r="N283" s="9" t="n"/>
     </row>
     <row r="284" ht="30" customHeight="1">
       <c r="A284" s="79" t="inlineStr">
@@ -18939,12 +18939,12 @@
       </c>
       <c r="C284" s="80" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>UALANI_DOCK_01</t>
         </is>
       </c>
       <c r="D284" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="N284" s="81" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
         </is>
       </c>
     </row>
@@ -19002,17 +19002,17 @@
       </c>
       <c r="B285" s="79" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C285" s="80" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>UALANI_FARM_01</t>
         </is>
       </c>
       <c r="D285" s="81" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
@@ -19041,20 +19041,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K285" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L285" s="80" t="inlineStr"/>
+      <c r="K285" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L285" s="80" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M285" s="83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N285" s="81" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
         </is>
       </c>
     </row>
@@ -19066,17 +19070,17 @@
       </c>
       <c r="B286" s="79" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C286" s="80" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>UALANI_BARRACKS_01</t>
         </is>
       </c>
       <c r="D286" s="81" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
@@ -19105,20 +19109,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K286" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L286" s="80" t="inlineStr"/>
+      <c r="K286" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L286" s="80" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M286" s="83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N286" s="81" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
         </is>
       </c>
     </row>
@@ -19130,17 +19138,17 @@
       </c>
       <c r="B287" s="79" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Ualani Expansion</t>
         </is>
       </c>
       <c r="C287" s="80" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
       <c r="D287" s="81" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
@@ -19169,20 +19177,24 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K287" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L287" s="80" t="inlineStr"/>
+      <c r="K287" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L287" s="80" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
       <c r="M287" s="83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N287" s="81" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
@@ -19194,17 +19206,17 @@
       </c>
       <c r="B288" s="79" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C288" s="80" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>CL_WASHINGTON_01</t>
         </is>
       </c>
       <c r="D288" s="81" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
@@ -19246,7 +19258,7 @@
       </c>
       <c r="N288" s="81" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
@@ -19258,32 +19270,32 @@
       </c>
       <c r="B289" s="79" t="inlineStr">
         <is>
-          <t>Commander Expansion</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C289" s="80" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_2</t>
+          <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
       <c r="D289" s="81" t="inlineStr">
         <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E289" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F289" s="81" t="inlineStr">
         <is>
-          <t>CMD_OBJECTIVE_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G289" s="81" t="inlineStr">
         <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H289" s="82" t="inlineStr">
@@ -19310,7 +19322,7 @@
       </c>
       <c r="N289" s="81" t="inlineStr">
         <is>
-          <t>Extend the commander arc beyond first objective</t>
+          <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
@@ -19322,17 +19334,17 @@
       </c>
       <c r="B290" s="79" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C290" s="80" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>CX_NYC_01</t>
         </is>
       </c>
       <c r="D290" s="81" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
@@ -19374,7 +19386,7 @@
       </c>
       <c r="N290" s="81" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
@@ -19386,17 +19398,17 @@
       </c>
       <c r="B291" s="79" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Espionage Events</t>
         </is>
       </c>
       <c r="C291" s="80" t="inlineStr">
         <is>
-          <t>SPRING_OFFENSIVE_01</t>
+          <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
       <c r="D291" s="81" t="inlineStr">
         <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
@@ -19438,55 +19450,103 @@
       </c>
       <c r="N291" s="81" t="inlineStr">
         <is>
-          <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="8" customHeight="1">
-      <c r="A292" s="9" t="n"/>
-      <c r="B292" s="9" t="n"/>
-      <c r="C292" s="9" t="n"/>
-      <c r="D292" s="9" t="n"/>
-      <c r="E292" s="9" t="n"/>
-      <c r="F292" s="9" t="n"/>
-      <c r="G292" s="9" t="n"/>
-      <c r="H292" s="9" t="n"/>
-      <c r="I292" s="9" t="n"/>
-      <c r="J292" s="9" t="n"/>
-      <c r="K292" s="9" t="n"/>
-      <c r="L292" s="9" t="n"/>
-      <c r="M292" s="9" t="n"/>
-      <c r="N292" s="9" t="n"/>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="30" customHeight="1">
+      <c r="A292" s="79" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B292" s="79" t="inlineStr">
+        <is>
+          <t>Commander Expansion</t>
+        </is>
+      </c>
+      <c r="C292" s="80" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_2</t>
+        </is>
+      </c>
+      <c r="D292" s="81" t="inlineStr">
+        <is>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E292" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F292" s="81" t="inlineStr">
+        <is>
+          <t>CMD_OBJECTIVE_1</t>
+        </is>
+      </c>
+      <c r="G292" s="81" t="inlineStr">
+        <is>
+          <t>→ CMD_OBJECTIVE_3?</t>
+        </is>
+      </c>
+      <c r="H292" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I292" s="80" t="inlineStr"/>
+      <c r="J292" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K292" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L292" s="80" t="inlineStr"/>
+      <c r="M292" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N292" s="81" t="inlineStr">
+        <is>
+          <t>Extend the commander arc beyond first objective</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="30" customHeight="1">
       <c r="A293" s="79" t="inlineStr">
         <is>
-          <t>Commander</t>
+          <t>Idea</t>
         </is>
       </c>
       <c r="B293" s="79" t="inlineStr">
         <is>
-          <t>Commander Arc</t>
+          <t>Seasonal Events</t>
         </is>
       </c>
       <c r="C293" s="80" t="inlineStr">
         <is>
-          <t>CMD_THANKS_INTIMATE</t>
+          <t>WINTER_SIEGE_01</t>
         </is>
       </c>
       <c r="D293" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMM... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E293" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
         </is>
       </c>
       <c r="F293" s="81" t="inlineStr">
         <is>
-          <t>CMD_THANKS (intimate choice)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G293" s="81" t="inlineStr">
@@ -19500,9 +19560,9 @@
         </is>
       </c>
       <c r="I293" s="80" t="inlineStr"/>
-      <c r="J293" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J293" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K293" s="83" t="inlineStr">
@@ -19518,269 +19578,269 @@
       </c>
       <c r="N293" s="81" t="inlineStr">
         <is>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="79" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B294" s="79" t="inlineStr">
+        <is>
+          <t>Seasonal Events</t>
+        </is>
+      </c>
+      <c r="C294" s="80" t="inlineStr">
+        <is>
+          <t>SPRING_OFFENSIVE_01</t>
+        </is>
+      </c>
+      <c r="D294" s="81" t="inlineStr">
+        <is>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F294" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G294" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H294" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I294" s="80" t="inlineStr"/>
+      <c r="J294" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K294" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L294" s="80" t="inlineStr"/>
+      <c r="M294" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N294" s="81" t="inlineStr">
+        <is>
+          <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="8" customHeight="1">
+      <c r="A295" s="9" t="n"/>
+      <c r="B295" s="9" t="n"/>
+      <c r="C295" s="9" t="n"/>
+      <c r="D295" s="9" t="n"/>
+      <c r="E295" s="9" t="n"/>
+      <c r="F295" s="9" t="n"/>
+      <c r="G295" s="9" t="n"/>
+      <c r="H295" s="9" t="n"/>
+      <c r="I295" s="9" t="n"/>
+      <c r="J295" s="9" t="n"/>
+      <c r="K295" s="9" t="n"/>
+      <c r="L295" s="9" t="n"/>
+      <c r="M295" s="9" t="n"/>
+      <c r="N295" s="9" t="n"/>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="79" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B296" s="79" t="inlineStr">
+        <is>
+          <t>Commander Arc</t>
+        </is>
+      </c>
+      <c r="C296" s="80" t="inlineStr">
+        <is>
+          <t>CMD_THANKS_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D296" s="81" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMM... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E296" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F296" s="81" t="inlineStr">
+        <is>
+          <t>CMD_THANKS (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G296" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H296" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I296" s="80" t="inlineStr"/>
+      <c r="J296" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K296" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L296" s="80" t="inlineStr"/>
+      <c r="M296" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N296" s="81" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of CMD_THANKS. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="8" customHeight="1">
-      <c r="A294" s="9" t="n"/>
-      <c r="B294" s="9" t="n"/>
-      <c r="C294" s="9" t="n"/>
-      <c r="D294" s="9" t="n"/>
-      <c r="E294" s="9" t="n"/>
-      <c r="F294" s="9" t="n"/>
-      <c r="G294" s="9" t="n"/>
-      <c r="H294" s="9" t="n"/>
-      <c r="I294" s="9" t="n"/>
-      <c r="J294" s="9" t="n"/>
-      <c r="K294" s="9" t="n"/>
-      <c r="L294" s="9" t="n"/>
-      <c r="M294" s="9" t="n"/>
-      <c r="N294" s="9" t="n"/>
-    </row>
-    <row r="295" ht="30" customHeight="1">
-      <c r="A295" s="79" t="inlineStr">
+    <row r="297" ht="8" customHeight="1">
+      <c r="A297" s="9" t="n"/>
+      <c r="B297" s="9" t="n"/>
+      <c r="C297" s="9" t="n"/>
+      <c r="D297" s="9" t="n"/>
+      <c r="E297" s="9" t="n"/>
+      <c r="F297" s="9" t="n"/>
+      <c r="G297" s="9" t="n"/>
+      <c r="H297" s="9" t="n"/>
+      <c r="I297" s="9" t="n"/>
+      <c r="J297" s="9" t="n"/>
+      <c r="K297" s="9" t="n"/>
+      <c r="L297" s="9" t="n"/>
+      <c r="M297" s="9" t="n"/>
+      <c r="N297" s="9" t="n"/>
+    </row>
+    <row r="298" ht="30" customHeight="1">
+      <c r="A298" s="79" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B295" s="79" t="inlineStr">
+      <c r="B298" s="79" t="inlineStr">
         <is>
           <t>Fort Disrepair</t>
         </is>
       </c>
-      <c r="C295" s="80" t="inlineStr">
+      <c r="C298" s="80" t="inlineStr">
         <is>
           <t>FORT_005_INTIMATE</t>
         </is>
       </c>
-      <c r="D295" s="81" t="inlineStr">
+      <c r="D298" s="81" t="inlineStr">
         <is>
           <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
-      <c r="E295" s="83" t="inlineStr">
+      <c r="E298" s="83" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F295" s="81" t="inlineStr">
+      <c r="F298" s="81" t="inlineStr">
         <is>
           <t>FORT_005 (intimate choice)</t>
         </is>
       </c>
-      <c r="G295" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H295" s="82" t="inlineStr">
+      <c r="G298" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H298" s="82" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I295" s="80" t="inlineStr"/>
-      <c r="J295" s="84" t="inlineStr">
+      <c r="I298" s="80" t="inlineStr"/>
+      <c r="J298" s="84" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K295" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L295" s="80" t="inlineStr"/>
-      <c r="M295" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N295" s="81" t="inlineStr">
+      <c r="K298" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L298" s="80" t="inlineStr"/>
+      <c r="M298" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N298" s="81" t="inlineStr">
         <is>
           <t>Stub — author intimate version of FORT_005. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="8" customHeight="1">
-      <c r="A296" s="9" t="n"/>
-      <c r="B296" s="9" t="n"/>
-      <c r="C296" s="9" t="n"/>
-      <c r="D296" s="9" t="n"/>
-      <c r="E296" s="9" t="n"/>
-      <c r="F296" s="9" t="n"/>
-      <c r="G296" s="9" t="n"/>
-      <c r="H296" s="9" t="n"/>
-      <c r="I296" s="9" t="n"/>
-      <c r="J296" s="9" t="n"/>
-      <c r="K296" s="9" t="n"/>
-      <c r="L296" s="9" t="n"/>
-      <c r="M296" s="9" t="n"/>
-      <c r="N296" s="9" t="n"/>
-    </row>
-    <row r="297" ht="30" customHeight="1">
-      <c r="A297" s="79" t="inlineStr">
-        <is>
-          <t>Collapse</t>
-        </is>
-      </c>
-      <c r="B297" s="79" t="inlineStr">
-        <is>
-          <t>Republic Falls</t>
-        </is>
-      </c>
-      <c r="C297" s="80" t="inlineStr">
-        <is>
-          <t>COLLAPSE_02_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D297" s="81" t="inlineStr">
-        <is>
-          <t>WASHINGTON STANDS ALONE — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E297" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F297" s="81" t="inlineStr">
-        <is>
-          <t>COLLAPSE_02 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G297" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H297" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I297" s="80" t="inlineStr"/>
-      <c r="J297" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K297" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L297" s="80" t="inlineStr"/>
-      <c r="M297" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N297" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of COLLAPSE_02. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="8" customHeight="1">
-      <c r="A298" s="9" t="n"/>
-      <c r="B298" s="9" t="n"/>
-      <c r="C298" s="9" t="n"/>
-      <c r="D298" s="9" t="n"/>
-      <c r="E298" s="9" t="n"/>
-      <c r="F298" s="9" t="n"/>
-      <c r="G298" s="9" t="n"/>
-      <c r="H298" s="9" t="n"/>
-      <c r="I298" s="9" t="n"/>
-      <c r="J298" s="9" t="n"/>
-      <c r="K298" s="9" t="n"/>
-      <c r="L298" s="9" t="n"/>
-      <c r="M298" s="9" t="n"/>
-      <c r="N298" s="9" t="n"/>
-    </row>
-    <row r="299" ht="30" customHeight="1">
-      <c r="A299" s="79" t="inlineStr">
-        <is>
-          <t>Tile Crisis</t>
-        </is>
-      </c>
-      <c r="B299" s="79" t="inlineStr">
-        <is>
-          <t>Harvest Crisis</t>
-        </is>
-      </c>
-      <c r="C299" s="80" t="inlineStr">
-        <is>
-          <t>HARVEST_VISIT_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D299" s="81" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE SAVES THE HARVEST — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E299" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F299" s="81" t="inlineStr">
-        <is>
-          <t>HARVEST_VISIT_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G299" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H299" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I299" s="80" t="inlineStr"/>
-      <c r="J299" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K299" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L299" s="80" t="inlineStr"/>
-      <c r="M299" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N299" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of HARVEST_VISIT_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+    <row r="299" ht="8" customHeight="1">
+      <c r="A299" s="9" t="n"/>
+      <c r="B299" s="9" t="n"/>
+      <c r="C299" s="9" t="n"/>
+      <c r="D299" s="9" t="n"/>
+      <c r="E299" s="9" t="n"/>
+      <c r="F299" s="9" t="n"/>
+      <c r="G299" s="9" t="n"/>
+      <c r="H299" s="9" t="n"/>
+      <c r="I299" s="9" t="n"/>
+      <c r="J299" s="9" t="n"/>
+      <c r="K299" s="9" t="n"/>
+      <c r="L299" s="9" t="n"/>
+      <c r="M299" s="9" t="n"/>
+      <c r="N299" s="9" t="n"/>
     </row>
     <row r="300" ht="30" customHeight="1">
       <c r="A300" s="79" t="inlineStr">
         <is>
-          <t>Tile Crisis</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="B300" s="79" t="inlineStr">
         <is>
-          <t>Election Arc</t>
+          <t>Republic Falls</t>
         </is>
       </c>
       <c r="C300" s="80" t="inlineStr">
         <is>
-          <t>STUMP_SPEECH_01_INTIMATE</t>
+          <t>COLLAPSE_02_INTIMATE</t>
         </is>
       </c>
       <c r="D300" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — ... — BY MORNING</t>
+          <t>WASHINGTON STANDS ALONE — BY MORNING</t>
         </is>
       </c>
       <c r="E300" s="83" t="inlineStr">
@@ -19790,7 +19850,7 @@
       </c>
       <c r="F300" s="81" t="inlineStr">
         <is>
-          <t>STUMP_SPEECH_01 (intimate choice)</t>
+          <t>COLLAPSE_02 (intimate choice)</t>
         </is>
       </c>
       <c r="G300" s="81" t="inlineStr">
@@ -19822,7 +19882,7 @@
       </c>
       <c r="N300" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of STUMP_SPEECH_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of COLLAPSE_02. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -19845,22 +19905,22 @@
     <row r="302" ht="30" customHeight="1">
       <c r="A302" s="79" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Tile Crisis</t>
         </is>
       </c>
       <c r="B302" s="79" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Harvest Crisis</t>
         </is>
       </c>
       <c r="C302" s="80" t="inlineStr">
         <is>
-          <t>VP_DOUBT_INTIMATE</t>
+          <t>HARVEST_VISIT_01_INTIMATE</t>
         </is>
       </c>
       <c r="D302" s="81" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QU... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE SAVES THE HARVEST — BY MORNING</t>
         </is>
       </c>
       <c r="E302" s="83" t="inlineStr">
@@ -19870,7 +19930,7 @@
       </c>
       <c r="F302" s="81" t="inlineStr">
         <is>
-          <t>VP_DOUBT (intimate choice)</t>
+          <t>HARVEST_VISIT_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G302" s="81" t="inlineStr">
@@ -19902,29 +19962,29 @@
       </c>
       <c r="N302" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of VP_DOUBT. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of HARVEST_VISIT_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1">
       <c r="A303" s="79" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Tile Crisis</t>
         </is>
       </c>
       <c r="B303" s="79" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Election Arc</t>
         </is>
       </c>
       <c r="C303" s="80" t="inlineStr">
         <is>
-          <t>VP_BATTLEFIELD_INTIMATE</t>
+          <t>STUMP_SPEECH_01_INTIMATE</t>
         </is>
       </c>
       <c r="D303" s="81" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAM... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — ... — BY MORNING</t>
         </is>
       </c>
       <c r="E303" s="83" t="inlineStr">
@@ -19934,7 +19994,7 @@
       </c>
       <c r="F303" s="81" t="inlineStr">
         <is>
-          <t>VP_BATTLEFIELD (intimate choice)</t>
+          <t>STUMP_SPEECH_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G303" s="81" t="inlineStr">
@@ -19966,73 +20026,25 @@
       </c>
       <c r="N303" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of VP_BATTLEFIELD. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="30" customHeight="1">
-      <c r="A304" s="79" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="B304" s="79" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="C304" s="80" t="inlineStr">
-        <is>
-          <t>VP_PRE_ELECTION_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D304" s="81" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [C... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E304" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F304" s="81" t="inlineStr">
-        <is>
-          <t>VP_PRE_ELECTION (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G304" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H304" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I304" s="80" t="inlineStr"/>
-      <c r="J304" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K304" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L304" s="80" t="inlineStr"/>
-      <c r="M304" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N304" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of VP_PRE_ELECTION. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of STUMP_SPEECH_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="8" customHeight="1">
+      <c r="A304" s="9" t="n"/>
+      <c r="B304" s="9" t="n"/>
+      <c r="C304" s="9" t="n"/>
+      <c r="D304" s="9" t="n"/>
+      <c r="E304" s="9" t="n"/>
+      <c r="F304" s="9" t="n"/>
+      <c r="G304" s="9" t="n"/>
+      <c r="H304" s="9" t="n"/>
+      <c r="I304" s="9" t="n"/>
+      <c r="J304" s="9" t="n"/>
+      <c r="K304" s="9" t="n"/>
+      <c r="L304" s="9" t="n"/>
+      <c r="M304" s="9" t="n"/>
+      <c r="N304" s="9" t="n"/>
     </row>
     <row r="305" ht="30" customHeight="1">
       <c r="A305" s="79" t="inlineStr">
@@ -20047,12 +20059,12 @@
       </c>
       <c r="C305" s="80" t="inlineStr">
         <is>
-          <t>VP_LEGACY_INTIMATE</t>
+          <t>VP_DOUBT_INTIMATE</t>
         </is>
       </c>
       <c r="D305" s="81" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] ... — BY MORNING</t>
+          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QU... — BY MORNING</t>
         </is>
       </c>
       <c r="E305" s="83" t="inlineStr">
@@ -20062,7 +20074,7 @@
       </c>
       <c r="F305" s="81" t="inlineStr">
         <is>
-          <t>VP_LEGACY (intimate choice)</t>
+          <t>VP_DOUBT (intimate choice)</t>
         </is>
       </c>
       <c r="G305" s="81" t="inlineStr">
@@ -20094,45 +20106,93 @@
       </c>
       <c r="N305" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of VP_LEGACY. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="8" customHeight="1">
-      <c r="A306" s="9" t="n"/>
-      <c r="B306" s="9" t="n"/>
-      <c r="C306" s="9" t="n"/>
-      <c r="D306" s="9" t="n"/>
-      <c r="E306" s="9" t="n"/>
-      <c r="F306" s="9" t="n"/>
-      <c r="G306" s="9" t="n"/>
-      <c r="H306" s="9" t="n"/>
-      <c r="I306" s="9" t="n"/>
-      <c r="J306" s="9" t="n"/>
-      <c r="K306" s="9" t="n"/>
-      <c r="L306" s="9" t="n"/>
-      <c r="M306" s="9" t="n"/>
-      <c r="N306" s="9" t="n"/>
+          <t>Stub — author intimate version of VP_DOUBT. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="79" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B306" s="79" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C306" s="80" t="inlineStr">
+        <is>
+          <t>VP_BATTLEFIELD_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D306" s="81" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAM... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E306" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F306" s="81" t="inlineStr">
+        <is>
+          <t>VP_BATTLEFIELD (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G306" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H306" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I306" s="80" t="inlineStr"/>
+      <c r="J306" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K306" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L306" s="80" t="inlineStr"/>
+      <c r="M306" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N306" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of VP_BATTLEFIELD. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="30" customHeight="1">
       <c r="A307" s="79" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B307" s="79" t="inlineStr">
         <is>
-          <t>Canadian Alliance</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C307" s="80" t="inlineStr">
         <is>
-          <t>CAN_CLEARWATER_01_INTIMATE</t>
+          <t>VP_PRE_ELECTION_INTIMATE</t>
         </is>
       </c>
       <c r="D307" s="81" t="inlineStr">
         <is>
-          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
+          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [C... — BY MORNING</t>
         </is>
       </c>
       <c r="E307" s="83" t="inlineStr">
@@ -20142,7 +20202,7 @@
       </c>
       <c r="F307" s="81" t="inlineStr">
         <is>
-          <t>CAN_CLEARWATER_01 (intimate choice)</t>
+          <t>VP_PRE_ELECTION (intimate choice)</t>
         </is>
       </c>
       <c r="G307" s="81" t="inlineStr">
@@ -20174,29 +20234,29 @@
       </c>
       <c r="N307" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of VP_PRE_ELECTION. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="308" ht="30" customHeight="1">
       <c r="A308" s="79" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B308" s="79" t="inlineStr">
         <is>
-          <t>Canadian Alliance</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C308" s="80" t="inlineStr">
         <is>
-          <t>CAN_JOINT_OPS_01_INTIMATE</t>
+          <t>VP_LEGACY_INTIMATE</t>
         </is>
       </c>
       <c r="D308" s="81" t="inlineStr">
         <is>
-          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] ... — BY MORNING</t>
         </is>
       </c>
       <c r="E308" s="83" t="inlineStr">
@@ -20206,7 +20266,7 @@
       </c>
       <c r="F308" s="81" t="inlineStr">
         <is>
-          <t>CAN_JOINT_OPS_01 (intimate choice)</t>
+          <t>VP_LEGACY (intimate choice)</t>
         </is>
       </c>
       <c r="G308" s="81" t="inlineStr">
@@ -20238,73 +20298,25 @@
       </c>
       <c r="N308" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="309" ht="30" customHeight="1">
-      <c r="A309" s="79" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B309" s="79" t="inlineStr">
-        <is>
-          <t>Canadian Alliance</t>
-        </is>
-      </c>
-      <c r="C309" s="80" t="inlineStr">
-        <is>
-          <t>CAN_SUMMIT_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D309" s="81" t="inlineStr">
-        <is>
-          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E309" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F309" s="81" t="inlineStr">
-        <is>
-          <t>CAN_SUMMIT_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G309" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H309" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I309" s="80" t="inlineStr"/>
-      <c r="J309" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K309" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L309" s="80" t="inlineStr"/>
-      <c r="M309" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N309" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of VP_LEGACY. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="8" customHeight="1">
+      <c r="A309" s="9" t="n"/>
+      <c r="B309" s="9" t="n"/>
+      <c r="C309" s="9" t="n"/>
+      <c r="D309" s="9" t="n"/>
+      <c r="E309" s="9" t="n"/>
+      <c r="F309" s="9" t="n"/>
+      <c r="G309" s="9" t="n"/>
+      <c r="H309" s="9" t="n"/>
+      <c r="I309" s="9" t="n"/>
+      <c r="J309" s="9" t="n"/>
+      <c r="K309" s="9" t="n"/>
+      <c r="L309" s="9" t="n"/>
+      <c r="M309" s="9" t="n"/>
+      <c r="N309" s="9" t="n"/>
     </row>
     <row r="310" ht="30" customHeight="1">
       <c r="A310" s="79" t="inlineStr">
@@ -20319,12 +20331,12 @@
       </c>
       <c r="C310" s="80" t="inlineStr">
         <is>
-          <t>CAN_ELECTION_LUCK_INTIMATE</t>
+          <t>CAN_CLEARWATER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D310" s="81" t="inlineStr">
         <is>
-          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
         </is>
       </c>
       <c r="E310" s="83" t="inlineStr">
@@ -20334,7 +20346,7 @@
       </c>
       <c r="F310" s="81" t="inlineStr">
         <is>
-          <t>CAN_ELECTION_LUCK (intimate choice)</t>
+          <t>CAN_CLEARWATER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G310" s="81" t="inlineStr">
@@ -20366,7 +20378,7 @@
       </c>
       <c r="N310" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20378,17 +20390,17 @@
       </c>
       <c r="B311" s="79" t="inlineStr">
         <is>
-          <t>Peace</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C311" s="80" t="inlineStr">
         <is>
-          <t>CAN_PEACE_01_INTIMATE</t>
+          <t>CAN_JOINT_OPS_01_INTIMATE</t>
         </is>
       </c>
       <c r="D311" s="81" t="inlineStr">
         <is>
-          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
         </is>
       </c>
       <c r="E311" s="83" t="inlineStr">
@@ -20398,7 +20410,7 @@
       </c>
       <c r="F311" s="81" t="inlineStr">
         <is>
-          <t>CAN_PEACE_01 (intimate choice)</t>
+          <t>CAN_JOINT_OPS_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G311" s="81" t="inlineStr">
@@ -20430,7 +20442,7 @@
       </c>
       <c r="N311" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20442,17 +20454,17 @@
       </c>
       <c r="B312" s="79" t="inlineStr">
         <is>
-          <t>Peace</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C312" s="80" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01_INTIMATE</t>
+          <t>CAN_SUMMIT_01_INTIMATE</t>
         </is>
       </c>
       <c r="D312" s="81" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
         </is>
       </c>
       <c r="E312" s="83" t="inlineStr">
@@ -20462,7 +20474,7 @@
       </c>
       <c r="F312" s="81" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01 (intimate choice)</t>
+          <t>CAN_SUMMIT_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G312" s="81" t="inlineStr">
@@ -20494,7 +20506,7 @@
       </c>
       <c r="N312" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20506,17 +20518,17 @@
       </c>
       <c r="B313" s="79" t="inlineStr">
         <is>
-          <t>Peace</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C313" s="80" t="inlineStr">
         <is>
-          <t>PEACE_USA_01_INTIMATE</t>
+          <t>CAN_ELECTION_LUCK_INTIMATE</t>
         </is>
       </c>
       <c r="D313" s="81" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
         </is>
       </c>
       <c r="E313" s="83" t="inlineStr">
@@ -20526,7 +20538,7 @@
       </c>
       <c r="F313" s="81" t="inlineStr">
         <is>
-          <t>PEACE_USA_01 (intimate choice)</t>
+          <t>CAN_ELECTION_LUCK (intimate choice)</t>
         </is>
       </c>
       <c r="G313" s="81" t="inlineStr">
@@ -20558,45 +20570,93 @@
       </c>
       <c r="N313" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="8" customHeight="1">
-      <c r="A314" s="9" t="n"/>
-      <c r="B314" s="9" t="n"/>
-      <c r="C314" s="9" t="n"/>
-      <c r="D314" s="9" t="n"/>
-      <c r="E314" s="9" t="n"/>
-      <c r="F314" s="9" t="n"/>
-      <c r="G314" s="9" t="n"/>
-      <c r="H314" s="9" t="n"/>
-      <c r="I314" s="9" t="n"/>
-      <c r="J314" s="9" t="n"/>
-      <c r="K314" s="9" t="n"/>
-      <c r="L314" s="9" t="n"/>
-      <c r="M314" s="9" t="n"/>
-      <c r="N314" s="9" t="n"/>
+          <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="79" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B314" s="79" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C314" s="80" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D314" s="81" t="inlineStr">
+        <is>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E314" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F314" s="81" t="inlineStr">
+        <is>
+          <t>CAN_PEACE_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G314" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H314" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I314" s="80" t="inlineStr"/>
+      <c r="J314" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K314" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L314" s="80" t="inlineStr"/>
+      <c r="M314" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N314" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="30" customHeight="1">
       <c r="A315" s="79" t="inlineStr">
         <is>
-          <t>CA Protector</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B315" s="79" t="inlineStr">
         <is>
-          <t>Le Wendigo</t>
+          <t>Peace</t>
         </is>
       </c>
       <c r="C315" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE_INTIMATE</t>
+          <t>PEACE_ALLIED_01_INTIMATE</t>
         </is>
       </c>
       <c r="D315" s="81" t="inlineStr">
         <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
         </is>
       </c>
       <c r="E315" s="83" t="inlineStr">
@@ -20606,7 +20666,7 @@
       </c>
       <c r="F315" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE (intimate choice)</t>
+          <t>PEACE_ALLIED_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G315" s="81" t="inlineStr">
@@ -20638,29 +20698,29 @@
       </c>
       <c r="N315" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="79" t="inlineStr">
         <is>
-          <t>CA Protector</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B316" s="79" t="inlineStr">
         <is>
-          <t>Le Loup-Garou</t>
+          <t>Peace</t>
         </is>
       </c>
       <c r="C316" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE_INTIMATE</t>
+          <t>PEACE_USA_01_INTIMATE</t>
         </is>
       </c>
       <c r="D316" s="81" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E316" s="83" t="inlineStr">
@@ -20670,7 +20730,7 @@
       </c>
       <c r="F316" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE (intimate choice)</t>
+          <t>PEACE_USA_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G316" s="81" t="inlineStr">
@@ -20702,73 +20762,25 @@
       </c>
       <c r="N316" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="317" ht="30" customHeight="1">
-      <c r="A317" s="79" t="inlineStr">
-        <is>
-          <t>CA Protector</t>
-        </is>
-      </c>
-      <c r="B317" s="79" t="inlineStr">
-        <is>
-          <t>Les Feux Follets</t>
-        </is>
-      </c>
-      <c r="C317" s="80" t="inlineStr">
-        <is>
-          <t>CA_PROT_03_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D317" s="81" t="inlineStr">
-        <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E317" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F317" s="81" t="inlineStr">
-        <is>
-          <t>CA_PROT_03_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G317" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H317" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I317" s="80" t="inlineStr"/>
-      <c r="J317" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K317" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L317" s="80" t="inlineStr"/>
-      <c r="M317" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N317" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="8" customHeight="1">
+      <c r="A317" s="9" t="n"/>
+      <c r="B317" s="9" t="n"/>
+      <c r="C317" s="9" t="n"/>
+      <c r="D317" s="9" t="n"/>
+      <c r="E317" s="9" t="n"/>
+      <c r="F317" s="9" t="n"/>
+      <c r="G317" s="9" t="n"/>
+      <c r="H317" s="9" t="n"/>
+      <c r="I317" s="9" t="n"/>
+      <c r="J317" s="9" t="n"/>
+      <c r="K317" s="9" t="n"/>
+      <c r="L317" s="9" t="n"/>
+      <c r="M317" s="9" t="n"/>
+      <c r="N317" s="9" t="n"/>
     </row>
     <row r="318" ht="30" customHeight="1">
       <c r="A318" s="79" t="inlineStr">
@@ -20778,17 +20790,17 @@
       </c>
       <c r="B318" s="79" t="inlineStr">
         <is>
-          <t>Mishepeshu</t>
+          <t>Le Wendigo</t>
         </is>
       </c>
       <c r="C318" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE_INTIMATE</t>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D318" s="81" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
         </is>
       </c>
       <c r="E318" s="83" t="inlineStr">
@@ -20798,7 +20810,7 @@
       </c>
       <c r="F318" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE (intimate choice)</t>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G318" s="81" t="inlineStr">
@@ -20830,7 +20842,7 @@
       </c>
       <c r="N318" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20842,17 +20854,17 @@
       </c>
       <c r="B319" s="79" t="inlineStr">
         <is>
-          <t>La Corriveau</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C319" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE_INTIMATE</t>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D319" s="81" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
       <c r="E319" s="83" t="inlineStr">
@@ -20862,7 +20874,7 @@
       </c>
       <c r="F319" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE (intimate choice)</t>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G319" s="81" t="inlineStr">
@@ -20894,7 +20906,7 @@
       </c>
       <c r="N319" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20906,17 +20918,17 @@
       </c>
       <c r="B320" s="79" t="inlineStr">
         <is>
-          <t>Le Carcajou</t>
+          <t>Les Feux Follets</t>
         </is>
       </c>
       <c r="C320" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE_INTIMATE</t>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D320" s="81" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
       <c r="E320" s="83" t="inlineStr">
@@ -20926,7 +20938,7 @@
       </c>
       <c r="F320" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_06_AGREE (intimate choice)</t>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G320" s="81" t="inlineStr">
@@ -20958,7 +20970,7 @@
       </c>
       <c r="N320" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20970,17 +20982,17 @@
       </c>
       <c r="B321" s="79" t="inlineStr">
         <is>
-          <t>La Chasse-Galerie</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C321" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE_INTIMATE</t>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D321" s="81" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E321" s="83" t="inlineStr">
@@ -20990,7 +21002,7 @@
       </c>
       <c r="F321" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE (intimate choice)</t>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G321" s="81" t="inlineStr">
@@ -21022,7 +21034,7 @@
       </c>
       <c r="N321" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21034,17 +21046,17 @@
       </c>
       <c r="B322" s="79" t="inlineStr">
         <is>
-          <t>Le Gougou</t>
+          <t>La Corriveau</t>
         </is>
       </c>
       <c r="C322" s="80" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE_INTIMATE</t>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D322" s="81" t="inlineStr">
         <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
       <c r="E322" s="83" t="inlineStr">
@@ -21054,7 +21066,7 @@
       </c>
       <c r="F322" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE (intimate choice)</t>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G322" s="81" t="inlineStr">
@@ -21086,45 +21098,93 @@
       </c>
       <c r="N322" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="323" ht="8" customHeight="1">
-      <c r="A323" s="9" t="n"/>
-      <c r="B323" s="9" t="n"/>
-      <c r="C323" s="9" t="n"/>
-      <c r="D323" s="9" t="n"/>
-      <c r="E323" s="9" t="n"/>
-      <c r="F323" s="9" t="n"/>
-      <c r="G323" s="9" t="n"/>
-      <c r="H323" s="9" t="n"/>
-      <c r="I323" s="9" t="n"/>
-      <c r="J323" s="9" t="n"/>
-      <c r="K323" s="9" t="n"/>
-      <c r="L323" s="9" t="n"/>
-      <c r="M323" s="9" t="n"/>
-      <c r="N323" s="9" t="n"/>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="30" customHeight="1">
+      <c r="A323" s="79" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B323" s="79" t="inlineStr">
+        <is>
+          <t>Le Carcajou</t>
+        </is>
+      </c>
+      <c r="C323" s="80" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D323" s="81" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E323" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F323" s="81" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G323" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H323" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I323" s="80" t="inlineStr"/>
+      <c r="J323" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K323" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L323" s="80" t="inlineStr"/>
+      <c r="M323" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N323" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="30" customHeight="1">
       <c r="A324" s="79" t="inlineStr">
         <is>
-          <t>Ualani</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B324" s="79" t="inlineStr">
         <is>
-          <t>Ambush</t>
+          <t>La Chasse-Galerie</t>
         </is>
       </c>
       <c r="C324" s="80" t="inlineStr">
         <is>
-          <t>UALANI_AMBUSH_01_INTIMATE</t>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D324" s="81" t="inlineStr">
         <is>
-          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
       <c r="E324" s="83" t="inlineStr">
@@ -21134,7 +21194,7 @@
       </c>
       <c r="F324" s="81" t="inlineStr">
         <is>
-          <t>UALANI_AMBUSH_01 (intimate choice)</t>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G324" s="81" t="inlineStr">
@@ -21166,29 +21226,29 @@
       </c>
       <c r="N324" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="325" ht="30" customHeight="1">
       <c r="A325" s="79" t="inlineStr">
         <is>
-          <t>Ualani</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B325" s="79" t="inlineStr">
         <is>
-          <t>Dignitary Reception</t>
+          <t>Le Gougou</t>
         </is>
       </c>
       <c r="C325" s="80" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01_INTIMATE</t>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D325" s="81" t="inlineStr">
         <is>
-          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
         </is>
       </c>
       <c r="E325" s="83" t="inlineStr">
@@ -21198,7 +21258,7 @@
       </c>
       <c r="F325" s="81" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G325" s="81" t="inlineStr">
@@ -21230,73 +21290,25 @@
       </c>
       <c r="N325" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="30" customHeight="1">
-      <c r="A326" s="79" t="inlineStr">
-        <is>
-          <t>Ualani</t>
-        </is>
-      </c>
-      <c r="B326" s="79" t="inlineStr">
-        <is>
-          <t>Memorial Address</t>
-        </is>
-      </c>
-      <c r="C326" s="80" t="inlineStr">
-        <is>
-          <t>UALANI_MEMORIAL_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D326" s="81" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E326" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F326" s="81" t="inlineStr">
-        <is>
-          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G326" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H326" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I326" s="80" t="inlineStr"/>
-      <c r="J326" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K326" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L326" s="80" t="inlineStr"/>
-      <c r="M326" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N326" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="8" customHeight="1">
+      <c r="A326" s="9" t="n"/>
+      <c r="B326" s="9" t="n"/>
+      <c r="C326" s="9" t="n"/>
+      <c r="D326" s="9" t="n"/>
+      <c r="E326" s="9" t="n"/>
+      <c r="F326" s="9" t="n"/>
+      <c r="G326" s="9" t="n"/>
+      <c r="H326" s="9" t="n"/>
+      <c r="I326" s="9" t="n"/>
+      <c r="J326" s="9" t="n"/>
+      <c r="K326" s="9" t="n"/>
+      <c r="L326" s="9" t="n"/>
+      <c r="M326" s="9" t="n"/>
+      <c r="N326" s="9" t="n"/>
     </row>
     <row r="327" ht="30" customHeight="1">
       <c r="A327" s="79" t="inlineStr">
@@ -21306,17 +21318,17 @@
       </c>
       <c r="B327" s="79" t="inlineStr">
         <is>
-          <t>Field Hospital</t>
+          <t>Ambush</t>
         </is>
       </c>
       <c r="C327" s="80" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01_INTIMATE</t>
+          <t>UALANI_AMBUSH_01_INTIMATE</t>
         </is>
       </c>
       <c r="D327" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
+          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
         </is>
       </c>
       <c r="E327" s="83" t="inlineStr">
@@ -21326,7 +21338,7 @@
       </c>
       <c r="F327" s="81" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01 (intimate choice)</t>
+          <t>UALANI_AMBUSH_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G327" s="81" t="inlineStr">
@@ -21358,7 +21370,7 @@
       </c>
       <c r="N327" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21370,17 +21382,17 @@
       </c>
       <c r="B328" s="79" t="inlineStr">
         <is>
-          <t>Forge Inspection</t>
+          <t>Dignitary Reception</t>
         </is>
       </c>
       <c r="C328" s="80" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01_INTIMATE</t>
+          <t>UALANI_DIGNITARY_01_INTIMATE</t>
         </is>
       </c>
       <c r="D328" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
+          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
         </is>
       </c>
       <c r="E328" s="83" t="inlineStr">
@@ -21390,7 +21402,7 @@
       </c>
       <c r="F328" s="81" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01 (intimate choice)</t>
+          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G328" s="81" t="inlineStr">
@@ -21422,7 +21434,7 @@
       </c>
       <c r="N328" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21434,17 +21446,17 @@
       </c>
       <c r="B329" s="79" t="inlineStr">
         <is>
-          <t>Culper Ring</t>
+          <t>Memorial Address</t>
         </is>
       </c>
       <c r="C329" s="80" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01_INTIMATE</t>
+          <t>UALANI_MEMORIAL_01_INTIMATE</t>
         </is>
       </c>
       <c r="D329" s="81" t="inlineStr">
         <is>
-          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E329" s="83" t="inlineStr">
@@ -21454,7 +21466,7 @@
       </c>
       <c r="F329" s="81" t="inlineStr">
         <is>
-          <t>UALANI_CULPER_01 (intimate choice)</t>
+          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G329" s="81" t="inlineStr">
@@ -21486,7 +21498,7 @@
       </c>
       <c r="N329" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21498,17 +21510,17 @@
       </c>
       <c r="B330" s="79" t="inlineStr">
         <is>
-          <t>Alliance Council</t>
+          <t>Field Hospital</t>
         </is>
       </c>
       <c r="C330" s="80" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01_INTIMATE</t>
+          <t>UALANI_WOUNDED_01_INTIMATE</t>
         </is>
       </c>
       <c r="D330" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
       <c r="E330" s="83" t="inlineStr">
@@ -21518,7 +21530,7 @@
       </c>
       <c r="F330" s="81" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
+          <t>UALANI_WOUNDED_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G330" s="81" t="inlineStr">
@@ -21550,7 +21562,7 @@
       </c>
       <c r="N330" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21562,17 +21574,17 @@
       </c>
       <c r="B331" s="79" t="inlineStr">
         <is>
-          <t>Frontier</t>
+          <t>Forge Inspection</t>
         </is>
       </c>
       <c r="C331" s="80" t="inlineStr">
         <is>
-          <t>UALANI_FRONTIER_01_INTIMATE</t>
+          <t>UALANI_FORGE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D331" s="81" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
         </is>
       </c>
       <c r="E331" s="83" t="inlineStr">
@@ -21582,7 +21594,7 @@
       </c>
       <c r="F331" s="81" t="inlineStr">
         <is>
-          <t>UALANI_FRONTIER_01 (intimate choice)</t>
+          <t>UALANI_FORGE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G331" s="81" t="inlineStr">
@@ -21614,45 +21626,93 @@
       </c>
       <c r="N331" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="332" ht="8" customHeight="1">
-      <c r="A332" s="9" t="n"/>
-      <c r="B332" s="9" t="n"/>
-      <c r="C332" s="9" t="n"/>
-      <c r="D332" s="9" t="n"/>
-      <c r="E332" s="9" t="n"/>
-      <c r="F332" s="9" t="n"/>
-      <c r="G332" s="9" t="n"/>
-      <c r="H332" s="9" t="n"/>
-      <c r="I332" s="9" t="n"/>
-      <c r="J332" s="9" t="n"/>
-      <c r="K332" s="9" t="n"/>
-      <c r="L332" s="9" t="n"/>
-      <c r="M332" s="9" t="n"/>
-      <c r="N332" s="9" t="n"/>
+          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="A332" s="79" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B332" s="79" t="inlineStr">
+        <is>
+          <t>Culper Ring</t>
+        </is>
+      </c>
+      <c r="C332" s="80" t="inlineStr">
+        <is>
+          <t>UALANI_CULPER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D332" s="81" t="inlineStr">
+        <is>
+          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E332" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F332" s="81" t="inlineStr">
+        <is>
+          <t>UALANI_CULPER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G332" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H332" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I332" s="80" t="inlineStr"/>
+      <c r="J332" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K332" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L332" s="80" t="inlineStr"/>
+      <c r="M332" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N332" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="30" customHeight="1">
       <c r="A333" s="79" t="inlineStr">
         <is>
-          <t>Protector</t>
+          <t>Ualani</t>
         </is>
       </c>
       <c r="B333" s="79" t="inlineStr">
         <is>
-          <t>Mothman</t>
+          <t>Alliance Council</t>
         </is>
       </c>
       <c r="C333" s="80" t="inlineStr">
         <is>
-          <t>PROT_01_AGREE_INTIMATE</t>
+          <t>UALANI_ALLIANCE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D333" s="81" t="inlineStr">
         <is>
-          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
+          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
         </is>
       </c>
       <c r="E333" s="83" t="inlineStr">
@@ -21662,7 +21722,7 @@
       </c>
       <c r="F333" s="81" t="inlineStr">
         <is>
-          <t>PROT_01_AGREE (intimate choice)</t>
+          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G333" s="81" t="inlineStr">
@@ -21694,141 +21754,89 @@
       </c>
       <c r="N333" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="334" ht="30" customHeight="1">
-      <c r="A334" s="23" t="inlineStr">
-        <is>
-          <t>Protector</t>
-        </is>
-      </c>
-      <c r="B334" s="23" t="inlineStr">
-        <is>
-          <t>Jersey Devil</t>
-        </is>
-      </c>
-      <c r="C334" s="24" t="inlineStr">
-        <is>
-          <t>PROT_02_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D334" s="25" t="inlineStr">
-        <is>
-          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E334" s="29" t="inlineStr">
+      <c r="A334" s="79" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B334" s="79" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="C334" s="80" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D334" s="81" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E334" s="83" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F334" s="25" t="inlineStr">
-        <is>
-          <t>PROT_02_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G334" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H334" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I334" s="24" t="inlineStr">
-        <is>
-          <t>prot_02_agree_intimate</t>
-        </is>
-      </c>
-      <c r="J334" s="27" t="inlineStr">
-        <is>
-          <t>Integrated</t>
-        </is>
-      </c>
-      <c r="K334" s="29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L334" s="24" t="inlineStr"/>
-      <c r="M334" s="29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N334" s="25" t="inlineStr">
-        <is>
-          <t>New Jersey's most complicated asset. By morning: recognition without negotiation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="30" customHeight="1">
-      <c r="A335" s="79" t="inlineStr">
-        <is>
-          <t>Protector</t>
-        </is>
-      </c>
-      <c r="B335" s="79" t="inlineStr">
-        <is>
-          <t>Bigfoot</t>
-        </is>
-      </c>
-      <c r="C335" s="80" t="inlineStr">
-        <is>
-          <t>PROT_03_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D335" s="81" t="inlineStr">
-        <is>
-          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E335" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F335" s="81" t="inlineStr">
-        <is>
-          <t>PROT_03_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G335" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H335" s="82" t="inlineStr">
+      <c r="F334" s="81" t="inlineStr">
+        <is>
+          <t>UALANI_FRONTIER_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G334" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H334" s="82" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I335" s="80" t="inlineStr"/>
-      <c r="J335" s="84" t="inlineStr">
+      <c r="I334" s="80" t="inlineStr"/>
+      <c r="J334" s="84" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K335" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L335" s="80" t="inlineStr"/>
-      <c r="M335" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N335" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+      <c r="K334" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L334" s="80" t="inlineStr"/>
+      <c r="M334" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N334" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="8" customHeight="1">
+      <c r="A335" s="9" t="n"/>
+      <c r="B335" s="9" t="n"/>
+      <c r="C335" s="9" t="n"/>
+      <c r="D335" s="9" t="n"/>
+      <c r="E335" s="9" t="n"/>
+      <c r="F335" s="9" t="n"/>
+      <c r="G335" s="9" t="n"/>
+      <c r="H335" s="9" t="n"/>
+      <c r="I335" s="9" t="n"/>
+      <c r="J335" s="9" t="n"/>
+      <c r="K335" s="9" t="n"/>
+      <c r="L335" s="9" t="n"/>
+      <c r="M335" s="9" t="n"/>
+      <c r="N335" s="9" t="n"/>
     </row>
     <row r="336" ht="30" customHeight="1">
       <c r="A336" s="79" t="inlineStr">
@@ -21838,17 +21846,17 @@
       </c>
       <c r="B336" s="79" t="inlineStr">
         <is>
-          <t>Thunderbird</t>
+          <t>Mothman</t>
         </is>
       </c>
       <c r="C336" s="80" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE_INTIMATE</t>
+          <t>PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D336" s="81" t="inlineStr">
         <is>
-          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
+          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E336" s="83" t="inlineStr">
@@ -21858,7 +21866,7 @@
       </c>
       <c r="F336" s="81" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE (intimate choice)</t>
+          <t>PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G336" s="81" t="inlineStr">
@@ -21890,71 +21898,75 @@
       </c>
       <c r="N336" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="337" ht="30" customHeight="1">
-      <c r="A337" s="79" t="inlineStr">
+      <c r="A337" s="23" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B337" s="79" t="inlineStr">
-        <is>
-          <t>Headless Horseman</t>
-        </is>
-      </c>
-      <c r="C337" s="80" t="inlineStr">
-        <is>
-          <t>PROT_05_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D337" s="81" t="inlineStr">
-        <is>
-          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E337" s="83" t="inlineStr">
+      <c r="B337" s="23" t="inlineStr">
+        <is>
+          <t>Jersey Devil</t>
+        </is>
+      </c>
+      <c r="C337" s="24" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D337" s="25" t="inlineStr">
+        <is>
+          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E337" s="29" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F337" s="81" t="inlineStr">
-        <is>
-          <t>PROT_05_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G337" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H337" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I337" s="80" t="inlineStr"/>
-      <c r="J337" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K337" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L337" s="80" t="inlineStr"/>
-      <c r="M337" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N337" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+      <c r="F337" s="25" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G337" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H337" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I337" s="24" t="inlineStr">
+        <is>
+          <t>prot_02_agree_intimate</t>
+        </is>
+      </c>
+      <c r="J337" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K337" s="29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L337" s="24" t="inlineStr"/>
+      <c r="M337" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N337" s="25" t="inlineStr">
+        <is>
+          <t>New Jersey's most complicated asset. By morning: recognition without negotiation.</t>
         </is>
       </c>
     </row>
@@ -21966,17 +21978,17 @@
       </c>
       <c r="B338" s="79" t="inlineStr">
         <is>
-          <t>Chessie</t>
+          <t>Bigfoot</t>
         </is>
       </c>
       <c r="C338" s="80" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE_INTIMATE</t>
+          <t>PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D338" s="81" t="inlineStr">
         <is>
-          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
         </is>
       </c>
       <c r="E338" s="83" t="inlineStr">
@@ -21986,7 +21998,7 @@
       </c>
       <c r="F338" s="81" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE (intimate choice)</t>
+          <t>PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G338" s="81" t="inlineStr">
@@ -22018,7 +22030,7 @@
       </c>
       <c r="N338" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22030,17 +22042,17 @@
       </c>
       <c r="B339" s="79" t="inlineStr">
         <is>
-          <t>Bell Witch</t>
+          <t>Thunderbird</t>
         </is>
       </c>
       <c r="C339" s="80" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE_INTIMATE</t>
+          <t>PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D339" s="81" t="inlineStr">
         <is>
-          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
+          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
         </is>
       </c>
       <c r="E339" s="83" t="inlineStr">
@@ -22050,7 +22062,7 @@
       </c>
       <c r="F339" s="81" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE (intimate choice)</t>
+          <t>PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G339" s="81" t="inlineStr">
@@ -22082,7 +22094,7 @@
       </c>
       <c r="N339" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22094,17 +22106,17 @@
       </c>
       <c r="B340" s="79" t="inlineStr">
         <is>
-          <t>Old Ironsides</t>
+          <t>Headless Horseman</t>
         </is>
       </c>
       <c r="C340" s="80" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE_INTIMATE</t>
+          <t>PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D340" s="81" t="inlineStr">
         <is>
-          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
         </is>
       </c>
       <c r="E340" s="83" t="inlineStr">
@@ -22114,7 +22126,7 @@
       </c>
       <c r="F340" s="81" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE (intimate choice)</t>
+          <t>PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G340" s="81" t="inlineStr">
@@ -22146,7 +22158,7 @@
       </c>
       <c r="N340" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22158,17 +22170,17 @@
       </c>
       <c r="B341" s="79" t="inlineStr">
         <is>
-          <t>Valley Forge Guardian</t>
+          <t>Chessie</t>
         </is>
       </c>
       <c r="C341" s="80" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE_INTIMATE</t>
+          <t>PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D341" s="81" t="inlineStr">
         <is>
-          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
+          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E341" s="83" t="inlineStr">
@@ -22178,7 +22190,7 @@
       </c>
       <c r="F341" s="81" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE (intimate choice)</t>
+          <t>PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G341" s="81" t="inlineStr">
@@ -22210,7 +22222,7 @@
       </c>
       <c r="N341" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22222,17 +22234,17 @@
       </c>
       <c r="B342" s="79" t="inlineStr">
         <is>
-          <t>Snallygaster</t>
+          <t>Bell Witch</t>
         </is>
       </c>
       <c r="C342" s="80" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE_INTIMATE</t>
+          <t>PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D342" s="81" t="inlineStr">
         <is>
-          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
+          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
         </is>
       </c>
       <c r="E342" s="83" t="inlineStr">
@@ -22242,7 +22254,7 @@
       </c>
       <c r="F342" s="81" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE (intimate choice)</t>
+          <t>PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G342" s="81" t="inlineStr">
@@ -22274,7 +22286,7 @@
       </c>
       <c r="N342" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22286,17 +22298,17 @@
       </c>
       <c r="B343" s="79" t="inlineStr">
         <is>
-          <t>Paul Revere</t>
+          <t>Old Ironsides</t>
         </is>
       </c>
       <c r="C343" s="80" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE_INTIMATE</t>
+          <t>PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D343" s="81" t="inlineStr">
         <is>
-          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
+          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E343" s="83" t="inlineStr">
@@ -22306,7 +22318,7 @@
       </c>
       <c r="F343" s="81" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE (intimate choice)</t>
+          <t>PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G343" s="81" t="inlineStr">
@@ -22338,7 +22350,7 @@
       </c>
       <c r="N343" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22350,17 +22362,17 @@
       </c>
       <c r="B344" s="79" t="inlineStr">
         <is>
-          <t>Liberty Bell</t>
+          <t>Valley Forge Guardian</t>
         </is>
       </c>
       <c r="C344" s="80" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE_INTIMATE</t>
+          <t>PROT_09_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D344" s="81" t="inlineStr">
         <is>
-          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
+          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E344" s="83" t="inlineStr">
@@ -22370,7 +22382,7 @@
       </c>
       <c r="F344" s="81" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE (intimate choice)</t>
+          <t>PROT_09_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G344" s="81" t="inlineStr">
@@ -22402,7 +22414,7 @@
       </c>
       <c r="N344" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22414,17 +22426,17 @@
       </c>
       <c r="B345" s="79" t="inlineStr">
         <is>
-          <t>Green Mountain Ghost</t>
+          <t>Snallygaster</t>
         </is>
       </c>
       <c r="C345" s="80" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE_INTIMATE</t>
+          <t>PROT_10_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D345" s="81" t="inlineStr">
         <is>
-          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
+          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
         </is>
       </c>
       <c r="E345" s="83" t="inlineStr">
@@ -22434,7 +22446,7 @@
       </c>
       <c r="F345" s="81" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE (intimate choice)</t>
+          <t>PROT_10_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G345" s="81" t="inlineStr">
@@ -22466,7 +22478,7 @@
       </c>
       <c r="N345" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22478,17 +22490,17 @@
       </c>
       <c r="B346" s="79" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Paul Revere</t>
         </is>
       </c>
       <c r="C346" s="80" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE_INTIMATE</t>
+          <t>PROT_11_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D346" s="81" t="inlineStr">
         <is>
-          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
+          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
         </is>
       </c>
       <c r="E346" s="83" t="inlineStr">
@@ -22498,7 +22510,7 @@
       </c>
       <c r="F346" s="81" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE (intimate choice)</t>
+          <t>PROT_11_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G346" s="81" t="inlineStr">
@@ -22530,7 +22542,7 @@
       </c>
       <c r="N346" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22542,17 +22554,17 @@
       </c>
       <c r="B347" s="79" t="inlineStr">
         <is>
-          <t>Skunk Ape</t>
+          <t>Liberty Bell</t>
         </is>
       </c>
       <c r="C347" s="80" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE_INTIMATE</t>
+          <t>PROT_12_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D347" s="81" t="inlineStr">
         <is>
-          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
+          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E347" s="83" t="inlineStr">
@@ -22562,7 +22574,7 @@
       </c>
       <c r="F347" s="81" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE (intimate choice)</t>
+          <t>PROT_12_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G347" s="81" t="inlineStr">
@@ -22594,7 +22606,7 @@
       </c>
       <c r="N347" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22606,17 +22618,17 @@
       </c>
       <c r="B348" s="79" t="inlineStr">
         <is>
-          <t>Minuteman</t>
+          <t>Green Mountain Ghost</t>
         </is>
       </c>
       <c r="C348" s="80" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE_INTIMATE</t>
+          <t>PROT_13_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D348" s="81" t="inlineStr">
         <is>
-          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
+          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
         </is>
       </c>
       <c r="E348" s="83" t="inlineStr">
@@ -22626,7 +22638,7 @@
       </c>
       <c r="F348" s="81" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE (intimate choice)</t>
+          <t>PROT_13_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G348" s="81" t="inlineStr">
@@ -22658,7 +22670,7 @@
       </c>
       <c r="N348" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22670,17 +22682,17 @@
       </c>
       <c r="B349" s="79" t="inlineStr">
         <is>
-          <t>Lincoln's Ghost</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="C349" s="80" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE_INTIMATE</t>
+          <t>PROT_14_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D349" s="81" t="inlineStr">
         <is>
-          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
+          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
         </is>
       </c>
       <c r="E349" s="83" t="inlineStr">
@@ -22690,7 +22702,7 @@
       </c>
       <c r="F349" s="81" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE (intimate choice)</t>
+          <t>PROT_14_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G349" s="81" t="inlineStr">
@@ -22722,45 +22734,93 @@
       </c>
       <c r="N349" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="8" customHeight="1">
-      <c r="A350" s="9" t="n"/>
-      <c r="B350" s="9" t="n"/>
-      <c r="C350" s="9" t="n"/>
-      <c r="D350" s="9" t="n"/>
-      <c r="E350" s="9" t="n"/>
-      <c r="F350" s="9" t="n"/>
-      <c r="G350" s="9" t="n"/>
-      <c r="H350" s="9" t="n"/>
-      <c r="I350" s="9" t="n"/>
-      <c r="J350" s="9" t="n"/>
-      <c r="K350" s="9" t="n"/>
-      <c r="L350" s="9" t="n"/>
-      <c r="M350" s="9" t="n"/>
-      <c r="N350" s="9" t="n"/>
+          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="30" customHeight="1">
+      <c r="A350" s="79" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B350" s="79" t="inlineStr">
+        <is>
+          <t>Skunk Ape</t>
+        </is>
+      </c>
+      <c r="C350" s="80" t="inlineStr">
+        <is>
+          <t>PROT_15_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D350" s="81" t="inlineStr">
+        <is>
+          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E350" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F350" s="81" t="inlineStr">
+        <is>
+          <t>PROT_15_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G350" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H350" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I350" s="80" t="inlineStr"/>
+      <c r="J350" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K350" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L350" s="80" t="inlineStr"/>
+      <c r="M350" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N350" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="30" customHeight="1">
       <c r="A351" s="79" t="inlineStr">
         <is>
-          <t>White House</t>
+          <t>Protector</t>
         </is>
       </c>
       <c r="B351" s="79" t="inlineStr">
         <is>
-          <t>Month 1</t>
+          <t>Minuteman</t>
         </is>
       </c>
       <c r="C351" s="80" t="inlineStr">
         <is>
-          <t>WH_SECRET_01_INTIMATE</t>
+          <t>PROT_16_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D351" s="81" t="inlineStr">
         <is>
-          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
+          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E351" s="83" t="inlineStr">
@@ -22770,7 +22830,7 @@
       </c>
       <c r="F351" s="81" t="inlineStr">
         <is>
-          <t>WH_SECRET_01 (intimate choice)</t>
+          <t>PROT_16_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G351" s="81" t="inlineStr">
@@ -22802,29 +22862,29 @@
       </c>
       <c r="N351" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="352" ht="30" customHeight="1">
       <c r="A352" s="79" t="inlineStr">
         <is>
-          <t>White House</t>
+          <t>Protector</t>
         </is>
       </c>
       <c r="B352" s="79" t="inlineStr">
         <is>
-          <t>Month 7</t>
+          <t>Lincoln's Ghost</t>
         </is>
       </c>
       <c r="C352" s="80" t="inlineStr">
         <is>
-          <t>WH_SECRET_07_INTIMATE</t>
+          <t>PROT_17_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D352" s="81" t="inlineStr">
         <is>
-          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
+          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
         </is>
       </c>
       <c r="E352" s="83" t="inlineStr">
@@ -22834,7 +22894,7 @@
       </c>
       <c r="F352" s="81" t="inlineStr">
         <is>
-          <t>WH_SECRET_07 (intimate choice)</t>
+          <t>PROT_17_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G352" s="81" t="inlineStr">
@@ -22866,73 +22926,25 @@
       </c>
       <c r="N352" s="81" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="353" ht="30" customHeight="1">
-      <c r="A353" s="79" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B353" s="79" t="inlineStr">
-        <is>
-          <t>Month 10</t>
-        </is>
-      </c>
-      <c r="C353" s="80" t="inlineStr">
-        <is>
-          <t>WH_SECRET_10_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D353" s="81" t="inlineStr">
-        <is>
-          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E353" s="83" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F353" s="81" t="inlineStr">
-        <is>
-          <t>WH_SECRET_10 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G353" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H353" s="82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I353" s="80" t="inlineStr"/>
-      <c r="J353" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K353" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L353" s="80" t="inlineStr"/>
-      <c r="M353" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N353" s="81" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="8" customHeight="1">
+      <c r="A353" s="9" t="n"/>
+      <c r="B353" s="9" t="n"/>
+      <c r="C353" s="9" t="n"/>
+      <c r="D353" s="9" t="n"/>
+      <c r="E353" s="9" t="n"/>
+      <c r="F353" s="9" t="n"/>
+      <c r="G353" s="9" t="n"/>
+      <c r="H353" s="9" t="n"/>
+      <c r="I353" s="9" t="n"/>
+      <c r="J353" s="9" t="n"/>
+      <c r="K353" s="9" t="n"/>
+      <c r="L353" s="9" t="n"/>
+      <c r="M353" s="9" t="n"/>
+      <c r="N353" s="9" t="n"/>
     </row>
     <row r="354" ht="30" customHeight="1">
       <c r="A354" s="79" t="inlineStr">
@@ -22942,17 +22954,17 @@
       </c>
       <c r="B354" s="79" t="inlineStr">
         <is>
-          <t>Month 12</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C354" s="80" t="inlineStr">
         <is>
-          <t>WH_SECRET_12_INTIMATE</t>
+          <t>WH_SECRET_01_INTIMATE</t>
         </is>
       </c>
       <c r="D354" s="81" t="inlineStr">
         <is>
-          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
+          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
         </is>
       </c>
       <c r="E354" s="83" t="inlineStr">
@@ -22962,7 +22974,7 @@
       </c>
       <c r="F354" s="81" t="inlineStr">
         <is>
-          <t>WH_SECRET_12 (intimate choice)</t>
+          <t>WH_SECRET_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G354" s="81" t="inlineStr">
@@ -22994,48 +23006,240 @@
       </c>
       <c r="N354" s="81" t="inlineStr">
         <is>
+          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="30" customHeight="1">
+      <c r="A355" s="79" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B355" s="79" t="inlineStr">
+        <is>
+          <t>Month 7</t>
+        </is>
+      </c>
+      <c r="C355" s="80" t="inlineStr">
+        <is>
+          <t>WH_SECRET_07_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D355" s="81" t="inlineStr">
+        <is>
+          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E355" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F355" s="81" t="inlineStr">
+        <is>
+          <t>WH_SECRET_07 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G355" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H355" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I355" s="80" t="inlineStr"/>
+      <c r="J355" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K355" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L355" s="80" t="inlineStr"/>
+      <c r="M355" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N355" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="30" customHeight="1">
+      <c r="A356" s="79" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B356" s="79" t="inlineStr">
+        <is>
+          <t>Month 10</t>
+        </is>
+      </c>
+      <c r="C356" s="80" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D356" s="81" t="inlineStr">
+        <is>
+          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E356" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F356" s="81" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G356" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H356" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I356" s="80" t="inlineStr"/>
+      <c r="J356" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K356" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L356" s="80" t="inlineStr"/>
+      <c r="M356" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N356" s="81" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="30" customHeight="1">
+      <c r="A357" s="79" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B357" s="79" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="C357" s="80" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D357" s="81" t="inlineStr">
+        <is>
+          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E357" s="83" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F357" s="81" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G357" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H357" s="82" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I357" s="80" t="inlineStr"/>
+      <c r="J357" s="84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K357" s="83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L357" s="80" t="inlineStr"/>
+      <c r="M357" s="83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N357" s="81" t="inlineStr">
+        <is>
           <t>Stub — author intimate version of WH_SECRET_12. By morning: emotional arc, no explicit imagery.</t>
         </is>
-      </c>
-    </row>
-    <row r="356" ht="20" customHeight="1">
-      <c r="A356" s="85" t="inlineStr">
-        <is>
-          <t>Total events in spreadsheet</t>
-        </is>
-      </c>
-      <c r="B356" s="86" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="357" ht="20" customHeight="1">
-      <c r="A357" s="85" t="inlineStr">
-        <is>
-          <t>FIRST PASS (coded &amp; wired)</t>
-        </is>
-      </c>
-      <c r="B357" s="86" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="358" ht="20" customHeight="1">
-      <c r="A358" s="85" t="inlineStr">
-        <is>
-          <t>IDEA (not yet implemented)</t>
-        </is>
-      </c>
-      <c r="B358" s="86" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
       <c r="A359" s="85" t="inlineStr">
         <is>
+          <t>Total events in spreadsheet</t>
+        </is>
+      </c>
+      <c r="B359" s="86" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="360" ht="20" customHeight="1">
+      <c r="A360" s="85" t="inlineStr">
+        <is>
+          <t>FIRST PASS (coded &amp; wired)</t>
+        </is>
+      </c>
+      <c r="B360" s="86" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="361" ht="20" customHeight="1">
+      <c r="A361" s="85" t="inlineStr">
+        <is>
+          <t>IDEA (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="B361" s="86" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="362" ht="20" customHeight="1">
+      <c r="A362" s="85" t="inlineStr">
+        <is>
           <t>Need explicit art (YES)</t>
         </is>
       </c>
-      <c r="B359" s="86" t="n">
-        <v>55</v>
+      <c r="B362" s="86" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -14286,9 +14286,9 @@
           <t>ARC_01_DONE</t>
         </is>
       </c>
-      <c r="H209" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H209" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I209" s="32" t="inlineStr"/>
@@ -23219,7 +23219,7 @@
         </is>
       </c>
       <c r="B360" s="86" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -314,6 +314,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F5E6F0"/>
       </patternFill>
     </fill>
@@ -330,11 +335,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -579,15 +579,6 @@
     <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -612,13 +603,22 @@
     <xf numFmtId="0" fontId="2" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -642,10 +642,10 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -780,12 +780,6 @@
     <xf numFmtId="0" fontId="22" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -796,6 +790,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14292,9 +14292,9 @@
         </is>
       </c>
       <c r="I209" s="32" t="inlineStr"/>
-      <c r="J209" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J209" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K209" s="34" t="inlineStr">
@@ -14355,14 +14355,10 @@
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="I210" s="32" t="inlineStr">
-        <is>
-          <t>arc_01_done_scene</t>
-        </is>
-      </c>
-      <c r="J210" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="I210" s="32" t="inlineStr"/>
+      <c r="J210" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K210" s="34" t="inlineStr">
@@ -14424,9 +14420,9 @@
         </is>
       </c>
       <c r="I211" s="32" t="inlineStr"/>
-      <c r="J211" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J211" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K211" s="34" t="inlineStr">
@@ -14488,9 +14484,9 @@
         </is>
       </c>
       <c r="I212" s="32" t="inlineStr"/>
-      <c r="J212" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J212" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K212" s="34" t="inlineStr">
@@ -14552,9 +14548,9 @@
         </is>
       </c>
       <c r="I213" s="32" t="inlineStr"/>
-      <c r="J213" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J213" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K213" s="34" t="inlineStr">
@@ -14616,9 +14612,9 @@
         </is>
       </c>
       <c r="I214" s="32" t="inlineStr"/>
-      <c r="J214" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J214" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K214" s="34" t="inlineStr">
@@ -14680,9 +14676,9 @@
         </is>
       </c>
       <c r="I215" s="32" t="inlineStr"/>
-      <c r="J215" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J215" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K215" s="34" t="inlineStr">
@@ -14744,9 +14740,9 @@
         </is>
       </c>
       <c r="I216" s="32" t="inlineStr"/>
-      <c r="J216" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J216" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K216" s="34" t="inlineStr">
@@ -14808,9 +14804,9 @@
         </is>
       </c>
       <c r="I217" s="32" t="inlineStr"/>
-      <c r="J217" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J217" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K217" s="34" t="inlineStr">
@@ -14872,9 +14868,9 @@
         </is>
       </c>
       <c r="I218" s="32" t="inlineStr"/>
-      <c r="J218" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J218" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K218" s="34" t="inlineStr">
@@ -14936,9 +14932,9 @@
         </is>
       </c>
       <c r="I219" s="32" t="inlineStr"/>
-      <c r="J219" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J219" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K219" s="34" t="inlineStr">
@@ -15000,9 +14996,9 @@
         </is>
       </c>
       <c r="I220" s="32" t="inlineStr"/>
-      <c r="J220" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J220" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K220" s="34" t="inlineStr">
@@ -15064,9 +15060,9 @@
         </is>
       </c>
       <c r="I221" s="32" t="inlineStr"/>
-      <c r="J221" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J221" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K221" s="34" t="inlineStr">
@@ -15128,9 +15124,9 @@
         </is>
       </c>
       <c r="I222" s="32" t="inlineStr"/>
-      <c r="J222" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J222" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K222" s="34" t="inlineStr">
@@ -15192,9 +15188,9 @@
         </is>
       </c>
       <c r="I223" s="32" t="inlineStr"/>
-      <c r="J223" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J223" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K223" s="34" t="inlineStr">
@@ -15256,9 +15252,9 @@
         </is>
       </c>
       <c r="I224" s="32" t="inlineStr"/>
-      <c r="J224" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J224" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K224" s="34" t="inlineStr">
@@ -15320,9 +15316,9 @@
         </is>
       </c>
       <c r="I225" s="32" t="inlineStr"/>
-      <c r="J225" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J225" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K225" s="34" t="inlineStr">
@@ -15384,9 +15380,9 @@
         </is>
       </c>
       <c r="I226" s="32" t="inlineStr"/>
-      <c r="J226" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J226" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K226" s="34" t="inlineStr">
@@ -15448,9 +15444,9 @@
         </is>
       </c>
       <c r="I227" s="32" t="inlineStr"/>
-      <c r="J227" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J227" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K227" s="34" t="inlineStr">
@@ -15512,9 +15508,9 @@
         </is>
       </c>
       <c r="I228" s="32" t="inlineStr"/>
-      <c r="J228" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J228" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K228" s="34" t="inlineStr">
@@ -15576,9 +15572,9 @@
         </is>
       </c>
       <c r="I229" s="32" t="inlineStr"/>
-      <c r="J229" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J229" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K229" s="34" t="inlineStr">
@@ -15640,9 +15636,9 @@
         </is>
       </c>
       <c r="I230" s="32" t="inlineStr"/>
-      <c r="J230" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J230" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K230" s="34" t="inlineStr">
@@ -15704,9 +15700,9 @@
         </is>
       </c>
       <c r="I231" s="32" t="inlineStr"/>
-      <c r="J231" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J231" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K231" s="34" t="inlineStr">
@@ -15768,9 +15764,9 @@
         </is>
       </c>
       <c r="I232" s="32" t="inlineStr"/>
-      <c r="J232" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J232" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K232" s="34" t="inlineStr">
@@ -15832,9 +15828,9 @@
         </is>
       </c>
       <c r="I233" s="32" t="inlineStr"/>
-      <c r="J233" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J233" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K233" s="34" t="inlineStr">
@@ -15896,9 +15892,9 @@
         </is>
       </c>
       <c r="I234" s="32" t="inlineStr"/>
-      <c r="J234" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J234" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K234" s="34" t="inlineStr">
@@ -15960,9 +15956,9 @@
         </is>
       </c>
       <c r="I235" s="32" t="inlineStr"/>
-      <c r="J235" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J235" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K235" s="34" t="inlineStr">
@@ -16024,9 +16020,9 @@
         </is>
       </c>
       <c r="I236" s="32" t="inlineStr"/>
-      <c r="J236" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J236" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K236" s="34" t="inlineStr">
@@ -16088,9 +16084,9 @@
         </is>
       </c>
       <c r="I237" s="32" t="inlineStr"/>
-      <c r="J237" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J237" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K237" s="34" t="inlineStr">
@@ -16152,9 +16148,9 @@
         </is>
       </c>
       <c r="I238" s="32" t="inlineStr"/>
-      <c r="J238" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J238" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K238" s="34" t="inlineStr">
@@ -16216,9 +16212,9 @@
         </is>
       </c>
       <c r="I239" s="32" t="inlineStr"/>
-      <c r="J239" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J239" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K239" s="34" t="inlineStr">
@@ -16280,9 +16276,9 @@
         </is>
       </c>
       <c r="I240" s="32" t="inlineStr"/>
-      <c r="J240" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J240" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K240" s="34" t="inlineStr">
@@ -16344,9 +16340,9 @@
         </is>
       </c>
       <c r="I241" s="32" t="inlineStr"/>
-      <c r="J241" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J241" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K241" s="34" t="inlineStr">
@@ -16408,9 +16404,9 @@
         </is>
       </c>
       <c r="I242" s="32" t="inlineStr"/>
-      <c r="J242" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J242" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K242" s="34" t="inlineStr">
@@ -16472,9 +16468,9 @@
         </is>
       </c>
       <c r="I243" s="32" t="inlineStr"/>
-      <c r="J243" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J243" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K243" s="34" t="inlineStr">
@@ -16536,9 +16532,9 @@
         </is>
       </c>
       <c r="I244" s="32" t="inlineStr"/>
-      <c r="J244" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J244" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K244" s="34" t="inlineStr">
@@ -16600,9 +16596,9 @@
         </is>
       </c>
       <c r="I245" s="32" t="inlineStr"/>
-      <c r="J245" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J245" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K245" s="34" t="inlineStr">
@@ -16664,9 +16660,9 @@
         </is>
       </c>
       <c r="I246" s="32" t="inlineStr"/>
-      <c r="J246" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J246" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K246" s="34" t="inlineStr">
@@ -16728,9 +16724,9 @@
         </is>
       </c>
       <c r="I247" s="32" t="inlineStr"/>
-      <c r="J247" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J247" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K247" s="34" t="inlineStr">
@@ -16792,9 +16788,9 @@
         </is>
       </c>
       <c r="I248" s="32" t="inlineStr"/>
-      <c r="J248" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J248" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K248" s="34" t="inlineStr">
@@ -16856,9 +16852,9 @@
         </is>
       </c>
       <c r="I249" s="32" t="inlineStr"/>
-      <c r="J249" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J249" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K249" s="34" t="inlineStr">
@@ -16920,9 +16916,9 @@
         </is>
       </c>
       <c r="I250" s="32" t="inlineStr"/>
-      <c r="J250" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J250" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K250" s="34" t="inlineStr">
@@ -16984,9 +16980,9 @@
         </is>
       </c>
       <c r="I251" s="32" t="inlineStr"/>
-      <c r="J251" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J251" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K251" s="34" t="inlineStr">
@@ -17048,9 +17044,9 @@
         </is>
       </c>
       <c r="I252" s="32" t="inlineStr"/>
-      <c r="J252" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J252" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K252" s="34" t="inlineStr">
@@ -17112,9 +17108,9 @@
         </is>
       </c>
       <c r="I253" s="32" t="inlineStr"/>
-      <c r="J253" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J253" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K253" s="34" t="inlineStr">
@@ -17176,9 +17172,9 @@
         </is>
       </c>
       <c r="I254" s="32" t="inlineStr"/>
-      <c r="J254" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J254" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K254" s="34" t="inlineStr">
@@ -17240,9 +17236,9 @@
         </is>
       </c>
       <c r="I255" s="32" t="inlineStr"/>
-      <c r="J255" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J255" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K255" s="34" t="inlineStr">
@@ -17304,9 +17300,9 @@
         </is>
       </c>
       <c r="I256" s="32" t="inlineStr"/>
-      <c r="J256" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J256" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K256" s="34" t="inlineStr">
@@ -17368,9 +17364,9 @@
         </is>
       </c>
       <c r="I257" s="32" t="inlineStr"/>
-      <c r="J257" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J257" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K257" s="34" t="inlineStr">
@@ -17432,9 +17428,9 @@
         </is>
       </c>
       <c r="I258" s="32" t="inlineStr"/>
-      <c r="J258" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J258" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K258" s="34" t="inlineStr">
@@ -17759,22 +17755,22 @@
       <c r="N264" s="9" t="n"/>
     </row>
     <row r="265" ht="30" customHeight="1">
-      <c r="A265" s="71" t="inlineStr">
+      <c r="A265" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B265" s="71" t="inlineStr">
+      <c r="B265" s="72" t="inlineStr">
         <is>
           <t>Month 1</t>
         </is>
       </c>
-      <c r="C265" s="72" t="inlineStr">
+      <c r="C265" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_01</t>
         </is>
       </c>
-      <c r="D265" s="73" t="inlineStr">
+      <c r="D265" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
         </is>
@@ -17784,12 +17780,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F265" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G265" s="73" t="inlineStr">
+      <c r="F265" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G265" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17799,7 +17795,7 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I265" s="72" t="inlineStr"/>
+      <c r="I265" s="73" t="inlineStr"/>
       <c r="J265" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -17810,39 +17806,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L265" s="72" t="inlineStr">
+      <c r="L265" s="73" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M265" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N265" s="73" t="inlineStr">
+      <c r="M265" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N265" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
         </is>
       </c>
     </row>
     <row r="266" ht="30" customHeight="1">
-      <c r="A266" s="71" t="inlineStr">
+      <c r="A266" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B266" s="71" t="inlineStr">
+      <c r="B266" s="72" t="inlineStr">
         <is>
           <t>Month 2</t>
         </is>
       </c>
-      <c r="C266" s="72" t="inlineStr">
+      <c r="C266" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_02</t>
         </is>
       </c>
-      <c r="D266" s="73" t="inlineStr">
+      <c r="D266" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
         </is>
@@ -17852,12 +17848,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F266" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G266" s="73" t="inlineStr">
+      <c r="F266" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G266" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17867,50 +17863,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I266" s="72" t="inlineStr"/>
+      <c r="I266" s="73" t="inlineStr"/>
       <c r="J266" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K266" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L266" s="72" t="inlineStr">
+      <c r="K266" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L266" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M266" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N266" s="73" t="inlineStr">
+      <c r="M266" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N266" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
         </is>
       </c>
     </row>
     <row r="267" ht="30" customHeight="1">
-      <c r="A267" s="71" t="inlineStr">
+      <c r="A267" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B267" s="71" t="inlineStr">
+      <c r="B267" s="72" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
-      <c r="C267" s="72" t="inlineStr">
+      <c r="C267" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_03</t>
         </is>
       </c>
-      <c r="D267" s="73" t="inlineStr">
+      <c r="D267" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
         </is>
@@ -17920,12 +17916,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F267" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G267" s="73" t="inlineStr">
+      <c r="F267" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G267" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17935,50 +17931,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I267" s="72" t="inlineStr"/>
+      <c r="I267" s="73" t="inlineStr"/>
       <c r="J267" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K267" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L267" s="72" t="inlineStr">
+      <c r="K267" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L267" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M267" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N267" s="73" t="inlineStr">
+      <c r="M267" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N267" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
         </is>
       </c>
     </row>
     <row r="268" ht="30" customHeight="1">
-      <c r="A268" s="71" t="inlineStr">
+      <c r="A268" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B268" s="71" t="inlineStr">
+      <c r="B268" s="72" t="inlineStr">
         <is>
           <t>Month 4</t>
         </is>
       </c>
-      <c r="C268" s="72" t="inlineStr">
+      <c r="C268" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_04</t>
         </is>
       </c>
-      <c r="D268" s="73" t="inlineStr">
+      <c r="D268" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — EASTER MORNING</t>
         </is>
@@ -17988,12 +17984,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F268" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G268" s="73" t="inlineStr">
+      <c r="F268" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G268" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18003,50 +17999,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I268" s="72" t="inlineStr"/>
+      <c r="I268" s="73" t="inlineStr"/>
       <c r="J268" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K268" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L268" s="72" t="inlineStr">
+      <c r="K268" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L268" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M268" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N268" s="73" t="inlineStr">
+      <c r="M268" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N268" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
         </is>
       </c>
     </row>
     <row r="269" ht="30" customHeight="1">
-      <c r="A269" s="71" t="inlineStr">
+      <c r="A269" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B269" s="71" t="inlineStr">
+      <c r="B269" s="72" t="inlineStr">
         <is>
           <t>Month 5</t>
         </is>
       </c>
-      <c r="C269" s="72" t="inlineStr">
+      <c r="C269" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_05</t>
         </is>
       </c>
-      <c r="D269" s="73" t="inlineStr">
+      <c r="D269" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
         </is>
@@ -18056,12 +18052,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F269" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G269" s="73" t="inlineStr">
+      <c r="F269" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G269" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18071,50 +18067,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I269" s="72" t="inlineStr"/>
+      <c r="I269" s="73" t="inlineStr"/>
       <c r="J269" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K269" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L269" s="72" t="inlineStr">
+      <c r="K269" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L269" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M269" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N269" s="73" t="inlineStr">
+      <c r="M269" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N269" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
         </is>
       </c>
     </row>
     <row r="270" ht="30" customHeight="1">
-      <c r="A270" s="71" t="inlineStr">
+      <c r="A270" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B270" s="71" t="inlineStr">
+      <c r="B270" s="72" t="inlineStr">
         <is>
           <t>Month 6</t>
         </is>
       </c>
-      <c r="C270" s="72" t="inlineStr">
+      <c r="C270" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_06</t>
         </is>
       </c>
-      <c r="D270" s="73" t="inlineStr">
+      <c r="D270" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — JUNETEENTH</t>
         </is>
@@ -18124,12 +18120,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F270" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G270" s="73" t="inlineStr">
+      <c r="F270" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G270" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18139,50 +18135,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I270" s="72" t="inlineStr"/>
+      <c r="I270" s="73" t="inlineStr"/>
       <c r="J270" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K270" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L270" s="72" t="inlineStr">
+      <c r="K270" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L270" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M270" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N270" s="73" t="inlineStr">
+      <c r="M270" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N270" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
         </is>
       </c>
     </row>
     <row r="271" ht="30" customHeight="1">
-      <c r="A271" s="71" t="inlineStr">
+      <c r="A271" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B271" s="71" t="inlineStr">
+      <c r="B271" s="72" t="inlineStr">
         <is>
           <t>Month 7</t>
         </is>
       </c>
-      <c r="C271" s="72" t="inlineStr">
+      <c r="C271" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_07</t>
         </is>
       </c>
-      <c r="D271" s="73" t="inlineStr">
+      <c r="D271" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
         </is>
@@ -18192,12 +18188,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F271" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G271" s="73" t="inlineStr">
+      <c r="F271" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G271" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18207,7 +18203,7 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I271" s="72" t="inlineStr"/>
+      <c r="I271" s="73" t="inlineStr"/>
       <c r="J271" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -18218,39 +18214,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L271" s="72" t="inlineStr">
+      <c r="L271" s="73" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M271" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N271" s="73" t="inlineStr">
+      <c r="M271" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N271" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
         </is>
       </c>
     </row>
     <row r="272" ht="30" customHeight="1">
-      <c r="A272" s="71" t="inlineStr">
+      <c r="A272" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B272" s="71" t="inlineStr">
+      <c r="B272" s="72" t="inlineStr">
         <is>
           <t>Month 8</t>
         </is>
       </c>
-      <c r="C272" s="72" t="inlineStr">
+      <c r="C272" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_08</t>
         </is>
       </c>
-      <c r="D272" s="73" t="inlineStr">
+      <c r="D272" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — DIWALI</t>
         </is>
@@ -18260,12 +18256,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F272" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G272" s="73" t="inlineStr">
+      <c r="F272" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G272" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18275,50 +18271,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I272" s="72" t="inlineStr"/>
+      <c r="I272" s="73" t="inlineStr"/>
       <c r="J272" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K272" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L272" s="72" t="inlineStr">
+      <c r="K272" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L272" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M272" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N272" s="73" t="inlineStr">
+      <c r="M272" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N272" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
         </is>
       </c>
     </row>
     <row r="273" ht="30" customHeight="1">
-      <c r="A273" s="71" t="inlineStr">
+      <c r="A273" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B273" s="71" t="inlineStr">
+      <c r="B273" s="72" t="inlineStr">
         <is>
           <t>Month 9</t>
         </is>
       </c>
-      <c r="C273" s="72" t="inlineStr">
+      <c r="C273" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_09</t>
         </is>
       </c>
-      <c r="D273" s="73" t="inlineStr">
+      <c r="D273" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — HALLOWEEN</t>
         </is>
@@ -18328,12 +18324,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F273" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G273" s="73" t="inlineStr">
+      <c r="F273" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G273" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18343,50 +18339,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I273" s="72" t="inlineStr"/>
+      <c r="I273" s="73" t="inlineStr"/>
       <c r="J273" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K273" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L273" s="72" t="inlineStr">
+      <c r="K273" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L273" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M273" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N273" s="73" t="inlineStr">
+      <c r="M273" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N273" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
         </is>
       </c>
     </row>
     <row r="274" ht="30" customHeight="1">
-      <c r="A274" s="71" t="inlineStr">
+      <c r="A274" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B274" s="71" t="inlineStr">
+      <c r="B274" s="72" t="inlineStr">
         <is>
           <t>Month 10</t>
         </is>
       </c>
-      <c r="C274" s="72" t="inlineStr">
+      <c r="C274" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_10</t>
         </is>
       </c>
-      <c r="D274" s="73" t="inlineStr">
+      <c r="D274" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
         </is>
@@ -18396,12 +18392,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F274" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G274" s="73" t="inlineStr">
+      <c r="F274" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G274" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18411,7 +18407,7 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I274" s="72" t="inlineStr"/>
+      <c r="I274" s="73" t="inlineStr"/>
       <c r="J274" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -18422,39 +18418,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L274" s="72" t="inlineStr">
+      <c r="L274" s="73" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M274" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N274" s="73" t="inlineStr">
+      <c r="M274" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N274" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
         </is>
       </c>
     </row>
     <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="71" t="inlineStr">
+      <c r="A275" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B275" s="71" t="inlineStr">
+      <c r="B275" s="72" t="inlineStr">
         <is>
           <t>Month 11</t>
         </is>
       </c>
-      <c r="C275" s="72" t="inlineStr">
+      <c r="C275" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_11</t>
         </is>
       </c>
-      <c r="D275" s="73" t="inlineStr">
+      <c r="D275" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — THANKSGIVING</t>
         </is>
@@ -18464,12 +18460,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F275" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G275" s="73" t="inlineStr">
+      <c r="F275" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G275" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18479,50 +18475,50 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I275" s="72" t="inlineStr"/>
+      <c r="I275" s="73" t="inlineStr"/>
       <c r="J275" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K275" s="74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L275" s="72" t="inlineStr">
+      <c r="K275" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L275" s="73" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M275" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N275" s="73" t="inlineStr">
+      <c r="M275" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N275" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
         </is>
       </c>
     </row>
     <row r="276" ht="30" customHeight="1">
-      <c r="A276" s="71" t="inlineStr">
+      <c r="A276" s="72" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B276" s="71" t="inlineStr">
+      <c r="B276" s="72" t="inlineStr">
         <is>
           <t>Month 12</t>
         </is>
       </c>
-      <c r="C276" s="72" t="inlineStr">
+      <c r="C276" s="73" t="inlineStr">
         <is>
           <t>WH_SECRET_12</t>
         </is>
       </c>
-      <c r="D276" s="73" t="inlineStr">
+      <c r="D276" s="74" t="inlineStr">
         <is>
           <t>WHITE HOUSE SECRET — CHRISTMAS</t>
         </is>
@@ -18532,12 +18528,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F276" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G276" s="73" t="inlineStr">
+      <c r="F276" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G276" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18547,7 +18543,7 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I276" s="72" t="inlineStr"/>
+      <c r="I276" s="73" t="inlineStr"/>
       <c r="J276" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -18558,17 +18554,17 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L276" s="72" t="inlineStr">
+      <c r="L276" s="73" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M276" s="74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N276" s="73" t="inlineStr">
+      <c r="M276" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N276" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
         </is>
@@ -18591,22 +18587,22 @@
       <c r="N277" s="9" t="n"/>
     </row>
     <row r="278" ht="30" customHeight="1">
-      <c r="A278" s="75" t="inlineStr">
+      <c r="A278" s="76" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B278" s="75" t="inlineStr">
+      <c r="B278" s="76" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C278" s="76" t="inlineStr">
+      <c r="C278" s="77" t="inlineStr">
         <is>
           <t>CHALCH_SUMMON</t>
         </is>
       </c>
-      <c r="D278" s="77" t="inlineStr">
+      <c r="D278" s="78" t="inlineStr">
         <is>
           <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
         </is>
@@ -18616,12 +18612,12 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F278" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G278" s="77" t="inlineStr">
+      <c r="F278" s="78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G278" s="78" t="inlineStr">
         <is>
           <t>CHALCH_Q1</t>
         </is>
@@ -18631,61 +18627,61 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I278" s="76" t="inlineStr"/>
+      <c r="I278" s="77" t="inlineStr"/>
       <c r="J278" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K278" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L278" s="76" t="inlineStr"/>
-      <c r="M278" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N278" s="77" t="inlineStr">
+      <c r="K278" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L278" s="77" t="inlineStr"/>
+      <c r="M278" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N278" s="78" t="inlineStr">
         <is>
           <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
         </is>
       </c>
     </row>
     <row r="279" ht="30" customHeight="1">
-      <c r="A279" s="75" t="inlineStr">
+      <c r="A279" s="76" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B279" s="75" t="inlineStr">
+      <c r="B279" s="76" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C279" s="76" t="inlineStr">
+      <c r="C279" s="77" t="inlineStr">
         <is>
           <t>CHALCH_Q1</t>
         </is>
       </c>
-      <c r="D279" s="77" t="inlineStr">
+      <c r="D279" s="78" t="inlineStr">
         <is>
           <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
         </is>
       </c>
-      <c r="E279" s="78" t="inlineStr">
+      <c r="E279" s="79" t="inlineStr">
         <is>
           <t>Quest 1</t>
         </is>
       </c>
-      <c r="F279" s="77" t="inlineStr">
+      <c r="F279" s="78" t="inlineStr">
         <is>
           <t>CHALCH_SUMMON</t>
         </is>
       </c>
-      <c r="G279" s="77" t="inlineStr">
+      <c r="G279" s="78" t="inlineStr">
         <is>
           <t>CHALCH_Q2</t>
         </is>
@@ -18695,61 +18691,61 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I279" s="76" t="inlineStr"/>
+      <c r="I279" s="77" t="inlineStr"/>
       <c r="J279" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K279" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L279" s="76" t="inlineStr"/>
-      <c r="M279" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N279" s="77" t="inlineStr">
+      <c r="K279" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L279" s="77" t="inlineStr"/>
+      <c r="M279" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N279" s="78" t="inlineStr">
         <is>
           <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
         </is>
       </c>
     </row>
     <row r="280" ht="30" customHeight="1">
-      <c r="A280" s="75" t="inlineStr">
+      <c r="A280" s="76" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B280" s="75" t="inlineStr">
+      <c r="B280" s="76" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C280" s="76" t="inlineStr">
+      <c r="C280" s="77" t="inlineStr">
         <is>
           <t>CHALCH_Q2</t>
         </is>
       </c>
-      <c r="D280" s="77" t="inlineStr">
+      <c r="D280" s="78" t="inlineStr">
         <is>
           <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
         </is>
       </c>
-      <c r="E280" s="78" t="inlineStr">
+      <c r="E280" s="79" t="inlineStr">
         <is>
           <t>Quest 2</t>
         </is>
       </c>
-      <c r="F280" s="77" t="inlineStr">
+      <c r="F280" s="78" t="inlineStr">
         <is>
           <t>CHALCH_Q1</t>
         </is>
       </c>
-      <c r="G280" s="77" t="inlineStr">
+      <c r="G280" s="78" t="inlineStr">
         <is>
           <t>CHALCH_Q3</t>
         </is>
@@ -18759,61 +18755,61 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I280" s="76" t="inlineStr"/>
+      <c r="I280" s="77" t="inlineStr"/>
       <c r="J280" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K280" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L280" s="76" t="inlineStr"/>
-      <c r="M280" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N280" s="77" t="inlineStr">
+      <c r="K280" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L280" s="77" t="inlineStr"/>
+      <c r="M280" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N280" s="78" t="inlineStr">
         <is>
           <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
         </is>
       </c>
     </row>
     <row r="281" ht="30" customHeight="1">
-      <c r="A281" s="75" t="inlineStr">
+      <c r="A281" s="76" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B281" s="75" t="inlineStr">
+      <c r="B281" s="76" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C281" s="76" t="inlineStr">
+      <c r="C281" s="77" t="inlineStr">
         <is>
           <t>CHALCH_Q3</t>
         </is>
       </c>
-      <c r="D281" s="77" t="inlineStr">
+      <c r="D281" s="78" t="inlineStr">
         <is>
           <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
         </is>
       </c>
-      <c r="E281" s="78" t="inlineStr">
+      <c r="E281" s="79" t="inlineStr">
         <is>
           <t>Quest 3</t>
         </is>
       </c>
-      <c r="F281" s="77" t="inlineStr">
+      <c r="F281" s="78" t="inlineStr">
         <is>
           <t>CHALCH_Q2</t>
         </is>
       </c>
-      <c r="G281" s="77" t="inlineStr">
+      <c r="G281" s="78" t="inlineStr">
         <is>
           <t>CHALCH_AGREE</t>
         </is>
@@ -18823,61 +18819,61 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I281" s="76" t="inlineStr"/>
+      <c r="I281" s="77" t="inlineStr"/>
       <c r="J281" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K281" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L281" s="76" t="inlineStr"/>
-      <c r="M281" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N281" s="77" t="inlineStr">
+      <c r="K281" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L281" s="77" t="inlineStr"/>
+      <c r="M281" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N281" s="78" t="inlineStr">
         <is>
           <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
         </is>
       </c>
     </row>
     <row r="282" ht="30" customHeight="1">
-      <c r="A282" s="75" t="inlineStr">
+      <c r="A282" s="76" t="inlineStr">
         <is>
           <t>Chalchiuhtotolin</t>
         </is>
       </c>
-      <c r="B282" s="75" t="inlineStr">
+      <c r="B282" s="76" t="inlineStr">
         <is>
           <t>Jade Turkey Arc</t>
         </is>
       </c>
-      <c r="C282" s="76" t="inlineStr">
+      <c r="C282" s="77" t="inlineStr">
         <is>
           <t>CHALCH_AGREE</t>
         </is>
       </c>
-      <c r="D282" s="77" t="inlineStr">
+      <c r="D282" s="78" t="inlineStr">
         <is>
           <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
         </is>
       </c>
-      <c r="E282" s="78" t="inlineStr">
+      <c r="E282" s="79" t="inlineStr">
         <is>
           <t>Resolution</t>
         </is>
       </c>
-      <c r="F282" s="77" t="inlineStr">
+      <c r="F282" s="78" t="inlineStr">
         <is>
           <t>CHALCH_Q3</t>
         </is>
       </c>
-      <c r="G282" s="77" t="inlineStr">
+      <c r="G282" s="78" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18887,24 +18883,24 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I282" s="76" t="inlineStr"/>
+      <c r="I282" s="77" t="inlineStr"/>
       <c r="J282" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K282" s="78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L282" s="76" t="inlineStr"/>
-      <c r="M282" s="78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N282" s="77" t="inlineStr">
+      <c r="K282" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L282" s="77" t="inlineStr"/>
+      <c r="M282" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N282" s="78" t="inlineStr">
         <is>
           <t>Fires when chalch_q3_done; BTN1: +100 food; closes the arc</t>
         </is>
@@ -18927,22 +18923,22 @@
       <c r="N283" s="9" t="n"/>
     </row>
     <row r="284" ht="30" customHeight="1">
-      <c r="A284" s="79" t="inlineStr">
+      <c r="A284" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B284" s="79" t="inlineStr">
+      <c r="B284" s="80" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C284" s="80" t="inlineStr">
+      <c r="C284" s="81" t="inlineStr">
         <is>
           <t>UALANI_DOCK_01</t>
         </is>
       </c>
-      <c r="D284" s="81" t="inlineStr">
+      <c r="D284" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
         </is>
@@ -18952,22 +18948,22 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F284" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G284" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H284" s="82" t="inlineStr">
+      <c r="F284" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G284" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H284" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I284" s="80" t="inlineStr"/>
+      <c r="I284" s="81" t="inlineStr"/>
       <c r="J284" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -18978,39 +18974,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L284" s="80" t="inlineStr">
+      <c r="L284" s="81" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M284" s="83" t="inlineStr">
+      <c r="M284" s="84" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N284" s="81" t="inlineStr">
+      <c r="N284" s="82" t="inlineStr">
         <is>
           <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
         </is>
       </c>
     </row>
     <row r="285" ht="30" customHeight="1">
-      <c r="A285" s="79" t="inlineStr">
+      <c r="A285" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B285" s="79" t="inlineStr">
+      <c r="B285" s="80" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C285" s="80" t="inlineStr">
+      <c r="C285" s="81" t="inlineStr">
         <is>
           <t>UALANI_FARM_01</t>
         </is>
       </c>
-      <c r="D285" s="81" t="inlineStr">
+      <c r="D285" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
         </is>
@@ -19020,22 +19016,22 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F285" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G285" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H285" s="82" t="inlineStr">
+      <c r="F285" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G285" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H285" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I285" s="80" t="inlineStr"/>
+      <c r="I285" s="81" t="inlineStr"/>
       <c r="J285" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -19046,39 +19042,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L285" s="80" t="inlineStr">
+      <c r="L285" s="81" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M285" s="83" t="inlineStr">
+      <c r="M285" s="84" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N285" s="81" t="inlineStr">
+      <c r="N285" s="82" t="inlineStr">
         <is>
           <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
         </is>
       </c>
     </row>
     <row r="286" ht="30" customHeight="1">
-      <c r="A286" s="79" t="inlineStr">
+      <c r="A286" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B286" s="79" t="inlineStr">
+      <c r="B286" s="80" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C286" s="80" t="inlineStr">
+      <c r="C286" s="81" t="inlineStr">
         <is>
           <t>UALANI_BARRACKS_01</t>
         </is>
       </c>
-      <c r="D286" s="81" t="inlineStr">
+      <c r="D286" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
         </is>
@@ -19088,22 +19084,22 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F286" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G286" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H286" s="82" t="inlineStr">
+      <c r="F286" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G286" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H286" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I286" s="80" t="inlineStr"/>
+      <c r="I286" s="81" t="inlineStr"/>
       <c r="J286" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -19114,39 +19110,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L286" s="80" t="inlineStr">
+      <c r="L286" s="81" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M286" s="83" t="inlineStr">
+      <c r="M286" s="84" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N286" s="81" t="inlineStr">
+      <c r="N286" s="82" t="inlineStr">
         <is>
           <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
         </is>
       </c>
     </row>
     <row r="287" ht="30" customHeight="1">
-      <c r="A287" s="79" t="inlineStr">
+      <c r="A287" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B287" s="79" t="inlineStr">
+      <c r="B287" s="80" t="inlineStr">
         <is>
           <t>Ualani Expansion</t>
         </is>
       </c>
-      <c r="C287" s="80" t="inlineStr">
+      <c r="C287" s="81" t="inlineStr">
         <is>
           <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
-      <c r="D287" s="81" t="inlineStr">
+      <c r="D287" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
@@ -19156,22 +19152,22 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F287" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G287" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H287" s="82" t="inlineStr">
+      <c r="F287" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G287" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H287" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I287" s="80" t="inlineStr"/>
+      <c r="I287" s="81" t="inlineStr"/>
       <c r="J287" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -19182,39 +19178,39 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="L287" s="80" t="inlineStr">
+      <c r="L287" s="81" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M287" s="83" t="inlineStr">
+      <c r="M287" s="84" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N287" s="81" t="inlineStr">
+      <c r="N287" s="82" t="inlineStr">
         <is>
           <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
     <row r="288" ht="30" customHeight="1">
-      <c r="A288" s="79" t="inlineStr">
+      <c r="A288" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B288" s="79" t="inlineStr">
+      <c r="B288" s="80" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C288" s="80" t="inlineStr">
+      <c r="C288" s="81" t="inlineStr">
         <is>
           <t>CL_WASHINGTON_01</t>
         </is>
       </c>
-      <c r="D288" s="81" t="inlineStr">
+      <c r="D288" s="82" t="inlineStr">
         <is>
           <t>WASHINGTON DC LIBERATED  ← IDEA</t>
         </is>
@@ -19224,61 +19220,61 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F288" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G288" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H288" s="82" t="inlineStr">
+      <c r="F288" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G288" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H288" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I288" s="80" t="inlineStr"/>
+      <c r="I288" s="81" t="inlineStr"/>
       <c r="J288" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K288" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L288" s="80" t="inlineStr"/>
-      <c r="M288" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N288" s="81" t="inlineStr">
+      <c r="K288" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L288" s="81" t="inlineStr"/>
+      <c r="M288" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N288" s="82" t="inlineStr">
         <is>
           <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
     <row r="289" ht="30" customHeight="1">
-      <c r="A289" s="79" t="inlineStr">
+      <c r="A289" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B289" s="79" t="inlineStr">
+      <c r="B289" s="80" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C289" s="80" t="inlineStr">
+      <c r="C289" s="81" t="inlineStr">
         <is>
           <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
-      <c r="D289" s="81" t="inlineStr">
+      <c r="D289" s="82" t="inlineStr">
         <is>
           <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
@@ -19288,61 +19284,61 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F289" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G289" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H289" s="82" t="inlineStr">
+      <c r="F289" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G289" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H289" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I289" s="80" t="inlineStr"/>
+      <c r="I289" s="81" t="inlineStr"/>
       <c r="J289" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K289" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L289" s="80" t="inlineStr"/>
-      <c r="M289" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N289" s="81" t="inlineStr">
+      <c r="K289" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L289" s="81" t="inlineStr"/>
+      <c r="M289" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N289" s="82" t="inlineStr">
         <is>
           <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
     <row r="290" ht="30" customHeight="1">
-      <c r="A290" s="79" t="inlineStr">
+      <c r="A290" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B290" s="79" t="inlineStr">
+      <c r="B290" s="80" t="inlineStr">
         <is>
           <t>More City Events</t>
         </is>
       </c>
-      <c r="C290" s="80" t="inlineStr">
+      <c r="C290" s="81" t="inlineStr">
         <is>
           <t>CX_NYC_01</t>
         </is>
       </c>
-      <c r="D290" s="81" t="inlineStr">
+      <c r="D290" s="82" t="inlineStr">
         <is>
           <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
@@ -19352,61 +19348,61 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F290" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G290" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H290" s="82" t="inlineStr">
+      <c r="F290" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G290" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H290" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I290" s="80" t="inlineStr"/>
+      <c r="I290" s="81" t="inlineStr"/>
       <c r="J290" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K290" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L290" s="80" t="inlineStr"/>
-      <c r="M290" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N290" s="81" t="inlineStr">
+      <c r="K290" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L290" s="81" t="inlineStr"/>
+      <c r="M290" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N290" s="82" t="inlineStr">
         <is>
           <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
     <row r="291" ht="30" customHeight="1">
-      <c r="A291" s="79" t="inlineStr">
+      <c r="A291" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B291" s="79" t="inlineStr">
+      <c r="B291" s="80" t="inlineStr">
         <is>
           <t>Espionage Events</t>
         </is>
       </c>
-      <c r="C291" s="80" t="inlineStr">
+      <c r="C291" s="81" t="inlineStr">
         <is>
           <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
-      <c r="D291" s="81" t="inlineStr">
+      <c r="D291" s="82" t="inlineStr">
         <is>
           <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
         </is>
@@ -19416,61 +19412,61 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F291" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G291" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H291" s="82" t="inlineStr">
+      <c r="F291" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G291" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H291" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I291" s="80" t="inlineStr"/>
+      <c r="I291" s="81" t="inlineStr"/>
       <c r="J291" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K291" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L291" s="80" t="inlineStr"/>
-      <c r="M291" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N291" s="81" t="inlineStr">
+      <c r="K291" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L291" s="81" t="inlineStr"/>
+      <c r="M291" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N291" s="82" t="inlineStr">
         <is>
           <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
         </is>
       </c>
     </row>
     <row r="292" ht="30" customHeight="1">
-      <c r="A292" s="79" t="inlineStr">
+      <c r="A292" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B292" s="79" t="inlineStr">
+      <c r="B292" s="80" t="inlineStr">
         <is>
           <t>Commander Expansion</t>
         </is>
       </c>
-      <c r="C292" s="80" t="inlineStr">
+      <c r="C292" s="81" t="inlineStr">
         <is>
           <t>CMD_OBJECTIVE_2</t>
         </is>
       </c>
-      <c r="D292" s="81" t="inlineStr">
+      <c r="D292" s="82" t="inlineStr">
         <is>
           <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
         </is>
@@ -19480,61 +19476,61 @@
           <t>Followup</t>
         </is>
       </c>
-      <c r="F292" s="81" t="inlineStr">
+      <c r="F292" s="82" t="inlineStr">
         <is>
           <t>CMD_OBJECTIVE_1</t>
         </is>
       </c>
-      <c r="G292" s="81" t="inlineStr">
+      <c r="G292" s="82" t="inlineStr">
         <is>
           <t>→ CMD_OBJECTIVE_3?</t>
         </is>
       </c>
-      <c r="H292" s="82" t="inlineStr">
+      <c r="H292" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I292" s="80" t="inlineStr"/>
+      <c r="I292" s="81" t="inlineStr"/>
       <c r="J292" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K292" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L292" s="80" t="inlineStr"/>
-      <c r="M292" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N292" s="81" t="inlineStr">
+      <c r="K292" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L292" s="81" t="inlineStr"/>
+      <c r="M292" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N292" s="82" t="inlineStr">
         <is>
           <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
     <row r="293" ht="30" customHeight="1">
-      <c r="A293" s="79" t="inlineStr">
+      <c r="A293" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B293" s="79" t="inlineStr">
+      <c r="B293" s="80" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C293" s="80" t="inlineStr">
+      <c r="C293" s="81" t="inlineStr">
         <is>
           <t>WINTER_SIEGE_01</t>
         </is>
       </c>
-      <c r="D293" s="81" t="inlineStr">
+      <c r="D293" s="82" t="inlineStr">
         <is>
           <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
@@ -19544,61 +19540,61 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F293" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G293" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H293" s="82" t="inlineStr">
+      <c r="F293" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G293" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H293" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I293" s="80" t="inlineStr"/>
+      <c r="I293" s="81" t="inlineStr"/>
       <c r="J293" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K293" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L293" s="80" t="inlineStr"/>
-      <c r="M293" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N293" s="81" t="inlineStr">
+      <c r="K293" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L293" s="81" t="inlineStr"/>
+      <c r="M293" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N293" s="82" t="inlineStr">
         <is>
           <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
         </is>
       </c>
     </row>
     <row r="294" ht="30" customHeight="1">
-      <c r="A294" s="79" t="inlineStr">
+      <c r="A294" s="80" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="B294" s="79" t="inlineStr">
+      <c r="B294" s="80" t="inlineStr">
         <is>
           <t>Seasonal Events</t>
         </is>
       </c>
-      <c r="C294" s="80" t="inlineStr">
+      <c r="C294" s="81" t="inlineStr">
         <is>
           <t>SPRING_OFFENSIVE_01</t>
         </is>
       </c>
-      <c r="D294" s="81" t="inlineStr">
+      <c r="D294" s="82" t="inlineStr">
         <is>
           <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
         </is>
@@ -19608,39 +19604,39 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="F294" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G294" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H294" s="82" t="inlineStr">
+      <c r="F294" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G294" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H294" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I294" s="80" t="inlineStr"/>
+      <c r="I294" s="81" t="inlineStr"/>
       <c r="J294" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K294" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L294" s="80" t="inlineStr"/>
-      <c r="M294" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N294" s="81" t="inlineStr">
+      <c r="K294" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L294" s="81" t="inlineStr"/>
+      <c r="M294" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N294" s="82" t="inlineStr">
         <is>
           <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
         </is>
@@ -19663,64 +19659,64 @@
       <c r="N295" s="9" t="n"/>
     </row>
     <row r="296" ht="30" customHeight="1">
-      <c r="A296" s="79" t="inlineStr">
+      <c r="A296" s="80" t="inlineStr">
         <is>
           <t>Commander</t>
         </is>
       </c>
-      <c r="B296" s="79" t="inlineStr">
+      <c r="B296" s="80" t="inlineStr">
         <is>
           <t>Commander Arc</t>
         </is>
       </c>
-      <c r="C296" s="80" t="inlineStr">
+      <c r="C296" s="81" t="inlineStr">
         <is>
           <t>CMD_THANKS_INTIMATE</t>
         </is>
       </c>
-      <c r="D296" s="81" t="inlineStr">
+      <c r="D296" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMM... — BY MORNING</t>
         </is>
       </c>
-      <c r="E296" s="83" t="inlineStr">
+      <c r="E296" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F296" s="81" t="inlineStr">
+      <c r="F296" s="82" t="inlineStr">
         <is>
           <t>CMD_THANKS (intimate choice)</t>
         </is>
       </c>
-      <c r="G296" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H296" s="82" t="inlineStr">
+      <c r="G296" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H296" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I296" s="80" t="inlineStr"/>
-      <c r="J296" s="84" t="inlineStr">
+      <c r="I296" s="81" t="inlineStr"/>
+      <c r="J296" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K296" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L296" s="80" t="inlineStr"/>
-      <c r="M296" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N296" s="81" t="inlineStr">
+      <c r="K296" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L296" s="81" t="inlineStr"/>
+      <c r="M296" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N296" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CMD_THANKS. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -19743,64 +19739,64 @@
       <c r="N297" s="9" t="n"/>
     </row>
     <row r="298" ht="30" customHeight="1">
-      <c r="A298" s="79" t="inlineStr">
+      <c r="A298" s="80" t="inlineStr">
         <is>
           <t>Fort Chain</t>
         </is>
       </c>
-      <c r="B298" s="79" t="inlineStr">
+      <c r="B298" s="80" t="inlineStr">
         <is>
           <t>Fort Disrepair</t>
         </is>
       </c>
-      <c r="C298" s="80" t="inlineStr">
+      <c r="C298" s="81" t="inlineStr">
         <is>
           <t>FORT_005_INTIMATE</t>
         </is>
       </c>
-      <c r="D298" s="81" t="inlineStr">
+      <c r="D298" s="82" t="inlineStr">
         <is>
           <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
-      <c r="E298" s="83" t="inlineStr">
+      <c r="E298" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F298" s="81" t="inlineStr">
+      <c r="F298" s="82" t="inlineStr">
         <is>
           <t>FORT_005 (intimate choice)</t>
         </is>
       </c>
-      <c r="G298" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H298" s="82" t="inlineStr">
+      <c r="G298" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H298" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I298" s="80" t="inlineStr"/>
-      <c r="J298" s="84" t="inlineStr">
+      <c r="I298" s="81" t="inlineStr"/>
+      <c r="J298" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K298" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L298" s="80" t="inlineStr"/>
-      <c r="M298" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N298" s="81" t="inlineStr">
+      <c r="K298" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L298" s="81" t="inlineStr"/>
+      <c r="M298" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N298" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of FORT_005. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -19823,64 +19819,64 @@
       <c r="N299" s="9" t="n"/>
     </row>
     <row r="300" ht="30" customHeight="1">
-      <c r="A300" s="79" t="inlineStr">
+      <c r="A300" s="80" t="inlineStr">
         <is>
           <t>Collapse</t>
         </is>
       </c>
-      <c r="B300" s="79" t="inlineStr">
+      <c r="B300" s="80" t="inlineStr">
         <is>
           <t>Republic Falls</t>
         </is>
       </c>
-      <c r="C300" s="80" t="inlineStr">
+      <c r="C300" s="81" t="inlineStr">
         <is>
           <t>COLLAPSE_02_INTIMATE</t>
         </is>
       </c>
-      <c r="D300" s="81" t="inlineStr">
+      <c r="D300" s="82" t="inlineStr">
         <is>
           <t>WASHINGTON STANDS ALONE — BY MORNING</t>
         </is>
       </c>
-      <c r="E300" s="83" t="inlineStr">
+      <c r="E300" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F300" s="81" t="inlineStr">
+      <c r="F300" s="82" t="inlineStr">
         <is>
           <t>COLLAPSE_02 (intimate choice)</t>
         </is>
       </c>
-      <c r="G300" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H300" s="82" t="inlineStr">
+      <c r="G300" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H300" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I300" s="80" t="inlineStr"/>
-      <c r="J300" s="84" t="inlineStr">
+      <c r="I300" s="81" t="inlineStr"/>
+      <c r="J300" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K300" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L300" s="80" t="inlineStr"/>
-      <c r="M300" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N300" s="81" t="inlineStr">
+      <c r="K300" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L300" s="81" t="inlineStr"/>
+      <c r="M300" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N300" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of COLLAPSE_02. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -19903,128 +19899,128 @@
       <c r="N301" s="9" t="n"/>
     </row>
     <row r="302" ht="30" customHeight="1">
-      <c r="A302" s="79" t="inlineStr">
+      <c r="A302" s="80" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B302" s="79" t="inlineStr">
+      <c r="B302" s="80" t="inlineStr">
         <is>
           <t>Harvest Crisis</t>
         </is>
       </c>
-      <c r="C302" s="80" t="inlineStr">
+      <c r="C302" s="81" t="inlineStr">
         <is>
           <t>HARVEST_VISIT_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D302" s="81" t="inlineStr">
+      <c r="D302" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE SAVES THE HARVEST — BY MORNING</t>
         </is>
       </c>
-      <c r="E302" s="83" t="inlineStr">
+      <c r="E302" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F302" s="81" t="inlineStr">
+      <c r="F302" s="82" t="inlineStr">
         <is>
           <t>HARVEST_VISIT_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G302" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H302" s="82" t="inlineStr">
+      <c r="G302" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H302" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I302" s="80" t="inlineStr"/>
-      <c r="J302" s="84" t="inlineStr">
+      <c r="I302" s="81" t="inlineStr"/>
+      <c r="J302" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K302" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L302" s="80" t="inlineStr"/>
-      <c r="M302" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N302" s="81" t="inlineStr">
+      <c r="K302" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L302" s="81" t="inlineStr"/>
+      <c r="M302" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N302" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of HARVEST_VISIT_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1">
-      <c r="A303" s="79" t="inlineStr">
+      <c r="A303" s="80" t="inlineStr">
         <is>
           <t>Tile Crisis</t>
         </is>
       </c>
-      <c r="B303" s="79" t="inlineStr">
+      <c r="B303" s="80" t="inlineStr">
         <is>
           <t>Election Arc</t>
         </is>
       </c>
-      <c r="C303" s="80" t="inlineStr">
+      <c r="C303" s="81" t="inlineStr">
         <is>
           <t>STUMP_SPEECH_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D303" s="81" t="inlineStr">
+      <c r="D303" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E303" s="83" t="inlineStr">
+      <c r="E303" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F303" s="81" t="inlineStr">
+      <c r="F303" s="82" t="inlineStr">
         <is>
           <t>STUMP_SPEECH_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G303" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H303" s="82" t="inlineStr">
+      <c r="G303" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H303" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I303" s="80" t="inlineStr"/>
-      <c r="J303" s="84" t="inlineStr">
+      <c r="I303" s="81" t="inlineStr"/>
+      <c r="J303" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K303" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L303" s="80" t="inlineStr"/>
-      <c r="M303" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N303" s="81" t="inlineStr">
+      <c r="K303" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L303" s="81" t="inlineStr"/>
+      <c r="M303" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N303" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of STUMP_SPEECH_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -20047,256 +20043,256 @@
       <c r="N304" s="9" t="n"/>
     </row>
     <row r="305" ht="30" customHeight="1">
-      <c r="A305" s="79" t="inlineStr">
+      <c r="A305" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B305" s="79" t="inlineStr">
+      <c r="B305" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C305" s="80" t="inlineStr">
+      <c r="C305" s="81" t="inlineStr">
         <is>
           <t>VP_DOUBT_INTIMATE</t>
         </is>
       </c>
-      <c r="D305" s="81" t="inlineStr">
+      <c r="D305" s="82" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QU... — BY MORNING</t>
         </is>
       </c>
-      <c r="E305" s="83" t="inlineStr">
+      <c r="E305" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F305" s="81" t="inlineStr">
+      <c r="F305" s="82" t="inlineStr">
         <is>
           <t>VP_DOUBT (intimate choice)</t>
         </is>
       </c>
-      <c r="G305" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H305" s="82" t="inlineStr">
+      <c r="G305" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H305" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I305" s="80" t="inlineStr"/>
-      <c r="J305" s="84" t="inlineStr">
+      <c r="I305" s="81" t="inlineStr"/>
+      <c r="J305" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K305" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L305" s="80" t="inlineStr"/>
-      <c r="M305" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N305" s="81" t="inlineStr">
+      <c r="K305" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L305" s="81" t="inlineStr"/>
+      <c r="M305" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N305" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of VP_DOUBT. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="306" ht="30" customHeight="1">
-      <c r="A306" s="79" t="inlineStr">
+      <c r="A306" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B306" s="79" t="inlineStr">
+      <c r="B306" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C306" s="80" t="inlineStr">
+      <c r="C306" s="81" t="inlineStr">
         <is>
           <t>VP_BATTLEFIELD_INTIMATE</t>
         </is>
       </c>
-      <c r="D306" s="81" t="inlineStr">
+      <c r="D306" s="82" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAM... — BY MORNING</t>
         </is>
       </c>
-      <c r="E306" s="83" t="inlineStr">
+      <c r="E306" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F306" s="81" t="inlineStr">
+      <c r="F306" s="82" t="inlineStr">
         <is>
           <t>VP_BATTLEFIELD (intimate choice)</t>
         </is>
       </c>
-      <c r="G306" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H306" s="82" t="inlineStr">
+      <c r="G306" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H306" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I306" s="80" t="inlineStr"/>
-      <c r="J306" s="84" t="inlineStr">
+      <c r="I306" s="81" t="inlineStr"/>
+      <c r="J306" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K306" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L306" s="80" t="inlineStr"/>
-      <c r="M306" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N306" s="81" t="inlineStr">
+      <c r="K306" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L306" s="81" t="inlineStr"/>
+      <c r="M306" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N306" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of VP_BATTLEFIELD. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="307" ht="30" customHeight="1">
-      <c r="A307" s="79" t="inlineStr">
+      <c r="A307" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B307" s="79" t="inlineStr">
+      <c r="B307" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C307" s="80" t="inlineStr">
+      <c r="C307" s="81" t="inlineStr">
         <is>
           <t>VP_PRE_ELECTION_INTIMATE</t>
         </is>
       </c>
-      <c r="D307" s="81" t="inlineStr">
+      <c r="D307" s="82" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [C... — BY MORNING</t>
         </is>
       </c>
-      <c r="E307" s="83" t="inlineStr">
+      <c r="E307" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F307" s="81" t="inlineStr">
+      <c r="F307" s="82" t="inlineStr">
         <is>
           <t>VP_PRE_ELECTION (intimate choice)</t>
         </is>
       </c>
-      <c r="G307" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H307" s="82" t="inlineStr">
+      <c r="G307" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H307" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I307" s="80" t="inlineStr"/>
-      <c r="J307" s="84" t="inlineStr">
+      <c r="I307" s="81" t="inlineStr"/>
+      <c r="J307" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K307" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L307" s="80" t="inlineStr"/>
-      <c r="M307" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N307" s="81" t="inlineStr">
+      <c r="K307" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L307" s="81" t="inlineStr"/>
+      <c r="M307" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N307" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of VP_PRE_ELECTION. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="308" ht="30" customHeight="1">
-      <c r="A308" s="79" t="inlineStr">
+      <c r="A308" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B308" s="79" t="inlineStr">
+      <c r="B308" s="80" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C308" s="80" t="inlineStr">
+      <c r="C308" s="81" t="inlineStr">
         <is>
           <t>VP_LEGACY_INTIMATE</t>
         </is>
       </c>
-      <c r="D308" s="81" t="inlineStr">
+      <c r="D308" s="82" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E308" s="83" t="inlineStr">
+      <c r="E308" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F308" s="81" t="inlineStr">
+      <c r="F308" s="82" t="inlineStr">
         <is>
           <t>VP_LEGACY (intimate choice)</t>
         </is>
       </c>
-      <c r="G308" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H308" s="82" t="inlineStr">
+      <c r="G308" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H308" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I308" s="80" t="inlineStr"/>
-      <c r="J308" s="84" t="inlineStr">
+      <c r="I308" s="81" t="inlineStr"/>
+      <c r="J308" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K308" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L308" s="80" t="inlineStr"/>
-      <c r="M308" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N308" s="81" t="inlineStr">
+      <c r="K308" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L308" s="81" t="inlineStr"/>
+      <c r="M308" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N308" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of VP_LEGACY. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -20319,448 +20315,448 @@
       <c r="N309" s="9" t="n"/>
     </row>
     <row r="310" ht="30" customHeight="1">
-      <c r="A310" s="79" t="inlineStr">
+      <c r="A310" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B310" s="79" t="inlineStr">
+      <c r="B310" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C310" s="80" t="inlineStr">
+      <c r="C310" s="81" t="inlineStr">
         <is>
           <t>CAN_CLEARWATER_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D310" s="81" t="inlineStr">
+      <c r="D310" s="82" t="inlineStr">
         <is>
           <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
         </is>
       </c>
-      <c r="E310" s="83" t="inlineStr">
+      <c r="E310" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F310" s="81" t="inlineStr">
+      <c r="F310" s="82" t="inlineStr">
         <is>
           <t>CAN_CLEARWATER_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G310" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H310" s="82" t="inlineStr">
+      <c r="G310" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H310" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I310" s="80" t="inlineStr"/>
-      <c r="J310" s="84" t="inlineStr">
+      <c r="I310" s="81" t="inlineStr"/>
+      <c r="J310" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K310" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L310" s="80" t="inlineStr"/>
-      <c r="M310" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N310" s="81" t="inlineStr">
+      <c r="K310" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L310" s="81" t="inlineStr"/>
+      <c r="M310" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N310" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="311" ht="30" customHeight="1">
-      <c r="A311" s="79" t="inlineStr">
+      <c r="A311" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B311" s="79" t="inlineStr">
+      <c r="B311" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C311" s="80" t="inlineStr">
+      <c r="C311" s="81" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D311" s="81" t="inlineStr">
+      <c r="D311" s="82" t="inlineStr">
         <is>
           <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
         </is>
       </c>
-      <c r="E311" s="83" t="inlineStr">
+      <c r="E311" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F311" s="81" t="inlineStr">
+      <c r="F311" s="82" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G311" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H311" s="82" t="inlineStr">
+      <c r="G311" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H311" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I311" s="80" t="inlineStr"/>
-      <c r="J311" s="84" t="inlineStr">
+      <c r="I311" s="81" t="inlineStr"/>
+      <c r="J311" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K311" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L311" s="80" t="inlineStr"/>
-      <c r="M311" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N311" s="81" t="inlineStr">
+      <c r="K311" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L311" s="81" t="inlineStr"/>
+      <c r="M311" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N311" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="312" ht="30" customHeight="1">
-      <c r="A312" s="79" t="inlineStr">
+      <c r="A312" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B312" s="79" t="inlineStr">
+      <c r="B312" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C312" s="80" t="inlineStr">
+      <c r="C312" s="81" t="inlineStr">
         <is>
           <t>CAN_SUMMIT_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D312" s="81" t="inlineStr">
+      <c r="D312" s="82" t="inlineStr">
         <is>
           <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
         </is>
       </c>
-      <c r="E312" s="83" t="inlineStr">
+      <c r="E312" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F312" s="81" t="inlineStr">
+      <c r="F312" s="82" t="inlineStr">
         <is>
           <t>CAN_SUMMIT_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G312" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H312" s="82" t="inlineStr">
+      <c r="G312" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H312" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I312" s="80" t="inlineStr"/>
-      <c r="J312" s="84" t="inlineStr">
+      <c r="I312" s="81" t="inlineStr"/>
+      <c r="J312" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K312" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L312" s="80" t="inlineStr"/>
-      <c r="M312" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N312" s="81" t="inlineStr">
+      <c r="K312" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L312" s="81" t="inlineStr"/>
+      <c r="M312" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N312" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="313" ht="30" customHeight="1">
-      <c r="A313" s="79" t="inlineStr">
+      <c r="A313" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B313" s="79" t="inlineStr">
+      <c r="B313" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C313" s="80" t="inlineStr">
+      <c r="C313" s="81" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK_INTIMATE</t>
         </is>
       </c>
-      <c r="D313" s="81" t="inlineStr">
+      <c r="D313" s="82" t="inlineStr">
         <is>
           <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E313" s="83" t="inlineStr">
+      <c r="E313" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F313" s="81" t="inlineStr">
+      <c r="F313" s="82" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK (intimate choice)</t>
         </is>
       </c>
-      <c r="G313" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H313" s="82" t="inlineStr">
+      <c r="G313" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H313" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I313" s="80" t="inlineStr"/>
-      <c r="J313" s="84" t="inlineStr">
+      <c r="I313" s="81" t="inlineStr"/>
+      <c r="J313" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K313" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L313" s="80" t="inlineStr"/>
-      <c r="M313" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N313" s="81" t="inlineStr">
+      <c r="K313" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L313" s="81" t="inlineStr"/>
+      <c r="M313" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N313" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="314" ht="30" customHeight="1">
-      <c r="A314" s="79" t="inlineStr">
+      <c r="A314" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B314" s="79" t="inlineStr">
+      <c r="B314" s="80" t="inlineStr">
         <is>
           <t>Peace</t>
         </is>
       </c>
-      <c r="C314" s="80" t="inlineStr">
+      <c r="C314" s="81" t="inlineStr">
         <is>
           <t>CAN_PEACE_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D314" s="81" t="inlineStr">
+      <c r="D314" s="82" t="inlineStr">
         <is>
           <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E314" s="83" t="inlineStr">
+      <c r="E314" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F314" s="81" t="inlineStr">
+      <c r="F314" s="82" t="inlineStr">
         <is>
           <t>CAN_PEACE_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G314" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H314" s="82" t="inlineStr">
+      <c r="G314" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H314" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I314" s="80" t="inlineStr"/>
-      <c r="J314" s="84" t="inlineStr">
+      <c r="I314" s="81" t="inlineStr"/>
+      <c r="J314" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K314" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L314" s="80" t="inlineStr"/>
-      <c r="M314" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N314" s="81" t="inlineStr">
+      <c r="K314" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L314" s="81" t="inlineStr"/>
+      <c r="M314" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N314" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="315" ht="30" customHeight="1">
-      <c r="A315" s="79" t="inlineStr">
+      <c r="A315" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B315" s="79" t="inlineStr">
+      <c r="B315" s="80" t="inlineStr">
         <is>
           <t>Peace</t>
         </is>
       </c>
-      <c r="C315" s="80" t="inlineStr">
+      <c r="C315" s="81" t="inlineStr">
         <is>
           <t>PEACE_ALLIED_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D315" s="81" t="inlineStr">
+      <c r="D315" s="82" t="inlineStr">
         <is>
           <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
         </is>
       </c>
-      <c r="E315" s="83" t="inlineStr">
+      <c r="E315" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F315" s="81" t="inlineStr">
+      <c r="F315" s="82" t="inlineStr">
         <is>
           <t>PEACE_ALLIED_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G315" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H315" s="82" t="inlineStr">
+      <c r="G315" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H315" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I315" s="80" t="inlineStr"/>
-      <c r="J315" s="84" t="inlineStr">
+      <c r="I315" s="81" t="inlineStr"/>
+      <c r="J315" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K315" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L315" s="80" t="inlineStr"/>
-      <c r="M315" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N315" s="81" t="inlineStr">
+      <c r="K315" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L315" s="81" t="inlineStr"/>
+      <c r="M315" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N315" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="316" ht="30" customHeight="1">
-      <c r="A316" s="79" t="inlineStr">
+      <c r="A316" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B316" s="79" t="inlineStr">
+      <c r="B316" s="80" t="inlineStr">
         <is>
           <t>Peace</t>
         </is>
       </c>
-      <c r="C316" s="80" t="inlineStr">
+      <c r="C316" s="81" t="inlineStr">
         <is>
           <t>PEACE_USA_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D316" s="81" t="inlineStr">
+      <c r="D316" s="82" t="inlineStr">
         <is>
           <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
         </is>
       </c>
-      <c r="E316" s="83" t="inlineStr">
+      <c r="E316" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F316" s="81" t="inlineStr">
+      <c r="F316" s="82" t="inlineStr">
         <is>
           <t>PEACE_USA_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G316" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H316" s="82" t="inlineStr">
+      <c r="G316" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H316" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I316" s="80" t="inlineStr"/>
-      <c r="J316" s="84" t="inlineStr">
+      <c r="I316" s="81" t="inlineStr"/>
+      <c r="J316" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K316" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L316" s="80" t="inlineStr"/>
-      <c r="M316" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N316" s="81" t="inlineStr">
+      <c r="K316" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L316" s="81" t="inlineStr"/>
+      <c r="M316" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N316" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -20783,512 +20779,512 @@
       <c r="N317" s="9" t="n"/>
     </row>
     <row r="318" ht="30" customHeight="1">
-      <c r="A318" s="79" t="inlineStr">
+      <c r="A318" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B318" s="79" t="inlineStr">
+      <c r="B318" s="80" t="inlineStr">
         <is>
           <t>Le Wendigo</t>
         </is>
       </c>
-      <c r="C318" s="80" t="inlineStr">
+      <c r="C318" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D318" s="81" t="inlineStr">
+      <c r="D318" s="82" t="inlineStr">
         <is>
           <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
         </is>
       </c>
-      <c r="E318" s="83" t="inlineStr">
+      <c r="E318" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F318" s="81" t="inlineStr">
+      <c r="F318" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G318" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H318" s="82" t="inlineStr">
+      <c r="G318" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H318" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I318" s="80" t="inlineStr"/>
-      <c r="J318" s="84" t="inlineStr">
+      <c r="I318" s="81" t="inlineStr"/>
+      <c r="J318" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K318" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L318" s="80" t="inlineStr"/>
-      <c r="M318" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N318" s="81" t="inlineStr">
+      <c r="K318" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L318" s="81" t="inlineStr"/>
+      <c r="M318" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N318" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="319" ht="30" customHeight="1">
-      <c r="A319" s="79" t="inlineStr">
+      <c r="A319" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B319" s="79" t="inlineStr">
+      <c r="B319" s="80" t="inlineStr">
         <is>
           <t>Le Loup-Garou</t>
         </is>
       </c>
-      <c r="C319" s="80" t="inlineStr">
+      <c r="C319" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D319" s="81" t="inlineStr">
+      <c r="D319" s="82" t="inlineStr">
         <is>
           <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
-      <c r="E319" s="83" t="inlineStr">
+      <c r="E319" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F319" s="81" t="inlineStr">
+      <c r="F319" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G319" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H319" s="82" t="inlineStr">
+      <c r="G319" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H319" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I319" s="80" t="inlineStr"/>
-      <c r="J319" s="84" t="inlineStr">
+      <c r="I319" s="81" t="inlineStr"/>
+      <c r="J319" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K319" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L319" s="80" t="inlineStr"/>
-      <c r="M319" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N319" s="81" t="inlineStr">
+      <c r="K319" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L319" s="81" t="inlineStr"/>
+      <c r="M319" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N319" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="320" ht="30" customHeight="1">
-      <c r="A320" s="79" t="inlineStr">
+      <c r="A320" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B320" s="79" t="inlineStr">
+      <c r="B320" s="80" t="inlineStr">
         <is>
           <t>Les Feux Follets</t>
         </is>
       </c>
-      <c r="C320" s="80" t="inlineStr">
+      <c r="C320" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D320" s="81" t="inlineStr">
+      <c r="D320" s="82" t="inlineStr">
         <is>
           <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
-      <c r="E320" s="83" t="inlineStr">
+      <c r="E320" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F320" s="81" t="inlineStr">
+      <c r="F320" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G320" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H320" s="82" t="inlineStr">
+      <c r="G320" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H320" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I320" s="80" t="inlineStr"/>
-      <c r="J320" s="84" t="inlineStr">
+      <c r="I320" s="81" t="inlineStr"/>
+      <c r="J320" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K320" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L320" s="80" t="inlineStr"/>
-      <c r="M320" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N320" s="81" t="inlineStr">
+      <c r="K320" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L320" s="81" t="inlineStr"/>
+      <c r="M320" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N320" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="321" ht="30" customHeight="1">
-      <c r="A321" s="79" t="inlineStr">
+      <c r="A321" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B321" s="79" t="inlineStr">
+      <c r="B321" s="80" t="inlineStr">
         <is>
           <t>Mishepeshu</t>
         </is>
       </c>
-      <c r="C321" s="80" t="inlineStr">
+      <c r="C321" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D321" s="81" t="inlineStr">
+      <c r="D321" s="82" t="inlineStr">
         <is>
           <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
-      <c r="E321" s="83" t="inlineStr">
+      <c r="E321" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F321" s="81" t="inlineStr">
+      <c r="F321" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G321" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H321" s="82" t="inlineStr">
+      <c r="G321" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H321" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I321" s="80" t="inlineStr"/>
-      <c r="J321" s="84" t="inlineStr">
+      <c r="I321" s="81" t="inlineStr"/>
+      <c r="J321" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K321" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L321" s="80" t="inlineStr"/>
-      <c r="M321" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N321" s="81" t="inlineStr">
+      <c r="K321" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L321" s="81" t="inlineStr"/>
+      <c r="M321" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N321" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="322" ht="30" customHeight="1">
-      <c r="A322" s="79" t="inlineStr">
+      <c r="A322" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B322" s="79" t="inlineStr">
+      <c r="B322" s="80" t="inlineStr">
         <is>
           <t>La Corriveau</t>
         </is>
       </c>
-      <c r="C322" s="80" t="inlineStr">
+      <c r="C322" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D322" s="81" t="inlineStr">
+      <c r="D322" s="82" t="inlineStr">
         <is>
           <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
-      <c r="E322" s="83" t="inlineStr">
+      <c r="E322" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F322" s="81" t="inlineStr">
+      <c r="F322" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G322" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H322" s="82" t="inlineStr">
+      <c r="G322" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H322" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I322" s="80" t="inlineStr"/>
-      <c r="J322" s="84" t="inlineStr">
+      <c r="I322" s="81" t="inlineStr"/>
+      <c r="J322" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K322" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L322" s="80" t="inlineStr"/>
-      <c r="M322" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N322" s="81" t="inlineStr">
+      <c r="K322" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L322" s="81" t="inlineStr"/>
+      <c r="M322" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N322" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="323" ht="30" customHeight="1">
-      <c r="A323" s="79" t="inlineStr">
+      <c r="A323" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B323" s="79" t="inlineStr">
+      <c r="B323" s="80" t="inlineStr">
         <is>
           <t>Le Carcajou</t>
         </is>
       </c>
-      <c r="C323" s="80" t="inlineStr">
+      <c r="C323" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D323" s="81" t="inlineStr">
+      <c r="D323" s="82" t="inlineStr">
         <is>
           <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
-      <c r="E323" s="83" t="inlineStr">
+      <c r="E323" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F323" s="81" t="inlineStr">
+      <c r="F323" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G323" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H323" s="82" t="inlineStr">
+      <c r="G323" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H323" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I323" s="80" t="inlineStr"/>
-      <c r="J323" s="84" t="inlineStr">
+      <c r="I323" s="81" t="inlineStr"/>
+      <c r="J323" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K323" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L323" s="80" t="inlineStr"/>
-      <c r="M323" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N323" s="81" t="inlineStr">
+      <c r="K323" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L323" s="81" t="inlineStr"/>
+      <c r="M323" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N323" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="324" ht="30" customHeight="1">
-      <c r="A324" s="79" t="inlineStr">
+      <c r="A324" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B324" s="79" t="inlineStr">
+      <c r="B324" s="80" t="inlineStr">
         <is>
           <t>La Chasse-Galerie</t>
         </is>
       </c>
-      <c r="C324" s="80" t="inlineStr">
+      <c r="C324" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D324" s="81" t="inlineStr">
+      <c r="D324" s="82" t="inlineStr">
         <is>
           <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
-      <c r="E324" s="83" t="inlineStr">
+      <c r="E324" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F324" s="81" t="inlineStr">
+      <c r="F324" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G324" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H324" s="82" t="inlineStr">
+      <c r="G324" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H324" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I324" s="80" t="inlineStr"/>
-      <c r="J324" s="84" t="inlineStr">
+      <c r="I324" s="81" t="inlineStr"/>
+      <c r="J324" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K324" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L324" s="80" t="inlineStr"/>
-      <c r="M324" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N324" s="81" t="inlineStr">
+      <c r="K324" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L324" s="81" t="inlineStr"/>
+      <c r="M324" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N324" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="325" ht="30" customHeight="1">
-      <c r="A325" s="79" t="inlineStr">
+      <c r="A325" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B325" s="79" t="inlineStr">
+      <c r="B325" s="80" t="inlineStr">
         <is>
           <t>Le Gougou</t>
         </is>
       </c>
-      <c r="C325" s="80" t="inlineStr">
+      <c r="C325" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D325" s="81" t="inlineStr">
+      <c r="D325" s="82" t="inlineStr">
         <is>
           <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
         </is>
       </c>
-      <c r="E325" s="83" t="inlineStr">
+      <c r="E325" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F325" s="81" t="inlineStr">
+      <c r="F325" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G325" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H325" s="82" t="inlineStr">
+      <c r="G325" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H325" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I325" s="80" t="inlineStr"/>
-      <c r="J325" s="84" t="inlineStr">
+      <c r="I325" s="81" t="inlineStr"/>
+      <c r="J325" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K325" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L325" s="80" t="inlineStr"/>
-      <c r="M325" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N325" s="81" t="inlineStr">
+      <c r="K325" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L325" s="81" t="inlineStr"/>
+      <c r="M325" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N325" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -21311,512 +21307,512 @@
       <c r="N326" s="9" t="n"/>
     </row>
     <row r="327" ht="30" customHeight="1">
-      <c r="A327" s="79" t="inlineStr">
+      <c r="A327" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B327" s="79" t="inlineStr">
+      <c r="B327" s="80" t="inlineStr">
         <is>
           <t>Ambush</t>
         </is>
       </c>
-      <c r="C327" s="80" t="inlineStr">
+      <c r="C327" s="81" t="inlineStr">
         <is>
           <t>UALANI_AMBUSH_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D327" s="81" t="inlineStr">
+      <c r="D327" s="82" t="inlineStr">
         <is>
           <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
         </is>
       </c>
-      <c r="E327" s="83" t="inlineStr">
+      <c r="E327" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F327" s="81" t="inlineStr">
+      <c r="F327" s="82" t="inlineStr">
         <is>
           <t>UALANI_AMBUSH_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G327" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H327" s="82" t="inlineStr">
+      <c r="G327" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H327" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I327" s="80" t="inlineStr"/>
-      <c r="J327" s="84" t="inlineStr">
+      <c r="I327" s="81" t="inlineStr"/>
+      <c r="J327" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K327" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L327" s="80" t="inlineStr"/>
-      <c r="M327" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N327" s="81" t="inlineStr">
+      <c r="K327" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L327" s="81" t="inlineStr"/>
+      <c r="M327" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N327" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="328" ht="30" customHeight="1">
-      <c r="A328" s="79" t="inlineStr">
+      <c r="A328" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B328" s="79" t="inlineStr">
+      <c r="B328" s="80" t="inlineStr">
         <is>
           <t>Dignitary Reception</t>
         </is>
       </c>
-      <c r="C328" s="80" t="inlineStr">
+      <c r="C328" s="81" t="inlineStr">
         <is>
           <t>UALANI_DIGNITARY_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D328" s="81" t="inlineStr">
+      <c r="D328" s="82" t="inlineStr">
         <is>
           <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
         </is>
       </c>
-      <c r="E328" s="83" t="inlineStr">
+      <c r="E328" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F328" s="81" t="inlineStr">
+      <c r="F328" s="82" t="inlineStr">
         <is>
           <t>UALANI_DIGNITARY_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G328" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H328" s="82" t="inlineStr">
+      <c r="G328" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H328" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I328" s="80" t="inlineStr"/>
-      <c r="J328" s="84" t="inlineStr">
+      <c r="I328" s="81" t="inlineStr"/>
+      <c r="J328" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K328" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L328" s="80" t="inlineStr"/>
-      <c r="M328" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N328" s="81" t="inlineStr">
+      <c r="K328" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L328" s="81" t="inlineStr"/>
+      <c r="M328" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N328" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="329" ht="30" customHeight="1">
-      <c r="A329" s="79" t="inlineStr">
+      <c r="A329" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B329" s="79" t="inlineStr">
+      <c r="B329" s="80" t="inlineStr">
         <is>
           <t>Memorial Address</t>
         </is>
       </c>
-      <c r="C329" s="80" t="inlineStr">
+      <c r="C329" s="81" t="inlineStr">
         <is>
           <t>UALANI_MEMORIAL_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D329" s="81" t="inlineStr">
+      <c r="D329" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E329" s="83" t="inlineStr">
+      <c r="E329" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F329" s="81" t="inlineStr">
+      <c r="F329" s="82" t="inlineStr">
         <is>
           <t>UALANI_MEMORIAL_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G329" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H329" s="82" t="inlineStr">
+      <c r="G329" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H329" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I329" s="80" t="inlineStr"/>
-      <c r="J329" s="84" t="inlineStr">
+      <c r="I329" s="81" t="inlineStr"/>
+      <c r="J329" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K329" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L329" s="80" t="inlineStr"/>
-      <c r="M329" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N329" s="81" t="inlineStr">
+      <c r="K329" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L329" s="81" t="inlineStr"/>
+      <c r="M329" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N329" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="330" ht="30" customHeight="1">
-      <c r="A330" s="79" t="inlineStr">
+      <c r="A330" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B330" s="79" t="inlineStr">
+      <c r="B330" s="80" t="inlineStr">
         <is>
           <t>Field Hospital</t>
         </is>
       </c>
-      <c r="C330" s="80" t="inlineStr">
+      <c r="C330" s="81" t="inlineStr">
         <is>
           <t>UALANI_WOUNDED_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D330" s="81" t="inlineStr">
+      <c r="D330" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
-      <c r="E330" s="83" t="inlineStr">
+      <c r="E330" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F330" s="81" t="inlineStr">
+      <c r="F330" s="82" t="inlineStr">
         <is>
           <t>UALANI_WOUNDED_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G330" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H330" s="82" t="inlineStr">
+      <c r="G330" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H330" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I330" s="80" t="inlineStr"/>
-      <c r="J330" s="84" t="inlineStr">
+      <c r="I330" s="81" t="inlineStr"/>
+      <c r="J330" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K330" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L330" s="80" t="inlineStr"/>
-      <c r="M330" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N330" s="81" t="inlineStr">
+      <c r="K330" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L330" s="81" t="inlineStr"/>
+      <c r="M330" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N330" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="331" ht="30" customHeight="1">
-      <c r="A331" s="79" t="inlineStr">
+      <c r="A331" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B331" s="79" t="inlineStr">
+      <c r="B331" s="80" t="inlineStr">
         <is>
           <t>Forge Inspection</t>
         </is>
       </c>
-      <c r="C331" s="80" t="inlineStr">
+      <c r="C331" s="81" t="inlineStr">
         <is>
           <t>UALANI_FORGE_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D331" s="81" t="inlineStr">
+      <c r="D331" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
         </is>
       </c>
-      <c r="E331" s="83" t="inlineStr">
+      <c r="E331" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F331" s="81" t="inlineStr">
+      <c r="F331" s="82" t="inlineStr">
         <is>
           <t>UALANI_FORGE_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G331" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H331" s="82" t="inlineStr">
+      <c r="G331" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H331" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I331" s="80" t="inlineStr"/>
-      <c r="J331" s="84" t="inlineStr">
+      <c r="I331" s="81" t="inlineStr"/>
+      <c r="J331" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K331" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L331" s="80" t="inlineStr"/>
-      <c r="M331" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N331" s="81" t="inlineStr">
+      <c r="K331" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L331" s="81" t="inlineStr"/>
+      <c r="M331" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N331" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="332" ht="30" customHeight="1">
-      <c r="A332" s="79" t="inlineStr">
+      <c r="A332" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B332" s="79" t="inlineStr">
+      <c r="B332" s="80" t="inlineStr">
         <is>
           <t>Culper Ring</t>
         </is>
       </c>
-      <c r="C332" s="80" t="inlineStr">
+      <c r="C332" s="81" t="inlineStr">
         <is>
           <t>UALANI_CULPER_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D332" s="81" t="inlineStr">
+      <c r="D332" s="82" t="inlineStr">
         <is>
           <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
         </is>
       </c>
-      <c r="E332" s="83" t="inlineStr">
+      <c r="E332" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F332" s="81" t="inlineStr">
+      <c r="F332" s="82" t="inlineStr">
         <is>
           <t>UALANI_CULPER_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G332" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H332" s="82" t="inlineStr">
+      <c r="G332" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H332" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I332" s="80" t="inlineStr"/>
-      <c r="J332" s="84" t="inlineStr">
+      <c r="I332" s="81" t="inlineStr"/>
+      <c r="J332" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K332" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L332" s="80" t="inlineStr"/>
-      <c r="M332" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N332" s="81" t="inlineStr">
+      <c r="K332" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L332" s="81" t="inlineStr"/>
+      <c r="M332" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N332" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="333" ht="30" customHeight="1">
-      <c r="A333" s="79" t="inlineStr">
+      <c r="A333" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B333" s="79" t="inlineStr">
+      <c r="B333" s="80" t="inlineStr">
         <is>
           <t>Alliance Council</t>
         </is>
       </c>
-      <c r="C333" s="80" t="inlineStr">
+      <c r="C333" s="81" t="inlineStr">
         <is>
           <t>UALANI_ALLIANCE_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D333" s="81" t="inlineStr">
+      <c r="D333" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
         </is>
       </c>
-      <c r="E333" s="83" t="inlineStr">
+      <c r="E333" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F333" s="81" t="inlineStr">
+      <c r="F333" s="82" t="inlineStr">
         <is>
           <t>UALANI_ALLIANCE_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G333" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H333" s="82" t="inlineStr">
+      <c r="G333" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H333" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I333" s="80" t="inlineStr"/>
-      <c r="J333" s="84" t="inlineStr">
+      <c r="I333" s="81" t="inlineStr"/>
+      <c r="J333" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K333" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L333" s="80" t="inlineStr"/>
-      <c r="M333" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N333" s="81" t="inlineStr">
+      <c r="K333" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L333" s="81" t="inlineStr"/>
+      <c r="M333" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N333" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="334" ht="30" customHeight="1">
-      <c r="A334" s="79" t="inlineStr">
+      <c r="A334" s="80" t="inlineStr">
         <is>
           <t>Ualani</t>
         </is>
       </c>
-      <c r="B334" s="79" t="inlineStr">
+      <c r="B334" s="80" t="inlineStr">
         <is>
           <t>Frontier</t>
         </is>
       </c>
-      <c r="C334" s="80" t="inlineStr">
+      <c r="C334" s="81" t="inlineStr">
         <is>
           <t>UALANI_FRONTIER_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D334" s="81" t="inlineStr">
+      <c r="D334" s="82" t="inlineStr">
         <is>
           <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E334" s="83" t="inlineStr">
+      <c r="E334" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F334" s="81" t="inlineStr">
+      <c r="F334" s="82" t="inlineStr">
         <is>
           <t>UALANI_FRONTIER_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G334" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H334" s="82" t="inlineStr">
+      <c r="G334" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H334" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I334" s="80" t="inlineStr"/>
-      <c r="J334" s="84" t="inlineStr">
+      <c r="I334" s="81" t="inlineStr"/>
+      <c r="J334" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K334" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L334" s="80" t="inlineStr"/>
-      <c r="M334" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N334" s="81" t="inlineStr">
+      <c r="K334" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L334" s="81" t="inlineStr"/>
+      <c r="M334" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N334" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -21839,64 +21835,64 @@
       <c r="N335" s="9" t="n"/>
     </row>
     <row r="336" ht="30" customHeight="1">
-      <c r="A336" s="79" t="inlineStr">
+      <c r="A336" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B336" s="79" t="inlineStr">
+      <c r="B336" s="80" t="inlineStr">
         <is>
           <t>Mothman</t>
         </is>
       </c>
-      <c r="C336" s="80" t="inlineStr">
+      <c r="C336" s="81" t="inlineStr">
         <is>
           <t>PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D336" s="81" t="inlineStr">
+      <c r="D336" s="82" t="inlineStr">
         <is>
           <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
         </is>
       </c>
-      <c r="E336" s="83" t="inlineStr">
+      <c r="E336" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F336" s="81" t="inlineStr">
+      <c r="F336" s="82" t="inlineStr">
         <is>
           <t>PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G336" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H336" s="82" t="inlineStr">
+      <c r="G336" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H336" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I336" s="80" t="inlineStr"/>
-      <c r="J336" s="84" t="inlineStr">
+      <c r="I336" s="81" t="inlineStr"/>
+      <c r="J336" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K336" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L336" s="80" t="inlineStr"/>
-      <c r="M336" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N336" s="81" t="inlineStr">
+      <c r="K336" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L336" s="81" t="inlineStr"/>
+      <c r="M336" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N336" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -21971,960 +21967,960 @@
       </c>
     </row>
     <row r="338" ht="30" customHeight="1">
-      <c r="A338" s="79" t="inlineStr">
+      <c r="A338" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B338" s="79" t="inlineStr">
+      <c r="B338" s="80" t="inlineStr">
         <is>
           <t>Bigfoot</t>
         </is>
       </c>
-      <c r="C338" s="80" t="inlineStr">
+      <c r="C338" s="81" t="inlineStr">
         <is>
           <t>PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D338" s="81" t="inlineStr">
+      <c r="D338" s="82" t="inlineStr">
         <is>
           <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
         </is>
       </c>
-      <c r="E338" s="83" t="inlineStr">
+      <c r="E338" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F338" s="81" t="inlineStr">
+      <c r="F338" s="82" t="inlineStr">
         <is>
           <t>PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G338" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H338" s="82" t="inlineStr">
+      <c r="G338" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H338" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I338" s="80" t="inlineStr"/>
-      <c r="J338" s="84" t="inlineStr">
+      <c r="I338" s="81" t="inlineStr"/>
+      <c r="J338" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K338" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L338" s="80" t="inlineStr"/>
-      <c r="M338" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N338" s="81" t="inlineStr">
+      <c r="K338" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L338" s="81" t="inlineStr"/>
+      <c r="M338" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N338" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="339" ht="30" customHeight="1">
-      <c r="A339" s="79" t="inlineStr">
+      <c r="A339" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B339" s="79" t="inlineStr">
+      <c r="B339" s="80" t="inlineStr">
         <is>
           <t>Thunderbird</t>
         </is>
       </c>
-      <c r="C339" s="80" t="inlineStr">
+      <c r="C339" s="81" t="inlineStr">
         <is>
           <t>PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D339" s="81" t="inlineStr">
+      <c r="D339" s="82" t="inlineStr">
         <is>
           <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
         </is>
       </c>
-      <c r="E339" s="83" t="inlineStr">
+      <c r="E339" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F339" s="81" t="inlineStr">
+      <c r="F339" s="82" t="inlineStr">
         <is>
           <t>PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G339" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H339" s="82" t="inlineStr">
+      <c r="G339" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H339" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I339" s="80" t="inlineStr"/>
-      <c r="J339" s="84" t="inlineStr">
+      <c r="I339" s="81" t="inlineStr"/>
+      <c r="J339" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K339" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L339" s="80" t="inlineStr"/>
-      <c r="M339" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N339" s="81" t="inlineStr">
+      <c r="K339" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L339" s="81" t="inlineStr"/>
+      <c r="M339" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N339" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="340" ht="30" customHeight="1">
-      <c r="A340" s="79" t="inlineStr">
+      <c r="A340" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B340" s="79" t="inlineStr">
+      <c r="B340" s="80" t="inlineStr">
         <is>
           <t>Headless Horseman</t>
         </is>
       </c>
-      <c r="C340" s="80" t="inlineStr">
+      <c r="C340" s="81" t="inlineStr">
         <is>
           <t>PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D340" s="81" t="inlineStr">
+      <c r="D340" s="82" t="inlineStr">
         <is>
           <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
         </is>
       </c>
-      <c r="E340" s="83" t="inlineStr">
+      <c r="E340" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F340" s="81" t="inlineStr">
+      <c r="F340" s="82" t="inlineStr">
         <is>
           <t>PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G340" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H340" s="82" t="inlineStr">
+      <c r="G340" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H340" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I340" s="80" t="inlineStr"/>
-      <c r="J340" s="84" t="inlineStr">
+      <c r="I340" s="81" t="inlineStr"/>
+      <c r="J340" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K340" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L340" s="80" t="inlineStr"/>
-      <c r="M340" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N340" s="81" t="inlineStr">
+      <c r="K340" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L340" s="81" t="inlineStr"/>
+      <c r="M340" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N340" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="341" ht="30" customHeight="1">
-      <c r="A341" s="79" t="inlineStr">
+      <c r="A341" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B341" s="79" t="inlineStr">
+      <c r="B341" s="80" t="inlineStr">
         <is>
           <t>Chessie</t>
         </is>
       </c>
-      <c r="C341" s="80" t="inlineStr">
+      <c r="C341" s="81" t="inlineStr">
         <is>
           <t>PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D341" s="81" t="inlineStr">
+      <c r="D341" s="82" t="inlineStr">
         <is>
           <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
-      <c r="E341" s="83" t="inlineStr">
+      <c r="E341" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F341" s="81" t="inlineStr">
+      <c r="F341" s="82" t="inlineStr">
         <is>
           <t>PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G341" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H341" s="82" t="inlineStr">
+      <c r="G341" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H341" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I341" s="80" t="inlineStr"/>
-      <c r="J341" s="84" t="inlineStr">
+      <c r="I341" s="81" t="inlineStr"/>
+      <c r="J341" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K341" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L341" s="80" t="inlineStr"/>
-      <c r="M341" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N341" s="81" t="inlineStr">
+      <c r="K341" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L341" s="81" t="inlineStr"/>
+      <c r="M341" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N341" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="342" ht="30" customHeight="1">
-      <c r="A342" s="79" t="inlineStr">
+      <c r="A342" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B342" s="79" t="inlineStr">
+      <c r="B342" s="80" t="inlineStr">
         <is>
           <t>Bell Witch</t>
         </is>
       </c>
-      <c r="C342" s="80" t="inlineStr">
+      <c r="C342" s="81" t="inlineStr">
         <is>
           <t>PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D342" s="81" t="inlineStr">
+      <c r="D342" s="82" t="inlineStr">
         <is>
           <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
         </is>
       </c>
-      <c r="E342" s="83" t="inlineStr">
+      <c r="E342" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F342" s="81" t="inlineStr">
+      <c r="F342" s="82" t="inlineStr">
         <is>
           <t>PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G342" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H342" s="82" t="inlineStr">
+      <c r="G342" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H342" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I342" s="80" t="inlineStr"/>
-      <c r="J342" s="84" t="inlineStr">
+      <c r="I342" s="81" t="inlineStr"/>
+      <c r="J342" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K342" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L342" s="80" t="inlineStr"/>
-      <c r="M342" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N342" s="81" t="inlineStr">
+      <c r="K342" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L342" s="81" t="inlineStr"/>
+      <c r="M342" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N342" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="343" ht="30" customHeight="1">
-      <c r="A343" s="79" t="inlineStr">
+      <c r="A343" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B343" s="79" t="inlineStr">
+      <c r="B343" s="80" t="inlineStr">
         <is>
           <t>Old Ironsides</t>
         </is>
       </c>
-      <c r="C343" s="80" t="inlineStr">
+      <c r="C343" s="81" t="inlineStr">
         <is>
           <t>PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D343" s="81" t="inlineStr">
+      <c r="D343" s="82" t="inlineStr">
         <is>
           <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
-      <c r="E343" s="83" t="inlineStr">
+      <c r="E343" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F343" s="81" t="inlineStr">
+      <c r="F343" s="82" t="inlineStr">
         <is>
           <t>PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G343" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H343" s="82" t="inlineStr">
+      <c r="G343" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H343" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I343" s="80" t="inlineStr"/>
-      <c r="J343" s="84" t="inlineStr">
+      <c r="I343" s="81" t="inlineStr"/>
+      <c r="J343" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K343" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L343" s="80" t="inlineStr"/>
-      <c r="M343" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N343" s="81" t="inlineStr">
+      <c r="K343" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L343" s="81" t="inlineStr"/>
+      <c r="M343" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N343" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="344" ht="30" customHeight="1">
-      <c r="A344" s="79" t="inlineStr">
+      <c r="A344" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B344" s="79" t="inlineStr">
+      <c r="B344" s="80" t="inlineStr">
         <is>
           <t>Valley Forge Guardian</t>
         </is>
       </c>
-      <c r="C344" s="80" t="inlineStr">
+      <c r="C344" s="81" t="inlineStr">
         <is>
           <t>PROT_09_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D344" s="81" t="inlineStr">
+      <c r="D344" s="82" t="inlineStr">
         <is>
           <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
-      <c r="E344" s="83" t="inlineStr">
+      <c r="E344" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F344" s="81" t="inlineStr">
+      <c r="F344" s="82" t="inlineStr">
         <is>
           <t>PROT_09_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G344" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H344" s="82" t="inlineStr">
+      <c r="G344" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H344" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I344" s="80" t="inlineStr"/>
-      <c r="J344" s="84" t="inlineStr">
+      <c r="I344" s="81" t="inlineStr"/>
+      <c r="J344" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K344" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L344" s="80" t="inlineStr"/>
-      <c r="M344" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N344" s="81" t="inlineStr">
+      <c r="K344" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L344" s="81" t="inlineStr"/>
+      <c r="M344" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N344" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="345" ht="30" customHeight="1">
-      <c r="A345" s="79" t="inlineStr">
+      <c r="A345" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B345" s="79" t="inlineStr">
+      <c r="B345" s="80" t="inlineStr">
         <is>
           <t>Snallygaster</t>
         </is>
       </c>
-      <c r="C345" s="80" t="inlineStr">
+      <c r="C345" s="81" t="inlineStr">
         <is>
           <t>PROT_10_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D345" s="81" t="inlineStr">
+      <c r="D345" s="82" t="inlineStr">
         <is>
           <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E345" s="83" t="inlineStr">
+      <c r="E345" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F345" s="81" t="inlineStr">
+      <c r="F345" s="82" t="inlineStr">
         <is>
           <t>PROT_10_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G345" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H345" s="82" t="inlineStr">
+      <c r="G345" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H345" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I345" s="80" t="inlineStr"/>
-      <c r="J345" s="84" t="inlineStr">
+      <c r="I345" s="81" t="inlineStr"/>
+      <c r="J345" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K345" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L345" s="80" t="inlineStr"/>
-      <c r="M345" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N345" s="81" t="inlineStr">
+      <c r="K345" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L345" s="81" t="inlineStr"/>
+      <c r="M345" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N345" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="346" ht="30" customHeight="1">
-      <c r="A346" s="79" t="inlineStr">
+      <c r="A346" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B346" s="79" t="inlineStr">
+      <c r="B346" s="80" t="inlineStr">
         <is>
           <t>Paul Revere</t>
         </is>
       </c>
-      <c r="C346" s="80" t="inlineStr">
+      <c r="C346" s="81" t="inlineStr">
         <is>
           <t>PROT_11_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D346" s="81" t="inlineStr">
+      <c r="D346" s="82" t="inlineStr">
         <is>
           <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
         </is>
       </c>
-      <c r="E346" s="83" t="inlineStr">
+      <c r="E346" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F346" s="81" t="inlineStr">
+      <c r="F346" s="82" t="inlineStr">
         <is>
           <t>PROT_11_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G346" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H346" s="82" t="inlineStr">
+      <c r="G346" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H346" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I346" s="80" t="inlineStr"/>
-      <c r="J346" s="84" t="inlineStr">
+      <c r="I346" s="81" t="inlineStr"/>
+      <c r="J346" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K346" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L346" s="80" t="inlineStr"/>
-      <c r="M346" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N346" s="81" t="inlineStr">
+      <c r="K346" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L346" s="81" t="inlineStr"/>
+      <c r="M346" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N346" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="347" ht="30" customHeight="1">
-      <c r="A347" s="79" t="inlineStr">
+      <c r="A347" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B347" s="79" t="inlineStr">
+      <c r="B347" s="80" t="inlineStr">
         <is>
           <t>Liberty Bell</t>
         </is>
       </c>
-      <c r="C347" s="80" t="inlineStr">
+      <c r="C347" s="81" t="inlineStr">
         <is>
           <t>PROT_12_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D347" s="81" t="inlineStr">
+      <c r="D347" s="82" t="inlineStr">
         <is>
           <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
         </is>
       </c>
-      <c r="E347" s="83" t="inlineStr">
+      <c r="E347" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F347" s="81" t="inlineStr">
+      <c r="F347" s="82" t="inlineStr">
         <is>
           <t>PROT_12_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G347" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H347" s="82" t="inlineStr">
+      <c r="G347" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H347" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I347" s="80" t="inlineStr"/>
-      <c r="J347" s="84" t="inlineStr">
+      <c r="I347" s="81" t="inlineStr"/>
+      <c r="J347" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K347" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L347" s="80" t="inlineStr"/>
-      <c r="M347" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N347" s="81" t="inlineStr">
+      <c r="K347" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L347" s="81" t="inlineStr"/>
+      <c r="M347" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N347" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="348" ht="30" customHeight="1">
-      <c r="A348" s="79" t="inlineStr">
+      <c r="A348" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B348" s="79" t="inlineStr">
+      <c r="B348" s="80" t="inlineStr">
         <is>
           <t>Green Mountain Ghost</t>
         </is>
       </c>
-      <c r="C348" s="80" t="inlineStr">
+      <c r="C348" s="81" t="inlineStr">
         <is>
           <t>PROT_13_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D348" s="81" t="inlineStr">
+      <c r="D348" s="82" t="inlineStr">
         <is>
           <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
         </is>
       </c>
-      <c r="E348" s="83" t="inlineStr">
+      <c r="E348" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F348" s="81" t="inlineStr">
+      <c r="F348" s="82" t="inlineStr">
         <is>
           <t>PROT_13_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G348" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H348" s="82" t="inlineStr">
+      <c r="G348" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H348" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I348" s="80" t="inlineStr"/>
-      <c r="J348" s="84" t="inlineStr">
+      <c r="I348" s="81" t="inlineStr"/>
+      <c r="J348" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K348" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L348" s="80" t="inlineStr"/>
-      <c r="M348" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N348" s="81" t="inlineStr">
+      <c r="K348" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L348" s="81" t="inlineStr"/>
+      <c r="M348" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N348" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="349" ht="30" customHeight="1">
-      <c r="A349" s="79" t="inlineStr">
+      <c r="A349" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B349" s="79" t="inlineStr">
+      <c r="B349" s="80" t="inlineStr">
         <is>
           <t>Mount Rushmore</t>
         </is>
       </c>
-      <c r="C349" s="80" t="inlineStr">
+      <c r="C349" s="81" t="inlineStr">
         <is>
           <t>PROT_14_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D349" s="81" t="inlineStr">
+      <c r="D349" s="82" t="inlineStr">
         <is>
           <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
         </is>
       </c>
-      <c r="E349" s="83" t="inlineStr">
+      <c r="E349" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F349" s="81" t="inlineStr">
+      <c r="F349" s="82" t="inlineStr">
         <is>
           <t>PROT_14_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G349" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H349" s="82" t="inlineStr">
+      <c r="G349" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H349" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I349" s="80" t="inlineStr"/>
-      <c r="J349" s="84" t="inlineStr">
+      <c r="I349" s="81" t="inlineStr"/>
+      <c r="J349" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K349" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L349" s="80" t="inlineStr"/>
-      <c r="M349" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N349" s="81" t="inlineStr">
+      <c r="K349" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L349" s="81" t="inlineStr"/>
+      <c r="M349" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N349" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="350" ht="30" customHeight="1">
-      <c r="A350" s="79" t="inlineStr">
+      <c r="A350" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B350" s="79" t="inlineStr">
+      <c r="B350" s="80" t="inlineStr">
         <is>
           <t>Skunk Ape</t>
         </is>
       </c>
-      <c r="C350" s="80" t="inlineStr">
+      <c r="C350" s="81" t="inlineStr">
         <is>
           <t>PROT_15_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D350" s="81" t="inlineStr">
+      <c r="D350" s="82" t="inlineStr">
         <is>
           <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
-      <c r="E350" s="83" t="inlineStr">
+      <c r="E350" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F350" s="81" t="inlineStr">
+      <c r="F350" s="82" t="inlineStr">
         <is>
           <t>PROT_15_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G350" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H350" s="82" t="inlineStr">
+      <c r="G350" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H350" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I350" s="80" t="inlineStr"/>
-      <c r="J350" s="84" t="inlineStr">
+      <c r="I350" s="81" t="inlineStr"/>
+      <c r="J350" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K350" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L350" s="80" t="inlineStr"/>
-      <c r="M350" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N350" s="81" t="inlineStr">
+      <c r="K350" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L350" s="81" t="inlineStr"/>
+      <c r="M350" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N350" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="351" ht="30" customHeight="1">
-      <c r="A351" s="79" t="inlineStr">
+      <c r="A351" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B351" s="79" t="inlineStr">
+      <c r="B351" s="80" t="inlineStr">
         <is>
           <t>Minuteman</t>
         </is>
       </c>
-      <c r="C351" s="80" t="inlineStr">
+      <c r="C351" s="81" t="inlineStr">
         <is>
           <t>PROT_16_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D351" s="81" t="inlineStr">
+      <c r="D351" s="82" t="inlineStr">
         <is>
           <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E351" s="83" t="inlineStr">
+      <c r="E351" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F351" s="81" t="inlineStr">
+      <c r="F351" s="82" t="inlineStr">
         <is>
           <t>PROT_16_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G351" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H351" s="82" t="inlineStr">
+      <c r="G351" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H351" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I351" s="80" t="inlineStr"/>
-      <c r="J351" s="84" t="inlineStr">
+      <c r="I351" s="81" t="inlineStr"/>
+      <c r="J351" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K351" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L351" s="80" t="inlineStr"/>
-      <c r="M351" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N351" s="81" t="inlineStr">
+      <c r="K351" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L351" s="81" t="inlineStr"/>
+      <c r="M351" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N351" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="352" ht="30" customHeight="1">
-      <c r="A352" s="79" t="inlineStr">
+      <c r="A352" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B352" s="79" t="inlineStr">
+      <c r="B352" s="80" t="inlineStr">
         <is>
           <t>Lincoln's Ghost</t>
         </is>
       </c>
-      <c r="C352" s="80" t="inlineStr">
+      <c r="C352" s="81" t="inlineStr">
         <is>
           <t>PROT_17_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D352" s="81" t="inlineStr">
+      <c r="D352" s="82" t="inlineStr">
         <is>
           <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
         </is>
       </c>
-      <c r="E352" s="83" t="inlineStr">
+      <c r="E352" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F352" s="81" t="inlineStr">
+      <c r="F352" s="82" t="inlineStr">
         <is>
           <t>PROT_17_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G352" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H352" s="82" t="inlineStr">
+      <c r="G352" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H352" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I352" s="80" t="inlineStr"/>
-      <c r="J352" s="84" t="inlineStr">
+      <c r="I352" s="81" t="inlineStr"/>
+      <c r="J352" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K352" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L352" s="80" t="inlineStr"/>
-      <c r="M352" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N352" s="81" t="inlineStr">
+      <c r="K352" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L352" s="81" t="inlineStr"/>
+      <c r="M352" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N352" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -22947,256 +22943,256 @@
       <c r="N353" s="9" t="n"/>
     </row>
     <row r="354" ht="30" customHeight="1">
-      <c r="A354" s="79" t="inlineStr">
+      <c r="A354" s="80" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B354" s="79" t="inlineStr">
+      <c r="B354" s="80" t="inlineStr">
         <is>
           <t>Month 1</t>
         </is>
       </c>
-      <c r="C354" s="80" t="inlineStr">
+      <c r="C354" s="81" t="inlineStr">
         <is>
           <t>WH_SECRET_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D354" s="81" t="inlineStr">
+      <c r="D354" s="82" t="inlineStr">
         <is>
           <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E354" s="83" t="inlineStr">
+      <c r="E354" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F354" s="81" t="inlineStr">
+      <c r="F354" s="82" t="inlineStr">
         <is>
           <t>WH_SECRET_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G354" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H354" s="82" t="inlineStr">
+      <c r="G354" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H354" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I354" s="80" t="inlineStr"/>
-      <c r="J354" s="84" t="inlineStr">
+      <c r="I354" s="81" t="inlineStr"/>
+      <c r="J354" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K354" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L354" s="80" t="inlineStr"/>
-      <c r="M354" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N354" s="81" t="inlineStr">
+      <c r="K354" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L354" s="81" t="inlineStr"/>
+      <c r="M354" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N354" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="355" ht="30" customHeight="1">
-      <c r="A355" s="79" t="inlineStr">
+      <c r="A355" s="80" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B355" s="79" t="inlineStr">
+      <c r="B355" s="80" t="inlineStr">
         <is>
           <t>Month 7</t>
         </is>
       </c>
-      <c r="C355" s="80" t="inlineStr">
+      <c r="C355" s="81" t="inlineStr">
         <is>
           <t>WH_SECRET_07_INTIMATE</t>
         </is>
       </c>
-      <c r="D355" s="81" t="inlineStr">
+      <c r="D355" s="82" t="inlineStr">
         <is>
           <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
         </is>
       </c>
-      <c r="E355" s="83" t="inlineStr">
+      <c r="E355" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F355" s="81" t="inlineStr">
+      <c r="F355" s="82" t="inlineStr">
         <is>
           <t>WH_SECRET_07 (intimate choice)</t>
         </is>
       </c>
-      <c r="G355" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H355" s="82" t="inlineStr">
+      <c r="G355" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H355" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I355" s="80" t="inlineStr"/>
-      <c r="J355" s="84" t="inlineStr">
+      <c r="I355" s="81" t="inlineStr"/>
+      <c r="J355" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K355" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L355" s="80" t="inlineStr"/>
-      <c r="M355" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N355" s="81" t="inlineStr">
+      <c r="K355" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L355" s="81" t="inlineStr"/>
+      <c r="M355" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N355" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="356" ht="30" customHeight="1">
-      <c r="A356" s="79" t="inlineStr">
+      <c r="A356" s="80" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B356" s="79" t="inlineStr">
+      <c r="B356" s="80" t="inlineStr">
         <is>
           <t>Month 10</t>
         </is>
       </c>
-      <c r="C356" s="80" t="inlineStr">
+      <c r="C356" s="81" t="inlineStr">
         <is>
           <t>WH_SECRET_10_INTIMATE</t>
         </is>
       </c>
-      <c r="D356" s="81" t="inlineStr">
+      <c r="D356" s="82" t="inlineStr">
         <is>
           <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
         </is>
       </c>
-      <c r="E356" s="83" t="inlineStr">
+      <c r="E356" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F356" s="81" t="inlineStr">
+      <c r="F356" s="82" t="inlineStr">
         <is>
           <t>WH_SECRET_10 (intimate choice)</t>
         </is>
       </c>
-      <c r="G356" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H356" s="82" t="inlineStr">
+      <c r="G356" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H356" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I356" s="80" t="inlineStr"/>
-      <c r="J356" s="84" t="inlineStr">
+      <c r="I356" s="81" t="inlineStr"/>
+      <c r="J356" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K356" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L356" s="80" t="inlineStr"/>
-      <c r="M356" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N356" s="81" t="inlineStr">
+      <c r="K356" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L356" s="81" t="inlineStr"/>
+      <c r="M356" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N356" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="357" ht="30" customHeight="1">
-      <c r="A357" s="79" t="inlineStr">
+      <c r="A357" s="80" t="inlineStr">
         <is>
           <t>White House</t>
         </is>
       </c>
-      <c r="B357" s="79" t="inlineStr">
+      <c r="B357" s="80" t="inlineStr">
         <is>
           <t>Month 12</t>
         </is>
       </c>
-      <c r="C357" s="80" t="inlineStr">
+      <c r="C357" s="81" t="inlineStr">
         <is>
           <t>WH_SECRET_12_INTIMATE</t>
         </is>
       </c>
-      <c r="D357" s="81" t="inlineStr">
+      <c r="D357" s="82" t="inlineStr">
         <is>
           <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E357" s="83" t="inlineStr">
+      <c r="E357" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F357" s="81" t="inlineStr">
+      <c r="F357" s="82" t="inlineStr">
         <is>
           <t>WH_SECRET_12 (intimate choice)</t>
         </is>
       </c>
-      <c r="G357" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H357" s="82" t="inlineStr">
+      <c r="G357" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H357" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I357" s="80" t="inlineStr"/>
-      <c r="J357" s="84" t="inlineStr">
+      <c r="I357" s="81" t="inlineStr"/>
+      <c r="J357" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K357" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L357" s="80" t="inlineStr"/>
-      <c r="M357" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N357" s="81" t="inlineStr">
+      <c r="K357" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L357" s="81" t="inlineStr"/>
+      <c r="M357" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N357" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of WH_SECRET_12. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -25985,448 +25981,448 @@
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="79" t="inlineStr">
+      <c r="A43" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C43" s="80" t="inlineStr">
+      <c r="C43" s="81" t="inlineStr">
         <is>
           <t>CAN_CLEARWATER_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D43" s="81" t="inlineStr">
+      <c r="D43" s="82" t="inlineStr">
         <is>
           <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
         </is>
       </c>
-      <c r="E43" s="83" t="inlineStr">
+      <c r="E43" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F43" s="81" t="inlineStr">
+      <c r="F43" s="82" t="inlineStr">
         <is>
           <t>CAN_CLEARWATER_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G43" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="82" t="inlineStr">
+      <c r="G43" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I43" s="80" t="inlineStr"/>
-      <c r="J43" s="84" t="inlineStr">
+      <c r="I43" s="81" t="inlineStr"/>
+      <c r="J43" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K43" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L43" s="80" t="inlineStr"/>
-      <c r="M43" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N43" s="81" t="inlineStr">
+      <c r="K43" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L43" s="81" t="inlineStr"/>
+      <c r="M43" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N43" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="79" t="inlineStr">
+      <c r="A44" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B44" s="79" t="inlineStr">
+      <c r="B44" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C44" s="80" t="inlineStr">
+      <c r="C44" s="81" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D44" s="81" t="inlineStr">
+      <c r="D44" s="82" t="inlineStr">
         <is>
           <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
         </is>
       </c>
-      <c r="E44" s="83" t="inlineStr">
+      <c r="E44" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F44" s="81" t="inlineStr">
+      <c r="F44" s="82" t="inlineStr">
         <is>
           <t>CAN_JOINT_OPS_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G44" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="82" t="inlineStr">
+      <c r="G44" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I44" s="80" t="inlineStr"/>
-      <c r="J44" s="84" t="inlineStr">
+      <c r="I44" s="81" t="inlineStr"/>
+      <c r="J44" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K44" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L44" s="80" t="inlineStr"/>
-      <c r="M44" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N44" s="81" t="inlineStr">
+      <c r="K44" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L44" s="81" t="inlineStr"/>
+      <c r="M44" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N44" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="79" t="inlineStr">
+      <c r="A45" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B45" s="79" t="inlineStr">
+      <c r="B45" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C45" s="80" t="inlineStr">
+      <c r="C45" s="81" t="inlineStr">
         <is>
           <t>CAN_SUMMIT_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D45" s="81" t="inlineStr">
+      <c r="D45" s="82" t="inlineStr">
         <is>
           <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
         </is>
       </c>
-      <c r="E45" s="83" t="inlineStr">
+      <c r="E45" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F45" s="81" t="inlineStr">
+      <c r="F45" s="82" t="inlineStr">
         <is>
           <t>CAN_SUMMIT_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G45" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="82" t="inlineStr">
+      <c r="G45" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I45" s="80" t="inlineStr"/>
-      <c r="J45" s="84" t="inlineStr">
+      <c r="I45" s="81" t="inlineStr"/>
+      <c r="J45" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K45" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L45" s="80" t="inlineStr"/>
-      <c r="M45" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N45" s="81" t="inlineStr">
+      <c r="K45" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L45" s="81" t="inlineStr"/>
+      <c r="M45" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N45" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="79" t="inlineStr">
+      <c r="A46" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B46" s="79" t="inlineStr">
+      <c r="B46" s="80" t="inlineStr">
         <is>
           <t>Canadian Alliance</t>
         </is>
       </c>
-      <c r="C46" s="80" t="inlineStr">
+      <c r="C46" s="81" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK_INTIMATE</t>
         </is>
       </c>
-      <c r="D46" s="81" t="inlineStr">
+      <c r="D46" s="82" t="inlineStr">
         <is>
           <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E46" s="83" t="inlineStr">
+      <c r="E46" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F46" s="81" t="inlineStr">
+      <c r="F46" s="82" t="inlineStr">
         <is>
           <t>CAN_ELECTION_LUCK (intimate choice)</t>
         </is>
       </c>
-      <c r="G46" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="82" t="inlineStr">
+      <c r="G46" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I46" s="80" t="inlineStr"/>
-      <c r="J46" s="84" t="inlineStr">
+      <c r="I46" s="81" t="inlineStr"/>
+      <c r="J46" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K46" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L46" s="80" t="inlineStr"/>
-      <c r="M46" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N46" s="81" t="inlineStr">
+      <c r="K46" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L46" s="81" t="inlineStr"/>
+      <c r="M46" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N46" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="79" t="inlineStr">
+      <c r="A47" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B47" s="79" t="inlineStr">
+      <c r="B47" s="80" t="inlineStr">
         <is>
           <t>Peace</t>
         </is>
       </c>
-      <c r="C47" s="80" t="inlineStr">
+      <c r="C47" s="81" t="inlineStr">
         <is>
           <t>CAN_PEACE_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D47" s="81" t="inlineStr">
+      <c r="D47" s="82" t="inlineStr">
         <is>
           <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
         </is>
       </c>
-      <c r="E47" s="83" t="inlineStr">
+      <c r="E47" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F47" s="81" t="inlineStr">
+      <c r="F47" s="82" t="inlineStr">
         <is>
           <t>CAN_PEACE_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G47" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="82" t="inlineStr">
+      <c r="G47" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I47" s="80" t="inlineStr"/>
-      <c r="J47" s="84" t="inlineStr">
+      <c r="I47" s="81" t="inlineStr"/>
+      <c r="J47" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K47" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L47" s="80" t="inlineStr"/>
-      <c r="M47" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N47" s="81" t="inlineStr">
+      <c r="K47" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L47" s="81" t="inlineStr"/>
+      <c r="M47" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N47" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="79" t="inlineStr">
+      <c r="A48" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B48" s="79" t="inlineStr">
+      <c r="B48" s="80" t="inlineStr">
         <is>
           <t>Peace</t>
         </is>
       </c>
-      <c r="C48" s="80" t="inlineStr">
+      <c r="C48" s="81" t="inlineStr">
         <is>
           <t>PEACE_ALLIED_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D48" s="81" t="inlineStr">
+      <c r="D48" s="82" t="inlineStr">
         <is>
           <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
         </is>
       </c>
-      <c r="E48" s="83" t="inlineStr">
+      <c r="E48" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F48" s="81" t="inlineStr">
+      <c r="F48" s="82" t="inlineStr">
         <is>
           <t>PEACE_ALLIED_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G48" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="82" t="inlineStr">
+      <c r="G48" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I48" s="80" t="inlineStr"/>
-      <c r="J48" s="84" t="inlineStr">
+      <c r="I48" s="81" t="inlineStr"/>
+      <c r="J48" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K48" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L48" s="80" t="inlineStr"/>
-      <c r="M48" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N48" s="81" t="inlineStr">
+      <c r="K48" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L48" s="81" t="inlineStr"/>
+      <c r="M48" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="79" t="inlineStr">
+      <c r="A49" s="80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B49" s="79" t="inlineStr">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t>Peace</t>
         </is>
       </c>
-      <c r="C49" s="80" t="inlineStr">
+      <c r="C49" s="81" t="inlineStr">
         <is>
           <t>PEACE_USA_01_INTIMATE</t>
         </is>
       </c>
-      <c r="D49" s="81" t="inlineStr">
+      <c r="D49" s="82" t="inlineStr">
         <is>
           <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
         </is>
       </c>
-      <c r="E49" s="83" t="inlineStr">
+      <c r="E49" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F49" s="81" t="inlineStr">
+      <c r="F49" s="82" t="inlineStr">
         <is>
           <t>PEACE_USA_01 (intimate choice)</t>
         </is>
       </c>
-      <c r="G49" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="82" t="inlineStr">
+      <c r="G49" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I49" s="80" t="inlineStr"/>
-      <c r="J49" s="84" t="inlineStr">
+      <c r="I49" s="81" t="inlineStr"/>
+      <c r="J49" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K49" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L49" s="80" t="inlineStr"/>
-      <c r="M49" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N49" s="81" t="inlineStr">
+      <c r="K49" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L49" s="81" t="inlineStr"/>
+      <c r="M49" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N49" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
@@ -26449,512 +26445,512 @@
       <c r="N50" s="9" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="79" t="inlineStr">
+      <c r="A51" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B51" s="79" t="inlineStr">
+      <c r="B51" s="80" t="inlineStr">
         <is>
           <t>Le Wendigo</t>
         </is>
       </c>
-      <c r="C51" s="80" t="inlineStr">
+      <c r="C51" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D51" s="81" t="inlineStr">
+      <c r="D51" s="82" t="inlineStr">
         <is>
           <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
         </is>
       </c>
-      <c r="E51" s="83" t="inlineStr">
+      <c r="E51" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F51" s="81" t="inlineStr">
+      <c r="F51" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G51" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="82" t="inlineStr">
+      <c r="G51" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I51" s="80" t="inlineStr"/>
-      <c r="J51" s="84" t="inlineStr">
+      <c r="I51" s="81" t="inlineStr"/>
+      <c r="J51" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K51" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L51" s="80" t="inlineStr"/>
-      <c r="M51" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N51" s="81" t="inlineStr">
+      <c r="K51" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L51" s="81" t="inlineStr"/>
+      <c r="M51" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N51" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="79" t="inlineStr">
+      <c r="A52" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B52" s="79" t="inlineStr">
+      <c r="B52" s="80" t="inlineStr">
         <is>
           <t>Le Loup-Garou</t>
         </is>
       </c>
-      <c r="C52" s="80" t="inlineStr">
+      <c r="C52" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D52" s="81" t="inlineStr">
+      <c r="D52" s="82" t="inlineStr">
         <is>
           <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
-      <c r="E52" s="83" t="inlineStr">
+      <c r="E52" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F52" s="81" t="inlineStr">
+      <c r="F52" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G52" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="82" t="inlineStr">
+      <c r="G52" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I52" s="80" t="inlineStr"/>
-      <c r="J52" s="84" t="inlineStr">
+      <c r="I52" s="81" t="inlineStr"/>
+      <c r="J52" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K52" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L52" s="80" t="inlineStr"/>
-      <c r="M52" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N52" s="81" t="inlineStr">
+      <c r="K52" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L52" s="81" t="inlineStr"/>
+      <c r="M52" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N52" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="79" t="inlineStr">
+      <c r="A53" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B53" s="79" t="inlineStr">
+      <c r="B53" s="80" t="inlineStr">
         <is>
           <t>Les Feux Follets</t>
         </is>
       </c>
-      <c r="C53" s="80" t="inlineStr">
+      <c r="C53" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_03_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D53" s="81" t="inlineStr">
+      <c r="D53" s="82" t="inlineStr">
         <is>
           <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
         </is>
       </c>
-      <c r="E53" s="83" t="inlineStr">
+      <c r="E53" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F53" s="81" t="inlineStr">
+      <c r="F53" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_03_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G53" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="82" t="inlineStr">
+      <c r="G53" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I53" s="80" t="inlineStr"/>
-      <c r="J53" s="84" t="inlineStr">
+      <c r="I53" s="81" t="inlineStr"/>
+      <c r="J53" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K53" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L53" s="80" t="inlineStr"/>
-      <c r="M53" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N53" s="81" t="inlineStr">
+      <c r="K53" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L53" s="81" t="inlineStr"/>
+      <c r="M53" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N53" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="79" t="inlineStr">
+      <c r="A54" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B54" s="79" t="inlineStr">
+      <c r="B54" s="80" t="inlineStr">
         <is>
           <t>Mishepeshu</t>
         </is>
       </c>
-      <c r="C54" s="80" t="inlineStr">
+      <c r="C54" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D54" s="81" t="inlineStr">
+      <c r="D54" s="82" t="inlineStr">
         <is>
           <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
-      <c r="E54" s="83" t="inlineStr">
+      <c r="E54" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F54" s="81" t="inlineStr">
+      <c r="F54" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G54" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="82" t="inlineStr">
+      <c r="G54" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I54" s="80" t="inlineStr"/>
-      <c r="J54" s="84" t="inlineStr">
+      <c r="I54" s="81" t="inlineStr"/>
+      <c r="J54" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K54" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L54" s="80" t="inlineStr"/>
-      <c r="M54" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N54" s="81" t="inlineStr">
+      <c r="K54" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L54" s="81" t="inlineStr"/>
+      <c r="M54" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N54" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="79" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B55" s="79" t="inlineStr">
+      <c r="B55" s="80" t="inlineStr">
         <is>
           <t>La Corriveau</t>
         </is>
       </c>
-      <c r="C55" s="80" t="inlineStr">
+      <c r="C55" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D55" s="81" t="inlineStr">
+      <c r="D55" s="82" t="inlineStr">
         <is>
           <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
-      <c r="E55" s="83" t="inlineStr">
+      <c r="E55" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F55" s="81" t="inlineStr">
+      <c r="F55" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G55" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="82" t="inlineStr">
+      <c r="G55" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I55" s="80" t="inlineStr"/>
-      <c r="J55" s="84" t="inlineStr">
+      <c r="I55" s="81" t="inlineStr"/>
+      <c r="J55" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K55" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L55" s="80" t="inlineStr"/>
-      <c r="M55" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N55" s="81" t="inlineStr">
+      <c r="K55" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L55" s="81" t="inlineStr"/>
+      <c r="M55" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="79" t="inlineStr">
+      <c r="A56" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B56" s="79" t="inlineStr">
+      <c r="B56" s="80" t="inlineStr">
         <is>
           <t>Le Carcajou</t>
         </is>
       </c>
-      <c r="C56" s="80" t="inlineStr">
+      <c r="C56" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D56" s="81" t="inlineStr">
+      <c r="D56" s="82" t="inlineStr">
         <is>
           <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
-      <c r="E56" s="83" t="inlineStr">
+      <c r="E56" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F56" s="81" t="inlineStr">
+      <c r="F56" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G56" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="82" t="inlineStr">
+      <c r="G56" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I56" s="80" t="inlineStr"/>
-      <c r="J56" s="84" t="inlineStr">
+      <c r="I56" s="81" t="inlineStr"/>
+      <c r="J56" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K56" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L56" s="80" t="inlineStr"/>
-      <c r="M56" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N56" s="81" t="inlineStr">
+      <c r="K56" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L56" s="81" t="inlineStr"/>
+      <c r="M56" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N56" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="79" t="inlineStr">
+      <c r="A57" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B57" s="79" t="inlineStr">
+      <c r="B57" s="80" t="inlineStr">
         <is>
           <t>La Chasse-Galerie</t>
         </is>
       </c>
-      <c r="C57" s="80" t="inlineStr">
+      <c r="C57" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D57" s="81" t="inlineStr">
+      <c r="D57" s="82" t="inlineStr">
         <is>
           <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
-      <c r="E57" s="83" t="inlineStr">
+      <c r="E57" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F57" s="81" t="inlineStr">
+      <c r="F57" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G57" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="82" t="inlineStr">
+      <c r="G57" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I57" s="80" t="inlineStr"/>
-      <c r="J57" s="84" t="inlineStr">
+      <c r="I57" s="81" t="inlineStr"/>
+      <c r="J57" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K57" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L57" s="80" t="inlineStr"/>
-      <c r="M57" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N57" s="81" t="inlineStr">
+      <c r="K57" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L57" s="81" t="inlineStr"/>
+      <c r="M57" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N57" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="79" t="inlineStr">
+      <c r="A58" s="80" t="inlineStr">
         <is>
           <t>CA Protector</t>
         </is>
       </c>
-      <c r="B58" s="79" t="inlineStr">
+      <c r="B58" s="80" t="inlineStr">
         <is>
           <t>Le Gougou</t>
         </is>
       </c>
-      <c r="C58" s="80" t="inlineStr">
+      <c r="C58" s="81" t="inlineStr">
         <is>
           <t>CA_PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
-      <c r="D58" s="81" t="inlineStr">
+      <c r="D58" s="82" t="inlineStr">
         <is>
           <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
         </is>
       </c>
-      <c r="E58" s="83" t="inlineStr">
+      <c r="E58" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F58" s="81" t="inlineStr">
+      <c r="F58" s="82" t="inlineStr">
         <is>
           <t>CA_PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
-      <c r="G58" s="81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="82" t="inlineStr">
+      <c r="G58" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I58" s="80" t="inlineStr"/>
-      <c r="J58" s="84" t="inlineStr">
+      <c r="I58" s="81" t="inlineStr"/>
+      <c r="J58" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K58" s="83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L58" s="80" t="inlineStr"/>
-      <c r="M58" s="83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N58" s="81" t="inlineStr">
+      <c r="K58" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L58" s="81" t="inlineStr"/>
+      <c r="M58" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N58" s="82" t="inlineStr">
         <is>
           <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_17</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL PLANTATION DESERTER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SWAMP WITCH)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield magic×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SWAMP WITCH)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARIBBEAN PRIVATEER)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield magic×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Hawaiian Refugee</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_20</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARIBBEAN PRIVATEER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL HAWAIIAN REFUGEE)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield food×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_20</t>
+          <t>GOV_LOYAL_ARC_21</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL HAWAIIAN REFUGEE)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BORDER MERCENARY)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield weapons×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_21</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BORDER MERCENARY)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>tile_yield weapons×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13970,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="B205" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C205" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="N205" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14106,17 +14106,17 @@
       </c>
       <c r="B206" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C206" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="N206" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14174,17 +14174,17 @@
       </c>
       <c r="B207" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C207" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_17</t>
         </is>
       </c>
       <c r="D207" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -14202,15 +14202,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H207" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H207" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I207" s="68" t="inlineStr"/>
-      <c r="J207" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J207" s="71" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K207" s="70" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="N207" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="B360" s="86" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -576,10 +576,10 @@
     <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -12576,12 +12576,12 @@
         </is>
       </c>
       <c r="I183" s="68" t="inlineStr"/>
-      <c r="J183" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K183" s="70" t="inlineStr">
+      <c r="J183" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K183" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12591,14 +12591,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M183" s="70" t="inlineStr">
+      <c r="M183" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N183" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -12644,12 +12644,12 @@
         </is>
       </c>
       <c r="I184" s="68" t="inlineStr"/>
-      <c r="J184" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K184" s="70" t="inlineStr">
+      <c r="J184" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K184" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12659,14 +12659,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M184" s="70" t="inlineStr">
+      <c r="M184" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N184" s="69" t="inlineStr">
         <is>
-          <t>tile_yield metal×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield metal×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -12712,12 +12712,12 @@
         </is>
       </c>
       <c r="I185" s="68" t="inlineStr"/>
-      <c r="J185" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K185" s="70" t="inlineStr">
+      <c r="J185" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K185" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12727,14 +12727,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M185" s="70" t="inlineStr">
+      <c r="M185" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N185" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -12780,12 +12780,12 @@
         </is>
       </c>
       <c r="I186" s="68" t="inlineStr"/>
-      <c r="J186" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K186" s="70" t="inlineStr">
+      <c r="J186" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K186" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12795,14 +12795,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M186" s="70" t="inlineStr">
+      <c r="M186" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N186" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield manpower×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -12848,12 +12848,12 @@
         </is>
       </c>
       <c r="I187" s="68" t="inlineStr"/>
-      <c r="J187" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K187" s="70" t="inlineStr">
+      <c r="J187" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K187" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12863,14 +12863,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M187" s="70" t="inlineStr">
+      <c r="M187" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N187" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield food×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -12916,12 +12916,12 @@
         </is>
       </c>
       <c r="I188" s="68" t="inlineStr"/>
-      <c r="J188" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K188" s="70" t="inlineStr">
+      <c r="J188" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K188" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12931,14 +12931,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M188" s="70" t="inlineStr">
+      <c r="M188" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N188" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -12984,12 +12984,12 @@
         </is>
       </c>
       <c r="I189" s="68" t="inlineStr"/>
-      <c r="J189" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K189" s="70" t="inlineStr">
+      <c r="J189" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K189" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -12999,14 +12999,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M189" s="70" t="inlineStr">
+      <c r="M189" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N189" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13052,12 +13052,12 @@
         </is>
       </c>
       <c r="I190" s="68" t="inlineStr"/>
-      <c r="J190" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K190" s="70" t="inlineStr">
+      <c r="J190" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K190" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13067,14 +13067,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M190" s="70" t="inlineStr">
+      <c r="M190" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N190" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13120,12 +13120,12 @@
         </is>
       </c>
       <c r="I191" s="68" t="inlineStr"/>
-      <c r="J191" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K191" s="70" t="inlineStr">
+      <c r="J191" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K191" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13135,14 +13135,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M191" s="70" t="inlineStr">
+      <c r="M191" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N191" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13188,12 +13188,12 @@
         </is>
       </c>
       <c r="I192" s="68" t="inlineStr"/>
-      <c r="J192" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K192" s="70" t="inlineStr">
+      <c r="J192" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K192" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13203,14 +13203,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M192" s="70" t="inlineStr">
+      <c r="M192" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N192" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield manpower×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13256,12 +13256,12 @@
         </is>
       </c>
       <c r="I193" s="68" t="inlineStr"/>
-      <c r="J193" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K193" s="70" t="inlineStr">
+      <c r="J193" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K193" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13271,14 +13271,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M193" s="70" t="inlineStr">
+      <c r="M193" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N193" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13324,12 +13324,12 @@
         </is>
       </c>
       <c r="I194" s="68" t="inlineStr"/>
-      <c r="J194" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K194" s="70" t="inlineStr">
+      <c r="J194" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K194" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13339,14 +13339,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M194" s="70" t="inlineStr">
+      <c r="M194" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N194" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13392,12 +13392,12 @@
         </is>
       </c>
       <c r="I195" s="68" t="inlineStr"/>
-      <c r="J195" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K195" s="70" t="inlineStr">
+      <c r="J195" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K195" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13407,14 +13407,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M195" s="70" t="inlineStr">
+      <c r="M195" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N195" s="69" t="inlineStr">
         <is>
-          <t>tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield boats×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13460,12 +13460,12 @@
         </is>
       </c>
       <c r="I196" s="68" t="inlineStr"/>
-      <c r="J196" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K196" s="70" t="inlineStr">
+      <c r="J196" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K196" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13475,14 +13475,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M196" s="70" t="inlineStr">
+      <c r="M196" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N196" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13528,12 +13528,12 @@
         </is>
       </c>
       <c r="I197" s="68" t="inlineStr"/>
-      <c r="J197" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K197" s="70" t="inlineStr">
+      <c r="J197" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K197" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13543,14 +13543,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M197" s="70" t="inlineStr">
+      <c r="M197" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_16</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL RUST BELT STEELWORKER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SWAMP WITCH)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13596,12 +13596,12 @@
         </is>
       </c>
       <c r="I198" s="68" t="inlineStr"/>
-      <c r="J198" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K198" s="70" t="inlineStr">
+      <c r="J198" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K198" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13611,14 +13611,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M198" s="70" t="inlineStr">
+      <c r="M198" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>tile_yield metal×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield magic×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SWAMP WITCH)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARIBBEAN PRIVATEER)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13664,12 +13664,12 @@
         </is>
       </c>
       <c r="I199" s="68" t="inlineStr"/>
-      <c r="J199" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K199" s="70" t="inlineStr">
+      <c r="J199" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K199" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13679,14 +13679,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M199" s="70" t="inlineStr">
+      <c r="M199" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield magic×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Hawaiian Refugee</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_20</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARIBBEAN PRIVATEER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL HAWAIIAN REFUGEE)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13732,12 +13732,12 @@
         </is>
       </c>
       <c r="I200" s="68" t="inlineStr"/>
-      <c r="J200" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K200" s="70" t="inlineStr">
+      <c r="J200" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K200" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13747,14 +13747,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M200" s="70" t="inlineStr">
+      <c r="M200" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield food×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_20</t>
+          <t>GOV_LOYAL_ARC_21</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL HAWAIIAN REFUGEE)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BORDER MERCENARY)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13800,12 +13800,12 @@
         </is>
       </c>
       <c r="I201" s="68" t="inlineStr"/>
-      <c r="J201" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K201" s="70" t="inlineStr">
+      <c r="J201" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K201" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13815,14 +13815,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M201" s="70" t="inlineStr">
+      <c r="M201" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield weapons×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_21</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BORDER MERCENARY)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13868,12 +13868,12 @@
         </is>
       </c>
       <c r="I202" s="68" t="inlineStr"/>
-      <c r="J202" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K202" s="70" t="inlineStr">
+      <c r="J202" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K202" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13883,14 +13883,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M202" s="70" t="inlineStr">
+      <c r="M202" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>tile_yield weapons×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13936,12 +13936,12 @@
         </is>
       </c>
       <c r="I203" s="68" t="inlineStr"/>
-      <c r="J203" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K203" s="70" t="inlineStr">
+      <c r="J203" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K203" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13951,14 +13951,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M203" s="70" t="inlineStr">
+      <c r="M203" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13970,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -14004,12 +14004,12 @@
         </is>
       </c>
       <c r="I204" s="68" t="inlineStr"/>
-      <c r="J204" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K204" s="70" t="inlineStr">
+      <c r="J204" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K204" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -14019,14 +14019,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M204" s="70" t="inlineStr">
+      <c r="M204" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="B205" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C205" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -14072,12 +14072,12 @@
         </is>
       </c>
       <c r="I205" s="68" t="inlineStr"/>
-      <c r="J205" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K205" s="70" t="inlineStr">
+      <c r="J205" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K205" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -14087,14 +14087,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M205" s="70" t="inlineStr">
+      <c r="M205" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N205" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -14106,17 +14106,17 @@
       </c>
       <c r="B206" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C206" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_16</t>
         </is>
       </c>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -14134,18 +14134,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H206" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H206" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I206" s="68" t="inlineStr"/>
-      <c r="J206" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K206" s="70" t="inlineStr">
+      <c r="J206" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K206" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -14155,14 +14155,14 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M206" s="70" t="inlineStr">
+      <c r="M206" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N206" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14208,12 +14208,12 @@
         </is>
       </c>
       <c r="I207" s="68" t="inlineStr"/>
-      <c r="J207" s="71" t="inlineStr">
+      <c r="J207" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K207" s="70" t="inlineStr">
+      <c r="K207" s="71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -14223,7 +14223,7 @@
           <t>standard</t>
         </is>
       </c>
-      <c r="M207" s="70" t="inlineStr">
+      <c r="M207" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14292,7 +14292,7 @@
         </is>
       </c>
       <c r="I209" s="32" t="inlineStr"/>
-      <c r="J209" s="71" t="inlineStr">
+      <c r="J209" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14356,7 +14356,7 @@
         </is>
       </c>
       <c r="I210" s="32" t="inlineStr"/>
-      <c r="J210" s="71" t="inlineStr">
+      <c r="J210" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="I211" s="32" t="inlineStr"/>
-      <c r="J211" s="71" t="inlineStr">
+      <c r="J211" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="I212" s="32" t="inlineStr"/>
-      <c r="J212" s="71" t="inlineStr">
+      <c r="J212" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14548,7 +14548,7 @@
         </is>
       </c>
       <c r="I213" s="32" t="inlineStr"/>
-      <c r="J213" s="71" t="inlineStr">
+      <c r="J213" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="I214" s="32" t="inlineStr"/>
-      <c r="J214" s="71" t="inlineStr">
+      <c r="J214" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="I215" s="32" t="inlineStr"/>
-      <c r="J215" s="71" t="inlineStr">
+      <c r="J215" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="I216" s="32" t="inlineStr"/>
-      <c r="J216" s="71" t="inlineStr">
+      <c r="J216" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14804,7 +14804,7 @@
         </is>
       </c>
       <c r="I217" s="32" t="inlineStr"/>
-      <c r="J217" s="71" t="inlineStr">
+      <c r="J217" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I218" s="32" t="inlineStr"/>
-      <c r="J218" s="71" t="inlineStr">
+      <c r="J218" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14932,7 +14932,7 @@
         </is>
       </c>
       <c r="I219" s="32" t="inlineStr"/>
-      <c r="J219" s="71" t="inlineStr">
+      <c r="J219" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="I220" s="32" t="inlineStr"/>
-      <c r="J220" s="71" t="inlineStr">
+      <c r="J220" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="I221" s="32" t="inlineStr"/>
-      <c r="J221" s="71" t="inlineStr">
+      <c r="J221" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15124,7 +15124,7 @@
         </is>
       </c>
       <c r="I222" s="32" t="inlineStr"/>
-      <c r="J222" s="71" t="inlineStr">
+      <c r="J222" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="I223" s="32" t="inlineStr"/>
-      <c r="J223" s="71" t="inlineStr">
+      <c r="J223" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15252,7 +15252,7 @@
         </is>
       </c>
       <c r="I224" s="32" t="inlineStr"/>
-      <c r="J224" s="71" t="inlineStr">
+      <c r="J224" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15316,7 +15316,7 @@
         </is>
       </c>
       <c r="I225" s="32" t="inlineStr"/>
-      <c r="J225" s="71" t="inlineStr">
+      <c r="J225" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="I226" s="32" t="inlineStr"/>
-      <c r="J226" s="71" t="inlineStr">
+      <c r="J226" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="I227" s="32" t="inlineStr"/>
-      <c r="J227" s="71" t="inlineStr">
+      <c r="J227" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="I228" s="32" t="inlineStr"/>
-      <c r="J228" s="71" t="inlineStr">
+      <c r="J228" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15572,7 +15572,7 @@
         </is>
       </c>
       <c r="I229" s="32" t="inlineStr"/>
-      <c r="J229" s="71" t="inlineStr">
+      <c r="J229" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="I230" s="32" t="inlineStr"/>
-      <c r="J230" s="71" t="inlineStr">
+      <c r="J230" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="I231" s="32" t="inlineStr"/>
-      <c r="J231" s="71" t="inlineStr">
+      <c r="J231" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15764,7 +15764,7 @@
         </is>
       </c>
       <c r="I232" s="32" t="inlineStr"/>
-      <c r="J232" s="71" t="inlineStr">
+      <c r="J232" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="I233" s="32" t="inlineStr"/>
-      <c r="J233" s="71" t="inlineStr">
+      <c r="J233" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="I234" s="32" t="inlineStr"/>
-      <c r="J234" s="71" t="inlineStr">
+      <c r="J234" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15956,7 +15956,7 @@
         </is>
       </c>
       <c r="I235" s="32" t="inlineStr"/>
-      <c r="J235" s="71" t="inlineStr">
+      <c r="J235" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16020,7 +16020,7 @@
         </is>
       </c>
       <c r="I236" s="32" t="inlineStr"/>
-      <c r="J236" s="71" t="inlineStr">
+      <c r="J236" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16084,7 +16084,7 @@
         </is>
       </c>
       <c r="I237" s="32" t="inlineStr"/>
-      <c r="J237" s="71" t="inlineStr">
+      <c r="J237" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="I238" s="32" t="inlineStr"/>
-      <c r="J238" s="71" t="inlineStr">
+      <c r="J238" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="I239" s="32" t="inlineStr"/>
-      <c r="J239" s="71" t="inlineStr">
+      <c r="J239" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16276,7 +16276,7 @@
         </is>
       </c>
       <c r="I240" s="32" t="inlineStr"/>
-      <c r="J240" s="71" t="inlineStr">
+      <c r="J240" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="I241" s="32" t="inlineStr"/>
-      <c r="J241" s="71" t="inlineStr">
+      <c r="J241" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="I242" s="32" t="inlineStr"/>
-      <c r="J242" s="71" t="inlineStr">
+      <c r="J242" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="I243" s="32" t="inlineStr"/>
-      <c r="J243" s="71" t="inlineStr">
+      <c r="J243" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="I244" s="32" t="inlineStr"/>
-      <c r="J244" s="71" t="inlineStr">
+      <c r="J244" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16596,7 +16596,7 @@
         </is>
       </c>
       <c r="I245" s="32" t="inlineStr"/>
-      <c r="J245" s="71" t="inlineStr">
+      <c r="J245" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16660,7 +16660,7 @@
         </is>
       </c>
       <c r="I246" s="32" t="inlineStr"/>
-      <c r="J246" s="71" t="inlineStr">
+      <c r="J246" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="I247" s="32" t="inlineStr"/>
-      <c r="J247" s="71" t="inlineStr">
+      <c r="J247" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="I248" s="32" t="inlineStr"/>
-      <c r="J248" s="71" t="inlineStr">
+      <c r="J248" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="I249" s="32" t="inlineStr"/>
-      <c r="J249" s="71" t="inlineStr">
+      <c r="J249" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="I250" s="32" t="inlineStr"/>
-      <c r="J250" s="71" t="inlineStr">
+      <c r="J250" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="I251" s="32" t="inlineStr"/>
-      <c r="J251" s="71" t="inlineStr">
+      <c r="J251" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17044,7 +17044,7 @@
         </is>
       </c>
       <c r="I252" s="32" t="inlineStr"/>
-      <c r="J252" s="71" t="inlineStr">
+      <c r="J252" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="I253" s="32" t="inlineStr"/>
-      <c r="J253" s="71" t="inlineStr">
+      <c r="J253" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17172,7 +17172,7 @@
         </is>
       </c>
       <c r="I254" s="32" t="inlineStr"/>
-      <c r="J254" s="71" t="inlineStr">
+      <c r="J254" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17236,7 +17236,7 @@
         </is>
       </c>
       <c r="I255" s="32" t="inlineStr"/>
-      <c r="J255" s="71" t="inlineStr">
+      <c r="J255" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17300,7 +17300,7 @@
         </is>
       </c>
       <c r="I256" s="32" t="inlineStr"/>
-      <c r="J256" s="71" t="inlineStr">
+      <c r="J256" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="I257" s="32" t="inlineStr"/>
-      <c r="J257" s="71" t="inlineStr">
+      <c r="J257" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="I258" s="32" t="inlineStr"/>
-      <c r="J258" s="71" t="inlineStr">
+      <c r="J258" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="I296" s="81" t="inlineStr"/>
-      <c r="J296" s="71" t="inlineStr">
+      <c r="J296" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="I298" s="81" t="inlineStr"/>
-      <c r="J298" s="71" t="inlineStr">
+      <c r="J298" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="I300" s="81" t="inlineStr"/>
-      <c r="J300" s="71" t="inlineStr">
+      <c r="J300" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="I302" s="81" t="inlineStr"/>
-      <c r="J302" s="71" t="inlineStr">
+      <c r="J302" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="I303" s="81" t="inlineStr"/>
-      <c r="J303" s="71" t="inlineStr">
+      <c r="J303" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20084,7 +20084,7 @@
         </is>
       </c>
       <c r="I305" s="81" t="inlineStr"/>
-      <c r="J305" s="71" t="inlineStr">
+      <c r="J305" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="I306" s="81" t="inlineStr"/>
-      <c r="J306" s="71" t="inlineStr">
+      <c r="J306" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="I307" s="81" t="inlineStr"/>
-      <c r="J307" s="71" t="inlineStr">
+      <c r="J307" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="I308" s="81" t="inlineStr"/>
-      <c r="J308" s="71" t="inlineStr">
+      <c r="J308" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20356,7 +20356,7 @@
         </is>
       </c>
       <c r="I310" s="81" t="inlineStr"/>
-      <c r="J310" s="71" t="inlineStr">
+      <c r="J310" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20420,7 +20420,7 @@
         </is>
       </c>
       <c r="I311" s="81" t="inlineStr"/>
-      <c r="J311" s="71" t="inlineStr">
+      <c r="J311" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20484,7 +20484,7 @@
         </is>
       </c>
       <c r="I312" s="81" t="inlineStr"/>
-      <c r="J312" s="71" t="inlineStr">
+      <c r="J312" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20548,7 +20548,7 @@
         </is>
       </c>
       <c r="I313" s="81" t="inlineStr"/>
-      <c r="J313" s="71" t="inlineStr">
+      <c r="J313" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20612,7 +20612,7 @@
         </is>
       </c>
       <c r="I314" s="81" t="inlineStr"/>
-      <c r="J314" s="71" t="inlineStr">
+      <c r="J314" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20676,7 +20676,7 @@
         </is>
       </c>
       <c r="I315" s="81" t="inlineStr"/>
-      <c r="J315" s="71" t="inlineStr">
+      <c r="J315" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20740,7 +20740,7 @@
         </is>
       </c>
       <c r="I316" s="81" t="inlineStr"/>
-      <c r="J316" s="71" t="inlineStr">
+      <c r="J316" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="I318" s="81" t="inlineStr"/>
-      <c r="J318" s="71" t="inlineStr">
+      <c r="J318" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="I319" s="81" t="inlineStr"/>
-      <c r="J319" s="71" t="inlineStr">
+      <c r="J319" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20948,7 +20948,7 @@
         </is>
       </c>
       <c r="I320" s="81" t="inlineStr"/>
-      <c r="J320" s="71" t="inlineStr">
+      <c r="J320" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="I321" s="81" t="inlineStr"/>
-      <c r="J321" s="71" t="inlineStr">
+      <c r="J321" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21076,7 +21076,7 @@
         </is>
       </c>
       <c r="I322" s="81" t="inlineStr"/>
-      <c r="J322" s="71" t="inlineStr">
+      <c r="J322" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21140,7 +21140,7 @@
         </is>
       </c>
       <c r="I323" s="81" t="inlineStr"/>
-      <c r="J323" s="71" t="inlineStr">
+      <c r="J323" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21204,7 +21204,7 @@
         </is>
       </c>
       <c r="I324" s="81" t="inlineStr"/>
-      <c r="J324" s="71" t="inlineStr">
+      <c r="J324" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21268,7 +21268,7 @@
         </is>
       </c>
       <c r="I325" s="81" t="inlineStr"/>
-      <c r="J325" s="71" t="inlineStr">
+      <c r="J325" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21348,7 +21348,7 @@
         </is>
       </c>
       <c r="I327" s="81" t="inlineStr"/>
-      <c r="J327" s="71" t="inlineStr">
+      <c r="J327" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21412,7 +21412,7 @@
         </is>
       </c>
       <c r="I328" s="81" t="inlineStr"/>
-      <c r="J328" s="71" t="inlineStr">
+      <c r="J328" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="I329" s="81" t="inlineStr"/>
-      <c r="J329" s="71" t="inlineStr">
+      <c r="J329" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="I330" s="81" t="inlineStr"/>
-      <c r="J330" s="71" t="inlineStr">
+      <c r="J330" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21604,7 +21604,7 @@
         </is>
       </c>
       <c r="I331" s="81" t="inlineStr"/>
-      <c r="J331" s="71" t="inlineStr">
+      <c r="J331" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21668,7 +21668,7 @@
         </is>
       </c>
       <c r="I332" s="81" t="inlineStr"/>
-      <c r="J332" s="71" t="inlineStr">
+      <c r="J332" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="I333" s="81" t="inlineStr"/>
-      <c r="J333" s="71" t="inlineStr">
+      <c r="J333" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21796,7 +21796,7 @@
         </is>
       </c>
       <c r="I334" s="81" t="inlineStr"/>
-      <c r="J334" s="71" t="inlineStr">
+      <c r="J334" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="I336" s="81" t="inlineStr"/>
-      <c r="J336" s="71" t="inlineStr">
+      <c r="J336" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22008,7 +22008,7 @@
         </is>
       </c>
       <c r="I338" s="81" t="inlineStr"/>
-      <c r="J338" s="71" t="inlineStr">
+      <c r="J338" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22072,7 +22072,7 @@
         </is>
       </c>
       <c r="I339" s="81" t="inlineStr"/>
-      <c r="J339" s="71" t="inlineStr">
+      <c r="J339" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="I340" s="81" t="inlineStr"/>
-      <c r="J340" s="71" t="inlineStr">
+      <c r="J340" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="I341" s="81" t="inlineStr"/>
-      <c r="J341" s="71" t="inlineStr">
+      <c r="J341" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="I342" s="81" t="inlineStr"/>
-      <c r="J342" s="71" t="inlineStr">
+      <c r="J342" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22328,7 +22328,7 @@
         </is>
       </c>
       <c r="I343" s="81" t="inlineStr"/>
-      <c r="J343" s="71" t="inlineStr">
+      <c r="J343" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22392,7 +22392,7 @@
         </is>
       </c>
       <c r="I344" s="81" t="inlineStr"/>
-      <c r="J344" s="71" t="inlineStr">
+      <c r="J344" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22456,7 +22456,7 @@
         </is>
       </c>
       <c r="I345" s="81" t="inlineStr"/>
-      <c r="J345" s="71" t="inlineStr">
+      <c r="J345" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22520,7 +22520,7 @@
         </is>
       </c>
       <c r="I346" s="81" t="inlineStr"/>
-      <c r="J346" s="71" t="inlineStr">
+      <c r="J346" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="I347" s="81" t="inlineStr"/>
-      <c r="J347" s="71" t="inlineStr">
+      <c r="J347" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22648,7 +22648,7 @@
         </is>
       </c>
       <c r="I348" s="81" t="inlineStr"/>
-      <c r="J348" s="71" t="inlineStr">
+      <c r="J348" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="I349" s="81" t="inlineStr"/>
-      <c r="J349" s="71" t="inlineStr">
+      <c r="J349" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="I350" s="81" t="inlineStr"/>
-      <c r="J350" s="71" t="inlineStr">
+      <c r="J350" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22840,7 +22840,7 @@
         </is>
       </c>
       <c r="I351" s="81" t="inlineStr"/>
-      <c r="J351" s="71" t="inlineStr">
+      <c r="J351" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22904,7 +22904,7 @@
         </is>
       </c>
       <c r="I352" s="81" t="inlineStr"/>
-      <c r="J352" s="71" t="inlineStr">
+      <c r="J352" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22984,7 +22984,7 @@
         </is>
       </c>
       <c r="I354" s="81" t="inlineStr"/>
-      <c r="J354" s="71" t="inlineStr">
+      <c r="J354" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="I355" s="81" t="inlineStr"/>
-      <c r="J355" s="71" t="inlineStr">
+      <c r="J355" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23112,7 +23112,7 @@
         </is>
       </c>
       <c r="I356" s="81" t="inlineStr"/>
-      <c r="J356" s="71" t="inlineStr">
+      <c r="J356" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="I357" s="81" t="inlineStr"/>
-      <c r="J357" s="71" t="inlineStr">
+      <c r="J357" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="B360" s="86" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="I43" s="81" t="inlineStr"/>
-      <c r="J43" s="71" t="inlineStr">
+      <c r="J43" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26086,7 +26086,7 @@
         </is>
       </c>
       <c r="I44" s="81" t="inlineStr"/>
-      <c r="J44" s="71" t="inlineStr">
+      <c r="J44" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26150,7 +26150,7 @@
         </is>
       </c>
       <c r="I45" s="81" t="inlineStr"/>
-      <c r="J45" s="71" t="inlineStr">
+      <c r="J45" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26214,7 +26214,7 @@
         </is>
       </c>
       <c r="I46" s="81" t="inlineStr"/>
-      <c r="J46" s="71" t="inlineStr">
+      <c r="J46" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26278,7 +26278,7 @@
         </is>
       </c>
       <c r="I47" s="81" t="inlineStr"/>
-      <c r="J47" s="71" t="inlineStr">
+      <c r="J47" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26342,7 +26342,7 @@
         </is>
       </c>
       <c r="I48" s="81" t="inlineStr"/>
-      <c r="J48" s="71" t="inlineStr">
+      <c r="J48" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26406,7 +26406,7 @@
         </is>
       </c>
       <c r="I49" s="81" t="inlineStr"/>
-      <c r="J49" s="71" t="inlineStr">
+      <c r="J49" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26486,7 +26486,7 @@
         </is>
       </c>
       <c r="I51" s="81" t="inlineStr"/>
-      <c r="J51" s="71" t="inlineStr">
+      <c r="J51" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26550,7 +26550,7 @@
         </is>
       </c>
       <c r="I52" s="81" t="inlineStr"/>
-      <c r="J52" s="71" t="inlineStr">
+      <c r="J52" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26614,7 +26614,7 @@
         </is>
       </c>
       <c r="I53" s="81" t="inlineStr"/>
-      <c r="J53" s="71" t="inlineStr">
+      <c r="J53" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26678,7 +26678,7 @@
         </is>
       </c>
       <c r="I54" s="81" t="inlineStr"/>
-      <c r="J54" s="71" t="inlineStr">
+      <c r="J54" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="I55" s="81" t="inlineStr"/>
-      <c r="J55" s="71" t="inlineStr">
+      <c r="J55" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26806,7 +26806,7 @@
         </is>
       </c>
       <c r="I56" s="81" t="inlineStr"/>
-      <c r="J56" s="71" t="inlineStr">
+      <c r="J56" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26870,7 +26870,7 @@
         </is>
       </c>
       <c r="I57" s="81" t="inlineStr"/>
-      <c r="J57" s="71" t="inlineStr">
+      <c r="J57" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -26934,7 +26934,7 @@
         </is>
       </c>
       <c r="I58" s="81" t="inlineStr"/>
-      <c r="J58" s="71" t="inlineStr">
+      <c r="J58" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_21</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BORDER MERCENARY)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield weapons×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13970,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="B205" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C205" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_16</t>
         </is>
       </c>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -14066,9 +14066,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H205" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H205" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I205" s="68" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="N205" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14106,17 +14106,17 @@
       </c>
       <c r="B206" s="67" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C206" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_16</t>
+          <t>GOV_LOYAL_ARC_17</t>
         </is>
       </c>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="N206" s="69" t="inlineStr">
         <is>
-          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14174,17 +14174,17 @@
       </c>
       <c r="B207" s="67" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C207" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_17</t>
+          <t>GOV_LOYAL_ARC_21</t>
         </is>
       </c>
       <c r="D207" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
+          <t>MERCENARY COMMANDER'S PATRIOTIC DISPLAY</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="N207" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: gold_and_army_buff Mercenary Zeal×10 turns + 50 gold; BTN2: army_buff Iron Discipline permanent; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="B360" s="86" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1163,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N362"/>
+  <dimension ref="A1:N359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_20</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL HAWAIIAN REFUGEE)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13970,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_16</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -13998,9 +13998,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H204" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I204" s="68" t="inlineStr"/>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="B205" s="67" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C205" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_16</t>
+          <t>GOV_LOYAL_ARC_17</t>
         </is>
       </c>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="N205" s="69" t="inlineStr">
         <is>
-          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14106,17 +14106,17 @@
       </c>
       <c r="B206" s="67" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C206" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_17</t>
+          <t>GOV_LOYAL_ARC_21</t>
         </is>
       </c>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
+          <t>MERCENARY COMMANDER'S PATRIOTIC DISPLAY</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -14162,93 +14162,89 @@
       </c>
       <c r="N206" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="67" t="inlineStr">
-        <is>
-          <t>Loyal Governor</t>
-        </is>
-      </c>
-      <c r="B207" s="67" t="inlineStr">
-        <is>
-          <t>Border Mercenary</t>
-        </is>
-      </c>
-      <c r="C207" s="68" t="inlineStr">
-        <is>
-          <t>GOV_LOYAL_ARC_21</t>
-        </is>
-      </c>
-      <c r="D207" s="69" t="inlineStr">
-        <is>
-          <t>MERCENARY COMMANDER'S PATRIOTIC DISPLAY</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F207" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G207" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H207" s="26" t="inlineStr">
+          <t>BTN1: gold_and_army_buff Mercenary Zeal×10 turns + 50 gold; BTN2: army_buff Iron Discipline permanent; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="8" customHeight="1">
+      <c r="A207" s="9" t="n"/>
+      <c r="B207" s="9" t="n"/>
+      <c r="C207" s="9" t="n"/>
+      <c r="D207" s="9" t="n"/>
+      <c r="E207" s="9" t="n"/>
+      <c r="F207" s="9" t="n"/>
+      <c r="G207" s="9" t="n"/>
+      <c r="H207" s="9" t="n"/>
+      <c r="I207" s="9" t="n"/>
+      <c r="J207" s="9" t="n"/>
+      <c r="K207" s="9" t="n"/>
+      <c r="L207" s="9" t="n"/>
+      <c r="M207" s="9" t="n"/>
+      <c r="N207" s="9" t="n"/>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B208" s="31" t="inlineStr">
+        <is>
+          <t>Wetlands Fisher</t>
+        </is>
+      </c>
+      <c r="C208" s="32" t="inlineStr">
+        <is>
+          <t>ARC_01_FIRST</t>
+        </is>
+      </c>
+      <c r="D208" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WETLANDS FISHER FIRST OBJECTIVE</t>
+        </is>
+      </c>
+      <c r="E208" s="34" t="inlineStr">
+        <is>
+          <t>Milestone 1</t>
+        </is>
+      </c>
+      <c r="F208" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="33" t="inlineStr">
+        <is>
+          <t>ARC_01_DONE</t>
+        </is>
+      </c>
+      <c r="H208" s="26" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="I207" s="68" t="inlineStr"/>
-      <c r="J207" s="70" t="inlineStr">
+      <c r="I208" s="32" t="inlineStr"/>
+      <c r="J208" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K207" s="71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L207" s="68" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M207" s="71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N207" s="69" t="inlineStr">
-        <is>
-          <t>BTN1: gold_and_army_buff Mercenary Zeal×10 turns + 50 gold; BTN2: army_buff Iron Discipline permanent; 3%/turn at loyalty≥8; once per governor</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="8" customHeight="1">
-      <c r="A208" s="9" t="n"/>
-      <c r="B208" s="9" t="n"/>
-      <c r="C208" s="9" t="n"/>
-      <c r="D208" s="9" t="n"/>
-      <c r="E208" s="9" t="n"/>
-      <c r="F208" s="9" t="n"/>
-      <c r="G208" s="9" t="n"/>
-      <c r="H208" s="9" t="n"/>
-      <c r="I208" s="9" t="n"/>
-      <c r="J208" s="9" t="n"/>
-      <c r="K208" s="9" t="n"/>
-      <c r="L208" s="9" t="n"/>
-      <c r="M208" s="9" t="n"/>
-      <c r="N208" s="9" t="n"/>
+      <c r="K208" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L208" s="32" t="inlineStr"/>
+      <c r="M208" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N208" s="33" t="inlineStr">
+        <is>
+          <t>Fires when ARC_01 completes objective 1; BTN1: nothing</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="30" customHeight="1">
       <c r="A209" s="31" t="inlineStr">
@@ -14263,27 +14259,27 @@
       </c>
       <c r="C209" s="32" t="inlineStr">
         <is>
+          <t>ARC_01_DONE</t>
+        </is>
+      </c>
+      <c r="D209" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WETLANDS FISHER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E209" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F209" s="33" t="inlineStr">
+        <is>
           <t>ARC_01_FIRST</t>
         </is>
       </c>
-      <c r="D209" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — WETLANDS FISHER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E209" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F209" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G209" s="33" t="inlineStr">
         <is>
-          <t>ARC_01_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H209" s="26" t="inlineStr">
@@ -14310,7 +14306,7 @@
       </c>
       <c r="N209" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_01 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_01 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -14322,37 +14318,37 @@
       </c>
       <c r="B210" s="31" t="inlineStr">
         <is>
-          <t>Wetlands Fisher</t>
+          <t>Appalachian Miner</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
         <is>
-          <t>ARC_01_DONE</t>
+          <t>ARC_02_FIRST</t>
         </is>
       </c>
       <c r="D210" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — WETLANDS FISHER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — APPALACHIAN MINER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E210" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F210" s="33" t="inlineStr">
         <is>
-          <t>ARC_01_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G210" s="33" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H210" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
+          <t>ARC_02_DONE</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I210" s="32" t="inlineStr"/>
@@ -14374,7 +14370,7 @@
       </c>
       <c r="N210" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_01 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_02 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14391,27 +14387,27 @@
       </c>
       <c r="C211" s="32" t="inlineStr">
         <is>
+          <t>ARC_02_DONE</t>
+        </is>
+      </c>
+      <c r="D211" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — APPALACHIAN MINER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E211" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F211" s="33" t="inlineStr">
+        <is>
           <t>ARC_02_FIRST</t>
         </is>
       </c>
-      <c r="D211" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — APPALACHIAN MINER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E211" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F211" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G211" s="33" t="inlineStr">
         <is>
-          <t>ARC_02_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
@@ -14438,7 +14434,7 @@
       </c>
       <c r="N211" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_02 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_02 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
         </is>
       </c>
     </row>
@@ -14450,32 +14446,32 @@
       </c>
       <c r="B212" s="31" t="inlineStr">
         <is>
-          <t>Appalachian Miner</t>
+          <t>Ivy League Dropout</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
         <is>
-          <t>ARC_02_DONE</t>
+          <t>ARC_03_FIRST</t>
         </is>
       </c>
       <c r="D212" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — APPALACHIAN MINER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E212" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F212" s="33" t="inlineStr">
         <is>
-          <t>ARC_02_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G212" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_03_DONE</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
@@ -14502,7 +14498,7 @@
       </c>
       <c r="N212" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_02 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
+          <t>Fires when ARC_03 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14519,27 +14515,27 @@
       </c>
       <c r="C213" s="32" t="inlineStr">
         <is>
+          <t>ARC_03_DONE</t>
+        </is>
+      </c>
+      <c r="D213" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E213" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F213" s="33" t="inlineStr">
+        <is>
           <t>ARC_03_FIRST</t>
         </is>
       </c>
-      <c r="D213" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E213" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F213" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G213" s="33" t="inlineStr">
         <is>
-          <t>ARC_03_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
@@ -14566,7 +14562,7 @@
       </c>
       <c r="N213" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_03 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_03 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -14578,32 +14574,32 @@
       </c>
       <c r="B214" s="31" t="inlineStr">
         <is>
-          <t>Ivy League Dropout</t>
+          <t>Seminole Fighter</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
         <is>
-          <t>ARC_03_DONE</t>
+          <t>ARC_04_FIRST</t>
         </is>
       </c>
       <c r="D214" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E214" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F214" s="33" t="inlineStr">
         <is>
-          <t>ARC_03_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G214" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_04_DONE</t>
         </is>
       </c>
       <c r="H214" s="6" t="inlineStr">
@@ -14630,7 +14626,7 @@
       </c>
       <c r="N214" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_03 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_04 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14647,27 +14643,27 @@
       </c>
       <c r="C215" s="32" t="inlineStr">
         <is>
+          <t>ARC_04_DONE</t>
+        </is>
+      </c>
+      <c r="D215" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E215" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F215" s="33" t="inlineStr">
+        <is>
           <t>ARC_04_FIRST</t>
         </is>
       </c>
-      <c r="D215" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E215" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F215" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G215" s="33" t="inlineStr">
         <is>
-          <t>ARC_04_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
@@ -14694,7 +14690,7 @@
       </c>
       <c r="N215" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_04 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_04 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
         </is>
       </c>
     </row>
@@ -14706,32 +14702,32 @@
       </c>
       <c r="B216" s="31" t="inlineStr">
         <is>
-          <t>Seminole Fighter</t>
+          <t>Green Mountain Farmer</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
         <is>
-          <t>ARC_04_DONE</t>
+          <t>ARC_05_FIRST</t>
         </is>
       </c>
       <c r="D216" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E216" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F216" s="33" t="inlineStr">
         <is>
-          <t>ARC_04_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G216" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_05_DONE</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
@@ -14758,7 +14754,7 @@
       </c>
       <c r="N216" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_04 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
+          <t>Fires when ARC_05 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14775,27 +14771,27 @@
       </c>
       <c r="C217" s="32" t="inlineStr">
         <is>
+          <t>ARC_05_DONE</t>
+        </is>
+      </c>
+      <c r="D217" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E217" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F217" s="33" t="inlineStr">
+        <is>
           <t>ARC_05_FIRST</t>
         </is>
       </c>
-      <c r="D217" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E217" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F217" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G217" s="33" t="inlineStr">
         <is>
-          <t>ARC_05_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
@@ -14822,7 +14818,7 @@
       </c>
       <c r="N217" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_05 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_05 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14830,32 @@
       </c>
       <c r="B218" s="31" t="inlineStr">
         <is>
-          <t>Green Mountain Farmer</t>
+          <t>Chesapeake Shipwright</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
         <is>
-          <t>ARC_05_DONE</t>
+          <t>ARC_06_FIRST</t>
         </is>
       </c>
       <c r="D218" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E218" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F218" s="33" t="inlineStr">
         <is>
-          <t>ARC_05_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G218" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_06_DONE</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
@@ -14886,7 +14882,7 @@
       </c>
       <c r="N218" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_05 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_06 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14903,27 +14899,27 @@
       </c>
       <c r="C219" s="32" t="inlineStr">
         <is>
+          <t>ARC_06_DONE</t>
+        </is>
+      </c>
+      <c r="D219" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E219" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F219" s="33" t="inlineStr">
+        <is>
           <t>ARC_06_FIRST</t>
         </is>
       </c>
-      <c r="D219" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E219" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F219" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G219" s="33" t="inlineStr">
         <is>
-          <t>ARC_06_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
@@ -14950,7 +14946,7 @@
       </c>
       <c r="N219" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_06 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_06 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
         </is>
       </c>
     </row>
@@ -14962,32 +14958,32 @@
       </c>
       <c r="B220" s="31" t="inlineStr">
         <is>
-          <t>Chesapeake Shipwright</t>
+          <t>Loyalist Turncoat</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
         <is>
-          <t>ARC_06_DONE</t>
+          <t>ARC_07_FIRST</t>
         </is>
       </c>
       <c r="D220" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E220" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F220" s="33" t="inlineStr">
         <is>
-          <t>ARC_06_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G220" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_07_DONE</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
@@ -15014,7 +15010,7 @@
       </c>
       <c r="N220" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_06 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+          <t>Fires when ARC_07 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15031,27 +15027,27 @@
       </c>
       <c r="C221" s="32" t="inlineStr">
         <is>
+          <t>ARC_07_DONE</t>
+        </is>
+      </c>
+      <c r="D221" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E221" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F221" s="33" t="inlineStr">
+        <is>
           <t>ARC_07_FIRST</t>
         </is>
       </c>
-      <c r="D221" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E221" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F221" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G221" s="33" t="inlineStr">
         <is>
-          <t>ARC_07_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
@@ -15078,7 +15074,7 @@
       </c>
       <c r="N221" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_07 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_07 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -15090,32 +15086,32 @@
       </c>
       <c r="B222" s="31" t="inlineStr">
         <is>
-          <t>Loyalist Turncoat</t>
+          <t>Tobacco Belt Drifter</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
         <is>
-          <t>ARC_07_DONE</t>
+          <t>ARC_08_FIRST</t>
         </is>
       </c>
       <c r="D222" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E222" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F222" s="33" t="inlineStr">
         <is>
-          <t>ARC_07_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G222" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_08_DONE</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
@@ -15142,7 +15138,7 @@
       </c>
       <c r="N222" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_07 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_08 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15159,27 +15155,27 @@
       </c>
       <c r="C223" s="32" t="inlineStr">
         <is>
+          <t>ARC_08_DONE</t>
+        </is>
+      </c>
+      <c r="D223" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E223" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F223" s="33" t="inlineStr">
+        <is>
           <t>ARC_08_FIRST</t>
         </is>
       </c>
-      <c r="D223" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E223" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F223" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G223" s="33" t="inlineStr">
         <is>
-          <t>ARC_08_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
@@ -15206,7 +15202,7 @@
       </c>
       <c r="N223" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_08 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_08 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -15218,32 +15214,32 @@
       </c>
       <c r="B224" s="31" t="inlineStr">
         <is>
-          <t>Tobacco Belt Drifter</t>
+          <t>War Widow</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
         <is>
-          <t>ARC_08_DONE</t>
+          <t>ARC_09_FIRST</t>
         </is>
       </c>
       <c r="D224" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — WAR WIDOW FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E224" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F224" s="33" t="inlineStr">
         <is>
-          <t>ARC_08_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G224" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_09_DONE</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
@@ -15270,7 +15266,7 @@
       </c>
       <c r="N224" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_08 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_09 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15287,27 +15283,27 @@
       </c>
       <c r="C225" s="32" t="inlineStr">
         <is>
+          <t>ARC_09_DONE</t>
+        </is>
+      </c>
+      <c r="D225" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — WAR WIDOW ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E225" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F225" s="33" t="inlineStr">
+        <is>
           <t>ARC_09_FIRST</t>
         </is>
       </c>
-      <c r="D225" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — WAR WIDOW FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E225" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F225" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G225" s="33" t="inlineStr">
         <is>
-          <t>ARC_09_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
@@ -15334,7 +15330,7 @@
       </c>
       <c r="N225" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_09 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_09 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -15346,32 +15342,32 @@
       </c>
       <c r="B226" s="31" t="inlineStr">
         <is>
-          <t>War Widow</t>
+          <t>Indigenous Scout</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
         <is>
-          <t>ARC_09_DONE</t>
+          <t>ARC_10_FIRST</t>
         </is>
       </c>
       <c r="D226" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — WAR WIDOW ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E226" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F226" s="33" t="inlineStr">
         <is>
-          <t>ARC_09_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G226" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_10_DONE</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
@@ -15398,7 +15394,7 @@
       </c>
       <c r="N226" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_09 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_10 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15415,27 +15411,27 @@
       </c>
       <c r="C227" s="32" t="inlineStr">
         <is>
+          <t>ARC_10_DONE</t>
+        </is>
+      </c>
+      <c r="D227" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E227" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F227" s="33" t="inlineStr">
+        <is>
           <t>ARC_10_FIRST</t>
         </is>
       </c>
-      <c r="D227" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E227" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F227" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G227" s="33" t="inlineStr">
         <is>
-          <t>ARC_10_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
@@ -15462,7 +15458,7 @@
       </c>
       <c r="N227" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_10 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_10 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
         </is>
       </c>
     </row>
@@ -15474,32 +15470,32 @@
       </c>
       <c r="B228" s="31" t="inlineStr">
         <is>
-          <t>Indigenous Scout</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
         <is>
-          <t>ARC_10_DONE</t>
+          <t>ARC_11_FIRST</t>
         </is>
       </c>
       <c r="D228" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E228" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F228" s="33" t="inlineStr">
         <is>
-          <t>ARC_10_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G228" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_11_DONE</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
@@ -15526,7 +15522,7 @@
       </c>
       <c r="N228" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_10 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+          <t>Fires when ARC_11 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15543,27 +15539,27 @@
       </c>
       <c r="C229" s="32" t="inlineStr">
         <is>
+          <t>ARC_11_DONE</t>
+        </is>
+      </c>
+      <c r="D229" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E229" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F229" s="33" t="inlineStr">
+        <is>
           <t>ARC_11_FIRST</t>
         </is>
       </c>
-      <c r="D229" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E229" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F229" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G229" s="33" t="inlineStr">
         <is>
-          <t>ARC_11_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
@@ -15590,7 +15586,7 @@
       </c>
       <c r="N229" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_11 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_11 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
         </is>
       </c>
     </row>
@@ -15602,32 +15598,32 @@
       </c>
       <c r="B230" s="31" t="inlineStr">
         <is>
-          <t>Boston Rabble-Rouser</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
         <is>
-          <t>ARC_11_DONE</t>
+          <t>ARC_12_FIRST</t>
         </is>
       </c>
       <c r="D230" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E230" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F230" s="33" t="inlineStr">
         <is>
-          <t>ARC_11_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G230" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_12_DONE</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
@@ -15654,7 +15650,7 @@
       </c>
       <c r="N230" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_11 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires when ARC_12 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15671,27 +15667,27 @@
       </c>
       <c r="C231" s="32" t="inlineStr">
         <is>
+          <t>ARC_12_DONE</t>
+        </is>
+      </c>
+      <c r="D231" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E231" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F231" s="33" t="inlineStr">
+        <is>
           <t>ARC_12_FIRST</t>
         </is>
       </c>
-      <c r="D231" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E231" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F231" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G231" s="33" t="inlineStr">
         <is>
-          <t>ARC_12_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
@@ -15718,7 +15714,7 @@
       </c>
       <c r="N231" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_12 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_12 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -15730,32 +15726,32 @@
       </c>
       <c r="B232" s="31" t="inlineStr">
         <is>
-          <t>Continental Surgeon</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
         <is>
-          <t>ARC_12_DONE</t>
+          <t>ARC_13_FIRST</t>
         </is>
       </c>
       <c r="D232" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — NANTUCKET SAILOR FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E232" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F232" s="33" t="inlineStr">
         <is>
-          <t>ARC_12_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G232" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_13_DONE</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
@@ -15782,7 +15778,7 @@
       </c>
       <c r="N232" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_12 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_13 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15799,27 +15795,27 @@
       </c>
       <c r="C233" s="32" t="inlineStr">
         <is>
+          <t>ARC_13_DONE</t>
+        </is>
+      </c>
+      <c r="D233" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — NANTUCKET SAILOR ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E233" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F233" s="33" t="inlineStr">
+        <is>
           <t>ARC_13_FIRST</t>
         </is>
       </c>
-      <c r="D233" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — NANTUCKET SAILOR FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E233" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F233" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G233" s="33" t="inlineStr">
         <is>
-          <t>ARC_13_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
@@ -15846,7 +15842,7 @@
       </c>
       <c r="N233" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_13 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_13 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -15858,32 +15854,32 @@
       </c>
       <c r="B234" s="31" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
         <is>
-          <t>ARC_13_DONE</t>
+          <t>ARC_14_FIRST</t>
         </is>
       </c>
       <c r="D234" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — NANTUCKET SAILOR ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — FRONTIER PREACHER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E234" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F234" s="33" t="inlineStr">
         <is>
-          <t>ARC_13_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G234" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_14_DONE</t>
         </is>
       </c>
       <c r="H234" s="6" t="inlineStr">
@@ -15910,7 +15906,7 @@
       </c>
       <c r="N234" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_13 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_14 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15927,27 +15923,27 @@
       </c>
       <c r="C235" s="32" t="inlineStr">
         <is>
+          <t>ARC_14_DONE</t>
+        </is>
+      </c>
+      <c r="D235" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — FRONTIER PREACHER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E235" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F235" s="33" t="inlineStr">
+        <is>
           <t>ARC_14_FIRST</t>
         </is>
       </c>
-      <c r="D235" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — FRONTIER PREACHER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E235" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F235" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G235" s="33" t="inlineStr">
         <is>
-          <t>ARC_14_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
@@ -15974,7 +15970,7 @@
       </c>
       <c r="N235" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_14 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_14 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
         </is>
       </c>
     </row>
@@ -15986,32 +15982,32 @@
       </c>
       <c r="B236" s="31" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
         <is>
-          <t>ARC_14_DONE</t>
+          <t>ARC_15_FIRST</t>
         </is>
       </c>
       <c r="D236" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — FRONTIER PREACHER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — DC BUREAUCRAT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E236" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F236" s="33" t="inlineStr">
         <is>
-          <t>ARC_14_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G236" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_15_DONE</t>
         </is>
       </c>
       <c r="H236" s="6" t="inlineStr">
@@ -16038,7 +16034,7 @@
       </c>
       <c r="N236" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_14 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires when ARC_15 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16055,27 +16051,27 @@
       </c>
       <c r="C237" s="32" t="inlineStr">
         <is>
+          <t>ARC_15_DONE</t>
+        </is>
+      </c>
+      <c r="D237" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — DC BUREAUCRAT ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E237" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F237" s="33" t="inlineStr">
+        <is>
           <t>ARC_15_FIRST</t>
         </is>
       </c>
-      <c r="D237" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — DC BUREAUCRAT FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E237" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F237" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G237" s="33" t="inlineStr">
         <is>
-          <t>ARC_15_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
@@ -16102,7 +16098,7 @@
       </c>
       <c r="N237" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_15 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_15 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -16114,32 +16110,32 @@
       </c>
       <c r="B238" s="31" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
         <is>
-          <t>ARC_15_DONE</t>
+          <t>ARC_16_FIRST</t>
         </is>
       </c>
       <c r="D238" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — DC BUREAUCRAT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E238" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F238" s="33" t="inlineStr">
         <is>
-          <t>ARC_15_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G238" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_16_DONE</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
@@ -16166,7 +16162,7 @@
       </c>
       <c r="N238" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_15 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_16 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16183,27 +16179,27 @@
       </c>
       <c r="C239" s="32" t="inlineStr">
         <is>
+          <t>ARC_16_DONE</t>
+        </is>
+      </c>
+      <c r="D239" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E239" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F239" s="33" t="inlineStr">
+        <is>
           <t>ARC_16_FIRST</t>
         </is>
       </c>
-      <c r="D239" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E239" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F239" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G239" s="33" t="inlineStr">
         <is>
-          <t>ARC_16_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
@@ -16230,7 +16226,7 @@
       </c>
       <c r="N239" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_16 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_16 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
         </is>
       </c>
     </row>
@@ -16242,32 +16238,32 @@
       </c>
       <c r="B240" s="31" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
         <is>
-          <t>ARC_16_DONE</t>
+          <t>ARC_17_FIRST</t>
         </is>
       </c>
       <c r="D240" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — PLANTATION DESERTER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E240" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F240" s="33" t="inlineStr">
         <is>
-          <t>ARC_16_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G240" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_17_DONE</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
@@ -16294,7 +16290,7 @@
       </c>
       <c r="N240" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_16 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
+          <t>Fires when ARC_17 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16311,27 +16307,27 @@
       </c>
       <c r="C241" s="32" t="inlineStr">
         <is>
+          <t>ARC_17_DONE</t>
+        </is>
+      </c>
+      <c r="D241" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — PLANTATION DESERTER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E241" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F241" s="33" t="inlineStr">
+        <is>
           <t>ARC_17_FIRST</t>
         </is>
       </c>
-      <c r="D241" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — PLANTATION DESERTER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E241" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F241" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G241" s="33" t="inlineStr">
         <is>
-          <t>ARC_17_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H241" s="6" t="inlineStr">
@@ -16358,7 +16354,7 @@
       </c>
       <c r="N241" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_17 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_17 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -16370,32 +16366,32 @@
       </c>
       <c r="B242" s="31" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
         <is>
-          <t>ARC_17_DONE</t>
+          <t>ARC_18_FIRST</t>
         </is>
       </c>
       <c r="D242" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — PLANTATION DESERTER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — SWAMP WITCH FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E242" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F242" s="33" t="inlineStr">
         <is>
-          <t>ARC_17_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G242" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_18_DONE</t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
@@ -16422,7 +16418,7 @@
       </c>
       <c r="N242" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_17 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_18 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16439,27 +16435,27 @@
       </c>
       <c r="C243" s="32" t="inlineStr">
         <is>
+          <t>ARC_18_DONE</t>
+        </is>
+      </c>
+      <c r="D243" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — SWAMP WITCH ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E243" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F243" s="33" t="inlineStr">
+        <is>
           <t>ARC_18_FIRST</t>
         </is>
       </c>
-      <c r="D243" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — SWAMP WITCH FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E243" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F243" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G243" s="33" t="inlineStr">
         <is>
-          <t>ARC_18_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
@@ -16486,7 +16482,7 @@
       </c>
       <c r="N243" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_18 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_18 completes all 3 objectives; BTN1: morale+20, BTN2: magic</t>
         </is>
       </c>
     </row>
@@ -16498,32 +16494,32 @@
       </c>
       <c r="B244" s="31" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
         <is>
-          <t>ARC_18_DONE</t>
+          <t>ARC_19_FIRST</t>
         </is>
       </c>
       <c r="D244" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — SWAMP WITCH ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E244" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F244" s="33" t="inlineStr">
         <is>
-          <t>ARC_18_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G244" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_19_DONE</t>
         </is>
       </c>
       <c r="H244" s="6" t="inlineStr">
@@ -16550,7 +16546,7 @@
       </c>
       <c r="N244" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_18 completes all 3 objectives; BTN1: morale+20, BTN2: magic</t>
+          <t>Fires when ARC_19 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16567,27 +16563,27 @@
       </c>
       <c r="C245" s="32" t="inlineStr">
         <is>
+          <t>ARC_19_DONE</t>
+        </is>
+      </c>
+      <c r="D245" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E245" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F245" s="33" t="inlineStr">
+        <is>
           <t>ARC_19_FIRST</t>
         </is>
       </c>
-      <c r="D245" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E245" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F245" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G245" s="33" t="inlineStr">
         <is>
-          <t>ARC_19_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
@@ -16614,7 +16610,7 @@
       </c>
       <c r="N245" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_19 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_19 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -16626,32 +16622,32 @@
       </c>
       <c r="B246" s="31" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
         <is>
-          <t>ARC_19_DONE</t>
+          <t>ARC_21_FIRST</t>
         </is>
       </c>
       <c r="D246" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — BORDER MERCENARY FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E246" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F246" s="33" t="inlineStr">
         <is>
-          <t>ARC_19_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G246" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_21_DONE</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
@@ -16678,7 +16674,7 @@
       </c>
       <c r="N246" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_19 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_21 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16690,32 +16686,32 @@
       </c>
       <c r="B247" s="31" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
         <is>
-          <t>ARC_20_FIRST</t>
+          <t>ARC_21_DONE</t>
         </is>
       </c>
       <c r="D247" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — HAWAIIAN REFUGEE FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — BORDER MERCENARY ARC COMPLETE</t>
         </is>
       </c>
       <c r="E247" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F247" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_21_FIRST</t>
         </is>
       </c>
       <c r="G247" s="33" t="inlineStr">
         <is>
-          <t>ARC_20_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
@@ -16742,7 +16738,7 @@
       </c>
       <c r="N247" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_20 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_21 completes all 3 objectives; BTN1: morale+20, BTN2: weapons</t>
         </is>
       </c>
     </row>
@@ -16754,32 +16750,32 @@
       </c>
       <c r="B248" s="31" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
         <is>
-          <t>ARC_20_DONE</t>
+          <t>ARC_22_FIRST</t>
         </is>
       </c>
       <c r="D248" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — HAWAIIAN REFUGEE ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E248" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F248" s="33" t="inlineStr">
         <is>
-          <t>ARC_20_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G248" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_22_DONE</t>
         </is>
       </c>
       <c r="H248" s="6" t="inlineStr">
@@ -16806,7 +16802,7 @@
       </c>
       <c r="N248" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_20 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires when ARC_22 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16818,32 +16814,32 @@
       </c>
       <c r="B249" s="31" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
         <is>
-          <t>ARC_21_FIRST</t>
+          <t>ARC_22_DONE</t>
         </is>
       </c>
       <c r="D249" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BORDER MERCENARY FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E249" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F249" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_22_FIRST</t>
         </is>
       </c>
       <c r="G249" s="33" t="inlineStr">
         <is>
-          <t>ARC_21_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
@@ -16870,7 +16866,7 @@
       </c>
       <c r="N249" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_21 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_22 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
         </is>
       </c>
     </row>
@@ -16882,32 +16878,32 @@
       </c>
       <c r="B250" s="31" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
         <is>
-          <t>ARC_21_DONE</t>
+          <t>ARC_23_FIRST</t>
         </is>
       </c>
       <c r="D250" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BORDER MERCENARY ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E250" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F250" s="33" t="inlineStr">
         <is>
-          <t>ARC_21_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G250" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_23_DONE</t>
         </is>
       </c>
       <c r="H250" s="6" t="inlineStr">
@@ -16934,7 +16930,7 @@
       </c>
       <c r="N250" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_21 completes all 3 objectives; BTN1: morale+20, BTN2: weapons</t>
+          <t>Fires when ARC_23 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16946,32 +16942,32 @@
       </c>
       <c r="B251" s="31" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
         <is>
-          <t>ARC_22_FIRST</t>
+          <t>ARC_23_DONE</t>
         </is>
       </c>
       <c r="D251" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E251" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F251" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_23_FIRST</t>
         </is>
       </c>
       <c r="G251" s="33" t="inlineStr">
         <is>
-          <t>ARC_22_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
@@ -16998,7 +16994,7 @@
       </c>
       <c r="N251" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_22 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_23 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
         </is>
       </c>
     </row>
@@ -17010,32 +17006,32 @@
       </c>
       <c r="B252" s="31" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
         <is>
-          <t>ARC_22_DONE</t>
+          <t>ARC_24_FIRST</t>
         </is>
       </c>
       <c r="D252" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E252" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F252" s="33" t="inlineStr">
         <is>
-          <t>ARC_22_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G252" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_24_DONE</t>
         </is>
       </c>
       <c r="H252" s="6" t="inlineStr">
@@ -17062,7 +17058,7 @@
       </c>
       <c r="N252" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_22 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+          <t>Fires when ARC_24 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -17074,32 +17070,32 @@
       </c>
       <c r="B253" s="31" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
         <is>
-          <t>ARC_23_FIRST</t>
+          <t>ARC_24_DONE</t>
         </is>
       </c>
       <c r="D253" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E253" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F253" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_24_FIRST</t>
         </is>
       </c>
       <c r="G253" s="33" t="inlineStr">
         <is>
-          <t>ARC_23_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H253" s="6" t="inlineStr">
@@ -17126,7 +17122,7 @@
       </c>
       <c r="N253" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_23 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_24 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
         </is>
       </c>
     </row>
@@ -17138,32 +17134,32 @@
       </c>
       <c r="B254" s="31" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
         <is>
-          <t>ARC_23_DONE</t>
+          <t>ARC_25_FIRST</t>
         </is>
       </c>
       <c r="D254" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CARNIVAL BARKER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E254" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F254" s="33" t="inlineStr">
         <is>
-          <t>ARC_23_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G254" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_25_DONE</t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr">
@@ -17190,7 +17186,7 @@
       </c>
       <c r="N254" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_23 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
+          <t>Fires when ARC_25 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -17202,32 +17198,32 @@
       </c>
       <c r="B255" s="31" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
         <is>
-          <t>ARC_24_FIRST</t>
+          <t>ARC_25_DONE</t>
         </is>
       </c>
       <c r="D255" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — CARNIVAL BARKER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E255" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F255" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_25_FIRST</t>
         </is>
       </c>
       <c r="G255" s="33" t="inlineStr">
         <is>
-          <t>ARC_24_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr">
@@ -17254,7 +17250,7 @@
       </c>
       <c r="N255" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_24 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_25 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -17266,27 +17262,27 @@
       </c>
       <c r="B256" s="31" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Governor Ceremony</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
         <is>
-          <t>ARC_24_DONE</t>
+          <t>GOV_LVL2_HONOR</t>
         </is>
       </c>
       <c r="D256" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER ARC COMPLETE</t>
+          <t>FIELD CITATION — [COMMANDER_NAME]</t>
         </is>
       </c>
       <c r="E256" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Level-Up</t>
         </is>
       </c>
       <c r="F256" s="33" t="inlineStr">
         <is>
-          <t>ARC_24_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G256" s="33" t="inlineStr">
@@ -17294,15 +17290,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H256" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H256" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I256" s="32" t="inlineStr"/>
-      <c r="J256" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J256" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K256" s="34" t="inlineStr">
@@ -17318,7 +17314,7 @@
       </c>
       <c r="N256" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_24 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires on promote_commander to lvl 2; BTN1: morale+10</t>
         </is>
       </c>
     </row>
@@ -17330,22 +17326,22 @@
       </c>
       <c r="B257" s="31" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Governor Ceremony</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
         <is>
-          <t>ARC_25_FIRST</t>
+          <t>GOV_LVL3_CEREMONY</t>
         </is>
       </c>
       <c r="D257" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARNIVAL BARKER FIRST OBJECTIVE</t>
+          <t>GENERAL [COMMANDER_NAME] — WHITE HOUSE RECOGNITION CEREMONY</t>
         </is>
       </c>
       <c r="E257" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Level-Up</t>
         </is>
       </c>
       <c r="F257" s="33" t="inlineStr">
@@ -17355,18 +17351,22 @@
       </c>
       <c r="G257" s="33" t="inlineStr">
         <is>
-          <t>ARC_25_DONE</t>
-        </is>
-      </c>
-      <c r="H257" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I257" s="32" t="inlineStr"/>
-      <c r="J257" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>GOV_REWARD</t>
+        </is>
+      </c>
+      <c r="H257" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I257" s="32" t="inlineStr">
+        <is>
+          <t>gov_lvl3_ceremony_scene</t>
+        </is>
+      </c>
+      <c r="J257" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
         </is>
       </c>
       <c r="K257" s="34" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="N257" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_25 completes objective 1; BTN1: nothing</t>
+          <t>Fires on promote_commander to lvl 3; BTN1: morale+20; BTN2: → GOV_REWARD</t>
         </is>
       </c>
     </row>
@@ -17394,27 +17394,27 @@
       </c>
       <c r="B258" s="31" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Governor Ceremony</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
         <is>
-          <t>ARC_25_DONE</t>
+          <t>GOV_REWARD</t>
         </is>
       </c>
       <c r="D258" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARNIVAL BARKER ARC COMPLETE</t>
+          <t>GENERAL [COMMANDER_NAME] — THE LINCOLN BEDROOM</t>
         </is>
       </c>
       <c r="E258" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Intimate</t>
         </is>
       </c>
       <c r="F258" s="33" t="inlineStr">
         <is>
-          <t>ARC_25_FIRST</t>
+          <t>GOV_LVL3_CEREMONY BTN2</t>
         </is>
       </c>
       <c r="G258" s="33" t="inlineStr">
@@ -17422,23 +17422,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H258" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I258" s="32" t="inlineStr"/>
-      <c r="J258" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K258" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L258" s="32" t="inlineStr"/>
+      <c r="H258" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I258" s="32" t="inlineStr">
+        <is>
+          <t>gov_reward_scene</t>
+        </is>
+      </c>
+      <c r="J258" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K258" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L258" s="32" t="inlineStr">
+        <is>
+          <t>intimate</t>
+        </is>
+      </c>
       <c r="M258" s="34" t="inlineStr">
         <is>
           <t>0</t>
@@ -17446,262 +17454,210 @@
       </c>
       <c r="N258" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_25 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="30" customHeight="1">
-      <c r="A259" s="31" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B259" s="31" t="inlineStr">
-        <is>
-          <t>Governor Ceremony</t>
-        </is>
-      </c>
-      <c r="C259" s="32" t="inlineStr">
-        <is>
-          <t>GOV_LVL2_HONOR</t>
-        </is>
-      </c>
-      <c r="D259" s="33" t="inlineStr">
-        <is>
-          <t>FIELD CITATION — [COMMANDER_NAME]</t>
-        </is>
-      </c>
-      <c r="E259" s="34" t="inlineStr">
-        <is>
-          <t>Level-Up</t>
-        </is>
-      </c>
-      <c r="F259" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G259" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H259" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I259" s="32" t="inlineStr"/>
-      <c r="J259" s="7" t="inlineStr">
+          <t>Fires from GOV_LVL3_CEREMONY BTN2; BTN1: governor_loyalty +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="8" customHeight="1">
+      <c r="A259" s="9" t="n"/>
+      <c r="B259" s="9" t="n"/>
+      <c r="C259" s="9" t="n"/>
+      <c r="D259" s="9" t="n"/>
+      <c r="E259" s="9" t="n"/>
+      <c r="F259" s="9" t="n"/>
+      <c r="G259" s="9" t="n"/>
+      <c r="H259" s="9" t="n"/>
+      <c r="I259" s="9" t="n"/>
+      <c r="J259" s="9" t="n"/>
+      <c r="K259" s="9" t="n"/>
+      <c r="L259" s="9" t="n"/>
+      <c r="M259" s="9" t="n"/>
+      <c r="N259" s="9" t="n"/>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="51" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B260" s="51" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C260" s="52" t="inlineStr">
+        <is>
+          <t>VP_LEGACY</t>
+        </is>
+      </c>
+      <c r="D260" s="53" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
+        </is>
+      </c>
+      <c r="E260" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
+        </is>
+      </c>
+      <c r="F260" s="53" t="inlineStr">
+        <is>
+          <t>VP_FIRST_MEETING (turn 96+)</t>
+        </is>
+      </c>
+      <c r="G260" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H260" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I260" s="52" t="inlineStr"/>
+      <c r="J260" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K259" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L259" s="32" t="inlineStr"/>
-      <c r="M259" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N259" s="33" t="inlineStr">
-        <is>
-          <t>Fires on promote_commander to lvl 2; BTN1: morale+10</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="30" customHeight="1">
-      <c r="A260" s="31" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B260" s="31" t="inlineStr">
-        <is>
-          <t>Governor Ceremony</t>
-        </is>
-      </c>
-      <c r="C260" s="32" t="inlineStr">
-        <is>
-          <t>GOV_LVL3_CEREMONY</t>
-        </is>
-      </c>
-      <c r="D260" s="33" t="inlineStr">
-        <is>
-          <t>GENERAL [COMMANDER_NAME] — WHITE HOUSE RECOGNITION CEREMONY</t>
-        </is>
-      </c>
-      <c r="E260" s="34" t="inlineStr">
-        <is>
-          <t>Level-Up</t>
-        </is>
-      </c>
-      <c r="F260" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G260" s="33" t="inlineStr">
-        <is>
-          <t>GOV_REWARD</t>
-        </is>
-      </c>
-      <c r="H260" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I260" s="32" t="inlineStr">
-        <is>
-          <t>gov_lvl3_ceremony_scene</t>
-        </is>
-      </c>
-      <c r="J260" s="27" t="inlineStr">
-        <is>
-          <t>Integrated</t>
-        </is>
-      </c>
-      <c r="K260" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L260" s="32" t="inlineStr"/>
-      <c r="M260" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N260" s="33" t="inlineStr">
-        <is>
-          <t>Fires on promote_commander to lvl 3; BTN1: morale+20; BTN2: → GOV_REWARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="30" customHeight="1">
-      <c r="A261" s="31" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B261" s="31" t="inlineStr">
-        <is>
-          <t>Governor Ceremony</t>
-        </is>
-      </c>
-      <c r="C261" s="32" t="inlineStr">
-        <is>
-          <t>GOV_REWARD</t>
-        </is>
-      </c>
-      <c r="D261" s="33" t="inlineStr">
-        <is>
-          <t>GENERAL [COMMANDER_NAME] — THE LINCOLN BEDROOM</t>
-        </is>
-      </c>
-      <c r="E261" s="34" t="inlineStr">
-        <is>
-          <t>Intimate</t>
-        </is>
-      </c>
-      <c r="F261" s="33" t="inlineStr">
-        <is>
-          <t>GOV_LVL3_CEREMONY BTN2</t>
-        </is>
-      </c>
-      <c r="G261" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H261" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I261" s="32" t="inlineStr">
-        <is>
-          <t>gov_reward_scene</t>
-        </is>
-      </c>
-      <c r="J261" s="27" t="inlineStr">
-        <is>
-          <t>Integrated</t>
-        </is>
-      </c>
-      <c r="K261" s="28" t="inlineStr">
+      <c r="K260" s="28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L261" s="32" t="inlineStr">
-        <is>
-          <t>intimate</t>
-        </is>
-      </c>
-      <c r="M261" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N261" s="33" t="inlineStr">
-        <is>
-          <t>Fires from GOV_LVL3_CEREMONY BTN2; BTN1: governor_loyalty +3</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="8" customHeight="1">
-      <c r="A262" s="9" t="n"/>
-      <c r="B262" s="9" t="n"/>
-      <c r="C262" s="9" t="n"/>
-      <c r="D262" s="9" t="n"/>
-      <c r="E262" s="9" t="n"/>
-      <c r="F262" s="9" t="n"/>
-      <c r="G262" s="9" t="n"/>
-      <c r="H262" s="9" t="n"/>
-      <c r="I262" s="9" t="n"/>
-      <c r="J262" s="9" t="n"/>
-      <c r="K262" s="9" t="n"/>
-      <c r="L262" s="9" t="n"/>
-      <c r="M262" s="9" t="n"/>
-      <c r="N262" s="9" t="n"/>
+      <c r="L260" s="52" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M260" s="54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N260" s="53" t="inlineStr">
+        <is>
+          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="8" customHeight="1">
+      <c r="A261" s="9" t="n"/>
+      <c r="B261" s="9" t="n"/>
+      <c r="C261" s="9" t="n"/>
+      <c r="D261" s="9" t="n"/>
+      <c r="E261" s="9" t="n"/>
+      <c r="F261" s="9" t="n"/>
+      <c r="G261" s="9" t="n"/>
+      <c r="H261" s="9" t="n"/>
+      <c r="I261" s="9" t="n"/>
+      <c r="J261" s="9" t="n"/>
+      <c r="K261" s="9" t="n"/>
+      <c r="L261" s="9" t="n"/>
+      <c r="M261" s="9" t="n"/>
+      <c r="N261" s="9" t="n"/>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="72" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B262" s="72" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="C262" s="73" t="inlineStr">
+        <is>
+          <t>WH_SECRET_01</t>
+        </is>
+      </c>
+      <c r="D262" s="74" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F262" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G262" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H262" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I262" s="73" t="inlineStr"/>
+      <c r="J262" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K262" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L262" s="73" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M262" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N262" s="74" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="51" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="B263" s="51" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="C263" s="52" t="inlineStr">
-        <is>
-          <t>VP_LEGACY</t>
-        </is>
-      </c>
-      <c r="D263" s="53" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
-        </is>
-      </c>
-      <c r="E263" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
-        </is>
-      </c>
-      <c r="F263" s="53" t="inlineStr">
-        <is>
-          <t>VP_FIRST_MEETING (turn 96+)</t>
-        </is>
-      </c>
-      <c r="G263" s="53" t="inlineStr">
+      <c r="A263" s="72" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B263" s="72" t="inlineStr">
+        <is>
+          <t>Month 2</t>
+        </is>
+      </c>
+      <c r="C263" s="73" t="inlineStr">
+        <is>
+          <t>WH_SECRET_02</t>
+        </is>
+      </c>
+      <c r="D263" s="74" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F263" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G263" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17711,48 +17667,100 @@
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I263" s="52" t="inlineStr"/>
+      <c r="I263" s="73" t="inlineStr"/>
       <c r="J263" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K263" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L263" s="52" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
-      <c r="M263" s="54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N263" s="53" t="inlineStr">
-        <is>
-          <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="8" customHeight="1">
-      <c r="A264" s="9" t="n"/>
-      <c r="B264" s="9" t="n"/>
-      <c r="C264" s="9" t="n"/>
-      <c r="D264" s="9" t="n"/>
-      <c r="E264" s="9" t="n"/>
-      <c r="F264" s="9" t="n"/>
-      <c r="G264" s="9" t="n"/>
-      <c r="H264" s="9" t="n"/>
-      <c r="I264" s="9" t="n"/>
-      <c r="J264" s="9" t="n"/>
-      <c r="K264" s="9" t="n"/>
-      <c r="L264" s="9" t="n"/>
-      <c r="M264" s="9" t="n"/>
-      <c r="N264" s="9" t="n"/>
+      <c r="K263" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L263" s="73" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M263" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N263" s="74" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="30" customHeight="1">
+      <c r="A264" s="72" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B264" s="72" t="inlineStr">
+        <is>
+          <t>Month 3</t>
+        </is>
+      </c>
+      <c r="C264" s="73" t="inlineStr">
+        <is>
+          <t>WH_SECRET_03</t>
+        </is>
+      </c>
+      <c r="D264" s="74" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F264" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G264" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H264" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I264" s="73" t="inlineStr"/>
+      <c r="J264" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K264" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L264" s="73" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M264" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N264" s="74" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="72" t="inlineStr">
@@ -17762,17 +17770,17 @@
       </c>
       <c r="B265" s="72" t="inlineStr">
         <is>
-          <t>Month 1</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C265" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_01</t>
+          <t>WH_SECRET_04</t>
         </is>
       </c>
       <c r="D265" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
+          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17801,14 +17809,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K265" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K265" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L265" s="73" t="inlineStr">
         <is>
-          <t>sensual option</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="M265" s="75" t="inlineStr">
@@ -17818,7 +17826,7 @@
       </c>
       <c r="N265" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
         </is>
       </c>
     </row>
@@ -17830,17 +17838,17 @@
       </c>
       <c r="B266" s="72" t="inlineStr">
         <is>
-          <t>Month 2</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C266" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_02</t>
+          <t>WH_SECRET_05</t>
         </is>
       </c>
       <c r="D266" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
+          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17886,7 +17894,7 @@
       </c>
       <c r="N266" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
         </is>
       </c>
     </row>
@@ -17898,17 +17906,17 @@
       </c>
       <c r="B267" s="72" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 6</t>
         </is>
       </c>
       <c r="C267" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_03</t>
+          <t>WH_SECRET_06</t>
         </is>
       </c>
       <c r="D267" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
+          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17954,7 +17962,7 @@
       </c>
       <c r="N267" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
         </is>
       </c>
     </row>
@@ -17966,17 +17974,17 @@
       </c>
       <c r="B268" s="72" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C268" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_04</t>
+          <t>WH_SECRET_07</t>
         </is>
       </c>
       <c r="D268" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
+          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -18005,14 +18013,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K268" s="75" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="K268" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="L268" s="73" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>explicit option</t>
         </is>
       </c>
       <c r="M268" s="75" t="inlineStr">
@@ -18022,7 +18030,7 @@
       </c>
       <c r="N268" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
         </is>
       </c>
     </row>
@@ -18034,17 +18042,17 @@
       </c>
       <c r="B269" s="72" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 8</t>
         </is>
       </c>
       <c r="C269" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_05</t>
+          <t>WH_SECRET_08</t>
         </is>
       </c>
       <c r="D269" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
+          <t>WHITE HOUSE SECRET — DIWALI</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -18090,7 +18098,7 @@
       </c>
       <c r="N269" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
         </is>
       </c>
     </row>
@@ -18102,17 +18110,17 @@
       </c>
       <c r="B270" s="72" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 9</t>
         </is>
       </c>
       <c r="C270" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_06</t>
+          <t>WH_SECRET_09</t>
         </is>
       </c>
       <c r="D270" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
+          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -18158,7 +18166,7 @@
       </c>
       <c r="N270" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
         </is>
       </c>
     </row>
@@ -18170,17 +18178,17 @@
       </c>
       <c r="B271" s="72" t="inlineStr">
         <is>
-          <t>Month 7</t>
+          <t>Month 10</t>
         </is>
       </c>
       <c r="C271" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_07</t>
+          <t>WH_SECRET_10</t>
         </is>
       </c>
       <c r="D271" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
+          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -18216,7 +18224,7 @@
       </c>
       <c r="L271" s="73" t="inlineStr">
         <is>
-          <t>explicit option</t>
+          <t>sensual option</t>
         </is>
       </c>
       <c r="M271" s="75" t="inlineStr">
@@ -18226,7 +18234,7 @@
       </c>
       <c r="N271" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
         </is>
       </c>
     </row>
@@ -18238,17 +18246,17 @@
       </c>
       <c r="B272" s="72" t="inlineStr">
         <is>
-          <t>Month 8</t>
+          <t>Month 11</t>
         </is>
       </c>
       <c r="C272" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_08</t>
+          <t>WH_SECRET_11</t>
         </is>
       </c>
       <c r="D272" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — DIWALI</t>
+          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -18294,7 +18302,7 @@
       </c>
       <c r="N272" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
         </is>
       </c>
     </row>
@@ -18306,17 +18314,17 @@
       </c>
       <c r="B273" s="72" t="inlineStr">
         <is>
-          <t>Month 9</t>
+          <t>Month 12</t>
         </is>
       </c>
       <c r="C273" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_09</t>
+          <t>WH_SECRET_12</t>
         </is>
       </c>
       <c r="D273" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
+          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -18345,14 +18353,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K273" s="75" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="K273" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="L273" s="73" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>sensual option</t>
         </is>
       </c>
       <c r="M273" s="75" t="inlineStr">
@@ -18362,229 +18370,217 @@
       </c>
       <c r="N273" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="30" customHeight="1">
-      <c r="A274" s="72" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B274" s="72" t="inlineStr">
-        <is>
-          <t>Month 10</t>
-        </is>
-      </c>
-      <c r="C274" s="73" t="inlineStr">
-        <is>
-          <t>WH_SECRET_10</t>
-        </is>
-      </c>
-      <c r="D274" s="74" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
-        </is>
-      </c>
-      <c r="E274" s="5" t="inlineStr">
+          <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="8" customHeight="1">
+      <c r="A274" s="9" t="n"/>
+      <c r="B274" s="9" t="n"/>
+      <c r="C274" s="9" t="n"/>
+      <c r="D274" s="9" t="n"/>
+      <c r="E274" s="9" t="n"/>
+      <c r="F274" s="9" t="n"/>
+      <c r="G274" s="9" t="n"/>
+      <c r="H274" s="9" t="n"/>
+      <c r="I274" s="9" t="n"/>
+      <c r="J274" s="9" t="n"/>
+      <c r="K274" s="9" t="n"/>
+      <c r="L274" s="9" t="n"/>
+      <c r="M274" s="9" t="n"/>
+      <c r="N274" s="9" t="n"/>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="76" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B275" s="76" t="inlineStr">
+        <is>
+          <t>Jade Turkey Arc</t>
+        </is>
+      </c>
+      <c r="C275" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_SUMMON</t>
+        </is>
+      </c>
+      <c r="D275" s="78" t="inlineStr">
+        <is>
+          <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F274" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G274" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H274" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I274" s="73" t="inlineStr"/>
-      <c r="J274" s="7" t="inlineStr">
+      <c r="F275" s="78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G275" s="78" t="inlineStr">
+        <is>
+          <t>CHALCH_Q1</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I275" s="77" t="inlineStr"/>
+      <c r="J275" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K274" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L274" s="73" t="inlineStr">
-        <is>
-          <t>sensual option</t>
-        </is>
-      </c>
-      <c r="M274" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N274" s="74" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="72" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B275" s="72" t="inlineStr">
-        <is>
-          <t>Month 11</t>
-        </is>
-      </c>
-      <c r="C275" s="73" t="inlineStr">
-        <is>
-          <t>WH_SECRET_11</t>
-        </is>
-      </c>
-      <c r="D275" s="74" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F275" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G275" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I275" s="73" t="inlineStr"/>
-      <c r="J275" s="7" t="inlineStr">
+      <c r="K275" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L275" s="77" t="inlineStr"/>
+      <c r="M275" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N275" s="78" t="inlineStr">
+        <is>
+          <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="76" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B276" s="76" t="inlineStr">
+        <is>
+          <t>Jade Turkey Arc</t>
+        </is>
+      </c>
+      <c r="C276" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_Q1</t>
+        </is>
+      </c>
+      <c r="D276" s="78" t="inlineStr">
+        <is>
+          <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
+        </is>
+      </c>
+      <c r="E276" s="79" t="inlineStr">
+        <is>
+          <t>Quest 1</t>
+        </is>
+      </c>
+      <c r="F276" s="78" t="inlineStr">
+        <is>
+          <t>CHALCH_SUMMON</t>
+        </is>
+      </c>
+      <c r="G276" s="78" t="inlineStr">
+        <is>
+          <t>CHALCH_Q2</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I276" s="77" t="inlineStr"/>
+      <c r="J276" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K275" s="75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L275" s="73" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M275" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N275" s="74" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="30" customHeight="1">
-      <c r="A276" s="72" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B276" s="72" t="inlineStr">
-        <is>
-          <t>Month 12</t>
-        </is>
-      </c>
-      <c r="C276" s="73" t="inlineStr">
-        <is>
-          <t>WH_SECRET_12</t>
-        </is>
-      </c>
-      <c r="D276" s="74" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
-        </is>
-      </c>
-      <c r="E276" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F276" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G276" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H276" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I276" s="73" t="inlineStr"/>
-      <c r="J276" s="7" t="inlineStr">
+      <c r="K276" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L276" s="77" t="inlineStr"/>
+      <c r="M276" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N276" s="78" t="inlineStr">
+        <is>
+          <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="30" customHeight="1">
+      <c r="A277" s="76" t="inlineStr">
+        <is>
+          <t>Chalchiuhtotolin</t>
+        </is>
+      </c>
+      <c r="B277" s="76" t="inlineStr">
+        <is>
+          <t>Jade Turkey Arc</t>
+        </is>
+      </c>
+      <c r="C277" s="77" t="inlineStr">
+        <is>
+          <t>CHALCH_Q2</t>
+        </is>
+      </c>
+      <c r="D277" s="78" t="inlineStr">
+        <is>
+          <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
+        </is>
+      </c>
+      <c r="E277" s="79" t="inlineStr">
+        <is>
+          <t>Quest 2</t>
+        </is>
+      </c>
+      <c r="F277" s="78" t="inlineStr">
+        <is>
+          <t>CHALCH_Q1</t>
+        </is>
+      </c>
+      <c r="G277" s="78" t="inlineStr">
+        <is>
+          <t>CHALCH_Q3</t>
+        </is>
+      </c>
+      <c r="H277" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I277" s="77" t="inlineStr"/>
+      <c r="J277" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K276" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L276" s="73" t="inlineStr">
-        <is>
-          <t>sensual option</t>
-        </is>
-      </c>
-      <c r="M276" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N276" s="74" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="8" customHeight="1">
-      <c r="A277" s="9" t="n"/>
-      <c r="B277" s="9" t="n"/>
-      <c r="C277" s="9" t="n"/>
-      <c r="D277" s="9" t="n"/>
-      <c r="E277" s="9" t="n"/>
-      <c r="F277" s="9" t="n"/>
-      <c r="G277" s="9" t="n"/>
-      <c r="H277" s="9" t="n"/>
-      <c r="I277" s="9" t="n"/>
-      <c r="J277" s="9" t="n"/>
-      <c r="K277" s="9" t="n"/>
-      <c r="L277" s="9" t="n"/>
-      <c r="M277" s="9" t="n"/>
-      <c r="N277" s="9" t="n"/>
+      <c r="K277" s="79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L277" s="77" t="inlineStr"/>
+      <c r="M277" s="79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N277" s="78" t="inlineStr">
+        <is>
+          <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="30" customHeight="1">
       <c r="A278" s="76" t="inlineStr">
@@ -18599,27 +18595,27 @@
       </c>
       <c r="C278" s="77" t="inlineStr">
         <is>
-          <t>CHALCH_SUMMON</t>
+          <t>CHALCH_Q3</t>
         </is>
       </c>
       <c r="D278" s="78" t="inlineStr">
         <is>
-          <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
-        </is>
-      </c>
-      <c r="E278" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
+        </is>
+      </c>
+      <c r="E278" s="79" t="inlineStr">
+        <is>
+          <t>Quest 3</t>
         </is>
       </c>
       <c r="F278" s="78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CHALCH_Q2</t>
         </is>
       </c>
       <c r="G278" s="78" t="inlineStr">
         <is>
-          <t>CHALCH_Q1</t>
+          <t>CHALCH_AGREE</t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr">
@@ -18646,7 +18642,7 @@
       </c>
       <c r="N278" s="78" t="inlineStr">
         <is>
-          <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
+          <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
         </is>
       </c>
     </row>
@@ -18663,27 +18659,27 @@
       </c>
       <c r="C279" s="77" t="inlineStr">
         <is>
-          <t>CHALCH_Q1</t>
+          <t>CHALCH_AGREE</t>
         </is>
       </c>
       <c r="D279" s="78" t="inlineStr">
         <is>
-          <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
+          <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
         </is>
       </c>
       <c r="E279" s="79" t="inlineStr">
         <is>
-          <t>Quest 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F279" s="78" t="inlineStr">
         <is>
-          <t>CHALCH_SUMMON</t>
+          <t>CHALCH_Q3</t>
         </is>
       </c>
       <c r="G279" s="78" t="inlineStr">
         <is>
-          <t>CHALCH_Q2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H279" s="6" t="inlineStr">
@@ -18710,217 +18706,229 @@
       </c>
       <c r="N279" s="78" t="inlineStr">
         <is>
-          <t>Fires when chalch_summoned + 3+ farms; reward: +30 food</t>
-        </is>
-      </c>
-    </row>
-    <row r="280" ht="30" customHeight="1">
-      <c r="A280" s="76" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B280" s="76" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C280" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q2</t>
-        </is>
-      </c>
-      <c r="D280" s="78" t="inlineStr">
-        <is>
-          <t>THE JADE TURKEY DEMANDS A STOCKPILE WORTHY OF ITS REGARD</t>
-        </is>
-      </c>
-      <c r="E280" s="79" t="inlineStr">
-        <is>
-          <t>Quest 2</t>
-        </is>
-      </c>
-      <c r="F280" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_Q1</t>
-        </is>
-      </c>
-      <c r="G280" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_Q3</t>
-        </is>
-      </c>
-      <c r="H280" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I280" s="77" t="inlineStr"/>
-      <c r="J280" s="7" t="inlineStr">
+          <t>Fires when chalch_q3_done; BTN1: +100 food; closes the arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="8" customHeight="1">
+      <c r="A280" s="9" t="n"/>
+      <c r="B280" s="9" t="n"/>
+      <c r="C280" s="9" t="n"/>
+      <c r="D280" s="9" t="n"/>
+      <c r="E280" s="9" t="n"/>
+      <c r="F280" s="9" t="n"/>
+      <c r="G280" s="9" t="n"/>
+      <c r="H280" s="9" t="n"/>
+      <c r="I280" s="9" t="n"/>
+      <c r="J280" s="9" t="n"/>
+      <c r="K280" s="9" t="n"/>
+      <c r="L280" s="9" t="n"/>
+      <c r="M280" s="9" t="n"/>
+      <c r="N280" s="9" t="n"/>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="80" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B281" s="80" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C281" s="81" t="inlineStr">
+        <is>
+          <t>UALANI_DOCK_01</t>
+        </is>
+      </c>
+      <c r="D281" s="82" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F281" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G281" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H281" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I281" s="81" t="inlineStr"/>
+      <c r="J281" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K280" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L280" s="77" t="inlineStr"/>
-      <c r="M280" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N280" s="78" t="inlineStr">
-        <is>
-          <t>Fires when chalch_q1_done + TotalFood &gt;= 150; reward: +50 food</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="30" customHeight="1">
-      <c r="A281" s="76" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B281" s="76" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C281" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q3</t>
-        </is>
-      </c>
-      <c r="D281" s="78" t="inlineStr">
-        <is>
-          <t>THE JADE TURKEY DEMANDS A NATION OF FARMS</t>
-        </is>
-      </c>
-      <c r="E281" s="79" t="inlineStr">
-        <is>
-          <t>Quest 3</t>
-        </is>
-      </c>
-      <c r="F281" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_Q2</t>
-        </is>
-      </c>
-      <c r="G281" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_AGREE</t>
-        </is>
-      </c>
-      <c r="H281" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I281" s="77" t="inlineStr"/>
-      <c r="J281" s="7" t="inlineStr">
+      <c r="K281" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L281" s="81" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M281" s="84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N281" s="82" t="inlineStr">
+        <is>
+          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="30" customHeight="1">
+      <c r="A282" s="80" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B282" s="80" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C282" s="81" t="inlineStr">
+        <is>
+          <t>UALANI_FARM_01</t>
+        </is>
+      </c>
+      <c r="D282" s="82" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F282" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G282" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H282" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I282" s="81" t="inlineStr"/>
+      <c r="J282" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K281" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L281" s="77" t="inlineStr"/>
-      <c r="M281" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N281" s="78" t="inlineStr">
-        <is>
-          <t>Fires when chalch_q2_done + 5+ farms; reward: +40 food</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="30" customHeight="1">
-      <c r="A282" s="76" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B282" s="76" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C282" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_AGREE</t>
-        </is>
-      </c>
-      <c r="D282" s="78" t="inlineStr">
-        <is>
-          <t>CHALCHIUHTOTOLIN ACCEPTS THE PACT — REPUBLIC EARNS TURKEY GOD'S PROTECTION</t>
-        </is>
-      </c>
-      <c r="E282" s="79" t="inlineStr">
-        <is>
-          <t>Resolution</t>
-        </is>
-      </c>
-      <c r="F282" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_Q3</t>
-        </is>
-      </c>
-      <c r="G282" s="78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H282" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I282" s="77" t="inlineStr"/>
-      <c r="J282" s="7" t="inlineStr">
+      <c r="K282" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L282" s="81" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M282" s="84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N282" s="82" t="inlineStr">
+        <is>
+          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="30" customHeight="1">
+      <c r="A283" s="80" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="B283" s="80" t="inlineStr">
+        <is>
+          <t>Ualani Expansion</t>
+        </is>
+      </c>
+      <c r="C283" s="81" t="inlineStr">
+        <is>
+          <t>UALANI_BARRACKS_01</t>
+        </is>
+      </c>
+      <c r="D283" s="82" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F283" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G283" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H283" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I283" s="81" t="inlineStr"/>
+      <c r="J283" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K282" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L282" s="77" t="inlineStr"/>
-      <c r="M282" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N282" s="78" t="inlineStr">
-        <is>
-          <t>Fires when chalch_q3_done; BTN1: +100 food; closes the arc</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="8" customHeight="1">
-      <c r="A283" s="9" t="n"/>
-      <c r="B283" s="9" t="n"/>
-      <c r="C283" s="9" t="n"/>
-      <c r="D283" s="9" t="n"/>
-      <c r="E283" s="9" t="n"/>
-      <c r="F283" s="9" t="n"/>
-      <c r="G283" s="9" t="n"/>
-      <c r="H283" s="9" t="n"/>
-      <c r="I283" s="9" t="n"/>
-      <c r="J283" s="9" t="n"/>
-      <c r="K283" s="9" t="n"/>
-      <c r="L283" s="9" t="n"/>
-      <c r="M283" s="9" t="n"/>
-      <c r="N283" s="9" t="n"/>
+      <c r="K283" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L283" s="81" t="inlineStr">
+        <is>
+          <t>explicit option</t>
+        </is>
+      </c>
+      <c r="M283" s="84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N283" s="82" t="inlineStr">
+        <is>
+          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="30" customHeight="1">
       <c r="A284" s="80" t="inlineStr">
@@ -18935,12 +18943,12 @@
       </c>
       <c r="C284" s="81" t="inlineStr">
         <is>
-          <t>UALANI_DOCK_01</t>
+          <t>UALANI_COURTHOUSE_01</t>
         </is>
       </c>
       <c r="D284" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SURVEYS THE HARBOR AT [TILE_NAME]  ← IDEA</t>
+          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
@@ -18986,7 +18994,7 @@
       </c>
       <c r="N284" s="82" t="inlineStr">
         <is>
-          <t>Ualani at tile with enabled Dock; follows UALANI_FORGE_01 pattern</t>
+          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
         </is>
       </c>
     </row>
@@ -18998,17 +19006,17 @@
       </c>
       <c r="B285" s="80" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C285" s="81" t="inlineStr">
         <is>
-          <t>UALANI_FARM_01</t>
+          <t>CL_WASHINGTON_01</t>
         </is>
       </c>
       <c r="D285" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS THE FARMLANDS AT [TILE_NAME]  ← IDEA</t>
+          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
@@ -19037,24 +19045,20 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K285" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L285" s="81" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
+      <c r="K285" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L285" s="81" t="inlineStr"/>
       <c r="M285" s="84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N285" s="82" t="inlineStr">
         <is>
-          <t>Ualani at Farm tile; variant of HARVEST_VISIT_01 but Ualani-led</t>
+          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
         </is>
       </c>
     </row>
@@ -19066,17 +19070,17 @@
       </c>
       <c r="B286" s="80" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C286" s="81" t="inlineStr">
         <is>
-          <t>UALANI_BARRACKS_01</t>
+          <t>CL_VALLEY_FORGE_01</t>
         </is>
       </c>
       <c r="D286" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS REGIMENTAL REVIEW AT [TILE_NAME]  ← IDEA</t>
+          <t>VALLEY FORGE SECURED  ← IDEA</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
@@ -19105,24 +19109,20 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K286" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L286" s="81" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
+      <c r="K286" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L286" s="81" t="inlineStr"/>
       <c r="M286" s="84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N286" s="82" t="inlineStr">
         <is>
-          <t>Ualani at tile with Barracks; army strength / loyalty focus</t>
+          <t>Tile 1; historically significant; would fire on liberation</t>
         </is>
       </c>
     </row>
@@ -19134,17 +19134,17 @@
       </c>
       <c r="B287" s="80" t="inlineStr">
         <is>
-          <t>Ualani Expansion</t>
+          <t>More City Events</t>
         </is>
       </c>
       <c r="C287" s="81" t="inlineStr">
         <is>
-          <t>UALANI_COURTHOUSE_01</t>
+          <t>CX_NYC_01</t>
         </is>
       </c>
       <c r="D287" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE HOLDS TOWN HALL AT [TILE_NAME]  ← IDEA</t>
+          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
@@ -19173,24 +19173,20 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K287" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L287" s="81" t="inlineStr">
-        <is>
-          <t>explicit option</t>
-        </is>
-      </c>
+      <c r="K287" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L287" s="81" t="inlineStr"/>
       <c r="M287" s="84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N287" s="82" t="inlineStr">
         <is>
-          <t>Ualani at Courthouse tile; complement to UALANI_DIGNITARY but different trigger (no moralDecay gate)</t>
+          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
         </is>
       </c>
     </row>
@@ -19202,17 +19198,17 @@
       </c>
       <c r="B288" s="80" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Espionage Events</t>
         </is>
       </c>
       <c r="C288" s="81" t="inlineStr">
         <is>
-          <t>CL_WASHINGTON_01</t>
+          <t>ESPIONAGE_DISCOVERY_01</t>
         </is>
       </c>
       <c r="D288" s="82" t="inlineStr">
         <is>
-          <t>WASHINGTON DC LIBERATED  ← IDEA</t>
+          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
@@ -19254,7 +19250,7 @@
       </c>
       <c r="N288" s="82" t="inlineStr">
         <is>
-          <t>Would fire when tile 188 is recaptured; natural counterpart to CX_001</t>
+          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
         </is>
       </c>
     </row>
@@ -19266,32 +19262,32 @@
       </c>
       <c r="B289" s="80" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Commander Expansion</t>
         </is>
       </c>
       <c r="C289" s="81" t="inlineStr">
         <is>
-          <t>CL_VALLEY_FORGE_01</t>
+          <t>CMD_OBJECTIVE_2</t>
         </is>
       </c>
       <c r="D289" s="82" t="inlineStr">
         <is>
-          <t>VALLEY FORGE SECURED  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E289" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
+        </is>
+      </c>
+      <c r="E289" s="22" t="inlineStr">
+        <is>
+          <t>Followup</t>
         </is>
       </c>
       <c r="F289" s="82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CMD_OBJECTIVE_1</t>
         </is>
       </c>
       <c r="G289" s="82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ CMD_OBJECTIVE_3?</t>
         </is>
       </c>
       <c r="H289" s="83" t="inlineStr">
@@ -19318,7 +19314,7 @@
       </c>
       <c r="N289" s="82" t="inlineStr">
         <is>
-          <t>Tile 1; historically significant; would fire on liberation</t>
+          <t>Extend the commander arc beyond first objective</t>
         </is>
       </c>
     </row>
@@ -19330,17 +19326,17 @@
       </c>
       <c r="B290" s="80" t="inlineStr">
         <is>
-          <t>More City Events</t>
+          <t>Seasonal Events</t>
         </is>
       </c>
       <c r="C290" s="81" t="inlineStr">
         <is>
-          <t>CX_NYC_01</t>
+          <t>WINTER_SIEGE_01</t>
         </is>
       </c>
       <c r="D290" s="82" t="inlineStr">
         <is>
-          <t>NEW YORK CITY FALLS AGAIN  ← IDEA</t>
+          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
@@ -19382,7 +19378,7 @@
       </c>
       <c r="N290" s="82" t="inlineStr">
         <is>
-          <t>Would fire if NYC is re-taken after CL_001; repeatable pair</t>
+          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
         </is>
       </c>
     </row>
@@ -19394,17 +19390,17 @@
       </c>
       <c r="B291" s="80" t="inlineStr">
         <is>
-          <t>Espionage Events</t>
+          <t>Seasonal Events</t>
         </is>
       </c>
       <c r="C291" s="81" t="inlineStr">
         <is>
-          <t>ESPIONAGE_DISCOVERY_01</t>
+          <t>SPRING_OFFENSIVE_01</t>
         </is>
       </c>
       <c r="D291" s="82" t="inlineStr">
         <is>
-          <t>SPY NETWORK DISCOVERED AT [TILE_NAME]  ← IDEA</t>
+          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
@@ -19446,103 +19442,55 @@
       </c>
       <c r="N291" s="82" t="inlineStr">
         <is>
-          <t>Would fire when espionageActive + enemy army arrives; uses existing espionage vars</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="30" customHeight="1">
-      <c r="A292" s="80" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B292" s="80" t="inlineStr">
-        <is>
-          <t>Commander Expansion</t>
-        </is>
-      </c>
-      <c r="C292" s="81" t="inlineStr">
-        <is>
-          <t>CMD_OBJECTIVE_2</t>
-        </is>
-      </c>
-      <c r="D292" s="82" t="inlineStr">
-        <is>
-          <t>A COMMANDER'S SECOND TASK  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E292" s="22" t="inlineStr">
-        <is>
-          <t>Followup</t>
-        </is>
-      </c>
-      <c r="F292" s="82" t="inlineStr">
-        <is>
-          <t>CMD_OBJECTIVE_1</t>
-        </is>
-      </c>
-      <c r="G292" s="82" t="inlineStr">
-        <is>
-          <t>→ CMD_OBJECTIVE_3?</t>
-        </is>
-      </c>
-      <c r="H292" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I292" s="81" t="inlineStr"/>
-      <c r="J292" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K292" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L292" s="81" t="inlineStr"/>
-      <c r="M292" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N292" s="82" t="inlineStr">
-        <is>
-          <t>Extend the commander arc beyond first objective</t>
-        </is>
-      </c>
+          <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="8" customHeight="1">
+      <c r="A292" s="9" t="n"/>
+      <c r="B292" s="9" t="n"/>
+      <c r="C292" s="9" t="n"/>
+      <c r="D292" s="9" t="n"/>
+      <c r="E292" s="9" t="n"/>
+      <c r="F292" s="9" t="n"/>
+      <c r="G292" s="9" t="n"/>
+      <c r="H292" s="9" t="n"/>
+      <c r="I292" s="9" t="n"/>
+      <c r="J292" s="9" t="n"/>
+      <c r="K292" s="9" t="n"/>
+      <c r="L292" s="9" t="n"/>
+      <c r="M292" s="9" t="n"/>
+      <c r="N292" s="9" t="n"/>
     </row>
     <row r="293" ht="30" customHeight="1">
       <c r="A293" s="80" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Commander</t>
         </is>
       </c>
       <c r="B293" s="80" t="inlineStr">
         <is>
-          <t>Seasonal Events</t>
+          <t>Commander Arc</t>
         </is>
       </c>
       <c r="C293" s="81" t="inlineStr">
         <is>
-          <t>WINTER_SIEGE_01</t>
+          <t>CMD_THANKS_INTIMATE</t>
         </is>
       </c>
       <c r="D293" s="82" t="inlineStr">
         <is>
-          <t>VALLEY FORGE CONDITIONS: ARMY SUFFERING IN THE FIELD  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E293" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
+          <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMM... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E293" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
         </is>
       </c>
       <c r="F293" s="82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CMD_THANKS (intimate choice)</t>
         </is>
       </c>
       <c r="G293" s="82" t="inlineStr">
@@ -19556,9 +19504,9 @@
         </is>
       </c>
       <c r="I293" s="81" t="inlineStr"/>
-      <c r="J293" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J293" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K293" s="84" t="inlineStr">
@@ -19574,269 +19522,269 @@
       </c>
       <c r="N293" s="82" t="inlineStr">
         <is>
-          <t>Generic winter hardship event; non-Ualani; uses winterScore + month check</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="30" customHeight="1">
-      <c r="A294" s="80" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="B294" s="80" t="inlineStr">
-        <is>
-          <t>Seasonal Events</t>
-        </is>
-      </c>
-      <c r="C294" s="81" t="inlineStr">
-        <is>
-          <t>SPRING_OFFENSIVE_01</t>
-        </is>
-      </c>
-      <c r="D294" s="82" t="inlineStr">
-        <is>
-          <t>THE THAW: CROWN FORCES RESUME OFFENSIVE OPERATIONS  ← IDEA</t>
-        </is>
-      </c>
-      <c r="E294" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F294" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G294" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H294" s="83" t="inlineStr">
+          <t>Stub — author intimate version of CMD_THANKS. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="8" customHeight="1">
+      <c r="A294" s="9" t="n"/>
+      <c r="B294" s="9" t="n"/>
+      <c r="C294" s="9" t="n"/>
+      <c r="D294" s="9" t="n"/>
+      <c r="E294" s="9" t="n"/>
+      <c r="F294" s="9" t="n"/>
+      <c r="G294" s="9" t="n"/>
+      <c r="H294" s="9" t="n"/>
+      <c r="I294" s="9" t="n"/>
+      <c r="J294" s="9" t="n"/>
+      <c r="K294" s="9" t="n"/>
+      <c r="L294" s="9" t="n"/>
+      <c r="M294" s="9" t="n"/>
+      <c r="N294" s="9" t="n"/>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="80" t="inlineStr">
+        <is>
+          <t>Fort Chain</t>
+        </is>
+      </c>
+      <c r="B295" s="80" t="inlineStr">
+        <is>
+          <t>Fort Disrepair</t>
+        </is>
+      </c>
+      <c r="C295" s="81" t="inlineStr">
+        <is>
+          <t>FORT_005_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D295" s="82" t="inlineStr">
+        <is>
+          <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME] — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E295" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F295" s="82" t="inlineStr">
+        <is>
+          <t>FORT_005 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G295" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H295" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I294" s="81" t="inlineStr"/>
-      <c r="J294" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K294" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L294" s="81" t="inlineStr"/>
-      <c r="M294" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N294" s="82" t="inlineStr">
-        <is>
-          <t>Month 3-4; UK neighbor + player army present; tactical pressure event</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="8" customHeight="1">
-      <c r="A295" s="9" t="n"/>
-      <c r="B295" s="9" t="n"/>
-      <c r="C295" s="9" t="n"/>
-      <c r="D295" s="9" t="n"/>
-      <c r="E295" s="9" t="n"/>
-      <c r="F295" s="9" t="n"/>
-      <c r="G295" s="9" t="n"/>
-      <c r="H295" s="9" t="n"/>
-      <c r="I295" s="9" t="n"/>
-      <c r="J295" s="9" t="n"/>
-      <c r="K295" s="9" t="n"/>
-      <c r="L295" s="9" t="n"/>
-      <c r="M295" s="9" t="n"/>
-      <c r="N295" s="9" t="n"/>
-    </row>
-    <row r="296" ht="30" customHeight="1">
-      <c r="A296" s="80" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B296" s="80" t="inlineStr">
-        <is>
-          <t>Commander Arc</t>
-        </is>
-      </c>
-      <c r="C296" s="81" t="inlineStr">
-        <is>
-          <t>CMD_THANKS_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D296" s="82" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE DELIVERS PERSONAL THANKS TO [COMM... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E296" s="84" t="inlineStr">
+      <c r="I295" s="81" t="inlineStr"/>
+      <c r="J295" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K295" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L295" s="81" t="inlineStr"/>
+      <c r="M295" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N295" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of FORT_005. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="8" customHeight="1">
+      <c r="A296" s="9" t="n"/>
+      <c r="B296" s="9" t="n"/>
+      <c r="C296" s="9" t="n"/>
+      <c r="D296" s="9" t="n"/>
+      <c r="E296" s="9" t="n"/>
+      <c r="F296" s="9" t="n"/>
+      <c r="G296" s="9" t="n"/>
+      <c r="H296" s="9" t="n"/>
+      <c r="I296" s="9" t="n"/>
+      <c r="J296" s="9" t="n"/>
+      <c r="K296" s="9" t="n"/>
+      <c r="L296" s="9" t="n"/>
+      <c r="M296" s="9" t="n"/>
+      <c r="N296" s="9" t="n"/>
+    </row>
+    <row r="297" ht="30" customHeight="1">
+      <c r="A297" s="80" t="inlineStr">
+        <is>
+          <t>Collapse</t>
+        </is>
+      </c>
+      <c r="B297" s="80" t="inlineStr">
+        <is>
+          <t>Republic Falls</t>
+        </is>
+      </c>
+      <c r="C297" s="81" t="inlineStr">
+        <is>
+          <t>COLLAPSE_02_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D297" s="82" t="inlineStr">
+        <is>
+          <t>WASHINGTON STANDS ALONE — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E297" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F296" s="82" t="inlineStr">
-        <is>
-          <t>CMD_THANKS (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G296" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H296" s="83" t="inlineStr">
+      <c r="F297" s="82" t="inlineStr">
+        <is>
+          <t>COLLAPSE_02 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G297" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H297" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I296" s="81" t="inlineStr"/>
-      <c r="J296" s="70" t="inlineStr">
+      <c r="I297" s="81" t="inlineStr"/>
+      <c r="J297" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K296" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L296" s="81" t="inlineStr"/>
-      <c r="M296" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N296" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CMD_THANKS. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="8" customHeight="1">
-      <c r="A297" s="9" t="n"/>
-      <c r="B297" s="9" t="n"/>
-      <c r="C297" s="9" t="n"/>
-      <c r="D297" s="9" t="n"/>
-      <c r="E297" s="9" t="n"/>
-      <c r="F297" s="9" t="n"/>
-      <c r="G297" s="9" t="n"/>
-      <c r="H297" s="9" t="n"/>
-      <c r="I297" s="9" t="n"/>
-      <c r="J297" s="9" t="n"/>
-      <c r="K297" s="9" t="n"/>
-      <c r="L297" s="9" t="n"/>
-      <c r="M297" s="9" t="n"/>
-      <c r="N297" s="9" t="n"/>
-    </row>
-    <row r="298" ht="30" customHeight="1">
-      <c r="A298" s="80" t="inlineStr">
-        <is>
-          <t>Fort Chain</t>
-        </is>
-      </c>
-      <c r="B298" s="80" t="inlineStr">
-        <is>
-          <t>Fort Disrepair</t>
-        </is>
-      </c>
-      <c r="C298" s="81" t="inlineStr">
-        <is>
-          <t>FORT_005_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D298" s="82" t="inlineStr">
-        <is>
-          <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME] — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E298" s="84" t="inlineStr">
+      <c r="K297" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L297" s="81" t="inlineStr"/>
+      <c r="M297" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N297" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of COLLAPSE_02. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="8" customHeight="1">
+      <c r="A298" s="9" t="n"/>
+      <c r="B298" s="9" t="n"/>
+      <c r="C298" s="9" t="n"/>
+      <c r="D298" s="9" t="n"/>
+      <c r="E298" s="9" t="n"/>
+      <c r="F298" s="9" t="n"/>
+      <c r="G298" s="9" t="n"/>
+      <c r="H298" s="9" t="n"/>
+      <c r="I298" s="9" t="n"/>
+      <c r="J298" s="9" t="n"/>
+      <c r="K298" s="9" t="n"/>
+      <c r="L298" s="9" t="n"/>
+      <c r="M298" s="9" t="n"/>
+      <c r="N298" s="9" t="n"/>
+    </row>
+    <row r="299" ht="30" customHeight="1">
+      <c r="A299" s="80" t="inlineStr">
+        <is>
+          <t>Tile Crisis</t>
+        </is>
+      </c>
+      <c r="B299" s="80" t="inlineStr">
+        <is>
+          <t>Harvest Crisis</t>
+        </is>
+      </c>
+      <c r="C299" s="81" t="inlineStr">
+        <is>
+          <t>HARVEST_VISIT_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D299" s="82" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE SAVES THE HARVEST — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E299" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F298" s="82" t="inlineStr">
-        <is>
-          <t>FORT_005 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G298" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H298" s="83" t="inlineStr">
+      <c r="F299" s="82" t="inlineStr">
+        <is>
+          <t>HARVEST_VISIT_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G299" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H299" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I298" s="81" t="inlineStr"/>
-      <c r="J298" s="70" t="inlineStr">
+      <c r="I299" s="81" t="inlineStr"/>
+      <c r="J299" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K298" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L298" s="81" t="inlineStr"/>
-      <c r="M298" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N298" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of FORT_005. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="8" customHeight="1">
-      <c r="A299" s="9" t="n"/>
-      <c r="B299" s="9" t="n"/>
-      <c r="C299" s="9" t="n"/>
-      <c r="D299" s="9" t="n"/>
-      <c r="E299" s="9" t="n"/>
-      <c r="F299" s="9" t="n"/>
-      <c r="G299" s="9" t="n"/>
-      <c r="H299" s="9" t="n"/>
-      <c r="I299" s="9" t="n"/>
-      <c r="J299" s="9" t="n"/>
-      <c r="K299" s="9" t="n"/>
-      <c r="L299" s="9" t="n"/>
-      <c r="M299" s="9" t="n"/>
-      <c r="N299" s="9" t="n"/>
+      <c r="K299" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L299" s="81" t="inlineStr"/>
+      <c r="M299" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N299" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of HARVEST_VISIT_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="30" customHeight="1">
       <c r="A300" s="80" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Tile Crisis</t>
         </is>
       </c>
       <c r="B300" s="80" t="inlineStr">
         <is>
-          <t>Republic Falls</t>
+          <t>Election Arc</t>
         </is>
       </c>
       <c r="C300" s="81" t="inlineStr">
         <is>
-          <t>COLLAPSE_02_INTIMATE</t>
+          <t>STUMP_SPEECH_01_INTIMATE</t>
         </is>
       </c>
       <c r="D300" s="82" t="inlineStr">
         <is>
-          <t>WASHINGTON STANDS ALONE — BY MORNING</t>
+          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — ... — BY MORNING</t>
         </is>
       </c>
       <c r="E300" s="84" t="inlineStr">
@@ -19846,7 +19794,7 @@
       </c>
       <c r="F300" s="82" t="inlineStr">
         <is>
-          <t>COLLAPSE_02 (intimate choice)</t>
+          <t>STUMP_SPEECH_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G300" s="82" t="inlineStr">
@@ -19878,7 +19826,7 @@
       </c>
       <c r="N300" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of COLLAPSE_02. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of STUMP_SPEECH_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -19901,22 +19849,22 @@
     <row r="302" ht="30" customHeight="1">
       <c r="A302" s="80" t="inlineStr">
         <is>
-          <t>Tile Crisis</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B302" s="80" t="inlineStr">
         <is>
-          <t>Harvest Crisis</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C302" s="81" t="inlineStr">
         <is>
-          <t>HARVEST_VISIT_01_INTIMATE</t>
+          <t>VP_DOUBT_INTIMATE</t>
         </is>
       </c>
       <c r="D302" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SAVES THE HARVEST — BY MORNING</t>
+          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QU... — BY MORNING</t>
         </is>
       </c>
       <c r="E302" s="84" t="inlineStr">
@@ -19926,7 +19874,7 @@
       </c>
       <c r="F302" s="82" t="inlineStr">
         <is>
-          <t>HARVEST_VISIT_01 (intimate choice)</t>
+          <t>VP_DOUBT (intimate choice)</t>
         </is>
       </c>
       <c r="G302" s="82" t="inlineStr">
@@ -19958,29 +19906,29 @@
       </c>
       <c r="N302" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of HARVEST_VISIT_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of VP_DOUBT. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1">
       <c r="A303" s="80" t="inlineStr">
         <is>
-          <t>Tile Crisis</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="B303" s="80" t="inlineStr">
         <is>
-          <t>Election Arc</t>
+          <t>VP Arc</t>
         </is>
       </c>
       <c r="C303" s="81" t="inlineStr">
         <is>
-          <t>STUMP_SPEECH_01_INTIMATE</t>
+          <t>VP_BATTLEFIELD_INTIMATE</t>
         </is>
       </c>
       <c r="D303" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — ... — BY MORNING</t>
+          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAM... — BY MORNING</t>
         </is>
       </c>
       <c r="E303" s="84" t="inlineStr">
@@ -19990,7 +19938,7 @@
       </c>
       <c r="F303" s="82" t="inlineStr">
         <is>
-          <t>STUMP_SPEECH_01 (intimate choice)</t>
+          <t>VP_BATTLEFIELD (intimate choice)</t>
         </is>
       </c>
       <c r="G303" s="82" t="inlineStr">
@@ -20022,25 +19970,73 @@
       </c>
       <c r="N303" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of STUMP_SPEECH_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="8" customHeight="1">
-      <c r="A304" s="9" t="n"/>
-      <c r="B304" s="9" t="n"/>
-      <c r="C304" s="9" t="n"/>
-      <c r="D304" s="9" t="n"/>
-      <c r="E304" s="9" t="n"/>
-      <c r="F304" s="9" t="n"/>
-      <c r="G304" s="9" t="n"/>
-      <c r="H304" s="9" t="n"/>
-      <c r="I304" s="9" t="n"/>
-      <c r="J304" s="9" t="n"/>
-      <c r="K304" s="9" t="n"/>
-      <c r="L304" s="9" t="n"/>
-      <c r="M304" s="9" t="n"/>
-      <c r="N304" s="9" t="n"/>
+          <t>Stub — author intimate version of VP_BATTLEFIELD. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="30" customHeight="1">
+      <c r="A304" s="80" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="B304" s="80" t="inlineStr">
+        <is>
+          <t>VP Arc</t>
+        </is>
+      </c>
+      <c r="C304" s="81" t="inlineStr">
+        <is>
+          <t>VP_PRE_ELECTION_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D304" s="82" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [C... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E304" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F304" s="82" t="inlineStr">
+        <is>
+          <t>VP_PRE_ELECTION (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G304" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H304" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I304" s="81" t="inlineStr"/>
+      <c r="J304" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K304" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L304" s="81" t="inlineStr"/>
+      <c r="M304" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N304" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of VP_PRE_ELECTION. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="30" customHeight="1">
       <c r="A305" s="80" t="inlineStr">
@@ -20055,12 +20051,12 @@
       </c>
       <c r="C305" s="81" t="inlineStr">
         <is>
-          <t>VP_DOUBT_INTIMATE</t>
+          <t>VP_LEGACY_INTIMATE</t>
         </is>
       </c>
       <c r="D305" s="82" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QU... — BY MORNING</t>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] ... — BY MORNING</t>
         </is>
       </c>
       <c r="E305" s="84" t="inlineStr">
@@ -20070,7 +20066,7 @@
       </c>
       <c r="F305" s="82" t="inlineStr">
         <is>
-          <t>VP_DOUBT (intimate choice)</t>
+          <t>VP_LEGACY (intimate choice)</t>
         </is>
       </c>
       <c r="G305" s="82" t="inlineStr">
@@ -20102,93 +20098,45 @@
       </c>
       <c r="N305" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of VP_DOUBT. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="30" customHeight="1">
-      <c r="A306" s="80" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="B306" s="80" t="inlineStr">
-        <is>
-          <t>VP Arc</t>
-        </is>
-      </c>
-      <c r="C306" s="81" t="inlineStr">
-        <is>
-          <t>VP_BATTLEFIELD_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D306" s="82" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAM... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E306" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F306" s="82" t="inlineStr">
-        <is>
-          <t>VP_BATTLEFIELD (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G306" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H306" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I306" s="81" t="inlineStr"/>
-      <c r="J306" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K306" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L306" s="81" t="inlineStr"/>
-      <c r="M306" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N306" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of VP_BATTLEFIELD. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of VP_LEGACY. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="8" customHeight="1">
+      <c r="A306" s="9" t="n"/>
+      <c r="B306" s="9" t="n"/>
+      <c r="C306" s="9" t="n"/>
+      <c r="D306" s="9" t="n"/>
+      <c r="E306" s="9" t="n"/>
+      <c r="F306" s="9" t="n"/>
+      <c r="G306" s="9" t="n"/>
+      <c r="H306" s="9" t="n"/>
+      <c r="I306" s="9" t="n"/>
+      <c r="J306" s="9" t="n"/>
+      <c r="K306" s="9" t="n"/>
+      <c r="L306" s="9" t="n"/>
+      <c r="M306" s="9" t="n"/>
+      <c r="N306" s="9" t="n"/>
     </row>
     <row r="307" ht="30" customHeight="1">
       <c r="A307" s="80" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B307" s="80" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C307" s="81" t="inlineStr">
         <is>
-          <t>VP_PRE_ELECTION_INTIMATE</t>
+          <t>CAN_CLEARWATER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D307" s="82" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [C... — BY MORNING</t>
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
         </is>
       </c>
       <c r="E307" s="84" t="inlineStr">
@@ -20198,7 +20146,7 @@
       </c>
       <c r="F307" s="82" t="inlineStr">
         <is>
-          <t>VP_PRE_ELECTION (intimate choice)</t>
+          <t>CAN_CLEARWATER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G307" s="82" t="inlineStr">
@@ -20230,29 +20178,29 @@
       </c>
       <c r="N307" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of VP_PRE_ELECTION. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="308" ht="30" customHeight="1">
       <c r="A308" s="80" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B308" s="80" t="inlineStr">
         <is>
-          <t>VP Arc</t>
+          <t>Canadian Alliance</t>
         </is>
       </c>
       <c r="C308" s="81" t="inlineStr">
         <is>
-          <t>VP_LEGACY_INTIMATE</t>
+          <t>CAN_JOINT_OPS_01_INTIMATE</t>
         </is>
       </c>
       <c r="D308" s="82" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] ... — BY MORNING</t>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
         </is>
       </c>
       <c r="E308" s="84" t="inlineStr">
@@ -20262,7 +20210,7 @@
       </c>
       <c r="F308" s="82" t="inlineStr">
         <is>
-          <t>VP_LEGACY (intimate choice)</t>
+          <t>CAN_JOINT_OPS_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G308" s="82" t="inlineStr">
@@ -20294,25 +20242,73 @@
       </c>
       <c r="N308" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of VP_LEGACY. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="309" ht="8" customHeight="1">
-      <c r="A309" s="9" t="n"/>
-      <c r="B309" s="9" t="n"/>
-      <c r="C309" s="9" t="n"/>
-      <c r="D309" s="9" t="n"/>
-      <c r="E309" s="9" t="n"/>
-      <c r="F309" s="9" t="n"/>
-      <c r="G309" s="9" t="n"/>
-      <c r="H309" s="9" t="n"/>
-      <c r="I309" s="9" t="n"/>
-      <c r="J309" s="9" t="n"/>
-      <c r="K309" s="9" t="n"/>
-      <c r="L309" s="9" t="n"/>
-      <c r="M309" s="9" t="n"/>
-      <c r="N309" s="9" t="n"/>
+          <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="80" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B309" s="80" t="inlineStr">
+        <is>
+          <t>Canadian Alliance</t>
+        </is>
+      </c>
+      <c r="C309" s="81" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D309" s="82" t="inlineStr">
+        <is>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E309" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F309" s="82" t="inlineStr">
+        <is>
+          <t>CAN_SUMMIT_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G309" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H309" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I309" s="81" t="inlineStr"/>
+      <c r="J309" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K309" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L309" s="81" t="inlineStr"/>
+      <c r="M309" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N309" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="30" customHeight="1">
       <c r="A310" s="80" t="inlineStr">
@@ -20327,12 +20323,12 @@
       </c>
       <c r="C310" s="81" t="inlineStr">
         <is>
-          <t>CAN_CLEARWATER_01_INTIMATE</t>
+          <t>CAN_ELECTION_LUCK_INTIMATE</t>
         </is>
       </c>
       <c r="D310" s="82" t="inlineStr">
         <is>
-          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUT... — BY MORNING</t>
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
         </is>
       </c>
       <c r="E310" s="84" t="inlineStr">
@@ -20342,7 +20338,7 @@
       </c>
       <c r="F310" s="82" t="inlineStr">
         <is>
-          <t>CAN_CLEARWATER_01 (intimate choice)</t>
+          <t>CAN_ELECTION_LUCK (intimate choice)</t>
         </is>
       </c>
       <c r="G310" s="82" t="inlineStr">
@@ -20374,7 +20370,7 @@
       </c>
       <c r="N310" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_CLEARWATER_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20386,17 +20382,17 @@
       </c>
       <c r="B311" s="80" t="inlineStr">
         <is>
-          <t>Canadian Alliance</t>
+          <t>Peace</t>
         </is>
       </c>
       <c r="C311" s="81" t="inlineStr">
         <is>
-          <t>CAN_JOINT_OPS_01_INTIMATE</t>
+          <t>CAN_PEACE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D311" s="82" t="inlineStr">
         <is>
-          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE O... — BY MORNING</t>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
         </is>
       </c>
       <c r="E311" s="84" t="inlineStr">
@@ -20406,7 +20402,7 @@
       </c>
       <c r="F311" s="82" t="inlineStr">
         <is>
-          <t>CAN_JOINT_OPS_01 (intimate choice)</t>
+          <t>CAN_PEACE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G311" s="82" t="inlineStr">
@@ -20438,7 +20434,7 @@
       </c>
       <c r="N311" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_JOINT_OPS_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20450,17 +20446,17 @@
       </c>
       <c r="B312" s="80" t="inlineStr">
         <is>
-          <t>Canadian Alliance</t>
+          <t>Peace</t>
         </is>
       </c>
       <c r="C312" s="81" t="inlineStr">
         <is>
-          <t>CAN_SUMMIT_01_INTIMATE</t>
+          <t>PEACE_ALLIED_01_INTIMATE</t>
         </is>
       </c>
       <c r="D312" s="82" t="inlineStr">
         <is>
-          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR TH... — BY MORNING</t>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
         </is>
       </c>
       <c r="E312" s="84" t="inlineStr">
@@ -20470,7 +20466,7 @@
       </c>
       <c r="F312" s="82" t="inlineStr">
         <is>
-          <t>CAN_SUMMIT_01 (intimate choice)</t>
+          <t>PEACE_ALLIED_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G312" s="82" t="inlineStr">
@@ -20502,7 +20498,7 @@
       </c>
       <c r="N312" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_SUMMIT_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20514,17 +20510,17 @@
       </c>
       <c r="B313" s="80" t="inlineStr">
         <is>
-          <t>Canadian Alliance</t>
+          <t>Peace</t>
         </is>
       </c>
       <c r="C313" s="81" t="inlineStr">
         <is>
-          <t>CAN_ELECTION_LUCK_INTIMATE</t>
+          <t>PEACE_USA_01_INTIMATE</t>
         </is>
       </c>
       <c r="D313" s="82" t="inlineStr">
         <is>
-          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY ... — BY MORNING</t>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E313" s="84" t="inlineStr">
@@ -20534,7 +20530,7 @@
       </c>
       <c r="F313" s="82" t="inlineStr">
         <is>
-          <t>CAN_ELECTION_LUCK (intimate choice)</t>
+          <t>PEACE_USA_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G313" s="82" t="inlineStr">
@@ -20566,93 +20562,45 @@
       </c>
       <c r="N313" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CAN_ELECTION_LUCK. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="30" customHeight="1">
-      <c r="A314" s="80" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B314" s="80" t="inlineStr">
-        <is>
-          <t>Peace</t>
-        </is>
-      </c>
-      <c r="C314" s="81" t="inlineStr">
-        <is>
-          <t>CAN_PEACE_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D314" s="82" t="inlineStr">
-        <is>
-          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E314" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F314" s="82" t="inlineStr">
-        <is>
-          <t>CAN_PEACE_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G314" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H314" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I314" s="81" t="inlineStr"/>
-      <c r="J314" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K314" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L314" s="81" t="inlineStr"/>
-      <c r="M314" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N314" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CAN_PEACE_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="8" customHeight="1">
+      <c r="A314" s="9" t="n"/>
+      <c r="B314" s="9" t="n"/>
+      <c r="C314" s="9" t="n"/>
+      <c r="D314" s="9" t="n"/>
+      <c r="E314" s="9" t="n"/>
+      <c r="F314" s="9" t="n"/>
+      <c r="G314" s="9" t="n"/>
+      <c r="H314" s="9" t="n"/>
+      <c r="I314" s="9" t="n"/>
+      <c r="J314" s="9" t="n"/>
+      <c r="K314" s="9" t="n"/>
+      <c r="L314" s="9" t="n"/>
+      <c r="M314" s="9" t="n"/>
+      <c r="N314" s="9" t="n"/>
     </row>
     <row r="315" ht="30" customHeight="1">
       <c r="A315" s="80" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B315" s="80" t="inlineStr">
         <is>
-          <t>Peace</t>
+          <t>Le Wendigo</t>
         </is>
       </c>
       <c r="C315" s="81" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01_INTIMATE</t>
+          <t>CA_PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D315" s="82" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE C... — BY MORNING</t>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
         </is>
       </c>
       <c r="E315" s="84" t="inlineStr">
@@ -20662,7 +20610,7 @@
       </c>
       <c r="F315" s="82" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01 (intimate choice)</t>
+          <t>CA_PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G315" s="82" t="inlineStr">
@@ -20694,29 +20642,29 @@
       </c>
       <c r="N315" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PEACE_ALLIED_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="80" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA Protector</t>
         </is>
       </c>
       <c r="B316" s="80" t="inlineStr">
         <is>
-          <t>Peace</t>
+          <t>Le Loup-Garou</t>
         </is>
       </c>
       <c r="C316" s="81" t="inlineStr">
         <is>
-          <t>PEACE_USA_01_INTIMATE</t>
+          <t>CA_PROT_02_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D316" s="82" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE... — BY MORNING</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
         </is>
       </c>
       <c r="E316" s="84" t="inlineStr">
@@ -20726,7 +20674,7 @@
       </c>
       <c r="F316" s="82" t="inlineStr">
         <is>
-          <t>PEACE_USA_01 (intimate choice)</t>
+          <t>CA_PROT_02_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G316" s="82" t="inlineStr">
@@ -20758,25 +20706,73 @@
       </c>
       <c r="N316" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PEACE_USA_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="317" ht="8" customHeight="1">
-      <c r="A317" s="9" t="n"/>
-      <c r="B317" s="9" t="n"/>
-      <c r="C317" s="9" t="n"/>
-      <c r="D317" s="9" t="n"/>
-      <c r="E317" s="9" t="n"/>
-      <c r="F317" s="9" t="n"/>
-      <c r="G317" s="9" t="n"/>
-      <c r="H317" s="9" t="n"/>
-      <c r="I317" s="9" t="n"/>
-      <c r="J317" s="9" t="n"/>
-      <c r="K317" s="9" t="n"/>
-      <c r="L317" s="9" t="n"/>
-      <c r="M317" s="9" t="n"/>
-      <c r="N317" s="9" t="n"/>
+          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="30" customHeight="1">
+      <c r="A317" s="80" t="inlineStr">
+        <is>
+          <t>CA Protector</t>
+        </is>
+      </c>
+      <c r="B317" s="80" t="inlineStr">
+        <is>
+          <t>Les Feux Follets</t>
+        </is>
+      </c>
+      <c r="C317" s="81" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D317" s="82" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E317" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F317" s="82" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G317" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H317" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I317" s="81" t="inlineStr"/>
+      <c r="J317" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K317" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L317" s="81" t="inlineStr"/>
+      <c r="M317" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N317" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="30" customHeight="1">
       <c r="A318" s="80" t="inlineStr">
@@ -20786,17 +20782,17 @@
       </c>
       <c r="B318" s="80" t="inlineStr">
         <is>
-          <t>Le Wendigo</t>
+          <t>Mishepeshu</t>
         </is>
       </c>
       <c r="C318" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE_INTIMATE</t>
+          <t>CA_PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D318" s="82" t="inlineStr">
         <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD — BY MORNING</t>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
         </is>
       </c>
       <c r="E318" s="84" t="inlineStr">
@@ -20806,7 +20802,7 @@
       </c>
       <c r="F318" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE (intimate choice)</t>
+          <t>CA_PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G318" s="82" t="inlineStr">
@@ -20838,7 +20834,7 @@
       </c>
       <c r="N318" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20850,17 +20846,17 @@
       </c>
       <c r="B319" s="80" t="inlineStr">
         <is>
-          <t>Le Loup-Garou</t>
+          <t>La Corriveau</t>
         </is>
       </c>
       <c r="C319" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE_INTIMATE</t>
+          <t>CA_PROT_05_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D319" s="82" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLED... — BY MORNING</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
         </is>
       </c>
       <c r="E319" s="84" t="inlineStr">
@@ -20870,7 +20866,7 @@
       </c>
       <c r="F319" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_02_AGREE (intimate choice)</t>
+          <t>CA_PROT_05_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G319" s="82" t="inlineStr">
@@ -20902,7 +20898,7 @@
       </c>
       <c r="N319" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_02_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20914,17 +20910,17 @@
       </c>
       <c r="B320" s="80" t="inlineStr">
         <is>
-          <t>Les Feux Follets</t>
+          <t>Le Carcajou</t>
         </is>
       </c>
       <c r="C320" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE_INTIMATE</t>
+          <t>CA_PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D320" s="82" t="inlineStr">
         <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JO... — BY MORNING</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
         </is>
       </c>
       <c r="E320" s="84" t="inlineStr">
@@ -20934,7 +20930,7 @@
       </c>
       <c r="F320" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_03_AGREE (intimate choice)</t>
+          <t>CA_PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G320" s="82" t="inlineStr">
@@ -20966,7 +20962,7 @@
       </c>
       <c r="N320" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -20978,17 +20974,17 @@
       </c>
       <c r="B321" s="80" t="inlineStr">
         <is>
-          <t>Mishepeshu</t>
+          <t>La Chasse-Galerie</t>
         </is>
       </c>
       <c r="C321" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE_INTIMATE</t>
+          <t>CA_PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D321" s="82" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE... — BY MORNING</t>
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
         </is>
       </c>
       <c r="E321" s="84" t="inlineStr">
@@ -20998,7 +20994,7 @@
       </c>
       <c r="F321" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE (intimate choice)</t>
+          <t>CA_PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G321" s="82" t="inlineStr">
@@ -21030,7 +21026,7 @@
       </c>
       <c r="N321" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21042,17 +21038,17 @@
       </c>
       <c r="B322" s="80" t="inlineStr">
         <is>
-          <t>La Corriveau</t>
+          <t>Le Gougou</t>
         </is>
       </c>
       <c r="C322" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE_INTIMATE</t>
+          <t>CA_PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D322" s="82" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THR... — BY MORNING</t>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
         </is>
       </c>
       <c r="E322" s="84" t="inlineStr">
@@ -21062,7 +21058,7 @@
       </c>
       <c r="F322" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE (intimate choice)</t>
+          <t>CA_PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G322" s="82" t="inlineStr">
@@ -21094,93 +21090,45 @@
       </c>
       <c r="N322" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="323" ht="30" customHeight="1">
-      <c r="A323" s="80" t="inlineStr">
-        <is>
-          <t>CA Protector</t>
-        </is>
-      </c>
-      <c r="B323" s="80" t="inlineStr">
-        <is>
-          <t>Le Carcajou</t>
-        </is>
-      </c>
-      <c r="C323" s="81" t="inlineStr">
-        <is>
-          <t>CA_PROT_06_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D323" s="82" t="inlineStr">
-        <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDO... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E323" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F323" s="82" t="inlineStr">
-        <is>
-          <t>CA_PROT_06_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G323" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H323" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I323" s="81" t="inlineStr"/>
-      <c r="J323" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K323" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L323" s="81" t="inlineStr"/>
-      <c r="M323" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N323" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of CA_PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="8" customHeight="1">
+      <c r="A323" s="9" t="n"/>
+      <c r="B323" s="9" t="n"/>
+      <c r="C323" s="9" t="n"/>
+      <c r="D323" s="9" t="n"/>
+      <c r="E323" s="9" t="n"/>
+      <c r="F323" s="9" t="n"/>
+      <c r="G323" s="9" t="n"/>
+      <c r="H323" s="9" t="n"/>
+      <c r="I323" s="9" t="n"/>
+      <c r="J323" s="9" t="n"/>
+      <c r="K323" s="9" t="n"/>
+      <c r="L323" s="9" t="n"/>
+      <c r="M323" s="9" t="n"/>
+      <c r="N323" s="9" t="n"/>
     </row>
     <row r="324" ht="30" customHeight="1">
       <c r="A324" s="80" t="inlineStr">
         <is>
-          <t>CA Protector</t>
+          <t>Ualani</t>
         </is>
       </c>
       <c r="B324" s="80" t="inlineStr">
         <is>
-          <t>La Chasse-Galerie</t>
+          <t>Ambush</t>
         </is>
       </c>
       <c r="C324" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE_INTIMATE</t>
+          <t>UALANI_AMBUSH_01_INTIMATE</t>
         </is>
       </c>
       <c r="D324" s="82" t="inlineStr">
         <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW — BY MORNING</t>
+          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
         </is>
       </c>
       <c r="E324" s="84" t="inlineStr">
@@ -21190,7 +21138,7 @@
       </c>
       <c r="F324" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_07_AGREE (intimate choice)</t>
+          <t>UALANI_AMBUSH_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G324" s="82" t="inlineStr">
@@ -21222,29 +21170,29 @@
       </c>
       <c r="N324" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="325" ht="30" customHeight="1">
       <c r="A325" s="80" t="inlineStr">
         <is>
-          <t>CA Protector</t>
+          <t>Ualani</t>
         </is>
       </c>
       <c r="B325" s="80" t="inlineStr">
         <is>
-          <t>Le Gougou</t>
+          <t>Dignitary Reception</t>
         </is>
       </c>
       <c r="C325" s="81" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE_INTIMATE</t>
+          <t>UALANI_DIGNITARY_01_INTIMATE</t>
         </is>
       </c>
       <c r="D325" s="82" t="inlineStr">
         <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE C... — BY MORNING</t>
+          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
         </is>
       </c>
       <c r="E325" s="84" t="inlineStr">
@@ -21254,7 +21202,7 @@
       </c>
       <c r="F325" s="82" t="inlineStr">
         <is>
-          <t>CA_PROT_08_AGREE (intimate choice)</t>
+          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G325" s="82" t="inlineStr">
@@ -21286,25 +21234,73 @@
       </c>
       <c r="N325" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of CA_PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="8" customHeight="1">
-      <c r="A326" s="9" t="n"/>
-      <c r="B326" s="9" t="n"/>
-      <c r="C326" s="9" t="n"/>
-      <c r="D326" s="9" t="n"/>
-      <c r="E326" s="9" t="n"/>
-      <c r="F326" s="9" t="n"/>
-      <c r="G326" s="9" t="n"/>
-      <c r="H326" s="9" t="n"/>
-      <c r="I326" s="9" t="n"/>
-      <c r="J326" s="9" t="n"/>
-      <c r="K326" s="9" t="n"/>
-      <c r="L326" s="9" t="n"/>
-      <c r="M326" s="9" t="n"/>
-      <c r="N326" s="9" t="n"/>
+          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="30" customHeight="1">
+      <c r="A326" s="80" t="inlineStr">
+        <is>
+          <t>Ualani</t>
+        </is>
+      </c>
+      <c r="B326" s="80" t="inlineStr">
+        <is>
+          <t>Memorial Address</t>
+        </is>
+      </c>
+      <c r="C326" s="81" t="inlineStr">
+        <is>
+          <t>UALANI_MEMORIAL_01_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D326" s="82" t="inlineStr">
+        <is>
+          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E326" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F326" s="82" t="inlineStr">
+        <is>
+          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G326" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H326" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I326" s="81" t="inlineStr"/>
+      <c r="J326" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K326" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L326" s="81" t="inlineStr"/>
+      <c r="M326" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N326" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="30" customHeight="1">
       <c r="A327" s="80" t="inlineStr">
@@ -21314,17 +21310,17 @@
       </c>
       <c r="B327" s="80" t="inlineStr">
         <is>
-          <t>Ambush</t>
+          <t>Field Hospital</t>
         </is>
       </c>
       <c r="C327" s="81" t="inlineStr">
         <is>
-          <t>UALANI_AMBUSH_01_INTIMATE</t>
+          <t>UALANI_WOUNDED_01_INTIMATE</t>
         </is>
       </c>
       <c r="D327" s="82" t="inlineStr">
         <is>
-          <t>CROWN AMBUSH AVERTED: PRESIDENT CARLISLE HOLDS THE W... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
         </is>
       </c>
       <c r="E327" s="84" t="inlineStr">
@@ -21334,7 +21330,7 @@
       </c>
       <c r="F327" s="82" t="inlineStr">
         <is>
-          <t>UALANI_AMBUSH_01 (intimate choice)</t>
+          <t>UALANI_WOUNDED_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G327" s="82" t="inlineStr">
@@ -21366,7 +21362,7 @@
       </c>
       <c r="N327" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_AMBUSH_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21378,17 +21374,17 @@
       </c>
       <c r="B328" s="80" t="inlineStr">
         <is>
-          <t>Dignitary Reception</t>
+          <t>Forge Inspection</t>
         </is>
       </c>
       <c r="C328" s="81" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01_INTIMATE</t>
+          <t>UALANI_FORGE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D328" s="82" t="inlineStr">
         <is>
-          <t>STATE RECEPTION AT [TILE_NAME]: PRESIDENT CARLISLE A... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
         </is>
       </c>
       <c r="E328" s="84" t="inlineStr">
@@ -21398,7 +21394,7 @@
       </c>
       <c r="F328" s="82" t="inlineStr">
         <is>
-          <t>UALANI_DIGNITARY_01 (intimate choice)</t>
+          <t>UALANI_FORGE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G328" s="82" t="inlineStr">
@@ -21430,7 +21426,7 @@
       </c>
       <c r="N328" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_DIGNITARY_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21442,17 +21438,17 @@
       </c>
       <c r="B329" s="80" t="inlineStr">
         <is>
-          <t>Memorial Address</t>
+          <t>Culper Ring</t>
         </is>
       </c>
       <c r="C329" s="81" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01_INTIMATE</t>
+          <t>UALANI_CULPER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D329" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS [TILE_NAME]: PRESIDENTIAL ... — BY MORNING</t>
+          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
         </is>
       </c>
       <c r="E329" s="84" t="inlineStr">
@@ -21462,7 +21458,7 @@
       </c>
       <c r="F329" s="82" t="inlineStr">
         <is>
-          <t>UALANI_MEMORIAL_01 (intimate choice)</t>
+          <t>UALANI_CULPER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G329" s="82" t="inlineStr">
@@ -21494,7 +21490,7 @@
       </c>
       <c r="N329" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_MEMORIAL_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21506,17 +21502,17 @@
       </c>
       <c r="B330" s="80" t="inlineStr">
         <is>
-          <t>Field Hospital</t>
+          <t>Alliance Council</t>
         </is>
       </c>
       <c r="C330" s="81" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01_INTIMATE</t>
+          <t>UALANI_ALLIANCE_01_INTIMATE</t>
         </is>
       </c>
       <c r="D330" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE VISITS FIELD HOSPITAL AT [TILE_NAME] — BY MORNING</t>
+          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
         </is>
       </c>
       <c r="E330" s="84" t="inlineStr">
@@ -21526,7 +21522,7 @@
       </c>
       <c r="F330" s="82" t="inlineStr">
         <is>
-          <t>UALANI_WOUNDED_01 (intimate choice)</t>
+          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G330" s="82" t="inlineStr">
@@ -21558,7 +21554,7 @@
       </c>
       <c r="N330" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_WOUNDED_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21570,17 +21566,17 @@
       </c>
       <c r="B331" s="80" t="inlineStr">
         <is>
-          <t>Forge Inspection</t>
+          <t>Frontier</t>
         </is>
       </c>
       <c r="C331" s="81" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01_INTIMATE</t>
+          <t>UALANI_FRONTIER_01_INTIMATE</t>
         </is>
       </c>
       <c r="D331" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE CONDUCTS SURPRISE INSPECTION OF F... — BY MORNING</t>
+          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
         </is>
       </c>
       <c r="E331" s="84" t="inlineStr">
@@ -21590,7 +21586,7 @@
       </c>
       <c r="F331" s="82" t="inlineStr">
         <is>
-          <t>UALANI_FORGE_01 (intimate choice)</t>
+          <t>UALANI_FRONTIER_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G331" s="82" t="inlineStr">
@@ -21622,93 +21618,45 @@
       </c>
       <c r="N331" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_FORGE_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="332" ht="30" customHeight="1">
-      <c r="A332" s="80" t="inlineStr">
-        <is>
-          <t>Ualani</t>
-        </is>
-      </c>
-      <c r="B332" s="80" t="inlineStr">
-        <is>
-          <t>Culper Ring</t>
-        </is>
-      </c>
-      <c r="C332" s="81" t="inlineStr">
-        <is>
-          <t>UALANI_CULPER_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D332" s="82" t="inlineStr">
-        <is>
-          <t>CULPER RING CONTACT AT [TILE_NAME]: INTELLIGENCE ASS... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E332" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F332" s="82" t="inlineStr">
-        <is>
-          <t>UALANI_CULPER_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G332" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H332" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I332" s="81" t="inlineStr"/>
-      <c r="J332" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K332" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L332" s="81" t="inlineStr"/>
-      <c r="M332" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N332" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of UALANI_CULPER_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="8" customHeight="1">
+      <c r="A332" s="9" t="n"/>
+      <c r="B332" s="9" t="n"/>
+      <c r="C332" s="9" t="n"/>
+      <c r="D332" s="9" t="n"/>
+      <c r="E332" s="9" t="n"/>
+      <c r="F332" s="9" t="n"/>
+      <c r="G332" s="9" t="n"/>
+      <c r="H332" s="9" t="n"/>
+      <c r="I332" s="9" t="n"/>
+      <c r="J332" s="9" t="n"/>
+      <c r="K332" s="9" t="n"/>
+      <c r="L332" s="9" t="n"/>
+      <c r="M332" s="9" t="n"/>
+      <c r="N332" s="9" t="n"/>
     </row>
     <row r="333" ht="30" customHeight="1">
       <c r="A333" s="80" t="inlineStr">
         <is>
-          <t>Ualani</t>
+          <t>Protector</t>
         </is>
       </c>
       <c r="B333" s="80" t="inlineStr">
         <is>
-          <t>Alliance Council</t>
+          <t>Mothman</t>
         </is>
       </c>
       <c r="C333" s="81" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01_INTIMATE</t>
+          <t>PROT_01_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D333" s="82" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE MEETS WITH [COMMANDER_NAME] AT [T... — BY MORNING</t>
+          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E333" s="84" t="inlineStr">
@@ -21718,7 +21666,7 @@
       </c>
       <c r="F333" s="82" t="inlineStr">
         <is>
-          <t>UALANI_ALLIANCE_01 (intimate choice)</t>
+          <t>PROT_01_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G333" s="82" t="inlineStr">
@@ -21750,89 +21698,141 @@
       </c>
       <c r="N333" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of UALANI_ALLIANCE_01. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="334" ht="30" customHeight="1">
-      <c r="A334" s="80" t="inlineStr">
-        <is>
-          <t>Ualani</t>
-        </is>
-      </c>
-      <c r="B334" s="80" t="inlineStr">
-        <is>
-          <t>Frontier</t>
-        </is>
-      </c>
-      <c r="C334" s="81" t="inlineStr">
-        <is>
-          <t>UALANI_FRONTIER_01_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D334" s="82" t="inlineStr">
-        <is>
-          <t>PRESIDENT CARLISLE ESTABLISHES FRONTIER PRESENCE AT ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E334" s="84" t="inlineStr">
+      <c r="A334" s="23" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B334" s="23" t="inlineStr">
+        <is>
+          <t>Jersey Devil</t>
+        </is>
+      </c>
+      <c r="C334" s="24" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D334" s="25" t="inlineStr">
+        <is>
+          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E334" s="29" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F334" s="82" t="inlineStr">
-        <is>
-          <t>UALANI_FRONTIER_01 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G334" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H334" s="83" t="inlineStr">
+      <c r="F334" s="25" t="inlineStr">
+        <is>
+          <t>PROT_02_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G334" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H334" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I334" s="24" t="inlineStr">
+        <is>
+          <t>prot_02_agree_intimate</t>
+        </is>
+      </c>
+      <c r="J334" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K334" s="29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L334" s="24" t="inlineStr"/>
+      <c r="M334" s="29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N334" s="25" t="inlineStr">
+        <is>
+          <t>New Jersey's most complicated asset. By morning: recognition without negotiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="30" customHeight="1">
+      <c r="A335" s="80" t="inlineStr">
+        <is>
+          <t>Protector</t>
+        </is>
+      </c>
+      <c r="B335" s="80" t="inlineStr">
+        <is>
+          <t>Bigfoot</t>
+        </is>
+      </c>
+      <c r="C335" s="81" t="inlineStr">
+        <is>
+          <t>PROT_03_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D335" s="82" t="inlineStr">
+        <is>
+          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E335" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F335" s="82" t="inlineStr">
+        <is>
+          <t>PROT_03_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G335" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H335" s="83" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="I334" s="81" t="inlineStr"/>
-      <c r="J334" s="70" t="inlineStr">
+      <c r="I335" s="81" t="inlineStr"/>
+      <c r="J335" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K334" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L334" s="81" t="inlineStr"/>
-      <c r="M334" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N334" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of UALANI_FRONTIER_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="8" customHeight="1">
-      <c r="A335" s="9" t="n"/>
-      <c r="B335" s="9" t="n"/>
-      <c r="C335" s="9" t="n"/>
-      <c r="D335" s="9" t="n"/>
-      <c r="E335" s="9" t="n"/>
-      <c r="F335" s="9" t="n"/>
-      <c r="G335" s="9" t="n"/>
-      <c r="H335" s="9" t="n"/>
-      <c r="I335" s="9" t="n"/>
-      <c r="J335" s="9" t="n"/>
-      <c r="K335" s="9" t="n"/>
-      <c r="L335" s="9" t="n"/>
-      <c r="M335" s="9" t="n"/>
-      <c r="N335" s="9" t="n"/>
+      <c r="K335" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L335" s="81" t="inlineStr"/>
+      <c r="M335" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N335" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="30" customHeight="1">
       <c r="A336" s="80" t="inlineStr">
@@ -21842,17 +21842,17 @@
       </c>
       <c r="B336" s="80" t="inlineStr">
         <is>
-          <t>Mothman</t>
+          <t>Thunderbird</t>
         </is>
       </c>
       <c r="C336" s="81" t="inlineStr">
         <is>
-          <t>PROT_01_AGREE_INTIMATE</t>
+          <t>PROT_04_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D336" s="82" t="inlineStr">
         <is>
-          <t>MOTHMAN FORMALLY ALLIES WITH THE CONTINENTAL REPUBLIC — BY MORNING</t>
+          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
         </is>
       </c>
       <c r="E336" s="84" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="F336" s="82" t="inlineStr">
         <is>
-          <t>PROT_01_AGREE (intimate choice)</t>
+          <t>PROT_04_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G336" s="82" t="inlineStr">
@@ -21894,75 +21894,71 @@
       </c>
       <c r="N336" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_01_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="337" ht="30" customHeight="1">
-      <c r="A337" s="23" t="inlineStr">
+      <c r="A337" s="80" t="inlineStr">
         <is>
           <t>Protector</t>
         </is>
       </c>
-      <c r="B337" s="23" t="inlineStr">
-        <is>
-          <t>Jersey Devil</t>
-        </is>
-      </c>
-      <c r="C337" s="24" t="inlineStr">
-        <is>
-          <t>PROT_02_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D337" s="25" t="inlineStr">
-        <is>
-          <t>JERSEY DEVIL FORMALLY ENDORSES THE CONTINENTAL CAUSE — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E337" s="29" t="inlineStr">
+      <c r="B337" s="80" t="inlineStr">
+        <is>
+          <t>Headless Horseman</t>
+        </is>
+      </c>
+      <c r="C337" s="81" t="inlineStr">
+        <is>
+          <t>PROT_05_AGREE_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D337" s="82" t="inlineStr">
+        <is>
+          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E337" s="84" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="F337" s="25" t="inlineStr">
-        <is>
-          <t>PROT_02_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G337" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H337" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I337" s="24" t="inlineStr">
-        <is>
-          <t>prot_02_agree_intimate</t>
-        </is>
-      </c>
-      <c r="J337" s="27" t="inlineStr">
-        <is>
-          <t>Integrated</t>
-        </is>
-      </c>
-      <c r="K337" s="29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L337" s="24" t="inlineStr"/>
-      <c r="M337" s="29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N337" s="25" t="inlineStr">
-        <is>
-          <t>New Jersey's most complicated asset. By morning: recognition without negotiation.</t>
+      <c r="F337" s="82" t="inlineStr">
+        <is>
+          <t>PROT_05_AGREE (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G337" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H337" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I337" s="81" t="inlineStr"/>
+      <c r="J337" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K337" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L337" s="81" t="inlineStr"/>
+      <c r="M337" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N337" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -21974,17 +21970,17 @@
       </c>
       <c r="B338" s="80" t="inlineStr">
         <is>
-          <t>Bigfoot</t>
+          <t>Chessie</t>
         </is>
       </c>
       <c r="C338" s="81" t="inlineStr">
         <is>
-          <t>PROT_03_AGREE_INTIMATE</t>
+          <t>PROT_06_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D338" s="82" t="inlineStr">
         <is>
-          <t>BIGFOOT FORMALLY GUIDES THE CONTINENTAL CAUSE THROUG... — BY MORNING</t>
+          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E338" s="84" t="inlineStr">
@@ -21994,7 +21990,7 @@
       </c>
       <c r="F338" s="82" t="inlineStr">
         <is>
-          <t>PROT_03_AGREE (intimate choice)</t>
+          <t>PROT_06_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G338" s="82" t="inlineStr">
@@ -22026,7 +22022,7 @@
       </c>
       <c r="N338" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_03_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22038,17 +22034,17 @@
       </c>
       <c r="B339" s="80" t="inlineStr">
         <is>
-          <t>Thunderbird</t>
+          <t>Bell Witch</t>
         </is>
       </c>
       <c r="C339" s="81" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE_INTIMATE</t>
+          <t>PROT_07_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D339" s="82" t="inlineStr">
         <is>
-          <t>THUNDERBIRD FORMALLY ALLIES WITH THE CONTINENTAL REP... — BY MORNING</t>
+          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
         </is>
       </c>
       <c r="E339" s="84" t="inlineStr">
@@ -22058,7 +22054,7 @@
       </c>
       <c r="F339" s="82" t="inlineStr">
         <is>
-          <t>PROT_04_AGREE (intimate choice)</t>
+          <t>PROT_07_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G339" s="82" t="inlineStr">
@@ -22090,7 +22086,7 @@
       </c>
       <c r="N339" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_04_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22102,17 +22098,17 @@
       </c>
       <c r="B340" s="80" t="inlineStr">
         <is>
-          <t>Headless Horseman</t>
+          <t>Old Ironsides</t>
         </is>
       </c>
       <c r="C340" s="81" t="inlineStr">
         <is>
-          <t>PROT_05_AGREE_INTIMATE</t>
+          <t>PROT_08_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D340" s="82" t="inlineStr">
         <is>
-          <t>THE HORSEMAN RIDES FOR THE REPUBLIC — FORMALLY — BY MORNING</t>
+          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
         </is>
       </c>
       <c r="E340" s="84" t="inlineStr">
@@ -22122,7 +22118,7 @@
       </c>
       <c r="F340" s="82" t="inlineStr">
         <is>
-          <t>PROT_05_AGREE (intimate choice)</t>
+          <t>PROT_08_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G340" s="82" t="inlineStr">
@@ -22154,7 +22150,7 @@
       </c>
       <c r="N340" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_05_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22166,17 +22162,17 @@
       </c>
       <c r="B341" s="80" t="inlineStr">
         <is>
-          <t>Chessie</t>
+          <t>Valley Forge Guardian</t>
         </is>
       </c>
       <c r="C341" s="81" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE_INTIMATE</t>
+          <t>PROT_09_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D341" s="82" t="inlineStr">
         <is>
-          <t>CHESSIE FORMALLY PATROLS FOR THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E341" s="84" t="inlineStr">
@@ -22186,7 +22182,7 @@
       </c>
       <c r="F341" s="82" t="inlineStr">
         <is>
-          <t>PROT_06_AGREE (intimate choice)</t>
+          <t>PROT_09_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G341" s="82" t="inlineStr">
@@ -22218,7 +22214,7 @@
       </c>
       <c r="N341" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_06_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22230,17 +22226,17 @@
       </c>
       <c r="B342" s="80" t="inlineStr">
         <is>
-          <t>Bell Witch</t>
+          <t>Snallygaster</t>
         </is>
       </c>
       <c r="C342" s="81" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE_INTIMATE</t>
+          <t>PROT_10_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D342" s="82" t="inlineStr">
         <is>
-          <t>THE BELL WITCH FORMALLY COMMITS TO THE CONTINENTAL C... — BY MORNING</t>
+          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
         </is>
       </c>
       <c r="E342" s="84" t="inlineStr">
@@ -22250,7 +22246,7 @@
       </c>
       <c r="F342" s="82" t="inlineStr">
         <is>
-          <t>PROT_07_AGREE (intimate choice)</t>
+          <t>PROT_10_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G342" s="82" t="inlineStr">
@@ -22282,7 +22278,7 @@
       </c>
       <c r="N342" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_07_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22294,17 +22290,17 @@
       </c>
       <c r="B343" s="80" t="inlineStr">
         <is>
-          <t>Old Ironsides</t>
+          <t>Paul Revere</t>
         </is>
       </c>
       <c r="C343" s="81" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE_INTIMATE</t>
+          <t>PROT_11_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D343" s="82" t="inlineStr">
         <is>
-          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY — BY MORNING</t>
+          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
         </is>
       </c>
       <c r="E343" s="84" t="inlineStr">
@@ -22314,7 +22310,7 @@
       </c>
       <c r="F343" s="82" t="inlineStr">
         <is>
-          <t>PROT_08_AGREE (intimate choice)</t>
+          <t>PROT_11_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G343" s="82" t="inlineStr">
@@ -22346,7 +22342,7 @@
       </c>
       <c r="N343" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_08_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22358,17 +22354,17 @@
       </c>
       <c r="B344" s="80" t="inlineStr">
         <is>
-          <t>Valley Forge Guardian</t>
+          <t>Liberty Bell</t>
         </is>
       </c>
       <c r="C344" s="81" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE_INTIMATE</t>
+          <t>PROT_12_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D344" s="82" t="inlineStr">
         <is>
-          <t>VALLEY FORGE GUARDIAN FORMALLY BLESSES THE CONTINENT... — BY MORNING</t>
+          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
         </is>
       </c>
       <c r="E344" s="84" t="inlineStr">
@@ -22378,7 +22374,7 @@
       </c>
       <c r="F344" s="82" t="inlineStr">
         <is>
-          <t>PROT_09_AGREE (intimate choice)</t>
+          <t>PROT_12_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G344" s="82" t="inlineStr">
@@ -22410,7 +22406,7 @@
       </c>
       <c r="N344" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_09_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22422,17 +22418,17 @@
       </c>
       <c r="B345" s="80" t="inlineStr">
         <is>
-          <t>Snallygaster</t>
+          <t>Green Mountain Ghost</t>
         </is>
       </c>
       <c r="C345" s="81" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE_INTIMATE</t>
+          <t>PROT_13_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D345" s="82" t="inlineStr">
         <is>
-          <t>SNALLYGASTER FORMALLY GUARDS THE CONTINENTAL SUPPLY ... — BY MORNING</t>
+          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
         </is>
       </c>
       <c r="E345" s="84" t="inlineStr">
@@ -22442,7 +22438,7 @@
       </c>
       <c r="F345" s="82" t="inlineStr">
         <is>
-          <t>PROT_10_AGREE (intimate choice)</t>
+          <t>PROT_13_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G345" s="82" t="inlineStr">
@@ -22474,7 +22470,7 @@
       </c>
       <c r="N345" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_10_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22486,17 +22482,17 @@
       </c>
       <c r="B346" s="80" t="inlineStr">
         <is>
-          <t>Paul Revere</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="C346" s="81" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE_INTIMATE</t>
+          <t>PROT_14_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D346" s="82" t="inlineStr">
         <is>
-          <t>PAUL REVERE FORMALLY INTEGRATES WITH CONTINENTAL INT... — BY MORNING</t>
+          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
         </is>
       </c>
       <c r="E346" s="84" t="inlineStr">
@@ -22506,7 +22502,7 @@
       </c>
       <c r="F346" s="82" t="inlineStr">
         <is>
-          <t>PROT_11_AGREE (intimate choice)</t>
+          <t>PROT_14_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G346" s="82" t="inlineStr">
@@ -22538,7 +22534,7 @@
       </c>
       <c r="N346" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_11_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22550,17 +22546,17 @@
       </c>
       <c r="B347" s="80" t="inlineStr">
         <is>
-          <t>Liberty Bell</t>
+          <t>Skunk Ape</t>
         </is>
       </c>
       <c r="C347" s="81" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE_INTIMATE</t>
+          <t>PROT_15_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D347" s="82" t="inlineStr">
         <is>
-          <t>THE LIBERTY BELL FORMALLY RINGS FOR THE REPUBLIC — BY MORNING</t>
+          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
         </is>
       </c>
       <c r="E347" s="84" t="inlineStr">
@@ -22570,7 +22566,7 @@
       </c>
       <c r="F347" s="82" t="inlineStr">
         <is>
-          <t>PROT_12_AGREE (intimate choice)</t>
+          <t>PROT_15_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G347" s="82" t="inlineStr">
@@ -22602,7 +22598,7 @@
       </c>
       <c r="N347" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_12_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22614,17 +22610,17 @@
       </c>
       <c r="B348" s="80" t="inlineStr">
         <is>
-          <t>Green Mountain Ghost</t>
+          <t>Minuteman</t>
         </is>
       </c>
       <c r="C348" s="81" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE_INTIMATE</t>
+          <t>PROT_16_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D348" s="82" t="inlineStr">
         <is>
-          <t>GREEN MOUNTAIN GHOST FORMALLY PROTECTS VERMONT FOR T... — BY MORNING</t>
+          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
         </is>
       </c>
       <c r="E348" s="84" t="inlineStr">
@@ -22634,7 +22630,7 @@
       </c>
       <c r="F348" s="82" t="inlineStr">
         <is>
-          <t>PROT_13_AGREE (intimate choice)</t>
+          <t>PROT_16_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G348" s="82" t="inlineStr">
@@ -22666,7 +22662,7 @@
       </c>
       <c r="N348" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_13_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
@@ -22678,17 +22674,17 @@
       </c>
       <c r="B349" s="80" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Lincoln's Ghost</t>
         </is>
       </c>
       <c r="C349" s="81" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE_INTIMATE</t>
+          <t>PROT_17_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="D349" s="82" t="inlineStr">
         <is>
-          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CAR... — BY MORNING</t>
+          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
         </is>
       </c>
       <c r="E349" s="84" t="inlineStr">
@@ -22698,7 +22694,7 @@
       </c>
       <c r="F349" s="82" t="inlineStr">
         <is>
-          <t>PROT_14_AGREE (intimate choice)</t>
+          <t>PROT_17_AGREE (intimate choice)</t>
         </is>
       </c>
       <c r="G349" s="82" t="inlineStr">
@@ -22730,93 +22726,45 @@
       </c>
       <c r="N349" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_14_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="30" customHeight="1">
-      <c r="A350" s="80" t="inlineStr">
-        <is>
-          <t>Protector</t>
-        </is>
-      </c>
-      <c r="B350" s="80" t="inlineStr">
-        <is>
-          <t>Skunk Ape</t>
-        </is>
-      </c>
-      <c r="C350" s="81" t="inlineStr">
-        <is>
-          <t>PROT_15_AGREE_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D350" s="82" t="inlineStr">
-        <is>
-          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENT... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E350" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F350" s="82" t="inlineStr">
-        <is>
-          <t>PROT_15_AGREE (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G350" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H350" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I350" s="81" t="inlineStr"/>
-      <c r="J350" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K350" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L350" s="81" t="inlineStr"/>
-      <c r="M350" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N350" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of PROT_15_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
+          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="8" customHeight="1">
+      <c r="A350" s="9" t="n"/>
+      <c r="B350" s="9" t="n"/>
+      <c r="C350" s="9" t="n"/>
+      <c r="D350" s="9" t="n"/>
+      <c r="E350" s="9" t="n"/>
+      <c r="F350" s="9" t="n"/>
+      <c r="G350" s="9" t="n"/>
+      <c r="H350" s="9" t="n"/>
+      <c r="I350" s="9" t="n"/>
+      <c r="J350" s="9" t="n"/>
+      <c r="K350" s="9" t="n"/>
+      <c r="L350" s="9" t="n"/>
+      <c r="M350" s="9" t="n"/>
+      <c r="N350" s="9" t="n"/>
     </row>
     <row r="351" ht="30" customHeight="1">
       <c r="A351" s="80" t="inlineStr">
         <is>
-          <t>Protector</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B351" s="80" t="inlineStr">
         <is>
-          <t>Minuteman</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C351" s="81" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE_INTIMATE</t>
+          <t>WH_SECRET_01_INTIMATE</t>
         </is>
       </c>
       <c r="D351" s="82" t="inlineStr">
         <is>
-          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL ... — BY MORNING</t>
+          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
         </is>
       </c>
       <c r="E351" s="84" t="inlineStr">
@@ -22826,7 +22774,7 @@
       </c>
       <c r="F351" s="82" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE (intimate choice)</t>
+          <t>WH_SECRET_01 (intimate choice)</t>
         </is>
       </c>
       <c r="G351" s="82" t="inlineStr">
@@ -22858,29 +22806,29 @@
       </c>
       <c r="N351" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_16_AGREE. By morning: emotional arc, no explicit imagery.</t>
+          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
         </is>
       </c>
     </row>
     <row r="352" ht="30" customHeight="1">
       <c r="A352" s="80" t="inlineStr">
         <is>
-          <t>Protector</t>
+          <t>White House</t>
         </is>
       </c>
       <c r="B352" s="80" t="inlineStr">
         <is>
-          <t>Lincoln's Ghost</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C352" s="81" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE_INTIMATE</t>
+          <t>WH_SECRET_07_INTIMATE</t>
         </is>
       </c>
       <c r="D352" s="82" t="inlineStr">
         <is>
-          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMIN... — BY MORNING</t>
+          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
         </is>
       </c>
       <c r="E352" s="84" t="inlineStr">
@@ -22890,7 +22838,7 @@
       </c>
       <c r="F352" s="82" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE (intimate choice)</t>
+          <t>WH_SECRET_07 (intimate choice)</t>
         </is>
       </c>
       <c r="G352" s="82" t="inlineStr">
@@ -22922,25 +22870,73 @@
       </c>
       <c r="N352" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of PROT_17_AGREE. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="353" ht="8" customHeight="1">
-      <c r="A353" s="9" t="n"/>
-      <c r="B353" s="9" t="n"/>
-      <c r="C353" s="9" t="n"/>
-      <c r="D353" s="9" t="n"/>
-      <c r="E353" s="9" t="n"/>
-      <c r="F353" s="9" t="n"/>
-      <c r="G353" s="9" t="n"/>
-      <c r="H353" s="9" t="n"/>
-      <c r="I353" s="9" t="n"/>
-      <c r="J353" s="9" t="n"/>
-      <c r="K353" s="9" t="n"/>
-      <c r="L353" s="9" t="n"/>
-      <c r="M353" s="9" t="n"/>
-      <c r="N353" s="9" t="n"/>
+          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="30" customHeight="1">
+      <c r="A353" s="80" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B353" s="80" t="inlineStr">
+        <is>
+          <t>Month 10</t>
+        </is>
+      </c>
+      <c r="C353" s="81" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10_INTIMATE</t>
+        </is>
+      </c>
+      <c r="D353" s="82" t="inlineStr">
+        <is>
+          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
+        </is>
+      </c>
+      <c r="E353" s="84" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="F353" s="82" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10 (intimate choice)</t>
+        </is>
+      </c>
+      <c r="G353" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H353" s="83" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="I353" s="81" t="inlineStr"/>
+      <c r="J353" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K353" s="84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L353" s="81" t="inlineStr"/>
+      <c r="M353" s="84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N353" s="82" t="inlineStr">
+        <is>
+          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="30" customHeight="1">
       <c r="A354" s="80" t="inlineStr">
@@ -22950,17 +22946,17 @@
       </c>
       <c r="B354" s="80" t="inlineStr">
         <is>
-          <t>Month 1</t>
+          <t>Month 12</t>
         </is>
       </c>
       <c r="C354" s="81" t="inlineStr">
         <is>
-          <t>WH_SECRET_01_INTIMATE</t>
+          <t>WH_SECRET_12_INTIMATE</t>
         </is>
       </c>
       <c r="D354" s="82" t="inlineStr">
         <is>
-          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES ... — BY MORNING</t>
+          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
         </is>
       </c>
       <c r="E354" s="84" t="inlineStr">
@@ -22970,7 +22966,7 @@
       </c>
       <c r="F354" s="82" t="inlineStr">
         <is>
-          <t>WH_SECRET_01 (intimate choice)</t>
+          <t>WH_SECRET_12 (intimate choice)</t>
         </is>
       </c>
       <c r="G354" s="82" t="inlineStr">
@@ -23002,239 +22998,47 @@
       </c>
       <c r="N354" s="82" t="inlineStr">
         <is>
-          <t>Stub — author intimate version of WH_SECRET_01. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="30" customHeight="1">
-      <c r="A355" s="80" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B355" s="80" t="inlineStr">
-        <is>
-          <t>Month 7</t>
-        </is>
-      </c>
-      <c r="C355" s="81" t="inlineStr">
-        <is>
-          <t>WH_SECRET_07_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D355" s="82" t="inlineStr">
-        <is>
-          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E355" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F355" s="82" t="inlineStr">
-        <is>
-          <t>WH_SECRET_07 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G355" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H355" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I355" s="81" t="inlineStr"/>
-      <c r="J355" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K355" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L355" s="81" t="inlineStr"/>
-      <c r="M355" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N355" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of WH_SECRET_07. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="356" ht="30" customHeight="1">
-      <c r="A356" s="80" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B356" s="80" t="inlineStr">
-        <is>
-          <t>Month 10</t>
-        </is>
-      </c>
-      <c r="C356" s="81" t="inlineStr">
-        <is>
-          <t>WH_SECRET_10_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D356" s="82" t="inlineStr">
-        <is>
-          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESS... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E356" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F356" s="82" t="inlineStr">
-        <is>
-          <t>WH_SECRET_10 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G356" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H356" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I356" s="81" t="inlineStr"/>
-      <c r="J356" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K356" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L356" s="81" t="inlineStr"/>
-      <c r="M356" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N356" s="82" t="inlineStr">
-        <is>
-          <t>Stub — author intimate version of WH_SECRET_10. By morning: emotional arc, no explicit imagery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="357" ht="30" customHeight="1">
-      <c r="A357" s="80" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B357" s="80" t="inlineStr">
-        <is>
-          <t>Month 12</t>
-        </is>
-      </c>
-      <c r="C357" s="81" t="inlineStr">
-        <is>
-          <t>WH_SECRET_12_INTIMATE</t>
-        </is>
-      </c>
-      <c r="D357" s="82" t="inlineStr">
-        <is>
-          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM ... — BY MORNING</t>
-        </is>
-      </c>
-      <c r="E357" s="84" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="F357" s="82" t="inlineStr">
-        <is>
-          <t>WH_SECRET_12 (intimate choice)</t>
-        </is>
-      </c>
-      <c r="G357" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H357" s="83" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="I357" s="81" t="inlineStr"/>
-      <c r="J357" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K357" s="84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L357" s="81" t="inlineStr"/>
-      <c r="M357" s="84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N357" s="82" t="inlineStr">
-        <is>
           <t>Stub — author intimate version of WH_SECRET_12. By morning: emotional arc, no explicit imagery.</t>
         </is>
+      </c>
+    </row>
+    <row r="356" ht="20" customHeight="1">
+      <c r="A356" s="85" t="inlineStr">
+        <is>
+          <t>Total events in spreadsheet</t>
+        </is>
+      </c>
+      <c r="B356" s="86" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="357" ht="20" customHeight="1">
+      <c r="A357" s="85" t="inlineStr">
+        <is>
+          <t>FIRST PASS (coded &amp; wired)</t>
+        </is>
+      </c>
+      <c r="B357" s="86" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="358" ht="20" customHeight="1">
+      <c r="A358" s="85" t="inlineStr">
+        <is>
+          <t>IDEA (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="B358" s="86" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
       <c r="A359" s="85" t="inlineStr">
         <is>
-          <t>Total events in spreadsheet</t>
+          <t>Need explicit art (YES)</t>
         </is>
       </c>
       <c r="B359" s="86" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="360" ht="20" customHeight="1">
-      <c r="A360" s="85" t="inlineStr">
-        <is>
-          <t>FIRST PASS (coded &amp; wired)</t>
-        </is>
-      </c>
-      <c r="B360" s="86" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="361" ht="20" customHeight="1">
-      <c r="A361" s="85" t="inlineStr">
-        <is>
-          <t>IDEA (not yet implemented)</t>
-        </is>
-      </c>
-      <c r="B361" s="86" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="362" ht="20" customHeight="1">
-      <c r="A362" s="85" t="inlineStr">
-        <is>
-          <t>Need explicit art (YES)</t>
-        </is>
-      </c>
-      <c r="B362" s="86" t="n">
         <v>56</v>
       </c>
     </row>

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARIBBEAN PRIVATEER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13930,9 +13930,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H203" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H203" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I203" s="68" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL SWAMP WITCH)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>tile_yield magic×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13862,9 +13862,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H202" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H202" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I202" s="68" t="inlineStr"/>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL ACADIAN FOREST RANGER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>tile_yield wood×5; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13794,9 +13794,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H201" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H201" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I201" s="68" t="inlineStr"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_16</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13970,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_16</t>
+          <t>GOV_LOYAL_ARC_17</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="B205" s="67" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C205" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_17</t>
+          <t>GOV_LOYAL_ARC_22</t>
         </is>
       </c>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS MAPPED EVERY TIMBER STAND WITHIN TWO DAYS' TRAVEL</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="N205" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13494,17 +13494,17 @@
       </c>
       <c r="B197" s="67" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C197" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_15</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL DC BUREAUCRAT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13726,9 +13726,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H200" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H200" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I200" s="68" t="inlineStr"/>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_15</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] AUDITS [TILE_NAME] AND FINDS THREE YEARS OF ACCOUNTING ERROR</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; BTN2: corrupt_windfall gold×10 +20 corruption; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13494,17 +13494,17 @@
       </c>
       <c r="B197" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C197" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL GETTYSBURG DESCENDANT)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13658,9 +13658,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H199" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H199" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I199" s="68" t="inlineStr"/>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13766,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_15</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] AUDITS [TILE_NAME] AND FINDS THREE YEARS OF ACCOUNTING ERROR</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; BTN2: corrupt_windfall gold×10 +20 corruption; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_15</t>
+          <t>GOV_LOYAL_ARC_16</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] AUDITS [TILE_NAME] AND FINDS THREE YEARS OF ACCOUNTING ERROR</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; BTN2: corrupt_windfall gold×10 +20 corruption; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13902,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_16</t>
+          <t>GOV_LOYAL_ARC_17</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13970,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_17</t>
+          <t>GOV_LOYAL_ARC_23</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] POSTS ONE MUSTER NOTICE; THE LINE FORMS BEFORE DAWN</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13426,17 +13426,17 @@
       </c>
       <c r="B196" s="67" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C196" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_14</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL FRONTIER PREACHER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13494,17 +13494,17 @@
       </c>
       <c r="B197" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C197" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13590,9 +13590,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H198" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H198" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I198" s="68" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_14</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RIDES ELEVEN DAYS THROUGH FOUR SETTLEMENTS AND COMES BACK WITH PLEDGES FROM ALL OF THEM</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13426,17 +13426,17 @@
       </c>
       <c r="B196" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C196" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL LGBTQ+ ORGANIZER)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="N196" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13494,17 +13494,17 @@
       </c>
       <c r="B197" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C197" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13522,9 +13522,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H197" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H197" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I197" s="68" t="inlineStr"/>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_14</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>FRONTIER PREACHER INSPIRES THOUSANDS</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield culture×5; BTN2: resource_change manpower 1000; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_14</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RIDES ELEVEN DAYS THROUGH FOUR SETTLEMENTS AND COMES BACK WITH PLEDGES FROM ALL OF THEM</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] ORGANIZED SOMETHING NOBODY OFFICIALLY SANCTIONED AND EVERYONE SHOWED UP</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13358,17 +13358,17 @@
       </c>
       <c r="B195" s="67" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C195" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_13</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL NANTUCKET SAILOR)</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="N195" s="69" t="inlineStr">
         <is>
-          <t>tile_yield boats×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
         </is>
       </c>
     </row>
@@ -13426,17 +13426,17 @@
       </c>
       <c r="B196" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C196" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13454,9 +13454,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H196" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H196" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I196" s="68" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="N196" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13494,17 +13494,17 @@
       </c>
       <c r="B197" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C197" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_13</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] REFLOATS A HULL THAT WAS LISTED ON THE CHARTS AS A NAVIGATION HAZARD</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13358,17 +13358,17 @@
       </c>
       <c r="B195" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C195" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CARNIVAL BARKER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -13386,9 +13386,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H195" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H195" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I195" s="68" t="inlineStr"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="N195" s="69" t="inlineStr">
         <is>
-          <t>tile_yield gold×3; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13426,17 +13426,17 @@
       </c>
       <c r="B196" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C196" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="N196" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13494,17 +13494,17 @@
       </c>
       <c r="B197" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C197" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_13</t>
         </is>
       </c>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] REFLOATS A HULL THAT WAS LISTED ON THE CHARTS AS A NAVIGATION HAZARD</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B198" s="67" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C198" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_13</t>
+          <t>GOV_LOYAL_ARC_14</t>
         </is>
       </c>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] REFLOATS A HULL THAT WAS LISTED ON THE CHARTS AS A NAVIGATION HAZARD</t>
+          <t>FRONTIER PREACHER INSPIRES THOUSANDS</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N198" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield culture×5; BTN2: resource_change manpower 1000; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_14</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>FRONTIER PREACHER INSPIRES THOUSANDS</t>
+          <t>FOR ONE NIGHT ONLY!</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield culture×5; BTN2: resource_change manpower 1000; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×5; BTN2: tile_building_mandate_surge×5 turns; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -14346,9 +14346,9 @@
           <t>ARC_02_DONE</t>
         </is>
       </c>
-      <c r="H210" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H210" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I210" s="32" t="inlineStr"/>
@@ -14410,9 +14410,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H211" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H211" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I211" s="32" t="inlineStr"/>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13290,17 +13290,17 @@
       </c>
       <c r="B194" s="67" t="inlineStr">
         <is>
-          <t>Continental Surgeon</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C194" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_12</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D194" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL CONTINENTAL SURGEON)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -13318,9 +13318,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H194" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H194" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I194" s="68" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="N194" s="69" t="inlineStr">
         <is>
-          <t>tile_yield food×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13358,17 +13358,17 @@
       </c>
       <c r="B195" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C195" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="N195" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13426,17 +13426,17 @@
       </c>
       <c r="B196" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C196" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_12</t>
         </is>
       </c>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>THE AMPUTEE'S HANDBOOK — [COMMANDER_NAME] SUBMITS A REPORT ON BATTLEFIELD MEDICINE</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="N196" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: all_armies_manpower_heal 25%; BTN2: set_governor_perk medical_science (+1 science all buildings); 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -13222,17 +13222,17 @@
       </c>
       <c r="B193" s="67" t="inlineStr">
         <is>
-          <t>Boston Rabble-Rouser</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C193" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_11</t>
+          <t>GOV_LOYAL_ARC_18</t>
         </is>
       </c>
       <c r="D193" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] (LOYAL BOSTON RABBLE-ROUSER)</t>
+          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -13250,9 +13250,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H193" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+      <c r="H193" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I193" s="68" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="N193" s="69" t="inlineStr">
         <is>
-          <t>tile_yield culture×4; 3%/turn at loyalty≥8; once per governor; text-only</t>
+          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13290,17 +13290,17 @@
       </c>
       <c r="B194" s="67" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C194" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_18</t>
+          <t>GOV_LOYAL_ARC_19</t>
         </is>
       </c>
       <c r="D194" s="69" t="inlineStr">
         <is>
-          <t>MESSAGE IN A BOTTLE FROM THE DEEP SWAMPS OF [TILE_NAME] — SEEK POWER? OR SEEK KNOWLEDGE?</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="N194" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield magic×10; BTN2: level_all_spell_schools ×10; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13358,17 +13358,17 @@
       </c>
       <c r="B195" s="67" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="C195" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_19</t>
+          <t>GOV_LOYAL_ARC_11</t>
         </is>
       </c>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] CLOSES AN UNDISCLOSED DEAL; GOLD ARRIVES WITHOUT EXPLANATION</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] DELIVERS A SPEECH THAT DOES NOT DISPERSE</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="N195" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="B357" s="86" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">

--- a/event_masterdoc.xlsx
+++ b/event_masterdoc.xlsx
@@ -1163,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N359"/>
+  <dimension ref="A1:N362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13418,209 +13418,105 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="30" customHeight="1">
-      <c r="A196" s="67" t="inlineStr">
-        <is>
-          <t>Loyal Governor</t>
-        </is>
-      </c>
-      <c r="B196" s="67" t="inlineStr">
-        <is>
-          <t>Continental Surgeon</t>
-        </is>
-      </c>
-      <c r="C196" s="68" t="inlineStr">
-        <is>
-          <t>GOV_LOYAL_ARC_12</t>
-        </is>
-      </c>
-      <c r="D196" s="69" t="inlineStr">
-        <is>
-          <t>THE AMPUTEE'S HANDBOOK — [COMMANDER_NAME] SUBMITS A REPORT ON BATTLEFIELD MEDICINE</t>
-        </is>
-      </c>
-      <c r="E196" s="5" t="inlineStr">
+    <row r="196" ht="8" customHeight="1">
+      <c r="A196" s="9" t="n"/>
+      <c r="B196" s="9" t="n"/>
+      <c r="C196" s="9" t="n"/>
+      <c r="D196" s="9" t="n"/>
+      <c r="E196" s="9" t="n"/>
+      <c r="F196" s="9" t="n"/>
+      <c r="G196" s="9" t="n"/>
+      <c r="H196" s="9" t="n"/>
+      <c r="I196" s="9" t="n"/>
+      <c r="J196" s="9" t="n"/>
+      <c r="K196" s="9" t="n"/>
+      <c r="L196" s="9" t="n"/>
+      <c r="M196" s="9" t="n"/>
+      <c r="N196" s="9" t="n"/>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B197" s="31" t="inlineStr">
+        <is>
+          <t>Boston Rabble-Rouser</t>
+        </is>
+      </c>
+      <c r="C197" s="32" t="inlineStr">
+        <is>
+          <t>ARC_11_MONARCHISTS</t>
+        </is>
+      </c>
+      <c r="D197" s="33" t="inlineStr">
+        <is>
+          <t>ORAL PERFORMANCE SWAYS MONARCHISTS — A MOB IN [TILE_NAME] IS LISTENING</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="F196" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G196" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H196" s="26" t="inlineStr">
+      <c r="F197" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H197" s="26" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="I196" s="68" t="inlineStr"/>
-      <c r="J196" s="70" t="inlineStr">
+      <c r="I197" s="32" t="inlineStr"/>
+      <c r="J197" s="70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K196" s="71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L196" s="68" t="inlineStr">
+      <c r="K197" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L197" s="32" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="M196" s="71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N196" s="69" t="inlineStr">
-        <is>
-          <t>BTN1: all_armies_manpower_heal 25%; BTN2: set_governor_perk medical_science (+1 science all buildings); 3%/turn at loyalty≥8; once per governor</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="67" t="inlineStr">
-        <is>
-          <t>Loyal Governor</t>
-        </is>
-      </c>
-      <c r="B197" s="67" t="inlineStr">
-        <is>
-          <t>Nantucket Sailor</t>
-        </is>
-      </c>
-      <c r="C197" s="68" t="inlineStr">
-        <is>
-          <t>GOV_LOYAL_ARC_13</t>
-        </is>
-      </c>
-      <c r="D197" s="69" t="inlineStr">
-        <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] REFLOATS A HULL THAT WAS LISTED ON THE CHARTS AS A NAVIGATION HAZARD</t>
-        </is>
-      </c>
-      <c r="E197" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F197" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G197" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H197" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I197" s="68" t="inlineStr"/>
-      <c r="J197" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K197" s="71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L197" s="68" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M197" s="71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N197" s="69" t="inlineStr">
-        <is>
-          <t>BTN1: tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="30" customHeight="1">
-      <c r="A198" s="67" t="inlineStr">
-        <is>
-          <t>Loyal Governor</t>
-        </is>
-      </c>
-      <c r="B198" s="67" t="inlineStr">
-        <is>
-          <t>Frontier Preacher</t>
-        </is>
-      </c>
-      <c r="C198" s="68" t="inlineStr">
-        <is>
-          <t>GOV_LOYAL_ARC_14</t>
-        </is>
-      </c>
-      <c r="D198" s="69" t="inlineStr">
-        <is>
-          <t>FRONTIER PREACHER INSPIRES THOUSANDS</t>
-        </is>
-      </c>
-      <c r="E198" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F198" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G198" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H198" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I198" s="68" t="inlineStr"/>
-      <c r="J198" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K198" s="71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L198" s="68" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M198" s="71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N198" s="69" t="inlineStr">
-        <is>
-          <t>BTN1: tile_yield culture×5; BTN2: resource_change manpower 1000; 3%/turn at loyalty≥8; once per governor</t>
-        </is>
-      </c>
+      <c r="M197" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N197" s="33" t="inlineStr">
+        <is>
+          <t>BTN1: resource_change manpower+1000; BTN2: reveal_british_tiles (fog reveal 1 turn); 3%/turn at loyalty≥5; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="8" customHeight="1">
+      <c r="A198" s="9" t="n"/>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="9" t="n"/>
+      <c r="E198" s="9" t="n"/>
+      <c r="F198" s="9" t="n"/>
+      <c r="G198" s="9" t="n"/>
+      <c r="H198" s="9" t="n"/>
+      <c r="I198" s="9" t="n"/>
+      <c r="J198" s="9" t="n"/>
+      <c r="K198" s="9" t="n"/>
+      <c r="L198" s="9" t="n"/>
+      <c r="M198" s="9" t="n"/>
+      <c r="N198" s="9" t="n"/>
     </row>
     <row r="199" ht="30" customHeight="1">
       <c r="A199" s="67" t="inlineStr">
@@ -13630,17 +13526,17 @@
       </c>
       <c r="B199" s="67" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C199" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_25</t>
+          <t>GOV_LOYAL_ARC_12</t>
         </is>
       </c>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>FOR ONE NIGHT ONLY!</t>
+          <t>THE AMPUTEE'S HANDBOOK — [COMMANDER_NAME] SUBMITS A REPORT ON BATTLEFIELD MEDICINE</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13686,7 +13582,7 @@
       </c>
       <c r="N199" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×5; BTN2: tile_building_mandate_surge×5 turns; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: all_armies_manpower_heal 25%; BTN2: set_governor_perk medical_science (+1 science all buildings); 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13594,17 @@
       </c>
       <c r="B200" s="67" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C200" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_24</t>
+          <t>GOV_LOYAL_ARC_13</t>
         </is>
       </c>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] ORGANIZED SOMETHING NOBODY OFFICIALLY SANCTIONED AND EVERYONE SHOWED UP</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] REFLOATS A HULL THAT WAS LISTED ON THE CHARTS AS A NAVIGATION HAZARD</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13754,7 +13650,7 @@
       </c>
       <c r="N200" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield boats×3; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13766,17 +13662,17 @@
       </c>
       <c r="B201" s="67" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C201" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_15</t>
+          <t>GOV_LOYAL_ARC_14</t>
         </is>
       </c>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] AUDITS [TILE_NAME] AND FINDS THREE YEARS OF ACCOUNTING ERROR</t>
+          <t>FRONTIER PREACHER INSPIRES THOUSANDS</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13822,7 +13718,7 @@
       </c>
       <c r="N201" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield gold×4; BTN2: corrupt_windfall gold×10 +20 corruption; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield culture×5; BTN2: resource_change manpower 1000; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13730,17 @@
       </c>
       <c r="B202" s="67" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C202" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_16</t>
+          <t>GOV_LOYAL_ARC_25</t>
         </is>
       </c>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
+          <t>FOR ONE NIGHT ONLY!</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13890,7 +13786,7 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×5; BTN2: tile_building_mandate_surge×5 turns; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13798,17 @@
       </c>
       <c r="B203" s="67" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C203" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_17</t>
+          <t>GOV_LOYAL_ARC_24</t>
         </is>
       </c>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] ORGANIZED SOMETHING NOBODY OFFICIALLY SANCTIONED AND EVERYONE SHOWED UP</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13958,7 +13854,7 @@
       </c>
       <c r="N203" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield culture×4; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -13970,17 +13866,17 @@
       </c>
       <c r="B204" s="67" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C204" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_23</t>
+          <t>GOV_LOYAL_ARC_15</t>
         </is>
       </c>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] POSTS ONE MUSTER NOTICE; THE LINE FORMS BEFORE DAWN</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] AUDITS [TILE_NAME] AND FINDS THREE YEARS OF ACCOUNTING ERROR</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -14026,7 +13922,7 @@
       </c>
       <c r="N204" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: tile_yield gold×4; BTN2: corrupt_windfall gold×10 +20 corruption; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14038,17 +13934,17 @@
       </c>
       <c r="B205" s="67" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C205" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_22</t>
+          <t>GOV_LOYAL_ARC_16</t>
         </is>
       </c>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS MAPPED EVERY TIMBER STAND WITHIN TWO DAYS' TRAVEL</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS A PROPOSAL FOR THE FOUNDRY</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -14094,7 +13990,7 @@
       </c>
       <c r="N205" s="69" t="inlineStr">
         <is>
-          <t>BTN1: tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
+          <t>BTN1: state_building_level_yield metal×10; BTN2: set_governor_perk community_steel; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
@@ -14106,17 +14002,17 @@
       </c>
       <c r="B206" s="67" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C206" s="68" t="inlineStr">
         <is>
-          <t>GOV_LOYAL_ARC_21</t>
+          <t>GOV_LOYAL_ARC_17</t>
         </is>
       </c>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>MERCENARY COMMANDER'S PATRIOTIC DISPLAY</t>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] RETURNS WITH RECRUITS WHO WERE WAITING</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -14162,217 +14058,229 @@
       </c>
       <c r="N206" s="69" t="inlineStr">
         <is>
+          <t>BTN1: tile_army_manpower_refill; BTN2: spawn_anarchist; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="67" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B207" s="67" t="inlineStr">
+        <is>
+          <t>Gettysburg Descendant</t>
+        </is>
+      </c>
+      <c r="C207" s="68" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_23</t>
+        </is>
+      </c>
+      <c r="D207" s="69" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] POSTS ONE MUSTER NOTICE; THE LINE FORMS BEFORE DAWN</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F207" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H207" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I207" s="68" t="inlineStr"/>
+      <c r="J207" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K207" s="71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L207" s="68" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M207" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N207" s="69" t="inlineStr">
+        <is>
+          <t>BTN1: tile_yield manpower×4; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="67" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B208" s="67" t="inlineStr">
+        <is>
+          <t>Acadian Forest Ranger</t>
+        </is>
+      </c>
+      <c r="C208" s="68" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_22</t>
+        </is>
+      </c>
+      <c r="D208" s="69" t="inlineStr">
+        <is>
+          <t>DISPATCH FROM [TILE_NAME] — [COMMANDER_NAME] HAS MAPPED EVERY TIMBER STAND WITHIN TWO DAYS' TRAVEL</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F208" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H208" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I208" s="68" t="inlineStr"/>
+      <c r="J208" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K208" s="71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L208" s="68" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M208" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N208" s="69" t="inlineStr">
+        <is>
+          <t>BTN1: tile_yield wood×5; 3%/turn at loyalty≥8; once per governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="67" t="inlineStr">
+        <is>
+          <t>Loyal Governor</t>
+        </is>
+      </c>
+      <c r="B209" s="67" t="inlineStr">
+        <is>
+          <t>Border Mercenary</t>
+        </is>
+      </c>
+      <c r="C209" s="68" t="inlineStr">
+        <is>
+          <t>GOV_LOYAL_ARC_21</t>
+        </is>
+      </c>
+      <c r="D209" s="69" t="inlineStr">
+        <is>
+          <t>MERCENARY COMMANDER'S PATRIOTIC DISPLAY</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F209" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H209" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I209" s="68" t="inlineStr"/>
+      <c r="J209" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K209" s="71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L209" s="68" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M209" s="71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N209" s="69" t="inlineStr">
+        <is>
           <t>BTN1: gold_and_army_buff Mercenary Zeal×10 turns + 50 gold; BTN2: army_buff Iron Discipline permanent; 3%/turn at loyalty≥8; once per governor</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="8" customHeight="1">
-      <c r="A207" s="9" t="n"/>
-      <c r="B207" s="9" t="n"/>
-      <c r="C207" s="9" t="n"/>
-      <c r="D207" s="9" t="n"/>
-      <c r="E207" s="9" t="n"/>
-      <c r="F207" s="9" t="n"/>
-      <c r="G207" s="9" t="n"/>
-      <c r="H207" s="9" t="n"/>
-      <c r="I207" s="9" t="n"/>
-      <c r="J207" s="9" t="n"/>
-      <c r="K207" s="9" t="n"/>
-      <c r="L207" s="9" t="n"/>
-      <c r="M207" s="9" t="n"/>
-      <c r="N207" s="9" t="n"/>
-    </row>
-    <row r="208" ht="30" customHeight="1">
-      <c r="A208" s="31" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B208" s="31" t="inlineStr">
-        <is>
-          <t>Wetlands Fisher</t>
-        </is>
-      </c>
-      <c r="C208" s="32" t="inlineStr">
-        <is>
-          <t>ARC_01_FIRST</t>
-        </is>
-      </c>
-      <c r="D208" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — WETLANDS FISHER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E208" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F208" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G208" s="33" t="inlineStr">
-        <is>
-          <t>ARC_01_DONE</t>
-        </is>
-      </c>
-      <c r="H208" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I208" s="32" t="inlineStr"/>
-      <c r="J208" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K208" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L208" s="32" t="inlineStr"/>
-      <c r="M208" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N208" s="33" t="inlineStr">
-        <is>
-          <t>Fires when ARC_01 completes objective 1; BTN1: nothing</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="30" customHeight="1">
-      <c r="A209" s="31" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B209" s="31" t="inlineStr">
-        <is>
-          <t>Wetlands Fisher</t>
-        </is>
-      </c>
-      <c r="C209" s="32" t="inlineStr">
-        <is>
-          <t>ARC_01_DONE</t>
-        </is>
-      </c>
-      <c r="D209" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — WETLANDS FISHER ARC COMPLETE</t>
-        </is>
-      </c>
-      <c r="E209" s="34" t="inlineStr">
-        <is>
-          <t>Resolution</t>
-        </is>
-      </c>
-      <c r="F209" s="33" t="inlineStr">
-        <is>
-          <t>ARC_01_FIRST</t>
-        </is>
-      </c>
-      <c r="G209" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H209" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I209" s="32" t="inlineStr"/>
-      <c r="J209" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K209" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L209" s="32" t="inlineStr"/>
-      <c r="M209" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N209" s="33" t="inlineStr">
-        <is>
-          <t>Fires when ARC_01 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="30" customHeight="1">
-      <c r="A210" s="31" t="inlineStr">
-        <is>
-          <t>Commander</t>
-        </is>
-      </c>
-      <c r="B210" s="31" t="inlineStr">
-        <is>
-          <t>Appalachian Miner</t>
-        </is>
-      </c>
-      <c r="C210" s="32" t="inlineStr">
-        <is>
-          <t>ARC_02_FIRST</t>
-        </is>
-      </c>
-      <c r="D210" s="33" t="inlineStr">
-        <is>
-          <t>[COMMANDER_NAME] — APPALACHIAN MINER FIRST OBJECTIVE</t>
-        </is>
-      </c>
-      <c r="E210" s="34" t="inlineStr">
-        <is>
-          <t>Milestone 1</t>
-        </is>
-      </c>
-      <c r="F210" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G210" s="33" t="inlineStr">
-        <is>
-          <t>ARC_02_DONE</t>
-        </is>
-      </c>
-      <c r="H210" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I210" s="32" t="inlineStr"/>
-      <c r="J210" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K210" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L210" s="32" t="inlineStr"/>
-      <c r="M210" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N210" s="33" t="inlineStr">
-        <is>
-          <t>Fires when ARC_02 completes objective 1; BTN1: nothing</t>
-        </is>
-      </c>
+    <row r="210" ht="8" customHeight="1">
+      <c r="A210" s="9" t="n"/>
+      <c r="B210" s="9" t="n"/>
+      <c r="C210" s="9" t="n"/>
+      <c r="D210" s="9" t="n"/>
+      <c r="E210" s="9" t="n"/>
+      <c r="F210" s="9" t="n"/>
+      <c r="G210" s="9" t="n"/>
+      <c r="H210" s="9" t="n"/>
+      <c r="I210" s="9" t="n"/>
+      <c r="J210" s="9" t="n"/>
+      <c r="K210" s="9" t="n"/>
+      <c r="L210" s="9" t="n"/>
+      <c r="M210" s="9" t="n"/>
+      <c r="N210" s="9" t="n"/>
     </row>
     <row r="211" ht="30" customHeight="1">
       <c r="A211" s="31" t="inlineStr">
@@ -14382,32 +14290,32 @@
       </c>
       <c r="B211" s="31" t="inlineStr">
         <is>
-          <t>Appalachian Miner</t>
+          <t>Wetlands Fisher</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
         <is>
-          <t>ARC_02_DONE</t>
+          <t>ARC_01_FIRST</t>
         </is>
       </c>
       <c r="D211" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — APPALACHIAN MINER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — WETLANDS FISHER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E211" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F211" s="33" t="inlineStr">
         <is>
-          <t>ARC_02_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G211" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_01_DONE</t>
         </is>
       </c>
       <c r="H211" s="26" t="inlineStr">
@@ -14434,7 +14342,7 @@
       </c>
       <c r="N211" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_02 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
+          <t>Fires when ARC_01 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14446,37 +14354,37 @@
       </c>
       <c r="B212" s="31" t="inlineStr">
         <is>
-          <t>Ivy League Dropout</t>
+          <t>Wetlands Fisher</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
         <is>
-          <t>ARC_03_FIRST</t>
+          <t>ARC_01_DONE</t>
         </is>
       </c>
       <c r="D212" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — WETLANDS FISHER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E212" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F212" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_01_FIRST</t>
         </is>
       </c>
       <c r="G212" s="33" t="inlineStr">
         <is>
-          <t>ARC_03_DONE</t>
-        </is>
-      </c>
-      <c r="H212" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H212" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I212" s="32" t="inlineStr"/>
@@ -14498,7 +14406,7 @@
       </c>
       <c r="N212" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_03 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_01 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -14510,37 +14418,37 @@
       </c>
       <c r="B213" s="31" t="inlineStr">
         <is>
-          <t>Ivy League Dropout</t>
+          <t>Appalachian Miner</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
         <is>
-          <t>ARC_03_DONE</t>
+          <t>ARC_02_FIRST</t>
         </is>
       </c>
       <c r="D213" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — APPALACHIAN MINER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E213" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F213" s="33" t="inlineStr">
         <is>
-          <t>ARC_03_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G213" s="33" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H213" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>ARC_02_DONE</t>
+        </is>
+      </c>
+      <c r="H213" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I213" s="32" t="inlineStr"/>
@@ -14562,7 +14470,7 @@
       </c>
       <c r="N213" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_03 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_02 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14574,37 +14482,37 @@
       </c>
       <c r="B214" s="31" t="inlineStr">
         <is>
-          <t>Seminole Fighter</t>
+          <t>Appalachian Miner</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
         <is>
-          <t>ARC_04_FIRST</t>
+          <t>ARC_02_DONE</t>
         </is>
       </c>
       <c r="D214" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — APPALACHIAN MINER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E214" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F214" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_02_FIRST</t>
         </is>
       </c>
       <c r="G214" s="33" t="inlineStr">
         <is>
-          <t>ARC_04_DONE</t>
-        </is>
-      </c>
-      <c r="H214" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H214" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
         </is>
       </c>
       <c r="I214" s="32" t="inlineStr"/>
@@ -14626,7 +14534,7 @@
       </c>
       <c r="N214" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_04 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_02 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
         </is>
       </c>
     </row>
@@ -14638,32 +14546,32 @@
       </c>
       <c r="B215" s="31" t="inlineStr">
         <is>
-          <t>Seminole Fighter</t>
+          <t>Ivy League Dropout</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
         <is>
-          <t>ARC_04_DONE</t>
+          <t>ARC_03_FIRST</t>
         </is>
       </c>
       <c r="D215" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E215" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F215" s="33" t="inlineStr">
         <is>
-          <t>ARC_04_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G215" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_03_DONE</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
@@ -14690,7 +14598,7 @@
       </c>
       <c r="N215" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_04 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
+          <t>Fires when ARC_03 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14702,32 +14610,32 @@
       </c>
       <c r="B216" s="31" t="inlineStr">
         <is>
-          <t>Green Mountain Farmer</t>
+          <t>Ivy League Dropout</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
         <is>
-          <t>ARC_05_FIRST</t>
+          <t>ARC_03_DONE</t>
         </is>
       </c>
       <c r="D216" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — IVY LEAGUE DROPOUT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E216" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F216" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_03_FIRST</t>
         </is>
       </c>
       <c r="G216" s="33" t="inlineStr">
         <is>
-          <t>ARC_05_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
@@ -14754,7 +14662,7 @@
       </c>
       <c r="N216" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_05 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_03 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -14766,32 +14674,32 @@
       </c>
       <c r="B217" s="31" t="inlineStr">
         <is>
-          <t>Green Mountain Farmer</t>
+          <t>Seminole Fighter</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
         <is>
-          <t>ARC_05_DONE</t>
+          <t>ARC_04_FIRST</t>
         </is>
       </c>
       <c r="D217" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E217" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F217" s="33" t="inlineStr">
         <is>
-          <t>ARC_05_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G217" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_04_DONE</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
@@ -14818,7 +14726,7 @@
       </c>
       <c r="N217" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_05 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_04 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14830,32 +14738,32 @@
       </c>
       <c r="B218" s="31" t="inlineStr">
         <is>
-          <t>Chesapeake Shipwright</t>
+          <t>Seminole Fighter</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
         <is>
-          <t>ARC_06_FIRST</t>
+          <t>ARC_04_DONE</t>
         </is>
       </c>
       <c r="D218" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — SEMINOLE FIGHTER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E218" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F218" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_04_FIRST</t>
         </is>
       </c>
       <c r="G218" s="33" t="inlineStr">
         <is>
-          <t>ARC_06_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
@@ -14882,7 +14790,7 @@
       </c>
       <c r="N218" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_06 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_04 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
         </is>
       </c>
     </row>
@@ -14894,32 +14802,32 @@
       </c>
       <c r="B219" s="31" t="inlineStr">
         <is>
-          <t>Chesapeake Shipwright</t>
+          <t>Green Mountain Farmer</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
         <is>
-          <t>ARC_06_DONE</t>
+          <t>ARC_05_FIRST</t>
         </is>
       </c>
       <c r="D219" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E219" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F219" s="33" t="inlineStr">
         <is>
-          <t>ARC_06_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G219" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_05_DONE</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
@@ -14946,7 +14854,7 @@
       </c>
       <c r="N219" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_06 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+          <t>Fires when ARC_05 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -14958,32 +14866,32 @@
       </c>
       <c r="B220" s="31" t="inlineStr">
         <is>
-          <t>Loyalist Turncoat</t>
+          <t>Green Mountain Farmer</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
         <is>
-          <t>ARC_07_FIRST</t>
+          <t>ARC_05_DONE</t>
         </is>
       </c>
       <c r="D220" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — GREEN MOUNTAIN FARMER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E220" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F220" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_05_FIRST</t>
         </is>
       </c>
       <c r="G220" s="33" t="inlineStr">
         <is>
-          <t>ARC_07_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
@@ -15010,7 +14918,7 @@
       </c>
       <c r="N220" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_07 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_05 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -15022,32 +14930,32 @@
       </c>
       <c r="B221" s="31" t="inlineStr">
         <is>
-          <t>Loyalist Turncoat</t>
+          <t>Chesapeake Shipwright</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
         <is>
-          <t>ARC_07_DONE</t>
+          <t>ARC_06_FIRST</t>
         </is>
       </c>
       <c r="D221" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E221" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F221" s="33" t="inlineStr">
         <is>
-          <t>ARC_07_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G221" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_06_DONE</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
@@ -15074,7 +14982,7 @@
       </c>
       <c r="N221" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_07 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_06 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15086,32 +14994,32 @@
       </c>
       <c r="B222" s="31" t="inlineStr">
         <is>
-          <t>Tobacco Belt Drifter</t>
+          <t>Chesapeake Shipwright</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
         <is>
-          <t>ARC_08_FIRST</t>
+          <t>ARC_06_DONE</t>
         </is>
       </c>
       <c r="D222" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — CHESAPEAKE SHIPWRIGHT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E222" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F222" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_06_FIRST</t>
         </is>
       </c>
       <c r="G222" s="33" t="inlineStr">
         <is>
-          <t>ARC_08_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
@@ -15138,7 +15046,7 @@
       </c>
       <c r="N222" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_08 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_06 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
         </is>
       </c>
     </row>
@@ -15150,32 +15058,32 @@
       </c>
       <c r="B223" s="31" t="inlineStr">
         <is>
-          <t>Tobacco Belt Drifter</t>
+          <t>Loyalist Turncoat</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
         <is>
-          <t>ARC_08_DONE</t>
+          <t>ARC_07_FIRST</t>
         </is>
       </c>
       <c r="D223" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E223" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F223" s="33" t="inlineStr">
         <is>
-          <t>ARC_08_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G223" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_07_DONE</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
@@ -15202,7 +15110,7 @@
       </c>
       <c r="N223" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_08 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_07 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15214,32 +15122,32 @@
       </c>
       <c r="B224" s="31" t="inlineStr">
         <is>
-          <t>War Widow</t>
+          <t>Loyalist Turncoat</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
         <is>
-          <t>ARC_09_FIRST</t>
+          <t>ARC_07_DONE</t>
         </is>
       </c>
       <c r="D224" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — WAR WIDOW FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — LOYALIST TURNCOAT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E224" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F224" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_07_FIRST</t>
         </is>
       </c>
       <c r="G224" s="33" t="inlineStr">
         <is>
-          <t>ARC_09_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
@@ -15266,7 +15174,7 @@
       </c>
       <c r="N224" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_09 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_07 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -15278,32 +15186,32 @@
       </c>
       <c r="B225" s="31" t="inlineStr">
         <is>
-          <t>War Widow</t>
+          <t>Tobacco Belt Drifter</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
         <is>
-          <t>ARC_09_DONE</t>
+          <t>ARC_08_FIRST</t>
         </is>
       </c>
       <c r="D225" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — WAR WIDOW ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E225" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F225" s="33" t="inlineStr">
         <is>
-          <t>ARC_09_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G225" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_08_DONE</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
@@ -15330,7 +15238,7 @@
       </c>
       <c r="N225" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_09 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_08 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15342,32 +15250,32 @@
       </c>
       <c r="B226" s="31" t="inlineStr">
         <is>
-          <t>Indigenous Scout</t>
+          <t>Tobacco Belt Drifter</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
         <is>
-          <t>ARC_10_FIRST</t>
+          <t>ARC_08_DONE</t>
         </is>
       </c>
       <c r="D226" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — TOBACCO BELT DRIFTER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E226" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F226" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_08_FIRST</t>
         </is>
       </c>
       <c r="G226" s="33" t="inlineStr">
         <is>
-          <t>ARC_10_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
@@ -15394,7 +15302,7 @@
       </c>
       <c r="N226" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_10 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_08 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -15406,32 +15314,32 @@
       </c>
       <c r="B227" s="31" t="inlineStr">
         <is>
-          <t>Indigenous Scout</t>
+          <t>War Widow</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
         <is>
-          <t>ARC_10_DONE</t>
+          <t>ARC_09_FIRST</t>
         </is>
       </c>
       <c r="D227" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — WAR WIDOW FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E227" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F227" s="33" t="inlineStr">
         <is>
-          <t>ARC_10_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G227" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_09_DONE</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
@@ -15458,7 +15366,7 @@
       </c>
       <c r="N227" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_10 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+          <t>Fires when ARC_09 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15470,32 +15378,32 @@
       </c>
       <c r="B228" s="31" t="inlineStr">
         <is>
-          <t>Boston Rabble-Rouser</t>
+          <t>War Widow</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
         <is>
-          <t>ARC_11_FIRST</t>
+          <t>ARC_09_DONE</t>
         </is>
       </c>
       <c r="D228" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — WAR WIDOW ARC COMPLETE</t>
         </is>
       </c>
       <c r="E228" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F228" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_09_FIRST</t>
         </is>
       </c>
       <c r="G228" s="33" t="inlineStr">
         <is>
-          <t>ARC_11_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
@@ -15522,7 +15430,7 @@
       </c>
       <c r="N228" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_11 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_09 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -15534,32 +15442,32 @@
       </c>
       <c r="B229" s="31" t="inlineStr">
         <is>
-          <t>Boston Rabble-Rouser</t>
+          <t>Indigenous Scout</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
         <is>
-          <t>ARC_11_DONE</t>
+          <t>ARC_10_FIRST</t>
         </is>
       </c>
       <c r="D229" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E229" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F229" s="33" t="inlineStr">
         <is>
-          <t>ARC_11_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G229" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_10_DONE</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
@@ -15586,7 +15494,7 @@
       </c>
       <c r="N229" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_11 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires when ARC_10 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15598,32 +15506,32 @@
       </c>
       <c r="B230" s="31" t="inlineStr">
         <is>
-          <t>Continental Surgeon</t>
+          <t>Indigenous Scout</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
         <is>
-          <t>ARC_12_FIRST</t>
+          <t>ARC_10_DONE</t>
         </is>
       </c>
       <c r="D230" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — INDIGENOUS SCOUT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E230" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F230" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_10_FIRST</t>
         </is>
       </c>
       <c r="G230" s="33" t="inlineStr">
         <is>
-          <t>ARC_12_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
@@ -15650,7 +15558,7 @@
       </c>
       <c r="N230" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_12 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_10 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
         </is>
       </c>
     </row>
@@ -15662,32 +15570,32 @@
       </c>
       <c r="B231" s="31" t="inlineStr">
         <is>
-          <t>Continental Surgeon</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
         <is>
-          <t>ARC_12_DONE</t>
+          <t>ARC_11_FIRST</t>
         </is>
       </c>
       <c r="D231" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E231" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F231" s="33" t="inlineStr">
         <is>
-          <t>ARC_12_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G231" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_11_DONE</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
@@ -15714,7 +15622,7 @@
       </c>
       <c r="N231" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_12 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_11 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15726,32 +15634,32 @@
       </c>
       <c r="B232" s="31" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
         <is>
-          <t>ARC_13_FIRST</t>
+          <t>ARC_11_DONE</t>
         </is>
       </c>
       <c r="D232" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — NANTUCKET SAILOR FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — BOSTON RABBLE-ROUSER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E232" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F232" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_11_FIRST</t>
         </is>
       </c>
       <c r="G232" s="33" t="inlineStr">
         <is>
-          <t>ARC_13_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
@@ -15778,7 +15686,7 @@
       </c>
       <c r="N232" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_13 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_11 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
         </is>
       </c>
     </row>
@@ -15790,32 +15698,32 @@
       </c>
       <c r="B233" s="31" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
         <is>
-          <t>ARC_13_DONE</t>
+          <t>ARC_12_FIRST</t>
         </is>
       </c>
       <c r="D233" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — NANTUCKET SAILOR ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E233" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F233" s="33" t="inlineStr">
         <is>
-          <t>ARC_13_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G233" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_12_DONE</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
@@ -15842,7 +15750,7 @@
       </c>
       <c r="N233" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_13 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_12 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15854,32 +15762,32 @@
       </c>
       <c r="B234" s="31" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
         <is>
-          <t>ARC_14_FIRST</t>
+          <t>ARC_12_DONE</t>
         </is>
       </c>
       <c r="D234" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — FRONTIER PREACHER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — CONTINENTAL SURGEON ARC COMPLETE</t>
         </is>
       </c>
       <c r="E234" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F234" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_12_FIRST</t>
         </is>
       </c>
       <c r="G234" s="33" t="inlineStr">
         <is>
-          <t>ARC_14_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H234" s="6" t="inlineStr">
@@ -15906,7 +15814,7 @@
       </c>
       <c r="N234" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_14 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_12 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -15918,32 +15826,32 @@
       </c>
       <c r="B235" s="31" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
         <is>
-          <t>ARC_14_DONE</t>
+          <t>ARC_13_FIRST</t>
         </is>
       </c>
       <c r="D235" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — FRONTIER PREACHER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — NANTUCKET SAILOR FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E235" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F235" s="33" t="inlineStr">
         <is>
-          <t>ARC_14_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G235" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_13_DONE</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
@@ -15970,7 +15878,7 @@
       </c>
       <c r="N235" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_14 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires when ARC_13 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -15982,32 +15890,32 @@
       </c>
       <c r="B236" s="31" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
         <is>
-          <t>ARC_15_FIRST</t>
+          <t>ARC_13_DONE</t>
         </is>
       </c>
       <c r="D236" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — DC BUREAUCRAT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — NANTUCKET SAILOR ARC COMPLETE</t>
         </is>
       </c>
       <c r="E236" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F236" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_13_FIRST</t>
         </is>
       </c>
       <c r="G236" s="33" t="inlineStr">
         <is>
-          <t>ARC_15_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H236" s="6" t="inlineStr">
@@ -16034,7 +15942,7 @@
       </c>
       <c r="N236" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_15 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_13 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -16046,32 +15954,32 @@
       </c>
       <c r="B237" s="31" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
         <is>
-          <t>ARC_15_DONE</t>
+          <t>ARC_14_FIRST</t>
         </is>
       </c>
       <c r="D237" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — DC BUREAUCRAT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — FRONTIER PREACHER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E237" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F237" s="33" t="inlineStr">
         <is>
-          <t>ARC_15_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G237" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_14_DONE</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
@@ -16098,7 +16006,7 @@
       </c>
       <c r="N237" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_15 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_14 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16110,32 +16018,32 @@
       </c>
       <c r="B238" s="31" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
         <is>
-          <t>ARC_16_FIRST</t>
+          <t>ARC_14_DONE</t>
         </is>
       </c>
       <c r="D238" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — FRONTIER PREACHER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E238" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F238" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_14_FIRST</t>
         </is>
       </c>
       <c r="G238" s="33" t="inlineStr">
         <is>
-          <t>ARC_16_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
@@ -16162,7 +16070,7 @@
       </c>
       <c r="N238" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_16 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_14 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
         </is>
       </c>
     </row>
@@ -16174,32 +16082,32 @@
       </c>
       <c r="B239" s="31" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
         <is>
-          <t>ARC_16_DONE</t>
+          <t>ARC_15_FIRST</t>
         </is>
       </c>
       <c r="D239" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — DC BUREAUCRAT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E239" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F239" s="33" t="inlineStr">
         <is>
-          <t>ARC_16_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G239" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_15_DONE</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
@@ -16226,7 +16134,7 @@
       </c>
       <c r="N239" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_16 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
+          <t>Fires when ARC_15 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16238,32 +16146,32 @@
       </c>
       <c r="B240" s="31" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
         <is>
-          <t>ARC_17_FIRST</t>
+          <t>ARC_15_DONE</t>
         </is>
       </c>
       <c r="D240" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — PLANTATION DESERTER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — DC BUREAUCRAT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E240" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F240" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_15_FIRST</t>
         </is>
       </c>
       <c r="G240" s="33" t="inlineStr">
         <is>
-          <t>ARC_17_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
@@ -16290,7 +16198,7 @@
       </c>
       <c r="N240" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_17 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_15 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -16302,32 +16210,32 @@
       </c>
       <c r="B241" s="31" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
         <is>
-          <t>ARC_17_DONE</t>
+          <t>ARC_16_FIRST</t>
         </is>
       </c>
       <c r="D241" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — PLANTATION DESERTER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E241" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F241" s="33" t="inlineStr">
         <is>
-          <t>ARC_17_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G241" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_16_DONE</t>
         </is>
       </c>
       <c r="H241" s="6" t="inlineStr">
@@ -16354,7 +16262,7 @@
       </c>
       <c r="N241" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_17 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
+          <t>Fires when ARC_16 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16366,32 +16274,32 @@
       </c>
       <c r="B242" s="31" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
         <is>
-          <t>ARC_18_FIRST</t>
+          <t>ARC_16_DONE</t>
         </is>
       </c>
       <c r="D242" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — SWAMP WITCH FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — RUST BELT STEELWORKER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E242" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F242" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_16_FIRST</t>
         </is>
       </c>
       <c r="G242" s="33" t="inlineStr">
         <is>
-          <t>ARC_18_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
@@ -16418,7 +16326,7 @@
       </c>
       <c r="N242" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_18 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_16 completes all 3 objectives; BTN1: morale+20, BTN2: metal</t>
         </is>
       </c>
     </row>
@@ -16430,32 +16338,32 @@
       </c>
       <c r="B243" s="31" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
         <is>
-          <t>ARC_18_DONE</t>
+          <t>ARC_17_FIRST</t>
         </is>
       </c>
       <c r="D243" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — SWAMP WITCH ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — PLANTATION DESERTER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E243" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F243" s="33" t="inlineStr">
         <is>
-          <t>ARC_18_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G243" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_17_DONE</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
@@ -16482,7 +16390,7 @@
       </c>
       <c r="N243" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_18 completes all 3 objectives; BTN1: morale+20, BTN2: magic</t>
+          <t>Fires when ARC_17 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16494,32 +16402,32 @@
       </c>
       <c r="B244" s="31" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
         <is>
-          <t>ARC_19_FIRST</t>
+          <t>ARC_17_DONE</t>
         </is>
       </c>
       <c r="D244" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — PLANTATION DESERTER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E244" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F244" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_17_FIRST</t>
         </is>
       </c>
       <c r="G244" s="33" t="inlineStr">
         <is>
-          <t>ARC_19_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H244" s="6" t="inlineStr">
@@ -16546,7 +16454,7 @@
       </c>
       <c r="N244" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_19 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_17 completes all 3 objectives; BTN1: morale+20, BTN2: food</t>
         </is>
       </c>
     </row>
@@ -16558,32 +16466,32 @@
       </c>
       <c r="B245" s="31" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
         <is>
-          <t>ARC_19_DONE</t>
+          <t>ARC_18_FIRST</t>
         </is>
       </c>
       <c r="D245" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — SWAMP WITCH FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E245" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F245" s="33" t="inlineStr">
         <is>
-          <t>ARC_19_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G245" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_18_DONE</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
@@ -16610,7 +16518,7 @@
       </c>
       <c r="N245" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_19 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_18 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16622,32 +16530,32 @@
       </c>
       <c r="B246" s="31" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
         <is>
-          <t>ARC_21_FIRST</t>
+          <t>ARC_18_DONE</t>
         </is>
       </c>
       <c r="D246" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BORDER MERCENARY FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — SWAMP WITCH ARC COMPLETE</t>
         </is>
       </c>
       <c r="E246" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F246" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_18_FIRST</t>
         </is>
       </c>
       <c r="G246" s="33" t="inlineStr">
         <is>
-          <t>ARC_21_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
@@ -16674,7 +16582,7 @@
       </c>
       <c r="N246" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_21 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_18 completes all 3 objectives; BTN1: morale+20, BTN2: magic</t>
         </is>
       </c>
     </row>
@@ -16686,32 +16594,32 @@
       </c>
       <c r="B247" s="31" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
         <is>
-          <t>ARC_21_DONE</t>
+          <t>ARC_19_FIRST</t>
         </is>
       </c>
       <c r="D247" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — BORDER MERCENARY ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E247" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F247" s="33" t="inlineStr">
         <is>
-          <t>ARC_21_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G247" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_19_DONE</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
@@ -16738,7 +16646,7 @@
       </c>
       <c r="N247" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_21 completes all 3 objectives; BTN1: morale+20, BTN2: weapons</t>
+          <t>Fires when ARC_19 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16750,32 +16658,32 @@
       </c>
       <c r="B248" s="31" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
         <is>
-          <t>ARC_22_FIRST</t>
+          <t>ARC_19_DONE</t>
         </is>
       </c>
       <c r="D248" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — CARIBBEAN PRIVATEER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E248" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F248" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_19_FIRST</t>
         </is>
       </c>
       <c r="G248" s="33" t="inlineStr">
         <is>
-          <t>ARC_22_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H248" s="6" t="inlineStr">
@@ -16802,7 +16710,7 @@
       </c>
       <c r="N248" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_22 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_19 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
         </is>
       </c>
     </row>
@@ -16814,32 +16722,32 @@
       </c>
       <c r="B249" s="31" t="inlineStr">
         <is>
-          <t>Acadian Forest Ranger</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
         <is>
-          <t>ARC_22_DONE</t>
+          <t>ARC_21_FIRST</t>
         </is>
       </c>
       <c r="D249" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — BORDER MERCENARY FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E249" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F249" s="33" t="inlineStr">
         <is>
-          <t>ARC_22_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G249" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_21_DONE</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
@@ -16866,7 +16774,7 @@
       </c>
       <c r="N249" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_22 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
+          <t>Fires when ARC_21 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -16878,32 +16786,32 @@
       </c>
       <c r="B250" s="31" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
         <is>
-          <t>ARC_23_FIRST</t>
+          <t>ARC_21_DONE</t>
         </is>
       </c>
       <c r="D250" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — BORDER MERCENARY ARC COMPLETE</t>
         </is>
       </c>
       <c r="E250" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F250" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_21_FIRST</t>
         </is>
       </c>
       <c r="G250" s="33" t="inlineStr">
         <is>
-          <t>ARC_23_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H250" s="6" t="inlineStr">
@@ -16930,7 +16838,7 @@
       </c>
       <c r="N250" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_23 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_21 completes all 3 objectives; BTN1: morale+20, BTN2: weapons</t>
         </is>
       </c>
     </row>
@@ -16942,32 +16850,32 @@
       </c>
       <c r="B251" s="31" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
         <is>
-          <t>ARC_23_DONE</t>
+          <t>ARC_22_FIRST</t>
         </is>
       </c>
       <c r="D251" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E251" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F251" s="33" t="inlineStr">
         <is>
-          <t>ARC_23_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G251" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_22_DONE</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
@@ -16994,7 +16902,7 @@
       </c>
       <c r="N251" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_23 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
+          <t>Fires when ARC_22 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -17006,32 +16914,32 @@
       </c>
       <c r="B252" s="31" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
         <is>
-          <t>ARC_24_FIRST</t>
+          <t>ARC_22_DONE</t>
         </is>
       </c>
       <c r="D252" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — ACADIAN FOREST RANGER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E252" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F252" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_22_FIRST</t>
         </is>
       </c>
       <c r="G252" s="33" t="inlineStr">
         <is>
-          <t>ARC_24_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H252" s="6" t="inlineStr">
@@ -17058,7 +16966,7 @@
       </c>
       <c r="N252" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_24 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_22 completes all 3 objectives; BTN1: morale+20, BTN2: wood</t>
         </is>
       </c>
     </row>
@@ -17070,32 +16978,32 @@
       </c>
       <c r="B253" s="31" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
         <is>
-          <t>ARC_24_DONE</t>
+          <t>ARC_23_FIRST</t>
         </is>
       </c>
       <c r="D253" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E253" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F253" s="33" t="inlineStr">
         <is>
-          <t>ARC_24_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G253" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_23_DONE</t>
         </is>
       </c>
       <c r="H253" s="6" t="inlineStr">
@@ -17122,7 +17030,7 @@
       </c>
       <c r="N253" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_24 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
+          <t>Fires when ARC_23 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -17134,32 +17042,32 @@
       </c>
       <c r="B254" s="31" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
         <is>
-          <t>ARC_25_FIRST</t>
+          <t>ARC_23_DONE</t>
         </is>
       </c>
       <c r="D254" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARNIVAL BARKER FIRST OBJECTIVE</t>
+          <t>[COMMANDER_NAME] — GETTYSBURG DESCENDANT ARC COMPLETE</t>
         </is>
       </c>
       <c r="E254" s="34" t="inlineStr">
         <is>
-          <t>Milestone 1</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F254" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_23_FIRST</t>
         </is>
       </c>
       <c r="G254" s="33" t="inlineStr">
         <is>
-          <t>ARC_25_DONE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr">
@@ -17186,7 +17094,7 @@
       </c>
       <c r="N254" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_25 completes objective 1; BTN1: nothing</t>
+          <t>Fires when ARC_23 completes all 3 objectives; BTN1: morale+20, BTN2: manpower</t>
         </is>
       </c>
     </row>
@@ -17198,32 +17106,32 @@
       </c>
       <c r="B255" s="31" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
         <is>
-          <t>ARC_25_DONE</t>
+          <t>ARC_24_FIRST</t>
         </is>
       </c>
       <c r="D255" s="33" t="inlineStr">
         <is>
-          <t>[COMMANDER_NAME] — CARNIVAL BARKER ARC COMPLETE</t>
+          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E255" s="34" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F255" s="33" t="inlineStr">
         <is>
-          <t>ARC_25_FIRST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G255" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_24_DONE</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr">
@@ -17250,7 +17158,7 @@
       </c>
       <c r="N255" s="33" t="inlineStr">
         <is>
-          <t>Fires when ARC_25 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+          <t>Fires when ARC_24 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -17262,27 +17170,27 @@
       </c>
       <c r="B256" s="31" t="inlineStr">
         <is>
-          <t>Governor Ceremony</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
         <is>
-          <t>GOV_LVL2_HONOR</t>
+          <t>ARC_24_DONE</t>
         </is>
       </c>
       <c r="D256" s="33" t="inlineStr">
         <is>
-          <t>FIELD CITATION — [COMMANDER_NAME]</t>
+          <t>[COMMANDER_NAME] — LGBTQ+ ORGANIZER ARC COMPLETE</t>
         </is>
       </c>
       <c r="E256" s="34" t="inlineStr">
         <is>
-          <t>Level-Up</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="F256" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ARC_24_FIRST</t>
         </is>
       </c>
       <c r="G256" s="33" t="inlineStr">
@@ -17290,15 +17198,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H256" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
+      <c r="H256" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
         </is>
       </c>
       <c r="I256" s="32" t="inlineStr"/>
-      <c r="J256" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J256" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K256" s="34" t="inlineStr">
@@ -17314,7 +17222,7 @@
       </c>
       <c r="N256" s="33" t="inlineStr">
         <is>
-          <t>Fires on promote_commander to lvl 2; BTN1: morale+10</t>
+          <t>Fires when ARC_24 completes all 3 objectives; BTN1: morale+20, BTN2: culture</t>
         </is>
       </c>
     </row>
@@ -17326,22 +17234,22 @@
       </c>
       <c r="B257" s="31" t="inlineStr">
         <is>
-          <t>Governor Ceremony</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
         <is>
-          <t>GOV_LVL3_CEREMONY</t>
+          <t>ARC_25_FIRST</t>
         </is>
       </c>
       <c r="D257" s="33" t="inlineStr">
         <is>
-          <t>GENERAL [COMMANDER_NAME] — WHITE HOUSE RECOGNITION CEREMONY</t>
+          <t>[COMMANDER_NAME] — CARNIVAL BARKER FIRST OBJECTIVE</t>
         </is>
       </c>
       <c r="E257" s="34" t="inlineStr">
         <is>
-          <t>Level-Up</t>
+          <t>Milestone 1</t>
         </is>
       </c>
       <c r="F257" s="33" t="inlineStr">
@@ -17351,22 +17259,18 @@
       </c>
       <c r="G257" s="33" t="inlineStr">
         <is>
-          <t>GOV_REWARD</t>
-        </is>
-      </c>
-      <c r="H257" s="26" t="inlineStr">
-        <is>
-          <t>FULL COMPLETION</t>
-        </is>
-      </c>
-      <c r="I257" s="32" t="inlineStr">
-        <is>
-          <t>gov_lvl3_ceremony_scene</t>
-        </is>
-      </c>
-      <c r="J257" s="27" t="inlineStr">
-        <is>
-          <t>Integrated</t>
+          <t>ARC_25_DONE</t>
+        </is>
+      </c>
+      <c r="H257" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I257" s="32" t="inlineStr"/>
+      <c r="J257" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K257" s="34" t="inlineStr">
@@ -17382,7 +17286,7 @@
       </c>
       <c r="N257" s="33" t="inlineStr">
         <is>
-          <t>Fires on promote_commander to lvl 3; BTN1: morale+20; BTN2: → GOV_REWARD</t>
+          <t>Fires when ARC_25 completes objective 1; BTN1: nothing</t>
         </is>
       </c>
     </row>
@@ -17394,373 +17298,365 @@
       </c>
       <c r="B258" s="31" t="inlineStr">
         <is>
+          <t>Carnival Barker</t>
+        </is>
+      </c>
+      <c r="C258" s="32" t="inlineStr">
+        <is>
+          <t>ARC_25_DONE</t>
+        </is>
+      </c>
+      <c r="D258" s="33" t="inlineStr">
+        <is>
+          <t>[COMMANDER_NAME] — CARNIVAL BARKER ARC COMPLETE</t>
+        </is>
+      </c>
+      <c r="E258" s="34" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+      <c r="F258" s="33" t="inlineStr">
+        <is>
+          <t>ARC_25_FIRST</t>
+        </is>
+      </c>
+      <c r="G258" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I258" s="32" t="inlineStr"/>
+      <c r="J258" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K258" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L258" s="32" t="inlineStr"/>
+      <c r="M258" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N258" s="33" t="inlineStr">
+        <is>
+          <t>Fires when ARC_25 completes all 3 objectives; BTN1: morale+20, BTN2: gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="30" customHeight="1">
+      <c r="A259" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B259" s="31" t="inlineStr">
+        <is>
           <t>Governor Ceremony</t>
         </is>
       </c>
-      <c r="C258" s="32" t="inlineStr">
+      <c r="C259" s="32" t="inlineStr">
+        <is>
+          <t>GOV_LVL2_HONOR</t>
+        </is>
+      </c>
+      <c r="D259" s="33" t="inlineStr">
+        <is>
+          <t>FIELD CITATION — [COMMANDER_NAME]</t>
+        </is>
+      </c>
+      <c r="E259" s="34" t="inlineStr">
+        <is>
+          <t>Level-Up</t>
+        </is>
+      </c>
+      <c r="F259" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G259" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H259" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I259" s="32" t="inlineStr"/>
+      <c r="J259" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K259" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L259" s="32" t="inlineStr"/>
+      <c r="M259" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N259" s="33" t="inlineStr">
+        <is>
+          <t>Fires on promote_commander to lvl 2; BTN1: morale+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B260" s="31" t="inlineStr">
+        <is>
+          <t>Governor Ceremony</t>
+        </is>
+      </c>
+      <c r="C260" s="32" t="inlineStr">
+        <is>
+          <t>GOV_LVL3_CEREMONY</t>
+        </is>
+      </c>
+      <c r="D260" s="33" t="inlineStr">
+        <is>
+          <t>GENERAL [COMMANDER_NAME] — WHITE HOUSE RECOGNITION CEREMONY</t>
+        </is>
+      </c>
+      <c r="E260" s="34" t="inlineStr">
+        <is>
+          <t>Level-Up</t>
+        </is>
+      </c>
+      <c r="F260" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="33" t="inlineStr">
         <is>
           <t>GOV_REWARD</t>
         </is>
       </c>
-      <c r="D258" s="33" t="inlineStr">
+      <c r="H260" s="26" t="inlineStr">
+        <is>
+          <t>FULL COMPLETION</t>
+        </is>
+      </c>
+      <c r="I260" s="32" t="inlineStr">
+        <is>
+          <t>gov_lvl3_ceremony_scene</t>
+        </is>
+      </c>
+      <c r="J260" s="27" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="K260" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L260" s="32" t="inlineStr"/>
+      <c r="M260" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N260" s="33" t="inlineStr">
+        <is>
+          <t>Fires on promote_commander to lvl 3; BTN1: morale+20; BTN2: → GOV_REWARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="31" t="inlineStr">
+        <is>
+          <t>Commander</t>
+        </is>
+      </c>
+      <c r="B261" s="31" t="inlineStr">
+        <is>
+          <t>Governor Ceremony</t>
+        </is>
+      </c>
+      <c r="C261" s="32" t="inlineStr">
+        <is>
+          <t>GOV_REWARD</t>
+        </is>
+      </c>
+      <c r="D261" s="33" t="inlineStr">
         <is>
           <t>GENERAL [COMMANDER_NAME] — THE LINCOLN BEDROOM</t>
         </is>
       </c>
-      <c r="E258" s="34" t="inlineStr">
+      <c r="E261" s="34" t="inlineStr">
         <is>
           <t>Intimate</t>
         </is>
       </c>
-      <c r="F258" s="33" t="inlineStr">
+      <c r="F261" s="33" t="inlineStr">
         <is>
           <t>GOV_LVL3_CEREMONY BTN2</t>
         </is>
       </c>
-      <c r="G258" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H258" s="26" t="inlineStr">
+      <c r="G261" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H261" s="26" t="inlineStr">
         <is>
           <t>FULL COMPLETION</t>
         </is>
       </c>
-      <c r="I258" s="32" t="inlineStr">
+      <c r="I261" s="32" t="inlineStr">
         <is>
           <t>gov_reward_scene</t>
         </is>
       </c>
-      <c r="J258" s="27" t="inlineStr">
+      <c r="J261" s="27" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
       </c>
-      <c r="K258" s="28" t="inlineStr">
+      <c r="K261" s="28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L258" s="32" t="inlineStr">
+      <c r="L261" s="32" t="inlineStr">
         <is>
           <t>intimate</t>
         </is>
       </c>
-      <c r="M258" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N258" s="33" t="inlineStr">
+      <c r="M261" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N261" s="33" t="inlineStr">
         <is>
           <t>Fires from GOV_LVL3_CEREMONY BTN2; BTN1: governor_loyalty +3</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="8" customHeight="1">
-      <c r="A259" s="9" t="n"/>
-      <c r="B259" s="9" t="n"/>
-      <c r="C259" s="9" t="n"/>
-      <c r="D259" s="9" t="n"/>
-      <c r="E259" s="9" t="n"/>
-      <c r="F259" s="9" t="n"/>
-      <c r="G259" s="9" t="n"/>
-      <c r="H259" s="9" t="n"/>
-      <c r="I259" s="9" t="n"/>
-      <c r="J259" s="9" t="n"/>
-      <c r="K259" s="9" t="n"/>
-      <c r="L259" s="9" t="n"/>
-      <c r="M259" s="9" t="n"/>
-      <c r="N259" s="9" t="n"/>
-    </row>
-    <row r="260" ht="30" customHeight="1">
-      <c r="A260" s="51" t="inlineStr">
+    <row r="262" ht="8" customHeight="1">
+      <c r="A262" s="9" t="n"/>
+      <c r="B262" s="9" t="n"/>
+      <c r="C262" s="9" t="n"/>
+      <c r="D262" s="9" t="n"/>
+      <c r="E262" s="9" t="n"/>
+      <c r="F262" s="9" t="n"/>
+      <c r="G262" s="9" t="n"/>
+      <c r="H262" s="9" t="n"/>
+      <c r="I262" s="9" t="n"/>
+      <c r="J262" s="9" t="n"/>
+      <c r="K262" s="9" t="n"/>
+      <c r="L262" s="9" t="n"/>
+      <c r="M262" s="9" t="n"/>
+      <c r="N262" s="9" t="n"/>
+    </row>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="51" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="B260" s="51" t="inlineStr">
+      <c r="B263" s="51" t="inlineStr">
         <is>
           <t>VP Arc</t>
         </is>
       </c>
-      <c r="C260" s="52" t="inlineStr">
+      <c r="C263" s="52" t="inlineStr">
         <is>
           <t>VP_LEGACY</t>
         </is>
       </c>
-      <c r="D260" s="53" t="inlineStr">
+      <c r="D263" s="53" t="inlineStr">
         <is>
           <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
         </is>
       </c>
-      <c r="E260" s="22" t="inlineStr">
+      <c r="E263" s="22" t="inlineStr">
         <is>
           <t>Followup</t>
         </is>
       </c>
-      <c r="F260" s="53" t="inlineStr">
+      <c r="F263" s="53" t="inlineStr">
         <is>
           <t>VP_FIRST_MEETING (turn 96+)</t>
         </is>
       </c>
-      <c r="G260" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H260" s="6" t="inlineStr">
+      <c r="G263" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr">
         <is>
           <t>FIRST PASS</t>
         </is>
       </c>
-      <c r="I260" s="52" t="inlineStr"/>
-      <c r="J260" s="7" t="inlineStr">
+      <c r="I263" s="52" t="inlineStr"/>
+      <c r="J263" s="7" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K260" s="28" t="inlineStr">
+      <c r="K263" s="28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L260" s="52" t="inlineStr">
+      <c r="L263" s="52" t="inlineStr">
         <is>
           <t>explicit option</t>
         </is>
       </c>
-      <c r="M260" s="54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N260" s="53" t="inlineStr">
+      <c r="M263" s="54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N263" s="53" t="inlineStr">
         <is>
           <t>Fires turn 96+; BTN1 claim +1 / BTN2 explicit morale +30</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="8" customHeight="1">
-      <c r="A261" s="9" t="n"/>
-      <c r="B261" s="9" t="n"/>
-      <c r="C261" s="9" t="n"/>
-      <c r="D261" s="9" t="n"/>
-      <c r="E261" s="9" t="n"/>
-      <c r="F261" s="9" t="n"/>
-      <c r="G261" s="9" t="n"/>
-      <c r="H261" s="9" t="n"/>
-      <c r="I261" s="9" t="n"/>
-      <c r="J261" s="9" t="n"/>
-      <c r="K261" s="9" t="n"/>
-      <c r="L261" s="9" t="n"/>
-      <c r="M261" s="9" t="n"/>
-      <c r="N261" s="9" t="n"/>
-    </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="72" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B262" s="72" t="inlineStr">
-        <is>
-          <t>Month 1</t>
-        </is>
-      </c>
-      <c r="C262" s="73" t="inlineStr">
-        <is>
-          <t>WH_SECRET_01</t>
-        </is>
-      </c>
-      <c r="D262" s="74" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
-        </is>
-      </c>
-      <c r="E262" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F262" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G262" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H262" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I262" s="73" t="inlineStr"/>
-      <c r="J262" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K262" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L262" s="73" t="inlineStr">
-        <is>
-          <t>sensual option</t>
-        </is>
-      </c>
-      <c r="M262" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N262" s="74" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="72" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B263" s="72" t="inlineStr">
-        <is>
-          <t>Month 2</t>
-        </is>
-      </c>
-      <c r="C263" s="73" t="inlineStr">
-        <is>
-          <t>WH_SECRET_02</t>
-        </is>
-      </c>
-      <c r="D263" s="74" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F263" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G263" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H263" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I263" s="73" t="inlineStr"/>
-      <c r="J263" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K263" s="75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L263" s="73" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M263" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N263" s="74" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="30" customHeight="1">
-      <c r="A264" s="72" t="inlineStr">
-        <is>
-          <t>White House</t>
-        </is>
-      </c>
-      <c r="B264" s="72" t="inlineStr">
-        <is>
-          <t>Month 3</t>
-        </is>
-      </c>
-      <c r="C264" s="73" t="inlineStr">
-        <is>
-          <t>WH_SECRET_03</t>
-        </is>
-      </c>
-      <c r="D264" s="74" t="inlineStr">
-        <is>
-          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F264" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G264" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H264" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I264" s="73" t="inlineStr"/>
-      <c r="J264" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K264" s="75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L264" s="73" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="M264" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N264" s="74" t="inlineStr">
-        <is>
-          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
-        </is>
-      </c>
+    <row r="264" ht="8" customHeight="1">
+      <c r="A264" s="9" t="n"/>
+      <c r="B264" s="9" t="n"/>
+      <c r="C264" s="9" t="n"/>
+      <c r="D264" s="9" t="n"/>
+      <c r="E264" s="9" t="n"/>
+      <c r="F264" s="9" t="n"/>
+      <c r="G264" s="9" t="n"/>
+      <c r="H264" s="9" t="n"/>
+      <c r="I264" s="9" t="n"/>
+      <c r="J264" s="9" t="n"/>
+      <c r="K264" s="9" t="n"/>
+      <c r="L264" s="9" t="n"/>
+      <c r="M264" s="9" t="n"/>
+      <c r="N264" s="9" t="n"/>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="72" t="inlineStr">
@@ -17770,17 +17666,17 @@
       </c>
       <c r="B265" s="72" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C265" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_04</t>
+          <t>WH_SECRET_01</t>
         </is>
       </c>
       <c r="D265" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
+          <t>WHITE HOUSE SECRET — NEW YEAR'S DAY</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17809,14 +17705,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K265" s="75" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="K265" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="L265" s="73" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>sensual option</t>
         </is>
       </c>
       <c r="M265" s="75" t="inlineStr">
@@ -17826,7 +17722,7 @@
       </c>
       <c r="N265" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 1; one-shot</t>
         </is>
       </c>
     </row>
@@ -17838,17 +17734,17 @@
       </c>
       <c r="B266" s="72" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C266" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_05</t>
+          <t>WH_SECRET_02</t>
         </is>
       </c>
       <c r="D266" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
+          <t>WHITE HOUSE SECRET — PRESIDENT'S DAY</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17894,7 +17790,7 @@
       </c>
       <c r="N266" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 2; one-shot</t>
         </is>
       </c>
     </row>
@@ -17906,17 +17802,17 @@
       </c>
       <c r="B267" s="72" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C267" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_06</t>
+          <t>WH_SECRET_03</t>
         </is>
       </c>
       <c r="D267" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
+          <t>WHITE HOUSE SECRET — CHERRY BLOSSOM SEASON</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17962,7 +17858,7 @@
       </c>
       <c r="N267" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 3; one-shot</t>
         </is>
       </c>
     </row>
@@ -17974,17 +17870,17 @@
       </c>
       <c r="B268" s="72" t="inlineStr">
         <is>
-          <t>Month 7</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C268" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_07</t>
+          <t>WH_SECRET_04</t>
         </is>
       </c>
       <c r="D268" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
+          <t>WHITE HOUSE SECRET — EASTER MORNING</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -18013,14 +17909,14 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K268" s="28" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="K268" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="L268" s="73" t="inlineStr">
         <is>
-          <t>explicit option</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="M268" s="75" t="inlineStr">
@@ -18030,7 +17926,7 @@
       </c>
       <c r="N268" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 4; one-shot</t>
         </is>
       </c>
     </row>
@@ -18042,17 +17938,17 @@
       </c>
       <c r="B269" s="72" t="inlineStr">
         <is>
-          <t>Month 8</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C269" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_08</t>
+          <t>WH_SECRET_05</t>
         </is>
       </c>
       <c r="D269" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — DIWALI</t>
+          <t>WHITE HOUSE SECRET — CINCO DE MAYO</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -18098,7 +17994,7 @@
       </c>
       <c r="N269" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 5; one-shot</t>
         </is>
       </c>
     </row>
@@ -18110,17 +18006,17 @@
       </c>
       <c r="B270" s="72" t="inlineStr">
         <is>
-          <t>Month 9</t>
+          <t>Month 6</t>
         </is>
       </c>
       <c r="C270" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_09</t>
+          <t>WH_SECRET_06</t>
         </is>
       </c>
       <c r="D270" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
+          <t>WHITE HOUSE SECRET — JUNETEENTH</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -18166,7 +18062,7 @@
       </c>
       <c r="N270" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 6; one-shot</t>
         </is>
       </c>
     </row>
@@ -18178,17 +18074,17 @@
       </c>
       <c r="B271" s="72" t="inlineStr">
         <is>
-          <t>Month 10</t>
+          <t>Month 7</t>
         </is>
       </c>
       <c r="C271" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_10</t>
+          <t>WH_SECRET_07</t>
         </is>
       </c>
       <c r="D271" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
+          <t>WHITE HOUSE SECRET — INDEPENDENCE DAY &amp; PRIDE</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -18224,7 +18120,7 @@
       </c>
       <c r="L271" s="73" t="inlineStr">
         <is>
-          <t>sensual option</t>
+          <t>explicit option</t>
         </is>
       </c>
       <c r="M271" s="75" t="inlineStr">
@@ -18234,7 +18130,7 @@
       </c>
       <c r="N271" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 7; one-shot</t>
         </is>
       </c>
     </row>
@@ -18246,17 +18142,17 @@
       </c>
       <c r="B272" s="72" t="inlineStr">
         <is>
-          <t>Month 11</t>
+          <t>Month 8</t>
         </is>
       </c>
       <c r="C272" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_11</t>
+          <t>WH_SECRET_08</t>
         </is>
       </c>
       <c r="D272" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
+          <t>WHITE HOUSE SECRET — DIWALI</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -18302,7 +18198,7 @@
       </c>
       <c r="N272" s="74" t="inlineStr">
         <is>
-          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
+          <t>Fires when Ualani in DC (tile 188) during month 8; one-shot</t>
         </is>
       </c>
     </row>
@@ -18314,17 +18210,17 @@
       </c>
       <c r="B273" s="72" t="inlineStr">
         <is>
-          <t>Month 12</t>
+          <t>Month 9</t>
         </is>
       </c>
       <c r="C273" s="73" t="inlineStr">
         <is>
-          <t>WH_SECRET_12</t>
+          <t>WH_SECRET_09</t>
         </is>
       </c>
       <c r="D273" s="74" t="inlineStr">
         <is>
-          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
+          <t>WHITE HOUSE SECRET — HALLOWEEN</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -18353,234 +18249,246 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K273" s="28" t="inlineStr">
+      <c r="K273" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L273" s="73" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M273" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N273" s="74" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 9; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="30" customHeight="1">
+      <c r="A274" s="72" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B274" s="72" t="inlineStr">
+        <is>
+          <t>Month 10</t>
+        </is>
+      </c>
+      <c r="C274" s="73" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10</t>
+        </is>
+      </c>
+      <c r="D274" s="74" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — INDIGENOUS PEOPLES DAY</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F274" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G274" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I274" s="73" t="inlineStr"/>
+      <c r="J274" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K274" s="28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L273" s="73" t="inlineStr">
+      <c r="L274" s="73" t="inlineStr">
         <is>
           <t>sensual option</t>
         </is>
       </c>
-      <c r="M273" s="75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N273" s="74" t="inlineStr">
+      <c r="M274" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N274" s="74" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 10; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="72" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B275" s="72" t="inlineStr">
+        <is>
+          <t>Month 11</t>
+        </is>
+      </c>
+      <c r="C275" s="73" t="inlineStr">
+        <is>
+          <t>WH_SECRET_11</t>
+        </is>
+      </c>
+      <c r="D275" s="74" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — THANKSGIVING</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F275" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G275" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I275" s="73" t="inlineStr"/>
+      <c r="J275" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K275" s="75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L275" s="73" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="M275" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N275" s="74" t="inlineStr">
+        <is>
+          <t>Fires when Ualani in DC (tile 188) during month 11; one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="72" t="inlineStr">
+        <is>
+          <t>White House</t>
+        </is>
+      </c>
+      <c r="B276" s="72" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="C276" s="73" t="inlineStr">
+        <is>
+          <t>WH_SECRET_12</t>
+        </is>
+      </c>
+      <c r="D276" s="74" t="inlineStr">
+        <is>
+          <t>WHITE HOUSE SECRET — CHRISTMAS</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="F276" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G276" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>FIRST PASS</t>
+        </is>
+      </c>
+      <c r="I276" s="73" t="inlineStr"/>
+      <c r="J276" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K276" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L276" s="73" t="inlineStr">
+        <is>
+          <t>sensual option</t>
+        </is>
+      </c>
+      <c r="M276" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N276" s="74" t="inlineStr">
         <is>
           <t>Fires when Ualani in DC (tile 188) during month 12; one-shot</t>
         </is>
       </c>
     </row>
-    <row r="274" ht="8" customHeight="1">
-      <c r="A274" s="9" t="n"/>
-      <c r="B274" s="9" t="n"/>
-      <c r="C274" s="9" t="n"/>
-      <c r="D274" s="9" t="n"/>
-      <c r="E274" s="9" t="n"/>
-      <c r="F274" s="9" t="n"/>
-      <c r="G274" s="9" t="n"/>
-      <c r="H274" s="9" t="n"/>
-      <c r="I274" s="9" t="n"/>
-      <c r="J274" s="9" t="n"/>
-      <c r="K274" s="9" t="n"/>
-      <c r="L274" s="9" t="n"/>
-      <c r="M274" s="9" t="n"/>
-      <c r="N274" s="9" t="n"/>
-    </row>
-    <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="76" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B275" s="76" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C275" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_SUMMON</t>
-        </is>
-      </c>
-      <c r="D275" s="78" t="inlineStr">
-        <is>
-          <t>CHALCHIUHTOTOLIN ARRIVES AT PLYMOUTH ON THANKSGIVING</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="inlineStr">
-        <is>
-          <t>Root</t>
-        </is>
-      </c>
-      <c r="F275" s="78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G275" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_Q1</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I275" s="77" t="inlineStr"/>
-      <c r="J275" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K275" s="79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L275" s="77" t="inlineStr"/>
-      <c r="M275" s="79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N275" s="78" t="inlineStr">
-        <is>
-          <t>Month 11, Ualani at tile 66 (Plymouth); one-shot; sets chalch_summoned flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="30" customHeight="1">
-      <c r="A276" s="76" t="inlineStr">
-        <is>
-          <t>Chalchiuhtotolin</t>
-        </is>
-      </c>
-      <c r="B276" s="76" t="inlineStr">
-        <is>
-          <t>Jade Turkey Arc</t>
-        </is>
-      </c>
-      <c r="C276" s="77" t="inlineStr">
-        <is>
-          <t>CHALCH_Q1</t>
-        </is>
-      </c>
-      <c r="D276" s="78" t="inlineStr">
-        <is>
-          <t>THE JADE TURKEY DEMANDS THREE GRANARIES</t>
-        </is>
-      </c>
-      <c r="E276" s="79" t="inlineStr">
-        <is>
-          <t>Quest 1</t>
-        </is>
-      </c>
-      <c r="F276" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_SUMMON</t>
-        </is>
-      </c>
-      <c r="G276" s="78" t="inlineStr">
-        <is>
-          <t>CHALCH_Q2</t>
-        </is>
-      </c>
-      <c r="H276" s="6" t="inlineStr">
-        <is>
-          <t>FIRST PASS</t>
-        </is>
-      </c>
-      <c r="I276" s="77" 